--- a/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
+++ b/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R230715d138084e5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="Rd664b083ff704d3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R866b4872e8514e69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R92a7b96f32334fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf98f4412e065401a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="Rfb1c639612d94e0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R2849b7576b5e4946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R386551f8f4aa482b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>325</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>85</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +540,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -3834,28 +3834,784 @@
       </x:c>
     </x:row>
     <x:row r="86" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A86" s="42" t="str"/>
-      <x:c r="B86" s="43" t="str"/>
-      <x:c r="C86" s="43" t="str"/>
-      <x:c r="D86" s="43" t="str"/>
-      <x:c r="E86" s="43" t="str"/>
-      <x:c r="F86" s="43" t="str"/>
-      <x:c r="G86" s="43" t="str"/>
-      <x:c r="H86" s="43" t="str">
+      <x:c r="A86" s="40" t="str"/>
+      <x:c r="B86" s="9" t="str"/>
+      <x:c r="C86" s="9" t="str"/>
+      <x:c r="D86" s="9" t="str"/>
+      <x:c r="E86" s="9" t="str"/>
+      <x:c r="F86" s="9" t="str"/>
+      <x:c r="G86" s="9" t="str"/>
+      <x:c r="H86" s="9" t="str">
         <x:v>BMW dealer locator</x:v>
       </x:c>
-      <x:c r="I86" s="43" t="str">
+      <x:c r="I86" s="9" t="str">
         <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
       </x:c>
-      <x:c r="J86" s="43" t="str">
+      <x:c r="J86" s="9" t="str">
         <x:v>Fuel-pressure diagnosis and campaign-history review</x:v>
       </x:c>
-      <x:c r="K86" s="43" t="str">
+      <x:c r="K86" s="9" t="str">
         <x:v>diagnostic service</x:v>
       </x:c>
-      <x:c r="L86" s="43" t="str"/>
-      <x:c r="M86" s="43" t="str"/>
-      <x:c r="N86" s="44" t="str"/>
+      <x:c r="L86" s="9" t="str"/>
+      <x:c r="M86" s="9" t="str"/>
+      <x:c r="N86" s="41" t="str"/>
+    </x:row>
+    <x:row r="87" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A87" s="40" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B87" s="9" t="str">
+        <x:v>bmw-5-series-n54-wastegate-2008</x:v>
+      </x:c>
+      <x:c r="C87" s="9" t="str">
+        <x:v>2008-2010 | BMW | 5 Series | N54</x:v>
+      </x:c>
+      <x:c r="D87" s="9" t="str">
+        <x:v>535i N54 Wastegate Clanking Requires Turbocharger Diagnosis</x:v>
+      </x:c>
+      <x:c r="E87" s="9" t="str">
+        <x:v>Confirm the exact N54 vehicle and modification history, distinguish normal slight rattle from the defined clanking condition, and follow current BMW diagnostic and repair instructions. The historical eight-year/82,000-mile emissions extension is not a current coverage promise. ShowMeTheParts returned four exact-fitment turbo oil/coolant-line candidates but no wastegate or turbocharger repair candidate, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F87" s="9" t="str">
+        <x:v>Exact N54 vehicle/modification check; distinguish normal slight rattle from bulletin-defined repeated clanking; BMW test plan</x:v>
+      </x:c>
+      <x:c r="G87" s="9" t="str">
+        <x:v>DIAGNOSIS FIRST / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H87" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I87" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J87" s="9" t="str">
+        <x:v>2008-2010 E60/E61 535i and 535i xDrive N54 wastegate/turbocharger diagnosis</x:v>
+      </x:c>
+      <x:c r="K87" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L87" s="9" t="str"/>
+      <x:c r="M87" s="9" t="str">
+        <x:v>The source explicitly says no exact wastegate or turbocharger candidate was found and that slight mechanical rattle is not itself a failure.</x:v>
+      </x:c>
+      <x:c r="N87" s="41" t="str">
+        <x:v>Do not sell a turbocharger, wastegate actuator or scanner from the complaint alone; verify the exact bulletin condition and modification history first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A88" s="40" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B88" s="9" t="str">
+        <x:v>bmw-5-series-n63-oil-consumption-2011</x:v>
+      </x:c>
+      <x:c r="C88" s="9" t="str">
+        <x:v>2010-2013 | BMW | 5 Series | N63</x:v>
+      </x:c>
+      <x:c r="D88" s="9" t="str">
+        <x:v>N63 Low-Oil Warning Requires 550i Oil-Consumption Testing</x:v>
+      </x:c>
+      <x:c r="E88" s="9" t="str">
+        <x:v>Confirm the VIN and service history, record oil additions and service intervals, and have a BMW-qualified technician perform the current oil-consumption test and applicable diagnosis. Historical settlement benefits and the N63 Customer Care Package must not be presented as current coverage. The official material describes multiple checks and condition-dependent repairs, so no single catalog part or retail link is approved.</x:v>
+      </x:c>
+      <x:c r="F88" s="9" t="str">
+        <x:v>VIN/service-history review; documented oil additions and intervals; current BMW oil-consumption measurement and condition-dependent diagnosis</x:v>
+      </x:c>
+      <x:c r="G88" s="9" t="str">
+        <x:v>DIAGNOSIS/SETTLEMENT-HISTORY FIRST / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H88" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I88" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J88" s="9" t="str">
+        <x:v>2010-2013 F10 550i/550i xDrive N63 oil-consumption test and service-history review</x:v>
+      </x:c>
+      <x:c r="K88" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L88" s="9" t="str"/>
+      <x:c r="M88" s="9" t="str">
+        <x:v>The repair path is measurement- and condition-dependent and the historical settlement does not identify one universal failed part.</x:v>
+      </x:c>
+      <x:c r="N88" s="41" t="str">
+        <x:v>Do not present the N63 Customer Care Package or settlement benefits as current coverage and do not preselect valve seals, rings or an engine.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A89" s="40" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B89" s="9" t="str">
+        <x:v>bmw-5-series-n63-timing-chain-2006</x:v>
+      </x:c>
+      <x:c r="C89" s="9" t="str">
+        <x:v>2010-2013 | BMW | 5 Series | N63</x:v>
+      </x:c>
+      <x:c r="D89" s="9" t="str">
+        <x:v>N63 550i Timing-Chain Wear Check</x:v>
+      </x:c>
+      <x:c r="E89" s="9" t="str">
+        <x:v>Confirm the N63 engine, production date and VIN history, resolve stored VANOS or camshaft-position faults first, and have a BMW-qualified technician run the prescribed timing-chain test. Replace both chains only if the approved test reports that the chain is not OK. ShowMeTheParts resolved the exact 2012 550i ENGINE COMPONENTS fitment but returned no timing-chain candidate, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F89" s="9" t="str">
+        <x:v>N63 engine/production-date/VIN confirmation; resolve VANOS/cam-position faults; prescribed timing-chain elongation test; both chains only on failed test</x:v>
+      </x:c>
+      <x:c r="G89" s="9" t="str">
+        <x:v>DIAGNOSIS FIRST / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H89" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I89" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J89" s="9" t="str">
+        <x:v>2010-2013 F10 550i/550i xDrive N63 timing-chain test plan</x:v>
+      </x:c>
+      <x:c r="K89" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L89" s="9" t="str"/>
+      <x:c r="M89" s="9" t="str">
+        <x:v>The How to Fix requires an approved test result and reports no exact timing-chain catalog candidate.</x:v>
+      </x:c>
+      <x:c r="N89" s="41" t="str">
+        <x:v>Correct the issue ID/year metadata to the actual 2010-2013 scope; this is not a recall and no chain kit or scanner is approved before the test.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="1056" hidden="0" customHeight="1">
+      <x:c r="A90" s="40" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B90" s="9" t="str">
+        <x:v>bmw-5-series-oil-leaks-2004</x:v>
+      </x:c>
+      <x:c r="C90" s="9" t="str">
+        <x:v>2004-2023 | BMW | 5 Series</x:v>
+      </x:c>
+      <x:c r="D90" s="9" t="str">
+        <x:v>Valve Cover Gasket &amp; Oil Filter Housing Gasket Leaks</x:v>
+      </x:c>
+      <x:c r="E90" s="9" t="str">
+        <x:v>Replace valve cover gasket ($400-$800 shop, $150-250 DIY parts) and/or oil filter housing gasket ($300-$600 shop, $80-150 DIY parts). Can be done separately or together depending on leak source. Use OEM BMW gaskets or quality German aftermarket (Elring, Victor Reinz brands) - cheap gaskets leak within 20k miles. Both are DIY-friendly for experienced mechanics: VCG takes 2-3 hours, OFHG takes 1-2 hours. YouTube has detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage). Address OFHG leaks EARLY - oil dripping on alternator causes $800+ alternator failure.</x:v>
+      </x:c>
+      <x:c r="F90" s="9" t="str">
+        <x:v>Leak-source diagnosis; engine-specific valve-cover gasket and/or oil-filter-housing gasket; related seals/bolts only as the exact engine procedure requires</x:v>
+      </x:c>
+      <x:c r="G90" s="9" t="str">
+        <x:v>SOURCE SPLIT REQUIRED / NO UNIVERSAL PART</x:v>
+      </x:c>
+      <x:c r="H90" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I90" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J90" s="9" t="str">
+        <x:v>2004-2023 5 Series leak-source and engine identification</x:v>
+      </x:c>
+      <x:c r="K90" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L90" s="9" t="str"/>
+      <x:c r="M90" s="9" t="str">
+        <x:v>The 20-year row has no trims or engines and spans many unrelated gasket designs; a single VCG or OFHG link would be unsafe fitment.</x:v>
+      </x:c>
+      <x:c r="N90" s="41" t="str">
+        <x:v>Split by chassis, trim, engine and gasket location. Remove universal failure, mileage, price and DIY claims unless supported for each split.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="1003.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A91" s="40" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B91" s="9" t="str">
+        <x:v>bmw-5-series-water-pump-2004</x:v>
+      </x:c>
+      <x:c r="C91" s="9" t="str">
+        <x:v>2004-2023 | BMW | 5 Series | N52, N54, N55, N20, N62, N63, B48, B58</x:v>
+      </x:c>
+      <x:c r="D91" s="9" t="str">
+        <x:v>Electric Water Pump Failure (All Engines)</x:v>
+      </x:c>
+      <x:c r="E91" s="9" t="str">
+        <x:v>Replace electric water pump ($600-$1,200 installed). Use OEM BMW or quality German aftermarket (Rein, Hepu brands) - cheap eBay pumps fail within 20k miles. Replace thermostat at same time ($200 additional parts) since labor is 80% done. Flush cooling system and refill with BMW-spec coolant (do NOT use generic green antifreeze - causes corrosion). PREVENTIVE: Replace water pump at 80,000 miles BEFORE failure to avoid being stranded. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps heads ($4,000+ repair). Call tow truck; do not attempt to drive.</x:v>
+      </x:c>
+      <x:c r="F91" s="9" t="str">
+        <x:v>Cooling-system diagnosis; engine-specific pump, thermostat where applicable, correct coolant and bleed procedure</x:v>
+      </x:c>
+      <x:c r="G91" s="9" t="str">
+        <x:v>CONTENT ERROR / ENGINE SPLIT REQUIRED</x:v>
+      </x:c>
+      <x:c r="H91" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I91" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J91" s="9" t="str">
+        <x:v>Identify exact 5 Series engine and pump architecture before ordering</x:v>
+      </x:c>
+      <x:c r="K91" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L91" s="9" t="str"/>
+      <x:c r="M91" s="9" t="str">
+        <x:v>The row incorrectly treats all listed engines and all 2004-2023 5 Series as one electric-water-pump application; pump type, thermostat and procedure vary by engine.</x:v>
+      </x:c>
+      <x:c r="N91" s="41" t="str">
+        <x:v>Split every engine/chassis generation, distinguish mechanical from electric pumps, verify thermostat and coolant requirements, and remove the unsupported universal failure-rate claim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="1056" hidden="0" customHeight="1">
+      <x:c r="A92" s="40" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B92" s="9" t="str">
+        <x:v>bmw-5-series-zf-6hp-mechatronic-2004</x:v>
+      </x:c>
+      <x:c r="C92" s="9" t="str">
+        <x:v>2004-2013 | BMW | 5 Series</x:v>
+      </x:c>
+      <x:c r="D92" s="9" t="str">
+        <x:v>ZF 6HP Transmission Mechatronic Sleeve &amp; Valve Body Failure</x:v>
+      </x:c>
+      <x:c r="E92" s="9" t="str">
+        <x:v>Replace mechatronic sealing sleeves (4 tubes + 1 square seal) and valve body adapter sleeve ($150-300 parts). DIY-friendly with transmission pan drop and valve body removal (4-6 hours, detailed guides on Bimmerfest). While valve body is out, replace transmission fluid/filter and clean solenoids ($200 additional). Dealer charges $1,500-2,500 for this repair; DIY costs $400-700 total. PREVENTIVE: Change transmission fluid every 50,000 miles (NOT "lifetime") with BMW-spec fluid (Pentosin/ZF Lifeguard 6). Fluid changes prevent 90% of ZF 6HP problems. If ignored, worn mechatronic destroys clutches requiring $5,000+ transmission rebuild.</x:v>
+      </x:c>
+      <x:c r="F92" s="9" t="str">
+        <x:v>Transmission-code and symptom diagnosis; exact 6HP sealing sleeves/bridge seal; transmission-specific pan/filter and approved fluid; valve-body work only if confirmed</x:v>
+      </x:c>
+      <x:c r="G92" s="9" t="str">
+        <x:v>TRANSMISSION SPLIT REQUIRED / NO UNIVERSAL KIT</x:v>
+      </x:c>
+      <x:c r="H92" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I92" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J92" s="9" t="str">
+        <x:v>2004-2013 5 Series transmission identification and hydraulic diagnosis</x:v>
+      </x:c>
+      <x:c r="K92" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L92" s="9" t="str"/>
+      <x:c r="M92" s="9" t="str">
+        <x:v>The row omits trim, engine, transmission variant and production split, so the sealing kit, pan/filter and fluid cannot be fit safely from YMM alone.</x:v>
+      </x:c>
+      <x:c r="N92" s="41" t="str">
+        <x:v>Split by exact ZF transmission code and VIN; do not claim every high-mileage 6HP has the same failure or that fluid changes prevent 90% of problems.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="594" hidden="0" customHeight="1">
+      <x:c r="A93" s="40" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B93" s="9" t="str">
+        <x:v>bmw-6-series-adaptive-headlight-2012</x:v>
+      </x:c>
+      <x:c r="C93" s="9" t="str">
+        <x:v>2012-2018 | BMW | 6 Series</x:v>
+      </x:c>
+      <x:c r="D93" s="9" t="str">
+        <x:v>Adaptive Headlight Module and Stepper Motor Failure</x:v>
+      </x:c>
+      <x:c r="E93" s="9" t="str">
+        <x:v>Replace the failed stepper motor within the headlight assembly. In some cases, the entire adaptive headlight control module must be replaced and coded to the vehicle. The stepper motor can often be replaced without removing the entire headlight assembly by accessing it from behind the headlight. If the control module is replaced, it must be programmed with BMW ISTA diagnostic software.</x:v>
+      </x:c>
+      <x:c r="F93" s="9" t="str">
+        <x:v>Fault isolation between wiring, stepper motor, headlamp electronics/control module and complete lamp; coding/programming only when the replaced module requires it</x:v>
+      </x:c>
+      <x:c r="G93" s="9" t="str">
+        <x:v>DIAGNOSIS/CODING FIRST / NO UNIVERSAL PART</x:v>
+      </x:c>
+      <x:c r="H93" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I93" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J93" s="9" t="str">
+        <x:v>2012-2018 6 Series adaptive-headlight diagnosis and programming</x:v>
+      </x:c>
+      <x:c r="K93" s="9" t="str">
+        <x:v>diagnostic/coding service</x:v>
+      </x:c>
+      <x:c r="L93" s="9" t="str"/>
+      <x:c r="M93" s="9" t="str">
+        <x:v>The source has no trim, lamp technology, side, module part number or failure diagnosis; a motor or module cannot be approved across the range.</x:v>
+      </x:c>
+      <x:c r="N93" s="41" t="str">
+        <x:v>Split by chassis, option code, headlamp type, left/right position and diagnosed component before adding any part link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="765.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A94" s="40" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B94" s="9" t="str">
+        <x:v>bmw-6-series-n63-valve-stem-seals-2012</x:v>
+      </x:c>
+      <x:c r="C94" s="9" t="str">
+        <x:v>2013-2018 | BMW | 6 Series | N63TU1</x:v>
+      </x:c>
+      <x:c r="D94" s="9" t="str">
+        <x:v>N63TU1 650i Oil Consumption Requires BMW Diagnosis</x:v>
+      </x:c>
+      <x:c r="E94" s="9" t="str">
+        <x:v>Confirm the exact chassis, engine, production date, VIN and service history, document oil additions, and have a BMW-qualified technician perform the current oil-consumption measurement and applicable test plans. Do not assume historical settlement eligibility or replace valve-stem seals without diagnosis. ShowMeTheParts returned one exact-fit 2015 650i valve-stem-oil-seal set, but catalog fitment does not establish defect identity or the required repair, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F94" s="9" t="str">
+        <x:v>N63TU1/chassis/production-date/VIN confirmation; documented oil-consumption measurement; BMW test plans; condition-dependent repair</x:v>
+      </x:c>
+      <x:c r="G94" s="9" t="str">
+        <x:v>DIAGNOSIS/SETTLEMENT-HISTORY FIRST / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H94" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I94" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J94" s="9" t="str">
+        <x:v>2013-2018 F12 and 2013-2017 F13 650i/650i xDrive N63TU1 oil-consumption diagnosis</x:v>
+      </x:c>
+      <x:c r="K94" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L94" s="9" t="str"/>
+      <x:c r="M94" s="9" t="str">
+        <x:v>A catalog valve-seal set does not establish that valve-stem seals caused the oil use, and the repair path is test-dependent.</x:v>
+      </x:c>
+      <x:c r="N94" s="41" t="str">
+        <x:v>Correct the issue ID/year metadata and do not assume historical settlement eligibility or a valve-seal repair without diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="818.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A95" s="40" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B95" s="9" t="str">
+        <x:v>bmw-6series-convertible-top-2004</x:v>
+      </x:c>
+      <x:c r="C95" s="9" t="str">
+        <x:v>2004-2018 | BMW | 6 Series</x:v>
+      </x:c>
+      <x:c r="D95" s="9" t="str">
+        <x:v>Convertible Top Hydraulic Pump &amp; Cylinder Failure (E64/F12)</x:v>
+      </x:c>
+      <x:c r="E95" s="9" t="str">
+        <x:v>Send hydraulic pump and/or cylinders to Top Hydraulics (tophydraulics.com) for rebuild service ($600-1,200 with 3-year warranty). This is universally recommended over new OEM parts. OEM pump replacement: E64 pump 54347154648 ($2,000-3,500), F12 pump 54347299838 (similar cost). Total cost: $600-5,000 depending on approach. Top Hydraulics rebuild service is universally recommended by E64/F12 forums - their rebuilt units often outlast new OEM parts and come with 3-year warranty.</x:v>
+      </x:c>
+      <x:c r="F95" s="9" t="str">
+        <x:v>Diagnose pump, cylinder, line, sensor/wiring and switch faults separately; rebuild the confirmed E64 or F12 hydraulic component</x:v>
+      </x:c>
+      <x:c r="G95" s="9" t="str">
+        <x:v>CHASSIS-SPLIT HYDRAULIC SERVICE APPROVAL</x:v>
+      </x:c>
+      <x:c r="H95" s="9" t="str">
+        <x:v>Top Hydraulics E63/E64 hydraulic pump rebuild 54347154648</x:v>
+      </x:c>
+      <x:c r="I95" s="9" t="str">
+        <x:v>https://tophydraulics.com/bmw-6-series-e63e64-2003-2010/464-4265-rebuild-service-for-e63-e64-hydraulic-pump.html#/30-order_method_-send_your_parts_to_top_hydraulics_first</x:v>
+      </x:c>
+      <x:c r="J95" s="9" t="str">
+        <x:v>2004-2010 E64 convertible; confirmed hydraulic pump only</x:v>
+      </x:c>
+      <x:c r="K95" s="9" t="str">
+        <x:v>mail-in rebuild service</x:v>
+      </x:c>
+      <x:c r="L95" s="9" t="str">
+        <x:v>https://tophydraulics.com/9-bmw</x:v>
+      </x:c>
+      <x:c r="M95" s="9" t="str">
+        <x:v>Top Hydraulics has live, chassis-specific E64 and F12 service listings. The source row is still too broad to assume every top stoppage is a pump or cylinder failure.</x:v>
+      </x:c>
+      <x:c r="N95" s="41" t="str">
+        <x:v>Separate E64 from F12 and diagnose Hall sensors/wiring, switches and fluid leaks before shipping a hydraulic unit. Prices and turnaround must come from the live listing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A96" s="40" t="str"/>
+      <x:c r="B96" s="9" t="str"/>
+      <x:c r="C96" s="9" t="str"/>
+      <x:c r="D96" s="9" t="str"/>
+      <x:c r="E96" s="9" t="str"/>
+      <x:c r="F96" s="9" t="str"/>
+      <x:c r="G96" s="9" t="str"/>
+      <x:c r="H96" s="9" t="str">
+        <x:v>Top Hydraulics F12 6 Series hydraulic service</x:v>
+      </x:c>
+      <x:c r="I96" s="9" t="str">
+        <x:v>https://tophydraulics.com/142-bmw-6-series-f12-2011-2018</x:v>
+      </x:c>
+      <x:c r="J96" s="9" t="str">
+        <x:v>2012-2018 F12 convertible; use listed pump service only after exact component/part-number confirmation</x:v>
+      </x:c>
+      <x:c r="K96" s="9" t="str">
+        <x:v>fitment-specific service category</x:v>
+      </x:c>
+      <x:c r="L96" s="9" t="str"/>
+      <x:c r="M96" s="9" t="str"/>
+      <x:c r="N96" s="41" t="str"/>
+    </x:row>
+    <x:row r="97" ht="831.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A97" s="40" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B97" s="9" t="str">
+        <x:v>bmw-6series-n62-coolant-pipe-2004</x:v>
+      </x:c>
+      <x:c r="C97" s="9" t="str">
+        <x:v>2004-2010 | BMW | 6 Series | 645Ci, 650i | N62</x:v>
+      </x:c>
+      <x:c r="D97" s="9" t="str">
+        <x:v>N62 Coolant Transfer Pipe Leak (Engine Valley Pipe)</x:v>
+      </x:c>
+      <x:c r="E97" s="9" t="str">
+        <x:v>Install BimmerFix Stent Repair Kit ($239) - community gold standard fix that repairs the leak from underneath without removing the intake manifold. Takes 2-3 hours vs multi-day full pipe replacement. Alternatively, full OEM pipe replacement using pipe 11141439975 or URO collapsible pipe kit costs $3,000-5,000 at shop due to extensive labor. Total cost: $239-5,000 depending on approach. BimmerFix stent is universally recommended on Bimmerpost and E63/E64 forums - avoids $3,000-5,000 full pipe replacement labor.</x:v>
+      </x:c>
+      <x:c r="F97" s="9" t="str">
+        <x:v>Confirm N62 valley/weep-hole coolant transfer-pipe leak; BimmerFix N62 stent kit or exact full-pipe alternative</x:v>
+      </x:c>
+      <x:c r="G97" s="9" t="str">
+        <x:v>EXACT N62 PRODUCT APPROVED</x:v>
+      </x:c>
+      <x:c r="H97" s="9" t="str">
+        <x:v>BimmerFix N62 coolant-pipe repair kit</x:v>
+      </x:c>
+      <x:c r="I97" s="9" t="str">
+        <x:v>https://bimmerfix.com/products/coolant-pipe-repair-kit-bmw-n62-v8-engines</x:v>
+      </x:c>
+      <x:c r="J97" s="9" t="str">
+        <x:v>2004-2007 645Ci and 2005-2010 650i E63/E64 N62; page explicitly lists both models</x:v>
+      </x:c>
+      <x:c r="K97" s="9" t="str">
+        <x:v>coolant transfer-pipe stent kit</x:v>
+      </x:c>
+      <x:c r="L97" s="9" t="str">
+        <x:v>https://bimmerfix.com/pages/n62-v8-n73-v12-coolant-leak-solutions</x:v>
+      </x:c>
+      <x:c r="M97" s="9" t="str">
+        <x:v>The live product is buyable in the US and explicitly lists E63/E64 645Ci and 650i N62 applications plus cross-reference 11141439975.</x:v>
+      </x:c>
+      <x:c r="N97" s="41" t="str">
+        <x:v>Correct the 645Ci year range to the verified application and confirm the leak is at the transfer-pipe/weep-hole system before ordering; this kit is not for every N62 coolant leak.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="792" hidden="0" customHeight="1">
+      <x:c r="A98" s="40" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B98" s="9" t="str">
+        <x:v>bmw-6series-n62-valve-stem-seals-2004</x:v>
+      </x:c>
+      <x:c r="C98" s="9" t="str">
+        <x:v>2004-2010 | BMW | 6 Series | 645Ci, 650i | N62</x:v>
+      </x:c>
+      <x:c r="D98" s="9" t="str">
+        <x:v>N62 Valve Stem Seal Failure (Heavy Oil Consumption &amp; Blue Smoke)</x:v>
+      </x:c>
+      <x:c r="E98" s="9" t="str">
+        <x:v>Replace all 32 valve stem seals using Elring seals 11340029751 ($78 for complete set). DIY in-car repair using AGA Tools N62 valve stem seal tool kit ($500-700) avoids cylinder head removal and costs $800-2,000 total. Dealer repair with head removal costs $8,000-12,000. The AGA tool kit allows valve spring compression and seal replacement through the spark plug holes with the heads still on the engine. Check oil every 500-1,000 miles on high-mileage N62 engines and carry spare quart in vehicle.</x:v>
+      </x:c>
+      <x:c r="F98" s="9" t="str">
+        <x:v>All 32 N62 valve-stem seals; valve-cover gaskets and other one-time-use parts as the exact repair requires; professional in-car N62 tool set</x:v>
+      </x:c>
+      <x:c r="G98" s="9" t="str">
+        <x:v>EXACT ENGINE PARTS/TOOL APPROVED</x:v>
+      </x:c>
+      <x:c r="H98" s="9" t="str">
+        <x:v>AGA 32-piece Elring N62 valve-stem seal kit 11340029751</x:v>
+      </x:c>
+      <x:c r="I98" s="9" t="str">
+        <x:v>https://agatools.com/products/valve-stem-seals</x:v>
+      </x:c>
+      <x:c r="J98" s="9" t="str">
+        <x:v>N62/N62TU; 32 seals, BMW part 11 34 0 029 751; valve-cover gaskets not included</x:v>
+      </x:c>
+      <x:c r="K98" s="9" t="str">
+        <x:v>valve-stem seals</x:v>
+      </x:c>
+      <x:c r="L98" s="9" t="str">
+        <x:v>https://www.ecstuning.com/b-genuine-bmw-parts/valve-seals/11340029751/</x:v>
+      </x:c>
+      <x:c r="M98" s="9" t="str">
+        <x:v>Both live AGA listings are buyable: the seal kit states 32 Elring seals and the BMW part number, while the master collection is explicitly for N62 engines.</x:v>
+      </x:c>
+      <x:c r="N98" s="41" t="str">
+        <x:v>The current prices are higher than the source text. Do not describe this as a simple DIY job or imply the seal kit includes valve-cover gaskets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A99" s="40" t="str"/>
+      <x:c r="B99" s="9" t="str"/>
+      <x:c r="C99" s="9" t="str"/>
+      <x:c r="D99" s="9" t="str"/>
+      <x:c r="E99" s="9" t="str"/>
+      <x:c r="F99" s="9" t="str"/>
+      <x:c r="G99" s="9" t="str"/>
+      <x:c r="H99" s="9" t="str">
+        <x:v>AGA N62 valve-stem-seal master tool collection</x:v>
+      </x:c>
+      <x:c r="I99" s="9" t="str">
+        <x:v>https://agatools.com/collections/n62-valve-stem-seal-tool-kit/products/aga-n62-vst-k-vk</x:v>
+      </x:c>
+      <x:c r="J99" s="9" t="str">
+        <x:v>Professional N62 in-car repair tool set; confirm training and all supplementary equipment</x:v>
+      </x:c>
+      <x:c r="K99" s="9" t="str">
+        <x:v>specialty tool kit</x:v>
+      </x:c>
+      <x:c r="L99" s="9" t="str"/>
+      <x:c r="M99" s="9" t="str"/>
+      <x:c r="N99" s="41" t="str"/>
+    </x:row>
+    <x:row r="100" ht="686.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A100" s="40" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B100" s="9" t="str">
+        <x:v>bmw-6series-n63-timing-chain-2012</x:v>
+      </x:c>
+      <x:c r="C100" s="9" t="str">
+        <x:v>2012-2013 | BMW | 6 Series | N63</x:v>
+      </x:c>
+      <x:c r="D100" s="9" t="str">
+        <x:v>Early N63 650i Timing-Chain Wear Check</x:v>
+      </x:c>
+      <x:c r="E100" s="9" t="str">
+        <x:v>Confirm the N63 engine, chassis, production date and VIN history, resolve stored VANOS or camshaft-position faults first, and have a BMW-qualified technician run the prescribed timing-chain test. Replace both chains only if the approved test reports that the chain is not OK. ShowMeTheParts resolved the exact 2012 650i ENGINE COMPONENTS fitment but returned no timing-chain candidate, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F100" s="9" t="str">
+        <x:v>N63/chassis/production-date/VIN confirmation; resolve VANOS/cam-position faults; BMW timing-chain elongation test; both chains only after failed test</x:v>
+      </x:c>
+      <x:c r="G100" s="9" t="str">
+        <x:v>DIAGNOSIS FIRST / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H100" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I100" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J100" s="9" t="str">
+        <x:v>2012-2013 F12/F13 650i N63 timing-chain test plan</x:v>
+      </x:c>
+      <x:c r="K100" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L100" s="9" t="str"/>
+      <x:c r="M100" s="9" t="str">
+        <x:v>The source reports no exact timing-chain candidate and requires the approved test result before replacement.</x:v>
+      </x:c>
+      <x:c r="N100" s="41" t="str">
+        <x:v>The check is not a recall or mandatory campaign; do not link a timing kit or scanner before diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="805.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A101" s="40" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B101" s="9" t="str">
+        <x:v>bmw-6series-smg-pump-2004</x:v>
+      </x:c>
+      <x:c r="C101" s="9" t="str">
+        <x:v>2004-2010 | BMW | 6 Series</x:v>
+      </x:c>
+      <x:c r="D101" s="9" t="str">
+        <x:v>SMG III Hydraulic Pump Failure (M6 and SMG-Equipped 645Ci/650i)</x:v>
+      </x:c>
+      <x:c r="E101" s="9" t="str">
+        <x:v>Try pump motor-only replacement FIRST ($200-350 from SMG Society) - 90% success rate and no hydraulic bleed needed. If motor replacement fails, install MLREng/BimmerWorld upgraded pump ($449). OEM full pump replacement 23427571297 costs $5,000-6,500 and should be LAST resort. Total cost: $500-7,700 depending on approach. CRITICAL: 90% of failures are the pump motor, not the full pump - do not let shops misdiagnose and charge $5,000+ when a $350 motor fixes the issue.</x:v>
+      </x:c>
+      <x:c r="F101" s="9" t="str">
+        <x:v>Identify non-M six-speed SMG versus M6 SMG III; diagnose pressure, relay, accumulator, motor and pump; transmission-specific motor only when confirmed</x:v>
+      </x:c>
+      <x:c r="G101" s="9" t="str">
+        <x:v>TRANSMISSION-SPLIT PRODUCT APPROVAL</x:v>
+      </x:c>
+      <x:c r="H101" s="9" t="str">
+        <x:v>SMG Society six-speed SMG pump motor</x:v>
+      </x:c>
+      <x:c r="I101" s="9" t="str">
+        <x:v>https://www.smgsociety.com/product/pump-motor-6-speed-smg/</x:v>
+      </x:c>
+      <x:c r="J101" s="9" t="str">
+        <x:v>E63 non-M six-speed SMG only; references 23427571297/23427507107; in stock</x:v>
+      </x:c>
+      <x:c r="K101" s="9" t="str">
+        <x:v>non-M SMG pump motor</x:v>
+      </x:c>
+      <x:c r="L101" s="9" t="str"/>
+      <x:c r="M101" s="9" t="str">
+        <x:v>Live pages confirm two different in-stock motors and compatibility groups. The source incorrectly treats M6 SMG III and 645Ci/650i six-speed SMG as one assembly.</x:v>
+      </x:c>
+      <x:c r="N101" s="41" t="str">
+        <x:v>Split M6 from non-M applications, remove the unsupported 90% success claim, and note BMW procedures may still require pressure reduction, checks or service functions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A102" s="40" t="str"/>
+      <x:c r="B102" s="9" t="str"/>
+      <x:c r="C102" s="9" t="str"/>
+      <x:c r="D102" s="9" t="str"/>
+      <x:c r="E102" s="9" t="str"/>
+      <x:c r="F102" s="9" t="str"/>
+      <x:c r="G102" s="9" t="str"/>
+      <x:c r="H102" s="9" t="str">
+        <x:v>SMG Society M6 SMG III pump motor 23017841032</x:v>
+      </x:c>
+      <x:c r="I102" s="9" t="str">
+        <x:v>https://www.smgsociety.com/product/pump-motor-bmw-e60-m5-e63-m6-smg-iii/</x:v>
+      </x:c>
+      <x:c r="J102" s="9" t="str">
+        <x:v>E63/E64 M6 SMG III only; in stock</x:v>
+      </x:c>
+      <x:c r="K102" s="9" t="str">
+        <x:v>M6 SMG III pump motor</x:v>
+      </x:c>
+      <x:c r="L102" s="9" t="str"/>
+      <x:c r="M102" s="9" t="str"/>
+      <x:c r="N102" s="41" t="str"/>
+    </x:row>
+    <x:row r="103" ht="897.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A103" s="40" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B103" s="9" t="str">
+        <x:v>bmw-7-series-air-suspension-compressor-2009</x:v>
+      </x:c>
+      <x:c r="C103" s="9" t="str">
+        <x:v>2016-2022 | BMW | 7 Series</x:v>
+      </x:c>
+      <x:c r="D103" s="9" t="str">
+        <x:v>G11/G12 Air-Suspension Strut Diagnosis</x:v>
+      </x:c>
+      <x:c r="E103" s="9" t="str">
+        <x:v>Confirm the exact model, production date, VIN and current WVI vehicle comments, then diagnose the specific sagging corner, ride-height complaint or suspension warning with BMW procedures. Replace only a strut assembly that is confirmed defective and eligible under the current instructions. Do not present the historical eight-year/80,000-mile extension as a universal or current coverage promise. ShowMeTheParts resolved exact 2018 740i and 740i xDrive suspension categories but returned no air-spring candidate, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F103" s="9" t="str">
+        <x:v>VIN/WVI eligibility check; diagnose the exact sagging corner and air-suspension fault; replace only a confirmed eligible strut</x:v>
+      </x:c>
+      <x:c r="G103" s="9" t="str">
+        <x:v>DIAGNOSIS/COVERAGE FIRST / NO COMPRESSOR LINK</x:v>
+      </x:c>
+      <x:c r="H103" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I103" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J103" s="9" t="str">
+        <x:v>2016-2022 G11/G12 air-suspension diagnosis and WVI review</x:v>
+      </x:c>
+      <x:c r="K103" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L103" s="9" t="str"/>
+      <x:c r="M103" s="9" t="str">
+        <x:v>The corrected source concerns component-specific front/rear struts and explicitly excludes other air-suspension components; it does not support a compressor link.</x:v>
+      </x:c>
+      <x:c r="N103" s="41" t="str">
+        <x:v>Correct the issue ID/year and title: do not generalize the historical strut extension to compressors, relays, dryers or all four corners.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A104" s="40" t="str"/>
+      <x:c r="B104" s="9" t="str"/>
+      <x:c r="C104" s="9" t="str"/>
+      <x:c r="D104" s="9" t="str"/>
+      <x:c r="E104" s="9" t="str"/>
+      <x:c r="F104" s="9" t="str"/>
+      <x:c r="G104" s="9" t="str"/>
+      <x:c r="H104" s="9" t="str">
+        <x:v>BMW recall and campaign lookup</x:v>
+      </x:c>
+      <x:c r="I104" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J104" s="9" t="str">
+        <x:v>VIN lookup; limited warranty extension is not a recall</x:v>
+      </x:c>
+      <x:c r="K104" s="9" t="str">
+        <x:v>official coverage check</x:v>
+      </x:c>
+      <x:c r="L104" s="9" t="str"/>
+      <x:c r="M104" s="9" t="str"/>
+      <x:c r="N104" s="41" t="str"/>
+    </x:row>
+    <x:row r="105" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A105" s="40" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B105" s="9" t="str">
+        <x:v>bmw-7-series-idrive-system-failures-2009</x:v>
+      </x:c>
+      <x:c r="C105" s="9" t="str">
+        <x:v>2009-2022 | BMW | 7 Series</x:v>
+      </x:c>
+      <x:c r="D105" s="9" t="str">
+        <x:v>iDrive Head Unit and CIC/NBT Module Failures</x:v>
+      </x:c>
+      <x:c r="E105" s="9" t="str">
+        <x:v>For CIC units (F01): replace the internal hard drive with an SSD upgrade, or replace the entire CIC module. For NBT units (G11): replace the head unit or have the eMMC chip reflowed/replaced by a specialist. Software updates from BMW can address some stability issues. Many aftermarket specialists offer rebuilt head units at 40-60% of dealer pricing. The unit must be coded to the vehicle VIN after replacement.</x:v>
+      </x:c>
+      <x:c r="F105" s="9" t="str">
+        <x:v>Identify chassis and exact head-unit generation; software/power/network diagnosis; VIN-matched programmed replacement or exact-unit specialist repair</x:v>
+      </x:c>
+      <x:c r="G105" s="9" t="str">
+        <x:v>GENERATION-SPLIT PARTIAL APPROVAL</x:v>
+      </x:c>
+      <x:c r="H105" s="9" t="str">
+        <x:v>BPM Sport VIN-matched CCC/CIC/NBT iDrive replacement</x:v>
+      </x:c>
+      <x:c r="I105" s="9" t="str">
+        <x:v>https://www.bpmsport.com/products/bmw-nav-replacement.html</x:v>
+      </x:c>
+      <x:c r="J105" s="9" t="str">
+        <x:v>2009-2016 only; VIN/year/sound-system selection and programming required; unit only, no display/controller/wiring</x:v>
+      </x:c>
+      <x:c r="K105" s="9" t="str">
+        <x:v>programmed replacement head unit</x:v>
+      </x:c>
+      <x:c r="L105" s="9" t="str"/>
+      <x:c r="M105" s="9" t="str">
+        <x:v>BPM Sport has a live buyable VIN-selected replacement covering CCC/CIC/NBT through 2016. The later G11/G12 range cannot be fit to that listing and remains diagnosis-first.</x:v>
+      </x:c>
+      <x:c r="N105" s="41" t="str">
+        <x:v>Split F01/F02 CIC/NBT from G11/G12 NBT Evo/MGU generations. Do not claim every blackout/reboot is a hard drive or eMMC failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="132" hidden="0" customHeight="1">
+      <x:c r="A106" s="42" t="str"/>
+      <x:c r="B106" s="43" t="str"/>
+      <x:c r="C106" s="43" t="str"/>
+      <x:c r="D106" s="43" t="str"/>
+      <x:c r="E106" s="43" t="str"/>
+      <x:c r="F106" s="43" t="str"/>
+      <x:c r="G106" s="43" t="str"/>
+      <x:c r="H106" s="43" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I106" s="43" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J106" s="43" t="str">
+        <x:v>2016-2022 G11/G12 NBT Evo/MGU-era diagnosis, software and coding</x:v>
+      </x:c>
+      <x:c r="K106" s="43" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L106" s="43" t="str"/>
+      <x:c r="M106" s="43" t="str"/>
+      <x:c r="N106" s="44" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3898,21 +4654,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="2" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>bmw-5-series-n54-wastegate-2008</x:v>
+        <x:v>bmw-7-series-panoramic-roof-2016</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2008-2010 | BMW | 5 Series | N54</x:v>
+        <x:v>2016-2025 | BMW | 7 Series</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>535i N54 Wastegate Clanking Requires Turbocharger Diagnosis</x:v>
+        <x:v>Panoramic Glass Roof Cracking and Drain Blockage</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Confirm the exact N54 vehicle and modification history, distinguish normal slight rattle from the defined clanking condition, and follow current BMW diagnostic and repair instructions. The historical eight-year/82,000-mile emissions extension is not a current coverage promise. ShowMeTheParts returned four exact-fitment turbo oil/coolant-line candidates but no wastegate or turbocharger repair candidate, so no commerce link is approved.</x:v>
+        <x:v>For cracked glass: the entire panoramic roof panel must be replaced. Check if covered under BMW's glass warranty (some cracks without impact evidence are covered as manufacturing defects). For drain blockage: clear all four drain channels (two front, two rear) using compressed air or a flexible drain snake. This should be done as preventive maintenance every 12 months. If the headliner is water-damaged, it must be removed and replaced.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -3921,21 +4677,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="3" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>bmw-5-series-n63-oil-consumption-2011</x:v>
+        <x:v>bmw-7series-air-suspension-2002</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2010-2013 | BMW | 5 Series | N63</x:v>
+        <x:v>2002-2023 | BMW | 7 Series</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>N63 Low-Oil Warning Requires 550i Oil-Consumption Testing</x:v>
+        <x:v>Air Suspension Compressor &amp; Strut Failure - All Generations</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Confirm the VIN and service history, record oil additions and service intervals, and have a BMW-qualified technician perform the current oil-consumption test and applicable diagnosis. Historical settlement benefits and the N63 Customer Care Package must not be presented as current coverage. The official material describes multiple checks and condition-dependent repairs, so no single catalog part or retail link is approved.</x:v>
+        <x:v>Replace failed air struts or compressor. Individual air struts can be replaced, but often multiple fail together. Compressor replacement is 3-5 hours labor. Some owners convert to conventional coil springs ($1,500-2,500) to avoid repeat air suspension repairs. Air strut replacement requires specialized tools and calibration. OEM BMW parts are extremely expensive; some aftermarket options (Arnott) available at lower cost but with mixed reliability.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -3944,21 +4700,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="4" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>bmw-5-series-n63-timing-chain-2006</x:v>
+        <x:v>bmw-7series-electrical-e65-2002</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2010-2013 | BMW | 5 Series | N63</x:v>
+        <x:v>2002-2008 | BMW | 7 Series</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>N63 550i Timing-Chain Wear Check</x:v>
+        <x:v>Widespread Electrical Issues - E65/E66 745i/750i/760i</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>Confirm the N63 engine, production date and VIN history, resolve stored VANOS or camshaft-position faults first, and have a BMW-qualified technician run the prescribed timing-chain test. Replace both chains only if the approved test reports that the chain is not OK. ShowMeTheParts resolved the exact 2012 550i ENGINE COMPONENTS fitment but returned no timing-chain candidate, so no commerce link is approved.</x:v>
+        <x:v>Diagnose specific module failures with BMW diagnostic software. Common fixes: CCC module replacement ($1,500-2,500), window regulator replacement ($300-600 per window), battery registration after replacement, and parasitic draw diagnosis. Many electrical issues require dealer-level diagnostics. Some problems can only be resolved with module replacements. E65/E66 ownership requires deep pockets or strong DIY skills. Avoid buying E65 without thorough pre-purchase inspection and warranty.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -3967,21 +4723,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="1056" hidden="0" customHeight="1">
+    <x:row r="5" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>bmw-5-series-oil-leaks-2004</x:v>
+        <x:v>bmw-7series-hpfp-2009</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2004-2023 | BMW | 5 Series</x:v>
+        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL | N63</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>Valve Cover Gasket &amp; Oil Filter Housing Gasket Leaks</x:v>
+        <x:v>High-Pressure Fuel Pump Failure - F01/F02 750i/750Li (N63)</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Replace valve cover gasket ($400-$800 shop, $150-250 DIY parts) and/or oil filter housing gasket ($300-$600 shop, $80-150 DIY parts). Can be done separately or together depending on leak source. Use OEM BMW gaskets or quality German aftermarket (Elring, Victor Reinz brands) - cheap gaskets leak within 20k miles. Both are DIY-friendly for experienced mechanics: VCG takes 2-3 hours, OFHG takes 1-2 hours. YouTube has detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage). Address OFHG leaks EARLY - oil dripping on alternator causes $800+ alternator failure.</x:v>
+        <x:v>Replace high-pressure fuel pump(s). BMW recommends replacing both HPFPs together on N63 engines. Flush fuel system if metal contamination is present. Use only OEM BMW or Bosch fuel pumps - aftermarket pumps have poor reliability. Labor is 4-6 hours. Some owners report multiple HPFP failures over vehicle life. N63 Customer Care Package may cover HPFP repairs on eligible VINs. Consider extended warranty for N63-powered cars.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -3990,21 +4746,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="1003.2000122070312" hidden="0" customHeight="1">
+    <x:row r="6" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>bmw-5-series-water-pump-2004</x:v>
+        <x:v>bmw-7series-n63-turbo-2009</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2004-2023 | BMW | 5 Series | N52, N54, N55, N20, N62, N63, B48, B58</x:v>
+        <x:v>2013-2015 | BMW | 7 Series | N63TU1</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>Electric Water Pump Failure (All Engines)</x:v>
+        <x:v>N63TU1 750i Oil-Consumption and Turbo-Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Replace electric water pump ($600-$1,200 installed). Use OEM BMW or quality German aftermarket (Rein, Hepu brands) - cheap eBay pumps fail within 20k miles. Replace thermostat at same time ($200 additional parts) since labor is 80% done. Flush cooling system and refill with BMW-spec coolant (do NOT use generic green antifreeze - causes corrosion). PREVENTIVE: Replace water pump at 80,000 miles BEFORE failure to avoid being stranded. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps heads ($4,000+ repair). Call tow truck; do not attempt to drive.</x:v>
+        <x:v>Confirm the exact chassis, N63TU1 engine, production date, engine serial number, VIN and current eligibility, then follow BMW electronic oil-level measurement and leak-inspection procedures. Repair only the component supported by the documented test result; replace turbochargers only when leakage is confirmed under the current instructions. Do not promise historical settlement coverage. ShowMeTheParts returned six exact 2014 750i/750i xDrive turbo oil-return-line fitments, but catalog fitment does not prove a leak, oil-consumption cause or repair role, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -4013,21 +4769,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="1056" hidden="0" customHeight="1">
+    <x:row r="7" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>bmw-5-series-zf-6hp-mechatronic-2004</x:v>
+        <x:v>bmw-7series-n63-valvetronic-2009</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2004-2013 | BMW | 5 Series</x:v>
+        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>ZF 6HP Transmission Mechatronic Sleeve &amp; Valve Body Failure</x:v>
+        <x:v>N63 Valvetronic Motor Failure - F01/F02 750i/750Li</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>Replace mechatronic sealing sleeves (4 tubes + 1 square seal) and valve body adapter sleeve ($150-300 parts). DIY-friendly with transmission pan drop and valve body removal (4-6 hours, detailed guides on Bimmerfest). While valve body is out, replace transmission fluid/filter and clean solenoids ($200 additional). Dealer charges $1,500-2,500 for this repair; DIY costs $400-700 total. PREVENTIVE: Change transmission fluid every 50,000 miles (NOT "lifetime") with BMW-spec fluid (Pentosin/ZF Lifeguard 6). Fluid changes prevent 90% of ZF 6HP problems. If ignored, worn mechatronic destroys clutches requiring $5,000+ transmission rebuild.</x:v>
+        <x:v>Replace Valvetronic eccentric shaft motor(s). Often both motors need replacement since wear is similar. Clean carbon buildup from Valvetronic mechanism during repair. N63 Customer Care Package may cover this repair on eligible VINs. Labor is 6-10 hours. Some shops recommend replacing Valvetronic motors preventively at 80,000 miles to avoid being stranded. Extended warranty highly recommended for N63-powered 7 Series.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -4036,21 +4792,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="594" hidden="0" customHeight="1">
+    <x:row r="8" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>bmw-6-series-adaptive-headlight-2012</x:v>
+        <x:v>bmw-8-series-adaptive-suspension-2019</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2012-2018 | BMW | 6 Series</x:v>
+        <x:v>2019-2025 | BMW | 8 Series</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>Adaptive Headlight Module and Stepper Motor Failure</x:v>
+        <x:v>Adaptive Suspension Damper Malfunction</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Replace the failed stepper motor within the headlight assembly. In some cases, the entire adaptive headlight control module must be replaced and coded to the vehicle. The stepper motor can often be replaced without removing the entire headlight assembly by accessing it from behind the headlight. If the control module is replaced, it must be programmed with BMW ISTA diagnostic software.</x:v>
+        <x:v>Replace the failed adaptive damper. BMW's diagnostic system can identify which specific damper has failed through the suspension control module fault memory. The damper must be coded to the vehicle after installation. Replace dampers in pairs (both fronts or both rears) if the vehicle has over 60,000 miles, as the remaining original damper is likely near end of life. Bilstein offers OE-equivalent adaptive dampers at lower cost than BMW parts.</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
@@ -4059,21 +4815,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="9" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>bmw-6-series-n63-valve-stem-seals-2012</x:v>
+        <x:v>bmw-8-series-b58-coolant-loss-2019</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2013-2018 | BMW | 6 Series | N63TU1</x:v>
+        <x:v>2019-2025 | BMW | 8 Series | B58</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>N63TU1 650i Oil Consumption Requires BMW Diagnosis</x:v>
+        <x:v>B58 Engine Coolant Loss from Expansion Tank and Water Pump</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Confirm the exact chassis, engine, production date, VIN and service history, document oil additions, and have a BMW-qualified technician perform the current oil-consumption measurement and applicable test plans. Do not assume historical settlement eligibility or replace valve-stem seals without diagnosis. ShowMeTheParts returned one exact-fit 2015 650i valve-stem-oil-seal set, but catalog fitment does not establish defect identity or the required repair, so no commerce link is approved.</x:v>
+        <x:v>Replace the coolant expansion tank with BMW's latest revision. Inspect the electric water pump and all quick-connect coolant fittings for leaks. Pressure test the entire cooling system after repairs. Replace the expansion tank cap as a weak cap allows premature boiling. Use only BMW-approved blue coolant — mixing coolant types causes gel formation.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -4082,21 +4838,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="10" ht="660" hidden="0" customHeight="1">
       <x:c r="A10" s="40" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>bmw-6series-convertible-top-2004</x:v>
+        <x:v>bmw-8-series-n63-oil-consumption-m850i-2019</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2004-2018 | BMW | 6 Series</x:v>
+        <x:v>2019-2025 | BMW | 8 Series | N63TU4, N63</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>Convertible Top Hydraulic Pump &amp; Cylinder Failure (E64/F12)</x:v>
+        <x:v>N63/S63 V8 Oil Consumption in M850i</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>Send hydraulic pump and/or cylinders to Top Hydraulics (tophydraulics.com) for rebuild service ($600-1,200 with 3-year warranty). This is universally recommended over new OEM parts. OEM pump replacement: E64 pump 54347154648 ($2,000-3,500), F12 pump 54347299838 (similar cost). Total cost: $600-5,000 depending on approach. Top Hydraulics rebuild service is universally recommended by E64/F12 forums - their rebuilt units often outlast new OEM parts and come with 3-year warranty.</x:v>
+        <x:v>BMW considers up to 1 quart per 1,200 miles as within specification for the N63 family. For excessive consumption beyond that, inspect turbo oil return lines for restriction (causes oil to push past turbo seals), check the crankcase ventilation system, and evaluate valve stem seal condition. The N63TU4 benefits from updated seals and coatings, so consumption rarely reaches the extreme levels of earlier N63 variants.</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
         <x:v>0</x:v>
@@ -4105,21 +4861,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="11" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>bmw-6series-n62-coolant-pipe-2004</x:v>
+        <x:v>bmw-8series-ibs-failure-2020</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2004-2010 | BMW | 6 Series | 645Ci, 650i | N62</x:v>
+        <x:v>2019-2021 | BMW | 8 Series</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>N62 Coolant Transfer Pipe Leak (Engine Valley Pipe)</x:v>
+        <x:v>2019-2021 8 Series Integrated Brake Recall 21V-062</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Install BimmerFix Stent Repair Kit ($239) - community gold standard fix that repairs the leak from underneath without removing the intake manifold. Takes 2-3 hours vs multi-day full pipe replacement. Alternatively, full OEM pipe replacement using pipe 11141439975 or URO collapsible pipe kit costs $3,000-5,000 at shop due to extensive labor. Total cost: $239-5,000 depending on approach. BimmerFix stent is universally recommended on Bimmerpost and E63/E64 forums - avoids $3,000-5,000 full pipe replacement labor.</x:v>
+        <x:v>Check the VIN for an open 21V-062 campaign and current remedy status with BMW/NHTSA. If the vehicle is included, have an authorized BMW center perform the recall repair at no charge. If brake warnings appear or pedal effort changes, slow safely, avoid hard braking and contact BMW or roadside assistance for direction. ShowMeTheParts resolved exact 2020 840i, 840i xDrive and M850i xDrive brake-hydraulics contexts but returned no brake-booster candidate; recall eligibility and remedy remain dealer-only.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -4128,21 +4884,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="792" hidden="0" customHeight="1">
+    <x:row r="12" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>bmw-6series-n62-valve-stem-seals-2004</x:v>
+        <x:v>bmw-8series-n63tu3-timing-chain-2019</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2004-2010 | BMW | 6 Series | 645Ci, 650i | N62</x:v>
+        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>N62 Valve Stem Seal Failure (Heavy Oil Consumption &amp; Blue Smoke)</x:v>
+        <x:v>N63TU3 Timing Chain Guide Wear (M850i)</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Replace all 32 valve stem seals using Elring seals 11340029751 ($78 for complete set). DIY in-car repair using AGA Tools N62 valve stem seal tool kit ($500-700) avoids cylinder head removal and costs $800-2,000 total. Dealer repair with head removal costs $8,000-12,000. The AGA tool kit allows valve spring compression and seal replacement through the spark plug holes with the heads still on the engine. Check oil every 500-1,000 miles on high-mileage N62 engines and carry spare quart in vehicle.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain guides, tensioners, and chain at 80,000-100,000 miles ($4,000-$7,500). Turner Motorsport timing chain kit 11317594899KT includes all necessary components. Individual parts: chain guides 11147574373, 11317574397, 11317592850, 11317592877; chain 11317598263. If chain has already skipped: engine damage likely requires $15,000-$25,000 engine replacement. CRITICAL: If you hear cold-start rattling, do NOT drive - tow to shop immediately to prevent catastrophic engine failure.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -4151,21 +4907,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="13" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>bmw-6series-n63-timing-chain-2012</x:v>
+        <x:v>bmw-8series-n63tu3-valve-stem-seals-2019</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2012-2013 | BMW | 6 Series | N63</x:v>
+        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i | N63TU3</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>Early N63 650i Timing-Chain Wear Check</x:v>
+        <x:v>N63TU3 Valve Stem Seal Failure &amp; Oil Consumption (M850i)</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Confirm the N63 engine, chassis, production date and VIN history, resolve stored VANOS or camshaft-position faults first, and have a BMW-qualified technician run the prescribed timing-chain test. Replace both chains only if the approved test reports that the chain is not OK. ShowMeTheParts resolved the exact 2012 650i ENGINE COMPONENTS fitment but returned no timing-chain candidate, so no commerce link is approved.</x:v>
+        <x:v>Replace valve stem seals ($3,500-$10,000 due to labor-intensive hot-V access). Use OEM Victor Reinz seals for durability. Replace spark plugs (Bosch 12120037581) when performing seal replacement. AGA Tools N63 Valve Stem Seal Kit AGA-N63-VSK-K ($500-800) provides specialized tooling for this job. Check VIN eligibility for N63 class action settlement which may cover repair costs. PREVENTIVE: Use quality synthetic oil (BMW LL-01 spec), change every 5,000-7,500 miles, and monitor oil level every 500-1,000 miles on M850i models.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -4174,21 +4930,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="805.2000122070312" hidden="0" customHeight="1">
+    <x:row r="14" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>bmw-6series-smg-pump-2004</x:v>
+        <x:v>bmw-8series-premature-tire-wear-2019</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2004-2010 | BMW | 6 Series</x:v>
+        <x:v>2019-2024 | BMW | 8 Series</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>SMG III Hydraulic Pump Failure (M6 and SMG-Equipped 645Ci/650i)</x:v>
+        <x:v>Premature Tire Wear (All 8 Series &amp; M8)</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Try pump motor-only replacement FIRST ($200-350 from SMG Society) - 90% success rate and no hydraulic bleed needed. If motor replacement fails, install MLREng/BimmerWorld upgraded pump ($449). OEM full pump replacement 23427571297 costs $5,000-6,500 and should be LAST resort. Total cost: $500-7,700 depending on approach. CRITICAL: 90% of failures are the pump motor, not the full pump - do not let shops misdiagnose and charge $5,000+ when a $350 motor fixes the issue.</x:v>
+        <x:v>Get a performance alignment reducing rear camber from factory -2.0 degrees to -1.5 degrees ($150-$300 at alignment shop). This significantly extends rear tire life from 9,000-15,000 miles to 20,000-25,000 miles while maintaining good street handling. Rotate front tires side-to-side every 5,000 miles (staggered setup prevents front-to-rear rotation). Replace rear tires in pairs when worn. COST SAVINGS: Alignment adjustment ($150-300) saves $1,200-2,400 per year in premature tire replacement on expensive performance tires ($300-600 each).</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -4197,21 +4953,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="15" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>bmw-7-series-air-suspension-compressor-2009</x:v>
+        <x:v>bmw-8series-zf-8hp-mechatronic-2019</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2016-2022 | BMW | 7 Series</x:v>
+        <x:v>2023-2023 | BMW | 8 Series</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>G11/G12 Air-Suspension Strut Diagnosis</x:v>
+        <x:v>2023 8 Series ITCU Recall 23V-821</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Confirm the exact model, production date, VIN and current WVI vehicle comments, then diagnose the specific sagging corner, ride-height complaint or suspension warning with BMW procedures. Replace only a strut assembly that is confirmed defective and eligible under the current instructions. Do not present the historical eight-year/80,000-mile extension as a universal or current coverage promise. ShowMeTheParts resolved exact 2018 740i and 740i xDrive suspension categories but returned no air-spring candidate, so no commerce link is approved.</x:v>
+        <x:v>Check the VIN for an open 23V-821 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW recall remedy, which replaces the transmission mechatronics module. Do not buy a sleeve kit or change fluid as a substitute for the recall. ShowMeTheParts resolved exact 2023 840i, 840i xDrive and M850i xDrive models but exposed no transmission category or ITCU candidate, and recall repair remains dealer-only.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -4220,21 +4976,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="16" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>bmw-7-series-idrive-system-failures-2009</x:v>
+        <x:v>bmw-driveshaft-flex-disc-e90</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2009-2022 | BMW | 7 Series</x:v>
+        <x:v>2011-2011 | BMW | 3 Series | N55, N54T, M57Y</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>iDrive Head Unit and CIC/NBT Module Failures</x:v>
+        <x:v>Certain 2011 3 Series Need a Rear-Driveshaft Flex-Disc Recall Check</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>For CIC units (F01): replace the internal hard drive with an SSD upgrade, or replace the entire CIC module. For NBT units (G11): replace the head unit or have the eMMC chip reflowed/replaced by a specialist. Software updates from BMW can address some stability issues. Many aftermarket specialists offer rebuilt head units at 40-60% of dealer pricing. The unit must be coded to the vehicle VIN after replacement.</x:v>
+        <x:v>Check the VIN for open recall 17V-067 before authorizing driveline parts. BMW instructs dealers to inspect the installed disc revision index and replace it only when required by the campaign. ShowMeTheParts exposed the exact 2011 335i DRIVE SHAFT category but returned no flex-disc candidate; no commerce link is approved for this recall repair.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
         <x:v>0</x:v>
@@ -4243,21 +4999,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="17" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>bmw-7-series-panoramic-roof-2016</x:v>
+        <x:v>bmw-i3-12v-battery-drain-2014</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2016-2025 | BMW | 7 Series</x:v>
+        <x:v>2014-2021 | BMW | i3</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>Panoramic Glass Roof Cracking and Drain Blockage</x:v>
+        <x:v>i3 12V Discharge Warning: ISTA Software-First Diagnosis</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>For cracked glass: the entire panoramic roof panel must be replaced. Check if covered under BMW's glass warranty (some cracks without impact evidence are covered as manufacturing defects). For drain blockage: clear all four drain channels (two front, two rear) using compressed air or a flexible drain snake. This should be done as preventive maintenance every 12 months. If the headliner is water-damaged, it must be removed and replaced.</x:v>
+        <x:v>Read the Check Control Message and fault memory, run BMW ISTA Energy Diagnosis and test the 12V battery before replacing anything. For the Controller condition, BMW says not to replace the Controller; program the vehicle when the measured I-level and diagnostic result meet SIB 61 05 20. For the early REx condition, follow SIB 61 39 14. Replace and register a 12V battery only if separate testing proves it failed. ShowMeTheParts resolved the exact 2014 i3 model but exposed no battery category or defensible 12V candidate, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -4266,21 +5022,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="18" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>bmw-7series-air-suspension-2002</x:v>
+        <x:v>bmw-i3-12v-parasitic-drain-2014</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2002-2023 | BMW | 7 Series</x:v>
+        <x:v>2014-2021 | BMW | i3</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure - All Generations</x:v>
+        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Replace failed air struts or compressor. Individual air struts can be replaced, but often multiple fail together. Compressor replacement is 3-5 hours labor. Some owners convert to conventional coil springs ($1,500-2,500) to avoid repeat air suspension repairs. Air strut replacement requires specialized tools and calibration. OEM BMW parts are extremely expensive; some aftermarket options (Arnott) available at lower cost but with mixed reliability.</x:v>
+        <x:v>Replace the 12V AGM battery with a fresh unit (OEM or high-quality AGM). Code the new battery using ISTA or BimmerCode to register it with the IBS (Intelligent Battery Sensor). Check for software updates that address module sleep behavior. Some owners install a battery tender for long-term parking.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -4289,21 +5045,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="19" ht="1108.800048828125" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>bmw-7series-electrical-e65-2002</x:v>
+        <x:v>bmw-i3-ac-compressor-black-death-2014</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2002-2008 | BMW | 7 Series</x:v>
+        <x:v>2014-2021 | BMW | i3</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>Widespread Electrical Issues - E65/E66 745i/750i/760i</x:v>
+        <x:v>Electric A/C Compressor Catastrophic Failure ("Black Death") - All I01</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Diagnose specific module failures with BMW diagnostic software. Common fixes: CCC module replacement ($1,500-2,500), window regulator replacement ($300-600 per window), battery registration after replacement, and parasitic draw diagnosis. Many electrical issues require dealer-level diagnostics. Some problems can only be resolved with module replacements. E65/E66 ownership requires deep pockets or strong DIY skills. Avoid buying E65 without thorough pre-purchase inspection and warranty.</x:v>
+        <x:v>If caught early (noise but still functioning), replace compressor before catastrophic failure. Latest OEM compressor: BMW 64529496107 (supersedes 64529320855, 64529343806, 64529347662, 64529364868). FCP Euro price ~$1,756. If metal contamination has occurred, entire system including battery cooling channels must be replaced ($10,600+). MUST use POE (Polyolester) anti-electrostatic compressor oil - standard PAG oil will destroy EV compressors. Independent AC shops that understand EV compressors can save 60-80% vs dealer. RYC Automotive offers remanufactured compressor (RYC-i3-01) as budget option. Aftermarket Nissens condenser ($152) available vs OEM ($581 via FCP Euro).</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -4312,21 +5068,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="20" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>bmw-7series-hpfp-2009</x:v>
+        <x:v>bmw-i3-ac-compressor-failure-2014</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL | N63</x:v>
+        <x:v>2014-2021 | BMW | i3</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump Failure - F01/F02 750i/750Li (N63)</x:v>
+        <x:v>Electric AC Compressor Failure</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Replace high-pressure fuel pump(s). BMW recommends replacing both HPFPs together on N63 engines. Flush fuel system if metal contamination is present. Use only OEM BMW or Bosch fuel pumps - aftermarket pumps have poor reliability. Labor is 4-6 hours. Some owners report multiple HPFP failures over vehicle life. N63 Customer Care Package may cover HPFP repairs on eligible VINs. Consider extended warranty for N63-powered cars.</x:v>
+        <x:v>Replace the electric AC compressor assembly. This requires a certified HV-trained technician to safely de-energize the high-voltage system before working on the compressor. The system must be evacuated, the compressor replaced, and the system recharged with the correct amount of R-1234yf refrigerant.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
         <x:v>0</x:v>
@@ -4335,21 +5091,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="21" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>bmw-7series-n63-turbo-2009</x:v>
+        <x:v>bmw-i3-battery-degradation-2014</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2013-2015 | BMW | 7 Series | N63TU1</x:v>
+        <x:v>2019-2021 | BMW | i3</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>N63TU1 750i Oil-Consumption and Turbo-Leak Diagnosis</x:v>
+        <x:v>2019-2021 i3 High-Voltage Battery Cell Recall 22V-683</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>Confirm the exact chassis, N63TU1 engine, production date, engine serial number, VIN and current eligibility, then follow BMW electronic oil-level measurement and leak-inspection procedures. Repair only the component supported by the documented test result; replace turbochargers only when leakage is confirmed under the current instructions. Do not promise historical settlement coverage. ShowMeTheParts returned six exact 2014 750i/750i xDrive turbo oil-return-line fitments, but catalog fitment does not prove a leak, oil-consumption cause or repair role, so no commerce link is approved.</x:v>
+        <x:v>Check the VIN for an open 22V-683 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy; BMW instructs replacement of the affected battery cell module. Do not buy a battery module or use capacity estimates as a substitute for the VIN recall check. This high-voltage, recall-only path intentionally carries no commerce.</x:v>
       </x:c>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
@@ -4358,21 +5114,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="22" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>bmw-7series-n63-valvetronic-2009</x:v>
+        <x:v>bmw-i3-connectivity-module-2014</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL</x:v>
+        <x:v>2014-2021 | BMW | i3</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>N63 Valvetronic Motor Failure - F01/F02 750i/750Li</x:v>
+        <x:v>i3 ConnectedDrive 3G Sunset: VIN-Specific Eligibility Path</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Replace Valvetronic eccentric shaft motor(s). Often both motors need replacement since wear is similar. Clean carbon buildup from Valvetronic mechanism during repair. N63 Customer Care Package may cover this repair on eligible VINs. Labor is 6-10 hours. Some shops recommend replacing Valvetronic motors preventively at 80,000 miles to avoid being stranded. Extended warranty highly recommended for N63-powered 7 Series.</x:v>
+        <x:v>Check the VIN in BMW AIR/DCSnet or My Garage before choosing a remedy. An early 3G vehicle marked non-eligible cannot be restored by buying the frozen card’s used TCB part. A later campaign-eligible 4G vehicle should receive the BMW programming action that writes the IMS configuration. Confirm current service availability with BMW ConnectedDrive support; do not order a telematics module from model year alone.</x:v>
       </x:c>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
@@ -4381,21 +5137,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="23" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>bmw-8-series-adaptive-suspension-2019</x:v>
+        <x:v>bmw-i3-dc-fast-charge-latch-2014</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2019-2025 | BMW | 8 Series</x:v>
+        <x:v>2014-2014 | BMW | i3</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>Adaptive Suspension Damper Malfunction</x:v>
+        <x:v>2014 i3 Level 2 Charging Delay: KLE Campaign Check</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Replace the failed adaptive damper. BMW's diagnostic system can identify which specific damper has failed through the suspension control module fault memory. The damper must be coded to the vehicle after installation. Replace dampers in pairs (both fronts or both rears) if the vehicle has over 60,000 miles, as the remaining original damper is likely near end of life. Bilstein offers OE-equivalent adaptive dampers at lower cost than BMW parts.</x:v>
+        <x:v>Check the VIN for the KLE service action and read charging and 12V faults with BMW diagnostics. For an open campaign, follow BMW’s KLE replacement and programming procedure. If the 12V battery is discharged, SIB 61 01 15 describes a controlled Level 2 recovery/programming path and says parts replacement does not solve its remaining intermittent delay. Do not drill or lubricate the charge port or buy a latch actuator based on this card.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -4404,21 +5160,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="24" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>bmw-8-series-b58-coolant-loss-2019</x:v>
+        <x:v>bmw-i3-hvac-heater-2014</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2019-2025 | BMW | 8 Series | B58</x:v>
+        <x:v>2014-2021 | BMW | i3</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>B58 Engine Coolant Loss from Expansion Tank and Water Pump</x:v>
+        <x:v>Electric Heater &amp; HVAC System Failures - Range Impact</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with BMW's latest revision. Inspect the electric water pump and all quick-connect coolant fittings for leaks. Pressure test the entire cooling system after repairs. Replace the expansion tank cap as a weak cap allows premature boiling. Use only BMW-approved blue coolant — mixing coolant types causes gel formation.</x:v>
+        <x:v>Electric heater element replacement ($800-1,500). Heat pump compressor replacement uses same compressor as AC system (64529496107) at $1,756-4,000. Blower motor replacement $300-600. HVAC control module reprogramming or replacement $500-1,000. Pre-conditioning the cabin while plugged in (before driving) reduces range impact significantly. Some owners install aftermarket heated seats and steering wheel to reduce HVAC load.</x:v>
       </x:c>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
@@ -4427,21 +5183,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="660" hidden="0" customHeight="1">
+    <x:row r="25" ht="726" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>bmw-8-series-n63-oil-consumption-m850i-2019</x:v>
+        <x:v>bmw-i3-rex-engine-issues-2014</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2019-2025 | BMW | 8 Series | N63TU4, N63</x:v>
+        <x:v>2014-2017 | BMW | i3 | W20 647cc</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>N63/S63 V8 Oil Consumption in M850i</x:v>
+        <x:v>2014-2017 i3 REx Fuel-Vent-Line Recall 17V-088</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>BMW considers up to 1 quart per 1,200 miles as within specification for the N63 family. For excessive consumption beyond that, inspect turbo oil return lines for restriction (causes oil to push past turbo seals), check the crankcase ventilation system, and evaluate valve stem seal condition. The N63TU4 benefits from updated seals and coatings, so consumption rarely reaches the extreme levels of earlier N63 variants.</x:v>
+        <x:v>Check the VIN for an open 17V-088 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy: inspect the fuel tank vent line, replace it if necessary and install the separating clip. Do not substitute a fuel-pump relay, injector cleaner or generic engine parts for the recall. ShowMeTheParts lists 2014 i3 fuel-system categories, but recall inclusion and remedy are VIN/dealer controlled, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -4450,21 +5206,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="26" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>bmw-8series-ibs-failure-2020</x:v>
+        <x:v>bmw-i3-rex-stale-fuel-2014</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2019-2021 | BMW | 8 Series</x:v>
+        <x:v>2014-2021 | BMW | i3 | W20 647cc</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>2019-2021 8 Series Integrated Brake Recall 21V-062</x:v>
+        <x:v>Range Extender Stale Fuel &amp; Engine Problems - I01 REx Only</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-062 campaign and current remedy status with BMW/NHTSA. If the vehicle is included, have an authorized BMW center perform the recall repair at no charge. If brake warnings appear or pedal effort changes, slow safely, avoid hard braking and contact BMW or roadside assistance for direction. ShowMeTheParts resolved exact 2020 840i, 840i xDrive and M850i xDrive brake-hydraulics contexts but returned no brake-booster candidate; recall eligibility and remedy remain dealer-only.</x:v>
+        <x:v>Preventive: Run the REx at least every 6 weeks for a minimum of 10-13 minutes to burn off moisture. Use fuel stabilizer (Sta-Bil) if vehicle sits for extended periods. Keep fuel tank above half to reduce vapor space. For fuel pump relay failure (most common), replace relay ($20-30). For injector issues, professional cleaning or replacement required. For coil failures, replace ignition coils. Maintain regular oil changes with BMW-approved oil despite low mileage. Some owners run premium fuel exclusively to reduce varnish formation.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -4473,21 +5229,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="27" ht="462" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>bmw-8series-n63tu3-timing-chain-2019</x:v>
+        <x:v>bmw-i4-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i</x:v>
+        <x:v>2022-2026 | BMW | i4</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>N63TU3 Timing Chain Guide Wear (M850i)</x:v>
+        <x:v>12V Auxiliary Battery Drain</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain guides, tensioners, and chain at 80,000-100,000 miles ($4,000-$7,500). Turner Motorsport timing chain kit 11317594899KT includes all necessary components. Individual parts: chain guides 11147574373, 11317574397, 11317592850, 11317592877; chain 11317598263. If chain has already skipped: engine damage likely requires $15,000-$25,000 engine replacement. CRITICAL: If you hear cold-start rattling, do NOT drive - tow to shop immediately to prevent catastrophic engine failure.</x:v>
+        <x:v>Ensure the latest software version is installed (BMW has released multiple OTA updates addressing sleep mode behavior). If the problem persists, have the dealer check for parasitic draw using ISTA diagnostics. In severe cases, the 12V battery may need replacement and proper registration.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -4496,21 +5252,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="28" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>bmw-8series-n63tu3-valve-stem-seals-2019</x:v>
+        <x:v>bmw-i4-12v-battery-sleep-mode-2022</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i | N63TU3</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>N63TU3 Valve Stem Seal Failure &amp; Oil Consumption (M850i)</x:v>
+        <x:v>12V Battery Drain - Sleep Mode Failure</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>Replace valve stem seals ($3,500-$10,000 due to labor-intensive hot-V access). Use OEM Victor Reinz seals for durability. Replace spark plugs (Bosch 12120037581) when performing seal replacement. AGA Tools N63 Valve Stem Seal Kit AGA-N63-VSK-K ($500-800) provides specialized tooling for this job. Check VIN eligibility for N63 class action settlement which may cover repair costs. PREVENTIVE: Use quality synthetic oil (BMW LL-01 spec), change every 5,000-7,500 miles, and monitor oil level every 500-1,000 miles on M850i models.</x:v>
+        <x:v>First check for latest software update - BMW has released updates to fix sleep mode bugs. If 12V battery has been deeply discharged, it may need replacement (60Ah AGM). Must register new battery using BimmerLink app (not BimmerCode - BimmerCode cannot register batteries). For vehicles that sit for extended periods, use a BMW-approved battery tender. If CCU is causing the issue, dealer diagnosis and CCU replacement under warranty. The DC-DC converter should maintain 12V charge from the HV battery, so persistent drain indicates a software or CCU hardware fault.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -4519,21 +5275,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="29" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>bmw-8series-premature-tire-wear-2019</x:v>
+        <x:v>bmw-i4-brake-feel-regen-2022</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2019-2024 | BMW | 8 Series</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>Premature Tire Wear (All 8 Series &amp; M8)</x:v>
+        <x:v>Regenerative Braking Pedal Feel Complaints - Grabby/Aggressive</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Get a performance alignment reducing rear camber from factory -2.0 degrees to -1.5 degrees ($150-$300 at alignment shop). This significantly extends rear tire life from 9,000-15,000 miles to 20,000-25,000 miles while maintaining good street handling. Rotate front tires side-to-side every 5,000 miles (staggered setup prevents front-to-rear rotation). Replace rear tires in pairs when worn. COST SAVINGS: Alignment adjustment ($150-300) saves $1,200-2,400 per year in premature tire replacement on expensive performance tires ($300-600 each).</x:v>
+        <x:v>This is a design characteristic of the blended braking system, not a defect per se. Adaptive approaches: Use "D" mode with Adaptive recuperation setting for the most natural brake feel - it adjusts regen based on traffic and road conditions. Avoid "B" mode unless you specifically want strong one-pedal driving. Practice feathering the brake pedal with very light, progressive pressure. Some owners report the brake feel improves slightly with software updates. If braking is truly abnormal (pulsating, grinding), have the integrated brake module checked as that could indicate a hardware issue covered under recall.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
         <x:v>0</x:v>
@@ -4542,21 +5298,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="30" ht="594" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>bmw-8series-zf-8hp-mechatronic-2019</x:v>
+        <x:v>bmw-i4-drivetrain-malfunction-2022</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2023-2023 | BMW | 8 Series</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>2023 8 Series ITCU Recall 23V-821</x:v>
+        <x:v>2022-2025 i4 Propulsion-Loss Recall 25V-395</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-821 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW recall remedy, which replaces the transmission mechatronics module. Do not buy a sleeve kit or change fluid as a substitute for the recall. ShowMeTheParts resolved exact 2023 840i, 840i xDrive and M850i xDrive models but exposed no transmission category or ITCU candidate, and recall repair remains dealer-only.</x:v>
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW’s free electric-drive-motor software update through the authorized dealer or the approved over-the-air recall process. Do not buy gear oil, gaskets or drivetrain parts as a substitute. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -4565,21 +5321,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="31" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>bmw-driveshaft-flex-disc-e90</x:v>
+        <x:v>bmw-i4-heat-pump-cold-weather-2022</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2011-2011 | BMW | 3 Series | N55, N54T, M57Y</x:v>
+        <x:v>2022-2024 | BMW | i4</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>Certain 2011 3 Series Need a Rear-Driveshaft Flex-Disc Recall Check</x:v>
+        <x:v>G26 i4 Coolant Changeover-Valve Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Check the VIN for open recall 17V-067 before authorizing driveline parts. BMW instructs dealers to inspect the installed disc revision index and replace it only when required by the campaign. ShowMeTheParts exposed the exact 2011 335i DRIVE SHAFT category but returned no flex-disc candidate; no commerce link is approved for this recall repair.</x:v>
+        <x:v>Check coolant level, read the exact BMW fault memory and inspect the G26 changeover valve for active or dried leakage. Follow SIB 17 01 24 and VIN-specific AIR/ETK instructions; replace the applicable older-production valve and bleed/test the cooling system with ISTA when the BMW criteria are met. ShowMeTheParts resolves exact 2022 i4 HVAC and water-pump categories but returned no changeover-valve candidate, so the frozen marketplace searches and generic coolant are removed.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -4588,21 +5344,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="32" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>bmw-i3-12v-battery-drain-2014</x:v>
+        <x:v>bmw-i4-heat-pump-malfunction-2022</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2022-2026 | BMW | i4</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>i3 12V Discharge Warning: ISTA Software-First Diagnosis</x:v>
+        <x:v>Heat Pump Malfunction in Cold Weather</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>Read the Check Control Message and fault memory, run BMW ISTA Energy Diagnosis and test the 12V battery before replacing anything. For the Controller condition, BMW says not to replace the Controller; program the vehicle when the measured I-level and diagnostic result meet SIB 61 05 20. For the early REx condition, follow SIB 61 39 14. Replace and register a 12V battery only if separate testing proves it failed. ShowMeTheParts resolved the exact 2014 i3 model but exposed no battery category or defensible 12V candidate, so no commerce link is approved.</x:v>
+        <x:v>BMW has released software updates to improve heat pump operation in cold weather. Visit the dealer for the latest calibration. Some cases require heat pump valve replacement. Pre-conditioning the cabin while plugged in reduces the impact on driving range.</x:v>
       </x:c>
       <x:c r="F32" s="9" t="n">
         <x:v>0</x:v>
@@ -4611,21 +5367,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="33" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>bmw-i3-12v-parasitic-drain-2014</x:v>
+        <x:v>bmw-i4-idrive8-software-bugs-2022</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
+        <x:v>iDrive 8 Software Bugs - Screen Crashes, Reboots &amp; Freezing</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Replace the 12V AGM battery with a fresh unit (OEM or high-quality AGM). Code the new battery using ISTA or BimmerCode to register it with the IBS (Intelligent Battery Sensor). Check for software updates that address module sleep behavior. Some owners install a battery tender for long-term parking.</x:v>
+        <x:v>Ensure vehicle has latest iDrive software via OTA update (Settings &gt; Software Update). Version .63 and later resolved many screen blank/reboot issues. For persistent crashes: Perform soft reset by holding volume knob/power button for 10+ seconds. For factory reset, use Settings &gt; General &gt; Reset to restore defaults. If issues persist after latest OTA, dealer can force-flash the head unit via ISTA. Some owners report that disconnecting phone from wireless CarPlay/Android Auto and using wired connection improves stability. BMW has released multiple major software updates addressing these issues.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -4634,21 +5390,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="34" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>bmw-i3-ac-compressor-black-death-2014</x:v>
+        <x:v>bmw-i4-infotainment-glitches-2022</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2022-2026 | BMW | i4</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>Electric A/C Compressor Catastrophic Failure ("Black Death") - All I01</x:v>
+        <x:v>iDrive 8 Software and Infotainment Glitches</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>If caught early (noise but still functioning), replace compressor before catastrophic failure. Latest OEM compressor: BMW 64529496107 (supersedes 64529320855, 64529343806, 64529347662, 64529364868). FCP Euro price ~$1,756. If metal contamination has occurred, entire system including battery cooling channels must be replaced ($10,600+). MUST use POE (Polyolester) anti-electrostatic compressor oil - standard PAG oil will destroy EV compressors. Independent AC shops that understand EV compressors can save 60-80% vs dealer. RYC Automotive offers remanufactured compressor (RYC-i3-01) as budget option. Aftermarket Nissens condenser ($152) available vs OEM ($581 via FCP Euro).</x:v>
+        <x:v>Keep software up to date via OTA updates or dealer visit. For persistent issues, a full iDrive system reset (Settings &gt; General &gt; Reset) can resolve cached data problems. Some owners have needed the head unit replaced under warranty for hardware-level display faults.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -4657,21 +5413,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="35" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>bmw-i3-ac-compressor-failure-2014</x:v>
+        <x:v>bmw-i4-pedestrian-sound-2022</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2022-2023 | BMW | i4</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>Electric AC Compressor Failure</x:v>
+        <x:v>2022-2023 i4 eDrive40 Sound-Generator Recall 23V-026</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Replace the electric AC compressor assembly. This requires a certified HV-trained technician to safely de-energize the high-voltage system before working on the compressor. The system must be evacuated, the compressor replaced, and the system recharged with the correct amount of R-1234yf refrigerant.</x:v>
+        <x:v>Check the VIN for an open 23V-026 campaign. If included, arrange the free BMW programming remedy for the Receiver Audio Module/external artificial sound generator. Do not replace a speaker or module based only on a missing sound; if the VIN is outside the campaign, diagnose the exact warning and faults separately.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
         <x:v>0</x:v>
@@ -4680,21 +5436,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="36" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>bmw-i3-battery-degradation-2014</x:v>
+        <x:v>bmw-i5-12v-battery-drain-2024</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2019-2021 | BMW | i3</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>2019-2021 i3 High-Voltage Battery Cell Recall 22V-683</x:v>
+        <x:v>12V Auxiliary Battery Drain and Dead Car Syndrome</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>Check the VIN for an open 22V-683 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy; BMW instructs replacement of the affected battery cell module. Do not buy a battery module or use capacity estimates as a substitute for the VIN recall check. This high-voltage, recall-only path intentionally carries no commerce.</x:v>
+        <x:v>Keep the i5 plugged in when parked for extended periods — the HV charger trickle-charges the 12V battery. Install a BMW-recommended battery maintainer connected to the 12V battery (accessible in the right side of the trunk). Update iDrive software to the latest version — BMW has released OTA updates that improve sleep-mode power management. If the 12V battery dies, the manual release cable under the hood allows emergency access.</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -4703,21 +5459,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="37" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>bmw-i3-connectivity-module-2014</x:v>
+        <x:v>bmw-i5-acoustic-pedestrian-warning-sound-generator-fault</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>i3 ConnectedDrive 3G Sunset: VIN-Specific Eligibility Path</x:v>
+        <x:v>2024 i5 Pedestrian Sound Recall 23V-885</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>Check the VIN in BMW AIR/DCSnet or My Garage before choosing a remedy. An early 3G vehicle marked non-eligible cannot be restored by buying the frozen card’s used TCB part. A later campaign-eligible 4G vehicle should receive the BMW programming action that writes the IMS configuration. Confirm current service availability with BMW ConnectedDrive support; do not order a telematics module from model year alone.</x:v>
+        <x:v>Check the VIN for an open 23V-885 campaign. If included, arrange BMW's free software programming remedy through the authorized dealer or the approved recall over-the-air process. Do not replace a speaker or module based only on a missing sound; diagnose vehicles outside the campaign separately.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -4726,21 +5482,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="38" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>bmw-i3-dc-fast-charge-latch-2014</x:v>
+        <x:v>bmw-i5-adaptive-suspension-calibration-2024</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2014-2014 | BMW | i3</x:v>
+        <x:v>2024-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>2014 i3 Level 2 Charging Delay: KLE Campaign Check</x:v>
+        <x:v>Adaptive Suspension Self-Leveling Calibration Errors</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Check the VIN for the KLE service action and read charging and 12V faults with BMW diagnostics. For an open campaign, follow BMW’s KLE replacement and programming procedure. If the 12V battery is discharged, SIB 61 01 15 describes a controlled Level 2 recovery/programming path and says parts replacement does not solve its remaining intermittent delay. Do not drill or lubricate the charge port or buy a latch actuator based on this card.</x:v>
+        <x:v>Perform a suspension calibration reset using BMW ISTA diagnostic software. If the issue persists, inspect the ride height sensors at each corner for damage or loose connectors. A dealer software update may also resolve the issue.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -4749,21 +5505,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="39" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>bmw-i3-hvac-heater-2014</x:v>
+        <x:v>bmw-i5-c-wiring-harness-damaged-during-cabin-filter-service</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2024-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>Electric Heater &amp; HVAC System Failures - Range Impact</x:v>
+        <x:v>2024-2026 i5 A/C Harness Recall 26V-096</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>Electric heater element replacement ($800-1,500). Heat pump compressor replacement uses same compressor as AC system (64529496107) at $1,756-4,000. Blower motor replacement $300-600. HVAC control module reprogramming or replacement $500-1,000. Pre-conditioning the cabin while plugged in (before driving) reduces range impact significantly. Some owners install aftermarket heated seats and steering wheel to reduce HVAC load.</x:v>
+        <x:v>Check the VIN for an open 26V-096 campaign. If included, have an authorized BMW dealer inspect the air-conditioning wiring harness and repair or replace it as required at no charge. Do not probe, splice or order harness parts from this card. If smoke, burning odor or an electrical warning appears, stop using the vehicle and follow BMW emergency guidance.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -4772,21 +5528,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="726" hidden="0" customHeight="1">
+    <x:row r="40" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A40" s="40" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>bmw-i3-rex-engine-issues-2014</x:v>
+        <x:v>bmw-i5-dc-fast-charge-throttling-loud-cooling-fans-repeated-session</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>2014-2017 | BMW | i3 | W20 647cc</x:v>
+        <x:v>2024-2025 | BMW | i5 | eDrive40, xDrive40, M60 xDrive</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>2014-2017 i3 REx Fuel-Vent-Line Recall 17V-088</x:v>
+        <x:v>DC Fast-Charge Throttling and Loud Cooling Fans on Repeated Sessions</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>Check the VIN for an open 17V-088 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy: inspect the fuel tank vent line, replace it if necessary and install the separating clip. Do not substitute a fuel-pump relay, injector cleaner or generic engine parts for the recall. ShowMeTheParts lists 2014 i3 fuel-system categories, but recall inclusion and remedy are VIN/dealer controlled, so no commerce link is approved.</x:v>
+        <x:v>Keep the i5 on the latest software, since BMW has released charging-curve/charging-management updates via OTA and dealer flashes. Precondition the battery before fast charging to reduce throttling, avoid back-to-back DC sessions when possible, and report persistent amp drops or skipped scheduled charges to the dealer (some cases were traced to software faults). Loud thermal-management fan noise is generally normal during/after DC charging.</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
         <x:v>0</x:v>
@@ -4795,21 +5551,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="41" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A41" s="40" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>bmw-i3-rex-stale-fuel-2014</x:v>
+        <x:v>bmw-i5-electric-drive-motor-software-false-isolation-fault-causing</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3 | W20 647cc</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>Range Extender Stale Fuel &amp; Engine Problems - I01 REx Only</x:v>
+        <x:v>2024 i5 Propulsion-Loss Recall 25V-395</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
-        <x:v>Preventive: Run the REx at least every 6 weeks for a minimum of 10-13 minutes to burn off moisture. Use fuel stabilizer (Sta-Bil) if vehicle sits for extended periods. Keep fuel tank above half to reduce vapor space. For fuel pump relay failure (most common), replace relay ($20-30). For injector issues, professional cleaning or replacement required. For coil failures, replace ignition coils. Maintain regular oil changes with BMW-approved oil despite low mileage. Some owners run premium fuel exclusively to reduce varnish formation.</x:v>
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or the approved recall over-the-air process. Do not order drivetrain or battery parts from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the remedy.</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
         <x:v>0</x:v>
@@ -4818,21 +5574,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="462" hidden="0" customHeight="1">
+    <x:row r="42" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A42" s="40" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>bmw-i4-12v-battery-drain-2022</x:v>
+        <x:v>bmw-i5-heat-pump-drip-tube-thunking-clunking-noise</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain</x:v>
+        <x:v>Early-Production G60 i5 Condensation-Drain Drum Noise</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Ensure the latest software version is installed (BMW has released multiple OTA updates addressing sleep mode behavior). If the problem persists, have the dealer check for parasitic draw using ISTA diagnostics. In severe cases, the 12V battery may need replacement and proper registration.</x:v>
+        <x:v>Confirm the production date and reproduce the rhythmic noise under the BMW bulletin conditions. If SIB 64 01 24 applies, an authorized high-voltage-qualified repair facility replaces the condensation-water drain with the optimized part; the procedure requires high-voltage battery removal. Do not cut or modify the drain. ShowMeTheParts resolved the exact 2024 i5 but returned no matching HVAC candidate, so no parts link is approved.</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
         <x:v>0</x:v>
@@ -4841,21 +5597,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="43" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A43" s="40" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>bmw-i4-12v-battery-sleep-mode-2022</x:v>
+        <x:v>bmw-i5-high-voltage-battery-module-insufficient-weld-seams</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>12V Battery Drain - Sleep Mode Failure</x:v>
+        <x:v>Single-Vehicle 2024 i5 Battery-Weld Recall 24V-135</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>First check for latest software update - BMW has released updates to fix sleep mode bugs. If 12V battery has been deeply discharged, it may need replacement (60Ah AGM). Must register new battery using BimmerLink app (not BimmerCode - BimmerCode cannot register batteries). For vehicles that sit for extended periods, use a BMW-approved battery tender. If CCU is causing the issue, dealer diagnosis and CCU replacement under warranty. The DC-DC converter should maintain 12V charge from the HV battery, so persistent drain indicates a software or CCU hardware fault.</x:v>
+        <x:v>Check the VIN for an open 24V-135 campaign. If included, follow BMW's instructions and have the affected high-voltage battery module replaced at no charge by an authorized high-voltage-qualified dealer. Do not open the battery pack or order modules independently; vehicles outside the campaign require separate fault-led diagnosis.</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
         <x:v>0</x:v>
@@ -4864,21 +5620,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="44" ht="528" hidden="0" customHeight="1">
       <x:c r="A44" s="40" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>bmw-i4-brake-feel-regen-2022</x:v>
+        <x:v>bmw-i5-integrated-brake-system-servomotor-weld-failure</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>Regenerative Braking Pedal Feel Complaints - Grabby/Aggressive</x:v>
+        <x:v>2024-2025 i5 Integrated-Brake Recall 24V-697</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>This is a design characteristic of the blended braking system, not a defect per se. Adaptive approaches: Use "D" mode with Adaptive recuperation setting for the most natural brake feel - it adjusts regen based on traffic and road conditions. Avoid "B" mode unless you specifically want strong one-pedal driving. Practice feathering the brake pedal with very light, progressive pressure. Some owners report the brake feel improves slightly with software updates. If braking is truly abnormal (pulsating, grinding), have the integrated brake module checked as that could indicate a hardware issue covered under recall.</x:v>
+        <x:v>Check the VIN for an open 24V-697 campaign. If included, have an authorized BMW dealer replace the integrated brake system at no charge. Do not buy pads, rotors, fluid or a generic actuator as a substitute. If a brake warning or changed pedal effort appears, stop driving when safe and arrange BMW assistance.</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
         <x:v>0</x:v>
@@ -4887,21 +5643,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="594" hidden="0" customHeight="1">
+    <x:row r="45" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A45" s="40" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>bmw-i4-drivetrain-malfunction-2022</x:v>
+        <x:v>bmw-i5-regen-braking-inconsistency-2024</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>2022-2025 i4 Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>Regenerative Braking Inconsistency in Cold Weather</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW’s free electric-drive-motor software update through the authorized dealer or the approved over-the-air recall process. Do not buy gear oil, gaskets or drivetrain parts as a substitute. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+        <x:v>Use the BMW departure timer to precondition the battery before driving — this warms the battery and restores full regen capability from the start. Set the regen level to "Adaptive" instead of "High" in winter, which provides smoother transitions. BMW software updates have improved regen ramping behavior. Rely more on friction brakes during the first 10-15 minutes of cold-weather driving until the battery warms.</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
         <x:v>0</x:v>
@@ -4910,22 +5666,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="46" ht="66" hidden="0" customHeight="1">
       <x:c r="A46" s="40" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>bmw-i4-heat-pump-cold-weather-2022</x:v>
+        <x:v>bmw-i5-software-glitches-2024</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>2022-2024 | BMW | i4</x:v>
+        <x:v>2024-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>G26 i4 Coolant Changeover-Valve Leak Diagnosis</x:v>
-      </x:c>
-      <x:c r="E46" s="9" t="str">
-        <x:v>Check coolant level, read the exact BMW fault memory and inspect the G26 changeover valve for active or dried leakage. Follow SIB 17 01 24 and VIN-specific AIR/ETK instructions; replace the applicable older-production valve and bleed/test the cooling system with ISTA when the BMW criteria are met. ShowMeTheParts resolves exact 2022 i4 HVAC and water-pump categories but returned no changeover-valve candidate, so the frozen marketplace searches and generic coolant are removed.</x:v>
-      </x:c>
+        <x:v>iDrive 8.5 Software Bugs and EV System Errors</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="str"/>
       <x:c r="F46" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4933,22 +5687,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="47" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A47" s="40" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>bmw-i4-heat-pump-malfunction-2022</x:v>
+        <x:v>bmw-i5-software-updates-2025</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2025-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>Heat Pump Malfunction in Cold Weather</x:v>
-      </x:c>
-      <x:c r="E47" s="9" t="str">
-        <x:v>BMW has released software updates to improve heat pump operation in cold weather. Visit the dealer for the latest calibration. Some cases require heat pump valve replacement. Pre-conditioning the cabin while plugged in reduces the impact on driving range.</x:v>
-      </x:c>
+        <x:v>iDrive 9 Software Updates and Calibration Issues</x:v>
+      </x:c>
+      <x:c r="E47" s="9" t="str"/>
       <x:c r="F47" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4956,21 +5708,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="48" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A48" s="40" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>bmw-i4-idrive8-software-bugs-2022</x:v>
+        <x:v>bmw-i5-steering-spindle-double-universal-joint-fracture</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>iDrive 8 Software Bugs - Screen Crashes, Reboots &amp; Freezing</x:v>
+        <x:v>2024-2025 i5 Steering-Spindle Recall 24V-714</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>Ensure vehicle has latest iDrive software via OTA update (Settings &gt; Software Update). Version .63 and later resolved many screen blank/reboot issues. For persistent crashes: Perform soft reset by holding volume knob/power button for 10+ seconds. For factory reset, use Settings &gt; General &gt; Reset to restore defaults. If issues persist after latest OTA, dealer can force-flash the head unit via ISTA. Some owners report that disconnecting phone from wireless CarPlay/Android Auto and using wired connection improves stability. BMW has released multiple major software updates addressing these issues.</x:v>
+        <x:v>Check the VIN for an open 24V-714 campaign. If included, have an authorized BMW dealer replace the steering spindle double universal joint at no charge. Do not order a steering joint from this card. If steering-column noise, notchy steering or increased effort appears, stop driving when safe and arrange BMW assistance.</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
         <x:v>0</x:v>
@@ -4979,22 +5731,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="49" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A49" s="40" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>bmw-i4-infotainment-glitches-2022</x:v>
+        <x:v>bmw-i7-air-suspension-calibration-2023</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2023-2026 | BMW | i7</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>iDrive 8 Software and Infotainment Glitches</x:v>
-      </x:c>
-      <x:c r="E49" s="9" t="str">
-        <x:v>Keep software up to date via OTA updates or dealer visit. For persistent issues, a full iDrive system reset (Settings &gt; General &gt; Reset) can resolve cached data problems. Some owners have needed the head unit replaced under warranty for hardware-level display faults.</x:v>
-      </x:c>
+        <x:v>Air Suspension Calibration and Sensor Issues</x:v>
+      </x:c>
+      <x:c r="E49" s="9" t="str"/>
       <x:c r="F49" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5002,21 +5752,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="50" ht="792" hidden="0" customHeight="1">
       <x:c r="A50" s="40" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>bmw-i4-pedestrian-sound-2022</x:v>
+        <x:v>bmw-i7-autonomous-system-updates-2025</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>2022-2023 | BMW | i4</x:v>
+        <x:v>2023-2024 | BMW | i7</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>2022-2023 i4 eDrive40 Sound-Generator Recall 23V-026</x:v>
+        <x:v>G70 i7 ADCAM Assistance-Limit Diagnosis</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-026 campaign. If included, arrange the free BMW programming remedy for the Receiver Audio Module/external artificial sound generator. Do not replace a speaker or module based only on a missing sound; if the VIN is outside the campaign, diagnose the exact warning and faults separately.</x:v>
+        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather and traffic conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the operating limits in the owner manual. BMW states that parts replacement does not correct environmental system limitations.</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
         <x:v>0</x:v>
@@ -5025,21 +5775,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="51" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A51" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>bmw-i5-12v-battery-drain-2024</x:v>
+        <x:v>bmw-i7-ota-update-failures-2025</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2023-2024 | BMW | i7</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain and Dead Car Syndrome</x:v>
+        <x:v>G70 i7 Comfort-Access Faults after Remote Upgrade</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
-        <x:v>Keep the i5 plugged in when parked for extended periods — the HV charger trickle-charges the 12V battery. Install a BMW-recommended battery maintainer connected to the 12V battery (accessible in the right side of the trunk). Update iDrive software to the latest version — BMW has released OTA updates that improve sleep-mode power management. If the 12V battery dies, the manual release cable under the hood allows emergency access.</x:v>
+        <x:v>Confirm that the complaint followed a BMW Remote Software Upgrade and read the exact BCP faults. Follow SIB 61 11 24 in ISTA to program and pair all FBD5/FBD5s remote-control receivers, clear faults and verify Comfort Access and Passive Go/Exit. Keep phones disconnected during receiver programming. BMW states that parts replacement will not solve this path. ShowMeTheParts resolves the exact 2023 i7 but has no software or receiver repair candidate, so all marketplace links are removed.</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
         <x:v>0</x:v>
@@ -5048,21 +5798,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="52" ht="528" hidden="0" customHeight="1">
       <x:c r="A52" s="40" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>bmw-i5-acoustic-pedestrian-warning-sound-generator-fault</x:v>
+        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2015-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>2024 i5 Pedestrian Sound Recall 23V-885</x:v>
+        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-885 campaign. If included, arrange BMW's free software programming remedy through the authorized dealer or the approved recall over-the-air process. Do not replace a speaker or module based only on a missing sound; diagnose vehicles outside the campaign separately.</x:v>
+        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
         <x:v>0</x:v>
@@ -5071,21 +5821,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="53" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A53" s="40" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>bmw-i5-adaptive-suspension-calibration-2024</x:v>
+        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>Adaptive Suspension Self-Leveling Calibration Errors</x:v>
+        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
-        <x:v>Perform a suspension calibration reset using BMW ISTA diagnostic software. If the issue persists, inspect the ride height sensors at each corner for damage or loose connectors. A dealer software update may also resolve the issue.</x:v>
+        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
         <x:v>0</x:v>
@@ -5094,21 +5844,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="54" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A54" s="40" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>bmw-i5-c-wiring-harness-damaged-during-cabin-filter-service</x:v>
+        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2014-2020 | BMW | i8 | B38</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>2024-2026 i5 A/C Harness Recall 26V-096</x:v>
+        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>Check the VIN for an open 26V-096 campaign. If included, have an authorized BMW dealer inspect the air-conditioning wiring harness and repair or replace it as required at no charge. Do not probe, splice or order harness parts from this card. If smoke, burning odor or an electrical warning appears, stop using the vehicle and follow BMW emergency guidance.</x:v>
+        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
         <x:v>0</x:v>
@@ -5117,21 +5867,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="55" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A55" s="40" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>bmw-i5-dc-fast-charge-throttling-loud-cooling-fans-repeated-session</x:v>
+        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5 | eDrive40, xDrive40, M60 xDrive</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>DC Fast-Charge Throttling and Loud Cooling Fans on Repeated Sessions</x:v>
+        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>Keep the i5 on the latest software, since BMW has released charging-curve/charging-management updates via OTA and dealer flashes. Precondition the battery before fast charging to reduce throttling, avoid back-to-back DC sessions when possible, and report persistent amp drops or skipped scheduled charges to the dealer (some cases were traced to software faults). Loud thermal-management fan noise is generally normal during/after DC charging.</x:v>
+        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
         <x:v>0</x:v>
@@ -5140,21 +5890,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="56" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A56" s="40" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>bmw-i5-electric-drive-motor-software-false-isolation-fault-causing</x:v>
+        <x:v>bmw-i8-charging-port-2014</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>2024 i5 Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or the approved recall over-the-air process. Do not order drivetrain or battery parts from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the remedy.</x:v>
+        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
         <x:v>0</x:v>
@@ -5163,21 +5913,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="57" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A57" s="40" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>bmw-i5-heat-pump-drip-tube-thunking-clunking-noise</x:v>
+        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2014-2015 | BMW | i8</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>Early-Production G60 i5 Condensation-Drain Drum Noise</x:v>
+        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>Confirm the production date and reproduce the rhythmic noise under the BMW bulletin conditions. If SIB 64 01 24 applies, an authorized high-voltage-qualified repair facility replaces the condensation-water drain with the optimized part; the procedure requires high-voltage battery removal. Do not cut or modify the drain. ShowMeTheParts resolved the exact 2024 i5 but returned no matching HVAC candidate, so no parts link is approved.</x:v>
+        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
       </x:c>
       <x:c r="F57" s="9" t="n">
         <x:v>0</x:v>
@@ -5186,21 +5936,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="58" ht="924" hidden="0" customHeight="1">
       <x:c r="A58" s="40" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>bmw-i5-high-voltage-battery-module-insufficient-weld-seams</x:v>
+        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>Single-Vehicle 2024 i5 Battery-Weld Recall 24V-135</x:v>
+        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-135 campaign. If included, follow BMW's instructions and have the affected high-voltage battery module replaced at no charge by an authorized high-voltage-qualified dealer. Do not open the battery pack or order modules independently; vehicles outside the campaign require separate fault-led diagnosis.</x:v>
+        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
       </x:c>
       <x:c r="F58" s="9" t="n">
         <x:v>0</x:v>
@@ -5209,21 +5959,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="528" hidden="0" customHeight="1">
+    <x:row r="59" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A59" s="40" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>bmw-i5-integrated-brake-system-servomotor-weld-failure</x:v>
+        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>2024-2025 i5 Integrated-Brake Recall 24V-697</x:v>
+        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-697 campaign. If included, have an authorized BMW dealer replace the integrated brake system at no charge. Do not buy pads, rotors, fluid or a generic actuator as a substitute. If a brake warning or changed pedal effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
       </x:c>
       <x:c r="F59" s="9" t="n">
         <x:v>0</x:v>
@@ -5237,16 +5987,16 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>bmw-i5-regen-braking-inconsistency-2024</x:v>
+        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2014-2014 | BMW | i8</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>Regenerative Braking Inconsistency in Cold Weather</x:v>
+        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>Use the BMW departure timer to precondition the battery before driving — this warms the battery and restores full regen capability from the start. Set the regen level to "Adaptive" instead of "High" in winter, which provides smoother transitions. BMW software updates have improved regen ramping behavior. Rely more on friction brakes during the first 10-15 minutes of cold-weather driving until the battery warms.</x:v>
+        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
       </x:c>
       <x:c r="F60" s="9" t="n">
         <x:v>0</x:v>
@@ -5255,20 +6005,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="66" hidden="0" customHeight="1">
+    <x:row r="61" ht="726" hidden="0" customHeight="1">
       <x:c r="A61" s="40" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>bmw-i5-software-glitches-2024</x:v>
+        <x:v>bmw-i8-hv-system-faults-2014</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2014-2017 | BMW | i8</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>iDrive 8.5 Software Bugs and EV System Errors</x:v>
-      </x:c>
-      <x:c r="E61" s="9" t="str"/>
+        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
+      </x:c>
+      <x:c r="E61" s="9" t="str">
+        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
+      </x:c>
       <x:c r="F61" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5276,20 +6028,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="62" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A62" s="40" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>bmw-i5-software-updates-2025</x:v>
+        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>2025-2026 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>iDrive 9 Software Updates and Calibration Issues</x:v>
-      </x:c>
-      <x:c r="E62" s="9" t="str"/>
+        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
+      </x:c>
+      <x:c r="E62" s="9" t="str">
+        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
+      </x:c>
       <x:c r="F62" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5297,21 +6051,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="63" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A63" s="40" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>bmw-i5-steering-spindle-double-universal-joint-fracture</x:v>
+        <x:v>bmw-ix-air-suspension-2022</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>2024-2025 i5 Steering-Spindle Recall 24V-714</x:v>
+        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-714 campaign. If included, have an authorized BMW dealer replace the steering spindle double universal joint at no charge. Do not order a steering joint from this card. If steering-column noise, notchy steering or increased effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
       </x:c>
       <x:c r="F63" s="9" t="n">
         <x:v>0</x:v>
@@ -5320,20 +6074,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="64" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A64" s="40" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>bmw-i7-air-suspension-calibration-2023</x:v>
+        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>2023-2026 | BMW | i7</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>Air Suspension Calibration and Sensor Issues</x:v>
-      </x:c>
-      <x:c r="E64" s="9" t="str"/>
+        <x:v>Air Suspension Calibration Errors</x:v>
+      </x:c>
+      <x:c r="E64" s="9" t="str">
+        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
+      </x:c>
       <x:c r="F64" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5341,21 +6097,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="792" hidden="0" customHeight="1">
+    <x:row r="65" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A65" s="40" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>bmw-i7-autonomous-system-updates-2025</x:v>
+        <x:v>bmw-ix-build-quality-2022</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>2023-2024 | BMW | i7</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>G70 i7 ADCAM Assistance-Limit Diagnosis</x:v>
+        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather and traffic conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the operating limits in the owner manual. BMW states that parts replacement does not correct environmental system limitations.</x:v>
+        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
       </x:c>
       <x:c r="F65" s="9" t="n">
         <x:v>0</x:v>
@@ -5364,21 +6120,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="66" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A66" s="40" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>bmw-i7-ota-update-failures-2025</x:v>
+        <x:v>bmw-ix-charging-failures-2022</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>2023-2024 | BMW | i7</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>G70 i7 Comfort-Access Faults after Remote Upgrade</x:v>
+        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>Confirm that the complaint followed a BMW Remote Software Upgrade and read the exact BCP faults. Follow SIB 61 11 24 in ISTA to program and pair all FBD5/FBD5s remote-control receivers, clear faults and verify Comfort Access and Passive Go/Exit. Keep phones disconnected during receiver programming. BMW states that parts replacement will not solve this path. ShowMeTheParts resolves the exact 2023 i7 but has no software or receiver repair candidate, so all marketplace links are removed.</x:v>
+        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
       </x:c>
       <x:c r="F66" s="9" t="n">
         <x:v>0</x:v>
@@ -5387,21 +6143,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="528" hidden="0" customHeight="1">
+    <x:row r="67" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A67" s="40" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
+        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>2015-2020 | BMW | i8</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
+        <x:v>DC Fast Charging Speed Inconsistency</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
-        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
+        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
       </x:c>
       <x:c r="F67" s="9" t="n">
         <x:v>0</x:v>
@@ -5410,21 +6166,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="68" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A68" s="40" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
+        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
+        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
       </x:c>
       <x:c r="F68" s="9" t="n">
         <x:v>0</x:v>
@@ -5433,21 +6189,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="69" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A69" s="40" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
+        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8 | B38</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
+        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
-        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
+        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
       </x:c>
       <x:c r="F69" s="9" t="n">
         <x:v>0</x:v>
@@ -5456,21 +6212,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="70" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A70" s="40" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
+        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
+        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
+        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
       </x:c>
       <x:c r="F70" s="9" t="n">
         <x:v>0</x:v>
@@ -5479,21 +6235,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="71" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A71" s="40" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="9" t="str">
-        <x:v>bmw-i8-charging-port-2014</x:v>
+        <x:v>bmw-ix-phantom-braking-2022</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D71" s="9" t="str">
-        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
+        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
       </x:c>
       <x:c r="E71" s="9" t="str">
-        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
+        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
       </x:c>
       <x:c r="F71" s="9" t="n">
         <x:v>0</x:v>
@@ -5502,21 +6258,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="72" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A72" s="40" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
+        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>2014-2015 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
-        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
+        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
       </x:c>
       <x:c r="E72" s="9" t="str">
-        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
+        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
       </x:c>
       <x:c r="F72" s="9" t="n">
         <x:v>0</x:v>
@@ -5525,21 +6281,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="924" hidden="0" customHeight="1">
+    <x:row r="73" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A73" s="40" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="9" t="str">
-        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
+        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
       </x:c>
       <x:c r="D73" s="9" t="str">
-        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
+        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
-        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
+        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
       </x:c>
       <x:c r="F73" s="9" t="n">
         <x:v>0</x:v>
@@ -5548,21 +6304,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="74" ht="660" hidden="0" customHeight="1">
       <x:c r="A74" s="40" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="9" t="str">
-        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
+        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2021-2021 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
+        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
-        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
+        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
       </x:c>
       <x:c r="F74" s="9" t="n">
         <x:v>0</x:v>
@@ -5571,21 +6327,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="75" ht="528" hidden="0" customHeight="1">
       <x:c r="A75" s="40" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="9" t="str">
-        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
+        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
-        <x:v>2014-2014 | BMW | i8</x:v>
+        <x:v>2021-2021 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D75" s="9" t="str">
-        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
+        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
       </x:c>
       <x:c r="E75" s="9" t="str">
-        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
+        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
       </x:c>
       <x:c r="F75" s="9" t="n">
         <x:v>0</x:v>
@@ -5594,21 +6350,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="726" hidden="0" customHeight="1">
+    <x:row r="76" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A76" s="40" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="9" t="str">
-        <x:v>bmw-i8-hv-system-faults-2014</x:v>
+        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
-        <x:v>2014-2017 | BMW | i8</x:v>
+        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
       </x:c>
       <x:c r="D76" s="9" t="str">
-        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
+        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
       </x:c>
       <x:c r="E76" s="9" t="str">
-        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
+        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
       </x:c>
       <x:c r="F76" s="9" t="n">
         <x:v>0</x:v>
@@ -5617,21 +6373,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="77" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A77" s="40" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="9" t="str">
-        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
+        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
+        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
       </x:c>
       <x:c r="E77" s="9" t="str">
-        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
+        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
       </x:c>
       <x:c r="F77" s="9" t="n">
         <x:v>0</x:v>
@@ -5640,21 +6396,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="78" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A78" s="40" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-2022</x:v>
+        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
+        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
       </x:c>
       <x:c r="E78" s="9" t="str">
-        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
+        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
       </x:c>
       <x:c r="F78" s="9" t="n">
         <x:v>0</x:v>
@@ -5663,21 +6419,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="79" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A79" s="40" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
+        <x:v>bmw-m2-charge-pipe-2016</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D79" s="9" t="str">
-        <x:v>Air Suspension Calibration Errors</x:v>
+        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
       </x:c>
       <x:c r="E79" s="9" t="str">
-        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
+        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
       </x:c>
       <x:c r="F79" s="9" t="n">
         <x:v>0</x:v>
@@ -5686,21 +6442,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="80" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A80" s="40" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="9" t="str">
-        <x:v>bmw-ix-build-quality-2022</x:v>
+        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2019-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
-        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
       </x:c>
       <x:c r="E80" s="9" t="str">
-        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
       </x:c>
       <x:c r="F80" s="9" t="n">
         <x:v>0</x:v>
@@ -5709,21 +6465,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="81" ht="726" hidden="0" customHeight="1">
       <x:c r="A81" s="40" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="9" t="str">
-        <x:v>bmw-ix-charging-failures-2022</x:v>
+        <x:v>bmw-m2-cooling-system-2016</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2016-2020 | BMW | M2 | S55</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
-        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
-        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
+        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F81" s="9" t="n">
         <x:v>0</x:v>
@@ -5732,21 +6488,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="82" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A82" s="40" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
+        <x:v>bmw-m2-dct-clutch-2016</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2016-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
-        <x:v>DC Fast Charging Speed Inconsistency</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E82" s="9" t="str">
-        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
+        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
       </x:c>
       <x:c r="F82" s="9" t="n">
         <x:v>0</x:v>
@@ -5755,21 +6511,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="83" ht="462" hidden="0" customHeight="1">
       <x:c r="A83" s="40" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
+        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2016-2021 | BMW | M2</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
       </x:c>
       <x:c r="F83" s="9" t="n">
         <x:v>0</x:v>
@@ -5778,21 +6534,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="84" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A84" s="40" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
+        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2016-2018 | BMW | M2 | N55</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
-        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
+        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
+        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
       </x:c>
       <x:c r="F84" s="9" t="n">
         <x:v>0</x:v>
@@ -5801,21 +6557,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="85" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A85" s="40" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="9" t="str">
-        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
+        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D85" s="9" t="str">
-        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
+        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
       </x:c>
       <x:c r="E85" s="9" t="str">
-        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
       </x:c>
       <x:c r="F85" s="9" t="n">
         <x:v>0</x:v>
@@ -5824,21 +6580,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="86" ht="858" hidden="0" customHeight="1">
       <x:c r="A86" s="40" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="9" t="str">
-        <x:v>bmw-ix-phantom-braking-2022</x:v>
+        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
-        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
+        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
-        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
+        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
       </x:c>
       <x:c r="F86" s="9" t="n">
         <x:v>0</x:v>
@@ -5847,21 +6603,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="87" ht="462" hidden="0" customHeight="1">
       <x:c r="A87" s="40" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
+        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
-        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
+        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
       </x:c>
       <x:c r="F87" s="9" t="n">
         <x:v>0</x:v>
@@ -5870,21 +6626,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="88" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A88" s="40" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="9" t="str">
-        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
+        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
-        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D88" s="9" t="str">
-        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E88" s="9" t="str">
-        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
+        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
       </x:c>
       <x:c r="F88" s="9" t="n">
         <x:v>0</x:v>
@@ -5893,21 +6649,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="660" hidden="0" customHeight="1">
+    <x:row r="89" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A89" s="40" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
+        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
+        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
+        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
       </x:c>
       <x:c r="F89" s="9" t="n">
         <x:v>0</x:v>
@@ -5921,16 +6677,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" s="9" t="str">
-        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
+        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
       </x:c>
       <x:c r="D90" s="9" t="str">
-        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
+        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
       </x:c>
       <x:c r="E90" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
+        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
       </x:c>
       <x:c r="F90" s="9" t="n">
         <x:v>0</x:v>
@@ -5939,21 +6695,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="91" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A91" s="40" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" s="9" t="str">
-        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
+        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
-        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D91" s="9" t="str">
-        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
+        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
       </x:c>
       <x:c r="E91" s="9" t="str">
-        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
+        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
       </x:c>
       <x:c r="F91" s="9" t="n">
         <x:v>0</x:v>
@@ -5962,21 +6718,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="92" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A92" s="40" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" s="9" t="str">
-        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
+        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
-        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
+        <x:v>Rear Subframe Mounting Point Cracking</x:v>
       </x:c>
       <x:c r="E92" s="9" t="str">
-        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
+        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
       </x:c>
       <x:c r="F92" s="9" t="n">
         <x:v>0</x:v>
@@ -5985,21 +6741,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="93" ht="594" hidden="0" customHeight="1">
       <x:c r="A93" s="40" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" s="9" t="str">
-        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
+        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
-        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
+        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
       </x:c>
       <x:c r="E93" s="9" t="str">
-        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
+        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
       </x:c>
       <x:c r="F93" s="9" t="n">
         <x:v>0</x:v>
@@ -6008,21 +6764,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="94" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A94" s="40" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>bmw-m2-charge-pipe-2016</x:v>
+        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
+        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
-        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
+        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
       </x:c>
       <x:c r="F94" s="9" t="n">
         <x:v>0</x:v>
@@ -6031,21 +6787,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="95" ht="396" hidden="0" customHeight="1">
       <x:c r="A95" s="40" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="9" t="str">
-        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
+        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
-        <x:v>2019-2020 | BMW | M2</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D95" s="9" t="str">
-        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
+        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
       </x:c>
       <x:c r="E95" s="9" t="str">
-        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
+        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
       </x:c>
       <x:c r="F95" s="9" t="n">
         <x:v>0</x:v>
@@ -6054,21 +6810,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="726" hidden="0" customHeight="1">
+    <x:row r="96" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A96" s="40" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" s="9" t="str">
-        <x:v>bmw-m2-cooling-system-2016</x:v>
+        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2 | S55</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
+        <x:v>EDC Electronic Damper Control System Failure</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
-        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
+        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
       </x:c>
       <x:c r="F96" s="9" t="n">
         <x:v>0</x:v>
@@ -6077,21 +6833,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="97" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A97" s="40" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" s="9" t="str">
-        <x:v>bmw-m2-dct-clutch-2016</x:v>
+        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2</x:v>
+        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
       </x:c>
       <x:c r="D97" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
+        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
       </x:c>
       <x:c r="E97" s="9" t="str">
-        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
+        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
       </x:c>
       <x:c r="F97" s="9" t="n">
         <x:v>0</x:v>
@@ -6100,21 +6856,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="462" hidden="0" customHeight="1">
+    <x:row r="98" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A98" s="40" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" s="9" t="str">
-        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
+        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
-        <x:v>2016-2021 | BMW | M2</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D98" s="9" t="str">
-        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
+        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
       </x:c>
       <x:c r="E98" s="9" t="str">
-        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
+        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
       </x:c>
       <x:c r="F98" s="9" t="n">
         <x:v>0</x:v>
@@ -6123,21 +6879,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="99" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A99" s="40" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" s="9" t="str">
-        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
+        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
-        <x:v>2016-2018 | BMW | M2 | N55</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D99" s="9" t="str">
-        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
+        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E99" s="9" t="str">
-        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
+        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
       </x:c>
       <x:c r="F99" s="9" t="n">
         <x:v>0</x:v>
@@ -6146,21 +6902,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="100" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A100" s="40" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" s="9" t="str">
-        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
+        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D100" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
+        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E100" s="9" t="str">
-        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
+        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
       </x:c>
       <x:c r="F100" s="9" t="n">
         <x:v>0</x:v>
@@ -6169,21 +6925,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="858" hidden="0" customHeight="1">
+    <x:row r="101" ht="660" hidden="0" customHeight="1">
       <x:c r="A101" s="40" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" s="9" t="str">
-        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
+        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
       </x:c>
       <x:c r="C101" s="9" t="str">
-        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D101" s="9" t="str">
-        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
+        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
       </x:c>
       <x:c r="E101" s="9" t="str">
-        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
+        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
       </x:c>
       <x:c r="F101" s="9" t="n">
         <x:v>0</x:v>
@@ -6192,21 +6948,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="462" hidden="0" customHeight="1">
+    <x:row r="102" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A102" s="40" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B102" s="9" t="str">
-        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
+        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D102" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
       </x:c>
       <x:c r="E102" s="9" t="str">
-        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
+        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
       </x:c>
       <x:c r="F102" s="9" t="n">
         <x:v>0</x:v>
@@ -6215,21 +6971,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="103" ht="726" hidden="0" customHeight="1">
       <x:c r="A103" s="40" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B103" s="9" t="str">
-        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
+        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C103" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D103" s="9" t="str">
-        <x:v>VANOS Solenoid O-Ring Failure</x:v>
+        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
       </x:c>
       <x:c r="E103" s="9" t="str">
-        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
+        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
       </x:c>
       <x:c r="F103" s="9" t="n">
         <x:v>0</x:v>
@@ -6238,44 +6994,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="104" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A104" s="40" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
+        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
+        <x:v>2015-2018 | BMW | M3</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
-        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
+        <x:v>Direct Fuel Injector Failure (S55)</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
-        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
+        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
       </x:c>
       <x:c r="F104" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G104" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="528" hidden="0" customHeight="1">
+    <x:row r="105" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A105" s="40" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B105" s="9" t="str">
-        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
+        <x:v>bmw-m3-f80-water-pump-2015</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D105" s="9" t="str">
-        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
+        <x:v>Electric Water Pump Failure (S55)</x:v>
       </x:c>
       <x:c r="E105" s="9" t="str">
-        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
+        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
       </x:c>
       <x:c r="F105" s="9" t="n">
         <x:v>0</x:v>
@@ -6284,21 +7040,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="106" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A106" s="40" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B106" s="9" t="str">
-        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
+        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D106" s="9" t="str">
-        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
+        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
       </x:c>
       <x:c r="E106" s="9" t="str">
-        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
+        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
       </x:c>
       <x:c r="F106" s="9" t="n">
         <x:v>0</x:v>
@@ -6307,21 +7063,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="107" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A107" s="40" t="n">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B107" s="9" t="str">
-        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
+        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
       </x:c>
       <x:c r="C107" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D107" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracking</x:v>
+        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
       </x:c>
       <x:c r="E107" s="9" t="str">
-        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
+        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
       </x:c>
       <x:c r="F107" s="9" t="n">
         <x:v>0</x:v>
@@ -6330,21 +7086,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="594" hidden="0" customHeight="1">
+    <x:row r="108" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A108" s="40" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B108" s="9" t="str">
-        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
+        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D108" s="9" t="str">
-        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
+        <x:v>Coolant System Issues (S58)</x:v>
       </x:c>
       <x:c r="E108" s="9" t="str">
-        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
+        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
       </x:c>
       <x:c r="F108" s="9" t="n">
         <x:v>0</x:v>
@@ -6353,21 +7109,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="109" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A109" s="40" t="n">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B109" s="9" t="str">
-        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
+        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D109" s="9" t="str">
-        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
+        <x:v>iDrive 8 Software/Electronics Issues</x:v>
       </x:c>
       <x:c r="E109" s="9" t="str">
-        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
+        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
       </x:c>
       <x:c r="F109" s="9" t="n">
         <x:v>0</x:v>
@@ -6376,21 +7132,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="396" hidden="0" customHeight="1">
+    <x:row r="110" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A110" s="40" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
+        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>2021-2021 | BMW | M3</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
+        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
-        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
+        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
       </x:c>
       <x:c r="F110" s="9" t="n">
         <x:v>0</x:v>
@@ -6404,16 +7160,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B111" s="9" t="str">
-        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
+        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
-        <x:v>EDC Electronic Damper Control System Failure</x:v>
+        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E111" s="9" t="str">
-        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
+        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
       </x:c>
       <x:c r="F111" s="9" t="n">
         <x:v>0</x:v>
@@ -6422,21 +7178,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="112" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A112" s="40" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
+        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
+        <x:v>Power window regulator failure and interior trim rattles</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
-        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
+        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
       </x:c>
       <x:c r="F112" s="9" t="n">
         <x:v>0</x:v>
@@ -6445,21 +7201,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="884.4000244140625" hidden="0" customHeight="1">
+    <x:row r="113" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A113" s="40" t="n">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B113" s="9" t="str">
-        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
+        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
-        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
+        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
-        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
+        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
       </x:c>
       <x:c r="F113" s="9" t="n">
         <x:v>0</x:v>
@@ -6468,21 +7224,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="114" ht="343.20001220703125" hidden="0" customHeight="1">
       <x:c r="A114" s="40" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B114" s="9" t="str">
-        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
+        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
-        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
+        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
-        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
+        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
       </x:c>
       <x:c r="F114" s="9" t="n">
         <x:v>0</x:v>
@@ -6491,21 +7247,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="115" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A115" s="40" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B115" s="9" t="str">
-        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
+        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
       </x:c>
       <x:c r="C115" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D115" s="9" t="str">
-        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
+        <x:v>S55 Crank Hub Slip/Failure</x:v>
       </x:c>
       <x:c r="E115" s="9" t="str">
-        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
+        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
       </x:c>
       <x:c r="F115" s="9" t="n">
         <x:v>0</x:v>
@@ -6514,21 +7270,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="660" hidden="0" customHeight="1">
+    <x:row r="116" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A116" s="40" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B116" s="9" t="str">
-        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
+        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
       </x:c>
       <x:c r="C116" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
       </x:c>
       <x:c r="D116" s="9" t="str">
-        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
+        <x:v>S55/S58 Electric Water Pump Failure</x:v>
       </x:c>
       <x:c r="E116" s="9" t="str">
-        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
+        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
       </x:c>
       <x:c r="F116" s="9" t="n">
         <x:v>0</x:v>
@@ -6537,21 +7293,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="117" ht="462" hidden="0" customHeight="1">
       <x:c r="A117" s="40" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B117" s="9" t="str">
-        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
+        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
+        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
-        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
+        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
       </x:c>
       <x:c r="F117" s="9" t="n">
         <x:v>0</x:v>
@@ -6560,21 +7316,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="726" hidden="0" customHeight="1">
+    <x:row r="118" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A118" s="40" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B118" s="9" t="str">
-        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
+        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
-        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
+        <x:v>S65 Throttle Body Actuator Failure</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
-        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
+        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
       </x:c>
       <x:c r="F118" s="9" t="n">
         <x:v>0</x:v>
@@ -6583,44 +7339,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="119" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A119" s="40" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B119" s="9" t="str">
-        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
+        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
       </x:c>
       <x:c r="C119" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>Direct Fuel Injector Failure (S55)</x:v>
+        <x:v>VANOS Solenoid Wear and Failure</x:v>
       </x:c>
       <x:c r="E119" s="9" t="str">
-        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
+        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
       </x:c>
       <x:c r="F119" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G119" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="120" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A120" s="40" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B120" s="9" t="str">
-        <x:v>bmw-m3-f80-water-pump-2015</x:v>
+        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
       </x:c>
       <x:c r="C120" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D120" s="9" t="str">
-        <x:v>Electric Water Pump Failure (S55)</x:v>
+        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
       </x:c>
       <x:c r="E120" s="9" t="str">
-        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
+        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals, often combined with an anti-rattle kit that addresses the cam-gear/shaft play. DIY on the seal kit is common; specialists also offer fully rebuilt exchange units.</x:v>
       </x:c>
       <x:c r="F120" s="9" t="n">
         <x:v>0</x:v>
@@ -6629,21 +7385,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="121" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A121" s="40" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B121" s="9" t="str">
-        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
+        <x:v>bmw-m3-worn-rear-trailing-arm-bushings-suspension-mounts</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
-        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
+        <x:v>Worn rear trailing arm bushings (RTAB) and suspension mounts</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
-        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
+        <x:v>Replace the RTABs with genuine BMW rubber bushings or upgraded poly/spherical bushings; many owners add RTAB limiter kits to reduce deflection. Inspect and renew rear shock mounts and engine/transmission mounts at the same time. The RTAB job is a common DIY that can be done with the trailing arms on the car.</x:v>
       </x:c>
       <x:c r="F121" s="9" t="n">
         <x:v>0</x:v>
@@ -6652,21 +7408,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="122" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A122" s="40" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B122" s="9" t="str">
-        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
+        <x:v>bmw-m340i-12v-battery-drain-failure-battery-registration-issues</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2019-2024 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D122" s="9" t="str">
-        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
+        <x:v>12V Battery Drain and Failure / Battery Registration Issues</x:v>
       </x:c>
       <x:c r="E122" s="9" t="str">
-        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
+        <x:v>Test and replace the AGM battery with the correct OEM-spec unit, then register the new battery with BimmerLink/ISTA so the charging strategy adapts. Diagnose parasitic drain and a faulty IBS cable/sensor if discharge persists. Drive long enough to fully recharge between trips.</x:v>
       </x:c>
       <x:c r="F122" s="9" t="n">
         <x:v>0</x:v>
@@ -6675,21 +7431,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="123" ht="528" hidden="0" customHeight="1">
       <x:c r="A123" s="40" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B123" s="9" t="str">
-        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
+        <x:v>bmw-m340i-b58-carbon-buildup-2020</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D123" s="9" t="str">
-        <x:v>Coolant System Issues (S58)</x:v>
+        <x:v>Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E123" s="9" t="str">
-        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
+        <x:v>Walnut blast the intake valves every 50,000-60,000 miles. This involves removing the intake manifold and blasting walnut shell media at the valve backs to remove carbon deposits. Some owners use catch cans to reduce oil vapor entering the intake. BMW's official position is that carbon buildup is normal for direct-injection engines.</x:v>
       </x:c>
       <x:c r="F123" s="9" t="n">
         <x:v>0</x:v>
@@ -6703,16 +7459,16 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B124" s="9" t="str">
-        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
+        <x:v>bmw-m340i-b58-coolant-loss-2020</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D124" s="9" t="str">
-        <x:v>iDrive 8 Software/Electronics Issues</x:v>
+        <x:v>Coolant Loss from Expansion Tank and Water Pump</x:v>
       </x:c>
       <x:c r="E124" s="9" t="str">
-        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
+        <x:v>Replace the coolant expansion tank at first sign of cracking. Proactively replace the electric water pump before 60,000 miles. Replace the coolant vent line per BMW TSB. Use only BMW-approved blue coolant. Monitor coolant level monthly and pressure test the cooling system at every major service.</x:v>
       </x:c>
       <x:c r="F124" s="9" t="n">
         <x:v>0</x:v>
@@ -6721,21 +7477,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="125" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A125" s="40" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B125" s="9" t="str">
-        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
+        <x:v>bmw-m340i-b58-hpfp-failure-2020</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
-        <x:v>2021-2021 | BMW | M3</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D125" s="9" t="str">
-        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
       </x:c>
       <x:c r="E125" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
+        <x:v>Replace the high-pressure fuel pump with the latest revised BMW part number. Verify the low-pressure fuel pump is providing adequate feed pressure. Use top-tier fuel and avoid running the tank below 1/4 to reduce strain on the fuel system. If under warranty, BMW will cover HPFP replacement.</x:v>
       </x:c>
       <x:c r="F125" s="9" t="n">
         <x:v>0</x:v>
@@ -6744,21 +7500,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="126" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A126" s="40" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
+        <x:v>bmw-m340i-b58-oil-filter-disintegration-2020</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6, B58</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
-        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
+        <x:v>Oil Filter Disintegration in Housing</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
+        <x:v>Use only genuine BMW or Mann-branded oil filters (Mann is the OEM supplier). Change oil and filter every 5,000-7,000 miles rather than BMW's recommended 10,000-mile interval. When removing the old filter, inspect it carefully for signs of deterioration. If filter fragments are found in the housing, flush the housing thoroughly before installing the new filter.</x:v>
       </x:c>
       <x:c r="F126" s="9" t="n">
         <x:v>0</x:v>
@@ -6767,21 +7523,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="127" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A127" s="40" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B127" s="9" t="str">
-        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
+        <x:v>bmw-m340i-b58-wastegate-rattle-2020</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>Power window regulator failure and interior trim rattles</x:v>
+        <x:v>Turbo Wastegate Rattle at Idle</x:v>
       </x:c>
       <x:c r="E127" s="9" t="str">
-        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
+        <x:v>Have the wastegate actuator inspected for excessive play. Minor rattle without fault codes can be monitored. If boost control faults develop, replace the turbocharger wastegate actuator. In severe cases, the entire turbocharger assembly may need replacement. BMW may cover under warranty if fault codes are present.</x:v>
       </x:c>
       <x:c r="F127" s="9" t="n">
         <x:v>0</x:v>
@@ -6790,21 +7546,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="128" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A128" s="40" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B128" s="9" t="str">
-        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
+        <x:v>bmw-m340i-loss-brake-assist-from-brake-vacuum-pump-damage</x:v>
       </x:c>
       <x:c r="C128" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2020-2020 | BMW | M340i | B58 3.0L turbo inline-six</x:v>
       </x:c>
       <x:c r="D128" s="9" t="str">
-        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
+        <x:v>2020 M340i Brake-Assist Recall 21V-598</x:v>
       </x:c>
       <x:c r="E128" s="9" t="str">
-        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
+        <x:v>Check the VIN for an open 21V-598 campaign. An authorized BMW dealer updates the engine-management software free of charge and replaces the combined oil/vacuum pump if diagnosis shows it was already damaged. Do not order generic brake-vacuum parts from this card.</x:v>
       </x:c>
       <x:c r="F128" s="9" t="n">
         <x:v>0</x:v>
@@ -6813,21 +7569,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="129" ht="462" hidden="0" customHeight="1">
       <x:c r="A129" s="40" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B129" s="9" t="str">
-        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
+        <x:v>bmw-m340i-seat-belt-warning-audio-failure</x:v>
       </x:c>
       <x:c r="C129" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2019-2022 | BMW | M340i</x:v>
       </x:c>
       <x:c r="D129" s="9" t="str">
-        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
+        <x:v>2019-2022 M340i Seat-Belt Warning Recall 23V-584</x:v>
       </x:c>
       <x:c r="E129" s="9" t="str">
-        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
+        <x:v>Check the VIN for an open 23V-584 campaign. An authorized BMW dealer installs updated Receiver Audio Module software free of charge; eligible vehicles may also receive the remedy by BMW Remote Software Upgrade. Always use the seat belt regardless of warning-chime behavior.</x:v>
       </x:c>
       <x:c r="F129" s="9" t="n">
         <x:v>0</x:v>
@@ -6836,21 +7592,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="130" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A130" s="40" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B130" s="9" t="str">
-        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
+        <x:v>bmw-m340i-valve-cover-oil-filter-housing-gasket-oil-leaks</x:v>
       </x:c>
       <x:c r="C130" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D130" s="9" t="str">
-        <x:v>S55 Crank Hub Slip/Failure</x:v>
+        <x:v>Valve Cover and Oil Filter Housing Gasket Oil Leaks (B58)</x:v>
       </x:c>
       <x:c r="E130" s="9" t="str">
-        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
+        <x:v>Replace the valve cover gasket and/or oil filter housing gasket. Many shops also replace the valve cover itself if it has warped. Clean any oil from spark-plug wells and inspect coils. Typical independent-shop cost is roughly $400-$900 depending on which gasket(s) and labor access.</x:v>
       </x:c>
       <x:c r="F130" s="9" t="n">
         <x:v>0</x:v>
@@ -6859,21 +7615,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="131" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A131" s="40" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B131" s="9" t="str">
-        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
+        <x:v>bmw-m340i-vanos-solenoid-o-ring-failure</x:v>
       </x:c>
       <x:c r="C131" s="9" t="str">
-        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D131" s="9" t="str">
-        <x:v>S55/S58 Electric Water Pump Failure</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E131" s="9" t="str">
-        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
+        <x:v>Diagnose with a scan tool (VANOS/camshaft position fault codes), then replace the affected intake/exhaust VANOS solenoid(s) and O-rings. Solenoids are relatively inexpensive parts; cost is mostly diagnosis and labor, typically a few hundred dollars.</x:v>
       </x:c>
       <x:c r="F131" s="9" t="n">
         <x:v>0</x:v>
@@ -6882,21 +7638,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="462" hidden="0" customHeight="1">
+    <x:row r="132" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A132" s="40" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B132" s="9" t="str">
-        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
+        <x:v>bmw-m340i-zf-8hp-harsh-jerky-low-speed-shifting-mechatronic-faults</x:v>
       </x:c>
       <x:c r="C132" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D132" s="9" t="str">
-        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
+        <x:v>ZF 8HP Harsh / Jerky Low-Speed Shifting and Mechatronic Faults</x:v>
       </x:c>
       <x:c r="E132" s="9" t="str">
-        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
+        <x:v>Perform the ZF 8-speed fluid-and-filter (pan) service rather than treating it as lifetime-fill; this resolves many shift-quality complaints. Let the drivetrain warm before hard driving. For persistent erratic shifting or warning lights, scan the transmission and repair/replace the mechatronic unit (valve body) as needed.</x:v>
       </x:c>
       <x:c r="F132" s="9" t="n">
         <x:v>0</x:v>
@@ -6905,21 +7661,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="133" ht="594" hidden="0" customHeight="1">
       <x:c r="A133" s="40" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B133" s="9" t="str">
-        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
+        <x:v>bmw-m3cs-idrive-software-2024</x:v>
       </x:c>
       <x:c r="C133" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D133" s="9" t="str">
-        <x:v>S65 Throttle Body Actuator Failure</x:v>
+        <x:v>iDrive 8 Software Glitches and Screen Blackouts</x:v>
       </x:c>
       <x:c r="E133" s="9" t="str">
-        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
+        <x:v>Check for and install the latest BMW iDrive 8 software updates, which can be delivered over-the-air or at a dealer. Perform a soft reset by holding the iDrive controller button for 30 seconds. If screen blackouts persist, the dealer may need to replace the head unit or update the gateway module firmware. Ensure the 12V battery is in good condition, as low voltage can trigger software instability.</x:v>
       </x:c>
       <x:c r="F133" s="9" t="n">
         <x:v>0</x:v>
@@ -6928,21 +7684,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="250.8000030517578" hidden="0" customHeight="1">
+    <x:row r="134" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A134" s="40" t="n">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B134" s="9" t="str">
-        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
+        <x:v>bmw-m3cs-s58-carbon-buildup-2024</x:v>
       </x:c>
       <x:c r="C134" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D134" s="9" t="str">
-        <x:v>VANOS Solenoid Wear and Failure</x:v>
+        <x:v>S58 Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E134" s="9" t="str">
-        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
+        <x:v>Schedule walnut blast cleaning of the intake valves at 40,000-50,000 mile intervals. Install an oil catch can to reduce oil vapor entering the intake system. Use high-quality synthetic oil meeting BMW LL-01 specification and change at 5,000-7,000 mile intervals. Allow the engine to fully warm up before high-boost driving to ensure proper oil vapor management.</x:v>
       </x:c>
       <x:c r="F134" s="9" t="n">
         <x:v>0</x:v>
@@ -6951,21 +7707,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="135" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A135" s="40" t="n">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B135" s="9" t="str">
-        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
+        <x:v>bmw-m3cs-s58-charge-pipe-crack-2024</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
-        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D135" s="9" t="str">
-        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
+        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
       </x:c>
       <x:c r="E135" s="9" t="str">
-        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals, often combined with an anti-rattle kit that addresses the cam-gear/shaft play. DIY on the seal kit is common; specialists also offer fully rebuilt exchange units.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF. These direct-fit replacements handle higher temperatures and pressures without risk of cracking. If the car is under warranty and the failure occurs on stock tune, BMW should cover the repair. Inspect the charge pipe during every service and before track days.</x:v>
       </x:c>
       <x:c r="F135" s="9" t="n">
         <x:v>0</x:v>
@@ -6974,21 +7730,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="136" ht="396" hidden="0" customHeight="1">
       <x:c r="A136" s="40" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B136" s="9" t="str">
-        <x:v>bmw-m3-worn-rear-trailing-arm-bushings-suspension-mounts</x:v>
+        <x:v>bmw-m4-charge-pipe-blowoff-2015</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D136" s="9" t="str">
-        <x:v>Worn rear trailing arm bushings (RTAB) and suspension mounts</x:v>
+        <x:v>Plastic Charge Pipe Blow-Off Under Boost</x:v>
       </x:c>
       <x:c r="E136" s="9" t="str">
-        <x:v>Replace the RTABs with genuine BMW rubber bushings or upgraded poly/spherical bushings; many owners add RTAB limiter kits to reduce deflection. Inspect and renew rear shock mounts and engine/transmission mounts at the same time. The RTAB job is a common DIY that can be done with the trailing arms on the car.</x:v>
+        <x:v>Replace with an aluminum or silicone charge pipe. This is considered a must-do upgrade for any F82 M4. Many aftermarket options are direct bolt-on replacements. The job takes about 1-2 hours and requires removing the intake duct to access the charge pipe.</x:v>
       </x:c>
       <x:c r="F136" s="9" t="n">
         <x:v>0</x:v>
@@ -6997,21 +7753,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="137" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A137" s="40" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B137" s="9" t="str">
-        <x:v>bmw-m340i-12v-battery-drain-failure-battery-registration-issues</x:v>
+        <x:v>bmw-m4-convertible-top-2015</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
-        <x:v>2019-2024 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D137" s="9" t="str">
-        <x:v>12V Battery Drain and Failure / Battery Registration Issues</x:v>
+        <x:v>Convertible Top Hydraulic Pump Failure - F83 M4 Convertible</x:v>
       </x:c>
       <x:c r="E137" s="9" t="str">
-        <x:v>Test and replace the AGM battery with the correct OEM-spec unit, then register the new battery with BimmerLink/ISTA so the charging strategy adapts. Diagnose parasitic drain and a faulty IBS cable/sensor if discharge persists. Drive long enough to fully recharge between trips.</x:v>
+        <x:v>Diagnose specific failure: hydraulic pump motor, lines, microswitches, or latch mechanisms. Pump motor replacement is most common ($1,500-2,500). Check hydraulic fluid level and refill if low. Regular top cycling (minimum once per month) prevents seal degradation. Store with top UP to reduce strain on hydraulic system. Rebuilt hydraulic pumps available at lower cost than new OEM. Complex repair requiring specialized BMW knowledge.</x:v>
       </x:c>
       <x:c r="F137" s="9" t="n">
         <x:v>0</x:v>
@@ -7020,21 +7776,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="528" hidden="0" customHeight="1">
+    <x:row r="138" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A138" s="40" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B138" s="9" t="str">
-        <x:v>bmw-m340i-b58-carbon-buildup-2020</x:v>
+        <x:v>bmw-m4-cooling-track-2015</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D138" s="9" t="str">
-        <x:v>Intake Valve Carbon Buildup</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E138" s="9" t="str">
-        <x:v>Walnut blast the intake valves every 50,000-60,000 miles. This involves removing the intake manifold and blasting walnut shell media at the valve backs to remove carbon deposits. Some owners use catch cans to reduce oil vapor entering the intake. BMW's official position is that carbon buildup is normal for direct-injection engines.</x:v>
+        <x:v>Install comprehensive cooling upgrades for track use: CSF or Mishimoto high-capacity radiator, aftermarket oil cooler, upgraded intercoolers (Wagner, CSF), and transmission cooler. Remove kidney grille blockage for improved airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Total cooling system upgrade costs $3,000-5,000 but essential for serious track use. For street-only M4s, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F138" s="9" t="n">
         <x:v>0</x:v>
@@ -7043,21 +7799,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="139" ht="462" hidden="0" customHeight="1">
       <x:c r="A139" s="40" t="n">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B139" s="9" t="str">
-        <x:v>bmw-m340i-b58-coolant-loss-2020</x:v>
+        <x:v>bmw-m4-crank-hub-bolt-2015</x:v>
       </x:c>
       <x:c r="C139" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>Coolant Loss from Expansion Tank and Water Pump</x:v>
+        <x:v>S55 Crank Hub Bolt Loosening</x:v>
       </x:c>
       <x:c r="E139" s="9" t="str">
-        <x:v>Replace the coolant expansion tank at first sign of cracking. Proactively replace the electric water pump before 60,000 miles. Replace the coolant vent line per BMW TSB. Use only BMW-approved blue coolant. Monitor coolant level monthly and pressure test the cooling system at every major service.</x:v>
+        <x:v>Replace with an upgraded aftermarket crank hub bolt (ARP or IND). The job requires removing the radiator fan, accessory belt, and harmonic balancer to access the bolt. Use proper torque specs for the upgraded bolt. This is a preventative maintenance item for any M4 owner.</x:v>
       </x:c>
       <x:c r="F139" s="9" t="n">
         <x:v>0</x:v>
@@ -7066,21 +7822,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="475.20001220703125" hidden="0" customHeight="1">
+    <x:row r="140" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A140" s="40" t="n">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B140" s="9" t="str">
-        <x:v>bmw-m340i-b58-hpfp-failure-2020</x:v>
+        <x:v>bmw-m4-dct-clutch-2015</x:v>
       </x:c>
       <x:c r="C140" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D140" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E140" s="9" t="str">
-        <x:v>Replace the high-pressure fuel pump with the latest revised BMW part number. Verify the low-pressure fuel pump is providing adequate feed pressure. Use top-tier fuel and avoid running the tank below 1/4 to reduce strain on the fuel system. If under warranty, BMW will cover HPFP replacement.</x:v>
+        <x:v>Replace DCT clutch pack when symptoms appear. BMW recommends replacing all clutches together. Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use (limit to special occasions). Transmission adaptation reset via BMW software may temporarily improve shift quality. Extended warranty highly recommended for DCT-equipped M4s. Labor-intensive repair requires transmission removal.</x:v>
       </x:c>
       <x:c r="F140" s="9" t="n">
         <x:v>0</x:v>
@@ -7089,21 +7845,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="141" ht="462" hidden="0" customHeight="1">
       <x:c r="A141" s="40" t="n">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B141" s="9" t="str">
-        <x:v>bmw-m340i-b58-oil-filter-disintegration-2020</x:v>
+        <x:v>bmw-m4-rear-subframe-crack-2015</x:v>
       </x:c>
       <x:c r="C141" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6, B58</x:v>
+        <x:v>2015-2026 | BMW | M4</x:v>
       </x:c>
       <x:c r="D141" s="9" t="str">
-        <x:v>Oil Filter Disintegration in Housing</x:v>
+        <x:v>Rear Subframe Cracking From Track Use</x:v>
       </x:c>
       <x:c r="E141" s="9" t="str">
-        <x:v>Use only genuine BMW or Mann-branded oil filters (Mann is the OEM supplier). Change oil and filter every 5,000-7,000 miles rather than BMW's recommended 10,000-mile interval. When removing the old filter, inspect it carefully for signs of deterioration. If filter fragments are found in the housing, flush the housing thoroughly before installing the new filter.</x:v>
+        <x:v>Inspect subframe mounting points and welds regularly if the car sees track use. Reinforce with aftermarket subframe reinforcement plates or weld-in gussets. Severely cracked subframes must be replaced entirely. Upgraded subframe bushings (solid or reinforced) help distribute loads more evenly.</x:v>
       </x:c>
       <x:c r="F141" s="9" t="n">
         <x:v>0</x:v>
@@ -7112,21 +7868,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="142" ht="805.2000122070312" hidden="0" customHeight="1">
       <x:c r="A142" s="40" t="n">
         <x:v>141</x:v>
       </x:c>
       <x:c r="B142" s="9" t="str">
-        <x:v>bmw-m340i-b58-wastegate-rattle-2020</x:v>
+        <x:v>bmw-m4-s55-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C142" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D142" s="9" t="str">
-        <x:v>Turbo Wastegate Rattle at Idle</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E142" s="9" t="str">
-        <x:v>Have the wastegate actuator inspected for excessive play. Minor rattle without fault codes can be monitored. If boost control faults develop, replace the turbocharger wastegate actuator. In severe cases, the entire turbocharger assembly may need replacement. BMW may cover under warranty if fault codes are present.</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway) that eliminates the slipping issue permanently. Installation requires crankshaft pulley removal and precise torque specs. This upgrade is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Cost is $1,200-2,500 installed vs. $20,000+ for engine replacement after failure.</x:v>
       </x:c>
       <x:c r="F142" s="9" t="n">
         <x:v>0</x:v>
@@ -7135,44 +7891,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="143" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A143" s="40" t="n">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B143" s="9" t="str">
-        <x:v>bmw-m340i-loss-brake-assist-from-brake-vacuum-pump-damage</x:v>
+        <x:v>bmw-m4-s55-injector-2015</x:v>
       </x:c>
       <x:c r="C143" s="9" t="str">
-        <x:v>2020-2020 | BMW | M340i | B58 3.0L turbo inline-six</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D143" s="9" t="str">
-        <x:v>2020 M340i Brake-Assist Recall 21V-598</x:v>
+        <x:v>S55 High-Pressure Fuel Injector Failure - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E143" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-598 campaign. An authorized BMW dealer updates the engine-management software free of charge and replaces the combined oil/vacuum pump if diagnosis shows it was already damaged. Do not order generic brake-vacuum parts from this card.</x:v>
+        <x:v>Replace all 6 injectors together to prevent repeat repairs. Perform walnut blast carbon cleaning on intake valves while injectors are removed (labor overlap saves $400-600). Use Top Tier gasoline to minimize carbon buildup. Add fuel system cleaner (Liqui Moly Valve Clean) every 5,000 miles to reduce carbon deposits. BMW parts are expensive; some shops use OEM Bosch injectors at lower cost. Labor is 4-6 hours for injector replacement.</x:v>
       </x:c>
       <x:c r="F143" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G143" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="462" hidden="0" customHeight="1">
+    <x:row r="144" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A144" s="40" t="n">
         <x:v>143</x:v>
       </x:c>
       <x:c r="B144" s="9" t="str">
-        <x:v>bmw-m340i-seat-belt-warning-audio-failure</x:v>
+        <x:v>bmw-m4-s55-rod-bearing-2015</x:v>
       </x:c>
       <x:c r="C144" s="9" t="str">
-        <x:v>2019-2022 | BMW | M340i</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D144" s="9" t="str">
-        <x:v>2019-2022 M340i Seat-Belt Warning Recall 23V-584</x:v>
+        <x:v>S55 Rod Bearing Premature Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E144" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-584 campaign. An authorized BMW dealer installs updated Receiver Audio Module software free of charge; eligible vehicles may also receive the remedy by BMW Remote Software Upgrade. Always use the seat belt regardless of warning-chime behavior.</x:v>
+        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles or before extensive track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability than OEM. Regular oil analysis (Blackstone Labs) every 5,000 miles to monitor bearing wear. Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max. Track-focused M4s should replace bearings every 50,000 miles. Labor is 8-12 hours, so many owners do this during clutch replacement.</x:v>
       </x:c>
       <x:c r="F144" s="9" t="n">
         <x:v>0</x:v>
@@ -7181,21 +7937,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="145" ht="660" hidden="0" customHeight="1">
       <x:c r="A145" s="40" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B145" s="9" t="str">
-        <x:v>bmw-m340i-valve-cover-oil-filter-housing-gasket-oil-leaks</x:v>
+        <x:v>bmw-m4cs-brake-wear-track-2024</x:v>
       </x:c>
       <x:c r="C145" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D145" s="9" t="str">
-        <x:v>Valve Cover and Oil Filter Housing Gasket Oil Leaks (B58)</x:v>
+        <x:v>Rapid Brake Pad and Rotor Wear from Track Use</x:v>
       </x:c>
       <x:c r="E145" s="9" t="str">
-        <x:v>Replace the valve cover gasket and/or oil filter housing gasket. Many shops also replace the valve cover itself if it has warped. Clean any oil from spark-plug wells and inspect coils. Typical independent-shop cost is roughly $400-$900 depending on which gasket(s) and labor access.</x:v>
+        <x:v>Inspect brake pads and rotors before and after every track day. Consider upgrading to aftermarket performance pads like Pagid RSC or Hawk DTC-70 for track use, and switch to street pads for daily driving. For frequent track users, the optional carbon ceramic brake package significantly extends rotor life. Use high-temperature brake fluid (DOT 5.1 or racing fluid) and flush before every track season.</x:v>
       </x:c>
       <x:c r="F145" s="9" t="n">
         <x:v>0</x:v>
@@ -7204,21 +7960,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="146" ht="462" hidden="0" customHeight="1">
       <x:c r="A146" s="40" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B146" s="9" t="str">
-        <x:v>bmw-m340i-vanos-solenoid-o-ring-failure</x:v>
+        <x:v>bmw-m4cs-s58-carbon-buildup-2024</x:v>
       </x:c>
       <x:c r="C146" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D146" s="9" t="str">
-        <x:v>VANOS Solenoid O-Ring Failure</x:v>
+        <x:v>S58 Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E146" s="9" t="str">
-        <x:v>Diagnose with a scan tool (VANOS/camshaft position fault codes), then replace the affected intake/exhaust VANOS solenoid(s) and O-rings. Solenoids are relatively inexpensive parts; cost is mostly diagnosis and labor, typically a few hundred dollars.</x:v>
+        <x:v>Walnut blast the intake valves every 40,000-50,000 miles. Consider installing an oil catch can to reduce oil vapor ingestion. Maintain strict 5,000-7,000 mile oil change intervals with BMW LL-01 approved oil. Allow full engine warmup before spirited driving to ensure proper crankcase ventilation operation.</x:v>
       </x:c>
       <x:c r="F146" s="9" t="n">
         <x:v>0</x:v>
@@ -7227,21 +7983,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="147" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A147" s="40" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B147" s="9" t="str">
-        <x:v>bmw-m340i-zf-8hp-harsh-jerky-low-speed-shifting-mechatronic-faults</x:v>
+        <x:v>bmw-m4cs-s58-charge-pipe-crack-2024</x:v>
       </x:c>
       <x:c r="C147" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D147" s="9" t="str">
-        <x:v>ZF 8HP Harsh / Jerky Low-Speed Shifting and Mechatronic Faults</x:v>
+        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
       </x:c>
       <x:c r="E147" s="9" t="str">
-        <x:v>Perform the ZF 8-speed fluid-and-filter (pan) service rather than treating it as lifetime-fill; this resolves many shift-quality complaints. Let the drivetrain warm before hard driving. For persistent erratic shifting or warning lights, scan the transmission and repair/replace the mechatronic unit (valve body) as needed.</x:v>
+        <x:v>Proactively replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF before any track use. These bolt-on replacements are rated for boost pressures well beyond what the S58 produces. Inspect the charge pipe at every service interval for signs of stress cracking or discoloration.</x:v>
       </x:c>
       <x:c r="F147" s="9" t="n">
         <x:v>0</x:v>
@@ -7250,21 +8006,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="594" hidden="0" customHeight="1">
+    <x:row r="148" ht="660" hidden="0" customHeight="1">
       <x:c r="A148" s="40" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B148" s="9" t="str">
-        <x:v>bmw-m3cs-idrive-software-2024</x:v>
+        <x:v>bmw-m5-absdsc-module-failure-triggering-2000</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D148" s="9" t="str">
-        <x:v>iDrive 8 Software Glitches and Screen Blackouts</x:v>
+        <x:v>ABS/DSC Module Failure Triggering ABS, Brake, and Traction Control Warning Lights</x:v>
       </x:c>
       <x:c r="E148" s="9" t="str">
-        <x:v>Check for and install the latest BMW iDrive 8 software updates, which can be delivered over-the-air or at a dealer. Perform a soft reset by holding the iDrive controller button for 30 seconds. If screen blackouts persist, the dealer may need to replace the head unit or update the gateway module firmware. Ensure the 12V battery is in good condition, as low voltage can trigger software instability.</x:v>
+        <x:v>Diagnosis should begin with scanning the ABS/DSC module for communication or wheel-speed sensor faults and verifying power, ground, and sensor signals. If the module intermittently loses communication or shows implausible internal faults, the usual repair is module rebuild or replacement, followed by coding if required. Wheel speed sensors should only be replaced after confirming they are actually faulty.</x:v>
       </x:c>
       <x:c r="F148" s="9" t="n">
         <x:v>0</x:v>
@@ -7273,21 +8029,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="149" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A149" s="40" t="n">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B149" s="9" t="str">
-        <x:v>bmw-m3cs-s58-carbon-buildup-2024</x:v>
+        <x:v>bmw-m5-clutch-slave-cylinder-and-2000</x:v>
       </x:c>
       <x:c r="C149" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D149" s="9" t="str">
-        <x:v>S58 Intake Valve Carbon Buildup</x:v>
+        <x:v>Clutch Slave Cylinder and Hydraulic Line Failure Causing Soft Pedal and Shift Engagement Problems</x:v>
       </x:c>
       <x:c r="E149" s="9" t="str">
-        <x:v>Schedule walnut blast cleaning of the intake valves at 40,000-50,000 mile intervals. Install an oil catch can to reduce oil vapor entering the intake system. Use high-quality synthetic oil meeting BMW LL-01 specification and change at 5,000-7,000 mile intervals. Allow the engine to fully warm up before high-boost driving to ensure proper oil vapor management.</x:v>
+        <x:v>Inspect the clutch hydraulic circuit for fluid leakage at the slave cylinder, master cylinder, and line connections, and verify brake/clutch fluid condition. Replace the failed slave cylinder and often the flexible hose, then bleed the system thoroughly; if symptoms persist, inspect the clutch, pressure plate, and pilot bearing.</x:v>
       </x:c>
       <x:c r="F149" s="9" t="n">
         <x:v>0</x:v>
@@ -7296,21 +8052,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="150" ht="1108.800048828125" hidden="0" customHeight="1">
       <x:c r="A150" s="40" t="n">
         <x:v>149</x:v>
       </x:c>
       <x:c r="B150" s="9" t="str">
-        <x:v>bmw-m3cs-s58-charge-pipe-crack-2024</x:v>
+        <x:v>bmw-m5-dct-clutch-2012</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2016 | BMW | M5</x:v>
       </x:c>
       <x:c r="D150" s="9" t="str">
-        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
+        <x:v>DCT Dual-Clutch Transmission Wear &amp; Judder - F10 M5</x:v>
       </x:c>
       <x:c r="E150" s="9" t="str">
-        <x:v>Replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF. These direct-fit replacements handle higher temperatures and pressures without risk of cracking. If the car is under warranty and the failure occurs on stock tune, BMW should cover the repair. Inspect the charge pipe during every service and before track days.</x:v>
+        <x:v>PREVENTIVE: Replace DCT transmission fluid and filter every 30,000-50,000 miles (BMW says "lifetime" but this causes premature failure). Use ONLY BMW DCTF-1 specification fluid ($189-$253 service, DIY: $100-$150). For judder/jerkiness: try fluid change and software update FIRST before clutch replacement - many issues resolved this way. For severe clutch wear: replace dual-clutch assembly with OEM ($2,394-$2,567 typical, $3,000-$4,000 dealership) or upgraded performance clutch kit. Consider NRC TitanTec or CNS Racing upgraded DCT clutch packs for improved durability if used for performance driving/track. Complete DCT transmission replacement: $8,000-$12,000.</x:v>
       </x:c>
       <x:c r="F150" s="9" t="n">
         <x:v>0</x:v>
@@ -7319,21 +8075,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="396" hidden="0" customHeight="1">
+    <x:row r="151" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A151" s="40" t="n">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B151" s="9" t="str">
-        <x:v>bmw-m4-charge-pipe-blowoff-2015</x:v>
+        <x:v>bmw-m5-door-vapor-barrier-and-2000</x:v>
       </x:c>
       <x:c r="C151" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D151" s="9" t="str">
-        <x:v>Plastic Charge Pipe Blow-Off Under Boost</x:v>
+        <x:v>Door Vapor Barrier and Sunroof Drain Leaks Causing Wet Carpets and Electrical Problems</x:v>
       </x:c>
       <x:c r="E151" s="9" t="str">
-        <x:v>Replace with an aluminum or silicone charge pipe. This is considered a must-do upgrade for any F82 M4. Many aftermarket options are direct bolt-on replacements. The job takes about 1-2 hours and requires removing the intake duct to access the charge pipe.</x:v>
+        <x:v>Remove the door panel and inspect the vapor barrier seal, especially along the lower edge, and verify all sunroof drains flow freely and exit properly. Reseal the vapor barrier with butyl ribbon or equivalent body sealer, clear the drains, dry the carpet and padding thoroughly, and inspect under-carpet wiring/connectors for corrosion.</x:v>
       </x:c>
       <x:c r="F151" s="9" t="n">
         <x:v>0</x:v>
@@ -7347,16 +8103,16 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B152" s="9" t="str">
-        <x:v>bmw-m4-convertible-top-2015</x:v>
+        <x:v>bmw-m5-e39-m5-vanos-solenoidseal-2000</x:v>
       </x:c>
       <x:c r="C152" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D152" s="9" t="str">
-        <x:v>Convertible Top Hydraulic Pump Failure - F83 M4 Convertible</x:v>
+        <x:v>E39 M5 VANOS Solenoid/Seal Failure Causing Rattle, Power Loss, and Check Engine Lights</x:v>
       </x:c>
       <x:c r="E152" s="9" t="str">
-        <x:v>Diagnose specific failure: hydraulic pump motor, lines, microswitches, or latch mechanisms. Pump motor replacement is most common ($1,500-2,500). Check hydraulic fluid level and refill if low. Regular top cycling (minimum once per month) prevents seal degradation. Store with top UP to reduce strain on hydraulic system. Rebuilt hydraulic pumps available at lower cost than new OEM. Complex repair requiring specialized BMW knowledge.</x:v>
+        <x:v>Diagnosis typically includes scanning for camshaft timing and VANOS activation faults, checking oil condition/pressure, and listening for startup rattle from the front of the engine. Repair usually involves rebuilding the VANOS units with upgraded seals, replacing failed solenoids or solenoid seals, and correcting any oil leaks or timing-related wear. Many owners address both banks preventively while the front of engine is apart.</x:v>
       </x:c>
       <x:c r="F152" s="9" t="n">
         <x:v>0</x:v>
@@ -7365,21 +8121,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="153" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A153" s="40" t="n">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B153" s="9" t="str">
-        <x:v>bmw-m4-cooling-track-2015</x:v>
+        <x:v>bmw-m5-front-thrust-arm-bushing-2000</x:v>
       </x:c>
       <x:c r="C153" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D153" s="9" t="str">
-        <x:v>Cooling System Inadequacy Under Track Use - F82/F83 M4</x:v>
+        <x:v>Front Thrust Arm Bushing Failure Causing 50-60 MPH Brake Shimmy and Steering Vibration</x:v>
       </x:c>
       <x:c r="E153" s="9" t="str">
-        <x:v>Install comprehensive cooling upgrades for track use: CSF or Mishimoto high-capacity radiator, aftermarket oil cooler, upgraded intercoolers (Wagner, CSF), and transmission cooler. Remove kidney grille blockage for improved airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Total cooling system upgrade costs $3,000-5,000 but essential for serious track use. For street-only M4s, stock cooling is adequate.</x:v>
+        <x:v>Inspect the front thrust arms and control arms for bushing cracks, fluid leakage from hydro-bushings, and ball-joint play. Replace the thrust arms or complete front control arm set, then perform a proper alignment; if brake pulsation remains, inspect rotor runout and wheel balance.</x:v>
       </x:c>
       <x:c r="F153" s="9" t="n">
         <x:v>0</x:v>
@@ -7388,21 +8144,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="462" hidden="0" customHeight="1">
+    <x:row r="154" ht="594" hidden="0" customHeight="1">
       <x:c r="A154" s="40" t="n">
         <x:v>153</x:v>
       </x:c>
       <x:c r="B154" s="9" t="str">
-        <x:v>bmw-m4-crank-hub-bolt-2015</x:v>
+        <x:v>bmw-m5-getrag-420g-6-speed-synchro-2000</x:v>
       </x:c>
       <x:c r="C154" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D154" s="9" t="str">
-        <x:v>S55 Crank Hub Bolt Loosening</x:v>
+        <x:v>Getrag 420G 6-Speed Synchro Wear and 2nd/3rd Gear Grinding</x:v>
       </x:c>
       <x:c r="E154" s="9" t="str">
-        <x:v>Replace with an upgraded aftermarket crank hub bolt (ARP or IND). The job requires removing the radiator fan, accessory belt, and harmonic balancer to access the bolt. Use proper torque specs for the upgraded bolt. This is a preventative maintenance item for any M4 owner.</x:v>
+        <x:v>Diagnosis involves road testing hot and cold, checking clutch release operation, and ruling out worn transmission mounts or old fluid before condemning the gearbox. Mild cases may improve with fresh fluid, but persistent grinding usually requires transmission rebuild with new synchros, bearings, and wear components. Clutch and shifter bushings are often serviced at the same time.</x:v>
       </x:c>
       <x:c r="F154" s="9" t="n">
         <x:v>0</x:v>
@@ -7411,21 +8167,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="155" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A155" s="40" t="n">
         <x:v>154</x:v>
       </x:c>
       <x:c r="B155" s="9" t="str">
-        <x:v>bmw-m4-dct-clutch-2015</x:v>
+        <x:v>bmw-m5-ignition-coils-2012</x:v>
       </x:c>
       <x:c r="C155" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2012-2023 | BMW | M5 | S63, S63TU</x:v>
       </x:c>
       <x:c r="D155" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F82/F83 M4</x:v>
+        <x:v>S63/S63TU Ignition Coil Premature Failure</x:v>
       </x:c>
       <x:c r="E155" s="9" t="str">
-        <x:v>Replace DCT clutch pack when symptoms appear. BMW recommends replacing all clutches together. Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use (limit to special occasions). Transmission adaptation reset via BMW software may temporarily improve shift quality. Extended warranty highly recommended for DCT-equipped M4s. Labor-intensive repair requires transmission removal.</x:v>
+        <x:v>Replace failed ignition coil(s) immediately to prevent catalytic converter damage ($3,000-$5,000 additional). When one coil fails, M5Post recommends replacing all 8 coils as preventative maintenance ($600-$900 parts + labor) - they typically fail within similar timeframes and saves second service visit. Use OEM Bosch coils for best reliability ($50-$80 each) - aftermarket options fail even faster on S63 due to heat and electrical demands. Replace spark plugs simultaneously if mileage exceeds 30,000 miles ($280-$320 for 8 plugs). Labor: 1-2 hours. Single coil replacement: $179-$235.</x:v>
       </x:c>
       <x:c r="F155" s="9" t="n">
         <x:v>0</x:v>
@@ -7434,21 +8190,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="462" hidden="0" customHeight="1">
+    <x:row r="156" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A156" s="40" t="n">
         <x:v>155</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>bmw-m4-rear-subframe-crack-2015</x:v>
+        <x:v>bmw-m5-instrument-cluster-pixel-failure-2000</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>2015-2026 | BMW | M4</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D156" s="9" t="str">
-        <x:v>Rear Subframe Cracking From Track Use</x:v>
+        <x:v>Instrument Cluster Pixel Failure and MID Display Dropout</x:v>
       </x:c>
       <x:c r="E156" s="9" t="str">
-        <x:v>Inspect subframe mounting points and welds regularly if the car sees track use. Reinforce with aftermarket subframe reinforcement plates or weld-in gussets. Severely cracked subframes must be replaced entirely. Upgraded subframe bushings (solid or reinforced) help distribute loads more evenly.</x:v>
+        <x:v>Diagnosis is usually visual, confirming missing display segments in the cluster or MID. Repair involves replacing or rebuilding the cluster/MID display ribbon and screen components, or sending the unit to a specialist rebuilder. Used replacement clusters require coding and mileage tamper considerations, so rebuild is often preferred.</x:v>
       </x:c>
       <x:c r="F156" s="9" t="n">
         <x:v>0</x:v>
@@ -7457,21 +8213,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="805.2000122070312" hidden="0" customHeight="1">
+    <x:row r="157" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A157" s="40" t="n">
         <x:v>156</x:v>
       </x:c>
       <x:c r="B157" s="9" t="str">
-        <x:v>bmw-m4-s55-crank-hub-2015</x:v>
+        <x:v>bmw-m5-maf-sensor-degradation-causing-2000</x:v>
       </x:c>
       <x:c r="C157" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D157" s="9" t="str">
-        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - F82/F83 M4</x:v>
+        <x:v>MAF Sensor Degradation Causing Lean Codes, Hesitation, and Reduced Power</x:v>
       </x:c>
       <x:c r="E157" s="9" t="str">
-        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway) that eliminates the slipping issue permanently. Installation requires crankshaft pulley removal and precise torque specs. This upgrade is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Cost is $1,200-2,500 installed vs. $20,000+ for engine replacement after failure.</x:v>
+        <x:v>Scan for fuel-trim and MAF-related faults, inspect for intake leaks first, then compare live airflow values bank-to-bank. If readings are implausible or one bank differs significantly, replace the affected MAF sensor(s) with OE-quality parts and clear adaptations; also inspect intake boots and air filter condition.</x:v>
       </x:c>
       <x:c r="F157" s="9" t="n">
         <x:v>0</x:v>
@@ -7480,44 +8236,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="158" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A158" s="40" t="n">
         <x:v>157</x:v>
       </x:c>
       <x:c r="B158" s="9" t="str">
-        <x:v>bmw-m4-s55-injector-2015</x:v>
+        <x:v>bmw-m5-radiator-end-tank-and-2000</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D158" s="9" t="str">
-        <x:v>S55 High-Pressure Fuel Injector Failure - F82/F83 M4</x:v>
+        <x:v>Radiator End Tank and Expansion Tank Cracking Causing Sudden Coolant Loss and Overheating</x:v>
       </x:c>
       <x:c r="E158" s="9" t="str">
-        <x:v>Replace all 6 injectors together to prevent repeat repairs. Perform walnut blast carbon cleaning on intake valves while injectors are removed (labor overlap saves $400-600). Use Top Tier gasoline to minimize carbon buildup. Add fuel system cleaner (Liqui Moly Valve Clean) every 5,000 miles to reduce carbon deposits. BMW parts are expensive; some shops use OEM Bosch injectors at lower cost. Labor is 4-6 hours for injector replacement.</x:v>
+        <x:v>Diagnose with a cooling-system pressure test and inspect the radiator side tanks, expansion tank seams, level sensor area, upper hose neck, and bleed screw area for seepage or cracks. Repair typically involves replacing the failed tank or radiator, and many owners proactively refresh the full cooling system with hoses, cap, thermostat, water pump, and coolant to prevent repeat failures.</x:v>
       </x:c>
       <x:c r="F158" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G158" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="159" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A159" s="40" t="n">
         <x:v>158</x:v>
       </x:c>
       <x:c r="B159" s="9" t="str">
-        <x:v>bmw-m4-s55-rod-bearing-2015</x:v>
+        <x:v>bmw-m5-rear-ball-joint-and-2000</x:v>
       </x:c>
       <x:c r="C159" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D159" s="9" t="str">
-        <x:v>S55 Rod Bearing Premature Wear - F82/F83 M4</x:v>
+        <x:v>Rear Ball Joint and Integral Link Wear Causing Clunks, Tire Wear, and Unstable Handling</x:v>
       </x:c>
       <x:c r="E159" s="9" t="str">
-        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles or before extensive track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability than OEM. Regular oil analysis (Blackstone Labs) every 5,000 miles to monitor bearing wear. Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max. Track-focused M4s should replace bearings every 50,000 miles. Labor is 8-12 hours, so many owners do this during clutch replacement.</x:v>
+        <x:v>Diagnosis includes checking rear wheel play on a lift, inspecting ball joints and links for torn boots or looseness, and measuring alignment. Repair typically involves replacing worn rear ball joints and links in pairs, followed by a four-wheel alignment. Many owners refresh multiple rear suspension wear items together to restore the M5's original handling precision.</x:v>
       </x:c>
       <x:c r="F159" s="9" t="n">
         <x:v>0</x:v>
@@ -7526,21 +8282,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="660" hidden="0" customHeight="1">
+    <x:row r="160" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A160" s="40" t="n">
         <x:v>159</x:v>
       </x:c>
       <x:c r="B160" s="9" t="str">
-        <x:v>bmw-m4cs-brake-wear-track-2024</x:v>
+        <x:v>bmw-m5-s63-rod-bearing-2012</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2016 | BMW | M5 | S63</x:v>
       </x:c>
       <x:c r="D160" s="9" t="str">
-        <x:v>Rapid Brake Pad and Rotor Wear from Track Use</x:v>
+        <x:v>S63 Twin-Turbo V8 Rod Bearing Wear</x:v>
       </x:c>
       <x:c r="E160" s="9" t="str">
-        <x:v>Inspect brake pads and rotors before and after every track day. Consider upgrading to aftermarket performance pads like Pagid RSC or Hawk DTC-70 for track use, and switch to street pads for daily driving. For frequent track users, the optional carbon ceramic brake package significantly extends rotor life. Use high-temperature brake fluid (DOT 5.1 or racing fluid) and flush before every track season.</x:v>
+        <x:v>Preventative rod bearing replacement with upgraded BE Bearings or ACL Race bearings every 60,000-80,000 miles. Requires oil pan removal and dropping the crankshaft to access all 8 rod bearings. Use strict 5,000-mile oil change intervals with BMW LL-01 approved 0W-40 oil.</x:v>
       </x:c>
       <x:c r="F160" s="9" t="n">
         <x:v>0</x:v>
@@ -7549,21 +8305,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="462" hidden="0" customHeight="1">
+    <x:row r="161" ht="1122" hidden="0" customHeight="1">
       <x:c r="A161" s="40" t="n">
         <x:v>160</x:v>
       </x:c>
       <x:c r="B161" s="9" t="str">
-        <x:v>bmw-m4cs-s58-carbon-buildup-2024</x:v>
+        <x:v>bmw-m5-s63-turbo-2012</x:v>
       </x:c>
       <x:c r="C161" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2016 | BMW | M5 | S63</x:v>
       </x:c>
       <x:c r="D161" s="9" t="str">
-        <x:v>S58 Intake Valve Carbon Buildup</x:v>
+        <x:v>S63 V8 Twin-Turbocharger Failure - F10 M5</x:v>
       </x:c>
       <x:c r="E161" s="9" t="str">
-        <x:v>Walnut blast the intake valves every 40,000-50,000 miles. Consider installing an oil catch can to reduce oil vapor ingestion. Maintain strict 5,000-7,000 mile oil change intervals with BMW LL-01 approved oil. Allow full engine warmup before spirited driving to ensure proper crankcase ventilation operation.</x:v>
+        <x:v>Replace failed turbocharger(s) with updated OEM units ($4,000-$6,000 per turbo, $8,000-$12,000 for both). Install BMW TSB heat insulators to protect turbo coolant and oil lines from excessive heat exposure ($200 preventive vs. $8,000+ turbo replacement). Use ONLY high-quality synthetic oil and maintain strict oil change intervals (5,000-7,500 miles MAX - NOT BMW's 10k recommendation). Avoid aggressive driving when engine cold - allow full warm-up before boost. For high-mileage vehicles (80,000+ miles), consider preventative turbo replacement or inspection. M5Post: when one turbo fails, seriously consider replacing both - labor overlap saves $2,000-$3,000 and other will likely fail soon.</x:v>
       </x:c>
       <x:c r="F161" s="9" t="n">
         <x:v>0</x:v>
@@ -7572,21 +8328,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="162" ht="1188" hidden="0" customHeight="1">
       <x:c r="A162" s="40" t="n">
         <x:v>161</x:v>
       </x:c>
       <x:c r="B162" s="9" t="str">
-        <x:v>bmw-m4cs-s58-charge-pipe-crack-2024</x:v>
+        <x:v>bmw-m5-s85-rod-bearing-2006</x:v>
       </x:c>
       <x:c r="C162" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D162" s="9" t="str">
-        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
+        <x:v>S85 V10 Rod Bearing Premature Failure (CATASTROPHIC) - E60 M5</x:v>
       </x:c>
       <x:c r="E162" s="9" t="str">
-        <x:v>Proactively replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF before any track use. These bolt-on replacements are rated for boost pressures well beyond what the S58 produces. Inspect the charge pipe at every service interval for signs of stress cracking or discoloration.</x:v>
+        <x:v>MANDATORY PREVENTATIVE: Replace rod bearings before 70,000 miles ($6,500-$8,600). Upgrade to BE Bearings, ACL Race, or VAC Motorsports high-performance bearings with increased clearances (0.0025" or greater) - DO NOT use OEM BMW bearings which have same design flaw. Perform regular oil analysis every 5,000 miles to detect early bearing wear. Use only BMW-approved 10W-60 synthetic oil with frequent oil changes (5,000-7,500 mile intervals). NEVER redline engine before reaching full operating temperature. Replace high-pressure VANOS line at same time as rod bearings (labor overlap saves $2,000-$3,000). If catastrophic failure occurs: Complete engine replacement required ($15,000-$32,000).</x:v>
       </x:c>
       <x:c r="F162" s="9" t="n">
         <x:v>0</x:v>
@@ -7595,21 +8351,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="660" hidden="0" customHeight="1">
+    <x:row r="163" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A163" s="40" t="n">
         <x:v>162</x:v>
       </x:c>
       <x:c r="B163" s="9" t="str">
-        <x:v>bmw-m5-absdsc-module-failure-triggering-2000</x:v>
+        <x:v>bmw-m5-s85-throttle-actuator-2006</x:v>
       </x:c>
       <x:c r="C163" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D163" s="9" t="str">
-        <x:v>ABS/DSC Module Failure Triggering ABS, Brake, and Traction Control Warning Lights</x:v>
+        <x:v>S85 V10 Throttle Body Actuator Failure - E60 M5</x:v>
       </x:c>
       <x:c r="E163" s="9" t="str">
-        <x:v>Diagnosis should begin with scanning the ABS/DSC module for communication or wheel-speed sensor faults and verifying power, ground, and sensor signals. If the module intermittently loses communication or shows implausible internal faults, the usual repair is module rebuild or replacement, followed by coding if required. Wheel speed sensors should only be replaced after confirming they are actually faulty.</x:v>
+        <x:v>Replace failed throttle actuator(s) with OEM units ($1,400-$1,700 each) or upgrade to Evolve Automotive uprated throttle actuators ($1,500-$1,800 each) for improved durability and increased lifespan - these have upgraded internal components that prevent repeat failure. ECU Testing and Euro Power Motorsports offer actuator rebuilds ($500-$800 per actuator) as cost-effective alternatives. M5Post consensus: when one actuator fails, replace both at same time to save labor costs since second will fail within 6-12 months. Labor: 3 hours professional / 4+ hours DIY.</x:v>
       </x:c>
       <x:c r="F163" s="9" t="n">
         <x:v>0</x:v>
@@ -7618,21 +8374,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="164" ht="1056" hidden="0" customHeight="1">
       <x:c r="A164" s="40" t="n">
         <x:v>163</x:v>
       </x:c>
       <x:c r="B164" s="9" t="str">
-        <x:v>bmw-m5-clutch-slave-cylinder-and-2000</x:v>
+        <x:v>bmw-m5-s85-vanos-pump-2006</x:v>
       </x:c>
       <x:c r="C164" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2006-2010 | BMW | M5 | S85</x:v>
       </x:c>
       <x:c r="D164" s="9" t="str">
-        <x:v>Clutch Slave Cylinder and Hydraulic Line Failure Causing Soft Pedal and Shift Engagement Problems</x:v>
+        <x:v>VANOS High-Pressure Pump &amp; Line Failure (CATASTROPHIC) - E60 M5</x:v>
       </x:c>
       <x:c r="E164" s="9" t="str">
-        <x:v>Inspect the clutch hydraulic circuit for fluid leakage at the slave cylinder, master cylinder, and line connections, and verify brake/clutch fluid condition. Replace the failed slave cylinder and often the flexible hose, then bleed the system thoroughly; if symptoms persist, inspect the clutch, pressure plate, and pilot bearing.</x:v>
+        <x:v>Replace high-pressure VANOS line with updated design that includes proper bend radius ($3,000 parts + labor). Replace VANOS high-pressure pump if showing signs of wear or contamination. DrVanos offers fully rebuilt S85 VANOS pumps ($1,800 + $400 core deposit) - M5Post gold standard for rebuilds. This repair is BEST performed simultaneously with rod bearing replacement to save on overlapping labor costs ($2,000-$4,000 savings). WARNING: DO NOT ignore VANOS line leaks - metal debris from failed pump circulates through entire lubrication system and can destroy engine. If catastrophic failure: engine replacement required ($32,000).</x:v>
       </x:c>
       <x:c r="F164" s="9" t="n">
         <x:v>0</x:v>
@@ -7641,21 +8397,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="165" ht="1188" hidden="0" customHeight="1">
       <x:c r="A165" s="40" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B165" s="9" t="str">
-        <x:v>bmw-m5-dct-clutch-2012</x:v>
+        <x:v>bmw-m5-smg-pump-2006</x:v>
       </x:c>
       <x:c r="C165" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D165" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Wear &amp; Judder - F10 M5</x:v>
+        <x:v>SMG III Hydraulic Pump Failure - E60 M5</x:v>
       </x:c>
       <x:c r="E165" s="9" t="str">
-        <x:v>PREVENTIVE: Replace DCT transmission fluid and filter every 30,000-50,000 miles (BMW says "lifetime" but this causes premature failure). Use ONLY BMW DCTF-1 specification fluid ($189-$253 service, DIY: $100-$150). For judder/jerkiness: try fluid change and software update FIRST before clutch replacement - many issues resolved this way. For severe clutch wear: replace dual-clutch assembly with OEM ($2,394-$2,567 typical, $3,000-$4,000 dealership) or upgraded performance clutch kit. Consider NRC TitanTec or CNS Racing upgraded DCT clutch packs for improved durability if used for performance driving/track. Complete DCT transmission replacement: $8,000-$12,000.</x:v>
+        <x:v>DIAGNOSIS FIRST: Insist on proper diagnosis before pump replacement - accumulator failure has similar symptoms and costs $500 vs. $5,000. If pump confirmed failed: Try rebuild first - carbon buildup can often be cleaned for fraction of replacement cost. SMG Society and specialty shops offer pump rebuilds ($300 pump + labor + fluids = $1,500-$2,500). If rebuild unsuccessful: Replace SMG pump with OEM or remanufactured unit ($5,000-$7,700 dealership, $5,000-$6,500 independent specialist). Replace hydraulic accumulator at same time if vehicle has 60,000+ miles ($300-$500 additional). Flush and replace SMG hydraulic fluid and manual transmission fluid during pump replacement.</x:v>
       </x:c>
       <x:c r="F165" s="9" t="n">
         <x:v>0</x:v>
@@ -7664,21 +8420,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="166" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A166" s="40" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B166" s="9" t="str">
-        <x:v>bmw-m5-door-vapor-barrier-and-2000</x:v>
+        <x:v>bmw-m5-timing-chain-guide-wear-2000</x:v>
       </x:c>
       <x:c r="C166" s="9" t="str">
         <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D166" s="9" t="str">
-        <x:v>Door Vapor Barrier and Sunroof Drain Leaks Causing Wet Carpets and Electrical Problems</x:v>
+        <x:v>Timing Chain Guide Wear and Chain Tensioner Noise on the S62 V8</x:v>
       </x:c>
       <x:c r="E166" s="9" t="str">
-        <x:v>Remove the door panel and inspect the vapor barrier seal, especially along the lower edge, and verify all sunroof drains flow freely and exit properly. Reseal the vapor barrier with butyl ribbon or equivalent body sealer, clear the drains, dry the carpet and padding thoroughly, and inspect under-carpet wiring/connectors for corrosion.</x:v>
+        <x:v>Diagnosis includes listening for chain noise on cold start, inspecting oil/filter for plastic guide debris, and checking timing adaptation/fault data. Repair generally requires replacing timing chain guides, tensioners, related rails, gaskets, and often addressing front-engine seals while disassembled. Preventive service is often recommended once noise appears rather than waiting for a failure.</x:v>
       </x:c>
       <x:c r="F166" s="9" t="n">
         <x:v>0</x:v>
@@ -7687,21 +8443,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="167" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A167" s="40" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B167" s="9" t="str">
-        <x:v>bmw-m5-e39-m5-vanos-solenoidseal-2000</x:v>
+        <x:v>bmw-m5-torque-converter-shudder-2018</x:v>
       </x:c>
       <x:c r="C167" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2018-2023 | BMW | M5</x:v>
       </x:c>
       <x:c r="D167" s="9" t="str">
-        <x:v>E39 M5 VANOS Solenoid/Seal Failure Causing Rattle, Power Loss, and Check Engine Lights</x:v>
+        <x:v>ZF 8HP Torque Converter Shudder</x:v>
       </x:c>
       <x:c r="E167" s="9" t="str">
-        <x:v>Diagnosis typically includes scanning for camshaft timing and VANOS activation faults, checking oil condition/pressure, and listening for startup rattle from the front of the engine. Repair usually involves rebuilding the VANOS units with upgraded seals, replacing failed solenoids or solenoid seals, and correcting any oil leaks or timing-related wear. Many owners address both banks preventively while the front of engine is apart.</x:v>
+        <x:v>Perform a transmission fluid and filter change using genuine ZF LifeGuard 8 fluid. If the shudder persists, the torque converter must be replaced. BMW issued a service bulletin for some VINs. A software update for shift calibration may also help in mild cases.</x:v>
       </x:c>
       <x:c r="F167" s="9" t="n">
         <x:v>0</x:v>
@@ -7710,21 +8466,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="168" ht="1108.800048828125" hidden="0" customHeight="1">
       <x:c r="A168" s="40" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B168" s="9" t="str">
-        <x:v>bmw-m5-front-thrust-arm-bushing-2000</x:v>
+        <x:v>bmw-m5-valve-stem-seals-2012</x:v>
       </x:c>
       <x:c r="C168" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2023 | BMW | M5</x:v>
       </x:c>
       <x:c r="D168" s="9" t="str">
-        <x:v>Front Thrust Arm Bushing Failure Causing 50-60 MPH Brake Shimmy and Steering Vibration</x:v>
+        <x:v>S63/S63TU Valve Stem Seal Failure &amp; Oil Consumption</x:v>
       </x:c>
       <x:c r="E168" s="9" t="str">
-        <x:v>Inspect the front thrust arms and control arms for bushing cracks, fluid leakage from hydro-bushings, and ball-joint play. Replace the thrust arms or complete front control arm set, then perform a proper alignment; if brake pulsation remains, inspect rotor runout and wheel balance.</x:v>
+        <x:v>Replace valve stem seals with updated OEM or performance seals ($3,500-$10,000 depending on method). Labor-intensive repair requiring either cylinder head removal ($6,000-$10,000) or specialized valve spring compressor tools with heads on engine ($3,500-$6,000). Address issue EARLY to prevent catalytic converter damage from oil burning (adds $3,000-$5,000 to repair). Perform more frequent oil changes (5,000 miles) to minimize damage. Blue smoke test: let engine idle 30+ minutes until hot, then rev to redline briefly - big blue smoke plume = valve seals. Find shop that can replace valve seals with heads installed (specialized tools required) - saves $4,000+ in labor vs. full head removal.</x:v>
       </x:c>
       <x:c r="F168" s="9" t="n">
         <x:v>0</x:v>
@@ -7733,21 +8489,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="594" hidden="0" customHeight="1">
+    <x:row r="169" ht="528" hidden="0" customHeight="1">
       <x:c r="A169" s="40" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B169" s="9" t="str">
-        <x:v>bmw-m5-getrag-420g-6-speed-synchro-2000</x:v>
+        <x:v>bmw-m6-e63-e64-active-steering-steering-gear-play-knock</x:v>
       </x:c>
       <x:c r="C169" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
       </x:c>
       <x:c r="D169" s="9" t="str">
-        <x:v>Getrag 420G 6-Speed Synchro Wear and 2nd/3rd Gear Grinding</x:v>
+        <x:v>E63/E64 Active Steering and Steering-Gear Play / Knock</x:v>
       </x:c>
       <x:c r="E169" s="9" t="str">
-        <x:v>Diagnosis involves road testing hot and cold, checking clutch release operation, and ruling out worn transmission mounts or old fluid before condemning the gearbox. Mild cases may improve with fresh fluid, but persistent grinding usually requires transmission rebuild with new synchros, bearings, and wear components. Clutch and shifter bushings are often serviced at the same time.</x:v>
+        <x:v>Inspect the steering gear and front control-arm/thrust-arm bushings for play. Replace worn control-arm bushings/ball joints first as they are cheaper and frequently the source of the knock; if the steering rack/gear itself has internal play or leaks, it requires replacement (a significant cost) followed by an alignment.</x:v>
       </x:c>
       <x:c r="F169" s="9" t="n">
         <x:v>0</x:v>
@@ -7756,21 +8512,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="170" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A170" s="40" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B170" s="9" t="str">
-        <x:v>bmw-m5-ignition-coils-2012</x:v>
+        <x:v>bmw-m6-f12-convertible-top-hydraulic-pump-relay-failure</x:v>
       </x:c>
       <x:c r="C170" s="9" t="str">
-        <x:v>2012-2023 | BMW | M5 | S63, S63TU</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Convertible (F12) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D170" s="9" t="str">
-        <x:v>S63/S63TU Ignition Coil Premature Failure</x:v>
+        <x:v>F12 Convertible Top Hydraulic Pump and Relay Failure</x:v>
       </x:c>
       <x:c r="E170" s="9" t="str">
-        <x:v>Replace failed ignition coil(s) immediately to prevent catalytic converter damage ($3,000-$5,000 additional). When one coil fails, M5Post recommends replacing all 8 coils as preventative maintenance ($600-$900 parts + labor) - they typically fail within similar timeframes and saves second service visit. Use OEM Bosch coils for best reliability ($50-$80 each) - aftermarket options fail even faster on S63 due to heat and electrical demands. Replace spark plugs simultaneously if mileage exceeds 30,000 miles ($280-$320 for 8 plugs). Labor: 1-2 hours. Single coil replacement: $179-$235.</x:v>
+        <x:v>Diagnose whether the fault is the pump's high-current relays (relatively cheap, often the cure), a pressure loss in the pump, a hydraulic leak, or a roof microswitch/sensor. Replace the relays first; if pressure loss persists, rebuild or replace the hydraulic pump unit (specialist rebuild services exist) and renew worn seals/sensors. Bleed and refill the hydraulic system after repair.</x:v>
       </x:c>
       <x:c r="F170" s="9" t="n">
         <x:v>0</x:v>
@@ -7779,21 +8535,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="171" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A171" s="40" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B171" s="9" t="str">
-        <x:v>bmw-m5-instrument-cluster-pixel-failure-2000</x:v>
+        <x:v>bmw-m6-f12-f13-7-speed-m-dct-mechatronic-clutch-pack-failure</x:v>
       </x:c>
       <x:c r="C171" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D171" s="9" t="str">
-        <x:v>Instrument Cluster Pixel Failure and MID Display Dropout</x:v>
+        <x:v>F12/F13 7-Speed M-DCT Mechatronic and Clutch Pack Failure</x:v>
       </x:c>
       <x:c r="E171" s="9" t="str">
-        <x:v>Diagnosis is usually visual, confirming missing display segments in the cluster or MID. Repair involves replacing or rebuilding the cluster/MID display ribbon and screen components, or sending the unit to a specialist rebuilder. Used replacement clusters require coding and mileage tamper considerations, so rebuild is often preferred.</x:v>
+        <x:v>Scan for transmission codes to confirm whether the fault is the mechatronic unit or worn clutch packs. Mechatronic units can often be repaired/replaced and must be reprogrammed and adapted to the vehicle afterward. Worn clutch packs require a clutch replacement (dealer cost often $3,000-$5,000). Regular DCT fluid and filter changes help prevent premature wear; avoid prolonged clutch slip in traffic.</x:v>
       </x:c>
       <x:c r="F171" s="9" t="n">
         <x:v>0</x:v>
@@ -7802,21 +8558,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="172" ht="594" hidden="0" customHeight="1">
       <x:c r="A172" s="40" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B172" s="9" t="str">
-        <x:v>bmw-m5-maf-sensor-degradation-causing-2000</x:v>
+        <x:v>bmw-m6-f12-f13-electric-water-pump-thermostat-failure</x:v>
       </x:c>
       <x:c r="C172" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D172" s="9" t="str">
-        <x:v>MAF Sensor Degradation Causing Lean Codes, Hesitation, and Reduced Power</x:v>
+        <x:v>F12/F13 Electric Water Pump and Thermostat Failure</x:v>
       </x:c>
       <x:c r="E172" s="9" t="str">
-        <x:v>Scan for fuel-trim and MAF-related faults, inspect for intake leaks first, then compare live airflow values bank-to-bank. If readings are implausible or one bank differs significantly, replace the affected MAF sensor(s) with OE-quality parts and clear adaptations; also inspect intake boots and air filter condition.</x:v>
+        <x:v>Replace the failed electric water pump and/or electronic thermostat with OEM units; inspect the radiator end-tanks and expansion tank for cracks and replace as needed. Pressure-test the cooling system, refresh coolant, and treat the pump/thermostat as wear items given the heat load. Address any overheating event immediately to avoid secondary engine damage.</x:v>
       </x:c>
       <x:c r="F172" s="9" t="n">
         <x:v>0</x:v>
@@ -7825,21 +8581,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="173" ht="528" hidden="0" customHeight="1">
       <x:c r="A173" s="40" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B173" s="9" t="str">
-        <x:v>bmw-m5-radiator-end-tank-and-2000</x:v>
+        <x:v>bmw-m6-f12-f13-turbocharger-wastegate-rattle-oil-starvation</x:v>
       </x:c>
       <x:c r="C173" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D173" s="9" t="str">
-        <x:v>Radiator End Tank and Expansion Tank Cracking Causing Sudden Coolant Loss and Overheating</x:v>
+        <x:v>F12/F13 Turbocharger Wastegate Rattle and Oil Starvation</x:v>
       </x:c>
       <x:c r="E173" s="9" t="str">
-        <x:v>Diagnose with a cooling-system pressure test and inspect the radiator side tanks, expansion tank seams, level sensor area, upper hose neck, and bleed screw area for seepage or cracks. Repair typically involves replacing the failed tank or radiator, and many owners proactively refresh the full cooling system with hoses, cap, thermostat, water pump, and coolant to prevent repeat failures.</x:v>
+        <x:v>Confirm wastegate rattle by listening at light throttle; worn actuators/linkages can be replaced or upgraded. For oil starvation, maintain strict oil-change intervals with the correct specification, allow proper cool-down after hard driving, and keep the cooling system healthy. Severely worn or whining turbos require rebuild or replacement.</x:v>
       </x:c>
       <x:c r="F173" s="9" t="n">
         <x:v>0</x:v>
@@ -7848,21 +8604,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="174" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A174" s="40" t="n">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B174" s="9" t="str">
-        <x:v>bmw-m5-rear-ball-joint-and-2000</x:v>
+        <x:v>bmw-m6-rod-bearing-wear-2005</x:v>
       </x:c>
       <x:c r="C174" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2005-2019 | BMW | M6 | S65, S63</x:v>
       </x:c>
       <x:c r="D174" s="9" t="str">
-        <x:v>Rear Ball Joint and Integral Link Wear Causing Clunks, Tire Wear, and Unstable Handling</x:v>
+        <x:v>Rod Bearing Premature Wear (S65/S63 Engines)</x:v>
       </x:c>
       <x:c r="E174" s="9" t="str">
-        <x:v>Diagnosis includes checking rear wheel play on a lift, inspecting ball joints and links for torn boots or looseness, and measuring alignment. Repair typically involves replacing worn rear ball joints and links in pairs, followed by a four-wheel alignment. Many owners refresh multiple rear suspension wear items together to restore the M5's original handling precision.</x:v>
+        <x:v>Perform a preventive rod bearing replacement between 60,000-80,000 miles on S65 engines, and inspect by 80,000-100,000 miles on S63 engines. Use upgraded ACL or King XP bearings with coated surfaces. Cut and send used oil filter for analysis — bearing material particles indicate wear progression. The job requires engine-out on the S65 (approximately 20 hours labor) or can be done in-car on the S63 with the oil pan dropped.</x:v>
       </x:c>
       <x:c r="F174" s="9" t="n">
         <x:v>0</x:v>
@@ -7871,21 +8627,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="175" ht="528" hidden="0" customHeight="1">
       <x:c r="A175" s="40" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B175" s="9" t="str">
-        <x:v>bmw-m5-s63-rod-bearing-2012</x:v>
+        <x:v>bmw-m6-s63-carbon-buildup-intake-valves</x:v>
       </x:c>
       <x:c r="C175" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5 | S63</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D175" s="9" t="str">
-        <x:v>S63 Twin-Turbo V8 Rod Bearing Wear</x:v>
+        <x:v>S63 Carbon Buildup on Intake Valves (Direct Injection)</x:v>
       </x:c>
       <x:c r="E175" s="9" t="str">
-        <x:v>Preventative rod bearing replacement with upgraded BE Bearings or ACL Race bearings every 60,000-80,000 miles. Requires oil pan removal and dropping the crankshaft to access all 8 rod bearings. Use strict 5,000-mile oil change intervals with BMW LL-01 approved 0W-40 oil.</x:v>
+        <x:v>Have the intake valves walnut-blasted (media-blast cleaning) to remove carbon deposits without removing the cylinder heads. Many owners do this every 50,000-70,000 km. A properly functioning PCV/crankcase ventilation system and quality oil reduce deposit rate. An oil-catch can is sometimes fitted to slow accumulation.</x:v>
       </x:c>
       <x:c r="F175" s="9" t="n">
         <x:v>0</x:v>
@@ -7894,21 +8650,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="1122" hidden="0" customHeight="1">
+    <x:row r="176" ht="528" hidden="0" customHeight="1">
       <x:c r="A176" s="40" t="n">
         <x:v>175</x:v>
       </x:c>
       <x:c r="B176" s="9" t="str">
-        <x:v>bmw-m5-s63-turbo-2012</x:v>
+        <x:v>bmw-m6-s63-high-pressure-fuel-pump-fuel-injector-cold-start-misfire</x:v>
       </x:c>
       <x:c r="C176" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5 | S63</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D176" s="9" t="str">
-        <x:v>S63 V8 Twin-Turbocharger Failure - F10 M5</x:v>
+        <x:v>S63 High-Pressure Fuel Pump / Fuel Injector Cold-Start Misfire</x:v>
       </x:c>
       <x:c r="E176" s="9" t="str">
-        <x:v>Replace failed turbocharger(s) with updated OEM units ($4,000-$6,000 per turbo, $8,000-$12,000 for both). Install BMW TSB heat insulators to protect turbo coolant and oil lines from excessive heat exposure ($200 preventive vs. $8,000+ turbo replacement). Use ONLY high-quality synthetic oil and maintain strict oil change intervals (5,000-7,500 miles MAX - NOT BMW's 10k recommendation). Avoid aggressive driving when engine cold - allow full warm-up before boost. For high-mileage vehicles (80,000+ miles), consider preventative turbo replacement or inspection. M5Post: when one turbo fails, seriously consider replacing both - labor overlap saves $2,000-$3,000 and other will likely fail soon.</x:v>
+        <x:v>Scan for misfire and fuel-system codes and test cold-start fuel-rail pressure. Replace a failing HPFP; for injector faults, replace the affected injector(s) with units of the correct matching index code (do not mix injector indexes on a bank) and re-code them. Address per the relevant BMW technical service bulletin for the N63/S63.</x:v>
       </x:c>
       <x:c r="F176" s="9" t="n">
         <x:v>0</x:v>
@@ -7917,21 +8673,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="1188" hidden="0" customHeight="1">
+    <x:row r="177" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A177" s="40" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B177" s="9" t="str">
-        <x:v>bmw-m5-s85-rod-bearing-2006</x:v>
+        <x:v>bmw-m6-s63-rod-bearing-2013</x:v>
       </x:c>
       <x:c r="C177" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2013-2018 | BMW | M6 | S63</x:v>
       </x:c>
       <x:c r="D177" s="9" t="str">
-        <x:v>S85 V10 Rod Bearing Premature Failure (CATASTROPHIC) - E60 M5</x:v>
+        <x:v>S63 Twin-Turbo V8 Rod Bearing Concerns (F06/F12/F13 M6)</x:v>
       </x:c>
       <x:c r="E177" s="9" t="str">
-        <x:v>MANDATORY PREVENTATIVE: Replace rod bearings before 70,000 miles ($6,500-$8,600). Upgrade to BE Bearings, ACL Race, or VAC Motorsports high-performance bearings with increased clearances (0.0025" or greater) - DO NOT use OEM BMW bearings which have same design flaw. Perform regular oil analysis every 5,000 miles to detect early bearing wear. Use only BMW-approved 10W-60 synthetic oil with frequent oil changes (5,000-7,500 mile intervals). NEVER redline engine before reaching full operating temperature. Replace high-pressure VANOS line at same time as rod bearings (labor overlap saves $2,000-$3,000). If catastrophic failure occurs: Complete engine replacement required ($15,000-$32,000).</x:v>
+        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles using ACL Race Rod Bearings 8B1578HX-STD ($150-250), King Bearings SV Series, or WPC-treated bearings from Lang Racing. Cost: $4,000-7,000 for preventive replacement. Oil changes every 5,000-7,500 miles mandatory (ignore BMW's 10,000-mile recommendation). Use Blackstone Labs oil analysis ($30/test) every 5,000 miles to monitor bearing wear metals. Preventive replacement recommended for peace of mind, especially on cars used for track days or spirited driving.</x:v>
       </x:c>
       <x:c r="F177" s="9" t="n">
         <x:v>0</x:v>
@@ -7940,21 +8696,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="178" ht="1069.199951171875" hidden="0" customHeight="1">
       <x:c r="A178" s="40" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B178" s="9" t="str">
-        <x:v>bmw-m5-s85-throttle-actuator-2006</x:v>
+        <x:v>bmw-m6-s85-rod-bearing-2006</x:v>
       </x:c>
       <x:c r="C178" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2006-2010 | BMW | M6 | S85</x:v>
       </x:c>
       <x:c r="D178" s="9" t="str">
-        <x:v>S85 V10 Throttle Body Actuator Failure - E60 M5</x:v>
+        <x:v>S85 V10 Rod Bearing Failure (Catastrophic Engine Destruction)</x:v>
       </x:c>
       <x:c r="E178" s="9" t="str">
-        <x:v>Replace failed throttle actuator(s) with OEM units ($1,400-$1,700 each) or upgrade to Evolve Automotive uprated throttle actuators ($1,500-$1,800 each) for improved durability and increased lifespan - these have upgraded internal components that prevent repeat failure. ECU Testing and Euro Power Motorsports offer actuator rebuilds ($500-$800 per actuator) as cost-effective alternatives. M5Post consensus: when one actuator fails, replace both at same time to save labor costs since second will fail within 6-12 months. Labor: 3 hours professional / 4+ hours DIY.</x:v>
+        <x:v>MANDATORY PREVENTIVE REPLACEMENT before 70,000 miles: Replace all 10 rod bearings with ACL Race Bearings 10B1580HX-STD (+0.001" clearance, $200-350) or WPC-treated bearings from Lang Racing, or VAC Motorsports kit VAC-HPRBK-S85, or Turner kit TMS222798, or FCP Euro kit 11247841703KT3. ALSO replace VANOS line 11367838669 and use ARP rod bolts (included in most kits). Cost: $6,500-9,500 preventive. If engine is destroyed from bearing failure: $15,000-32,000 for engine replacement or rebuild. NEVER use OEM bearings as replacements. Use Blackstone Labs oil analysis every 5,000 miles ($30/test) to monitor bearing wear metals.</x:v>
       </x:c>
       <x:c r="F178" s="9" t="n">
         <x:v>0</x:v>
@@ -7963,21 +8719,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="179" ht="1056" hidden="0" customHeight="1">
+    <x:row r="179" ht="924" hidden="0" customHeight="1">
       <x:c r="A179" s="40" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B179" s="9" t="str">
-        <x:v>bmw-m5-s85-vanos-pump-2006</x:v>
+        <x:v>bmw-m6-s85-throttle-actuator-2006</x:v>
       </x:c>
       <x:c r="C179" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5 | S85</x:v>
+        <x:v>2006-2010 | BMW | M6 | S85</x:v>
       </x:c>
       <x:c r="D179" s="9" t="str">
-        <x:v>VANOS High-Pressure Pump &amp; Line Failure (CATASTROPHIC) - E60 M5</x:v>
+        <x:v>S85 V10 Throttle Actuator Failure (Plastic Gear Stripping)</x:v>
       </x:c>
       <x:c r="E179" s="9" t="str">
-        <x:v>Replace high-pressure VANOS line with updated design that includes proper bend radius ($3,000 parts + labor). Replace VANOS high-pressure pump if showing signs of wear or contamination. DrVanos offers fully rebuilt S85 VANOS pumps ($1,800 + $400 core deposit) - M5Post gold standard for rebuilds. This repair is BEST performed simultaneously with rod bearing replacement to save on overlapping labor costs ($2,000-$4,000 savings). WARNING: DO NOT ignore VANOS line leaks - metal debris from failed pump circulates through entire lubrication system and can destroy engine. If catastrophic failure: engine replacement required ($32,000).</x:v>
+        <x:v>Rebuild throttle actuators using Beisan Systems BS101 sintered metal gear kit ($250/set, need 2 sets for both actuators) for permanent fix. Beisan BS102 full rebuild service available ($300). Alternatively, rebuilt actuators from Euro Power Motorsports ($500-800 each). OEM replacement actuators from BMW cost $2,000-4,500. Total cost: $500-4,500 depending on approach. Beisan Systems sintered metal gears are THE permanent fix - they replace the weak plastic PPA gears with metal gears that will not strip. Always rebuild both actuators simultaneously.</x:v>
       </x:c>
       <x:c r="F179" s="9" t="n">
         <x:v>0</x:v>
@@ -7986,21 +8742,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="1188" hidden="0" customHeight="1">
+    <x:row r="180" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A180" s="40" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B180" s="9" t="str">
-        <x:v>bmw-m5-smg-pump-2006</x:v>
+        <x:v>bmw-m6-s85-v10-vanos-high-pressure-oil-pump-failure</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
       </x:c>
       <x:c r="D180" s="9" t="str">
-        <x:v>SMG III Hydraulic Pump Failure - E60 M5</x:v>
+        <x:v>S85 V10 VANOS High-Pressure Oil Pump Failure</x:v>
       </x:c>
       <x:c r="E180" s="9" t="str">
-        <x:v>DIAGNOSIS FIRST: Insist on proper diagnosis before pump replacement - accumulator failure has similar symptoms and costs $500 vs. $5,000. If pump confirmed failed: Try rebuild first - carbon buildup can often be cleaned for fraction of replacement cost. SMG Society and specialty shops offer pump rebuilds ($300 pump + labor + fluids = $1,500-$2,500). If rebuild unsuccessful: Replace SMG pump with OEM or remanufactured unit ($5,000-$7,700 dealership, $5,000-$6,500 independent specialist). Replace hydraulic accumulator at same time if vehicle has 60,000+ miles ($300-$500 additional). Flush and replace SMG hydraulic fluid and manual transmission fluid during pump replacement.</x:v>
+        <x:v>Perform an oil-pressure test on the VANOS circuit at the first sign of cold-start knocking. Replace or professionally rebuild the high-pressure VANOS pump and renew the high-pressure lines/seals. Many owners do the VANOS pump preventively at the same time as the rod-bearing service since the oil pan is already removed. Use only BMW-spec oil and strict change intervals to prolong pump life.</x:v>
       </x:c>
       <x:c r="F180" s="9" t="n">
         <x:v>0</x:v>
@@ -8009,21 +8765,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="181" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A181" s="40" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B181" s="9" t="str">
-        <x:v>bmw-m5-timing-chain-guide-wear-2000</x:v>
+        <x:v>bmw-m6-smg-pump-failure-2005</x:v>
       </x:c>
       <x:c r="C181" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2005-2010 | BMW | M6</x:v>
       </x:c>
       <x:c r="D181" s="9" t="str">
-        <x:v>Timing Chain Guide Wear and Chain Tensioner Noise on the S62 V8</x:v>
+        <x:v>SMG Hydraulic Pump and Clutch Actuator Failure</x:v>
       </x:c>
       <x:c r="E181" s="9" t="str">
-        <x:v>Diagnosis includes listening for chain noise on cold start, inspecting oil/filter for plastic guide debris, and checking timing adaptation/fault data. Repair generally requires replacing timing chain guides, tensioners, related rails, gaskets, and often addressing front-engine seals while disassembled. Preventive service is often recommended once noise appears rather than waiting for a failure.</x:v>
+        <x:v>Replace the SMG hydraulic pump and pressure accumulator. Bleed and refill the SMG hydraulic system with Pentosin CHF 11S fluid. Many owners convert to a traditional 6-speed manual swap using an aftermarket kit from companies like OS Giken or using the E90 M3 6MT parts. Budget $2,000-4,000 for SMG repair or $5,000-8,000 for a manual conversion.</x:v>
       </x:c>
       <x:c r="F181" s="9" t="n">
         <x:v>0</x:v>
@@ -8032,21 +8788,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="182" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A182" s="40" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B182" s="9" t="str">
-        <x:v>bmw-m5-torque-converter-shudder-2018</x:v>
+        <x:v>bmw-m8-adaptive-suspension-leak-2020</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
-        <x:v>2018-2023 | BMW | M5</x:v>
+        <x:v>2020-2025 | BMW | M8</x:v>
       </x:c>
       <x:c r="D182" s="9" t="str">
-        <x:v>ZF 8HP Torque Converter Shudder</x:v>
+        <x:v>Adaptive Suspension Damper Leaks</x:v>
       </x:c>
       <x:c r="E182" s="9" t="str">
-        <x:v>Perform a transmission fluid and filter change using genuine ZF LifeGuard 8 fluid. If the shudder persists, the torque converter must be replaced. BMW issued a service bulletin for some VINs. A software update for shift calibration may also help in mild cases.</x:v>
+        <x:v>Replace the leaking damper(s). BMW adaptive dampers must be replaced as complete units — they cannot be rebuilt. After replacement, a suspension calibration via ISTA is required to integrate the new damper into the adaptive system. Replacing in pairs (front or rear axle) is recommended.</x:v>
       </x:c>
       <x:c r="F182" s="9" t="n">
         <x:v>0</x:v>
@@ -8055,21 +8811,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="183" ht="990" hidden="0" customHeight="1">
       <x:c r="A183" s="40" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B183" s="9" t="str">
-        <x:v>bmw-m5-valve-stem-seals-2012</x:v>
+        <x:v>bmw-m8-carbon-ceramic-brakes-2020</x:v>
       </x:c>
       <x:c r="C183" s="9" t="str">
-        <x:v>2012-2023 | BMW | M5</x:v>
+        <x:v>2020-2024 | BMW | M8</x:v>
       </x:c>
       <x:c r="D183" s="9" t="str">
-        <x:v>S63/S63TU Valve Stem Seal Failure &amp; Oil Consumption</x:v>
+        <x:v>M8 Carbon Ceramic Brake (CCB) Issues</x:v>
       </x:c>
       <x:c r="E183" s="9" t="str">
-        <x:v>Replace valve stem seals with updated OEM or performance seals ($3,500-$10,000 depending on method). Labor-intensive repair requiring either cylinder head removal ($6,000-$10,000) or specialized valve spring compressor tools with heads on engine ($3,500-$6,000). Address issue EARLY to prevent catalytic converter damage from oil burning (adds $3,000-$5,000 to repair). Perform more frequent oil changes (5,000 miles) to minimize damage. Blue smoke test: let engine idle 30+ minutes until hot, then rev to redline briefly - big blue smoke plume = valve seals. Find shop that can replace valve seals with heads installed (specialized tools required) - saves $4,000+ in labor vs. full head removal.</x:v>
+        <x:v>Replace damaged CCB rotors ($3,000-$4,000 per corner, $12,000-$16,000 for all four). CCB rotors cannot be resurfaced - replacement is only option. Alternatively, convert to iron rotors using BimmerWorld CCB-to-iron conversion kit ($3,000-$5,000 total for all four corners) for dramatically lower running costs. PREVENTION: Avoid driving through standing water with hot brakes (thermal shock cracks rotors). Avoid aggressive braking over potholes or road debris. Squealing at low speed is normal for CCB material - not a defect. If only using car for street driving, iron conversion is more practical and cost-effective.</x:v>
       </x:c>
       <x:c r="F183" s="9" t="n">
         <x:v>0</x:v>
@@ -8078,21 +8834,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="528" hidden="0" customHeight="1">
+    <x:row r="184" ht="396" hidden="0" customHeight="1">
       <x:c r="A184" s="40" t="n">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B184" s="9" t="str">
-        <x:v>bmw-m6-e63-e64-active-steering-steering-gear-play-knock</x:v>
+        <x:v>bmw-m8-s63tu4-oil-consumption-2020</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
+        <x:v>2020-2025 | BMW | M8 | S63TU4</x:v>
       </x:c>
       <x:c r="D184" s="9" t="str">
-        <x:v>E63/E64 Active Steering and Steering-Gear Play / Knock</x:v>
+        <x:v>S63TU4 V8 Excessive Oil Consumption</x:v>
       </x:c>
       <x:c r="E184" s="9" t="str">
-        <x:v>Inspect the steering gear and front control-arm/thrust-arm bushings for play. Replace worn control-arm bushings/ball joints first as they are cheaper and frequently the source of the knock; if the steering rack/gear itself has internal play or leaks, it requires replacement (a significant cost) followed by an alignment.</x:v>
+        <x:v>Monitor oil level regularly using iDrive oil level check. For excessive consumption beyond BMW's threshold, valve stem seal replacement may be warranted under warranty. Updated piston rings are available for severe cases. Always keep oil topped up between changes.</x:v>
       </x:c>
       <x:c r="F184" s="9" t="n">
         <x:v>0</x:v>
@@ -8101,21 +8857,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="185" ht="858" hidden="0" customHeight="1">
       <x:c r="A185" s="40" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B185" s="9" t="str">
-        <x:v>bmw-m6-f12-convertible-top-hydraulic-pump-relay-failure</x:v>
+        <x:v>bmw-m8-s63tu4-rod-bearing-2020</x:v>
       </x:c>
       <x:c r="C185" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Convertible (F12) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2020-2024 | BMW | M8</x:v>
       </x:c>
       <x:c r="D185" s="9" t="str">
-        <x:v>F12 Convertible Top Hydraulic Pump and Relay Failure</x:v>
+        <x:v>S63TU4 Rod Bearing Wear (M8/M8 Competition)</x:v>
       </x:c>
       <x:c r="E185" s="9" t="str">
-        <x:v>Diagnose whether the fault is the pump's high-current relays (relatively cheap, often the cure), a pressure loss in the pump, a hydraulic leak, or a roof microswitch/sensor. Replace the relays first; if pressure loss persists, rebuild or replace the hydraulic pump unit (specialist rebuild services exist) and renew worn seals/sensors. Bleed and refill the hydraulic system after repair.</x:v>
+        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles or sooner if tracked ($5,000-$8,000). Use ACL Race bearings 8B1578HX-STD ($200-350) which have wider clearance tolerances than OEM for better oil film protection. Monitor bearing health with Blackstone Labs oil analysis ($30/sample) every oil change - elevated copper/lead indicates bearing wear starting. If bearings have failed: engine replacement required ($20,000-$40,000). CRITICAL: If you hear any knocking from bottom end, stop driving immediately and tow to shop.</x:v>
       </x:c>
       <x:c r="F185" s="9" t="n">
         <x:v>0</x:v>
@@ -8124,21 +8880,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="186" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A186" s="40" t="n">
         <x:v>185</x:v>
       </x:c>
       <x:c r="B186" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-7-speed-m-dct-mechatronic-clutch-pack-failure</x:v>
+        <x:v>bmw-n54-hpfp</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2007-2010 | BMW | 3 Series | N54</x:v>
       </x:c>
       <x:c r="D186" s="9" t="str">
-        <x:v>F12/F13 7-Speed M-DCT Mechatronic and Clutch Pack Failure</x:v>
+        <x:v>N54 Long Crank or Power Loss Requires Fuel-Pressure Diagnosis</x:v>
       </x:c>
       <x:c r="E186" s="9" t="str">
-        <x:v>Scan for transmission codes to confirm whether the fault is the mechatronic unit or worn clutch packs. Mechatronic units can often be repaired/replaced and must be reprogrammed and adapted to the vehicle afterward. Worn clutch packs require a clutch replacement (dealer cost often $3,000-$5,000). Regular DCT fluid and filter changes help prevent premature wear; avoid prolonged clutch slip in traffic.</x:v>
+        <x:v>Have a BMW-qualified technician read fault memory and follow the bulletin pressure tests for 2FBF, 29DC, 29F1 or 29F2 before replacing the pump. The historical ten-year/120,000-mile emissions-warranty extension has expired for this population and is not a current coverage promise. ShowMeTheParts resolved three 2009 335i fuel-pump candidates, but catalog fitment is not diagnosis or remedy proof and no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F186" s="9" t="n">
         <x:v>0</x:v>
@@ -8147,21 +8903,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="594" hidden="0" customHeight="1">
+    <x:row r="187" ht="290.3999938964844" hidden="0" customHeight="1">
       <x:c r="A187" s="40" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B187" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-electric-water-pump-thermostat-failure</x:v>
+        <x:v>bmw-n55-boost-solenoid-2012</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
       </x:c>
       <x:c r="D187" s="9" t="str">
-        <x:v>F12/F13 Electric Water Pump and Thermostat Failure</x:v>
+        <x:v>Wastegate/Boost Solenoid Issues</x:v>
       </x:c>
       <x:c r="E187" s="9" t="str">
-        <x:v>Replace the failed electric water pump and/or electronic thermostat with OEM units; inspect the radiator end-tanks and expansion tank for cracks and replace as needed. Pressure-test the cooling system, refresh coolant, and treat the pump/thermostat as wear items given the heat load. Address any overheating event immediately to avoid secondary engine damage.</x:v>
+        <x:v>Diagnose boost system for proper operation. Replace wastegate actuator or boost solenoid as needed. Check vacuum lines for leaks. Software update may address some issues.</x:v>
       </x:c>
       <x:c r="F187" s="9" t="n">
         <x:v>0</x:v>
@@ -8170,21 +8926,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="528" hidden="0" customHeight="1">
+    <x:row r="188" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A188" s="40" t="n">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B188" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-turbocharger-wastegate-rattle-oil-starvation</x:v>
+        <x:v>bmw-n55-carbon-buildup-2012</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
       </x:c>
       <x:c r="D188" s="9" t="str">
-        <x:v>F12/F13 Turbocharger Wastegate Rattle and Oil Starvation</x:v>
+        <x:v>Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E188" s="9" t="str">
-        <x:v>Confirm wastegate rattle by listening at light throttle; worn actuators/linkages can be replaced or upgraded. For oil starvation, maintain strict oil-change intervals with the correct specification, allow proper cool-down after hard driving, and keep the cooling system healthy. Severely worn or whining turbos require rebuild or replacement.</x:v>
+        <x:v>Walnut blast cleaning of intake valves every 50,000-70,000 miles. Install catch can to reduce oil vapor. Use quality fuel. BMW port injection on later engines helps reduce this issue.</x:v>
       </x:c>
       <x:c r="F188" s="9" t="n">
         <x:v>0</x:v>
@@ -8193,21 +8949,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="189" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A189" s="40" t="n">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B189" s="9" t="str">
-        <x:v>bmw-m6-rod-bearing-wear-2005</x:v>
+        <x:v>bmw-n55-charge-pipe-2012</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
-        <x:v>2005-2019 | BMW | M6 | S65, S63</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D189" s="9" t="str">
-        <x:v>Rod Bearing Premature Wear (S65/S63 Engines)</x:v>
+        <x:v>Charge Pipe Failure/Cracking</x:v>
       </x:c>
       <x:c r="E189" s="9" t="str">
-        <x:v>Perform a preventive rod bearing replacement between 60,000-80,000 miles on S65 engines, and inspect by 80,000-100,000 miles on S63 engines. Use upgraded ACL or King XP bearings with coated surfaces. Cut and send used oil filter for analysis — bearing material particles indicate wear progression. The job requires engine-out on the S65 (approximately 20 hours labor) or can be done in-car on the S63 with the oil pan dropped.</x:v>
+        <x:v>Replace with upgraded aluminum charge pipe for reliability. If keeping stock, inspect regularly for cracks. Upgraded pipe is recommended for any tuned vehicle. Installation is relatively straightforward.</x:v>
       </x:c>
       <x:c r="F189" s="9" t="n">
         <x:v>0</x:v>
@@ -8216,21 +8972,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="528" hidden="0" customHeight="1">
+    <x:row r="190" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A190" s="40" t="n">
         <x:v>189</x:v>
       </x:c>
       <x:c r="B190" s="9" t="str">
-        <x:v>bmw-m6-s63-carbon-buildup-intake-valves</x:v>
+        <x:v>bmw-n55-injector-2012</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D190" s="9" t="str">
-        <x:v>S63 Carbon Buildup on Intake Valves (Direct Injection)</x:v>
+        <x:v>High-Pressure Fuel Injector Issues</x:v>
       </x:c>
       <x:c r="E190" s="9" t="str">
-        <x:v>Have the intake valves walnut-blasted (media-blast cleaning) to remove carbon deposits without removing the cylinder heads. Many owners do this every 50,000-70,000 km. A properly functioning PCV/crankcase ventilation system and quality oil reduce deposit rate. An oil-catch can is sometimes fitted to slow accumulation.</x:v>
+        <x:v>Replace failed injector(s) with correct index version. Consider cleaning service for carbon buildup. Use quality fuel. All injectors should be same index for proper operation.</x:v>
       </x:c>
       <x:c r="F190" s="9" t="n">
         <x:v>0</x:v>
@@ -8239,21 +8995,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="528" hidden="0" customHeight="1">
+    <x:row r="191" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A191" s="40" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="B191" s="9" t="str">
-        <x:v>bmw-m6-s63-high-pressure-fuel-pump-fuel-injector-cold-start-misfire</x:v>
+        <x:v>bmw-n55-oil-filter-housing-2012</x:v>
       </x:c>
       <x:c r="C191" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D191" s="9" t="str">
-        <x:v>S63 High-Pressure Fuel Pump / Fuel Injector Cold-Start Misfire</x:v>
+        <x:v>Certain 2012 F30 N55 Vehicles Need an Oil-Filter-Housing Campaign Check</x:v>
       </x:c>
       <x:c r="E191" s="9" t="str">
-        <x:v>Scan for misfire and fuel-system codes and test cold-start fuel-rail pressure. Replace a failing HPFP; for injector faults, replace the affected injector(s) with units of the correct matching index code (do not mix injector indexes on a bank) and re-code them. Address per the relevant BMW technical service bulletin for the N63/S63.</x:v>
+        <x:v>Check the VIN and service-action history, then have a BMW-qualified technician inspect the housing material and leak source. Under the bulletin, the black plastic housing is replaced while the silver aluminum housing is left in place. ShowMeTheParts returned no exact 2012 335i oil-filter-housing candidate, and the former generic gasket links were removed.</x:v>
       </x:c>
       <x:c r="F191" s="9" t="n">
         <x:v>0</x:v>
@@ -8262,21 +9018,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="192" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A192" s="40" t="n">
         <x:v>191</x:v>
       </x:c>
       <x:c r="B192" s="9" t="str">
-        <x:v>bmw-m6-s63-rod-bearing-2013</x:v>
+        <x:v>bmw-n55-valve-cover-2012</x:v>
       </x:c>
       <x:c r="C192" s="9" t="str">
-        <x:v>2013-2018 | BMW | M6 | S63</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D192" s="9" t="str">
-        <x:v>S63 Twin-Turbo V8 Rod Bearing Concerns (F06/F12/F13 M6)</x:v>
+        <x:v>Valve Cover/Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E192" s="9" t="str">
-        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles using ACL Race Rod Bearings 8B1578HX-STD ($150-250), King Bearings SV Series, or WPC-treated bearings from Lang Racing. Cost: $4,000-7,000 for preventive replacement. Oil changes every 5,000-7,500 miles mandatory (ignore BMW's 10,000-mile recommendation). Use Blackstone Labs oil analysis ($30/test) every 5,000 miles to monitor bearing wear metals. Preventive replacement recommended for peace of mind, especially on cars used for track days or spirited driving.</x:v>
+        <x:v>Replace valve cover and gasket as an assembly (PCV valve is integrated). Clean oil from exhaust manifold. Monitor for leaks after repair. This is a common maintenance item at higher mileage.</x:v>
       </x:c>
       <x:c r="F192" s="9" t="n">
         <x:v>0</x:v>
@@ -8285,21 +9041,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="1069.199951171875" hidden="0" customHeight="1">
+    <x:row r="193" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A193" s="40" t="n">
         <x:v>192</x:v>
       </x:c>
       <x:c r="B193" s="9" t="str">
-        <x:v>bmw-m6-s85-rod-bearing-2006</x:v>
+        <x:v>bmw-n55-vanos-2012</x:v>
       </x:c>
       <x:c r="C193" s="9" t="str">
-        <x:v>2006-2010 | BMW | M6 | S85</x:v>
+        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D193" s="9" t="str">
-        <x:v>S85 V10 Rod Bearing Failure (Catastrophic Engine Destruction)</x:v>
+        <x:v>Certain 2012 N55 3 Series Need a VANOS Gear-Bolt Recall Check</x:v>
       </x:c>
       <x:c r="E193" s="9" t="str">
-        <x:v>MANDATORY PREVENTIVE REPLACEMENT before 70,000 miles: Replace all 10 rod bearings with ACL Race Bearings 10B1580HX-STD (+0.001" clearance, $200-350) or WPC-treated bearings from Lang Racing, or VAC Motorsports kit VAC-HPRBK-S85, or Turner kit TMS222798, or FCP Euro kit 11247841703KT3. ALSO replace VANOS line 11367838669 and use ARP rod bolts (included in most kits). Cost: $6,500-9,500 preventive. If engine is destroyed from bearing failure: $15,000-32,000 for engine replacement or rebuild. NEVER use OEM bearings as replacements. Use Blackstone Labs oil analysis every 5,000 miles ($30/test) to monitor bearing wear metals.</x:v>
+        <x:v>Check the VIN for campaign 14V-176 before ordering VANOS solenoids or gears. For an affected vehicle, BMW specifies replacing the VANOS gear bolts and inspecting for loose or broken bolts, with additional gear work only when the campaign procedure requires it. Recall work belongs with an authorized BMW center, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F193" s="9" t="n">
         <x:v>0</x:v>
@@ -8308,21 +9064,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="924" hidden="0" customHeight="1">
+    <x:row r="194" ht="660" hidden="0" customHeight="1">
       <x:c r="A194" s="40" t="n">
         <x:v>193</x:v>
       </x:c>
       <x:c r="B194" s="9" t="str">
-        <x:v>bmw-m6-s85-throttle-actuator-2006</x:v>
+        <x:v>bmw-n55-water-pump-2012</x:v>
       </x:c>
       <x:c r="C194" s="9" t="str">
-        <x:v>2006-2010 | BMW | M6 | S85</x:v>
+        <x:v>2012-2013 | BMW | 3 Series | N54T, N55</x:v>
       </x:c>
       <x:c r="D194" s="9" t="str">
-        <x:v>S85 V10 Throttle Actuator Failure (Plastic Gear Stripping)</x:v>
+        <x:v>2012-2013 335i/335is Overheat Warnings Need Coolant-Pump Diagnosis</x:v>
       </x:c>
       <x:c r="E194" s="9" t="str">
-        <x:v>Rebuild throttle actuators using Beisan Systems BS101 sintered metal gear kit ($250/set, need 2 sets for both actuators) for permanent fix. Beisan BS102 full rebuild service available ($300). Alternatively, rebuilt actuators from Euro Power Motorsports ($500-800 each). OEM replacement actuators from BMW cost $2,000-4,500. Total cost: $500-4,500 depending on approach. Beisan Systems sintered metal gears are THE permanent fix - they replace the weak plastic PPA gears with metal gears that will not strip. Always rebuild both actuators simultaneously.</x:v>
+        <x:v>Stop safely if an overheat warning appears and avoid continued operation until the cooling system is checked. Verify the chassis, engine and VIN, read fault memory and follow the current coolant-pump test plan before replacement. Settlement benefits were time-limited. ShowMeTheParts resolved five 2012 335i water-pump candidates, but fitment does not prove failure or remedy, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F194" s="9" t="n">
         <x:v>0</x:v>
@@ -8331,21 +9087,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="195" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A195" s="40" t="n">
         <x:v>194</x:v>
       </x:c>
       <x:c r="B195" s="9" t="str">
-        <x:v>bmw-m6-s85-v10-vanos-high-pressure-oil-pump-failure</x:v>
+        <x:v>bmw-x1-coolant-leak-2016</x:v>
       </x:c>
       <x:c r="C195" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
+        <x:v>2016-2023 | BMW | X1 | B-series</x:v>
       </x:c>
       <x:c r="D195" s="9" t="str">
-        <x:v>S85 V10 VANOS High-Pressure Oil Pump Failure</x:v>
+        <x:v>Coolant Leaks - Water Pump &amp; Thermostat - F48 X1</x:v>
       </x:c>
       <x:c r="E195" s="9" t="str">
-        <x:v>Perform an oil-pressure test on the VANOS circuit at the first sign of cold-start knocking. Replace or professionally rebuild the high-pressure VANOS pump and renew the high-pressure lines/seals. Many owners do the VANOS pump preventively at the same time as the rod-bearing service since the oil pan is already removed. Use only BMW-spec oil and strict change intervals to prolong pump life.</x:v>
+        <x:v>Replace failed water pump or thermostat housing. Electric water pump replacement is 2-3 hours labor. Thermostat housing is 1-2 hours. Always use BMW-approved coolant (blue or orange, do not mix). Properly bleed cooling system after repair to prevent air pockets. Inspect all coolant hoses during repair and replace if cracked. Preventive replacement of water pump at 80,000 miles recommended.</x:v>
       </x:c>
       <x:c r="F195" s="9" t="n">
         <x:v>0</x:v>
@@ -8354,21 +9110,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="196" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A196" s="40" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="B196" s="9" t="str">
-        <x:v>bmw-m6-smg-pump-failure-2005</x:v>
+        <x:v>bmw-x1-n20-timing-chain-2013</x:v>
       </x:c>
       <x:c r="C196" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6</x:v>
+        <x:v>2013-2015 | BMW | X1 | N20</x:v>
       </x:c>
       <x:c r="D196" s="9" t="str">
-        <x:v>SMG Hydraulic Pump and Clutch Actuator Failure</x:v>
+        <x:v>Lower-Engine Whine Requires X1 N20 Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E196" s="9" t="str">
-        <x:v>Replace the SMG hydraulic pump and pressure accumulator. Bleed and refill the SMG hydraulic system with Pentosin CHF 11S fluid. Many owners convert to a traditional 6-speed manual swap using an aftermarket kit from companies like OS Giken or using the E90 M3 6MT parts. Budget $2,000-4,000 for SMG repair or $5,000-8,000 for a manual conversion.</x:v>
+        <x:v>Confirm the exact model, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F196" s="9" t="n">
         <x:v>0</x:v>
@@ -8377,21 +9133,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="197" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A197" s="40" t="n">
         <x:v>196</x:v>
       </x:c>
       <x:c r="B197" s="9" t="str">
-        <x:v>bmw-m8-adaptive-suspension-leak-2020</x:v>
+        <x:v>bmw-x1-n20-timing-chain-guide-2013</x:v>
       </x:c>
       <x:c r="C197" s="9" t="str">
-        <x:v>2020-2025 | BMW | M8</x:v>
+        <x:v>2013-2015 | BMW | X1 | N20</x:v>
       </x:c>
       <x:c r="D197" s="9" t="str">
-        <x:v>Adaptive Suspension Damper Leaks</x:v>
+        <x:v>N20 Timing Chain Guide Failure</x:v>
       </x:c>
       <x:c r="E197" s="9" t="str">
-        <x:v>Replace the leaking damper(s). BMW adaptive dampers must be replaced as complete units — they cannot be rebuilt. After replacement, a suspension calibration via ISTA is required to integrate the new damper into the adaptive system. Replacing in pairs (front or rear axle) is recommended.</x:v>
+        <x:v>Replace timing chain, guides, tensioner, and both sprockets as a complete kit. The repair requires removing the front of the engine and is labor-intensive. Updated guide materials are available. Preventive replacement at 80,000 miles is recommended for high-mileage N20 engines.</x:v>
       </x:c>
       <x:c r="F197" s="9" t="n">
         <x:v>0</x:v>
@@ -8400,44 +9156,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" ht="990" hidden="0" customHeight="1">
+    <x:row r="198" ht="396" hidden="0" customHeight="1">
       <x:c r="A198" s="40" t="n">
         <x:v>197</x:v>
       </x:c>
       <x:c r="B198" s="9" t="str">
-        <x:v>bmw-m8-carbon-ceramic-brakes-2020</x:v>
+        <x:v>bmw-x1-oil-filter-housing-gasket-2013</x:v>
       </x:c>
       <x:c r="C198" s="9" t="str">
-        <x:v>2020-2024 | BMW | M8</x:v>
+        <x:v>2013-2022 | BMW | X1 | N20, B48</x:v>
       </x:c>
       <x:c r="D198" s="9" t="str">
-        <x:v>M8 Carbon Ceramic Brake (CCB) Issues</x:v>
+        <x:v>Oil Filter Housing Gasket Leak</x:v>
       </x:c>
       <x:c r="E198" s="9" t="str">
-        <x:v>Replace damaged CCB rotors ($3,000-$4,000 per corner, $12,000-$16,000 for all four). CCB rotors cannot be resurfaced - replacement is only option. Alternatively, convert to iron rotors using BimmerWorld CCB-to-iron conversion kit ($3,000-$5,000 total for all four corners) for dramatically lower running costs. PREVENTION: Avoid driving through standing water with hot brakes (thermal shock cracks rotors). Avoid aggressive braking over potholes or road debris. Squealing at low speed is normal for CCB material - not a defect. If only using car for street driving, iron conversion is more practical and cost-effective.</x:v>
+        <x:v>Replace the oil filter housing gasket and clean all affected surfaces. Also inspect and replace the oil cooler gasket if present. Use only OEM-quality gaskets as aftermarket gaskets tend to fail prematurely. Typical repair takes 2-3 hours.</x:v>
       </x:c>
       <x:c r="F198" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G198" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="396" hidden="0" customHeight="1">
+    <x:row r="199" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A199" s="40" t="n">
         <x:v>198</x:v>
       </x:c>
       <x:c r="B199" s="9" t="str">
-        <x:v>bmw-m8-s63tu4-oil-consumption-2020</x:v>
+        <x:v>bmw-x1-oil-leak-2016</x:v>
       </x:c>
       <x:c r="C199" s="9" t="str">
-        <x:v>2020-2025 | BMW | M8 | S63TU4</x:v>
+        <x:v>2016-2023 | BMW | X1 | B46, B48</x:v>
       </x:c>
       <x:c r="D199" s="9" t="str">
-        <x:v>S63TU4 V8 Excessive Oil Consumption</x:v>
+        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - F48 X1</x:v>
       </x:c>
       <x:c r="E199" s="9" t="str">
-        <x:v>Monitor oil level regularly using iDrive oil level check. For excessive consumption beyond BMW's threshold, valve stem seal replacement may be warranted under warranty. Updated piston rings are available for severe cases. Always keep oil topped up between changes.</x:v>
+        <x:v>Replace valve cover gasket and/or oil filter housing gasket as needed. Valve cover replacement is 2-3 hours labor. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on B-series engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
       </x:c>
       <x:c r="F199" s="9" t="n">
         <x:v>0</x:v>
@@ -8446,21 +9202,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="858" hidden="0" customHeight="1">
+    <x:row r="200" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A200" s="40" t="n">
         <x:v>199</x:v>
       </x:c>
       <x:c r="B200" s="9" t="str">
-        <x:v>bmw-m8-s63tu4-rod-bearing-2020</x:v>
+        <x:v>bmw-x1-suspension-bushing-2016</x:v>
       </x:c>
       <x:c r="C200" s="9" t="str">
-        <x:v>2020-2024 | BMW | M8</x:v>
+        <x:v>2016-2023 | BMW | X1</x:v>
       </x:c>
       <x:c r="D200" s="9" t="str">
-        <x:v>S63TU4 Rod Bearing Wear (M8/M8 Competition)</x:v>
+        <x:v>Front Suspension Bushing &amp; Control Arm Wear - F48 X1</x:v>
       </x:c>
       <x:c r="E200" s="9" t="str">
-        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles or sooner if tracked ($5,000-$8,000). Use ACL Race bearings 8B1578HX-STD ($200-350) which have wider clearance tolerances than OEM for better oil film protection. Monitor bearing health with Blackstone Labs oil analysis ($30/sample) every oil change - elevated copper/lead indicates bearing wear starting. If bearings have failed: engine replacement required ($20,000-$40,000). CRITICAL: If you hear any knocking from bottom end, stop driving immediately and tow to shop.</x:v>
+        <x:v>Replace worn control arms or bushings. Most shops replace complete control arms (with integrated bushings) rather than pressing in new bushings alone. Alignment required after replacement. Inspect all suspension components while vehicle is lifted. Consider replacing both sides even if only one shows symptoms to avoid repeat labor costs. Use OEM or quality aftermarket parts (Lemforder, Meyle HD) for longevity.</x:v>
       </x:c>
       <x:c r="F200" s="9" t="n">
         <x:v>0</x:v>
@@ -8469,21 +9225,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="201" ht="660" hidden="0" customHeight="1">
       <x:c r="A201" s="40" t="n">
         <x:v>200</x:v>
       </x:c>
       <x:c r="B201" s="9" t="str">
-        <x:v>bmw-n54-hpfp</x:v>
+        <x:v>bmw-x1-transfer-case-2013</x:v>
       </x:c>
       <x:c r="C201" s="9" t="str">
-        <x:v>2007-2010 | BMW | 3 Series | N54</x:v>
+        <x:v>2013-2023 | BMW | X1</x:v>
       </x:c>
       <x:c r="D201" s="9" t="str">
-        <x:v>N54 Long Crank or Power Loss Requires Fuel-Pressure Diagnosis</x:v>
+        <x:v>Transfer Case Failure - xDrive Models E84/F48 X1</x:v>
       </x:c>
       <x:c r="E201" s="9" t="str">
-        <x:v>Have a BMW-qualified technician read fault memory and follow the bulletin pressure tests for 2FBF, 29DC, 29F1 or 29F2 before replacing the pump. The historical ten-year/120,000-mile emissions-warranty extension has expired for this population and is not a current coverage promise. ShowMeTheParts resolved three 2009 335i fuel-pump candidates, but catalog fitment is not diagnosis or remedy proof and no commerce link is approved.</x:v>
+        <x:v>Diagnose specific failure point. Transfer case actuator motor can be replaced separately ($800-1,200) if caught early. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors for better durability. Common wear item on high-mileage xDrive models.</x:v>
       </x:c>
       <x:c r="F201" s="9" t="n">
         <x:v>0</x:v>
@@ -8492,21 +9248,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="290.3999938964844" hidden="0" customHeight="1">
+    <x:row r="202" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A202" s="40" t="n">
         <x:v>201</x:v>
       </x:c>
       <x:c r="B202" s="9" t="str">
-        <x:v>bmw-n55-boost-solenoid-2012</x:v>
+        <x:v>bmw-x1-transfer-case-actuator-2013</x:v>
       </x:c>
       <x:c r="C202" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
+        <x:v>2013-2022 | BMW | X1</x:v>
       </x:c>
       <x:c r="D202" s="9" t="str">
-        <x:v>Wastegate/Boost Solenoid Issues</x:v>
+        <x:v>Transfer Case Actuator Motor Failure</x:v>
       </x:c>
       <x:c r="E202" s="9" t="str">
-        <x:v>Diagnose boost system for proper operation. Replace wastegate actuator or boost solenoid as needed. Check vacuum lines for leaks. Software update may address some issues.</x:v>
+        <x:v>Replace the transfer case actuator motor (also called the servo motor). The transfer case itself usually does not need replacement. Ensure the transfer case fluid is changed at the same time. Some owners report success with rebuilt actuators at lower cost.</x:v>
       </x:c>
       <x:c r="F202" s="9" t="n">
         <x:v>0</x:v>
@@ -8515,21 +9271,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="203" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A203" s="40" t="n">
         <x:v>202</x:v>
       </x:c>
       <x:c r="B203" s="9" t="str">
-        <x:v>bmw-n55-carbon-buildup-2012</x:v>
+        <x:v>bmw-x2-b48-timing-chain-tensioner-2018</x:v>
       </x:c>
       <x:c r="C203" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
+        <x:v>2018-2023 | BMW | X2 | B48</x:v>
       </x:c>
       <x:c r="D203" s="9" t="str">
-        <x:v>Intake Valve Carbon Buildup</x:v>
+        <x:v>B48 Timing Chain Tensioner Weakness</x:v>
       </x:c>
       <x:c r="E203" s="9" t="str">
-        <x:v>Walnut blast cleaning of intake valves every 50,000-70,000 miles. Install catch can to reduce oil vapor. Use quality fuel. BMW port injection on later engines helps reduce this issue.</x:v>
+        <x:v>Replace the timing chain tensioner and inspect the chain and guides. If the chain has stretched beyond specification, replace the full timing chain kit. Updated tensioner design from BMW addresses the oil pressure retention issue.</x:v>
       </x:c>
       <x:c r="F203" s="9" t="n">
         <x:v>0</x:v>
@@ -8538,21 +9294,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="204" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A204" s="40" t="n">
         <x:v>203</x:v>
       </x:c>
       <x:c r="B204" s="9" t="str">
-        <x:v>bmw-n55-charge-pipe-2012</x:v>
+        <x:v>bmw-x2-crankshaft-sensor-recall-2018</x:v>
       </x:c>
       <x:c r="C204" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2018-2018 | BMW | X2</x:v>
       </x:c>
       <x:c r="D204" s="9" t="str">
-        <x:v>Charge Pipe Failure/Cracking</x:v>
+        <x:v>2018 X2 Crankshaft Sensor Safety Recall 18V-465</x:v>
       </x:c>
       <x:c r="E204" s="9" t="str">
-        <x:v>Replace with upgraded aluminum charge pipe for reliability. If keeping stock, inspect regularly for cracks. Upgraded pipe is recommended for any tuned vehicle. Installation is relatively straightforward.</x:v>
+        <x:v>Check the VIN for an open 18V-465 campaign. If open, an authorized BMW dealer replaces the crankshaft sensor free of charge. A stall or sudden loss of power requires moving to a safe location and arranging BMW assistance; do not order a sensor from this card. ShowMeTheParts resolved exact X2 category fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F204" s="9" t="n">
         <x:v>0</x:v>
@@ -8561,21 +9317,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="277.20001220703125" hidden="0" customHeight="1">
+    <x:row r="205" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A205" s="40" t="n">
         <x:v>204</x:v>
       </x:c>
       <x:c r="B205" s="9" t="str">
-        <x:v>bmw-n55-injector-2012</x:v>
+        <x:v>bmw-x2-front-control-arm-bushings-2018</x:v>
       </x:c>
       <x:c r="C205" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2018-2023 | BMW | X2</x:v>
       </x:c>
       <x:c r="D205" s="9" t="str">
-        <x:v>High-Pressure Fuel Injector Issues</x:v>
+        <x:v>Front Control Arm Bushing Premature Wear</x:v>
       </x:c>
       <x:c r="E205" s="9" t="str">
-        <x:v>Replace failed injector(s) with correct index version. Consider cleaning service for carbon buildup. Use quality fuel. All injectors should be same index for proper operation.</x:v>
+        <x:v>Replace front control arms with new bushings (sold as complete assemblies by BMW). Aftermarket options with upgraded polyurethane bushings are available for longer life. Perform a four-wheel alignment after replacement.</x:v>
       </x:c>
       <x:c r="F205" s="9" t="n">
         <x:v>0</x:v>
@@ -8584,21 +9340,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="206" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A206" s="40" t="n">
         <x:v>205</x:v>
       </x:c>
       <x:c r="B206" s="9" t="str">
-        <x:v>bmw-n55-oil-filter-housing-2012</x:v>
+        <x:v>bmw-x2-oil-filter-housing-2018</x:v>
       </x:c>
       <x:c r="C206" s="9" t="str">
-        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
+        <x:v>2018-2023 | BMW | X2 | sDrive28i, xDrive28i | B48</x:v>
       </x:c>
       <x:c r="D206" s="9" t="str">
-        <x:v>Certain 2012 F30 N55 Vehicles Need an Oil-Filter-Housing Campaign Check</x:v>
+        <x:v>B48 Oil Filter Housing Gasket Leak/Cracking</x:v>
       </x:c>
       <x:c r="E206" s="9" t="str">
-        <x:v>Check the VIN and service-action history, then have a BMW-qualified technician inspect the housing material and leak source. Under the bulletin, the black plastic housing is replaced while the silver aluminum housing is left in place. ShowMeTheParts returned no exact 2012 335i oil-filter-housing candidate, and the former generic gasket links were removed.</x:v>
+        <x:v>Replace the cracked oil filter housing. OEM plastic housing replacement (BMW 11428596283, $412 dealer) will eventually crack again. RECOMMENDED: Install aftermarket aluminum upgrade housing ($250-350) which permanently eliminates the heat-cycling crack issue. FCP Euro kit 11428596283KT ($450) includes all gaskets and seals. If coolant and oil have mixed, perform complete oil flush and coolant system flush before installing new housing. Check for engine damage if contamination was prolonged.</x:v>
       </x:c>
       <x:c r="F206" s="9" t="n">
         <x:v>0</x:v>
@@ -8607,21 +9363,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="207" ht="330" hidden="0" customHeight="1">
       <x:c r="A207" s="40" t="n">
         <x:v>206</x:v>
       </x:c>
       <x:c r="B207" s="9" t="str">
-        <x:v>bmw-n55-valve-cover-2012</x:v>
+        <x:v>bmw-x2-oil-filter-housing-gasket-2018</x:v>
       </x:c>
       <x:c r="C207" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2018-2023 | BMW | X2 | B48</x:v>
       </x:c>
       <x:c r="D207" s="9" t="str">
-        <x:v>Valve Cover/Gasket Oil Leak</x:v>
+        <x:v>Oil Filter Housing Gasket Leak</x:v>
       </x:c>
       <x:c r="E207" s="9" t="str">
-        <x:v>Replace valve cover and gasket as an assembly (PCV valve is integrated). Clean oil from exhaust manifold. Monitor for leaks after repair. This is a common maintenance item at higher mileage.</x:v>
+        <x:v>Replace the oil filter housing gasket. Clean all oil-contaminated surfaces and inspect the serpentine belt for oil damage. Replace belt if oil-soaked. Use OEM-quality gasket material for longevity.</x:v>
       </x:c>
       <x:c r="F207" s="9" t="n">
         <x:v>0</x:v>
@@ -8630,21 +9386,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="208" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="208" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A208" s="40" t="n">
         <x:v>207</x:v>
       </x:c>
       <x:c r="B208" s="9" t="str">
-        <x:v>bmw-n55-vanos-2012</x:v>
+        <x:v>bmw-x2-tie-rod-recall-2019</x:v>
       </x:c>
       <x:c r="C208" s="9" t="str">
-        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
+        <x:v>2019-2019 | BMW | X2</x:v>
       </x:c>
       <x:c r="D208" s="9" t="str">
-        <x:v>Certain 2012 N55 3 Series Need a VANOS Gear-Bolt Recall Check</x:v>
+        <x:v>2019 X2 Steering Tie-Rod Safety Recall 19V-601</x:v>
       </x:c>
       <x:c r="E208" s="9" t="str">
-        <x:v>Check the VIN for campaign 14V-176 before ordering VANOS solenoids or gears. For an affected vehicle, BMW specifies replacing the VANOS gear bolts and inspecting for loose or broken bolts, with additional gear work only when the campaign procedure requires it. Recall work belongs with an authorized BMW center, so no commerce link is approved.</x:v>
+        <x:v>Check the VIN in BMW AIR or NHTSA for an open 19V-601 campaign. If open, an authorized BMW dealer checks both tie rods and replaces the tie rods and ball joints as necessary free of charge. Do not infer recall eligibility from model year alone or order steering parts from this card.</x:v>
       </x:c>
       <x:c r="F208" s="9" t="n">
         <x:v>0</x:v>
@@ -8653,21 +9409,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" ht="660" hidden="0" customHeight="1">
+    <x:row r="209" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A209" s="40" t="n">
         <x:v>208</x:v>
       </x:c>
       <x:c r="B209" s="9" t="str">
-        <x:v>bmw-n55-water-pump-2012</x:v>
+        <x:v>bmw-x2-transmission-jerking-2018</x:v>
       </x:c>
       <x:c r="C209" s="9" t="str">
-        <x:v>2012-2013 | BMW | 3 Series | N54T, N55</x:v>
+        <x:v>2018-2020 | BMW | X2</x:v>
       </x:c>
       <x:c r="D209" s="9" t="str">
-        <x:v>2012-2013 335i/335is Overheat Warnings Need Coolant-Pump Diagnosis</x:v>
+        <x:v>Aisin 8-Speed Transmission Jerking</x:v>
       </x:c>
       <x:c r="E209" s="9" t="str">
-        <x:v>Stop safely if an overheat warning appears and avoid continued operation until the cooling system is checked. Verify the chassis, engine and VIN, read fault memory and follow the current coolant-pump test plan before replacement. Settlement benefits were time-limited. ShowMeTheParts resolved five 2012 335i water-pump candidates, but fitment does not prove failure or remedy, so no commerce link is approved.</x:v>
+        <x:v>Start with transmission software recalibration at BMW dealer ($200-500) which may resolve calibration-related shifting issues. If software update does not resolve, transmission may require oil pump replacement or internal repair ($2,000-5,000). In severe cases with extensive oil pump neck wear, complete transmission replacement required ($5,000-7,000). Reference TSB GBSEL-SELP24 when visiting dealer.</x:v>
       </x:c>
       <x:c r="F209" s="9" t="n">
         <x:v>0</x:v>
@@ -8676,21 +9432,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="210" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A210" s="40" t="n">
         <x:v>209</x:v>
       </x:c>
       <x:c r="B210" s="9" t="str">
-        <x:v>bmw-x1-coolant-leak-2016</x:v>
+        <x:v>bmw-x2-valve-cover-gasket-2018</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1 | B-series</x:v>
+        <x:v>2018-2023 | BMW | X2</x:v>
       </x:c>
       <x:c r="D210" s="9" t="str">
-        <x:v>Coolant Leaks - Water Pump &amp; Thermostat - F48 X1</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E210" s="9" t="str">
-        <x:v>Replace failed water pump or thermostat housing. Electric water pump replacement is 2-3 hours labor. Thermostat housing is 1-2 hours. Always use BMW-approved coolant (blue or orange, do not mix). Properly bleed cooling system after repair to prevent air pockets. Inspect all coolant hoses during repair and replace if cracked. Preventive replacement of water pump at 80,000 miles recommended.</x:v>
+        <x:v>Replace valve cover gasket. Genuine BMW valve cover assembly 11127611278 ($200-350) includes integrated gasket. Labor typically 2-3 hours ($300-500). Total cost $700-1,000 at shop. DIY possible with basic tools to save $300-500 in labor. Replace spark plug tube seals at same time if applicable - labor overlap saves money. Monitor oil level between repairs.</x:v>
       </x:c>
       <x:c r="F210" s="9" t="n">
         <x:v>0</x:v>
@@ -8699,21 +9455,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="211" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="211" ht="990" hidden="0" customHeight="1">
       <x:c r="A211" s="40" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="B211" s="9" t="str">
-        <x:v>bmw-x1-n20-timing-chain-2013</x:v>
+        <x:v>bmw-x3-coolant-expansion-tank-2004</x:v>
       </x:c>
       <x:c r="C211" s="9" t="str">
-        <x:v>2013-2015 | BMW | X1 | N20</x:v>
+        <x:v>2004-2023 | BMW | X3</x:v>
       </x:c>
       <x:c r="D211" s="9" t="str">
-        <x:v>Lower-Engine Whine Requires X1 N20 Timing-Chain Diagnosis</x:v>
+        <x:v>Coolant Expansion Tank Cracking</x:v>
       </x:c>
       <x:c r="E211" s="9" t="str">
-        <x:v>Confirm the exact model, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Replace expansion tank and coolant ($50-100 DIY parts, $200-400 independent shop, $400-580 dealer). Very simple DIY repair taking 30 minutes - drain coolant, unbolt old tank, install new tank, refill with BMW-spec coolant (blue or pink/orange premix). Use Behr or OEM BMW expansion tank - Dorman aftermarket tanks may fail prematurely. YouTube and Pelicanparts have detailed DIY guides. PREVENTIVE: Replace every 5-7 years or 80-100k miles before cracks develop. Check tank regularly for hairline cracks. Don't ignore coolant leaks - can lead to catastrophic overheating and head gasket failure.</x:v>
       </x:c>
       <x:c r="F211" s="9" t="n">
         <x:v>0</x:v>
@@ -8722,67 +9478,67 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="212" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="212" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A212" s="40" t="n">
         <x:v>211</x:v>
       </x:c>
       <x:c r="B212" s="9" t="str">
-        <x:v>bmw-x1-n20-timing-chain-guide-2013</x:v>
+        <x:v>bmw-x3-electric-water-pump-2011</x:v>
       </x:c>
       <x:c r="C212" s="9" t="str">
-        <x:v>2013-2015 | BMW | X1 | N20</x:v>
+        <x:v>2011-2026 | BMW | X3</x:v>
       </x:c>
       <x:c r="D212" s="9" t="str">
-        <x:v>N20 Timing Chain Guide Failure</x:v>
+        <x:v>Electric Water Pump Failure</x:v>
       </x:c>
       <x:c r="E212" s="9" t="str">
-        <x:v>Replace timing chain, guides, tensioner, and both sprockets as a complete kit. The repair requires removing the front of the engine and is labor-intensive. Updated guide materials are available. Preventive replacement at 80,000 miles is recommended for high-mileage N20 engines.</x:v>
+        <x:v>Replace the electric water pump and thermostat together, as they are part of the same cooling circuit and the thermostat often fails concurrently. Bleed the cooling system thoroughly after replacement. Some owners carry a spare pump due to the sudden failure nature.</x:v>
       </x:c>
       <x:c r="F212" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G212" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="213" ht="396" hidden="0" customHeight="1">
+    <x:row r="213" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A213" s="40" t="n">
         <x:v>212</x:v>
       </x:c>
       <x:c r="B213" s="9" t="str">
-        <x:v>bmw-x1-oil-filter-housing-gasket-2013</x:v>
+        <x:v>bmw-x3-m-electric-wastegate-actuator-adaptation-fault-boost-cutout-ea</x:v>
       </x:c>
       <x:c r="C213" s="9" t="str">
-        <x:v>2013-2022 | BMW | X1 | N20, B48</x:v>
+        <x:v>2020-2020 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D213" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak</x:v>
+        <x:v>2020 X3 M Wastegate Adaptation Faults Require Software Diagnosis</x:v>
       </x:c>
       <x:c r="E213" s="9" t="str">
-        <x:v>Replace the oil filter housing gasket and clean all affected surfaces. Also inspect and replace the oil cooler gasket if present. Use only OEM-quality gaskets as aftermarket gaskets tend to fail prematurely. Typical repair takes 2-3 hours.</x:v>
+        <x:v>Confirm the production date, fault codes and current vehicle integration level. If the I-level is below S15A-20-03-510, a BMW-qualified repairer follows the bulletin and programs the vehicle with the specified or newer approved ISTA level. Diagnose unrelated mechanical noise separately; do not replace an actuator or turbocharger from this card.</x:v>
       </x:c>
       <x:c r="F213" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G213" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="214" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="214" ht="462" hidden="0" customHeight="1">
       <x:c r="A214" s="40" t="n">
         <x:v>213</x:v>
       </x:c>
       <x:c r="B214" s="9" t="str">
-        <x:v>bmw-x1-oil-leak-2016</x:v>
+        <x:v>bmw-x3-m-fuel-tank-inlet-check-valve-weld-failure-2021-x3-m</x:v>
       </x:c>
       <x:c r="C214" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1 | B46, B48</x:v>
+        <x:v>2021-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D214" s="9" t="str">
-        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - F48 X1</x:v>
+        <x:v>2021 X3 M Fuel-Tank Safety Recall 21V-199</x:v>
       </x:c>
       <x:c r="E214" s="9" t="str">
-        <x:v>Replace valve cover gasket and/or oil filter housing gasket as needed. Valve cover replacement is 2-3 hours labor. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on B-series engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
+        <x:v>Check the VIN for an open 21V-199 campaign. If open, an authorized BMW dealer replaces the fuel tank free of charge. If fuel odor or leakage appears, move safely away from traffic, stop, have occupants exit and contact BMW roadside assistance; do not continue driving or order a tank from this card.</x:v>
       </x:c>
       <x:c r="F214" s="9" t="n">
         <x:v>0</x:v>
@@ -8791,21 +9547,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="215" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="215" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A215" s="40" t="n">
         <x:v>214</x:v>
       </x:c>
       <x:c r="B215" s="9" t="str">
-        <x:v>bmw-x1-suspension-bushing-2016</x:v>
+        <x:v>bmw-x3-m-idrive-control-display-blank-screen-infotainment-glitches-f9</x:v>
       </x:c>
       <x:c r="C215" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1</x:v>
+        <x:v>2020-2021 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D215" s="9" t="str">
-        <x:v>Front Suspension Bushing &amp; Control Arm Wear - F48 X1</x:v>
+        <x:v>iDrive Control Display Blank Screen and Infotainment Glitches - F97 X3 M (2019-2021)</x:v>
       </x:c>
       <x:c r="E215" s="9" t="str">
-        <x:v>Replace worn control arms or bushings. Most shops replace complete control arms (with integrated bushings) rather than pressing in new bushings alone. Alignment required after replacement. Inspect all suspension components while vehicle is lifted. Consider replacing both sides even if only one shows symptoms to avoid repeat labor costs. Use OEM or quality aftermarket parts (Lemforder, Meyle HD) for longevity.</x:v>
+        <x:v>First try the latest iDrive/head-unit software update at the dealer, which resolves many of the early glitches, reboots, and camera issues. If the display panel hardware has failed (lines, persistent blank screen with backlight off), the control display/screen assembly is replaced. A soft reset (press-and-hold volume/power) can temporarily clear a frozen screen.</x:v>
       </x:c>
       <x:c r="F215" s="9" t="n">
         <x:v>0</x:v>
@@ -8814,21 +9570,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="216" ht="660" hidden="0" customHeight="1">
+    <x:row r="216" ht="462" hidden="0" customHeight="1">
       <x:c r="A216" s="40" t="n">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B216" s="9" t="str">
-        <x:v>bmw-x1-transfer-case-2013</x:v>
+        <x:v>bmw-x3-m-improperly-welded-front-seat-frame-2019-2021-x3-m</x:v>
       </x:c>
       <x:c r="C216" s="9" t="str">
-        <x:v>2013-2023 | BMW | X1</x:v>
+        <x:v>2021-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D216" s="9" t="str">
-        <x:v>Transfer Case Failure - xDrive Models E84/F48 X1</x:v>
+        <x:v>2021 X3 M Front Seat-Frame Safety Recall 23V-211</x:v>
       </x:c>
       <x:c r="E216" s="9" t="str">
-        <x:v>Diagnose specific failure point. Transfer case actuator motor can be replaced separately ($800-1,200) if caught early. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors for better durability. Common wear item on high-mileage xDrive models.</x:v>
+        <x:v>Check the VIN for an open 23V-211 campaign. If open, an authorized BMW dealer replaces the affected front seat frame and backrest free of charge using VIN-selected parts. Contact BMW promptly if a front seat vibrates or makes abnormal noise; do not order seat components from this card.</x:v>
       </x:c>
       <x:c r="F216" s="9" t="n">
         <x:v>0</x:v>
@@ -8837,21 +9593,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="217" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="217" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A217" s="40" t="n">
         <x:v>216</x:v>
       </x:c>
       <x:c r="B217" s="9" t="str">
-        <x:v>bmw-x1-transfer-case-actuator-2013</x:v>
+        <x:v>bmw-x3-m-low-mounted-engine-oil-cooler-vulnerable-to-road-debris-punc</x:v>
       </x:c>
       <x:c r="C217" s="9" t="str">
-        <x:v>2013-2022 | BMW | X1</x:v>
+        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D217" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure</x:v>
+        <x:v>Low-Mounted Engine Oil Cooler Vulnerable to Road-Debris Puncture - F97 X3 M (S58)</x:v>
       </x:c>
       <x:c r="E217" s="9" t="str">
-        <x:v>Replace the transfer case actuator motor (also called the servo motor). The transfer case itself usually does not need replacement. Ensure the transfer case fluid is changed at the same time. Some owners report success with rebuilt actuators at lower cost.</x:v>
+        <x:v>Inspect the oil cooler periodically for stone damage and weeping; fit a protective mesh/guard in front of the cooler as preventive insurance (popular among track and spirited-use owners). If punctured, stop driving immediately and replace the oil cooler and refill with the correct oil; verify no bearing damage occurred from any oil starvation.</x:v>
       </x:c>
       <x:c r="F217" s="9" t="n">
         <x:v>0</x:v>
@@ -8860,21 +9616,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="218" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="218" ht="594" hidden="0" customHeight="1">
       <x:c r="A218" s="40" t="n">
         <x:v>217</x:v>
       </x:c>
       <x:c r="B218" s="9" t="str">
-        <x:v>bmw-x2-b48-timing-chain-tensioner-2018</x:v>
+        <x:v>bmw-x3-m-oem-plastic-charge-pipe-cracking-blow-off-under-boost-f97-x3</x:v>
       </x:c>
       <x:c r="C218" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | B48</x:v>
+        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D218" s="9" t="str">
-        <x:v>B48 Timing Chain Tensioner Weakness</x:v>
+        <x:v>OEM Plastic Charge Pipe Cracking / Blow-Off Under Boost - F97 X3 M (S58)</x:v>
       </x:c>
       <x:c r="E218" s="9" t="str">
-        <x:v>Replace the timing chain tensioner and inspect the chain and guides. If the chain has stretched beyond specification, replace the full timing chain kit. Updated tensioner design from BMW addresses the oil pressure retention issue.</x:v>
+        <x:v>Replace the OEM plastic charge pipe with an aluminum (or reinforced) aftermarket charge pipe from suppliers such as FTP, Racing Dynamics, or Kies; this is the standard durable fix and is strongly recommended before or alongside any tune. A failed OEM pipe can be re-fitted with a new OEM unit but the same failure mode tends to recur, especially on modified cars.</x:v>
       </x:c>
       <x:c r="F218" s="9" t="n">
         <x:v>0</x:v>
@@ -8883,21 +9639,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="219" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="219" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A219" s="40" t="n">
         <x:v>218</x:v>
       </x:c>
       <x:c r="B219" s="9" t="str">
-        <x:v>bmw-x2-crankshaft-sensor-recall-2018</x:v>
+        <x:v>bmw-x3-n20-timing-chain-2011</x:v>
       </x:c>
       <x:c r="C219" s="9" t="str">
-        <x:v>2018-2018 | BMW | X2</x:v>
+        <x:v>2011-2017 | BMW | X3 | N20</x:v>
       </x:c>
       <x:c r="D219" s="9" t="str">
-        <x:v>2018 X2 Crankshaft Sensor Safety Recall 18V-465</x:v>
+        <x:v>N20 Timing Chain Guide Failure</x:v>
       </x:c>
       <x:c r="E219" s="9" t="str">
-        <x:v>Check the VIN for an open 18V-465 campaign. If open, an authorized BMW dealer replaces the crankshaft sensor free of charge. A stall or sudden loss of power requires moving to a safe location and arranging BMW assistance; do not order a sensor from this card. ShowMeTheParts resolved exact X2 category fitment only, so no commerce link is approved.</x:v>
+        <x:v>Replace the complete timing chain kit including chain, guides, tensioner, and sprockets. Preventive replacement is strongly recommended at 80,000 miles before failure occurs. The updated guide design uses more durable materials.</x:v>
       </x:c>
       <x:c r="F219" s="9" t="n">
         <x:v>0</x:v>
@@ -8906,21 +9662,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="220" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="220" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A220" s="40" t="n">
         <x:v>219</x:v>
       </x:c>
       <x:c r="B220" s="9" t="str">
-        <x:v>bmw-x2-front-control-arm-bushings-2018</x:v>
+        <x:v>bmw-x3-n20-timing-chain-2012</x:v>
       </x:c>
       <x:c r="C220" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2</x:v>
+        <x:v>2013-2015 | BMW | X3 | N20</x:v>
       </x:c>
       <x:c r="D220" s="9" t="str">
-        <x:v>Front Control Arm Bushing Premature Wear</x:v>
+        <x:v>Lower-Engine Whine Requires X3 N20 Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E220" s="9" t="str">
-        <x:v>Replace front control arms with new bushings (sold as complete assemblies by BMW). Aftermarket options with upgraded polyurethane bushings are available for longer life. Perform a four-wheel alignment after replacement.</x:v>
+        <x:v>Confirm the exact X3 variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F220" s="9" t="n">
         <x:v>0</x:v>
@@ -8929,21 +9685,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="221" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="221" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A221" s="40" t="n">
         <x:v>220</x:v>
       </x:c>
       <x:c r="B221" s="9" t="str">
-        <x:v>bmw-x2-oil-filter-housing-2018</x:v>
+        <x:v>bmw-x3-oil-filter-housing-gasket-2007</x:v>
       </x:c>
       <x:c r="C221" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | sDrive28i, xDrive28i | B48</x:v>
+        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
       </x:c>
       <x:c r="D221" s="9" t="str">
-        <x:v>B48 Oil Filter Housing Gasket Leak/Cracking</x:v>
+        <x:v>Oil Filter Housing Gasket Leak (N52, N20 Engines)</x:v>
       </x:c>
       <x:c r="E221" s="9" t="str">
-        <x:v>Replace the cracked oil filter housing. OEM plastic housing replacement (BMW 11428596283, $412 dealer) will eventually crack again. RECOMMENDED: Install aftermarket aluminum upgrade housing ($250-350) which permanently eliminates the heat-cycling crack issue. FCP Euro kit 11428596283KT ($450) includes all gaskets and seals. If coolant and oil have mixed, perform complete oil flush and coolant system flush before installing new housing. Check for engine damage if contamination was prolonged.</x:v>
+        <x:v>Replace oil filter housing gasket and oil cooler gasket ($40-80 DIY repair kit, $300-500 independent shop, $500-800 dealer). Requires draining some coolant and oil, removing housing, replacing gaskets, reassembling. Moderate DIY difficulty - Pelicanparts and YouTube have detailed model-specific guides. Use Victor Reinz or OEM BMW gasket kit for long-lasting seal - cheap gaskets leak within 20k miles. Address leak early before oil damages serpentine belt or alternator.</x:v>
       </x:c>
       <x:c r="F221" s="9" t="n">
         <x:v>0</x:v>
@@ -8952,21 +9708,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="222" ht="330" hidden="0" customHeight="1">
+    <x:row r="222" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A222" s="40" t="n">
         <x:v>221</x:v>
       </x:c>
       <x:c r="B222" s="9" t="str">
-        <x:v>bmw-x2-oil-filter-housing-gasket-2018</x:v>
+        <x:v>bmw-x3-transfer-case-actuator-2004</x:v>
       </x:c>
       <x:c r="C222" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | B48</x:v>
+        <x:v>2004-2023 | BMW | X3</x:v>
       </x:c>
       <x:c r="D222" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak</x:v>
+        <x:v>Transfer Case Actuator Motor Failure (xDrive AWD System)</x:v>
       </x:c>
       <x:c r="E222" s="9" t="str">
-        <x:v>Replace the oil filter housing gasket. Clean all oil-contaminated surfaces and inspect the serpentine belt for oil damage. Replace belt if oil-soaked. Use OEM-quality gasket material for longevity.</x:v>
+        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket repair kit. DIY repair kits cost $100-150 and include replacement plastic gears, clips, and seals - straightforward installation saves $1,200+. Complete actuator motor replacement costs $540 for the assembly if DIY, or $1,500-2,200 at dealer. If transfer case itself is damaged from prolonged actuator failure, complete transfer case replacement costs $1,400-3,300. PREVENTIVE: If buying used X3 over 80k miles, budget for this repair - it's "when not if" on xDrive models. Check for clicking noise when shutting off ignition.</x:v>
       </x:c>
       <x:c r="F222" s="9" t="n">
         <x:v>0</x:v>
@@ -8975,21 +9731,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="223" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="223" ht="396" hidden="0" customHeight="1">
       <x:c r="A223" s="40" t="n">
         <x:v>222</x:v>
       </x:c>
       <x:c r="B223" s="9" t="str">
-        <x:v>bmw-x2-tie-rod-recall-2019</x:v>
+        <x:v>bmw-x3-transfer-case-actuator-2011</x:v>
       </x:c>
       <x:c r="C223" s="9" t="str">
-        <x:v>2019-2019 | BMW | X2</x:v>
+        <x:v>2011-2026 | BMW | X3</x:v>
       </x:c>
       <x:c r="D223" s="9" t="str">
-        <x:v>2019 X2 Steering Tie-Rod Safety Recall 19V-601</x:v>
+        <x:v>Transfer Case Actuator Motor Failure</x:v>
       </x:c>
       <x:c r="E223" s="9" t="str">
-        <x:v>Check the VIN in BMW AIR or NHTSA for an open 19V-601 campaign. If open, an authorized BMW dealer checks both tie rods and replaces the tie rods and ball joints as necessary free of charge. Do not infer recall eligibility from model year alone or order steering parts from this card.</x:v>
+        <x:v>Replace the transfer case actuator motor. Change the transfer case fluid at the same time. The actuator can be replaced without removing the entire transfer case. Rebuilt units are available at lower cost but OEM is recommended for reliability.</x:v>
       </x:c>
       <x:c r="F223" s="9" t="n">
         <x:v>0</x:v>
@@ -8998,67 +9754,67 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="224" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="224" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A224" s="40" t="n">
         <x:v>223</x:v>
       </x:c>
       <x:c r="B224" s="9" t="str">
-        <x:v>bmw-x2-transmission-jerking-2018</x:v>
+        <x:v>bmw-x3-valve-cover-gasket-2004</x:v>
       </x:c>
       <x:c r="C224" s="9" t="str">
-        <x:v>2018-2020 | BMW | X2</x:v>
+        <x:v>2004-2017 | BMW | X3 | 2.5i, 3.0i, 3.0si | M54, N52</x:v>
       </x:c>
       <x:c r="D224" s="9" t="str">
-        <x:v>Aisin 8-Speed Transmission Jerking</x:v>
+        <x:v>Valve Cover Gasket Oil Leaks (M54, N52 Engines)</x:v>
       </x:c>
       <x:c r="E224" s="9" t="str">
-        <x:v>Start with transmission software recalibration at BMW dealer ($200-500) which may resolve calibration-related shifting issues. If software update does not resolve, transmission may require oil pump replacement or internal repair ($2,000-5,000). In severe cases with extensive oil pump neck wear, complete transmission replacement required ($5,000-7,000). Reference TSB GBSEL-SELP24 when visiting dealer.</x:v>
+        <x:v>Replace valve cover gasket and VANOS solenoid o-rings ($300-500 independent shop, $700-1,000 dealer, $80-150 DIY parts). On M54 engines, also replace ignition coil boots if contaminated by oil ($50 additional). Use OEM BMW gasket or Victor Reinz brand - aftermarket quality matters for long-term seal. Relatively straightforward DIY repair - saves $200-400 in labor. YouTube and Bimmerfest have detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage).</x:v>
       </x:c>
       <x:c r="F224" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G224" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="225" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="225" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A225" s="40" t="n">
         <x:v>224</x:v>
       </x:c>
       <x:c r="B225" s="9" t="str">
-        <x:v>bmw-x2-valve-cover-gasket-2018</x:v>
+        <x:v>bmw-x3-valve-cover-gasket-2011</x:v>
       </x:c>
       <x:c r="C225" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2</x:v>
+        <x:v>2011-2022 | BMW | X3 | N20, B48</x:v>
       </x:c>
       <x:c r="D225" s="9" t="str">
         <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E225" s="9" t="str">
-        <x:v>Replace valve cover gasket. Genuine BMW valve cover assembly 11127611278 ($200-350) includes integrated gasket. Labor typically 2-3 hours ($300-500). Total cost $700-1,000 at shop. DIY possible with basic tools to save $300-500 in labor. Replace spark plug tube seals at same time if applicable - labor overlap saves money. Monitor oil level between repairs.</x:v>
+        <x:v>Replace the valve cover gasket. Inspect the valve cover for warping or cracks — if damaged, replace the entire cover assembly. Clean all oil residue from surrounding components. Use a torque wrench to prevent over-tightening which causes cover warping.</x:v>
       </x:c>
       <x:c r="F225" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G225" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="226" ht="990" hidden="0" customHeight="1">
+    <x:row r="226" ht="858" hidden="0" customHeight="1">
       <x:c r="A226" s="40" t="n">
         <x:v>225</x:v>
       </x:c>
       <x:c r="B226" s="9" t="str">
-        <x:v>bmw-x3-coolant-expansion-tank-2004</x:v>
+        <x:v>bmw-x3-vanos-solenoid-2007</x:v>
       </x:c>
       <x:c r="C226" s="9" t="str">
-        <x:v>2004-2023 | BMW | X3</x:v>
+        <x:v>2007-2017 | BMW | X3 | M40i, M50, xDrive35i | N52, N55</x:v>
       </x:c>
       <x:c r="D226" s="9" t="str">
-        <x:v>Coolant Expansion Tank Cracking</x:v>
+        <x:v>VANOS Solenoid Failure (N52, N55 Engines)</x:v>
       </x:c>
       <x:c r="E226" s="9" t="str">
-        <x:v>Replace expansion tank and coolant ($50-100 DIY parts, $200-400 independent shop, $400-580 dealer). Very simple DIY repair taking 30 minutes - drain coolant, unbolt old tank, install new tank, refill with BMW-spec coolant (blue or pink/orange premix). Use Behr or OEM BMW expansion tank - Dorman aftermarket tanks may fail prematurely. YouTube and Pelicanparts have detailed DIY guides. PREVENTIVE: Replace every 5-7 years or 80-100k miles before cracks develop. Check tank regularly for hairline cracks. Don't ignore coolant leaks - can lead to catastrophic overheating and head gasket failure.</x:v>
+        <x:v>Replace VANOS solenoids and seals ($250-400 European shops, $729-882 US average). Use high-quality oil (5W-30 or 0W-40 BMW LL-01 spec) and change every 5,000-7,000 miles to prevent future failures - cheap oil or extended intervals kill VANOS solenoids. Some cases may require complete VANOS unit rebuild ($1,500-2,500). PREVENTIVE: Replace VANOS solenoids and seals every 50k miles as maintenance - much cheaper than waiting for failure. On F25 X3 with N52/N55, check TSB SI B12 14 10 for VANOS gear assembly bolt issue.</x:v>
       </x:c>
       <x:c r="F226" s="9" t="n">
         <x:v>0</x:v>
@@ -9067,44 +9823,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="227" ht="1016.4000244140625" hidden="0" customHeight="1">
       <x:c r="A227" s="40" t="n">
         <x:v>226</x:v>
       </x:c>
       <x:c r="B227" s="9" t="str">
-        <x:v>bmw-x3-electric-water-pump-2011</x:v>
+        <x:v>bmw-x3-wastegate-rattle-2011</x:v>
       </x:c>
       <x:c r="C227" s="9" t="str">
-        <x:v>2011-2026 | BMW | X3</x:v>
+        <x:v>2011-2023 | BMW | X3 | M40i, M50, sDrive30i, xDrive28i, xDrive30i, xDrive35i</x:v>
       </x:c>
       <x:c r="D227" s="9" t="str">
-        <x:v>Electric Water Pump Failure</x:v>
+        <x:v>Turbocharger Wastegate Rattle (N55, N20, B58 Engines)</x:v>
       </x:c>
       <x:c r="E227" s="9" t="str">
-        <x:v>Replace the electric water pump and thermostat together, as they are part of the same cooling circuit and the thermostat often fails concurrently. Bleed the cooling system thoroughly after replacement. Some owners carry a spare pump due to the sudden failure nature.</x:v>
+        <x:v>Replace wastegate actuator ($400-800) or use aftermarket wastegate repair kit with upgraded stainless steel bushings ($150-300). Some cases require complete turbocharger replacement ($2,000-$4,000). VTT (Vargas Turbo Technologies) repair kits popular on forums - upgraded materials prevent future rattle. MONITORING: Early wastegate rattle may be harmless (annoying but no performance loss). If car boosts normally and no underboost codes, can monitor rattle without urgent repair. However, if check engine light appears with code 30FF or boost pressure drops, repair immediately to prevent turbo damage.</x:v>
       </x:c>
       <x:c r="F227" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G227" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="228" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="228" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A228" s="40" t="n">
         <x:v>227</x:v>
       </x:c>
       <x:c r="B228" s="9" t="str">
-        <x:v>bmw-x3-m-electric-wastegate-actuator-adaptation-fault-boost-cutout-ea</x:v>
+        <x:v>bmw-x3-water-pump-2007</x:v>
       </x:c>
       <x:c r="C228" s="9" t="str">
-        <x:v>2020-2020 | BMW | X3 M | S58</x:v>
+        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
       </x:c>
       <x:c r="D228" s="9" t="str">
-        <x:v>2020 X3 M Wastegate Adaptation Faults Require Software Diagnosis</x:v>
+        <x:v>Electric Water Pump Failure (N52, N20 Engines)</x:v>
       </x:c>
       <x:c r="E228" s="9" t="str">
-        <x:v>Confirm the production date, fault codes and current vehicle integration level. If the I-level is below S15A-20-03-510, a BMW-qualified repairer follows the bulletin and programs the vehicle with the specified or newer approved ISTA level. Diagnose unrelated mechanical noise separately; do not replace an actuator or turbocharger from this card.</x:v>
+        <x:v>Replace electric water pump at first sign of failure ($800 parts + labor). Consider preventative replacement at 70-80k miles to avoid being stranded ($400 parts, DIY-able). CRITICAL: If you own 2013-2017 X3 28i, verify recall repair (protective shield installation) has been completed to prevent fire risk - check with BMW dealer using VIN. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps cylinder heads ($4,000+ repair). Call tow truck.</x:v>
       </x:c>
       <x:c r="F228" s="9" t="n">
         <x:v>0</x:v>
@@ -9113,21 +9869,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="229" ht="462" hidden="0" customHeight="1">
+    <x:row r="229" ht="1240.800048828125" hidden="0" customHeight="1">
       <x:c r="A229" s="40" t="n">
         <x:v>228</x:v>
       </x:c>
       <x:c r="B229" s="9" t="str">
-        <x:v>bmw-x3-m-fuel-tank-inlet-check-valve-weld-failure-2021-x3-m</x:v>
+        <x:v>bmw-x3m-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C229" s="9" t="str">
-        <x:v>2021-2021 | BMW | X3 M</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D229" s="9" t="str">
-        <x:v>2021 X3 M Fuel-Tank Safety Recall 21V-199</x:v>
+        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E229" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-199 campaign. If open, an authorized BMW dealer replaces the fuel tank free of charge. If fuel odor or leakage appears, move safely away from traffic, stop, have occupants exit and contact BMW roadside assistance; do not continue driving or order a tank from this card.</x:v>
+        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
       </x:c>
       <x:c r="F229" s="9" t="n">
         <x:v>0</x:v>
@@ -9136,21 +9892,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="230" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="230" ht="1188" hidden="0" customHeight="1">
       <x:c r="A230" s="40" t="n">
         <x:v>229</x:v>
       </x:c>
       <x:c r="B230" s="9" t="str">
-        <x:v>bmw-x3-m-idrive-control-display-blank-screen-infotainment-glitches-f9</x:v>
+        <x:v>bmw-x3m-cooling-track-use-2020</x:v>
       </x:c>
       <x:c r="C230" s="9" t="str">
-        <x:v>2020-2021 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D230" s="9" t="str">
-        <x:v>iDrive Control Display Blank Screen and Infotainment Glitches - F97 X3 M (2019-2021)</x:v>
+        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E230" s="9" t="str">
-        <x:v>First try the latest iDrive/head-unit software update at the dealer, which resolves many of the early glitches, reboots, and camera issues. If the display panel hardware has failed (lines, persistent blank screen with backlight off), the control display/screen assembly is replaced. A soft reset (press-and-hold volume/power) can temporarily clear a frozen screen.</x:v>
+        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
       </x:c>
       <x:c r="F230" s="9" t="n">
         <x:v>0</x:v>
@@ -9159,21 +9915,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="231" ht="462" hidden="0" customHeight="1">
+    <x:row r="231" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A231" s="40" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="B231" s="9" t="str">
-        <x:v>bmw-x3-m-improperly-welded-front-seat-frame-2019-2021-x3-m</x:v>
+        <x:v>bmw-x3m-differential-bolt-2020</x:v>
       </x:c>
       <x:c r="C231" s="9" t="str">
-        <x:v>2021-2021 | BMW | X3 M</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D231" s="9" t="str">
-        <x:v>2021 X3 M Front Seat-Frame Safety Recall 23V-211</x:v>
+        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E231" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-211 campaign. If open, an authorized BMW dealer replaces the affected front seat frame and backrest free of charge using VIN-selected parts. Contact BMW promptly if a front seat vibrates or makes abnormal noise; do not order seat components from this card.</x:v>
+        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
       </x:c>
       <x:c r="F231" s="9" t="n">
         <x:v>0</x:v>
@@ -9182,21 +9938,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="232" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="232" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A232" s="40" t="n">
         <x:v>231</x:v>
       </x:c>
       <x:c r="B232" s="9" t="str">
-        <x:v>bmw-x3-m-low-mounted-engine-oil-cooler-vulnerable-to-road-debris-punc</x:v>
+        <x:v>bmw-x3m-s58-bearing-recall-2020</x:v>
       </x:c>
       <x:c r="C232" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D232" s="9" t="str">
-        <x:v>Low-Mounted Engine Oil Cooler Vulnerable to Road-Debris Puncture - F97 X3 M (S58)</x:v>
+        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E232" s="9" t="str">
-        <x:v>Inspect the oil cooler periodically for stone damage and weeping; fit a protective mesh/guard in front of the cooler as preventive insurance (popular among track and spirited-use owners). If punctured, stop driving immediately and replace the oil cooler and refill with the correct oil; verify no bearing damage occurred from any oil starvation.</x:v>
+        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
       </x:c>
       <x:c r="F232" s="9" t="n">
         <x:v>0</x:v>
@@ -9205,21 +9961,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="233" ht="594" hidden="0" customHeight="1">
+    <x:row r="233" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A233" s="40" t="n">
         <x:v>232</x:v>
       </x:c>
       <x:c r="B233" s="9" t="str">
-        <x:v>bmw-x3-m-oem-plastic-charge-pipe-cracking-blow-off-under-boost-f97-x3</x:v>
+        <x:v>bmw-x3m-transfer-case-2020</x:v>
       </x:c>
       <x:c r="C233" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D233" s="9" t="str">
-        <x:v>OEM Plastic Charge Pipe Cracking / Blow-Off Under Boost - F97 X3 M (S58)</x:v>
+        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E233" s="9" t="str">
-        <x:v>Replace the OEM plastic charge pipe with an aluminum (or reinforced) aftermarket charge pipe from suppliers such as FTP, Racing Dynamics, or Kies; this is the standard durable fix and is strongly recommended before or alongside any tune. A failed OEM pipe can be re-fitted with a new OEM unit but the same failure mode tends to recur, especially on modified cars.</x:v>
+        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
       </x:c>
       <x:c r="F233" s="9" t="n">
         <x:v>0</x:v>
@@ -9228,21 +9984,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="234" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="234" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A234" s="40" t="n">
         <x:v>233</x:v>
       </x:c>
       <x:c r="B234" s="9" t="str">
-        <x:v>bmw-x3-n20-timing-chain-2011</x:v>
+        <x:v>bmw-x4-n20-timing-chain-2015</x:v>
       </x:c>
       <x:c r="C234" s="9" t="str">
-        <x:v>2011-2017 | BMW | X3 | N20</x:v>
+        <x:v>2015-2016 | BMW | X4 | xDrive28i, xDrive30i</x:v>
       </x:c>
       <x:c r="D234" s="9" t="str">
-        <x:v>N20 Timing Chain Guide Failure</x:v>
+        <x:v>N20 Timing Chain Premature Failure - F26 X4 xDrive28i</x:v>
       </x:c>
       <x:c r="E234" s="9" t="str">
-        <x:v>Replace the complete timing chain kit including chain, guides, tensioner, and sprockets. Preventive replacement is strongly recommended at 80,000 miles before failure occurs. The updated guide design uses more durable materials.</x:v>
+        <x:v>Complete timing chain kit replacement including chain, guides, tensioner, and sprockets. Must be performed by experienced BMW technician. Preventive replacement recommended at 60,000-80,000 miles. BMW extended warranty to 8 years/100,000 miles under class action settlement. Upgraded reinforced chain kit available from aftermarket. Labor is 10-14 hours for X4 due to AWD and tight engine bay.</x:v>
       </x:c>
       <x:c r="F234" s="9" t="n">
         <x:v>0</x:v>
@@ -9251,21 +10007,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="235" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A235" s="40" t="n">
         <x:v>234</x:v>
       </x:c>
       <x:c r="B235" s="9" t="str">
-        <x:v>bmw-x3-n20-timing-chain-2012</x:v>
+        <x:v>bmw-x4-n20-timing-chain-guide-2015</x:v>
       </x:c>
       <x:c r="C235" s="9" t="str">
-        <x:v>2013-2015 | BMW | X3 | N20</x:v>
+        <x:v>2015-2015 | BMW | X4 | N20</x:v>
       </x:c>
       <x:c r="D235" s="9" t="str">
-        <x:v>Lower-Engine Whine Requires X3 N20 Timing-Chain Diagnosis</x:v>
+        <x:v>2015 X4 N20 Lower-Engine Whine Requires Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E235" s="9" t="str">
-        <x:v>Confirm the exact X3 variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Confirm the exact xDrive28i variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F235" s="9" t="n">
         <x:v>0</x:v>
@@ -9274,21 +10030,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="236" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="236" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A236" s="40" t="n">
         <x:v>235</x:v>
       </x:c>
       <x:c r="B236" s="9" t="str">
-        <x:v>bmw-x3-oil-filter-housing-gasket-2007</x:v>
+        <x:v>bmw-x4-oil-leak-2015</x:v>
       </x:c>
       <x:c r="C236" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D236" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak (N52, N20 Engines)</x:v>
+        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - All Models</x:v>
       </x:c>
       <x:c r="E236" s="9" t="str">
-        <x:v>Replace oil filter housing gasket and oil cooler gasket ($40-80 DIY repair kit, $300-500 independent shop, $500-800 dealer). Requires draining some coolant and oil, removing housing, replacing gaskets, reassembling. Moderate DIY difficulty - Pelicanparts and YouTube have detailed model-specific guides. Use Victor Reinz or OEM BMW gasket kit for long-lasting seal - cheap gaskets leak within 20k miles. Address leak early before oil damages serpentine belt or alternator.</x:v>
+        <x:v>Replace valve cover gasket and/or oil filter housing gasket. Valve cover replacement is 3-4 hours labor on X4. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on BMW turbo engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
       </x:c>
       <x:c r="F236" s="9" t="n">
         <x:v>0</x:v>
@@ -9297,21 +10053,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="237" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="237" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A237" s="40" t="n">
         <x:v>236</x:v>
       </x:c>
       <x:c r="B237" s="9" t="str">
-        <x:v>bmw-x3-transfer-case-actuator-2004</x:v>
+        <x:v>bmw-x4-rear-differential-mount-2015</x:v>
       </x:c>
       <x:c r="C237" s="9" t="str">
-        <x:v>2004-2023 | BMW | X3</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D237" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure (xDrive AWD System)</x:v>
+        <x:v>Rear Differential Mount Bushing Failure</x:v>
       </x:c>
       <x:c r="E237" s="9" t="str">
-        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket repair kit. DIY repair kits cost $100-150 and include replacement plastic gears, clips, and seals - straightforward installation saves $1,200+. Complete actuator motor replacement costs $540 for the assembly if DIY, or $1,500-2,200 at dealer. If transfer case itself is damaged from prolonged actuator failure, complete transfer case replacement costs $1,400-3,300. PREVENTIVE: If buying used X3 over 80k miles, budget for this repair - it's "when not if" on xDrive models. Check for clicking noise when shutting off ignition.</x:v>
+        <x:v>Replace rear differential mount bushings. Both front and rear differential bushings should be inspected and replaced as a set. Upgraded aftermarket bushings with stiffer rubber or polyurethane are available for longer service life.</x:v>
       </x:c>
       <x:c r="F237" s="9" t="n">
         <x:v>0</x:v>
@@ -9320,21 +10076,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="238" ht="396" hidden="0" customHeight="1">
+    <x:row r="238" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A238" s="40" t="n">
         <x:v>237</x:v>
       </x:c>
       <x:c r="B238" s="9" t="str">
-        <x:v>bmw-x3-transfer-case-actuator-2011</x:v>
+        <x:v>bmw-x4-transfer-case-2015</x:v>
       </x:c>
       <x:c r="C238" s="9" t="str">
-        <x:v>2011-2026 | BMW | X3</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D238" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure</x:v>
+        <x:v>Transfer Case Actuator Motor Failure - All xDrive X4</x:v>
       </x:c>
       <x:c r="E238" s="9" t="str">
-        <x:v>Replace the transfer case actuator motor. Change the transfer case fluid at the same time. The actuator can be replaced without removing the entire transfer case. Rebuilt units are available at lower cost but OEM is recommended for reliability.</x:v>
+        <x:v>Diagnose specific failure. Transfer case actuator motor replacement ($800-1,200) is most common. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors. Common wear item on high-mileage xDrive BMW models.</x:v>
       </x:c>
       <x:c r="F238" s="9" t="n">
         <x:v>0</x:v>
@@ -9343,67 +10099,67 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="239" ht="1240.800048828125" hidden="0" customHeight="1">
       <x:c r="A239" s="40" t="n">
         <x:v>238</x:v>
       </x:c>
       <x:c r="B239" s="9" t="str">
-        <x:v>bmw-x3-valve-cover-gasket-2004</x:v>
+        <x:v>bmw-x4m-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C239" s="9" t="str">
-        <x:v>2004-2017 | BMW | X3 | 2.5i, 3.0i, 3.0si | M54, N52</x:v>
+        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
       </x:c>
       <x:c r="D239" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leaks (M54, N52 Engines)</x:v>
+        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E239" s="9" t="str">
-        <x:v>Replace valve cover gasket and VANOS solenoid o-rings ($300-500 independent shop, $700-1,000 dealer, $80-150 DIY parts). On M54 engines, also replace ignition coil boots if contaminated by oil ($50 additional). Use OEM BMW gasket or Victor Reinz brand - aftermarket quality matters for long-term seal. Relatively straightforward DIY repair - saves $200-400 in labor. YouTube and Bimmerfest have detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage).</x:v>
+        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
       </x:c>
       <x:c r="F239" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G239" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="240" ht="1188" hidden="0" customHeight="1">
       <x:c r="A240" s="40" t="n">
         <x:v>239</x:v>
       </x:c>
       <x:c r="B240" s="9" t="str">
-        <x:v>bmw-x3-valve-cover-gasket-2011</x:v>
+        <x:v>bmw-x4m-cooling-track-use-2020</x:v>
       </x:c>
       <x:c r="C240" s="9" t="str">
-        <x:v>2011-2022 | BMW | X3 | N20, B48</x:v>
+        <x:v>2020-2023 | BMW | X4 M</x:v>
       </x:c>
       <x:c r="D240" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E240" s="9" t="str">
-        <x:v>Replace the valve cover gasket. Inspect the valve cover for warping or cracks — if damaged, replace the entire cover assembly. Clean all oil residue from surrounding components. Use a torque wrench to prevent over-tightening which causes cover warping.</x:v>
+        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
       </x:c>
       <x:c r="F240" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G240" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="241" ht="858" hidden="0" customHeight="1">
+    <x:row r="241" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A241" s="40" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="B241" s="9" t="str">
-        <x:v>bmw-x3-vanos-solenoid-2007</x:v>
+        <x:v>bmw-x4m-differential-bolt-2020</x:v>
       </x:c>
       <x:c r="C241" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | M40i, M50, xDrive35i | N52, N55</x:v>
+        <x:v>2020-2023 | BMW | X4 M</x:v>
       </x:c>
       <x:c r="D241" s="9" t="str">
-        <x:v>VANOS Solenoid Failure (N52, N55 Engines)</x:v>
+        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E241" s="9" t="str">
-        <x:v>Replace VANOS solenoids and seals ($250-400 European shops, $729-882 US average). Use high-quality oil (5W-30 or 0W-40 BMW LL-01 spec) and change every 5,000-7,000 miles to prevent future failures - cheap oil or extended intervals kill VANOS solenoids. Some cases may require complete VANOS unit rebuild ($1,500-2,500). PREVENTIVE: Replace VANOS solenoids and seals every 50k miles as maintenance - much cheaper than waiting for failure. On F25 X3 with N52/N55, check TSB SI B12 14 10 for VANOS gear assembly bolt issue.</x:v>
+        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
       </x:c>
       <x:c r="F241" s="9" t="n">
         <x:v>0</x:v>
@@ -9412,21 +10168,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="242" ht="1016.4000244140625" hidden="0" customHeight="1">
+    <x:row r="242" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A242" s="40" t="n">
         <x:v>241</x:v>
       </x:c>
       <x:c r="B242" s="9" t="str">
-        <x:v>bmw-x3-wastegate-rattle-2011</x:v>
+        <x:v>bmw-x4m-s58-bearing-recall-2020</x:v>
       </x:c>
       <x:c r="C242" s="9" t="str">
-        <x:v>2011-2023 | BMW | X3 | M40i, M50, sDrive30i, xDrive28i, xDrive30i, xDrive35i</x:v>
+        <x:v>2020-2021 | BMW | X4 M | M40i, xDrive35i | S58</x:v>
       </x:c>
       <x:c r="D242" s="9" t="str">
-        <x:v>Turbocharger Wastegate Rattle (N55, N20, B58 Engines)</x:v>
+        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E242" s="9" t="str">
-        <x:v>Replace wastegate actuator ($400-800) or use aftermarket wastegate repair kit with upgraded stainless steel bushings ($150-300). Some cases require complete turbocharger replacement ($2,000-$4,000). VTT (Vargas Turbo Technologies) repair kits popular on forums - upgraded materials prevent future rattle. MONITORING: Early wastegate rattle may be harmless (annoying but no performance loss). If car boosts normally and no underboost codes, can monitor rattle without urgent repair. However, if check engine light appears with code 30FF or boost pressure drops, repair immediately to prevent turbo damage.</x:v>
+        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
       </x:c>
       <x:c r="F242" s="9" t="n">
         <x:v>0</x:v>
@@ -9435,21 +10191,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="243" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="243" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A243" s="40" t="n">
         <x:v>242</x:v>
       </x:c>
       <x:c r="B243" s="9" t="str">
-        <x:v>bmw-x3-water-pump-2007</x:v>
+        <x:v>bmw-x4m-transfer-case-2020</x:v>
       </x:c>
       <x:c r="C243" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
+        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
       </x:c>
       <x:c r="D243" s="9" t="str">
-        <x:v>Electric Water Pump Failure (N52, N20 Engines)</x:v>
+        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E243" s="9" t="str">
-        <x:v>Replace electric water pump at first sign of failure ($800 parts + labor). Consider preventative replacement at 70-80k miles to avoid being stranded ($400 parts, DIY-able). CRITICAL: If you own 2013-2017 X3 28i, verify recall repair (protective shield installation) has been completed to prevent fire risk - check with BMW dealer using VIN. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps cylinder heads ($4,000+ repair). Call tow truck.</x:v>
+        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
       </x:c>
       <x:c r="F243" s="9" t="n">
         <x:v>0</x:v>
@@ -9458,21 +10214,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="244" ht="1240.800048828125" hidden="0" customHeight="1">
+    <x:row r="244" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A244" s="40" t="n">
         <x:v>243</x:v>
       </x:c>
       <x:c r="B244" s="9" t="str">
-        <x:v>bmw-x3m-brake-wear-2020</x:v>
+        <x:v>bmw-x5-air-suspension-2007</x:v>
       </x:c>
       <x:c r="C244" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2019-2026 | BMW | X5</x:v>
       </x:c>
       <x:c r="D244" s="9" t="str">
-        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F97 X3 M / F98 X4 M</x:v>
+        <x:v>G05 Suspension Warning: Check Faults and Campaigns Before Parts</x:v>
       </x:c>
       <x:c r="E244" s="9" t="str">
-        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
+        <x:v>Start with the VIN build/options, open-campaign status, exact warning, complete fault memory, and BMW ISTA test plan. If the VIN and production date match a BMW action, follow that bulletin: inspect the specified sensor-link holders, apply the specified software correction, or inspect the affected air line as directed. For other vehicles, test the particular system shown by the VIN and fault path before selecting any component. Do not buy a compressor, strut, spring, or conversion kit until the failed part and its VIN-specific number are established. This article intentionally has no retail link because no single part repairs all of these conditions.</x:v>
       </x:c>
       <x:c r="F244" s="9" t="n">
         <x:v>0</x:v>
@@ -9481,44 +10237,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="245" ht="1188" hidden="0" customHeight="1">
+    <x:row r="245" ht="1148.4000244140625" hidden="0" customHeight="1">
       <x:c r="A245" s="40" t="n">
         <x:v>244</x:v>
       </x:c>
       <x:c r="B245" s="9" t="str">
-        <x:v>bmw-x3m-cooling-track-use-2020</x:v>
+        <x:v>bmw-x5-air-suspension-compressor-2007</x:v>
       </x:c>
       <x:c r="C245" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive35i, xDrive48i, xDrive50i, X5 M | N52, N62, M57, N55, N63, S63</x:v>
       </x:c>
       <x:c r="D245" s="9" t="str">
-        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F97 X3 M / F98 X4 M</x:v>
+        <x:v>E70 Rear Air-Supply Unit: Diagnose the Self-Leveling System First</x:v>
       </x:c>
       <x:c r="E245" s="9" t="str">
-        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
+        <x:v>Read the EHC fault memory and run the applicable BMW ISTA test plan before ordering a compressor. Confirm the vehicle is equipped with rear self-leveling suspension, compare left/right ride height, check system power and wiring, inspect the height-sensor links, and leak-test the air springs, lines, and valve system. Test the air supply only after those checks isolate it. If BMW ETK/AIR selects the E70 air-supply system for the VIN and diagnosis confirms that assembly, replace it with current part 37-20-6-859-714, follow the BMW repair procedure, clear faults, and perform the required ride-height calibration. Do not install a generic compressor or a coil-conversion kit from symptoms alone.</x:v>
       </x:c>
       <x:c r="F245" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G245" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="246" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="246" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A246" s="40" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="B246" s="9" t="str">
-        <x:v>bmw-x3m-differential-bolt-2020</x:v>
+        <x:v>bmw-x5-carbon-buildup-2007</x:v>
       </x:c>
       <x:c r="C246" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2011-2018 | BMW | X5 | xDrive35i, xDrive50i | N55, N63, N63TU1</x:v>
       </x:c>
       <x:c r="D246" s="9" t="str">
-        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F97 X3 M / F98 X4 M</x:v>
+        <x:v>Possible Intake-Valve Deposits on Direct-Injected Gasoline Engines</x:v>
       </x:c>
       <x:c r="E246" s="9" t="str">
-        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
+        <x:v>Diagnose the actual symptom before authorizing cleaning: read BMW-specific faults and misfire counters, check ignition and fueling, smoke-test the intake where indicated, verify crankcase ventilation operation, and inspect the intake valves with a borescope or by removing the intake manifold when the test plan supports it. If substantial deposits are confirmed and match the complaint, use an engine-specific professional mechanical-cleaning procedure that protects closed valves and removes all blasting media before reassembly. Do not present a universal catch can, chemical spray, fuel brand, short oil interval, or high-RPM driving as a proven repair. Any crankcase-ventilation modification also requires engine-specific fitment and emissions-law review.</x:v>
       </x:c>
       <x:c r="F246" s="9" t="n">
         <x:v>0</x:v>
@@ -9527,67 +10283,67 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="247" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="247" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A247" s="40" t="n">
         <x:v>246</x:v>
       </x:c>
       <x:c r="B247" s="9" t="str">
-        <x:v>bmw-x3m-s58-bearing-recall-2020</x:v>
+        <x:v>bmw-x5-coolant-pipe-leak-2007</x:v>
       </x:c>
       <x:c r="C247" s="9" t="str">
-        <x:v>2020-2021 | BMW | X3 M</x:v>
+        <x:v>2007-2010 | BMW | X5 | 4.8i, xDrive48i | N62, N62TU</x:v>
       </x:c>
       <x:c r="D247" s="9" t="str">
-        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F97 X3 M / F98 X4 M</x:v>
+        <x:v>E70 N62 Coolant Transfer Pipe Leak (Pressure-Test First)</x:v>
       </x:c>
       <x:c r="E247" s="9" t="str">
-        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
+        <x:v>Pressure-test the cooling system cold and inspect the engine valley and all accessible connections to identify the exact leak before ordering parts. If inspection confirms the N62 transfer pipe and BMW ETK/AIR selects it for the VIN, replace pipe 11-14-1-439-975 with the required seals and one-time-use hardware from the VIN-specific repair diagram. Refill and bleed the cooling system with the specified coolant, repeat the pressure test, and verify stable temperature. Do not automatically replace an N63 pipe, thermostat, or unrelated hoses from this article.</x:v>
       </x:c>
       <x:c r="F247" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G247" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="248" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="248" ht="1082.4000244140625" hidden="0" customHeight="1">
       <x:c r="A248" s="40" t="n">
         <x:v>247</x:v>
       </x:c>
       <x:c r="B248" s="9" t="str">
-        <x:v>bmw-x3m-transfer-case-2020</x:v>
+        <x:v>bmw-x5-n63-timing-chain-2008</x:v>
       </x:c>
       <x:c r="C248" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2010-2013 | BMW | X5 | xDrive50i | N63</x:v>
       </x:c>
       <x:c r="D248" s="9" t="str">
-        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F97 X3 M / F98 X4 M</x:v>
+        <x:v>Early N63 Timing-Chain Wear Check: ISTA Test Before Repair</x:v>
       </x:c>
       <x:c r="E248" s="9" t="str">
-        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
+        <x:v>Check the VIN and service history with a BMW center, diagnose stored VANOS/camshaft faults first, and run BMW's ISTA timing-chain elongation test. If the result is 'Timing chain is OK,' do not replace parts on this claim. If it is 'not OK,' BMW SIB 11 16 14 directs replacement of both timing chains under the VIN-specific repair instruction, followed by the required oil/filter service, priming steps, programming, and shorter oil-service interval. A single tensioner 11-31-7-557-741 or a generic Cloyes kit is not the complete repair and must not be presented as what the owner needs. Tow the vehicle rather than driving it when severe mechanical noise, oil-pressure warnings, or loss of timing is present.</x:v>
       </x:c>
       <x:c r="F248" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G248" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="249" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="249" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A249" s="40" t="n">
         <x:v>248</x:v>
       </x:c>
       <x:c r="B249" s="9" t="str">
-        <x:v>bmw-x4-n20-timing-chain-2015</x:v>
+        <x:v>bmw-x5-n63-wastegate-2008</x:v>
       </x:c>
       <x:c r="C249" s="9" t="str">
-        <x:v>2015-2016 | BMW | X4 | xDrive28i, xDrive30i</x:v>
+        <x:v>2010-2018 | BMW | X5 | xDrive50i | N63, N63TU</x:v>
       </x:c>
       <x:c r="D249" s="9" t="str">
-        <x:v>N20 Timing Chain Premature Failure - F26 X4 xDrive28i</x:v>
+        <x:v>N63/N63TU Low Boost or Turbo Rattle: Diagnose Vacuum Control First</x:v>
       </x:c>
       <x:c r="E249" s="9" t="str">
-        <x:v>Complete timing chain kit replacement including chain, guides, tensioner, and sprockets. Must be performed by experienced BMW technician. Preventive replacement recommended at 60,000-80,000 miles. BMW extended warranty to 8 years/100,000 miles under class action settlement. Upgraded reinforced chain kit available from aftermarket. Labor is 10-14 hours for X4 due to AWD and tight engine bay.</x:v>
+        <x:v>Read all DME faults and compare requested versus actual boost under the BMW test plan. Pressure- or smoke-test the intake and charge-air path, verify vacuum supply from the pump and reservoir, inspect both banks' hoses and pressure converters, and test actuator movement before condemning a turbocharger. Identify the engine generation, failed bank, and exact hardware in BMW ETK/AIR. Check a 2010-2013 E70 VIN for the N63 Customer Care Package only as applicable; its published six-point scope includes air-mass sensors, injectors, vacuum pump, low-pressure fuel sensor/feed line, fresh-air turbo seals, and crankcase-ventilation lines, not an automatic wastegate replacement. No retail link is published until diagnosis selects a VIN-specific component.</x:v>
       </x:c>
       <x:c r="F249" s="9" t="n">
         <x:v>0</x:v>
@@ -9596,136 +10352,136 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="250" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="250" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A250" s="40" t="n">
         <x:v>249</x:v>
       </x:c>
       <x:c r="B250" s="9" t="str">
-        <x:v>bmw-x4-n20-timing-chain-guide-2015</x:v>
+        <x:v>bmw-x5-oil-leaks-2000</x:v>
       </x:c>
       <x:c r="C250" s="9" t="str">
-        <x:v>2015-2015 | BMW | X4 | N20</x:v>
+        <x:v>2003-2006 | BMW | X5 | 3.0i | M54</x:v>
       </x:c>
       <x:c r="D250" s="9" t="str">
-        <x:v>2015 X4 N20 Lower-Engine Whine Requires Timing-Chain Diagnosis</x:v>
+        <x:v>E53 3.0i M54 Valve-Cover Gasket Leak (Confirm the Source)</x:v>
       </x:c>
       <x:c r="E250" s="9" t="str">
-        <x:v>Confirm the exact xDrive28i variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Clean the engine and trace the highest fresh-oil source before ordering a gasket. If the leak is at the M54 cylinder-head-cover perimeter or spark-plug-well seals, inspect the plastic cover for cracks, warpage, damaged fastener grommets, and crankcase-ventilation faults. Reuse the cover only if it passes inspection, then install VIN/production-confirmed gasket set 11-12-0-030-496 with the BMW-specified grommets and sealant locations and torque sequence. If the cover or another oil circuit is the source, select that separate repair instead.</x:v>
       </x:c>
       <x:c r="F250" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G250" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="251" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="251" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A251" s="40" t="n">
         <x:v>250</x:v>
       </x:c>
       <x:c r="B251" s="9" t="str">
-        <x:v>bmw-x4-oil-leak-2015</x:v>
+        <x:v>bmw-x5-transfer-case-actuator-2000</x:v>
       </x:c>
       <x:c r="C251" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive48i, X5 M | N52, N62, M57, S63</x:v>
       </x:c>
       <x:c r="D251" s="9" t="str">
-        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - All Models</x:v>
+        <x:v>E70 ATC700 Transfer-Case Positioning Motor (Diagnosis Required)</x:v>
       </x:c>
       <x:c r="E251" s="9" t="str">
-        <x:v>Replace valve cover gasket and/or oil filter housing gasket. Valve cover replacement is 3-4 hours labor on X4. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on BMW turbo engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
+        <x:v>Read BMW VTG/DSC faults and run the applicable ISTA transfer-case test plan before buying a motor. Confirm tire sizes and wear, battery voltage, wiring, transfer-case type, fluid condition, calibration, and—especially after differential or transfer-case replacement—the VIN-correct front and rear gear ratios. If testing confirms the ATC700 positioning motor and BMW ETK/AIR selects this application for the VIN, current BMW exchange servomotor 27-10-2-449-709 supersedes 27-10-7-568-267. Install the correct classification resistor/hardware supplied or specified for the VIN and perform the required VTG initialization/calibration. A generic gear-only kit is not a universal BMW repair and should not be ordered without opening and confirming the exact motor failure.</x:v>
       </x:c>
       <x:c r="F251" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G251" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="252" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="252" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A252" s="40" t="n">
         <x:v>251</x:v>
       </x:c>
       <x:c r="B252" s="9" t="str">
-        <x:v>bmw-x4-rear-differential-mount-2015</x:v>
+        <x:v>bmw-x5-transfer-case-actuator-2007</x:v>
       </x:c>
       <x:c r="C252" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2019-2026 | BMW | X5</x:v>
       </x:c>
       <x:c r="D252" s="9" t="str">
-        <x:v>Rear Differential Mount Bushing Failure</x:v>
+        <x:v>G05/F95 Transfer-Case Shudder: Tires and Fluid Diagnosis First</x:v>
       </x:c>
       <x:c r="E252" s="9" t="str">
-        <x:v>Replace rear differential mount bushings. Both front and rear differential bushings should be inspected and replaced as a set. Upgraded aftermarket bushings with stiffer rubber or polyurethane are available for longer service life.</x:v>
+        <x:v>Follow BMW SIB 27 02 20 in order: verify all four tires for VIN-correct size, brand/application, axle placement, and wear; diagnose any powertrain faults; then use ISTA to temporarily deactivate the transfer-case clutch and road-test the complaint. Only if the shudder disappears with the VTG deactivated does BMW direct an ATX13-X oil change with DTF-1, followed by VTG calibration. The clutch plates can require up to 125 miles after the service to become fully saturated and smooth out. If the symptom remains, continue diagnosis rather than buying an actuator or transfer case. Part numbers for any further repair must be selected by VIN in ETK/AIR.</x:v>
       </x:c>
       <x:c r="F252" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G252" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="253" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A253" s="40" t="n">
         <x:v>252</x:v>
       </x:c>
       <x:c r="B253" s="9" t="str">
-        <x:v>bmw-x4-transfer-case-2015</x:v>
+        <x:v>bmw-x5-vanos-solenoid-2000</x:v>
       </x:c>
       <x:c r="C253" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2010-2013 | BMW | X5 | xDrive30i, xDrive35i | N51, N52K, N52T, N55</x:v>
       </x:c>
       <x:c r="D253" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure - All xDrive X4</x:v>
+        <x:v>VANOS Adjustment-Unit Bolt Recall 23V-707 (E70 Inline-Six)</x:v>
       </x:c>
       <x:c r="E253" s="9" t="str">
-        <x:v>Diagnose specific failure. Transfer case actuator motor replacement ($800-1,200) is most common. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors. Common wear item on high-mileage xDrive BMW models.</x:v>
+        <x:v>Enter the VIN in BMW's official recall lookup and have an authorized BMW center complete recall 23V-707 if it is open. BMW's procedure is inspection-dependent: intact affected bolts are replaced; if bolts are loose or broken, the affected VANOS adjustment unit is replaced, and missing fragments must be recovered. The recall repair is free, so do not buy a solenoid or VANOS part first. If the VIN is outside the recall or a fault remains after the remedy, use BMW-capable diagnostics to test oil supply and pressure, wiring, sensors, control solenoids, adjustment units, and mechanical timing before selecting a part. If the engine runs roughly, makes unusual mechanical noise, loses power, or stalls, move out of traffic safely, stop driving, and contact BMW for transport guidance.</x:v>
       </x:c>
       <x:c r="F253" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G253" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="254" ht="1240.800048828125" hidden="0" customHeight="1">
+    <x:row r="254" ht="1148.4000244140625" hidden="0" customHeight="1">
       <x:c r="A254" s="40" t="n">
         <x:v>253</x:v>
       </x:c>
       <x:c r="B254" s="9" t="str">
-        <x:v>bmw-x4m-brake-wear-2020</x:v>
+        <x:v>bmw-x5-water-pump-2007</x:v>
       </x:c>
       <x:c r="C254" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
+        <x:v>2011-2013 | BMW | X5 | xDrive35i | N55</x:v>
       </x:c>
       <x:c r="D254" s="9" t="str">
-        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F98 X4 M / F98 X4 M</x:v>
+        <x:v>E70 xDrive35i N55 Electric Coolant Pump (Fault-Confirmed)</x:v>
       </x:c>
       <x:c r="E254" s="9" t="str">
-        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
+        <x:v>If the engine-temperature warning appears, stop safely, shut the engine off, and tow the vehicle if normal temperature cannot be confirmed. When cool, check coolant level and leaks, read BMW-specific faults, verify pump power/ground and communication, and run the ISTA coolant-pump activation/test plan. If those tests confirm the pump and BMW ETK/AIR selects 11-51-5-A05-704 for the VIN, replace it using the BMW procedure, select the thermostat separately only if testing or preventive planning justifies it, vacuum-fill or bleed the system as specified, and verify commanded pump operation and stable temperature. Do not use a fixed-mileage rule or this part number for an N52, N63, or F15 without VIN confirmation.</x:v>
       </x:c>
       <x:c r="F254" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G254" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" ht="1188" hidden="0" customHeight="1">
+    <x:row r="255" ht="1056" hidden="0" customHeight="1">
       <x:c r="A255" s="40" t="n">
         <x:v>254</x:v>
       </x:c>
       <x:c r="B255" s="9" t="str">
-        <x:v>bmw-x4m-cooling-track-use-2020</x:v>
+        <x:v>bmw-x5m-brake-system-2010</x:v>
       </x:c>
       <x:c r="C255" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M</x:v>
+        <x:v>2010-2023 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D255" s="9" t="str">
-        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F98 X4 M / F98 X4 M</x:v>
+        <x:v>Heavy-Duty Brake System Accelerated Wear - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E255" s="9" t="str">
-        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
+        <x:v>E70 X5 M brakes: OEM front pads 34116799964 ($150-$250), rear pads 34216794879 ($120-$200). F85 X5 M front brake rotors: 34112284101/34112284102 with 6-pot caliper 34117845747/34117845748 and pads 34112284869. F85 rear: 385mm x 24mm perforated rotors 34212284903/34212284904 with 4-pot Brembo caliper and Textar pads. Budget $1,500-$2,500 per axle for complete brake service. For track use: EBC Yellowstuff or Hawk HPS 5.0 pads ($200-$350 per axle) with StopTech slotted rotors for improved heat management. Use Motul RBF 660 or ATE Typ 200 brake fluid - flush every 12 months. Budget $3,000-$5,000 per year for brake maintenance if driving spiritedly.</x:v>
       </x:c>
       <x:c r="F255" s="9" t="n">
         <x:v>0</x:v>
@@ -9734,21 +10490,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="256" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="256" ht="1122" hidden="0" customHeight="1">
       <x:c r="A256" s="40" t="n">
         <x:v>255</x:v>
       </x:c>
       <x:c r="B256" s="9" t="str">
-        <x:v>bmw-x4m-differential-bolt-2020</x:v>
+        <x:v>bmw-x5m-rear-differential-2010</x:v>
       </x:c>
       <x:c r="C256" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M</x:v>
+        <x:v>2010-2023 | BMW | X5 M | S63</x:v>
       </x:c>
       <x:c r="D256" s="9" t="str">
-        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F98 X4 M / F98 X4 M</x:v>
+        <x:v>Rear Differential Wear &amp; Fluid Degradation - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E256" s="9" t="str">
-        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
+        <x:v>Change rear differential fluid every 30,000 miles (ignore BMW "lifetime fill" claim). E70 X5 M: No drain plug - fluid must be extracted through fill port with hand pump or suction device. Recommended fluid: Royal Purple 75W-140 GL5 synthetic or Red Line 75W-140 GL5 ($40-$60 per fill). Capacity approximately 1.2 liters. For limited-slip diff, ensure fluid is GL5 rated with limited-slip additive. If differential is making whining/howling noise: have a limited-slip differential specialist inspect internals (not generic BMW shop). Diff rebuild: $1,500-$3,000 at specialist. Complete differential replacement: $3,000-$5,500 + labor. Labor for fluid change: $150-$300 at independent shop.</x:v>
       </x:c>
       <x:c r="F256" s="9" t="n">
         <x:v>0</x:v>
@@ -9757,21 +10513,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="257" ht="1386" hidden="0" customHeight="1">
       <x:c r="A257" s="40" t="n">
         <x:v>256</x:v>
       </x:c>
       <x:c r="B257" s="9" t="str">
-        <x:v>bmw-x4m-s58-bearing-recall-2020</x:v>
+        <x:v>bmw-x5m-s63-cooling-system-2010</x:v>
       </x:c>
       <x:c r="C257" s="9" t="str">
-        <x:v>2020-2021 | BMW | X4 M | M40i, xDrive35i | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D257" s="9" t="str">
-        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F98 X4 M / F98 X4 M</x:v>
+        <x:v>S63 Cooling System Component Failures - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E257" s="9" t="str">
-        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
+        <x:v>PROACTIVE MAINTENANCE SCHEDULE: Replace electric water pump at 60,000 miles ($400-$700 + labor). Replace thermostat at same time ($150-$250). Replace expansion tank at 60,000-80,000 miles ($100-$200). Inspect all coolant hoses at every oil change - replace any that are soft, bulging, or showing surface cracks. E70 X5 M expansion tank vent hose: 17128627119 ($30-$50). Flush coolant system every 2 years or 30,000 miles (more frequent than BMW's 4-year recommendation). Use ONLY BMW coolant mixed 50/50 with distilled water. For E70 hot-V turbo coolant lines: GRYPHONTEK repair kit eliminates plastic T-fitting failure (see separate issue entry). Budget $1,500-$2,500 for complete cooling system refresh at 60,000 miles. This prevents catastrophic overheating that can destroy the S63 engine ($15,000-$34,000 engine replacement).</x:v>
       </x:c>
       <x:c r="F257" s="9" t="n">
         <x:v>0</x:v>
@@ -9780,21 +10536,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="258" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="258" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A258" s="40" t="n">
         <x:v>257</x:v>
       </x:c>
       <x:c r="B258" s="9" t="str">
-        <x:v>bmw-x4m-transfer-case-2020</x:v>
+        <x:v>bmw-x5m-s63-oil-leaks-2010</x:v>
       </x:c>
       <x:c r="C258" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D258" s="9" t="str">
-        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F98 X4 M / F98 X4 M</x:v>
+        <x:v>S63 V8 Chronic Oil Leaks (Valve Cover, Oil Pan, Turbo Lines) - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E258" s="9" t="str">
-        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
+        <x:v>Valve cover gasket replacement (both sides): $1,200-$2,500 with labor. BMW plastic valve covers can crack and must be replaced entirely (not just gasket) - inspect during service. Oil filter housing gasket: $400-$800 with labor. Oil pan gasket: $2,000-$3,500 (requires engine/subframe drop). Turbo oil feed/return lines: replace with GRYPHONTEK or MAMBA upgraded silicone/braided lines during any turbo service ($200-$400). VANOS solenoid seals: $100-$200 (DIY-friendly). For comprehensive oil leak repair at 80,000+ miles: budget $3,000-$5,000 to address all common leak points simultaneously. Valve cover bolt torque is CRITICAL - too tight cracks the cover ($800-$1,200 per cover), too loose and it leaks.</x:v>
       </x:c>
       <x:c r="F258" s="9" t="n">
         <x:v>0</x:v>
@@ -9803,21 +10559,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="259" ht="1412.4000244140625" hidden="0" customHeight="1">
       <x:c r="A259" s="40" t="n">
         <x:v>258</x:v>
       </x:c>
       <x:c r="B259" s="9" t="str">
-        <x:v>bmw-x5-air-suspension-2007</x:v>
+        <x:v>bmw-x5m-s63-rod-bearing-2010</x:v>
       </x:c>
       <x:c r="C259" s="9" t="str">
-        <x:v>2019-2026 | BMW | X5</x:v>
+        <x:v>2010-2018 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i</x:v>
       </x:c>
       <x:c r="D259" s="9" t="str">
-        <x:v>G05 Suspension Warning: Check Faults and Campaigns Before Parts</x:v>
+        <x:v>S63 V8 Rod Bearing Premature Wear &amp; Failure - E70/F85 X5 M</x:v>
       </x:c>
       <x:c r="E259" s="9" t="str">
-        <x:v>Start with the VIN build/options, open-campaign status, exact warning, complete fault memory, and BMW ISTA test plan. If the VIN and production date match a BMW action, follow that bulletin: inspect the specified sensor-link holders, apply the specified software correction, or inspect the affected air line as directed. For other vehicles, test the particular system shown by the VIN and fault path before selecting any component. Do not buy a compressor, strut, spring, or conversion kit until the failed part and its VIN-specific number are established. This article intentionally has no retail link because no single part repairs all of these conditions.</x:v>
+        <x:v>PREVENTIVE: For track-driven X5 M, replace rod bearings proactively at 60,000-80,000 miles. ACL Race Series rod bearings (8B1578HX-STD for S63B44, +0.001" extra oil clearance) are the community gold standard ($200-$350 for bearing set). WPC surface-treated bearings from Lang Racing are the premium choice ($400-$600 set). Total cost for preventive rod bearing service: $4,500-$8,500 depending on shop. Oil analysis every 5,000 miles through Blackstone Labs ($30/test) to monitor bearing wear metals (lead and copper). Use only BMW 10W-60 synthetic oil with 5,000-7,500 mile oil change intervals. Never track the car on cold oil. Mporium BMW offers specialized S63 rod bearing service starting at $4,499. If catastrophic failure: rebuilt S63 engine from RK Autowerks (~$8,500 + installation), new BMW engine (~$34,000), or complete engine rebuild ($12,000-$18,000).</x:v>
       </x:c>
       <x:c r="F259" s="9" t="n">
         <x:v>0</x:v>
@@ -9826,44 +10582,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="260" ht="1148.4000244140625" hidden="0" customHeight="1">
+    <x:row r="260" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A260" s="40" t="n">
         <x:v>259</x:v>
       </x:c>
       <x:c r="B260" s="9" t="str">
-        <x:v>bmw-x5-air-suspension-compressor-2007</x:v>
+        <x:v>bmw-x5m-s63-turbo-coolant-line-2010</x:v>
       </x:c>
       <x:c r="C260" s="9" t="str">
-        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive35i, xDrive48i, xDrive50i, X5 M | N52, N62, M57, N55, N63, S63</x:v>
+        <x:v>2010-2013 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D260" s="9" t="str">
-        <x:v>E70 Rear Air-Supply Unit: Diagnose the Self-Leveling System First</x:v>
+        <x:v>S63 Turbo Coolant Line Plastic T-Fitting Failure (Hot-V Design) - E70 X5 M</x:v>
       </x:c>
       <x:c r="E260" s="9" t="str">
-        <x:v>Read the EHC fault memory and run the applicable BMW ISTA test plan before ordering a compressor. Confirm the vehicle is equipped with rear self-leveling suspension, compare left/right ride height, check system power and wiring, inspect the height-sensor links, and leak-test the air springs, lines, and valve system. Test the air supply only after those checks isolate it. If BMW ETK/AIR selects the E70 air-supply system for the VIN and diagnosis confirms that assembly, replace it with current part 37-20-6-859-714, follow the BMW repair procedure, clear faults, and perform the required ride-height calibration. Do not install a generic compressor or a coil-conversion kit from symptoms alone.</x:v>
+        <x:v>Replace ALL factory plastic turbo coolant T-fittings and hoses with GRYPHONTEK S63 Turbo Coolant Line Repair Kit ($200-$400). Kit includes pre-shaped multi-layer reinforced silicone hoses, brass T-fittings (replacing factory plastic), and all necessary hose clamps. Direct bolt-on installation designed for the E70/E71 S63 engine bay. MAMBA Turbo also offers a reinforced turbo coolant line kit with brass and silicone components ($150-$350). This is a PROACTIVE replacement - do not wait for failure. Replace at first sign of coolant weeping or during any turbo service. Labor: $800-$1,500 due to tight access in hot-V engine valley. If turbo bearings are damaged from overheating: turbo replacement $3,000-$5,000 per unit.</x:v>
       </x:c>
       <x:c r="F260" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G260" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="261" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="261" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A261" s="40" t="n">
         <x:v>260</x:v>
       </x:c>
       <x:c r="B261" s="9" t="str">
-        <x:v>bmw-x5-carbon-buildup-2007</x:v>
+        <x:v>bmw-x5m-s63-vanos-solenoid-2010</x:v>
       </x:c>
       <x:c r="C261" s="9" t="str">
-        <x:v>2011-2018 | BMW | X5 | xDrive35i, xDrive50i | N55, N63, N63TU1</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D261" s="9" t="str">
-        <x:v>Possible Intake-Valve Deposits on Direct-Injected Gasoline Engines</x:v>
+        <x:v>S63 VANOS Solenoid Failure - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E261" s="9" t="str">
-        <x:v>Diagnose the actual symptom before authorizing cleaning: read BMW-specific faults and misfire counters, check ignition and fueling, smoke-test the intake where indicated, verify crankcase ventilation operation, and inspect the intake valves with a borescope or by removing the intake manifold when the test plan supports it. If substantial deposits are confirmed and match the complaint, use an engine-specific professional mechanical-cleaning procedure that protects closed valves and removes all blasting media before reassembly. Do not present a universal catch can, chemical spray, fuel brand, short oil interval, or high-RPM driving as a proven repair. Any crankcase-ventilation modification also requires engine-specific fitment and emissions-law review.</x:v>
+        <x:v>Replace all 4 VANOS solenoids simultaneously - they are same age and if one has failed, others are close behind. Pierburg 11368605123 (OEM supplier) at $30-$50 each from Turner Motorsport or BimmerWorld. Genuine BMW 11368482268 for S63TU applications at $50-$70 each. Total parts cost: $120-$280 for all 4 solenoids. Also replace VANOS solenoid O-rings and filter screens during service. Labor: 1-2 hours professional ($150-$400 labor). This is one of the easier S63 repairs - accessible from top of engine without removing intake manifold. Natafox and Febi also offer quality aftermarket VANOS solenoids at lower cost ($20-$35 each). Clean VANOS system with fresh oil change immediately after solenoid replacement.</x:v>
       </x:c>
       <x:c r="F261" s="9" t="n">
         <x:v>0</x:v>
@@ -9872,67 +10628,67 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="262" ht="884.4000244140625" hidden="0" customHeight="1">
+    <x:row r="262" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A262" s="40" t="n">
         <x:v>261</x:v>
       </x:c>
       <x:c r="B262" s="9" t="str">
-        <x:v>bmw-x5-coolant-pipe-leak-2007</x:v>
+        <x:v>bmw-x5m-s63-wastegate-rattle-2010</x:v>
       </x:c>
       <x:c r="C262" s="9" t="str">
-        <x:v>2007-2010 | BMW | X5 | 4.8i, xDrive48i | N62, N62TU</x:v>
+        <x:v>2010-2018 | BMW | X5 M | S63</x:v>
       </x:c>
       <x:c r="D262" s="9" t="str">
-        <x:v>E70 N62 Coolant Transfer Pipe Leak (Pressure-Test First)</x:v>
+        <x:v>S63 Twin Turbo Wastegate Rattle - E70/F85 X5 M</x:v>
       </x:c>
       <x:c r="E262" s="9" t="str">
-        <x:v>Pressure-test the cooling system cold and inspect the engine valley and all accessible connections to identify the exact leak before ordering parts. If inspection confirms the N62 transfer pipe and BMW ETK/AIR selects it for the VIN, replace pipe 11-14-1-439-975 with the required seals and one-time-use hardware from the VIN-specific repair diagram. Refill and bleed the cooling system with the specified coolant, repeat the pressure test, and verify stable temperature. Do not automatically replace an N63 pipe, thermostat, or unrelated hoses from this article.</x:v>
+        <x:v>Option 1 (Most cost-effective): MAMBA SUS316 stainless steel wastegate rattle flapper repair kit for S63 MGT2260 (part 077-0024, replaces 790463-2 / 790484-3), approximately $150-$300 per turbo. Requires turbo removal for installation. Option 2: Lskioer turbo wastegate rattle flapper repair kit for S63/S63TU MGT2260DSL ($80-$150 per kit on Amazon). Option 3: Replace turbo wastegate actuators with new OEM units ($300-$500 each). Option 4: Full turbocharger replacement with new or remanufactured units ($3,000-$5,000 per turbo + labor). Labor for turbo removal and reinstallation: $2,000-$3,500 for both turbos. While turbos are out: replace turbo oil feed/return lines, coolant lines, and all gaskets (GRYPHONTEK turbo coolant line repair kit for E70 X5M, ~$200-$400).</x:v>
       </x:c>
       <x:c r="F262" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G262" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="263" ht="1082.4000244140625" hidden="0" customHeight="1">
+    <x:row r="263" ht="1069.199951171875" hidden="0" customHeight="1">
       <x:c r="A263" s="40" t="n">
         <x:v>262</x:v>
       </x:c>
       <x:c r="B263" s="9" t="str">
-        <x:v>bmw-x5-n63-timing-chain-2008</x:v>
+        <x:v>bmw-x5m-transfer-case-actuator-2010</x:v>
       </x:c>
       <x:c r="C263" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 | xDrive50i | N63</x:v>
+        <x:v>2010-2023 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D263" s="9" t="str">
-        <x:v>Early N63 Timing-Chain Wear Check: ISTA Test Before Repair</x:v>
+        <x:v>xDrive Transfer Case Actuator Motor Failure - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E263" s="9" t="str">
-        <x:v>Check the VIN and service history with a BMW center, diagnose stored VANOS/camshaft faults first, and run BMW's ISTA timing-chain elongation test. If the result is 'Timing chain is OK,' do not replace parts on this claim. If it is 'not OK,' BMW SIB 11 16 14 directs replacement of both timing chains under the VIN-specific repair instruction, followed by the required oil/filter service, priming steps, programming, and shorter oil-service interval. A single tensioner 11-31-7-557-741 or a generic Cloyes kit is not the complete repair and must not be presented as what the owner needs. Tow the vehicle rather than driving it when severe mechanical noise, oil-pressure warnings, or loss of timing is present.</x:v>
+        <x:v>Replace transfer case actuator motor. E70 X5 M: BMW 27107566296 or equivalent ($250-$450 for actuator motor). F85 X5 M: BMW 27608643153 or equivalent ($300-$500). F95 X5 M: check VIN-specific part number with dealer. FCP Euro has an excellent DIY guide for BMW transfer case actuator repair - the actuator can be replaced without removing the entire transfer case. Labor: 2-3 hours at specialist shop ($300-$600 labor). Change transfer case fluid at same time with BMW DTF-1 specification fluid. XeMODeX offers remanufactured transfer case actuator motors at reduced cost ($200-$350). For complete transfer case failure: $3,500-$6,000 for replacement unit + labor.</x:v>
       </x:c>
       <x:c r="F263" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G263" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="264" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="264" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A264" s="40" t="n">
         <x:v>263</x:v>
       </x:c>
       <x:c r="B264" s="9" t="str">
-        <x:v>bmw-x5-n63-wastegate-2008</x:v>
+        <x:v>bmw-x6-adaptive-drive-malfunction-2008</x:v>
       </x:c>
       <x:c r="C264" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 | xDrive50i | N63, N63TU</x:v>
+        <x:v>2008-2019 | BMW | X6</x:v>
       </x:c>
       <x:c r="D264" s="9" t="str">
-        <x:v>N63/N63TU Low Boost or Turbo Rattle: Diagnose Vacuum Control First</x:v>
+        <x:v>Adaptive Drive System Malfunction</x:v>
       </x:c>
       <x:c r="E264" s="9" t="str">
-        <x:v>Read all DME faults and compare requested versus actual boost under the BMW test plan. Pressure- or smoke-test the intake and charge-air path, verify vacuum supply from the pump and reservoir, inspect both banks' hoses and pressure converters, and test actuator movement before condemning a turbocharger. Identify the engine generation, failed bank, and exact hardware in BMW ETK/AIR. Check a 2010-2013 E70 VIN for the N63 Customer Care Package only as applicable; its published six-point scope includes air-mass sensors, injectors, vacuum pump, low-pressure fuel sensor/feed line, fresh-air turbo seals, and crankcase-ventilation lines, not an automatic wastegate replacement. No retail link is published until diagnosis selects a VIN-specific component.</x:v>
+        <x:v>Diagnose specific Adaptive Drive component failure using BMW ISTA diagnostics. Replace the failed component — most commonly the hydraulic pump or valve block. If repair cost is prohibitive, some owners convert to conventional anti-roll bars as a permanent fix at lower cost.</x:v>
       </x:c>
       <x:c r="F264" s="9" t="n">
         <x:v>0</x:v>
@@ -9941,136 +10697,136 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="265" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="265" ht="858" hidden="0" customHeight="1">
       <x:c r="A265" s="40" t="n">
         <x:v>264</x:v>
       </x:c>
       <x:c r="B265" s="9" t="str">
-        <x:v>bmw-x5-oil-leaks-2000</x:v>
+        <x:v>bmw-x6-air-suspension-2008</x:v>
       </x:c>
       <x:c r="C265" s="9" t="str">
-        <x:v>2003-2006 | BMW | X5 | 3.0i | M54</x:v>
+        <x:v>2008-2023 | BMW | X6</x:v>
       </x:c>
       <x:c r="D265" s="9" t="str">
-        <x:v>E53 3.0i M54 Valve-Cover Gasket Leak (Confirm the Source)</x:v>
+        <x:v>Air Suspension Compressor &amp; Strut Failure</x:v>
       </x:c>
       <x:c r="E265" s="9" t="str">
-        <x:v>Clean the engine and trace the highest fresh-oil source before ordering a gasket. If the leak is at the M54 cylinder-head-cover perimeter or spark-plug-well seals, inspect the plastic cover for cracks, warpage, damaged fastener grommets, and crankcase-ventilation faults. Reuse the cover only if it passes inspection, then install VIN/production-confirmed gasket set 11-12-0-030-496 with the BMW-specified grommets and sealant locations and torque sequence. If the cover or another oil circuit is the source, select that separate repair instead.</x:v>
+        <x:v>Replace failed air springs or compressor. Arnott rear air spring A-2642 ($200-300 each). OEM F16 spring 37126795013 ($200). Arnott compressor P-2655 ($599). Or convert to coil springs: Strutmasters BB2RBM conversion kit ($1,200-1,800) permanently eliminates air suspension issues. Conversion is cheaper long-term than continued air suspension repairs. If keeping air suspension: inspect air springs at 60,000-80,000 miles for cracks/leaks before compressor damage occurs. Replace both air springs on same axle simultaneously.</x:v>
       </x:c>
       <x:c r="F265" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G265" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="266" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="266" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A266" s="40" t="n">
         <x:v>265</x:v>
       </x:c>
       <x:c r="B266" s="9" t="str">
-        <x:v>bmw-x5-transfer-case-actuator-2000</x:v>
+        <x:v>bmw-x6-ibs-brake-recall-2023</x:v>
       </x:c>
       <x:c r="C266" s="9" t="str">
-        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive48i, X5 M | N52, N62, M57, S63</x:v>
+        <x:v>2024-2024 | BMW | X6</x:v>
       </x:c>
       <x:c r="D266" s="9" t="str">
-        <x:v>E70 ATC700 Transfer-Case Positioning Motor (Diagnosis Required)</x:v>
+        <x:v>2024 X6 Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E266" s="9" t="str">
-        <x:v>Read BMW VTG/DSC faults and run the applicable ISTA transfer-case test plan before buying a motor. Confirm tire sizes and wear, battery voltage, wiring, transfer-case type, fluid condition, calibration, and—especially after differential or transfer-case replacement—the VIN-correct front and rear gear ratios. If testing confirms the ATC700 positioning motor and BMW ETK/AIR selects this application for the VIN, current BMW exchange servomotor 27-10-2-449-709 supersedes 27-10-7-568-267. Install the correct classification resistor/hardware supplied or specified for the VIN and perform the required VTG initialization/calibration. A generic gear-only kit is not a universal BMW repair and should not be ordered without opening and confirming the exact motor failure.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
       </x:c>
       <x:c r="F266" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G266" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="267" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="267" ht="924" hidden="0" customHeight="1">
       <x:c r="A267" s="40" t="n">
         <x:v>266</x:v>
       </x:c>
       <x:c r="B267" s="9" t="str">
-        <x:v>bmw-x5-transfer-case-actuator-2007</x:v>
+        <x:v>bmw-x6-n63-timing-chain-2008</x:v>
       </x:c>
       <x:c r="C267" s="9" t="str">
-        <x:v>2019-2026 | BMW | X5</x:v>
+        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
       </x:c>
       <x:c r="D267" s="9" t="str">
-        <x:v>G05/F95 Transfer-Case Shudder: Tires and Fluid Diagnosis First</x:v>
+        <x:v>N63 Timing Chain Stretch &amp; Guide Failure (E71/F16 xDrive50i)</x:v>
       </x:c>
       <x:c r="E267" s="9" t="str">
-        <x:v>Follow BMW SIB 27 02 20 in order: verify all four tires for VIN-correct size, brand/application, axle placement, and wear; diagnose any powertrain faults; then use ISTA to temporarily deactivate the transfer-case clutch and road-test the complaint. Only if the shudder disappears with the VTG deactivated does BMW direct an ATX13-X oil change with DTF-1, followed by VTG calibration. The clutch plates can require up to 125 miles after the service to become fully saturated and smooth out. If the symptom remains, continue diagnosis rather than buying an actuator or transfer case. Part numbers for any further repair must be selected by VIN in ETK/AIR.</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: If you own 2008-2014 E71 xDrive50i with N63, replace timing chain guides and tensioners IMMEDIATELY at 60,000-80,000 miles ($4,000-6,000) BEFORE failure. IWIS timing chain kit 90001521 ($800-1,200) or Turner kit 11317594899KT recommended. Replace lower chain guide 11147574373 at same time. If chain has already failed: complete engine replacement required ($15,000-25,000). Check VIN with BMW dealer for extended warranty eligibility. 2015+ N63TU engines have improved timing components but still require monitoring.</x:v>
       </x:c>
       <x:c r="F267" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G267" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="268" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="268" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A268" s="40" t="n">
         <x:v>267</x:v>
       </x:c>
       <x:c r="B268" s="9" t="str">
-        <x:v>bmw-x5-vanos-solenoid-2000</x:v>
+        <x:v>bmw-x6-n63-valve-stem-seal-wear-2008</x:v>
       </x:c>
       <x:c r="C268" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 | xDrive30i, xDrive35i | N51, N52K, N52T, N55</x:v>
+        <x:v>2008-2019 | BMW | X6 | N63</x:v>
       </x:c>
       <x:c r="D268" s="9" t="str">
-        <x:v>VANOS Adjustment-Unit Bolt Recall 23V-707 (E70 Inline-Six)</x:v>
+        <x:v>N63 Valve Stem Seal Degradation and Oil Burning</x:v>
       </x:c>
       <x:c r="E268" s="9" t="str">
-        <x:v>Enter the VIN in BMW's official recall lookup and have an authorized BMW center complete recall 23V-707 if it is open. BMW's procedure is inspection-dependent: intact affected bolts are replaced; if bolts are loose or broken, the affected VANOS adjustment unit is replaced, and missing fragments must be recovered. The recall repair is free, so do not buy a solenoid or VANOS part first. If the VIN is outside the recall or a fault remains after the remedy, use BMW-capable diagnostics to test oil supply and pressure, wiring, sensors, control solenoids, adjustment units, and mechanical timing before selecting a part. If the engine runs roughly, makes unusual mechanical noise, loses power, or stalls, move out of traffic safely, stop driving, and contact BMW for transport guidance.</x:v>
+        <x:v>Replace all intake and exhaust valve stem seals. This is a major job requiring head work. Also replace turbo oil return lines and update engine software per BMW N63 Customer Care Package specifications. Ensure proper oil grade (BMW LL-01) is used.</x:v>
       </x:c>
       <x:c r="F268" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="269" ht="1148.4000244140625" hidden="0" customHeight="1">
+    <x:row r="269" ht="858" hidden="0" customHeight="1">
       <x:c r="A269" s="40" t="n">
         <x:v>268</x:v>
       </x:c>
       <x:c r="B269" s="9" t="str">
-        <x:v>bmw-x5-water-pump-2007</x:v>
+        <x:v>bmw-x6-n63-valve-stem-seals-2008</x:v>
       </x:c>
       <x:c r="C269" s="9" t="str">
-        <x:v>2011-2013 | BMW | X5 | xDrive35i | N55</x:v>
+        <x:v>2008-2023 | BMW | X6 | M50i, xDrive50i | N63</x:v>
       </x:c>
       <x:c r="D269" s="9" t="str">
-        <x:v>E70 xDrive35i N55 Electric Coolant Pump (Fault-Confirmed)</x:v>
+        <x:v>N63 Valve Stem Seal / Oil Consumption (xDrive50i)</x:v>
       </x:c>
       <x:c r="E269" s="9" t="str">
-        <x:v>If the engine-temperature warning appears, stop safely, shut the engine off, and tow the vehicle if normal temperature cannot be confirmed. When cool, check coolant level and leaks, read BMW-specific faults, verify pump power/ground and communication, and run the ISTA coolant-pump activation/test plan. If those tests confirm the pump and BMW ETK/AIR selects 11-51-5-A05-704 for the VIN, replace it using the BMW procedure, select the thermostat separately only if testing or preventive planning justifies it, vacuum-fill or bleed the system as specified, and verify commanded pump operation and stable temperature. Do not use a fixed-mileage rule or this part number for an N52, N63, or F15 without VIN confirmation.</x:v>
+        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 ($80-120/set of 16, need 2 sets for V8). 5150 AutoSport Viton upgraded seals ($150-200) are recommended for better heat resistance in hot-vee configuration. AGA Tools kit AGA-N63-VSK-K ($500-800) includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Some owners monitor oil levels and add as needed rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil.</x:v>
       </x:c>
       <x:c r="F269" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G269" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="270" ht="1056" hidden="0" customHeight="1">
+    <x:row r="270" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A270" s="40" t="n">
         <x:v>269</x:v>
       </x:c>
       <x:c r="B270" s="9" t="str">
-        <x:v>bmw-x5m-brake-system-2010</x:v>
+        <x:v>bmw-x6-n63-wastegate-2008</x:v>
       </x:c>
       <x:c r="C270" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M</x:v>
+        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
       </x:c>
       <x:c r="D270" s="9" t="str">
-        <x:v>Heavy-Duty Brake System Accelerated Wear - E70/F85/F95 X5 M</x:v>
+        <x:v>N63 Turbo Wastegate Rattle (xDrive50i)</x:v>
       </x:c>
       <x:c r="E270" s="9" t="str">
-        <x:v>E70 X5 M brakes: OEM front pads 34116799964 ($150-$250), rear pads 34216794879 ($120-$200). F85 X5 M front brake rotors: 34112284101/34112284102 with 6-pot caliper 34117845747/34117845748 and pads 34112284869. F85 rear: 385mm x 24mm perforated rotors 34212284903/34212284904 with 4-pot Brembo caliper and Textar pads. Budget $1,500-$2,500 per axle for complete brake service. For track use: EBC Yellowstuff or Hawk HPS 5.0 pads ($200-$350 per axle) with StopTech slotted rotors for improved heat management. Use Motul RBF 660 or ATE Typ 200 brake fluid - flush every 12 months. Budget $3,000-$5,000 per year for brake maintenance if driving spiritedly.</x:v>
+        <x:v>Repair options range from flapper repair kits ($50-100/turbo) to complete turbocharger replacement ($4,000-8,000 for both). Garrett MGT2256S flapper repair kit ($50-100 per turbo) is cheapest fix. MAMBA adjustable actuator kit ($150-300) provides more durable solution. OEM actuators 11657646093 available from BMW. Complete turbo replacement $2,000-4,000 per turbo. MONITORING: Wastegate rattle is early warning - address before complete turbo failure to avoid $8,000+ repair.</x:v>
       </x:c>
       <x:c r="F270" s="9" t="n">
         <x:v>0</x:v>
@@ -10079,21 +10835,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="271" ht="1122" hidden="0" customHeight="1">
+    <x:row r="271" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A271" s="40" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="B271" s="9" t="str">
-        <x:v>bmw-x5m-rear-differential-2010</x:v>
+        <x:v>bmw-x6-rear-differential-bushing-2008</x:v>
       </x:c>
       <x:c r="C271" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | S63</x:v>
+        <x:v>2008-2026 | BMW | X6</x:v>
       </x:c>
       <x:c r="D271" s="9" t="str">
-        <x:v>Rear Differential Wear &amp; Fluid Degradation - E70/F85/F95 X5 M</x:v>
+        <x:v>Rear Differential Bushing Deterioration</x:v>
       </x:c>
       <x:c r="E271" s="9" t="str">
-        <x:v>Change rear differential fluid every 30,000 miles (ignore BMW "lifetime fill" claim). E70 X5 M: No drain plug - fluid must be extracted through fill port with hand pump or suction device. Recommended fluid: Royal Purple 75W-140 GL5 synthetic or Red Line 75W-140 GL5 ($40-$60 per fill). Capacity approximately 1.2 liters. For limited-slip diff, ensure fluid is GL5 rated with limited-slip additive. If differential is making whining/howling noise: have a limited-slip differential specialist inspect internals (not generic BMW shop). Diff rebuild: $1,500-$3,000 at specialist. Complete differential replacement: $3,000-$5,500 + labor. Labor for fluid change: $150-$300 at independent shop.</x:v>
+        <x:v>Replace all rear differential mount bushings. Use OEM or equivalent quality bushings (Lemforder is the OEM supplier). Inspect the differential housing for any damage from excessive movement. Perform subframe alignment check after bushing replacement.</x:v>
       </x:c>
       <x:c r="F271" s="9" t="n">
         <x:v>0</x:v>
@@ -10102,21 +10858,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="272" ht="1386" hidden="0" customHeight="1">
+    <x:row r="272" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A272" s="40" t="n">
         <x:v>271</x:v>
       </x:c>
       <x:c r="B272" s="9" t="str">
-        <x:v>bmw-x5m-s63-cooling-system-2010</x:v>
+        <x:v>bmw-x6-transfer-case-2008</x:v>
       </x:c>
       <x:c r="C272" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2008-2023 | BMW | X6</x:v>
       </x:c>
       <x:c r="D272" s="9" t="str">
-        <x:v>S63 Cooling System Component Failures - E70/F85/F95 X5 M</x:v>
+        <x:v>Transfer Case Actuator Motor Failure (All xDrive Models)</x:v>
       </x:c>
       <x:c r="E272" s="9" t="str">
-        <x:v>PROACTIVE MAINTENANCE SCHEDULE: Replace electric water pump at 60,000 miles ($400-$700 + labor). Replace thermostat at same time ($150-$250). Replace expansion tank at 60,000-80,000 miles ($100-$200). Inspect all coolant hoses at every oil change - replace any that are soft, bulging, or showing surface cracks. E70 X5 M expansion tank vent hose: 17128627119 ($30-$50). Flush coolant system every 2 years or 30,000 miles (more frequent than BMW's 4-year recommendation). Use ONLY BMW coolant mixed 50/50 with distilled water. For E70 hot-V turbo coolant lines: GRYPHONTEK repair kit eliminates plastic T-fitting failure (see separate issue entry). Budget $1,500-$2,500 for complete cooling system refresh at 60,000 miles. This prevents catastrophic overheating that can destroy the S63 engine ($15,000-$34,000 engine replacement).</x:v>
+        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket gear repair kit ($100-150). G06 actuator motor 27609469023 ($400-600) for complete replacement. DIY gear repair kits are straightforward and save $1,200+ over dealer replacement. Complete transfer case replacement if internal damage occurred: $1,400-3,300. PREVENTIVE: If buying used X6 over 80k miles, budget for this repair and listen for clicking noise when shutting off ignition.</x:v>
       </x:c>
       <x:c r="F272" s="9" t="n">
         <x:v>0</x:v>
@@ -10125,21 +10881,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="273" ht="1135.199951171875" hidden="0" customHeight="1">
+    <x:row r="273" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A273" s="40" t="n">
         <x:v>272</x:v>
       </x:c>
       <x:c r="B273" s="9" t="str">
-        <x:v>bmw-x5m-s63-oil-leaks-2010</x:v>
+        <x:v>bmw-x6m-front-thrust-arm-bushing-2015</x:v>
       </x:c>
       <x:c r="C273" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2015-2025 | BMW | X6 M</x:v>
       </x:c>
       <x:c r="D273" s="9" t="str">
-        <x:v>S63 V8 Chronic Oil Leaks (Valve Cover, Oil Pan, Turbo Lines) - E70/F85/F95 X5 M</x:v>
+        <x:v>Front Thrust Arm Bushing (Tension Strut) Premature Wear</x:v>
       </x:c>
       <x:c r="E273" s="9" t="str">
-        <x:v>Valve cover gasket replacement (both sides): $1,200-$2,500 with labor. BMW plastic valve covers can crack and must be replaced entirely (not just gasket) - inspect during service. Oil filter housing gasket: $400-$800 with labor. Oil pan gasket: $2,000-$3,500 (requires engine/subframe drop). Turbo oil feed/return lines: replace with GRYPHONTEK or MAMBA upgraded silicone/braided lines during any turbo service ($200-$400). VANOS solenoid seals: $100-$200 (DIY-friendly). For comprehensive oil leak repair at 80,000+ miles: budget $3,000-$5,000 to address all common leak points simultaneously. Valve cover bolt torque is CRITICAL - too tight cracks the cover ($800-$1,200 per cover), too loose and it leaks.</x:v>
+        <x:v>Replace both front thrust arms as complete assemblies (the bushings are not serviceable separately). Use genuine BMW M-spec parts or Lemforder equivalents. Perform a 4-wheel alignment immediately after replacement. Upgrade to Powerflex polyurethane thrust arm bushings for extended lifespan, especially on tracked cars.</x:v>
       </x:c>
       <x:c r="F273" s="9" t="n">
         <x:v>0</x:v>
@@ -10148,21 +10904,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="274" ht="1412.4000244140625" hidden="0" customHeight="1">
+    <x:row r="274" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A274" s="40" t="n">
         <x:v>273</x:v>
       </x:c>
       <x:c r="B274" s="9" t="str">
-        <x:v>bmw-x5m-s63-rod-bearing-2010</x:v>
+        <x:v>bmw-x6m-s63-rod-bearing-2010</x:v>
       </x:c>
       <x:c r="C274" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i</x:v>
+        <x:v>2010-2023 | BMW | X6 M | M50i, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D274" s="9" t="str">
-        <x:v>S63 V8 Rod Bearing Premature Wear &amp; Failure - E70/F85 X5 M</x:v>
+        <x:v>S63 Rod Bearing Failure (X6 M)</x:v>
       </x:c>
       <x:c r="E274" s="9" t="str">
-        <x:v>PREVENTIVE: For track-driven X5 M, replace rod bearings proactively at 60,000-80,000 miles. ACL Race Series rod bearings (8B1578HX-STD for S63B44, +0.001" extra oil clearance) are the community gold standard ($200-$350 for bearing set). WPC surface-treated bearings from Lang Racing are the premium choice ($400-$600 set). Total cost for preventive rod bearing service: $4,500-$8,500 depending on shop. Oil analysis every 5,000 miles through Blackstone Labs ($30/test) to monitor bearing wear metals (lead and copper). Use only BMW 10W-60 synthetic oil with 5,000-7,500 mile oil change intervals. Never track the car on cold oil. Mporium BMW offers specialized S63 rod bearing service starting at $4,499. If catastrophic failure: rebuilt S63 engine from RK Autowerks (~$8,500 + installation), new BMW engine (~$34,000), or complete engine rebuild ($12,000-$18,000).</x:v>
+        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles ($2,500-5,000 labor-intensive job). Use ACL Race 8B1578HX-STD ($150-250) or King CR8049SV ($120-200) upgraded bearings - these are stronger than OEM and provide better durability under high loads. Send oil samples for analysis (Blackstone Labs ~$30) every 5,000 miles to monitor bearing wear metals. If bearings have already failed: engine replacement required ($15,000-30,000). DO NOT buy used X6 M without documented bearing replacement history or fresh oil analysis.</x:v>
       </x:c>
       <x:c r="F274" s="9" t="n">
         <x:v>0</x:v>
@@ -10171,21 +10927,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="275" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="275" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A275" s="40" t="n">
         <x:v>274</x:v>
       </x:c>
       <x:c r="B275" s="9" t="str">
-        <x:v>bmw-x5m-s63-turbo-coolant-line-2010</x:v>
+        <x:v>bmw-x6m-vanos-solenoid-2015</x:v>
       </x:c>
       <x:c r="C275" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 M</x:v>
+        <x:v>2015-2021 | BMW | X6 M | S63</x:v>
       </x:c>
       <x:c r="D275" s="9" t="str">
-        <x:v>S63 Turbo Coolant Line Plastic T-Fitting Failure (Hot-V Design) - E70 X5 M</x:v>
+        <x:v>VANOS Solenoid Oil Sludge Buildup</x:v>
       </x:c>
       <x:c r="E275" s="9" t="str">
-        <x:v>Replace ALL factory plastic turbo coolant T-fittings and hoses with GRYPHONTEK S63 Turbo Coolant Line Repair Kit ($200-$400). Kit includes pre-shaped multi-layer reinforced silicone hoses, brass T-fittings (replacing factory plastic), and all necessary hose clamps. Direct bolt-on installation designed for the E70/E71 S63 engine bay. MAMBA Turbo also offers a reinforced turbo coolant line kit with brass and silicone components ($150-$350). This is a PROACTIVE replacement - do not wait for failure. Replace at first sign of coolant weeping or during any turbo service. Labor: $800-$1,500 due to tight access in hot-V engine valley. If turbo bearings are damaged from overheating: turbo replacement $3,000-$5,000 per unit.</x:v>
+        <x:v>Remove and clean or replace the VANOS solenoids. Perform an engine oil flush. Strictly follow 7,500-mile oil change intervals with BMW LL-01 rated 0W-40 synthetic oil.</x:v>
       </x:c>
       <x:c r="F275" s="9" t="n">
         <x:v>0</x:v>
@@ -10194,21 +10950,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="276" ht="1135.199951171875" hidden="0" customHeight="1">
+    <x:row r="276" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A276" s="40" t="n">
         <x:v>275</x:v>
       </x:c>
       <x:c r="B276" s="9" t="str">
-        <x:v>bmw-x5m-s63-vanos-solenoid-2010</x:v>
+        <x:v>bmw-x7-48v-battery-2020</x:v>
       </x:c>
       <x:c r="C276" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2020-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D276" s="9" t="str">
-        <x:v>S63 VANOS Solenoid Failure - E70/F85/F95 X5 M</x:v>
+        <x:v>48V Mild Hybrid Battery Issues</x:v>
       </x:c>
       <x:c r="E276" s="9" t="str">
-        <x:v>Replace all 4 VANOS solenoids simultaneously - they are same age and if one has failed, others are close behind. Pierburg 11368605123 (OEM supplier) at $30-$50 each from Turner Motorsport or BimmerWorld. Genuine BMW 11368482268 for S63TU applications at $50-$70 each. Total parts cost: $120-$280 for all 4 solenoids. Also replace VANOS solenoid O-rings and filter screens during service. Labor: 1-2 hours professional ($150-$400 labor). This is one of the easier S63 repairs - accessible from top of engine without removing intake manifold. Natafox and Febi also offer quality aftermarket VANOS solenoids at lower cost ($20-$35 each). Clean VANOS system with fresh oil change immediately after solenoid replacement.</x:v>
+        <x:v>Replace the 48V mild hybrid battery ($1,000-2,000 at dealer). Requires dealer-level diagnostic tools and coding after installation - this is NOT a DIY repair. The 48V battery is separate from the main 12V battery. No aftermarket alternatives currently available. Check if vehicle is still under BMW warranty or extended warranty coverage. Some owners choose to live with the failed auto start-stop rather than pay for replacement.</x:v>
       </x:c>
       <x:c r="F276" s="9" t="n">
         <x:v>0</x:v>
@@ -10217,21 +10973,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="277" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="277" ht="726" hidden="0" customHeight="1">
       <x:c r="A277" s="40" t="n">
         <x:v>276</x:v>
       </x:c>
       <x:c r="B277" s="9" t="str">
-        <x:v>bmw-x5m-s63-wastegate-rattle-2010</x:v>
+        <x:v>bmw-x7-air-suspension-2019</x:v>
       </x:c>
       <x:c r="C277" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 M | S63</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D277" s="9" t="str">
-        <x:v>S63 Twin Turbo Wastegate Rattle - E70/F85 X5 M</x:v>
+        <x:v>Air Suspension Compressor &amp; Strut Failure (Standard Equipment)</x:v>
       </x:c>
       <x:c r="E277" s="9" t="str">
-        <x:v>Option 1 (Most cost-effective): MAMBA SUS316 stainless steel wastegate rattle flapper repair kit for S63 MGT2260 (part 077-0024, replaces 790463-2 / 790484-3), approximately $150-$300 per turbo. Requires turbo removal for installation. Option 2: Lskioer turbo wastegate rattle flapper repair kit for S63/S63TU MGT2260DSL ($80-$150 per kit on Amazon). Option 3: Replace turbo wastegate actuators with new OEM units ($300-$500 each). Option 4: Full turbocharger replacement with new or remanufactured units ($3,000-$5,000 per turbo + labor). Labor for turbo removal and reinstallation: $2,000-$3,500 for both turbos. While turbos are out: replace turbo oil feed/return lines, coolant lines, and all gaskets (GRYPHONTEK turbo coolant line repair kit for E70 X5M, ~$200-$400).</x:v>
+        <x:v>Replace failed air struts and/or compressor. Front strut left 37106869035 ($1,500-2,000), right 37106869036 ($1,500-2,000), rear 37106869039 ($1,000-1,500). Compressor 37206861882 ($800-1,200). RebuildMasterTech rebuilt struts ($600-900 each) are a more affordable alternative. Total repair can reach $2,180-5,000+ depending on which components have failed. Replace both struts on same axle simultaneously. Inspect at 50,000 miles for early signs of leaking.</x:v>
       </x:c>
       <x:c r="F277" s="9" t="n">
         <x:v>0</x:v>
@@ -10240,21 +10996,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="278" ht="1069.199951171875" hidden="0" customHeight="1">
+    <x:row r="278" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A278" s="40" t="n">
         <x:v>277</x:v>
       </x:c>
       <x:c r="B278" s="9" t="str">
-        <x:v>bmw-x5m-transfer-case-actuator-2010</x:v>
+        <x:v>bmw-x7-air-suspension-compressor-2019</x:v>
       </x:c>
       <x:c r="C278" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M</x:v>
+        <x:v>2019-2026 | BMW | X7</x:v>
       </x:c>
       <x:c r="D278" s="9" t="str">
-        <x:v>xDrive Transfer Case Actuator Motor Failure - E70/F85/F95 X5 M</x:v>
+        <x:v>Air Suspension Compressor Failure</x:v>
       </x:c>
       <x:c r="E278" s="9" t="str">
-        <x:v>Replace transfer case actuator motor. E70 X5 M: BMW 27107566296 or equivalent ($250-$450 for actuator motor). F85 X5 M: BMW 27608643153 or equivalent ($300-$500). F95 X5 M: check VIN-specific part number with dealer. FCP Euro has an excellent DIY guide for BMW transfer case actuator repair - the actuator can be replaced without removing the entire transfer case. Labor: 2-3 hours at specialist shop ($300-$600 labor). Change transfer case fluid at same time with BMW DTF-1 specification fluid. XeMODeX offers remanufactured transfer case actuator motors at reduced cost ($200-$350). For complete transfer case failure: $3,500-$6,000 for replacement unit + labor.</x:v>
+        <x:v>Replace the air suspension compressor. Inspect all four air springs for leaks using soapy water solution. Replace any leaking air springs to prevent repeated compressor failure. Check the valve block for proper operation. The compressor is located under the rear of the vehicle.</x:v>
       </x:c>
       <x:c r="F278" s="9" t="n">
         <x:v>0</x:v>
@@ -10263,21 +11019,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="279" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="279" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A279" s="40" t="n">
         <x:v>278</x:v>
       </x:c>
       <x:c r="B279" s="9" t="str">
-        <x:v>bmw-x6-adaptive-drive-malfunction-2008</x:v>
+        <x:v>bmw-x7-b58-coolant-2019</x:v>
       </x:c>
       <x:c r="C279" s="9" t="str">
-        <x:v>2008-2019 | BMW | X6</x:v>
+        <x:v>2019-2023 | BMW | X7 | xDrive40i | B58</x:v>
       </x:c>
       <x:c r="D279" s="9" t="str">
-        <x:v>Adaptive Drive System Malfunction</x:v>
+        <x:v>B58 Coolant System Failures (xDrive40i)</x:v>
       </x:c>
       <x:c r="E279" s="9" t="str">
-        <x:v>Diagnose specific Adaptive Drive component failure using BMW ISTA diagnostics. Replace the failed component — most commonly the hydraulic pump or valve block. If repair cost is prohibitive, some owners convert to conventional anti-roll bars as a permanent fix at lower cost.</x:v>
+        <x:v>Replace failed coolant system components. Water pump 11518482250 ($300-400). Thermostat 11537644811 ($150-250). Replace expansion tank and all plastic coolant connections when performing repair to prevent cascading failures. For 2023+ models, check VIN for recall 24V-608 coverage for coolant pump connector. Total repair $500-2,500 depending on extent of damage. PREVENTIVE: Replace thermostat and water pump at 60,000-70,000 miles before failure. Inspect coolant hoses and connections at every oil change after 50k miles.</x:v>
       </x:c>
       <x:c r="F279" s="9" t="n">
         <x:v>0</x:v>
@@ -10286,21 +11042,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="280" ht="858" hidden="0" customHeight="1">
+    <x:row r="280" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A280" s="40" t="n">
         <x:v>279</x:v>
       </x:c>
       <x:c r="B280" s="9" t="str">
-        <x:v>bmw-x6-air-suspension-2008</x:v>
+        <x:v>bmw-x7-b58-coolant-expansion-tank-2019</x:v>
       </x:c>
       <x:c r="C280" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6</x:v>
+        <x:v>2019-2026 | BMW | X7 | B58</x:v>
       </x:c>
       <x:c r="D280" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure</x:v>
+        <x:v>B58 Coolant Expansion Tank Crack</x:v>
       </x:c>
       <x:c r="E280" s="9" t="str">
-        <x:v>Replace failed air springs or compressor. Arnott rear air spring A-2642 ($200-300 each). OEM F16 spring 37126795013 ($200). Arnott compressor P-2655 ($599). Or convert to coil springs: Strutmasters BB2RBM conversion kit ($1,200-1,800) permanently eliminates air suspension issues. Conversion is cheaper long-term than continued air suspension repairs. If keeping air suspension: inspect air springs at 60,000-80,000 miles for cracks/leaks before compressor damage occurs. Replace both air springs on same axle simultaneously.</x:v>
+        <x:v>Replace the coolant expansion tank with an updated BMW part that uses improved plastic composition. Also replace the cap and inspect all coolant hoses. Flush and refill the cooling system with BMW-approved coolant. Check for coolant contamination from the old tank.</x:v>
       </x:c>
       <x:c r="F280" s="9" t="n">
         <x:v>0</x:v>
@@ -10314,13 +11070,13 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="B281" s="9" t="str">
-        <x:v>bmw-x6-ibs-brake-recall-2023</x:v>
+        <x:v>bmw-x7-ibs-brake-recall-2023</x:v>
       </x:c>
       <x:c r="C281" s="9" t="str">
-        <x:v>2024-2024 | BMW | X6</x:v>
+        <x:v>2023-2025 | BMW | X7</x:v>
       </x:c>
       <x:c r="D281" s="9" t="str">
-        <x:v>2024 X6 Integrated Brake System Recall 26V-422</x:v>
+        <x:v>2023-2025 X7 Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E281" s="9" t="str">
         <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
@@ -10332,21 +11088,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="282" ht="924" hidden="0" customHeight="1">
+    <x:row r="282" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A282" s="40" t="n">
         <x:v>281</x:v>
       </x:c>
       <x:c r="B282" s="9" t="str">
-        <x:v>bmw-x6-n63-timing-chain-2008</x:v>
+        <x:v>bmw-x7-n63-oil-consumption-2019</x:v>
       </x:c>
       <x:c r="C282" s="9" t="str">
-        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
+        <x:v>2019-2023 | BMW | X7 | M50i, M60i, xDrive50i | N63TU3</x:v>
       </x:c>
       <x:c r="D282" s="9" t="str">
-        <x:v>N63 Timing Chain Stretch &amp; Guide Failure (E71/F16 xDrive50i)</x:v>
+        <x:v>N63TU3 Oil Consumption &amp; Valve Stem Seal Degradation (xDrive50i/M50i/M60i)</x:v>
       </x:c>
       <x:c r="E282" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: If you own 2008-2014 E71 xDrive50i with N63, replace timing chain guides and tensioners IMMEDIATELY at 60,000-80,000 miles ($4,000-6,000) BEFORE failure. IWIS timing chain kit 90001521 ($800-1,200) or Turner kit 11317594899KT recommended. Replace lower chain guide 11147574373 at same time. If chain has already failed: complete engine replacement required ($15,000-25,000). Check VIN with BMW dealer for extended warranty eligibility. 2015+ N63TU engines have improved timing components but still require monitoring.</x:v>
+        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 for OEM spec. 5150 AutoSport Viton upgraded seals ($150-200) recommended for better heat resistance. AGA Tools kit includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Check eligibility for class action settlement coverage. Some owners monitor oil levels and top off rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil and check level every 500-1,000 miles.</x:v>
       </x:c>
       <x:c r="F282" s="9" t="n">
         <x:v>0</x:v>
@@ -10355,21 +11111,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="283" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="283" ht="396" hidden="0" customHeight="1">
       <x:c r="A283" s="40" t="n">
         <x:v>282</x:v>
       </x:c>
       <x:c r="B283" s="9" t="str">
-        <x:v>bmw-x6-n63-valve-stem-seal-wear-2008</x:v>
+        <x:v>bmw-x7-panoramic-roof-rattle-2019</x:v>
       </x:c>
       <x:c r="C283" s="9" t="str">
-        <x:v>2008-2019 | BMW | X6 | N63</x:v>
+        <x:v>2019-2026 | BMW | X7</x:v>
       </x:c>
       <x:c r="D283" s="9" t="str">
-        <x:v>N63 Valve Stem Seal Degradation and Oil Burning</x:v>
+        <x:v>Panoramic Sunroof Rattle and Creak</x:v>
       </x:c>
       <x:c r="E283" s="9" t="str">
-        <x:v>Replace all intake and exhaust valve stem seals. This is a major job requiring head work. Also replace turbo oil return lines and update engine software per BMW N63 Customer Care Package specifications. Ensure proper oil grade (BMW LL-01) is used.</x:v>
+        <x:v>Apply BMW-approved felt tape or lubricant to sunroof guide rails. Replace worn guide rail bushings. In severe cases, the sunroof cassette or seal may need replacement under warranty. BMW has issued updated guide rail components for early production vehicles.</x:v>
       </x:c>
       <x:c r="F283" s="9" t="n">
         <x:v>0</x:v>
@@ -10378,21 +11134,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="284" ht="858" hidden="0" customHeight="1">
+    <x:row r="284" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A284" s="40" t="n">
         <x:v>283</x:v>
       </x:c>
       <x:c r="B284" s="9" t="str">
-        <x:v>bmw-x6-n63-valve-stem-seals-2008</x:v>
+        <x:v>bmw-x7-sunroof-leak-2019</x:v>
       </x:c>
       <x:c r="C284" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6 | M50i, xDrive50i | N63</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D284" s="9" t="str">
-        <x:v>N63 Valve Stem Seal / Oil Consumption (xDrive50i)</x:v>
+        <x:v>Panoramic Sunroof Water Leak</x:v>
       </x:c>
       <x:c r="E284" s="9" t="str">
-        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 ($80-120/set of 16, need 2 sets for V8). 5150 AutoSport Viton upgraded seals ($150-200) are recommended for better heat resistance in hot-vee configuration. AGA Tools kit AGA-N63-VSK-K ($500-800) includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Some owners monitor oil levels and add as needed rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil.</x:v>
+        <x:v>Clear clogged sunroof drain tubes ($100-300 at shop). Reference TSB SIB 54 11 19 when visiting dealer. For persistent leaks, drain tube connections or sunroof seal may need replacement ($500-1,500). If water has damaged interior electronics, repair costs can reach $3,000. PREVENTIVE: Clear sunroof drains annually, especially in areas with heavy tree debris. Run compressed air or flexible drain snake through drain tubes during oil changes. Keep sunroof track clean of debris.</x:v>
       </x:c>
       <x:c r="F284" s="9" t="n">
         <x:v>0</x:v>
@@ -10401,21 +11157,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="285" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="285" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A285" s="40" t="n">
         <x:v>284</x:v>
       </x:c>
       <x:c r="B285" s="9" t="str">
-        <x:v>bmw-x6-n63-wastegate-2008</x:v>
+        <x:v>bmw-x7-tire-wear-2019</x:v>
       </x:c>
       <x:c r="C285" s="9" t="str">
-        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D285" s="9" t="str">
-        <x:v>N63 Turbo Wastegate Rattle (xDrive50i)</x:v>
+        <x:v>Premature Tire Wear (Especially 21"/22" Wheels)</x:v>
       </x:c>
       <x:c r="E285" s="9" t="str">
-        <x:v>Repair options range from flapper repair kits ($50-100/turbo) to complete turbocharger replacement ($4,000-8,000 for both). Garrett MGT2256S flapper repair kit ($50-100 per turbo) is cheapest fix. MAMBA adjustable actuator kit ($150-300) provides more durable solution. OEM actuators 11657646093 available from BMW. Complete turbo replacement $2,000-4,000 per turbo. MONITORING: Wastegate rattle is early warning - address before complete turbo failure to avoid $8,000+ repair.</x:v>
+        <x:v>Have alignment adjusted to reduce aggressive camber settings ($200-400). Switch to quality tires designed for heavy SUVs: Michelin Pilot Sport 4S or Continental PremiumContact 6 are recommended. If possible, avoid 22" wheels and opt for 21" or smaller for better tire longevity and ride comfort. Alignment adjustment can extend tire life from 15,000 to 30,000+ miles. Total cost $200-2,000 depending on tire replacement needs. Check alignment every 10,000 miles.</x:v>
       </x:c>
       <x:c r="F285" s="9" t="n">
         <x:v>0</x:v>
@@ -10424,21 +11180,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="286" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="286" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A286" s="40" t="n">
         <x:v>285</x:v>
       </x:c>
       <x:c r="B286" s="9" t="str">
-        <x:v>bmw-x6-rear-differential-bushing-2008</x:v>
+        <x:v>bmw-xm-airbag-passenger-knee-recall-2023</x:v>
       </x:c>
       <x:c r="C286" s="9" t="str">
-        <x:v>2008-2026 | BMW | X6</x:v>
+        <x:v>2023-2023 | BMW | XM</x:v>
       </x:c>
       <x:c r="D286" s="9" t="str">
-        <x:v>Rear Differential Bushing Deterioration</x:v>
+        <x:v>2023 XM Front-Passenger Knee-Airbag Recall 23V-622</x:v>
       </x:c>
       <x:c r="E286" s="9" t="str">
-        <x:v>Replace all rear differential mount bushings. Use OEM or equivalent quality bushings (Lemforder is the OEM supplier). Inspect the differential housing for any damage from excessive movement. Perform subframe alignment check after bushing replacement.</x:v>
+        <x:v>Check the VIN for an open 23V-622 campaign. If open, an authorized BMW dealer replaces the front-passenger knee airbag free of charge. Do not attempt airbag diagnosis or order a clock spring or airbag module from this card; supplemental-restraint work requires trained personnel and VIN-selected parts.</x:v>
       </x:c>
       <x:c r="F286" s="9" t="n">
         <x:v>0</x:v>
@@ -10447,21 +11203,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="287" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="287" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A287" s="40" t="n">
         <x:v>286</x:v>
       </x:c>
       <x:c r="B287" s="9" t="str">
-        <x:v>bmw-x6-transfer-case-2008</x:v>
+        <x:v>bmw-xm-hybrid-drivetrain-hesitation-2023</x:v>
       </x:c>
       <x:c r="C287" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6</x:v>
+        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid, S68</x:v>
       </x:c>
       <x:c r="D287" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure (All xDrive Models)</x:v>
+        <x:v>Hybrid Drivetrain Hesitation and Power Delivery Lag</x:v>
       </x:c>
       <x:c r="E287" s="9" t="str">
-        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket gear repair kit ($100-150). G06 actuator motor 27609469023 ($400-600) for complete replacement. DIY gear repair kits are straightforward and save $1,200+ over dealer replacement. Complete transfer case replacement if internal damage occurred: $1,400-3,300. PREVENTIVE: If buying used X6 over 80k miles, budget for this repair and listen for clicking noise when shutting off ignition.</x:v>
+        <x:v>Visit the dealer for the latest transmission and hybrid system software calibration updates. Select Sport or Sport Plus mode for more consistent power delivery. The latest software revisions significantly improve the electric-to-V8 handoff smoothness. If hesitation persists after updates, the dealer can reset the transmission adaptation values to relearn driving patterns.</x:v>
       </x:c>
       <x:c r="F287" s="9" t="n">
         <x:v>0</x:v>
@@ -10470,21 +11226,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="288" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="288" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A288" s="40" t="n">
         <x:v>287</x:v>
       </x:c>
       <x:c r="B288" s="9" t="str">
-        <x:v>bmw-x6m-front-thrust-arm-bushing-2015</x:v>
+        <x:v>bmw-xm-integrated-brake-system-recall-2023</x:v>
       </x:c>
       <x:c r="C288" s="9" t="str">
-        <x:v>2015-2025 | BMW | X6 M</x:v>
+        <x:v>2023-2024 | BMW | XM</x:v>
       </x:c>
       <x:c r="D288" s="9" t="str">
-        <x:v>Front Thrust Arm Bushing (Tension Strut) Premature Wear</x:v>
+        <x:v>2023-2024 XM Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E288" s="9" t="str">
-        <x:v>Replace both front thrust arms as complete assemblies (the bushings are not serviceable separately). Use genuine BMW M-spec parts or Lemforder equivalents. Perform a 4-wheel alignment immediately after replacement. Upgrade to Powerflex polyurethane thrust arm bushings for extended lifespan, especially on tracked cars.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; wheel-speed sensors are not the recall remedy.</x:v>
       </x:c>
       <x:c r="F288" s="9" t="n">
         <x:v>0</x:v>
@@ -10493,21 +11249,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="289" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="289" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A289" s="40" t="n">
         <x:v>288</x:v>
       </x:c>
       <x:c r="B289" s="9" t="str">
-        <x:v>bmw-x6m-s63-rod-bearing-2010</x:v>
+        <x:v>bmw-xm-suspension-ride-quality-2023</x:v>
       </x:c>
       <x:c r="C289" s="9" t="str">
-        <x:v>2010-2023 | BMW | X6 M | M50i, xDrive50i | S63</x:v>
+        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid</x:v>
       </x:c>
       <x:c r="D289" s="9" t="str">
-        <x:v>S63 Rod Bearing Failure (X6 M)</x:v>
+        <x:v>Harsh Ride Quality and Suspension Stiffness</x:v>
       </x:c>
       <x:c r="E289" s="9" t="str">
-        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles ($2,500-5,000 labor-intensive job). Use ACL Race 8B1578HX-STD ($150-250) or King CR8049SV ($120-200) upgraded bearings - these are stronger than OEM and provide better durability under high loads. Send oil samples for analysis (Blackstone Labs ~$30) every 5,000 miles to monitor bearing wear metals. If bearings have already failed: engine replacement required ($15,000-30,000). DO NOT buy used X6 M without documented bearing replacement history or fresh oil analysis.</x:v>
+        <x:v>Check tire pressures regularly - overinflated tires significantly worsen the harsh ride. Some owners report improved comfort by switching to a tire with a taller sidewall profile (if available for the XM's wheel size). Use Comfort mode for daily driving. Unfortunately, no aftermarket spring or damper solution currently exists to significantly improve the ride without compromising the handling needed for the XM's weight.</x:v>
       </x:c>
       <x:c r="F289" s="9" t="n">
         <x:v>0</x:v>
@@ -10516,21 +11272,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="290" ht="277.20001220703125" hidden="0" customHeight="1">
+    <x:row r="290" ht="528" hidden="0" customHeight="1">
       <x:c r="A290" s="40" t="n">
         <x:v>289</x:v>
       </x:c>
       <x:c r="B290" s="9" t="str">
-        <x:v>bmw-x6m-vanos-solenoid-2015</x:v>
+        <x:v>bmw-z3-convertible-top-rear-window-cracking-clouding-bead-separatio</x:v>
       </x:c>
       <x:c r="C290" s="9" t="str">
-        <x:v>2015-2021 | BMW | X6 M | S63</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D290" s="9" t="str">
-        <x:v>VANOS Solenoid Oil Sludge Buildup</x:v>
+        <x:v>Convertible Top Rear Window Cracking, Clouding, and Bead Separation</x:v>
       </x:c>
       <x:c r="E290" s="9" t="str">
-        <x:v>Remove and clean or replace the VANOS solenoids. Perform an engine oil flush. Strictly follow 7,500-mile oil change intervals with BMW LL-01 rated 0W-40 synthetic oil.</x:v>
+        <x:v>Replace the rear window panel only — BMW used a zipper system so the clouded/cracked window unzips and a new window zips/tapes in without disturbing the fabric top. Re-gluing separated bead trim rarely holds, so window replacement is the durable fix. Job is a DIY-feasible 1-1.5 hours; replace the whole top only if the fabric is also degraded.</x:v>
       </x:c>
       <x:c r="F290" s="9" t="n">
         <x:v>0</x:v>
@@ -10539,22 +11295,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="291" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="291" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A291" s="40" t="n">
         <x:v>290</x:v>
       </x:c>
       <x:c r="B291" s="9" t="str">
-        <x:v>bmw-x7-48v-battery-2020</x:v>
+        <x:v>bmw-z3-cooling-system-failure-1996</x:v>
       </x:c>
       <x:c r="C291" s="9" t="str">
-        <x:v>2020-2023 | BMW | X7</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D291" s="9" t="str">
-        <x:v>48V Mild Hybrid Battery Issues</x:v>
-      </x:c>
-      <x:c r="E291" s="9" t="str">
-        <x:v>Replace the 48V mild hybrid battery ($1,000-2,000 at dealer). Requires dealer-level diagnostic tools and coding after installation - this is NOT a DIY repair. The 48V battery is separate from the main 12V battery. No aftermarket alternatives currently available. Check if vehicle is still under BMW warranty or extended warranty coverage. Some owners choose to live with the failed auto start-stop rather than pay for replacement.</x:v>
-      </x:c>
+        <x:v>Cooling System Component Failures</x:v>
+      </x:c>
+      <x:c r="E291" s="9" t="str"/>
       <x:c r="F291" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -10562,21 +11316,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="292" ht="726" hidden="0" customHeight="1">
+    <x:row r="292" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A292" s="40" t="n">
         <x:v>291</x:v>
       </x:c>
       <x:c r="B292" s="9" t="str">
-        <x:v>bmw-x7-air-suspension-2019</x:v>
+        <x:v>bmw-z3-cracked-exhaust-manifold-1-9l-4-cylinder</x:v>
       </x:c>
       <x:c r="C292" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>1996-2002 | BMW | Z3 | 1.9, 1.9i, Z3 1.9 | 1.9L M44 4-cylinder, 1.9L M43TU 4-cylinder</x:v>
       </x:c>
       <x:c r="D292" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure (Standard Equipment)</x:v>
+        <x:v>Cracked Exhaust Manifold on 1.9L 4-Cylinder (M44/M43)</x:v>
       </x:c>
       <x:c r="E292" s="9" t="str">
-        <x:v>Replace failed air struts and/or compressor. Front strut left 37106869035 ($1,500-2,000), right 37106869036 ($1,500-2,000), rear 37106869039 ($1,000-1,500). Compressor 37206861882 ($800-1,200). RebuildMasterTech rebuilt struts ($600-900 each) are a more affordable alternative. Total repair can reach $2,180-5,000+ depending on which components have failed. Replace both struts on same axle simultaneously. Inspect at 50,000 miles for early signs of leaking.</x:v>
+        <x:v>Inspect the manifold for hairline cracks (a cold-engine listen or smoke test confirms the leak). Replace the cracked manifold with a used OE unit or an aftermarket stainless tubular header, and renew the manifold gasket and hardware. Allow roughly 3-4 hours labor.</x:v>
       </x:c>
       <x:c r="F292" s="9" t="n">
         <x:v>0</x:v>
@@ -10585,21 +11339,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="293" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="293" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A293" s="40" t="n">
         <x:v>292</x:v>
       </x:c>
       <x:c r="B293" s="9" t="str">
-        <x:v>bmw-x7-air-suspension-compressor-2019</x:v>
+        <x:v>bmw-z3-differential-mount-ear-trunk-floor-pan-tearing</x:v>
       </x:c>
       <x:c r="C293" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D293" s="9" t="str">
-        <x:v>Air Suspension Compressor Failure</x:v>
+        <x:v>Differential Mount Ear and Trunk Floor Pan Tearing</x:v>
       </x:c>
       <x:c r="E293" s="9" t="str">
-        <x:v>Replace the air suspension compressor. Inspect all four air springs for leaks using soapy water solution. Replace any leaking air springs to prevent repeated compressor failure. Check the valve block for proper operation. The compressor is located under the rear of the vehicle.</x:v>
+        <x:v>Inspect the trunk floor around the differential mount and rear subframe pickup points for cracks, torn metal, and broken spot welds. Repair requires welding and a reinforcement/re-fabrication plate kit to tie the diff mount/subframe back into the floor. Switching the diff carrier bushings to polyurethane reduces carrier movement and the stress that causes the tearing. Catching it early greatly limits the repair scope.</x:v>
       </x:c>
       <x:c r="F293" s="9" t="n">
         <x:v>0</x:v>
@@ -10608,21 +11362,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="294" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="294" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A294" s="40" t="n">
         <x:v>293</x:v>
       </x:c>
       <x:c r="B294" s="9" t="str">
-        <x:v>bmw-x7-b58-coolant-2019</x:v>
+        <x:v>bmw-z3-door-window-regulator-clip-mounting-tab-failure</x:v>
       </x:c>
       <x:c r="C294" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7 | xDrive40i | B58</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D294" s="9" t="str">
-        <x:v>B58 Coolant System Failures (xDrive40i)</x:v>
+        <x:v>Door Window Regulator Clip / Mounting Tab Failure</x:v>
       </x:c>
       <x:c r="E294" s="9" t="str">
-        <x:v>Replace failed coolant system components. Water pump 11518482250 ($300-400). Thermostat 11537644811 ($150-250). Replace expansion tank and all plastic coolant connections when performing repair to prevent cascading failures. For 2023+ models, check VIN for recall 24V-608 coverage for coolant pump connector. Total repair $500-2,500 depending on extent of damage. PREVENTIVE: Replace thermostat and water pump at 60,000-70,000 miles before failure. Inspect coolant hoses and connections at every oil change after 50k miles.</x:v>
+        <x:v>Replace the broken plastic regulator clips, or replace the regulator assembly if the cable or mechanism is also worn. If the welded mounting tab/anchor has torn from the door frame, it must be re-welded or reinforced before fitting a new regulator. Lubricate the window channels to reduce drag on the new parts.</x:v>
       </x:c>
       <x:c r="F294" s="9" t="n">
         <x:v>0</x:v>
@@ -10631,21 +11385,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="295" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="295" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A295" s="40" t="n">
         <x:v>294</x:v>
       </x:c>
       <x:c r="B295" s="9" t="str">
-        <x:v>bmw-x7-b58-coolant-expansion-tank-2019</x:v>
+        <x:v>bmw-z3-fuel-level-sender-failure-causing-erratic-dead-fuel-gauge</x:v>
       </x:c>
       <x:c r="C295" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7 | B58</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D295" s="9" t="str">
-        <x:v>B58 Coolant Expansion Tank Crack</x:v>
+        <x:v>Fuel Level Sender Failure Causing Erratic or Dead Fuel Gauge</x:v>
       </x:c>
       <x:c r="E295" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with an updated BMW part that uses improved plastic composition. Also replace the cap and inspect all coolant hoses. Flush and refill the cooling system with BMW-approved coolant. Check for coolant contamination from the old tank.</x:v>
+        <x:v>Remove the access panel behind the seats and inspect the sender. A dirty or lightly worn ceramic/resistor plate can sometimes be cleaned, but a cracked plate or worn brushes requires replacing the sender unit (or the complete fuel-pump/sender carrier assembly). Also check the tank vent valve, as tank vacuum can deform the float arm. Confirm wiring/ground integrity before condemning the sender.</x:v>
       </x:c>
       <x:c r="F295" s="9" t="n">
         <x:v>0</x:v>
@@ -10654,21 +11408,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="296" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="296" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A296" s="40" t="n">
         <x:v>295</x:v>
       </x:c>
       <x:c r="B296" s="9" t="str">
-        <x:v>bmw-x7-ibs-brake-recall-2023</x:v>
+        <x:v>bmw-z3-hvac-blower-final-stage-resistor-failure</x:v>
       </x:c>
       <x:c r="C296" s="9" t="str">
-        <x:v>2023-2025 | BMW | X7</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D296" s="9" t="str">
-        <x:v>2023-2025 X7 Integrated Brake System Recall 26V-422</x:v>
+        <x:v>HVAC Blower Final Stage Resistor Failure (Fan Only Works on Max)</x:v>
       </x:c>
       <x:c r="E296" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
+        <x:v>Replace the blower final stage resistor (A/C cars: part under the scuttle/cowl; non-A/C cars: behind the passenger footwell panel). If a new resistor does not restore all speeds, test the blower motor itself, which may also be worn. Inspect for corrosion/water intrusion at the cowl on A/C cars.</x:v>
       </x:c>
       <x:c r="F296" s="9" t="n">
         <x:v>0</x:v>
@@ -10677,21 +11431,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="297" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="297" ht="1584" hidden="0" customHeight="1">
       <x:c r="A297" s="40" t="n">
         <x:v>296</x:v>
       </x:c>
       <x:c r="B297" s="9" t="str">
-        <x:v>bmw-x7-n63-oil-consumption-2019</x:v>
+        <x:v>bmw-z3-rear-subframe-crack-1996</x:v>
       </x:c>
       <x:c r="C297" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7 | M50i, M60i, xDrive50i | N63TU3</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D297" s="9" t="str">
-        <x:v>N63TU3 Oil Consumption &amp; Valve Stem Seal Degradation (xDrive50i/M50i/M60i)</x:v>
+        <x:v>Rear Subframe Mounting Point Cracking</x:v>
       </x:c>
       <x:c r="E297" s="9" t="str">
-        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 for OEM spec. 5150 AutoSport Viton upgraded seals ($150-200) recommended for better heat resistance. AGA Tools kit includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Check eligibility for class action settlement coverage. Some owners monitor oil levels and top off rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil and check level every 500-1,000 miles.</x:v>
+        <x:v>Inspect the trunk floor, differential mount area, and all rear subframe mounting points from above and below the car for spot-weld separation, torn sheet metal, and cracked seams; a dye penetrant test or removing trunk trim/seam sealer may be needed to reveal early damage. If cracking is present, the proper repair is to drop the rear axle carrier/subframe, weld and reinforce the damaged unibody mounting points and trunk floor with a reinforcement kit (commonly Randy Forbes-style dual-ear/differential mount reinforcement or equivalent), then reinstall with new subframe bushings, differential mount bushings, and perform a 4-wheel alignment. Minor early cracks may be repairable before major deformation, but advanced damage often requires fabrication and extensive welding by a chassis/body specialist; typical cost ranges from about $2,000-$3,500 for early reinforcement repairs and can exceed $4,000-$6,000 if the floor is torn or multiple mounting points are damaged.</x:v>
       </x:c>
       <x:c r="F297" s="9" t="n">
         <x:v>0</x:v>
@@ -10700,22 +11454,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="298" ht="396" hidden="0" customHeight="1">
+    <x:row r="298" ht="66" hidden="0" customHeight="1">
       <x:c r="A298" s="40" t="n">
         <x:v>297</x:v>
       </x:c>
       <x:c r="B298" s="9" t="str">
-        <x:v>bmw-x7-panoramic-roof-rattle-2019</x:v>
+        <x:v>bmw-z3-rear-subframe-cracking-1996</x:v>
       </x:c>
       <x:c r="C298" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7</x:v>
+        <x:v>1996-2002 | BMW | Z3 | M52, M54</x:v>
       </x:c>
       <x:c r="D298" s="9" t="str">
-        <x:v>Panoramic Sunroof Rattle and Creak</x:v>
-      </x:c>
-      <x:c r="E298" s="9" t="str">
-        <x:v>Apply BMW-approved felt tape or lubricant to sunroof guide rails. Replace worn guide rail bushings. In severe cases, the sunroof cassette or seal may need replacement under warranty. BMW has issued updated guide rail components for early production vehicles.</x:v>
-      </x:c>
+        <x:v>Rear Subframe Mounting Point Cracks</x:v>
+      </x:c>
+      <x:c r="E298" s="9" t="str"/>
       <x:c r="F298" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -10723,21 +11475,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="299" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="299" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A299" s="40" t="n">
         <x:v>298</x:v>
       </x:c>
       <x:c r="B299" s="9" t="str">
-        <x:v>bmw-x7-sunroof-leak-2019</x:v>
+        <x:v>bmw-z3-valve-cover-gasket-oil-leak</x:v>
       </x:c>
       <x:c r="C299" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>1997-2002 | BMW | Z3 | 2.3, 2.5i, 2.8, 3.0i | M52 2.8, M52TU 2.5/2.8, M54 2.5/3.0</x:v>
       </x:c>
       <x:c r="D299" s="9" t="str">
-        <x:v>Panoramic Sunroof Water Leak</x:v>
+        <x:v>Valve Cover Gasket Oil Leak (M52/M54 6-Cylinder)</x:v>
       </x:c>
       <x:c r="E299" s="9" t="str">
-        <x:v>Clear clogged sunroof drain tubes ($100-300 at shop). Reference TSB SIB 54 11 19 when visiting dealer. For persistent leaks, drain tube connections or sunroof seal may need replacement ($500-1,500). If water has damaged interior electronics, repair costs can reach $3,000. PREVENTIVE: Clear sunroof drains annually, especially in areas with heavy tree debris. Run compressed air or flexible drain snake through drain tubes during oil changes. Keep sunroof track clean of debris.</x:v>
+        <x:v>Replace the valve cover gasket, the spark-plug-well/grommet seals, and the cover bolt seals. On M54 engines also clean oil from the plug wells and replace any oil-contaminated coil boots/coils. Use the correct torque sequence to avoid re-leaking. Inspect the cover for warping or cracks while it is off.</x:v>
       </x:c>
       <x:c r="F299" s="9" t="n">
         <x:v>0</x:v>
@@ -10746,21 +11498,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="300" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="300" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A300" s="40" t="n">
         <x:v>299</x:v>
       </x:c>
       <x:c r="B300" s="9" t="str">
-        <x:v>bmw-x7-tire-wear-2019</x:v>
+        <x:v>bmw-z3-vanos-seals-1999</x:v>
       </x:c>
       <x:c r="C300" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>1999-2002 | BMW | Z3 | M52, M54, S52</x:v>
       </x:c>
       <x:c r="D300" s="9" t="str">
-        <x:v>Premature Tire Wear (Especially 21"/22" Wheels)</x:v>
+        <x:v>VANOS Seal Failure (M52/M54/S52)</x:v>
       </x:c>
       <x:c r="E300" s="9" t="str">
-        <x:v>Have alignment adjusted to reduce aggressive camber settings ($200-400). Switch to quality tires designed for heavy SUVs: Michelin Pilot Sport 4S or Continental PremiumContact 6 are recommended. If possible, avoid 22" wheels and opt for 21" or smaller for better tire longevity and ride comfort. Alignment adjustment can extend tire life from 15,000 to 30,000+ miles. Total cost $200-2,000 depending on tire replacement needs. Check alignment every 10,000 miles.</x:v>
+        <x:v>Confirm the fault by checking for cold-start VANOS rattle, rough idle, hesitation, and scanning for cam timing or mixture-related fault codes; on M52TU/M54/S52 engines, inspect VANOS operation and rule out vacuum leaks before disassembly. Repair typically involves removing the valve cover and VANOS unit, replacing the internal piston seals/O-rings with updated Viton/Teflon seals, renewing the valve cover gasket and VANOS oil line sealing washers, and then re-timing the cams to BMW specifications if required. If the unit still rattles after resealing, the VANOS bearing/anti-rattle components or the complete VANOS assembly may need replacement. Typical cost is about $60-$150 in seals/gaskets for DIY repair, $300-$700 for an independent shop reseal, or $800-$1,500+ if a rebuilt/replacement VANOS unit is installed.</x:v>
       </x:c>
       <x:c r="F300" s="9" t="n">
         <x:v>0</x:v>
@@ -10774,16 +11526,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="B301" s="9" t="str">
-        <x:v>bmw-xm-airbag-passenger-knee-recall-2023</x:v>
+        <x:v>bmw-z4-b58-coolant-tank-2019</x:v>
       </x:c>
       <x:c r="C301" s="9" t="str">
-        <x:v>2023-2023 | BMW | XM</x:v>
+        <x:v>2019-2026 | BMW | Z4 | B58</x:v>
       </x:c>
       <x:c r="D301" s="9" t="str">
-        <x:v>2023 XM Front-Passenger Knee-Airbag Recall 23V-622</x:v>
+        <x:v>B58 Coolant Expansion Tank Cracking</x:v>
       </x:c>
       <x:c r="E301" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-622 campaign. If open, an authorized BMW dealer replaces the front-passenger knee airbag free of charge. Do not attempt airbag diagnosis or order a clock spring or airbag module from this card; supplemental-restraint work requires trained personnel and VIN-selected parts.</x:v>
+        <x:v>Replace the coolant expansion tank with an updated BMW part or aftermarket aluminum tank. Inspect the tank and cap regularly for signs of cracking, discoloration, or seepage. When replacing, also replace the cap and check all coolant hoses for brittleness. Flush and refill with BMW-approved coolant.</x:v>
       </x:c>
       <x:c r="F301" s="9" t="n">
         <x:v>0</x:v>
@@ -10792,21 +11544,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="302" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="302" ht="1306.800048828125" hidden="0" customHeight="1">
       <x:c r="A302" s="40" t="n">
         <x:v>301</x:v>
       </x:c>
       <x:c r="B302" s="9" t="str">
-        <x:v>bmw-xm-hybrid-drivetrain-hesitation-2023</x:v>
+        <x:v>bmw-z4-e85-convertible-top-hydraulic-2003</x:v>
       </x:c>
       <x:c r="C302" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid, S68</x:v>
+        <x:v>2003-2008 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D302" s="9" t="str">
-        <x:v>Hybrid Drivetrain Hesitation and Power Delivery Lag</x:v>
+        <x:v>Convertible Top Hydraulic Pump Motor Failure - E85 Z4</x:v>
       </x:c>
       <x:c r="E302" s="9" t="str">
-        <x:v>Visit the dealer for the latest transmission and hybrid system software calibration updates. Select Sport or Sport Plus mode for more consistent power delivery. The latest software revisions significantly improve the electric-to-V8 handoff smoothness. If hesitation persists after updates, the dealer can reset the transmission adaptation values to relearn driving patterns.</x:v>
+        <x:v>Replace hydraulic pump motor assembly (BMW 54347193448 / supersedes 54347119633). OEM Genuine BMW pump: $800-$1,200. Aftermarket alternatives available on Amazon for $150-$300 but quality varies significantly. Dealer labor is $1,500-$2,500+ as BMW procedure requires full top removal. ZRoadster.org members have documented a motor relocation to the boot/trunk area which allows much easier future access. Hydraulic fluid: use Aral Vitamol ZHM or BMW 54340394395 hydraulic oil. PREVENTION: Clean drain holes annually, ensure rubber bungs are properly seated, and check for water intrusion in pump area at every service. Some owners have had success with pump motor rebuilds from roofmotors.co.uk ($300-$500) but quality of rebuilds varies.</x:v>
       </x:c>
       <x:c r="F302" s="9" t="n">
         <x:v>0</x:v>
@@ -10815,21 +11567,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="303" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="303" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A303" s="40" t="n">
         <x:v>302</x:v>
       </x:c>
       <x:c r="B303" s="9" t="str">
-        <x:v>bmw-xm-integrated-brake-system-recall-2023</x:v>
+        <x:v>bmw-z4-e85-window-regulator-2003</x:v>
       </x:c>
       <x:c r="C303" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM</x:v>
+        <x:v>2003-2008 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D303" s="9" t="str">
-        <x:v>2023-2024 XM Integrated Brake System Recall 26V-422</x:v>
+        <x:v>Power Window Regulator Failure - E85 Z4</x:v>
       </x:c>
       <x:c r="E303" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; wheel-speed sensors are not the recall remedy.</x:v>
+        <x:v>Option 1 (Budget): Window regulator repair kit - replacement cables and rollers for ~$18-$25 from eBay/Amazon (BWR974 for left/driver side). Requires removing door panel and threading new cables through existing regulator frame. DIY-friendly with Z4-forum.com guides. Option 2 (Recommended): Full window regulator replacement. Driver side: BMW 51337198909 ($180-$280 OEM, $80-$150 aftermarket). Passenger side: BMW 51337198910 ($180-$280 OEM, $80-$150 aftermarket). Labor: $200-$400 at independent shop, $500-$700+ at dealer. DIY: 2-3 hours with door panel removal guide from Pelican Parts. ZRoadster.org recommends full replacement over repair kit for long-term reliability.</x:v>
       </x:c>
       <x:c r="F303" s="9" t="n">
         <x:v>0</x:v>
@@ -10838,21 +11590,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="304" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="304" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A304" s="40" t="n">
         <x:v>303</x:v>
       </x:c>
       <x:c r="B304" s="9" t="str">
-        <x:v>bmw-xm-suspension-ride-quality-2023</x:v>
+        <x:v>bmw-z4-electric-steering-rack-2003</x:v>
       </x:c>
       <x:c r="C304" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid</x:v>
+        <x:v>2012-2012 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D304" s="9" t="str">
-        <x:v>Harsh Ride Quality and Suspension Stiffness</x:v>
+        <x:v>2012 Z4 Electric Power-Steering Recall 12V-302</x:v>
       </x:c>
       <x:c r="E304" s="9" t="str">
-        <x:v>Check tire pressures regularly - overinflated tires significantly worsen the harsh ride. Some owners report improved comfort by switching to a tire with a taller sidewall profile (if available for the XM's wheel size). Use Comfort mode for daily driving. Unfortunately, no aftermarket spring or damper solution currently exists to significantly improve the ride without compromising the handling needed for the XM's weight.</x:v>
+        <x:v>Check the VIN for an open 12V-302 campaign. If open, an authorized BMW dealer replaces the steering-assistance module free of charge. If the steering warning and audible alert occur, maintain control, reduce speed, stop safely and arrange dealer or roadside assistance; do not replace a steering rack from this card.</x:v>
       </x:c>
       <x:c r="F304" s="9" t="n">
         <x:v>0</x:v>
@@ -10861,21 +11613,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="305" ht="528" hidden="0" customHeight="1">
+    <x:row r="305" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A305" s="40" t="n">
         <x:v>304</x:v>
       </x:c>
       <x:c r="B305" s="9" t="str">
-        <x:v>bmw-z3-convertible-top-rear-window-cracking-clouding-bead-separatio</x:v>
+        <x:v>bmw-z4-electric-water-pump-2006</x:v>
       </x:c>
       <x:c r="C305" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
+        <x:v>2012-2016 | BMW | Z4 | N20</x:v>
       </x:c>
       <x:c r="D305" s="9" t="str">
-        <x:v>Convertible Top Rear Window Cracking, Clouding, and Bead Separation</x:v>
+        <x:v>2012-2016 Z4 sDrive28i Water-Pump Connector Recall 24V-608</x:v>
       </x:c>
       <x:c r="E305" s="9" t="str">
-        <x:v>Replace the rear window panel only — BMW used a zipper system so the clouded/cracked window unzips and a new window zips/tapes in without disturbing the fabric top. Re-gluing separated bead trim rarely holds, so window replacement is the durable fix. Job is a DIY-feasible 1-1.5 hours; replace the whole top only if the fabric is also degraded.</x:v>
+        <x:v>Check the VIN for an open 24V-608 campaign. If open, an authorized BMW dealer inspects the water pump and connector, replaces them if necessary, and installs the protective shield free of charge. If smoke appears from the engine compartment, stop safely, switch off the vehicle, have occupants exit, move away from traffic and call emergency or roadside assistance; do not order a pump from this card.</x:v>
       </x:c>
       <x:c r="F305" s="9" t="n">
         <x:v>0</x:v>
@@ -10884,42 +11636,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="306" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="306" ht="1359.5999755859375" hidden="0" customHeight="1">
       <x:c r="A306" s="40" t="n">
         <x:v>305</x:v>
       </x:c>
       <x:c r="B306" s="9" t="str">
-        <x:v>bmw-z3-cooling-system-failure-1996</x:v>
+        <x:v>bmw-z4-g29-b58-water-pump-2019</x:v>
       </x:c>
       <x:c r="C306" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
+        <x:v>2019-2025 | BMW | Z4 | M40i, sDrive35i, sDrive35is | B48, B58</x:v>
       </x:c>
       <x:c r="D306" s="9" t="str">
-        <x:v>Cooling System Component Failures</x:v>
-      </x:c>
-      <x:c r="E306" s="9" t="str"/>
+        <x:v>B48/B58 Electric Water Pump &amp; Thermostat Failure - G29 Z4</x:v>
+      </x:c>
+      <x:c r="E306" s="9" t="str">
+        <x:v>Preventative replacement recommended at 60,000 miles. Always replace water pump and thermostat together - they share labor overlap and frequently fail concurrently. B48 sDrive30i: Water pump BMW 11518632586 ($300-$450), Thermostat BMW 11538685978 ($100-$150). B58 M40i: Water pump BMW 11518650986 ($350-$500), Thermostat BMW 11538685978 ($100-$150). Mishimoto offers performance water pump alternatives for B58 with improved impeller design. Replace 3 O-rings between thermostat and pump housing, plus 2 O-rings on coolant tube to head. Must replace water pump mounting bolts (torque-to-yield). Labor: 3-4 hours. FCP Euro lifetime warranty kits available. Also inspect plastic cylinder head coolant outlet adapter - known to shear off causing massive coolant leak.</x:v>
+      </x:c>
       <x:c r="F306" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G306" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="307" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="307" ht="1122" hidden="0" customHeight="1">
       <x:c r="A307" s="40" t="n">
         <x:v>306</x:v>
       </x:c>
       <x:c r="B307" s="9" t="str">
-        <x:v>bmw-z3-cracked-exhaust-manifold-1-9l-4-cylinder</x:v>
+        <x:v>bmw-z4-n54-hpfp-2009</x:v>
       </x:c>
       <x:c r="C307" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3 | 1.9, 1.9i, Z3 1.9 | 1.9L M44 4-cylinder, 1.9L M43TU 4-cylinder</x:v>
+        <x:v>2009-2011 | BMW | Z4 | M40i, sDrive35i, sDrive35is | N54</x:v>
       </x:c>
       <x:c r="D307" s="9" t="str">
-        <x:v>Cracked Exhaust Manifold on 1.9L 4-Cylinder (M44/M43)</x:v>
+        <x:v>N54 High Pressure Fuel Pump (HPFP) Failure - E89 Z4 sDrive35i/35is</x:v>
       </x:c>
       <x:c r="E307" s="9" t="str">
-        <x:v>Inspect the manifold for hairline cracks (a cold-engine listen or smoke test confirms the leak). Replace the cracked manifold with a used OE unit or an aftermarket stainless tubular header, and renew the manifold gasket and hardware. Allow roughly 3-4 hours labor.</x:v>
+        <x:v>Replace HPFP with latest revision Genuine BMW unit. The pump went through multiple revisions - ONLY install the latest version. Part number evolution: Original -&gt; 13517592881 (Index 10, TSB fix) -&gt; 13517616170 (latest revision, most reliable). Genuine BMW 13517616170 is the definitive fix ($350-$550 for pump). Replacement is straightforward DIY (1-2 hours) with basic tools. Also available as complete kit from FCP Euro with lifetime warranty. BMW extended warranty coverage to 10 years/120,000 miles under customer care package for original owners - check VIN eligibility. Replace low-pressure fuel sensor at same time (13537537319) as it may have been damaged by pressure fluctuations ($35-$55).</x:v>
       </x:c>
       <x:c r="F307" s="9" t="n">
         <x:v>0</x:v>
@@ -10928,21 +11682,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="308" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="308" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A308" s="40" t="n">
         <x:v>307</x:v>
       </x:c>
       <x:c r="B308" s="9" t="str">
-        <x:v>bmw-z3-differential-mount-ear-trunk-floor-pan-tearing</x:v>
+        <x:v>bmw-z4-n54-wastegate-rattle-2009</x:v>
       </x:c>
       <x:c r="C308" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
+        <x:v>2009-2010 | BMW | Z4 | N54</x:v>
       </x:c>
       <x:c r="D308" s="9" t="str">
-        <x:v>Differential Mount Ear and Trunk Floor Pan Tearing</x:v>
+        <x:v>2009-2010 Z4 sDrive35i N54 Wastegate Diagnosis</x:v>
       </x:c>
       <x:c r="E308" s="9" t="str">
-        <x:v>Inspect the trunk floor around the differential mount and rear subframe pickup points for cracks, torn metal, and broken spot welds. Repair requires welding and a reinforcement/re-fabrication plate kit to tie the diff mount/subframe back into the floor. Switching the diff carrier bushings to polyurethane reduces carrier movement and the stress that causes the tearing. Catching it early greatly limits the repair scope.</x:v>
+        <x:v>Confirm the VIN, engine, production date, DME faults, boost-control data and noise source using current BMW diagnostic information. Check VIN-specific coverage history with BMW, recognizing that the bulletin's time/mileage window may have expired. Do not replace a turbocharger, actuator or wastegate from this card without the required diagnosis.</x:v>
       </x:c>
       <x:c r="F308" s="9" t="n">
         <x:v>0</x:v>
@@ -10951,21 +11705,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="309" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="309" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A309" s="40" t="n">
         <x:v>308</x:v>
       </x:c>
       <x:c r="B309" s="9" t="str">
-        <x:v>bmw-z3-door-window-regulator-clip-mounting-tab-failure</x:v>
+        <x:v>bmw-z4-soft-top-hydraulic-2003</x:v>
       </x:c>
       <x:c r="C309" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
+        <x:v>2009-2016 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D309" s="9" t="str">
-        <x:v>Door Window Regulator Clip / Mounting Tab Failure</x:v>
+        <x:v>Retractable Hard Top Hydraulic Mechanism Failure</x:v>
       </x:c>
       <x:c r="E309" s="9" t="str">
-        <x:v>Replace the broken plastic regulator clips, or replace the regulator assembly if the cable or mechanism is also worn. If the welded mounting tab/anchor has torn from the door frame, it must be re-welded or reinforced before fitting a new regulator. Lubricate the window channels to reduce drag on the new parts.</x:v>
+        <x:v>Diagnose the leak location and replace the failed component. Common failure points are the main hydraulic cylinders (left and right), the hydraulic pump motor, and the flexible hoses. The hydraulic fluid should be flushed and replaced with BMW-approved CHF 11S fluid. A full system bleed is required after any repair.</x:v>
       </x:c>
       <x:c r="F309" s="9" t="n">
         <x:v>0</x:v>
@@ -10974,21 +11728,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="310" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="310" ht="1188" hidden="0" customHeight="1">
       <x:c r="A310" s="40" t="n">
         <x:v>309</x:v>
       </x:c>
       <x:c r="B310" s="9" t="str">
-        <x:v>bmw-z3-fuel-level-sender-failure-causing-erratic-dead-fuel-gauge</x:v>
+        <x:v>bmw-z4-vanos-solenoid-2003</x:v>
       </x:c>
       <x:c r="C310" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
+        <x:v>2003-2016 | BMW | Z4 | 2.5i, 3.0i, 3.0si, M40i, sDrive28i, sDrive30i, sDrive35i, sDrive35is | M54, N52, N54, N20</x:v>
       </x:c>
       <x:c r="D310" s="9" t="str">
-        <x:v>Fuel Level Sender Failure Causing Erratic or Dead Fuel Gauge</x:v>
+        <x:v>VANOS Solenoid &amp; System Failure - E85/E89 Z4 (All Engines)</x:v>
       </x:c>
       <x:c r="E310" s="9" t="str">
-        <x:v>Remove the access panel behind the seats and inspect the sender. A dirty or lightly worn ceramic/resistor plate can sometimes be cleaned, but a cracked plate or worn brushes requires replacing the sender unit (or the complete fuel-pump/sender carrier assembly). Also check the tank vent valve, as tank vacuum can deform the float arm. Confirm wiring/ground integrity before condemning the sender.</x:v>
+        <x:v>Replace VANOS solenoids - inexpensive and straightforward repair. M54 (E85 2003-2005): 2 solenoids required, BMW 11361707323 ($35-$65 each). N52 (E85 2006-2008 / E89 2009-2011 28i): 2 solenoids, BMW 11367585425 ($40-$70 each). N54 (E89 35i/35is): 2 solenoids, BMW 11367585425 ($40-$70 each). N20 (E89 sDrive28i 2012-2016): 2 solenoids, BMW 11367585425 ($40-$70 each). Labor: under 1 hour for experienced mechanic, 2-3 hours DIY. Replace all solenoids at once even if only one has failed - the others are same age and will fail soon. Also replace VANOS solenoid O-rings and sealing plates during service. Clean VANOS system with Beisan Systems VANOS cleaning procedure for best results.</x:v>
       </x:c>
       <x:c r="F310" s="9" t="n">
         <x:v>0</x:v>
@@ -10997,369 +11751,26 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="311" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A311" s="40" t="n">
+    <x:row r="311" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A311" s="42" t="n">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="B311" s="9" t="str">
-        <x:v>bmw-z3-hvac-blower-final-stage-resistor-failure</x:v>
-      </x:c>
-      <x:c r="C311" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D311" s="9" t="str">
-        <x:v>HVAC Blower Final Stage Resistor Failure (Fan Only Works on Max)</x:v>
-      </x:c>
-      <x:c r="E311" s="9" t="str">
-        <x:v>Replace the blower final stage resistor (A/C cars: part under the scuttle/cowl; non-A/C cars: behind the passenger footwell panel). If a new resistor does not restore all speeds, test the blower motor itself, which may also be worn. Inspect for corrosion/water intrusion at the cowl on A/C cars.</x:v>
-      </x:c>
-      <x:c r="F311" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G311" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="312" ht="1584" hidden="0" customHeight="1">
-      <x:c r="A312" s="40" t="n">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="B312" s="9" t="str">
-        <x:v>bmw-z3-rear-subframe-crack-1996</x:v>
-      </x:c>
-      <x:c r="C312" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D312" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracking</x:v>
-      </x:c>
-      <x:c r="E312" s="9" t="str">
-        <x:v>Inspect the trunk floor, differential mount area, and all rear subframe mounting points from above and below the car for spot-weld separation, torn sheet metal, and cracked seams; a dye penetrant test or removing trunk trim/seam sealer may be needed to reveal early damage. If cracking is present, the proper repair is to drop the rear axle carrier/subframe, weld and reinforce the damaged unibody mounting points and trunk floor with a reinforcement kit (commonly Randy Forbes-style dual-ear/differential mount reinforcement or equivalent), then reinstall with new subframe bushings, differential mount bushings, and perform a 4-wheel alignment. Minor early cracks may be repairable before major deformation, but advanced damage often requires fabrication and extensive welding by a chassis/body specialist; typical cost ranges from about $2,000-$3,500 for early reinforcement repairs and can exceed $4,000-$6,000 if the floor is torn or multiple mounting points are damaged.</x:v>
-      </x:c>
-      <x:c r="F312" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G312" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="313" ht="66" hidden="0" customHeight="1">
-      <x:c r="A313" s="40" t="n">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="B313" s="9" t="str">
-        <x:v>bmw-z3-rear-subframe-cracking-1996</x:v>
-      </x:c>
-      <x:c r="C313" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3 | M52, M54</x:v>
-      </x:c>
-      <x:c r="D313" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracks</x:v>
-      </x:c>
-      <x:c r="E313" s="9" t="str"/>
-      <x:c r="F313" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G313" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="314" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A314" s="40" t="n">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="B314" s="9" t="str">
-        <x:v>bmw-z3-valve-cover-gasket-oil-leak</x:v>
-      </x:c>
-      <x:c r="C314" s="9" t="str">
-        <x:v>1997-2002 | BMW | Z3 | 2.3, 2.5i, 2.8, 3.0i | M52 2.8, M52TU 2.5/2.8, M54 2.5/3.0</x:v>
-      </x:c>
-      <x:c r="D314" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak (M52/M54 6-Cylinder)</x:v>
-      </x:c>
-      <x:c r="E314" s="9" t="str">
-        <x:v>Replace the valve cover gasket, the spark-plug-well/grommet seals, and the cover bolt seals. On M54 engines also clean oil from the plug wells and replace any oil-contaminated coil boots/coils. Use the correct torque sequence to avoid re-leaking. Inspect the cover for warping or cracks while it is off.</x:v>
-      </x:c>
-      <x:c r="F314" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G314" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="315" ht="1293.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A315" s="40" t="n">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="B315" s="9" t="str">
-        <x:v>bmw-z3-vanos-seals-1999</x:v>
-      </x:c>
-      <x:c r="C315" s="9" t="str">
-        <x:v>1999-2002 | BMW | Z3 | M52, M54, S52</x:v>
-      </x:c>
-      <x:c r="D315" s="9" t="str">
-        <x:v>VANOS Seal Failure (M52/M54/S52)</x:v>
-      </x:c>
-      <x:c r="E315" s="9" t="str">
-        <x:v>Confirm the fault by checking for cold-start VANOS rattle, rough idle, hesitation, and scanning for cam timing or mixture-related fault codes; on M52TU/M54/S52 engines, inspect VANOS operation and rule out vacuum leaks before disassembly. Repair typically involves removing the valve cover and VANOS unit, replacing the internal piston seals/O-rings with updated Viton/Teflon seals, renewing the valve cover gasket and VANOS oil line sealing washers, and then re-timing the cams to BMW specifications if required. If the unit still rattles after resealing, the VANOS bearing/anti-rattle components or the complete VANOS assembly may need replacement. Typical cost is about $60-$150 in seals/gaskets for DIY repair, $300-$700 for an independent shop reseal, or $800-$1,500+ if a rebuilt/replacement VANOS unit is installed.</x:v>
-      </x:c>
-      <x:c r="F315" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G315" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="316" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A316" s="40" t="n">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="B316" s="9" t="str">
-        <x:v>bmw-z4-b58-coolant-tank-2019</x:v>
-      </x:c>
-      <x:c r="C316" s="9" t="str">
-        <x:v>2019-2026 | BMW | Z4 | B58</x:v>
-      </x:c>
-      <x:c r="D316" s="9" t="str">
-        <x:v>B58 Coolant Expansion Tank Cracking</x:v>
-      </x:c>
-      <x:c r="E316" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with an updated BMW part or aftermarket aluminum tank. Inspect the tank and cap regularly for signs of cracking, discoloration, or seepage. When replacing, also replace the cap and check all coolant hoses for brittleness. Flush and refill with BMW-approved coolant.</x:v>
-      </x:c>
-      <x:c r="F316" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G316" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="317" ht="1306.800048828125" hidden="0" customHeight="1">
-      <x:c r="A317" s="40" t="n">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="B317" s="9" t="str">
-        <x:v>bmw-z4-e85-convertible-top-hydraulic-2003</x:v>
-      </x:c>
-      <x:c r="C317" s="9" t="str">
-        <x:v>2003-2008 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D317" s="9" t="str">
-        <x:v>Convertible Top Hydraulic Pump Motor Failure - E85 Z4</x:v>
-      </x:c>
-      <x:c r="E317" s="9" t="str">
-        <x:v>Replace hydraulic pump motor assembly (BMW 54347193448 / supersedes 54347119633). OEM Genuine BMW pump: $800-$1,200. Aftermarket alternatives available on Amazon for $150-$300 but quality varies significantly. Dealer labor is $1,500-$2,500+ as BMW procedure requires full top removal. ZRoadster.org members have documented a motor relocation to the boot/trunk area which allows much easier future access. Hydraulic fluid: use Aral Vitamol ZHM or BMW 54340394395 hydraulic oil. PREVENTION: Clean drain holes annually, ensure rubber bungs are properly seated, and check for water intrusion in pump area at every service. Some owners have had success with pump motor rebuilds from roofmotors.co.uk ($300-$500) but quality of rebuilds varies.</x:v>
-      </x:c>
-      <x:c r="F317" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G317" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="318" ht="1135.199951171875" hidden="0" customHeight="1">
-      <x:c r="A318" s="40" t="n">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="B318" s="9" t="str">
-        <x:v>bmw-z4-e85-window-regulator-2003</x:v>
-      </x:c>
-      <x:c r="C318" s="9" t="str">
-        <x:v>2003-2008 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D318" s="9" t="str">
-        <x:v>Power Window Regulator Failure - E85 Z4</x:v>
-      </x:c>
-      <x:c r="E318" s="9" t="str">
-        <x:v>Option 1 (Budget): Window regulator repair kit - replacement cables and rollers for ~$18-$25 from eBay/Amazon (BWR974 for left/driver side). Requires removing door panel and threading new cables through existing regulator frame. DIY-friendly with Z4-forum.com guides. Option 2 (Recommended): Full window regulator replacement. Driver side: BMW 51337198909 ($180-$280 OEM, $80-$150 aftermarket). Passenger side: BMW 51337198910 ($180-$280 OEM, $80-$150 aftermarket). Labor: $200-$400 at independent shop, $500-$700+ at dealer. DIY: 2-3 hours with door panel removal guide from Pelican Parts. ZRoadster.org recommends full replacement over repair kit for long-term reliability.</x:v>
-      </x:c>
-      <x:c r="F318" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G318" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="319" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A319" s="40" t="n">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="B319" s="9" t="str">
-        <x:v>bmw-z4-electric-steering-rack-2003</x:v>
-      </x:c>
-      <x:c r="C319" s="9" t="str">
-        <x:v>2012-2012 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D319" s="9" t="str">
-        <x:v>2012 Z4 Electric Power-Steering Recall 12V-302</x:v>
-      </x:c>
-      <x:c r="E319" s="9" t="str">
-        <x:v>Check the VIN for an open 12V-302 campaign. If open, an authorized BMW dealer replaces the steering-assistance module free of charge. If the steering warning and audible alert occur, maintain control, reduce speed, stop safely and arrange dealer or roadside assistance; do not replace a steering rack from this card.</x:v>
-      </x:c>
-      <x:c r="F319" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G319" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="320" ht="633.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A320" s="40" t="n">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="B320" s="9" t="str">
-        <x:v>bmw-z4-electric-water-pump-2006</x:v>
-      </x:c>
-      <x:c r="C320" s="9" t="str">
-        <x:v>2012-2016 | BMW | Z4 | N20</x:v>
-      </x:c>
-      <x:c r="D320" s="9" t="str">
-        <x:v>2012-2016 Z4 sDrive28i Water-Pump Connector Recall 24V-608</x:v>
-      </x:c>
-      <x:c r="E320" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-608 campaign. If open, an authorized BMW dealer inspects the water pump and connector, replaces them if necessary, and installs the protective shield free of charge. If smoke appears from the engine compartment, stop safely, switch off the vehicle, have occupants exit, move away from traffic and call emergency or roadside assistance; do not order a pump from this card.</x:v>
-      </x:c>
-      <x:c r="F320" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G320" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="321" ht="1359.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A321" s="40" t="n">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="B321" s="9" t="str">
-        <x:v>bmw-z4-g29-b58-water-pump-2019</x:v>
-      </x:c>
-      <x:c r="C321" s="9" t="str">
-        <x:v>2019-2025 | BMW | Z4 | M40i, sDrive35i, sDrive35is | B48, B58</x:v>
-      </x:c>
-      <x:c r="D321" s="9" t="str">
-        <x:v>B48/B58 Electric Water Pump &amp; Thermostat Failure - G29 Z4</x:v>
-      </x:c>
-      <x:c r="E321" s="9" t="str">
-        <x:v>Preventative replacement recommended at 60,000 miles. Always replace water pump and thermostat together - they share labor overlap and frequently fail concurrently. B48 sDrive30i: Water pump BMW 11518632586 ($300-$450), Thermostat BMW 11538685978 ($100-$150). B58 M40i: Water pump BMW 11518650986 ($350-$500), Thermostat BMW 11538685978 ($100-$150). Mishimoto offers performance water pump alternatives for B58 with improved impeller design. Replace 3 O-rings between thermostat and pump housing, plus 2 O-rings on coolant tube to head. Must replace water pump mounting bolts (torque-to-yield). Labor: 3-4 hours. FCP Euro lifetime warranty kits available. Also inspect plastic cylinder head coolant outlet adapter - known to shear off causing massive coolant leak.</x:v>
-      </x:c>
-      <x:c r="F321" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G321" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="322" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A322" s="40" t="n">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B322" s="9" t="str">
-        <x:v>bmw-z4-n54-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C322" s="9" t="str">
-        <x:v>2009-2011 | BMW | Z4 | M40i, sDrive35i, sDrive35is | N54</x:v>
-      </x:c>
-      <x:c r="D322" s="9" t="str">
-        <x:v>N54 High Pressure Fuel Pump (HPFP) Failure - E89 Z4 sDrive35i/35is</x:v>
-      </x:c>
-      <x:c r="E322" s="9" t="str">
-        <x:v>Replace HPFP with latest revision Genuine BMW unit. The pump went through multiple revisions - ONLY install the latest version. Part number evolution: Original -&gt; 13517592881 (Index 10, TSB fix) -&gt; 13517616170 (latest revision, most reliable). Genuine BMW 13517616170 is the definitive fix ($350-$550 for pump). Replacement is straightforward DIY (1-2 hours) with basic tools. Also available as complete kit from FCP Euro with lifetime warranty. BMW extended warranty coverage to 10 years/120,000 miles under customer care package for original owners - check VIN eligibility. Replace low-pressure fuel sensor at same time (13537537319) as it may have been damaged by pressure fluctuations ($35-$55).</x:v>
-      </x:c>
-      <x:c r="F322" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G322" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="323" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A323" s="40" t="n">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="B323" s="9" t="str">
-        <x:v>bmw-z4-n54-wastegate-rattle-2009</x:v>
-      </x:c>
-      <x:c r="C323" s="9" t="str">
-        <x:v>2009-2010 | BMW | Z4 | N54</x:v>
-      </x:c>
-      <x:c r="D323" s="9" t="str">
-        <x:v>2009-2010 Z4 sDrive35i N54 Wastegate Diagnosis</x:v>
-      </x:c>
-      <x:c r="E323" s="9" t="str">
-        <x:v>Confirm the VIN, engine, production date, DME faults, boost-control data and noise source using current BMW diagnostic information. Check VIN-specific coverage history with BMW, recognizing that the bulletin's time/mileage window may have expired. Do not replace a turbocharger, actuator or wastegate from this card without the required diagnosis.</x:v>
-      </x:c>
-      <x:c r="F323" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G323" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="324" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A324" s="40" t="n">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="B324" s="9" t="str">
-        <x:v>bmw-z4-soft-top-hydraulic-2003</x:v>
-      </x:c>
-      <x:c r="C324" s="9" t="str">
-        <x:v>2009-2016 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D324" s="9" t="str">
-        <x:v>Retractable Hard Top Hydraulic Mechanism Failure</x:v>
-      </x:c>
-      <x:c r="E324" s="9" t="str">
-        <x:v>Diagnose the leak location and replace the failed component. Common failure points are the main hydraulic cylinders (left and right), the hydraulic pump motor, and the flexible hoses. The hydraulic fluid should be flushed and replaced with BMW-approved CHF 11S fluid. A full system bleed is required after any repair.</x:v>
-      </x:c>
-      <x:c r="F324" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G324" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="325" ht="1188" hidden="0" customHeight="1">
-      <x:c r="A325" s="40" t="n">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="B325" s="9" t="str">
-        <x:v>bmw-z4-vanos-solenoid-2003</x:v>
-      </x:c>
-      <x:c r="C325" s="9" t="str">
-        <x:v>2003-2016 | BMW | Z4 | 2.5i, 3.0i, 3.0si, M40i, sDrive28i, sDrive30i, sDrive35i, sDrive35is | M54, N52, N54, N20</x:v>
-      </x:c>
-      <x:c r="D325" s="9" t="str">
-        <x:v>VANOS Solenoid &amp; System Failure - E85/E89 Z4 (All Engines)</x:v>
-      </x:c>
-      <x:c r="E325" s="9" t="str">
-        <x:v>Replace VANOS solenoids - inexpensive and straightforward repair. M54 (E85 2003-2005): 2 solenoids required, BMW 11361707323 ($35-$65 each). N52 (E85 2006-2008 / E89 2009-2011 28i): 2 solenoids, BMW 11367585425 ($40-$70 each). N54 (E89 35i/35is): 2 solenoids, BMW 11367585425 ($40-$70 each). N20 (E89 sDrive28i 2012-2016): 2 solenoids, BMW 11367585425 ($40-$70 each). Labor: under 1 hour for experienced mechanic, 2-3 hours DIY. Replace all solenoids at once even if only one has failed - the others are same age and will fail soon. Also replace VANOS solenoid O-rings and sealing plates during service. Clean VANOS system with Beisan Systems VANOS cleaning procedure for best results.</x:v>
-      </x:c>
-      <x:c r="F325" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G325" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="326" ht="554.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A326" s="42" t="n">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="B326" s="43" t="str">
+      <x:c r="B311" s="43" t="str">
         <x:v>bmw-z8-soft-top-mechanism-2000</x:v>
       </x:c>
-      <x:c r="C326" s="43" t="str">
+      <x:c r="C311" s="43" t="str">
         <x:v>2000-2003 | BMW | Z8</x:v>
       </x:c>
-      <x:c r="D326" s="43" t="str">
+      <x:c r="D311" s="43" t="str">
         <x:v>Power Soft Top Hydraulic System and Cable Failure</x:v>
       </x:c>
-      <x:c r="E326" s="43" t="str">
+      <x:c r="E311" s="43" t="str">
         <x:v>Rebuild the hydraulic cylinders with new seals rather than replacing ($200 vs $2,000+). Inspect and replace frayed cables. Adjust or replace the microswitch sensors at the windshield header latch. Lubricate the top mechanism pivot points with silicone grease annually. Store the car with the top up to reduce stress on the hydraulic system.</x:v>
       </x:c>
-      <x:c r="F326" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G326" s="44" t="str">
+      <x:c r="F311" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G311" s="44" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>

--- a/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
+++ b/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf98f4412e065401a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="Rfb1c639612d94e0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R2849b7576b5e4946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R386551f8f4aa482b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R281e99e7ac6442ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="Rb9d83947515940a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R57a2076393cb4f26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Re3ed6452063147e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>310</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>105</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +540,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -4590,28 +4590,1526 @@
       </x:c>
     </x:row>
     <x:row r="106" ht="132" hidden="0" customHeight="1">
-      <x:c r="A106" s="42" t="str"/>
-      <x:c r="B106" s="43" t="str"/>
-      <x:c r="C106" s="43" t="str"/>
-      <x:c r="D106" s="43" t="str"/>
-      <x:c r="E106" s="43" t="str"/>
-      <x:c r="F106" s="43" t="str"/>
-      <x:c r="G106" s="43" t="str"/>
-      <x:c r="H106" s="43" t="str">
+      <x:c r="A106" s="40" t="str"/>
+      <x:c r="B106" s="9" t="str"/>
+      <x:c r="C106" s="9" t="str"/>
+      <x:c r="D106" s="9" t="str"/>
+      <x:c r="E106" s="9" t="str"/>
+      <x:c r="F106" s="9" t="str"/>
+      <x:c r="G106" s="9" t="str"/>
+      <x:c r="H106" s="9" t="str">
         <x:v>BMW dealer locator</x:v>
       </x:c>
-      <x:c r="I106" s="43" t="str">
+      <x:c r="I106" s="9" t="str">
         <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
       </x:c>
-      <x:c r="J106" s="43" t="str">
+      <x:c r="J106" s="9" t="str">
         <x:v>2016-2022 G11/G12 NBT Evo/MGU-era diagnosis, software and coding</x:v>
       </x:c>
-      <x:c r="K106" s="43" t="str">
+      <x:c r="K106" s="9" t="str">
         <x:v>diagnostic/programming service</x:v>
       </x:c>
-      <x:c r="L106" s="43" t="str"/>
-      <x:c r="M106" s="43" t="str"/>
-      <x:c r="N106" s="44" t="str"/>
+      <x:c r="L106" s="9" t="str"/>
+      <x:c r="M106" s="9" t="str"/>
+      <x:c r="N106" s="41" t="str"/>
+    </x:row>
+    <x:row r="107" ht="739.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A107" s="40" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B107" s="9" t="str">
+        <x:v>bmw-7-series-panoramic-roof-2016</x:v>
+      </x:c>
+      <x:c r="C107" s="9" t="str">
+        <x:v>2016-2025 | BMW | 7 Series</x:v>
+      </x:c>
+      <x:c r="D107" s="9" t="str">
+        <x:v>Panoramic Glass Roof Cracking and Drain Blockage</x:v>
+      </x:c>
+      <x:c r="E107" s="9" t="str">
+        <x:v>For cracked glass: the entire panoramic roof panel must be replaced. Check if covered under BMW's glass warranty (some cracks without impact evidence are covered as manufacturing defects). For drain blockage: clear all four drain channels (two front, two rear) using compressed air or a flexible drain snake. This should be done as preventive maintenance every 12 months. If the headliner is water-damaged, it must be removed and replaced.</x:v>
+      </x:c>
+      <x:c r="F107" s="9" t="str">
+        <x:v>Impact/manufacturing inspection for cracked glass; exact roof panel by VIN; drain-path diagnosis/cleaning; headliner only if confirmed damaged</x:v>
+      </x:c>
+      <x:c r="G107" s="9" t="str">
+        <x:v>DIAGNOSIS/GLASS-SERVICE FIRST</x:v>
+      </x:c>
+      <x:c r="H107" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I107" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J107" s="9" t="str">
+        <x:v>2016-2025 7 Series roof-glass, drain and warranty diagnosis</x:v>
+      </x:c>
+      <x:c r="K107" s="9" t="str">
+        <x:v>glass/roof service</x:v>
+      </x:c>
+      <x:c r="L107" s="9" t="str"/>
+      <x:c r="M107" s="9" t="str">
+        <x:v>The row lacks body/roof option, panel position and part number, and warranty depends on inspection rather than model year alone.</x:v>
+      </x:c>
+      <x:c r="N107" s="41" t="str">
+        <x:v>Do not tell users to blow compressed air through drains without the model procedure; split cracked glass, blocked drains and water-damaged trim.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A108" s="40" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B108" s="9" t="str">
+        <x:v>bmw-7series-air-suspension-2002</x:v>
+      </x:c>
+      <x:c r="C108" s="9" t="str">
+        <x:v>2002-2023 | BMW | 7 Series</x:v>
+      </x:c>
+      <x:c r="D108" s="9" t="str">
+        <x:v>Air Suspension Compressor &amp; Strut Failure - All Generations</x:v>
+      </x:c>
+      <x:c r="E108" s="9" t="str">
+        <x:v>Replace failed air struts or compressor. Individual air struts can be replaced, but often multiple fail together. Compressor replacement is 3-5 hours labor. Some owners convert to conventional coil springs ($1,500-2,500) to avoid repeat air suspension repairs. Air strut replacement requires specialized tools and calibration. OEM BMW parts are extremely expensive; some aftermarket options (Arnott) available at lower cost but with mixed reliability.</x:v>
+      </x:c>
+      <x:c r="F108" s="9" t="str">
+        <x:v>Generation-specific leak and ride-height diagnosis; exact failed strut, compressor, valve block, line or sensor; calibration; coil conversion only where engineered and legal</x:v>
+      </x:c>
+      <x:c r="G108" s="9" t="str">
+        <x:v>SOURCE SPLIT REQUIRED / NO UNIVERSAL PART</x:v>
+      </x:c>
+      <x:c r="H108" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I108" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J108" s="9" t="str">
+        <x:v>2002-2023 7 Series chassis/VIN-specific air-suspension diagnosis</x:v>
+      </x:c>
+      <x:c r="K108" s="9" t="str">
+        <x:v>diagnostic/calibration service</x:v>
+      </x:c>
+      <x:c r="L108" s="9" t="str"/>
+      <x:c r="M108" s="9" t="str">
+        <x:v>Twenty-one model years span E65/E66, F01/F02 and G11/G12 systems; one strut, compressor or conversion kit cannot fit the row.</x:v>
+      </x:c>
+      <x:c r="N108" s="41" t="str">
+        <x:v>Split by chassis, axle, side, suspension option and diagnosed component. Remove universal multi-failure and price claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="818.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A109" s="40" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B109" s="9" t="str">
+        <x:v>bmw-7series-electrical-e65-2002</x:v>
+      </x:c>
+      <x:c r="C109" s="9" t="str">
+        <x:v>2002-2008 | BMW | 7 Series</x:v>
+      </x:c>
+      <x:c r="D109" s="9" t="str">
+        <x:v>Widespread Electrical Issues - E65/E66 745i/750i/760i</x:v>
+      </x:c>
+      <x:c r="E109" s="9" t="str">
+        <x:v>Diagnose specific module failures with BMW diagnostic software. Common fixes: CCC module replacement ($1,500-2,500), window regulator replacement ($300-600 per window), battery registration after replacement, and parasitic draw diagnosis. Many electrical issues require dealer-level diagnostics. Some problems can only be resolved with module replacements. E65/E66 ownership requires deep pockets or strong DIY skills. Avoid buying E65 without thorough pre-purchase inspection and warranty.</x:v>
+      </x:c>
+      <x:c r="F109" s="9" t="str">
+        <x:v>Module/network and parasitic-draw diagnosis; condition-specific CCC, window regulator, battery/registration or other exact repair</x:v>
+      </x:c>
+      <x:c r="G109" s="9" t="str">
+        <x:v>DIAGNOSIS FIRST / NO GENERIC ELECTRICAL CART</x:v>
+      </x:c>
+      <x:c r="H109" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I109" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J109" s="9" t="str">
+        <x:v>2002-2008 E65/E66 electrical/network diagnosis and programming</x:v>
+      </x:c>
+      <x:c r="K109" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L109" s="9" t="str"/>
+      <x:c r="M109" s="9" t="str">
+        <x:v>The row combines unrelated modules, windows and battery conditions without a specific symptom, position, option or part number.</x:v>
+      </x:c>
+      <x:c r="N109" s="41" t="str">
+        <x:v>Split each known issue by component and symptom; remove ownership advice and unsupported blanket repair pricing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A110" s="40" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B110" s="9" t="str">
+        <x:v>bmw-7series-hpfp-2009</x:v>
+      </x:c>
+      <x:c r="C110" s="9" t="str">
+        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL | N63</x:v>
+      </x:c>
+      <x:c r="D110" s="9" t="str">
+        <x:v>High-Pressure Fuel Pump Failure - F01/F02 750i/750Li (N63)</x:v>
+      </x:c>
+      <x:c r="E110" s="9" t="str">
+        <x:v>Replace high-pressure fuel pump(s). BMW recommends replacing both HPFPs together on N63 engines. Flush fuel system if metal contamination is present. Use only OEM BMW or Bosch fuel pumps - aftermarket pumps have poor reliability. Labor is 4-6 hours. Some owners report multiple HPFP failures over vehicle life. N63 Customer Care Package may cover HPFP repairs on eligible VINs. Consider extended warranty for N63-powered cars.</x:v>
+      </x:c>
+      <x:c r="F110" s="9" t="str">
+        <x:v>Measured low/high fuel-pressure diagnosis; N63A versus N63TU split; one or both pumps only as diagnosis directs; contamination inspection; required seals/adapters</x:v>
+      </x:c>
+      <x:c r="G110" s="9" t="str">
+        <x:v>ENGINE-GENERATION SPLIT PRODUCT APPROVAL</x:v>
+      </x:c>
+      <x:c r="H110" s="9" t="str">
+        <x:v>Bosch HPFP 13517595339 for early N63A</x:v>
+      </x:c>
+      <x:c r="I110" s="9" t="str">
+        <x:v>https://www.bimmerworld.com/Intake-Fuel/Fuel-Filters/BMW-Hgh-Presion-Pump-13517595339.html</x:v>
+      </x:c>
+      <x:c r="J110" s="9" t="str">
+        <x:v>2009-2012 F01/F02 750i/750Li N63A only; sold individually, two used per car; in stock</x:v>
+      </x:c>
+      <x:c r="K110" s="9" t="str">
+        <x:v>early N63A high-pressure fuel pump</x:v>
+      </x:c>
+      <x:c r="L110" s="9" t="str"/>
+      <x:c r="M110" s="9" t="str">
+        <x:v>Two live in-stock Bosch listings provide explicit 2009-2012 N63A and 2013-2015 N63TU 750i splits, part numbers and quantity notes.</x:v>
+      </x:c>
+      <x:c r="N110" s="41" t="str">
+        <x:v>Add 750Li/xDrive trims, engine generation and production date. Do not promise Customer Care Package coverage or automatically replace both pumps without measured diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A111" s="40" t="str"/>
+      <x:c r="B111" s="9" t="str"/>
+      <x:c r="C111" s="9" t="str"/>
+      <x:c r="D111" s="9" t="str"/>
+      <x:c r="E111" s="9" t="str"/>
+      <x:c r="F111" s="9" t="str"/>
+      <x:c r="G111" s="9" t="str"/>
+      <x:c r="H111" s="9" t="str">
+        <x:v>Bosch HPFP 13518604232 for N63TU</x:v>
+      </x:c>
+      <x:c r="I111" s="9" t="str">
+        <x:v>https://www.bimmerworld.com/Intake-Fuel/Fuel-Filters/High-Pressure-Fuel-Pump-O-On-Engine-N63-V8.html</x:v>
+      </x:c>
+      <x:c r="J111" s="9" t="str">
+        <x:v>2013-2015 F01/F02 750i/750Li N63TU; sold individually; pre-12/2013 cars require listed wiring adapter</x:v>
+      </x:c>
+      <x:c r="K111" s="9" t="str">
+        <x:v>N63TU high-pressure fuel pump</x:v>
+      </x:c>
+      <x:c r="L111" s="9" t="str"/>
+      <x:c r="M111" s="9" t="str"/>
+      <x:c r="N111" s="41" t="str"/>
+    </x:row>
+    <x:row r="112" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A112" s="40" t="str"/>
+      <x:c r="B112" s="9" t="str"/>
+      <x:c r="C112" s="9" t="str"/>
+      <x:c r="D112" s="9" t="str"/>
+      <x:c r="E112" s="9" t="str"/>
+      <x:c r="F112" s="9" t="str"/>
+      <x:c r="G112" s="9" t="str"/>
+      <x:c r="H112" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I112" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J112" s="9" t="str">
+        <x:v>Fuel-pressure, bank and contamination diagnosis plus VIN history</x:v>
+      </x:c>
+      <x:c r="K112" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L112" s="9" t="str"/>
+      <x:c r="M112" s="9" t="str"/>
+      <x:c r="N112" s="41" t="str"/>
+    </x:row>
+    <x:row r="113" ht="950.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A113" s="40" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B113" s="9" t="str">
+        <x:v>bmw-7series-n63-turbo-2009</x:v>
+      </x:c>
+      <x:c r="C113" s="9" t="str">
+        <x:v>2013-2015 | BMW | 7 Series | N63TU1</x:v>
+      </x:c>
+      <x:c r="D113" s="9" t="str">
+        <x:v>N63TU1 750i Oil-Consumption and Turbo-Leak Diagnosis</x:v>
+      </x:c>
+      <x:c r="E113" s="9" t="str">
+        <x:v>Confirm the exact chassis, N63TU1 engine, production date, engine serial number, VIN and current eligibility, then follow BMW electronic oil-level measurement and leak-inspection procedures. Repair only the component supported by the documented test result; replace turbochargers only when leakage is confirmed under the current instructions. Do not promise historical settlement coverage. ShowMeTheParts returned six exact 2014 750i/750i xDrive turbo oil-return-line fitments, but catalog fitment does not prove a leak, oil-consumption cause or repair role, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F113" s="9" t="str">
+        <x:v>N63TU1/chassis/production/engine-serial/VIN confirmation; electronic oil-level and leak tests; turbocharger only if leakage is documented</x:v>
+      </x:c>
+      <x:c r="G113" s="9" t="str">
+        <x:v>DIAGNOSIS FIRST / NO RETAIL TURBO</x:v>
+      </x:c>
+      <x:c r="H113" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I113" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J113" s="9" t="str">
+        <x:v>2013-2015 750i/750Li N63TU1 oil-consumption and turbo-leak diagnosis</x:v>
+      </x:c>
+      <x:c r="K113" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L113" s="9" t="str"/>
+      <x:c r="M113" s="9" t="str">
+        <x:v>Exact oil-return-line fitment does not establish a leak or prove that a turbocharger is the oil-consumption cause.</x:v>
+      </x:c>
+      <x:c r="N113" s="41" t="str">
+        <x:v>Correct issue ID/year and add the actual 750i/750Li trims; no turbo, line or scanner link before documented tests.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="739.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A114" s="40" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B114" s="9" t="str">
+        <x:v>bmw-7series-n63-valvetronic-2009</x:v>
+      </x:c>
+      <x:c r="C114" s="9" t="str">
+        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL</x:v>
+      </x:c>
+      <x:c r="D114" s="9" t="str">
+        <x:v>N63 Valvetronic Motor Failure - F01/F02 750i/750Li</x:v>
+      </x:c>
+      <x:c r="E114" s="9" t="str">
+        <x:v>Replace Valvetronic eccentric shaft motor(s). Often both motors need replacement since wear is similar. Clean carbon buildup from Valvetronic mechanism during repair. N63 Customer Care Package may cover this repair on eligible VINs. Labor is 6-10 hours. Some shops recommend replacing Valvetronic motors preventively at 80,000 miles to avoid being stranded. Extended warranty highly recommended for N63-powered 7 Series.</x:v>
+      </x:c>
+      <x:c r="F114" s="9" t="str">
+        <x:v>N63 generation/bank/VIN and fault diagnosis; eccentric-shaft motor only when confirmed; inspect mechanism and wiring; program/teach-in as required</x:v>
+      </x:c>
+      <x:c r="G114" s="9" t="str">
+        <x:v>DIAGNOSIS FIRST / ENGINE SPLIT REQUIRED</x:v>
+      </x:c>
+      <x:c r="H114" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I114" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J114" s="9" t="str">
+        <x:v>2009-2015 F01/F02 750i/750Li Valvetronic diagnosis and teach-in</x:v>
+      </x:c>
+      <x:c r="K114" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L114" s="9" t="str"/>
+      <x:c r="M114" s="9" t="str">
+        <x:v>The row spans N63A and N63TU hardware and supplies no bank, part number or confirmed fault; replacing both motors preventively is not justified.</x:v>
+      </x:c>
+      <x:c r="N114" s="41" t="str">
+        <x:v>Split by engine generation, bank and production date; remove unsupported preventive replacement and historical-coverage claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="739.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A115" s="40" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B115" s="9" t="str">
+        <x:v>bmw-8-series-adaptive-suspension-2019</x:v>
+      </x:c>
+      <x:c r="C115" s="9" t="str">
+        <x:v>2019-2025 | BMW | 8 Series</x:v>
+      </x:c>
+      <x:c r="D115" s="9" t="str">
+        <x:v>Adaptive Suspension Damper Malfunction</x:v>
+      </x:c>
+      <x:c r="E115" s="9" t="str">
+        <x:v>Replace the failed adaptive damper. BMW's diagnostic system can identify which specific damper has failed through the suspension control module fault memory. The damper must be coded to the vehicle after installation. Replace dampers in pairs (both fronts or both rears) if the vehicle has over 60,000 miles, as the remaining original damper is likely near end of life. Bilstein offers OE-equivalent adaptive dampers at lower cost than BMW parts.</x:v>
+      </x:c>
+      <x:c r="F115" s="9" t="str">
+        <x:v>Fault-memory and physical diagnosis; exact chassis/option/axle/side adaptive damper; programming/calibration only where required; pair replacement based on condition</x:v>
+      </x:c>
+      <x:c r="G115" s="9" t="str">
+        <x:v>POSITION/OPTION SPLIT REQUIRED</x:v>
+      </x:c>
+      <x:c r="H115" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I115" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J115" s="9" t="str">
+        <x:v>2019-2025 G14/G15/G16/F91/F92/F93 adaptive-suspension diagnosis and coding</x:v>
+      </x:c>
+      <x:c r="K115" s="9" t="str">
+        <x:v>diagnostic/calibration service</x:v>
+      </x:c>
+      <x:c r="L115" s="9" t="str"/>
+      <x:c r="M115" s="9" t="str">
+        <x:v>The row has no trim, suspension option, axle, side or damper part number; 8 Series and M8 applications cannot share a universal Bilstein link.</x:v>
+      </x:c>
+      <x:c r="N115" s="41" t="str">
+        <x:v>Split by chassis, trim, suspension option, front/rear and left/right. Do not mandate pair replacement or coding for every damper without procedure support.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A116" s="40" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B116" s="9" t="str">
+        <x:v>bmw-8-series-b58-coolant-loss-2019</x:v>
+      </x:c>
+      <x:c r="C116" s="9" t="str">
+        <x:v>2019-2025 | BMW | 8 Series | B58</x:v>
+      </x:c>
+      <x:c r="D116" s="9" t="str">
+        <x:v>B58 Engine Coolant Loss from Expansion Tank and Water Pump</x:v>
+      </x:c>
+      <x:c r="E116" s="9" t="str">
+        <x:v>Replace the coolant expansion tank with BMW's latest revision. Inspect the electric water pump and all quick-connect coolant fittings for leaks. Pressure test the entire cooling system after repairs. Replace the expansion tank cap as a weak cap allows premature boiling. Use only BMW-approved blue coolant — mixing coolant types causes gel formation.</x:v>
+      </x:c>
+      <x:c r="F116" s="9" t="str">
+        <x:v>Pressure-test and locate leak; production-specific 840i expansion tank/cap only if failed; inspect mechanical pump and quick-connect fittings; correct VIN-specified coolant</x:v>
+      </x:c>
+      <x:c r="G116" s="9" t="str">
+        <x:v>YEAR-SPLIT PARTIAL PRODUCT APPROVAL</x:v>
+      </x:c>
+      <x:c r="H116" s="9" t="str">
+        <x:v>Genuine BMW expansion tank 17139846642</x:v>
+      </x:c>
+      <x:c r="I116" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/parts/bmw-expansion_tank-17139846642.html</x:v>
+      </x:c>
+      <x:c r="J116" s="9" t="str">
+        <x:v>2021-2025 BMW 840i/840i xDrive 3.0L only; select VIN to confirm; ships in 1-3 business days</x:v>
+      </x:c>
+      <x:c r="K116" s="9" t="str">
+        <x:v>coolant expansion tank</x:v>
+      </x:c>
+      <x:c r="L116" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/parts-list/2020-bmw-840i-coupe_g15/cooling_exhaust_system/expansion_tank.html</x:v>
+      </x:c>
+      <x:c r="M116" s="9" t="str">
+        <x:v>The live part page explicitly fits 2021-2025 840i, while 2019-2020 catalog data shows a different production split and is held for VIN confirmation.</x:v>
+      </x:c>
+      <x:c r="N116" s="41" t="str">
+        <x:v>The B58 uses a mechanical coolant pump, not the electric-pump wording implied by the row. Do not replace tank/cap without locating the leak or prescribe blue coolant across all production dates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A117" s="40" t="str"/>
+      <x:c r="B117" s="9" t="str"/>
+      <x:c r="C117" s="9" t="str"/>
+      <x:c r="D117" s="9" t="str"/>
+      <x:c r="E117" s="9" t="str"/>
+      <x:c r="F117" s="9" t="str"/>
+      <x:c r="G117" s="9" t="str"/>
+      <x:c r="H117" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I117" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J117" s="9" t="str">
+        <x:v>2019-2020 production split and cooling-system pressure diagnosis</x:v>
+      </x:c>
+      <x:c r="K117" s="9" t="str">
+        <x:v>diagnostic/fitment service</x:v>
+      </x:c>
+      <x:c r="L117" s="9" t="str"/>
+      <x:c r="M117" s="9" t="str"/>
+      <x:c r="N117" s="41" t="str"/>
+    </x:row>
+    <x:row r="118" ht="660" hidden="0" customHeight="1">
+      <x:c r="A118" s="40" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B118" s="9" t="str">
+        <x:v>bmw-8-series-n63-oil-consumption-m850i-2019</x:v>
+      </x:c>
+      <x:c r="C118" s="9" t="str">
+        <x:v>2019-2025 | BMW | 8 Series | N63TU4, N63</x:v>
+      </x:c>
+      <x:c r="D118" s="9" t="str">
+        <x:v>N63/S63 V8 Oil Consumption in M850i</x:v>
+      </x:c>
+      <x:c r="E118" s="9" t="str">
+        <x:v>BMW considers up to 1 quart per 1,200 miles as within specification for the N63 family. For excessive consumption beyond that, inspect turbo oil return lines for restriction (causes oil to push past turbo seals), check the crankcase ventilation system, and evaluate valve stem seal condition. The N63TU4 benefits from updated seals and coatings, so consumption rarely reaches the extreme levels of earlier N63 variants.</x:v>
+      </x:c>
+      <x:c r="F118" s="9" t="str">
+        <x:v>Controlled oil-consumption measurement; external/turbo-return/crankcase-ventilation checks; valve-seal diagnosis only if supported</x:v>
+      </x:c>
+      <x:c r="G118" s="9" t="str">
+        <x:v>DIAGNOSIS FIRST / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H118" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I118" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J118" s="9" t="str">
+        <x:v>2019-2025 M850i N63 oil-consumption measurement and leak diagnosis</x:v>
+      </x:c>
+      <x:c r="K118" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L118" s="9" t="str"/>
+      <x:c r="M118" s="9" t="str">
+        <x:v>The How to Fix names several possible causes but no confirmed failed component, part number or exact engine-generation split.</x:v>
+      </x:c>
+      <x:c r="N118" s="41" t="str">
+        <x:v>Verify the current BMW oil-consumption specification and engine designation by VIN; do not present one generic rate or preselect turbo lines, ventilation parts or seals.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="844.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A119" s="40" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B119" s="9" t="str">
+        <x:v>bmw-8series-ibs-failure-2020</x:v>
+      </x:c>
+      <x:c r="C119" s="9" t="str">
+        <x:v>2019-2021 | BMW | 8 Series</x:v>
+      </x:c>
+      <x:c r="D119" s="9" t="str">
+        <x:v>2019-2021 8 Series Integrated Brake Recall 21V-062</x:v>
+      </x:c>
+      <x:c r="E119" s="9" t="str">
+        <x:v>Check the VIN for an open 21V-062 campaign and current remedy status with BMW/NHTSA. If the vehicle is included, have an authorized BMW center perform the recall repair at no charge. If brake warnings appear or pedal effort changes, slow safely, avoid hard braking and contact BMW or roadside assistance for direction. ShowMeTheParts resolved exact 2020 840i, 840i xDrive and M850i xDrive brake-hydraulics contexts but returned no brake-booster candidate; recall eligibility and remedy remain dealer-only.</x:v>
+      </x:c>
+      <x:c r="F119" s="9" t="str">
+        <x:v>VIN check for recall 21V-062; authorized integrated-brake remedy; immediate service direction for brake warnings or changed pedal effort</x:v>
+      </x:c>
+      <x:c r="G119" s="9" t="str">
+        <x:v>RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H119" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I119" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J119" s="9" t="str">
+        <x:v>2019-2021 8 Series; VIN required for 21V-062</x:v>
+      </x:c>
+      <x:c r="K119" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L119" s="9" t="str"/>
+      <x:c r="M119" s="9" t="str">
+        <x:v>The corrected source is a VIN-controlled safety recall and reports no defensible retail brake-booster candidate.</x:v>
+      </x:c>
+      <x:c r="N119" s="41" t="str">
+        <x:v>Rename the issue away from 'IBS failure'; IBS commonly means Intelligent Battery Sensor and is misleading here.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="66" hidden="0" customHeight="1">
+      <x:c r="A120" s="40" t="str"/>
+      <x:c r="B120" s="9" t="str"/>
+      <x:c r="C120" s="9" t="str"/>
+      <x:c r="D120" s="9" t="str"/>
+      <x:c r="E120" s="9" t="str"/>
+      <x:c r="F120" s="9" t="str"/>
+      <x:c r="G120" s="9" t="str"/>
+      <x:c r="H120" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I120" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J120" s="9" t="str">
+        <x:v>US VIN confirmation and recall details</x:v>
+      </x:c>
+      <x:c r="K120" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L120" s="9" t="str"/>
+      <x:c r="M120" s="9" t="str"/>
+      <x:c r="N120" s="41" t="str"/>
+    </x:row>
+    <x:row r="121" ht="897.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A121" s="40" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B121" s="9" t="str">
+        <x:v>bmw-8series-n63tu3-timing-chain-2019</x:v>
+      </x:c>
+      <x:c r="C121" s="9" t="str">
+        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i</x:v>
+      </x:c>
+      <x:c r="D121" s="9" t="str">
+        <x:v>N63TU3 Timing Chain Guide Wear (M850i)</x:v>
+      </x:c>
+      <x:c r="E121" s="9" t="str">
+        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain guides, tensioners, and chain at 80,000-100,000 miles ($4,000-$7,500). Turner Motorsport timing chain kit 11317594899KT includes all necessary components. Individual parts: chain guides 11147574373, 11317574397, 11317592850, 11317592877; chain 11317598263. If chain has already skipped: engine damage likely requires $15,000-$25,000 engine replacement. CRITICAL: If you hear cold-start rattling, do NOT drive - tow to shop immediately to prevent catastrophic engine failure.</x:v>
+      </x:c>
+      <x:c r="F121" s="9" t="str">
+        <x:v>Confirm actual M850i N63 generation and timing fault; BMW test plan; VIN-specific chain/guide/tensioner parts only after diagnosis</x:v>
+      </x:c>
+      <x:c r="G121" s="9" t="str">
+        <x:v>CONTENT/FITMENT ERROR / REJECT NAMED KIT</x:v>
+      </x:c>
+      <x:c r="H121" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I121" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J121" s="9" t="str">
+        <x:v>2019-2024 M850i N63 timing-system diagnosis and VIN-specific parts</x:v>
+      </x:c>
+      <x:c r="K121" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L121" s="9" t="str">
+        <x:v>https://www.turnermotorsport.com/p-5553284-timing-chain-kit-n63-44l/</x:v>
+      </x:c>
+      <x:c r="M121" s="9" t="str">
+        <x:v>Turner says 11317594899KT has no vehicle applications; the detailed fitment found elsewhere is for older N63TU/N63N applications, not the M850i N63TU3 row.</x:v>
+      </x:c>
+      <x:c r="N121" s="41" t="str">
+        <x:v>Remove impossible E31 trims (840Ci/850Ci/850CSi), the universal preventive interval and catastrophic cost claims. Do not use 11317594899KT for M850i without VIN/ETK confirmation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="871.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A122" s="40" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B122" s="9" t="str">
+        <x:v>bmw-8series-n63tu3-valve-stem-seals-2019</x:v>
+      </x:c>
+      <x:c r="C122" s="9" t="str">
+        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i | N63TU3</x:v>
+      </x:c>
+      <x:c r="D122" s="9" t="str">
+        <x:v>N63TU3 Valve Stem Seal Failure &amp; Oil Consumption (M850i)</x:v>
+      </x:c>
+      <x:c r="E122" s="9" t="str">
+        <x:v>Replace valve stem seals ($3,500-$10,000 due to labor-intensive hot-V access). Use OEM Victor Reinz seals for durability. Replace spark plugs (Bosch 12120037581) when performing seal replacement. AGA Tools N63 Valve Stem Seal Kit AGA-N63-VSK-K ($500-800) provides specialized tooling for this job. Check VIN eligibility for N63 class action settlement which may cover repair costs. PREVENTIVE: Use quality synthetic oil (BMW LL-01 spec), change every 5,000-7,500 miles, and monitor oil level every 500-1,000 miles on M850i models.</x:v>
+      </x:c>
+      <x:c r="F122" s="9" t="str">
+        <x:v>Confirm M850i N63 generation and oil-consumption cause; engine-generation-specific seals/tooling; spark plugs only when repair procedure or condition calls for them</x:v>
+      </x:c>
+      <x:c r="G122" s="9" t="str">
+        <x:v>CONTENT/FITMENT ERROR / NO APPROVED RETAIL TOOL</x:v>
+      </x:c>
+      <x:c r="H122" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I122" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J122" s="9" t="str">
+        <x:v>2019-2024 M850i oil-consumption and valve-seal diagnosis</x:v>
+      </x:c>
+      <x:c r="K122" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L122" s="9" t="str">
+        <x:v>https://agatools.com/collections/valve-tools/products/aga-n63-vsk-k
+https://www.turnermotorsport.com/p-49265628-n63tu-valve-stem-seal-tool-kit/</x:v>
+      </x:c>
+      <x:c r="M122" s="9" t="str">
+        <x:v>AGA-N63-VSK-K is explicitly for N63/S63 and the N63TU tool listing has no vehicle applications; neither verifies N63TU3 M850i fitment.</x:v>
+      </x:c>
+      <x:c r="N122" s="41" t="str">
+        <x:v>Remove impossible E31 trims, use the actual M850i engine designation, and do not promise class-action coverage or link older N63/N63TU tools.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="897.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A123" s="40" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B123" s="9" t="str">
+        <x:v>bmw-8series-premature-tire-wear-2019</x:v>
+      </x:c>
+      <x:c r="C123" s="9" t="str">
+        <x:v>2019-2024 | BMW | 8 Series</x:v>
+      </x:c>
+      <x:c r="D123" s="9" t="str">
+        <x:v>Premature Tire Wear (All 8 Series &amp; M8)</x:v>
+      </x:c>
+      <x:c r="E123" s="9" t="str">
+        <x:v>Get a performance alignment reducing rear camber from factory -2.0 degrees to -1.5 degrees ($150-$300 at alignment shop). This significantly extends rear tire life from 9,000-15,000 miles to 20,000-25,000 miles while maintaining good street handling. Rotate front tires side-to-side every 5,000 miles (staggered setup prevents front-to-rear rotation). Replace rear tires in pairs when worn. COST SAVINGS: Alignment adjustment ($150-300) saves $1,200-2,400 per year in premature tire replacement on expensive performance tires ($300-600 each).</x:v>
+      </x:c>
+      <x:c r="F123" s="9" t="str">
+        <x:v>Inspect wear pattern, pressure and suspension; alignment within safe BMW/tire specifications; exact-size/load/speed-rated tires in axle pairs where required</x:v>
+      </x:c>
+      <x:c r="G123" s="9" t="str">
+        <x:v>ALIGNMENT/INSTALLER SERVICE APPROVAL</x:v>
+      </x:c>
+      <x:c r="H123" s="9" t="str">
+        <x:v>Tire Rack recommended installer locator</x:v>
+      </x:c>
+      <x:c r="I123" s="9" t="str">
+        <x:v>https://www.tirerack.com/installer/Installer.jsp</x:v>
+      </x:c>
+      <x:c r="J123" s="9" t="str">
+        <x:v>ZIP-based US tire installation route; select exact vehicle and tire product before checkout</x:v>
+      </x:c>
+      <x:c r="K123" s="9" t="str">
+        <x:v>tire installer locator</x:v>
+      </x:c>
+      <x:c r="L123" s="9" t="str"/>
+      <x:c r="M123" s="9" t="str">
+        <x:v>A live ZIP-based installer route is valid, but the row lacks wheel size, tire size, load/speed rating and trim needed for a tire product link.</x:v>
+      </x:c>
+      <x:c r="N123" s="41" t="str">
+        <x:v>Do not prescribe one rear-camber target or tire-life savings to every 8 Series/M8. Split staggered, square, rear-steer and M applications.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A124" s="40" t="str"/>
+      <x:c r="B124" s="9" t="str"/>
+      <x:c r="C124" s="9" t="str"/>
+      <x:c r="D124" s="9" t="str"/>
+      <x:c r="E124" s="9" t="str"/>
+      <x:c r="F124" s="9" t="str"/>
+      <x:c r="G124" s="9" t="str"/>
+      <x:c r="H124" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I124" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J124" s="9" t="str">
+        <x:v>8 Series/M8 alignment and suspension inspection</x:v>
+      </x:c>
+      <x:c r="K124" s="9" t="str">
+        <x:v>alignment service</x:v>
+      </x:c>
+      <x:c r="L124" s="9" t="str"/>
+      <x:c r="M124" s="9" t="str"/>
+      <x:c r="N124" s="41" t="str"/>
+    </x:row>
+    <x:row r="125" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A125" s="40" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B125" s="9" t="str">
+        <x:v>bmw-8series-zf-8hp-mechatronic-2019</x:v>
+      </x:c>
+      <x:c r="C125" s="9" t="str">
+        <x:v>2023-2023 | BMW | 8 Series</x:v>
+      </x:c>
+      <x:c r="D125" s="9" t="str">
+        <x:v>2023 8 Series ITCU Recall 23V-821</x:v>
+      </x:c>
+      <x:c r="E125" s="9" t="str">
+        <x:v>Check the VIN for an open 23V-821 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW recall remedy, which replaces the transmission mechatronics module. Do not buy a sleeve kit or change fluid as a substitute for the recall. ShowMeTheParts resolved exact 2023 840i, 840i xDrive and M850i xDrive models but exposed no transmission category or ITCU candidate, and recall repair remains dealer-only.</x:v>
+      </x:c>
+      <x:c r="F125" s="9" t="str">
+        <x:v>VIN check for recall 23V-821; authorized replacement of the transmission mechatronics module when included</x:v>
+      </x:c>
+      <x:c r="G125" s="9" t="str">
+        <x:v>RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H125" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I125" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J125" s="9" t="str">
+        <x:v>2023 840i/840i xDrive/M850i xDrive; VIN required for 23V-821</x:v>
+      </x:c>
+      <x:c r="K125" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L125" s="9" t="str"/>
+      <x:c r="M125" s="9" t="str">
+        <x:v>The source explicitly rejects sleeve kits and fluid service as substitutes for the dealer-only ITCU recall remedy.</x:v>
+      </x:c>
+      <x:c r="N125" s="41" t="str">
+        <x:v>Keep the issue titled as an ITCU recall, not a generic ZF 8HP mechatronic wear problem.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A126" s="40" t="str"/>
+      <x:c r="B126" s="9" t="str"/>
+      <x:c r="C126" s="9" t="str"/>
+      <x:c r="D126" s="9" t="str"/>
+      <x:c r="E126" s="9" t="str"/>
+      <x:c r="F126" s="9" t="str"/>
+      <x:c r="G126" s="9" t="str"/>
+      <x:c r="H126" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I126" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J126" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K126" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L126" s="9" t="str"/>
+      <x:c r="M126" s="9" t="str"/>
+      <x:c r="N126" s="41" t="str"/>
+    </x:row>
+    <x:row r="127" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A127" s="40" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B127" s="9" t="str">
+        <x:v>bmw-driveshaft-flex-disc-e90</x:v>
+      </x:c>
+      <x:c r="C127" s="9" t="str">
+        <x:v>2011-2011 | BMW | 3 Series | N55, N54T, M57Y</x:v>
+      </x:c>
+      <x:c r="D127" s="9" t="str">
+        <x:v>Certain 2011 3 Series Need a Rear-Driveshaft Flex-Disc Recall Check</x:v>
+      </x:c>
+      <x:c r="E127" s="9" t="str">
+        <x:v>Check the VIN for open recall 17V-067 before authorizing driveline parts. BMW instructs dealers to inspect the installed disc revision index and replace it only when required by the campaign. ShowMeTheParts exposed the exact 2011 335i DRIVE SHAFT category but returned no flex-disc candidate; no commerce link is approved for this recall repair.</x:v>
+      </x:c>
+      <x:c r="F127" s="9" t="str">
+        <x:v>VIN recall check; installed rear-flex-disc revision inspection; dealer replacement only when campaign requires</x:v>
+      </x:c>
+      <x:c r="G127" s="9" t="str">
+        <x:v>RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H127" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I127" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J127" s="9" t="str">
+        <x:v>Certain 2011 3 Series; VIN required for 17V-067</x:v>
+      </x:c>
+      <x:c r="K127" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L127" s="9" t="str"/>
+      <x:c r="M127" s="9" t="str">
+        <x:v>BMW requires inspection of the installed revision and the catalog returned no exact flex-disc candidate; the free recall remedy controls.</x:v>
+      </x:c>
+      <x:c r="N127" s="41" t="str">
+        <x:v>Add the exact affected body/trim/drivetrain scope from the recall before any future retail flex-disc link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A128" s="40" t="str"/>
+      <x:c r="B128" s="9" t="str"/>
+      <x:c r="C128" s="9" t="str"/>
+      <x:c r="D128" s="9" t="str"/>
+      <x:c r="E128" s="9" t="str"/>
+      <x:c r="F128" s="9" t="str"/>
+      <x:c r="G128" s="9" t="str"/>
+      <x:c r="H128" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I128" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J128" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K128" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L128" s="9" t="str"/>
+      <x:c r="M128" s="9" t="str"/>
+      <x:c r="N128" s="41" t="str"/>
+    </x:row>
+    <x:row r="129" ht="871.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A129" s="40" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B129" s="9" t="str">
+        <x:v>bmw-i3-12v-battery-drain-2014</x:v>
+      </x:c>
+      <x:c r="C129" s="9" t="str">
+        <x:v>2014-2021 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D129" s="9" t="str">
+        <x:v>i3 12V Discharge Warning: ISTA Software-First Diagnosis</x:v>
+      </x:c>
+      <x:c r="E129" s="9" t="str">
+        <x:v>Read the Check Control Message and fault memory, run BMW ISTA Energy Diagnosis and test the 12V battery before replacing anything. For the Controller condition, BMW says not to replace the Controller; program the vehicle when the measured I-level and diagnostic result meet SIB 61 05 20. For the early REx condition, follow SIB 61 39 14. Replace and register a 12V battery only if separate testing proves it failed. ShowMeTheParts resolved the exact 2014 i3 model but exposed no battery category or defensible 12V candidate, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F129" s="9" t="str">
+        <x:v>Check Control/fault-memory review; ISTA Energy Diagnosis and 12V test; software-first Controller remedy; battery only if separately failed and then register it</x:v>
+      </x:c>
+      <x:c r="G129" s="9" t="str">
+        <x:v>SOFTWARE/DIAGNOSIS FIRST / NO BATTERY LINK</x:v>
+      </x:c>
+      <x:c r="H129" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I129" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J129" s="9" t="str">
+        <x:v>2014-2021 i3 ISTA Energy Diagnosis, programming and battery registration</x:v>
+      </x:c>
+      <x:c r="K129" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L129" s="9" t="str"/>
+      <x:c r="M129" s="9" t="str">
+        <x:v>The corrected source says not to replace the Controller and found no defensible battery candidate for this specific software-first condition.</x:v>
+      </x:c>
+      <x:c r="N129" s="41" t="str">
+        <x:v>Do not turn the discharge warning into an automatic battery or scanner sale; link a battery only after failed testing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="488.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A130" s="40" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B130" s="9" t="str">
+        <x:v>bmw-i3-12v-parasitic-drain-2014</x:v>
+      </x:c>
+      <x:c r="C130" s="9" t="str">
+        <x:v>2014-2021 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D130" s="9" t="str">
+        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
+      </x:c>
+      <x:c r="E130" s="9" t="str">
+        <x:v>Replace the 12V AGM battery with a fresh unit (OEM or high-quality AGM). Code the new battery using ISTA or BimmerCode to register it with the IBS (Intelligent Battery Sensor). Check for software updates that address module sleep behavior. Some owners install a battery tender for long-term parking.</x:v>
+      </x:c>
+      <x:c r="F130" s="9" t="str">
+        <x:v>Parasitic-draw/software diagnosis and 12V load test; AUX18L AGM battery only if failed; battery registration after replacement</x:v>
+      </x:c>
+      <x:c r="G130" s="9" t="str">
+        <x:v>DIAGNOSIS-GATED BATTERY APPROVAL</x:v>
+      </x:c>
+      <x:c r="H130" s="9" t="str">
+        <x:v>East Penn/Deka AUX18L AGM i3 battery</x:v>
+      </x:c>
+      <x:c r="I130" s="9" t="str">
+        <x:v>https://remybattery.com/start-stop-aux18l-auxiliary-battery.html</x:v>
+      </x:c>
+      <x:c r="J130" s="9" t="str">
+        <x:v>2014-2021 BMW i3; live page identifies AUX18L as the OEM factory-installed i3 battery; confirm terminals and current stock</x:v>
+      </x:c>
+      <x:c r="K130" s="9" t="str">
+        <x:v>12V AGM auxiliary battery</x:v>
+      </x:c>
+      <x:c r="L130" s="9" t="str"/>
+      <x:c r="M130" s="9" t="str">
+        <x:v>The live AUX18L product is buyable and explicitly identifies BMW i3 OEM fitment, but battery replacement does not diagnose parasitic drain.</x:v>
+      </x:c>
+      <x:c r="N130" s="41" t="str">
+        <x:v>Do not tell users BimmerCode necessarily performs battery registration; name the supported registration tool/procedure only after verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A131" s="40" t="str"/>
+      <x:c r="B131" s="9" t="str"/>
+      <x:c r="C131" s="9" t="str"/>
+      <x:c r="D131" s="9" t="str"/>
+      <x:c r="E131" s="9" t="str"/>
+      <x:c r="F131" s="9" t="str"/>
+      <x:c r="G131" s="9" t="str"/>
+      <x:c r="H131" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I131" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J131" s="9" t="str">
+        <x:v>Parasitic-draw diagnosis, software check and battery registration</x:v>
+      </x:c>
+      <x:c r="K131" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L131" s="9" t="str"/>
+      <x:c r="M131" s="9" t="str"/>
+      <x:c r="N131" s="41" t="str"/>
+    </x:row>
+    <x:row r="132" ht="1108.800048828125" hidden="0" customHeight="1">
+      <x:c r="A132" s="40" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B132" s="9" t="str">
+        <x:v>bmw-i3-ac-compressor-black-death-2014</x:v>
+      </x:c>
+      <x:c r="C132" s="9" t="str">
+        <x:v>2014-2021 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D132" s="9" t="str">
+        <x:v>Electric A/C Compressor Catastrophic Failure ("Black Death") - All I01</x:v>
+      </x:c>
+      <x:c r="E132" s="9" t="str">
+        <x:v>If caught early (noise but still functioning), replace compressor before catastrophic failure. Latest OEM compressor: BMW 64529496107 (supersedes 64529320855, 64529343806, 64529347662, 64529364868). FCP Euro price ~$1,756. If metal contamination has occurred, entire system including battery cooling channels must be replaced ($10,600+). MUST use POE (Polyolester) anti-electrostatic compressor oil - standard PAG oil will destroy EV compressors. Independent AC shops that understand EV compressors can save 60-80% vs dealer. RYC Automotive offers remanufactured compressor (RYC-i3-01) as budget option. Aftermarket Nissens condenser ($152) available vs OEM ($581 via FCP Euro).</x:v>
+      </x:c>
+      <x:c r="F132" s="9" t="str">
+        <x:v>HV isolation and refrigerant/oil contamination diagnosis; exact electric compressor; contaminated circuit and battery-cooling components only as the HV-EV procedure requires</x:v>
+      </x:c>
+      <x:c r="G132" s="9" t="str">
+        <x:v>HV-DIAGNOSIS-GATED COMPRESSOR APPROVAL</x:v>
+      </x:c>
+      <x:c r="H132" s="9" t="str">
+        <x:v>Genuine BMW i3 electric A/C compressor 64529496107</x:v>
+      </x:c>
+      <x:c r="I132" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/products/bmw-ac-compressor-genuine-bmw-64529496107</x:v>
+      </x:c>
+      <x:c r="J132" s="9" t="str">
+        <x:v>BMW i3/i3s; available; confirm VIN, supersession, refrigerant and specified electrically insulating oil</x:v>
+      </x:c>
+      <x:c r="K132" s="9" t="str">
+        <x:v>electric A/C compressor</x:v>
+      </x:c>
+      <x:c r="L132" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/BMW-parts/i3/AC-Compressor/</x:v>
+      </x:c>
+      <x:c r="M132" s="9" t="str">
+        <x:v>FCP Euro's live i3 compressor catalog lists genuine 64529496107 as available for i3/i3s. It does not justify buying the compressor before contamination/HV diagnosis.</x:v>
+      </x:c>
+      <x:c r="N132" s="41" t="str">
+        <x:v>Remove unverified fixed prices and 'entire system' wording; specify the exact BMW refrigerant oil by procedure and never substitute PAG oil.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="132" hidden="0" customHeight="1">
+      <x:c r="A133" s="40" t="str"/>
+      <x:c r="B133" s="9" t="str"/>
+      <x:c r="C133" s="9" t="str"/>
+      <x:c r="D133" s="9" t="str"/>
+      <x:c r="E133" s="9" t="str"/>
+      <x:c r="F133" s="9" t="str"/>
+      <x:c r="G133" s="9" t="str"/>
+      <x:c r="H133" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I133" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J133" s="9" t="str">
+        <x:v>HV-safe A/C diagnosis, evacuation, contamination assessment and repair</x:v>
+      </x:c>
+      <x:c r="K133" s="9" t="str">
+        <x:v>HV A/C service</x:v>
+      </x:c>
+      <x:c r="L133" s="9" t="str"/>
+      <x:c r="M133" s="9" t="str"/>
+      <x:c r="N133" s="41" t="str"/>
+    </x:row>
+    <x:row r="134" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A134" s="40" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B134" s="9" t="str">
+        <x:v>bmw-i3-ac-compressor-failure-2014</x:v>
+      </x:c>
+      <x:c r="C134" s="9" t="str">
+        <x:v>2014-2021 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D134" s="9" t="str">
+        <x:v>Electric AC Compressor Failure</x:v>
+      </x:c>
+      <x:c r="E134" s="9" t="str">
+        <x:v>Replace the electric AC compressor assembly. This requires a certified HV-trained technician to safely de-energize the high-voltage system before working on the compressor. The system must be evacuated, the compressor replaced, and the system recharged with the correct amount of R-1234yf refrigerant.</x:v>
+      </x:c>
+      <x:c r="F134" s="9" t="str">
+        <x:v>HV-safe A/C diagnosis and de-energization; exact electric compressor; system evacuation/recharge with VIN-specified refrigerant and oil</x:v>
+      </x:c>
+      <x:c r="G134" s="9" t="str">
+        <x:v>HV-DIAGNOSIS-GATED COMPRESSOR APPROVAL</x:v>
+      </x:c>
+      <x:c r="H134" s="9" t="str">
+        <x:v>Genuine BMW i3 electric A/C compressor 64529496107</x:v>
+      </x:c>
+      <x:c r="I134" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/products/bmw-ac-compressor-genuine-bmw-64529496107</x:v>
+      </x:c>
+      <x:c r="J134" s="9" t="str">
+        <x:v>BMW i3/i3s; confirm VIN and supersession before ordering</x:v>
+      </x:c>
+      <x:c r="K134" s="9" t="str">
+        <x:v>electric A/C compressor</x:v>
+      </x:c>
+      <x:c r="L134" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/BMW-parts/i3/AC-Compressor/</x:v>
+      </x:c>
+      <x:c r="M134" s="9" t="str">
+        <x:v>The exact live compressor is valid, while installation and charging require trained HV/A-C service.</x:v>
+      </x:c>
+      <x:c r="N134" s="41" t="str">
+        <x:v>Do not assume R-1234yf across every 2014-2021 build without the under-hood label/VIN procedure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A135" s="40" t="str"/>
+      <x:c r="B135" s="9" t="str"/>
+      <x:c r="C135" s="9" t="str"/>
+      <x:c r="D135" s="9" t="str"/>
+      <x:c r="E135" s="9" t="str"/>
+      <x:c r="F135" s="9" t="str"/>
+      <x:c r="G135" s="9" t="str"/>
+      <x:c r="H135" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I135" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J135" s="9" t="str">
+        <x:v>Certified HV A/C service and exact refrigerant/oil verification</x:v>
+      </x:c>
+      <x:c r="K135" s="9" t="str">
+        <x:v>HV A/C service</x:v>
+      </x:c>
+      <x:c r="L135" s="9" t="str"/>
+      <x:c r="M135" s="9" t="str"/>
+      <x:c r="N135" s="41" t="str"/>
+    </x:row>
+    <x:row r="136" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A136" s="40" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B136" s="9" t="str">
+        <x:v>bmw-i3-battery-degradation-2014</x:v>
+      </x:c>
+      <x:c r="C136" s="9" t="str">
+        <x:v>2019-2021 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D136" s="9" t="str">
+        <x:v>2019-2021 i3 High-Voltage Battery Cell Recall 22V-683</x:v>
+      </x:c>
+      <x:c r="E136" s="9" t="str">
+        <x:v>Check the VIN for an open 22V-683 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy; BMW instructs replacement of the affected battery cell module. Do not buy a battery module or use capacity estimates as a substitute for the VIN recall check. This high-voltage, recall-only path intentionally carries no commerce.</x:v>
+      </x:c>
+      <x:c r="F136" s="9" t="str">
+        <x:v>VIN check for recall 22V-683; authorized replacement of affected high-voltage battery cell module</x:v>
+      </x:c>
+      <x:c r="G136" s="9" t="str">
+        <x:v>HIGH-VOLTAGE RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H136" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I136" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J136" s="9" t="str">
+        <x:v>2019-2021 i3; VIN required for 22V-683</x:v>
+      </x:c>
+      <x:c r="K136" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L136" s="9" t="str"/>
+      <x:c r="M136" s="9" t="str">
+        <x:v>This is a VIN-controlled high-voltage safety recall; retail battery modules and capacity estimates are not substitutes.</x:v>
+      </x:c>
+      <x:c r="N136" s="41" t="str">
+        <x:v>Rename the issue to the cell-module recall rather than generic battery degradation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A137" s="40" t="str"/>
+      <x:c r="B137" s="9" t="str"/>
+      <x:c r="C137" s="9" t="str"/>
+      <x:c r="D137" s="9" t="str"/>
+      <x:c r="E137" s="9" t="str"/>
+      <x:c r="F137" s="9" t="str"/>
+      <x:c r="G137" s="9" t="str"/>
+      <x:c r="H137" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I137" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J137" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K137" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L137" s="9" t="str"/>
+      <x:c r="M137" s="9" t="str"/>
+      <x:c r="N137" s="41" t="str"/>
+    </x:row>
+    <x:row r="138" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A138" s="40" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B138" s="9" t="str">
+        <x:v>bmw-i3-connectivity-module-2014</x:v>
+      </x:c>
+      <x:c r="C138" s="9" t="str">
+        <x:v>2014-2021 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D138" s="9" t="str">
+        <x:v>i3 ConnectedDrive 3G Sunset: VIN-Specific Eligibility Path</x:v>
+      </x:c>
+      <x:c r="E138" s="9" t="str">
+        <x:v>Check the VIN in BMW AIR/DCSnet or My Garage before choosing a remedy. An early 3G vehicle marked non-eligible cannot be restored by buying the frozen card’s used TCB part. A later campaign-eligible 4G vehicle should receive the BMW programming action that writes the IMS configuration. Confirm current service availability with BMW ConnectedDrive support; do not order a telematics module from model year alone.</x:v>
+      </x:c>
+      <x:c r="F138" s="9" t="str">
+        <x:v>VIN/AIR/My Garage eligibility check; campaign programming for eligible 4G vehicle; current ConnectedDrive service confirmation; no used TCB by model year</x:v>
+      </x:c>
+      <x:c r="G138" s="9" t="str">
+        <x:v>VIN/SERVICE ELIGIBILITY ONLY</x:v>
+      </x:c>
+      <x:c r="H138" s="9" t="str">
+        <x:v>My BMW Garage</x:v>
+      </x:c>
+      <x:c r="I138" s="9" t="str">
+        <x:v>https://mygarage.bmwusa.com/</x:v>
+      </x:c>
+      <x:c r="J138" s="9" t="str">
+        <x:v>VIN-linked vehicle/campaign and service information</x:v>
+      </x:c>
+      <x:c r="K138" s="9" t="str">
+        <x:v>official eligibility route</x:v>
+      </x:c>
+      <x:c r="L138" s="9" t="str"/>
+      <x:c r="M138" s="9" t="str">
+        <x:v>The source explicitly says an early non-eligible 3G vehicle cannot be restored by buying the frozen card's used TCB part.</x:v>
+      </x:c>
+      <x:c r="N138" s="41" t="str">
+        <x:v>Do not promise a hardware upgrade or service restoration from model year alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A139" s="40" t="str"/>
+      <x:c r="B139" s="9" t="str"/>
+      <x:c r="C139" s="9" t="str"/>
+      <x:c r="D139" s="9" t="str"/>
+      <x:c r="E139" s="9" t="str"/>
+      <x:c r="F139" s="9" t="str"/>
+      <x:c r="G139" s="9" t="str"/>
+      <x:c r="H139" s="9" t="str">
+        <x:v>BMW contact and ConnectedDrive support</x:v>
+      </x:c>
+      <x:c r="I139" s="9" t="str">
+        <x:v>https://www.bmwusa.com/contact-us.html</x:v>
+      </x:c>
+      <x:c r="J139" s="9" t="str">
+        <x:v>Confirm current ConnectedDrive availability and support options</x:v>
+      </x:c>
+      <x:c r="K139" s="9" t="str">
+        <x:v>official support</x:v>
+      </x:c>
+      <x:c r="L139" s="9" t="str"/>
+      <x:c r="M139" s="9" t="str"/>
+      <x:c r="N139" s="41" t="str"/>
+    </x:row>
+    <x:row r="140" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A140" s="40" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B140" s="9" t="str">
+        <x:v>bmw-i3-dc-fast-charge-latch-2014</x:v>
+      </x:c>
+      <x:c r="C140" s="9" t="str">
+        <x:v>2014-2014 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D140" s="9" t="str">
+        <x:v>2014 i3 Level 2 Charging Delay: KLE Campaign Check</x:v>
+      </x:c>
+      <x:c r="E140" s="9" t="str">
+        <x:v>Check the VIN for the KLE service action and read charging and 12V faults with BMW diagnostics. For an open campaign, follow BMW’s KLE replacement and programming procedure. If the 12V battery is discharged, SIB 61 01 15 describes a controlled Level 2 recovery/programming path and says parts replacement does not solve its remaining intermittent delay. Do not drill or lubricate the charge port or buy a latch actuator based on this card.</x:v>
+      </x:c>
+      <x:c r="F140" s="9" t="str">
+        <x:v>VIN KLE action check; charging and 12V diagnostics; campaign KLE replacement/programming where open; controlled Level 2 recovery where applicable</x:v>
+      </x:c>
+      <x:c r="G140" s="9" t="str">
+        <x:v>CAMPAIGN/PROGRAMMING FIRST / NO LATCH PART</x:v>
+      </x:c>
+      <x:c r="H140" s="9" t="str">
+        <x:v>BMW recall and campaign lookup</x:v>
+      </x:c>
+      <x:c r="I140" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J140" s="9" t="str">
+        <x:v>2014 i3 VIN/campaign check</x:v>
+      </x:c>
+      <x:c r="K140" s="9" t="str">
+        <x:v>official campaign route</x:v>
+      </x:c>
+      <x:c r="L140" s="9" t="str"/>
+      <x:c r="M140" s="9" t="str">
+        <x:v>The corrected source says this is a KLE/charging-delay path, not a DC fast-charge latch failure, and explicitly rejects buying a latch actuator.</x:v>
+      </x:c>
+      <x:c r="N140" s="41" t="str">
+        <x:v>Rename the issue to the Level 2/KLE campaign condition and remove drilling/lubrication advice.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A141" s="40" t="str"/>
+      <x:c r="B141" s="9" t="str"/>
+      <x:c r="C141" s="9" t="str"/>
+      <x:c r="D141" s="9" t="str"/>
+      <x:c r="E141" s="9" t="str"/>
+      <x:c r="F141" s="9" t="str"/>
+      <x:c r="G141" s="9" t="str"/>
+      <x:c r="H141" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I141" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J141" s="9" t="str">
+        <x:v>KLE/charging diagnosis and programming</x:v>
+      </x:c>
+      <x:c r="K141" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L141" s="9" t="str"/>
+      <x:c r="M141" s="9" t="str"/>
+      <x:c r="N141" s="41" t="str"/>
+    </x:row>
+    <x:row r="142" ht="739.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A142" s="40" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B142" s="9" t="str">
+        <x:v>bmw-i3-hvac-heater-2014</x:v>
+      </x:c>
+      <x:c r="C142" s="9" t="str">
+        <x:v>2014-2021 | BMW | i3</x:v>
+      </x:c>
+      <x:c r="D142" s="9" t="str">
+        <x:v>Electric Heater &amp; HVAC System Failures - Range Impact</x:v>
+      </x:c>
+      <x:c r="E142" s="9" t="str">
+        <x:v>Electric heater element replacement ($800-1,500). Heat pump compressor replacement uses same compressor as AC system (64529496107) at $1,756-4,000. Blower motor replacement $300-600. HVAC control module reprogramming or replacement $500-1,000. Pre-conditioning the cabin while plugged in (before driving) reduces range impact significantly. Some owners install aftermarket heated seats and steering wheel to reduce HVAC load.</x:v>
+      </x:c>
+      <x:c r="F142" s="9" t="str">
+        <x:v>HVAC fault and HV isolation diagnosis; exact heater, compressor, blower or control/software repair only as confirmed</x:v>
+      </x:c>
+      <x:c r="G142" s="9" t="str">
+        <x:v>COMPONENT-SPLIT PARTIAL APPROVAL</x:v>
+      </x:c>
+      <x:c r="H142" s="9" t="str">
+        <x:v>Genuine BMW i3 electric A/C compressor 64529496107</x:v>
+      </x:c>
+      <x:c r="I142" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/products/bmw-ac-compressor-genuine-bmw-64529496107</x:v>
+      </x:c>
+      <x:c r="J142" s="9" t="str">
+        <x:v>i3/i3s compressor circuit only after diagnosis; not a heater or blower part</x:v>
+      </x:c>
+      <x:c r="K142" s="9" t="str">
+        <x:v>electric HVAC compressor</x:v>
+      </x:c>
+      <x:c r="L142" s="9" t="str">
+        <x:v>https://www.fcpeuro.com/BMW-parts/i3/AC-Compressor/</x:v>
+      </x:c>
+      <x:c r="M142" s="9" t="str">
+        <x:v>The How to Fix names several unrelated HVAC components; only the exact compressor has a verified live i3/i3s product page.</x:v>
+      </x:c>
+      <x:c r="N142" s="41" t="str">
+        <x:v>Split heater element, heat-pump compressor, blower motor and control software into separate issues; remove fixed price claims.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A143" s="40" t="str"/>
+      <x:c r="B143" s="9" t="str"/>
+      <x:c r="C143" s="9" t="str"/>
+      <x:c r="D143" s="9" t="str"/>
+      <x:c r="E143" s="9" t="str"/>
+      <x:c r="F143" s="9" t="str"/>
+      <x:c r="G143" s="9" t="str"/>
+      <x:c r="H143" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I143" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J143" s="9" t="str">
+        <x:v>HVAC/HV diagnosis, software, heater and blower identification</x:v>
+      </x:c>
+      <x:c r="K143" s="9" t="str">
+        <x:v>HV HVAC service</x:v>
+      </x:c>
+      <x:c r="L143" s="9" t="str"/>
+      <x:c r="M143" s="9" t="str"/>
+      <x:c r="N143" s="41" t="str"/>
+    </x:row>
+    <x:row r="144" ht="726" hidden="0" customHeight="1">
+      <x:c r="A144" s="40" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B144" s="9" t="str">
+        <x:v>bmw-i3-rex-engine-issues-2014</x:v>
+      </x:c>
+      <x:c r="C144" s="9" t="str">
+        <x:v>2014-2017 | BMW | i3 | W20 647cc</x:v>
+      </x:c>
+      <x:c r="D144" s="9" t="str">
+        <x:v>2014-2017 i3 REx Fuel-Vent-Line Recall 17V-088</x:v>
+      </x:c>
+      <x:c r="E144" s="9" t="str">
+        <x:v>Check the VIN for an open 17V-088 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy: inspect the fuel tank vent line, replace it if necessary and install the separating clip. Do not substitute a fuel-pump relay, injector cleaner or generic engine parts for the recall. ShowMeTheParts lists 2014 i3 fuel-system categories, but recall inclusion and remedy are VIN/dealer controlled, so no commerce link is approved.</x:v>
+      </x:c>
+      <x:c r="F144" s="9" t="str">
+        <x:v>VIN check for recall 17V-088; inspect fuel-tank vent line; replace line if required and install separating clip</x:v>
+      </x:c>
+      <x:c r="G144" s="9" t="str">
+        <x:v>RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H144" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I144" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J144" s="9" t="str">
+        <x:v>2014-2017 i3 REx; VIN required for 17V-088</x:v>
+      </x:c>
+      <x:c r="K144" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L144" s="9" t="str"/>
+      <x:c r="M144" s="9" t="str">
+        <x:v>The recall remedy is dealer/VIN controlled and the source explicitly rejects generic engine products as substitutes.</x:v>
+      </x:c>
+      <x:c r="N144" s="41" t="str">
+        <x:v>Rename the issue to the fuel-vent-line recall rather than generic REx engine issues.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A145" s="40" t="str"/>
+      <x:c r="B145" s="9" t="str"/>
+      <x:c r="C145" s="9" t="str"/>
+      <x:c r="D145" s="9" t="str"/>
+      <x:c r="E145" s="9" t="str"/>
+      <x:c r="F145" s="9" t="str"/>
+      <x:c r="G145" s="9" t="str"/>
+      <x:c r="H145" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I145" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J145" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K145" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L145" s="9" t="str"/>
+      <x:c r="M145" s="9" t="str"/>
+      <x:c r="N145" s="41" t="str"/>
+    </x:row>
+    <x:row r="146" ht="871.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A146" s="40" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B146" s="9" t="str">
+        <x:v>bmw-i3-rex-stale-fuel-2014</x:v>
+      </x:c>
+      <x:c r="C146" s="9" t="str">
+        <x:v>2014-2021 | BMW | i3 | W20 647cc</x:v>
+      </x:c>
+      <x:c r="D146" s="9" t="str">
+        <x:v>Range Extender Stale Fuel &amp; Engine Problems - I01 REx Only</x:v>
+      </x:c>
+      <x:c r="E146" s="9" t="str">
+        <x:v>Preventive: Run the REx at least every 6 weeks for a minimum of 10-13 minutes to burn off moisture. Use fuel stabilizer (Sta-Bil) if vehicle sits for extended periods. Keep fuel tank above half to reduce vapor space. For fuel pump relay failure (most common), replace relay ($20-30). For injector issues, professional cleaning or replacement required. For coil failures, replace ignition coils. Maintain regular oil changes with BMW-approved oil despite low mileage. Some owners run premium fuel exclusively to reduce varnish formation.</x:v>
+      </x:c>
+      <x:c r="F146" s="9" t="str">
+        <x:v>REx operating/storage practice; fuel stabilizer for extended storage; diagnose fuel-pressure, injector or ignition faults; exact relay/coils only when confirmed</x:v>
+      </x:c>
+      <x:c r="G146" s="9" t="str">
+        <x:v>PREVENTIVE PRODUCT + DIAGNOSIS-GATED REX PARTS</x:v>
+      </x:c>
+      <x:c r="H146" s="9" t="str">
+        <x:v>STA-BIL Storage Fuel Stabilizer 32 oz 22214</x:v>
+      </x:c>
+      <x:c r="I146" s="9" t="str">
+        <x:v>https://www.academy.com/p/sta-bil%C2%AE-fuel-stabilizer-200000214</x:v>
+      </x:c>
+      <x:c r="J146" s="9" t="str">
+        <x:v>Universal gasoline storage treatment; follow label dosage; live shipping/add-to-cart page</x:v>
+      </x:c>
+      <x:c r="K146" s="9" t="str">
+        <x:v>fuel stabilizer</x:v>
+      </x:c>
+      <x:c r="L146" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/parts-list/2017-bmw-i3-range_extender_i01/vehicle_electrical_system/relay_electric_fuel_pump.html
+https://www.goldeagle.com/product/sta-bil-fuel-stabilizer/</x:v>
+      </x:c>
+      <x:c r="M146" s="9" t="str">
+        <x:v>The three live buyable pages match items explicitly named in How to Fix; relay and coils remain conditional on the diagnosed fault, while stabilizer is preventive.</x:v>
+      </x:c>
+      <x:c r="N146" s="41" t="str">
+        <x:v>Do not call the relay the most common failure without evidence, do not prescribe premium fuel universally, and separate preventive storage advice from fault repair.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A147" s="40" t="str"/>
+      <x:c r="B147" s="9" t="str"/>
+      <x:c r="C147" s="9" t="str"/>
+      <x:c r="D147" s="9" t="str"/>
+      <x:c r="E147" s="9" t="str"/>
+      <x:c r="F147" s="9" t="str"/>
+      <x:c r="G147" s="9" t="str"/>
+      <x:c r="H147" s="9" t="str">
+        <x:v>Genuine BMW sky-blue relay 61366915327</x:v>
+      </x:c>
+      <x:c r="I147" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/parts/bmw-relay_make_contact_sky_blue-61366915327.html</x:v>
+      </x:c>
+      <x:c r="J147" s="9" t="str">
+        <x:v>2014-2017 i3 REx fuel-pump relay catalog application; confirm relay position and failed relay before ordering</x:v>
+      </x:c>
+      <x:c r="K147" s="9" t="str">
+        <x:v>conditional fuel-pump relay</x:v>
+      </x:c>
+      <x:c r="L147" s="9" t="str"/>
+      <x:c r="M147" s="9" t="str"/>
+      <x:c r="N147" s="41" t="str"/>
+    </x:row>
+    <x:row r="148" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A148" s="40" t="str"/>
+      <x:c r="B148" s="9" t="str"/>
+      <x:c r="C148" s="9" t="str"/>
+      <x:c r="D148" s="9" t="str"/>
+      <x:c r="E148" s="9" t="str"/>
+      <x:c r="F148" s="9" t="str"/>
+      <x:c r="G148" s="9" t="str"/>
+      <x:c r="H148" s="9" t="str">
+        <x:v>Genuine BMW i3 REx ignition coil 12138569194</x:v>
+      </x:c>
+      <x:c r="I148" s="9" t="str">
+        <x:v>https://www.bimmerworld.com/Engine/Ignition/Ignition-Coil-Genuine-BMW-I01-i3-Rex.html</x:v>
+      </x:c>
+      <x:c r="J148" s="9" t="str">
+        <x:v>2014-2021 issue scope; I01 REx 60Ah/94Ah/120Ah; in stock; sold individually, two per car</x:v>
+      </x:c>
+      <x:c r="K148" s="9" t="str">
+        <x:v>conditional ignition coil</x:v>
+      </x:c>
+      <x:c r="L148" s="9" t="str"/>
+      <x:c r="M148" s="9" t="str"/>
+      <x:c r="N148" s="41" t="str"/>
+    </x:row>
+    <x:row r="149" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A149" s="42" t="str"/>
+      <x:c r="B149" s="43" t="str"/>
+      <x:c r="C149" s="43" t="str"/>
+      <x:c r="D149" s="43" t="str"/>
+      <x:c r="E149" s="43" t="str"/>
+      <x:c r="F149" s="43" t="str"/>
+      <x:c r="G149" s="43" t="str"/>
+      <x:c r="H149" s="43" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I149" s="43" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J149" s="43" t="str">
+        <x:v>REx fuel/ignition diagnosis and injector service</x:v>
+      </x:c>
+      <x:c r="K149" s="43" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L149" s="43" t="str"/>
+      <x:c r="M149" s="43" t="str"/>
+      <x:c r="N149" s="44" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4654,21 +6152,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="2" ht="462" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>bmw-7-series-panoramic-roof-2016</x:v>
+        <x:v>bmw-i4-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2016-2025 | BMW | 7 Series</x:v>
+        <x:v>2022-2026 | BMW | i4</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>Panoramic Glass Roof Cracking and Drain Blockage</x:v>
+        <x:v>12V Auxiliary Battery Drain</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>For cracked glass: the entire panoramic roof panel must be replaced. Check if covered under BMW's glass warranty (some cracks without impact evidence are covered as manufacturing defects). For drain blockage: clear all four drain channels (two front, two rear) using compressed air or a flexible drain snake. This should be done as preventive maintenance every 12 months. If the headliner is water-damaged, it must be removed and replaced.</x:v>
+        <x:v>Ensure the latest software version is installed (BMW has released multiple OTA updates addressing sleep mode behavior). If the problem persists, have the dealer check for parasitic draw using ISTA diagnostics. In severe cases, the 12V battery may need replacement and proper registration.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -4677,21 +6175,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="3" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>bmw-7series-air-suspension-2002</x:v>
+        <x:v>bmw-i4-12v-battery-sleep-mode-2022</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2002-2023 | BMW | 7 Series</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure - All Generations</x:v>
+        <x:v>12V Battery Drain - Sleep Mode Failure</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Replace failed air struts or compressor. Individual air struts can be replaced, but often multiple fail together. Compressor replacement is 3-5 hours labor. Some owners convert to conventional coil springs ($1,500-2,500) to avoid repeat air suspension repairs. Air strut replacement requires specialized tools and calibration. OEM BMW parts are extremely expensive; some aftermarket options (Arnott) available at lower cost but with mixed reliability.</x:v>
+        <x:v>First check for latest software update - BMW has released updates to fix sleep mode bugs. If 12V battery has been deeply discharged, it may need replacement (60Ah AGM). Must register new battery using BimmerLink app (not BimmerCode - BimmerCode cannot register batteries). For vehicles that sit for extended periods, use a BMW-approved battery tender. If CCU is causing the issue, dealer diagnosis and CCU replacement under warranty. The DC-DC converter should maintain 12V charge from the HV battery, so persistent drain indicates a software or CCU hardware fault.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -4700,21 +6198,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="4" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>bmw-7series-electrical-e65-2002</x:v>
+        <x:v>bmw-i4-brake-feel-regen-2022</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2002-2008 | BMW | 7 Series</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>Widespread Electrical Issues - E65/E66 745i/750i/760i</x:v>
+        <x:v>Regenerative Braking Pedal Feel Complaints - Grabby/Aggressive</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>Diagnose specific module failures with BMW diagnostic software. Common fixes: CCC module replacement ($1,500-2,500), window regulator replacement ($300-600 per window), battery registration after replacement, and parasitic draw diagnosis. Many electrical issues require dealer-level diagnostics. Some problems can only be resolved with module replacements. E65/E66 ownership requires deep pockets or strong DIY skills. Avoid buying E65 without thorough pre-purchase inspection and warranty.</x:v>
+        <x:v>This is a design characteristic of the blended braking system, not a defect per se. Adaptive approaches: Use "D" mode with Adaptive recuperation setting for the most natural brake feel - it adjusts regen based on traffic and road conditions. Avoid "B" mode unless you specifically want strong one-pedal driving. Practice feathering the brake pedal with very light, progressive pressure. Some owners report the brake feel improves slightly with software updates. If braking is truly abnormal (pulsating, grinding), have the integrated brake module checked as that could indicate a hardware issue covered under recall.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -4723,21 +6221,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="5" ht="594" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>bmw-7series-hpfp-2009</x:v>
+        <x:v>bmw-i4-drivetrain-malfunction-2022</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL | N63</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump Failure - F01/F02 750i/750Li (N63)</x:v>
+        <x:v>2022-2025 i4 Propulsion-Loss Recall 25V-395</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Replace high-pressure fuel pump(s). BMW recommends replacing both HPFPs together on N63 engines. Flush fuel system if metal contamination is present. Use only OEM BMW or Bosch fuel pumps - aftermarket pumps have poor reliability. Labor is 4-6 hours. Some owners report multiple HPFP failures over vehicle life. N63 Customer Care Package may cover HPFP repairs on eligible VINs. Consider extended warranty for N63-powered cars.</x:v>
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW’s free electric-drive-motor software update through the authorized dealer or the approved over-the-air recall process. Do not buy gear oil, gaskets or drivetrain parts as a substitute. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -4746,21 +6244,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="6" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>bmw-7series-n63-turbo-2009</x:v>
+        <x:v>bmw-i4-heat-pump-cold-weather-2022</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2013-2015 | BMW | 7 Series | N63TU1</x:v>
+        <x:v>2022-2024 | BMW | i4</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>N63TU1 750i Oil-Consumption and Turbo-Leak Diagnosis</x:v>
+        <x:v>G26 i4 Coolant Changeover-Valve Leak Diagnosis</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Confirm the exact chassis, N63TU1 engine, production date, engine serial number, VIN and current eligibility, then follow BMW electronic oil-level measurement and leak-inspection procedures. Repair only the component supported by the documented test result; replace turbochargers only when leakage is confirmed under the current instructions. Do not promise historical settlement coverage. ShowMeTheParts returned six exact 2014 750i/750i xDrive turbo oil-return-line fitments, but catalog fitment does not prove a leak, oil-consumption cause or repair role, so no commerce link is approved.</x:v>
+        <x:v>Check coolant level, read the exact BMW fault memory and inspect the G26 changeover valve for active or dried leakage. Follow SIB 17 01 24 and VIN-specific AIR/ETK instructions; replace the applicable older-production valve and bleed/test the cooling system with ISTA when the BMW criteria are met. ShowMeTheParts resolves exact 2022 i4 HVAC and water-pump categories but returned no changeover-valve candidate, so the frozen marketplace searches and generic coolant are removed.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -4769,21 +6267,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="7" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>bmw-7series-n63-valvetronic-2009</x:v>
+        <x:v>bmw-i4-heat-pump-malfunction-2022</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2009-2015 | BMW | 7 Series | 750Li, 750i, 750iL</x:v>
+        <x:v>2022-2026 | BMW | i4</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>N63 Valvetronic Motor Failure - F01/F02 750i/750Li</x:v>
+        <x:v>Heat Pump Malfunction in Cold Weather</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>Replace Valvetronic eccentric shaft motor(s). Often both motors need replacement since wear is similar. Clean carbon buildup from Valvetronic mechanism during repair. N63 Customer Care Package may cover this repair on eligible VINs. Labor is 6-10 hours. Some shops recommend replacing Valvetronic motors preventively at 80,000 miles to avoid being stranded. Extended warranty highly recommended for N63-powered 7 Series.</x:v>
+        <x:v>BMW has released software updates to improve heat pump operation in cold weather. Visit the dealer for the latest calibration. Some cases require heat pump valve replacement. Pre-conditioning the cabin while plugged in reduces the impact on driving range.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -4792,21 +6290,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="8" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>bmw-8-series-adaptive-suspension-2019</x:v>
+        <x:v>bmw-i4-idrive8-software-bugs-2022</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2019-2025 | BMW | 8 Series</x:v>
+        <x:v>2022-2025 | BMW | i4</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>Adaptive Suspension Damper Malfunction</x:v>
+        <x:v>iDrive 8 Software Bugs - Screen Crashes, Reboots &amp; Freezing</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Replace the failed adaptive damper. BMW's diagnostic system can identify which specific damper has failed through the suspension control module fault memory. The damper must be coded to the vehicle after installation. Replace dampers in pairs (both fronts or both rears) if the vehicle has over 60,000 miles, as the remaining original damper is likely near end of life. Bilstein offers OE-equivalent adaptive dampers at lower cost than BMW parts.</x:v>
+        <x:v>Ensure vehicle has latest iDrive software via OTA update (Settings &gt; Software Update). Version .63 and later resolved many screen blank/reboot issues. For persistent crashes: Perform soft reset by holding volume knob/power button for 10+ seconds. For factory reset, use Settings &gt; General &gt; Reset to restore defaults. If issues persist after latest OTA, dealer can force-flash the head unit via ISTA. Some owners report that disconnecting phone from wireless CarPlay/Android Auto and using wired connection improves stability. BMW has released multiple major software updates addressing these issues.</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
@@ -4815,21 +6313,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="9" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>bmw-8-series-b58-coolant-loss-2019</x:v>
+        <x:v>bmw-i4-infotainment-glitches-2022</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2019-2025 | BMW | 8 Series | B58</x:v>
+        <x:v>2022-2026 | BMW | i4</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>B58 Engine Coolant Loss from Expansion Tank and Water Pump</x:v>
+        <x:v>iDrive 8 Software and Infotainment Glitches</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with BMW's latest revision. Inspect the electric water pump and all quick-connect coolant fittings for leaks. Pressure test the entire cooling system after repairs. Replace the expansion tank cap as a weak cap allows premature boiling. Use only BMW-approved blue coolant — mixing coolant types causes gel formation.</x:v>
+        <x:v>Keep software up to date via OTA updates or dealer visit. For persistent issues, a full iDrive system reset (Settings &gt; General &gt; Reset) can resolve cached data problems. Some owners have needed the head unit replaced under warranty for hardware-level display faults.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -4838,21 +6336,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="660" hidden="0" customHeight="1">
+    <x:row r="10" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A10" s="40" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>bmw-8-series-n63-oil-consumption-m850i-2019</x:v>
+        <x:v>bmw-i4-pedestrian-sound-2022</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2019-2025 | BMW | 8 Series | N63TU4, N63</x:v>
+        <x:v>2022-2023 | BMW | i4</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>N63/S63 V8 Oil Consumption in M850i</x:v>
+        <x:v>2022-2023 i4 eDrive40 Sound-Generator Recall 23V-026</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>BMW considers up to 1 quart per 1,200 miles as within specification for the N63 family. For excessive consumption beyond that, inspect turbo oil return lines for restriction (causes oil to push past turbo seals), check the crankcase ventilation system, and evaluate valve stem seal condition. The N63TU4 benefits from updated seals and coatings, so consumption rarely reaches the extreme levels of earlier N63 variants.</x:v>
+        <x:v>Check the VIN for an open 23V-026 campaign. If included, arrange the free BMW programming remedy for the Receiver Audio Module/external artificial sound generator. Do not replace a speaker or module based only on a missing sound; if the VIN is outside the campaign, diagnose the exact warning and faults separately.</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
         <x:v>0</x:v>
@@ -4861,21 +6359,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="11" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>bmw-8series-ibs-failure-2020</x:v>
+        <x:v>bmw-i5-12v-battery-drain-2024</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2019-2021 | BMW | 8 Series</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>2019-2021 8 Series Integrated Brake Recall 21V-062</x:v>
+        <x:v>12V Auxiliary Battery Drain and Dead Car Syndrome</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-062 campaign and current remedy status with BMW/NHTSA. If the vehicle is included, have an authorized BMW center perform the recall repair at no charge. If brake warnings appear or pedal effort changes, slow safely, avoid hard braking and contact BMW or roadside assistance for direction. ShowMeTheParts resolved exact 2020 840i, 840i xDrive and M850i xDrive brake-hydraulics contexts but returned no brake-booster candidate; recall eligibility and remedy remain dealer-only.</x:v>
+        <x:v>Keep the i5 plugged in when parked for extended periods — the HV charger trickle-charges the 12V battery. Install a BMW-recommended battery maintainer connected to the 12V battery (accessible in the right side of the trunk). Update iDrive software to the latest version — BMW has released OTA updates that improve sleep-mode power management. If the 12V battery dies, the manual release cable under the hood allows emergency access.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -4884,21 +6382,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="12" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>bmw-8series-n63tu3-timing-chain-2019</x:v>
+        <x:v>bmw-i5-acoustic-pedestrian-warning-sound-generator-fault</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>N63TU3 Timing Chain Guide Wear (M850i)</x:v>
+        <x:v>2024 i5 Pedestrian Sound Recall 23V-885</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: Replace timing chain guides, tensioners, and chain at 80,000-100,000 miles ($4,000-$7,500). Turner Motorsport timing chain kit 11317594899KT includes all necessary components. Individual parts: chain guides 11147574373, 11317574397, 11317592850, 11317592877; chain 11317598263. If chain has already skipped: engine damage likely requires $15,000-$25,000 engine replacement. CRITICAL: If you hear cold-start rattling, do NOT drive - tow to shop immediately to prevent catastrophic engine failure.</x:v>
+        <x:v>Check the VIN for an open 23V-885 campaign. If included, arrange BMW's free software programming remedy through the authorized dealer or the approved recall over-the-air process. Do not replace a speaker or module based only on a missing sound; diagnose vehicles outside the campaign separately.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -4907,21 +6405,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="13" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>bmw-8series-n63tu3-valve-stem-seals-2019</x:v>
+        <x:v>bmw-i5-adaptive-suspension-calibration-2024</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2019-2024 | BMW | 8 Series | 840Ci, 850CSi, 850Ci, M850i | N63TU3</x:v>
+        <x:v>2024-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>N63TU3 Valve Stem Seal Failure &amp; Oil Consumption (M850i)</x:v>
+        <x:v>Adaptive Suspension Self-Leveling Calibration Errors</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Replace valve stem seals ($3,500-$10,000 due to labor-intensive hot-V access). Use OEM Victor Reinz seals for durability. Replace spark plugs (Bosch 12120037581) when performing seal replacement. AGA Tools N63 Valve Stem Seal Kit AGA-N63-VSK-K ($500-800) provides specialized tooling for this job. Check VIN eligibility for N63 class action settlement which may cover repair costs. PREVENTIVE: Use quality synthetic oil (BMW LL-01 spec), change every 5,000-7,500 miles, and monitor oil level every 500-1,000 miles on M850i models.</x:v>
+        <x:v>Perform a suspension calibration reset using BMW ISTA diagnostic software. If the issue persists, inspect the ride height sensors at each corner for damage or loose connectors. A dealer software update may also resolve the issue.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -4930,21 +6428,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="14" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>bmw-8series-premature-tire-wear-2019</x:v>
+        <x:v>bmw-i5-c-wiring-harness-damaged-during-cabin-filter-service</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2019-2024 | BMW | 8 Series</x:v>
+        <x:v>2024-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>Premature Tire Wear (All 8 Series &amp; M8)</x:v>
+        <x:v>2024-2026 i5 A/C Harness Recall 26V-096</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Get a performance alignment reducing rear camber from factory -2.0 degrees to -1.5 degrees ($150-$300 at alignment shop). This significantly extends rear tire life from 9,000-15,000 miles to 20,000-25,000 miles while maintaining good street handling. Rotate front tires side-to-side every 5,000 miles (staggered setup prevents front-to-rear rotation). Replace rear tires in pairs when worn. COST SAVINGS: Alignment adjustment ($150-300) saves $1,200-2,400 per year in premature tire replacement on expensive performance tires ($300-600 each).</x:v>
+        <x:v>Check the VIN for an open 26V-096 campaign. If included, have an authorized BMW dealer inspect the air-conditioning wiring harness and repair or replace it as required at no charge. Do not probe, splice or order harness parts from this card. If smoke, burning odor or an electrical warning appears, stop using the vehicle and follow BMW emergency guidance.</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -4958,16 +6456,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>bmw-8series-zf-8hp-mechatronic-2019</x:v>
+        <x:v>bmw-i5-dc-fast-charge-throttling-loud-cooling-fans-repeated-session</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2023-2023 | BMW | 8 Series</x:v>
+        <x:v>2024-2025 | BMW | i5 | eDrive40, xDrive40, M60 xDrive</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>2023 8 Series ITCU Recall 23V-821</x:v>
+        <x:v>DC Fast-Charge Throttling and Loud Cooling Fans on Repeated Sessions</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-821 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW recall remedy, which replaces the transmission mechatronics module. Do not buy a sleeve kit or change fluid as a substitute for the recall. ShowMeTheParts resolved exact 2023 840i, 840i xDrive and M850i xDrive models but exposed no transmission category or ITCU candidate, and recall repair remains dealer-only.</x:v>
+        <x:v>Keep the i5 on the latest software, since BMW has released charging-curve/charging-management updates via OTA and dealer flashes. Precondition the battery before fast charging to reduce throttling, avoid back-to-back DC sessions when possible, and report persistent amp drops or skipped scheduled charges to the dealer (some cases were traced to software faults). Loud thermal-management fan noise is generally normal during/after DC charging.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -4981,16 +6479,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>bmw-driveshaft-flex-disc-e90</x:v>
+        <x:v>bmw-i5-electric-drive-motor-software-false-isolation-fault-causing</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2011-2011 | BMW | 3 Series | N55, N54T, M57Y</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>Certain 2011 3 Series Need a Rear-Driveshaft Flex-Disc Recall Check</x:v>
+        <x:v>2024 i5 Propulsion-Loss Recall 25V-395</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Check the VIN for open recall 17V-067 before authorizing driveline parts. BMW instructs dealers to inspect the installed disc revision index and replace it only when required by the campaign. ShowMeTheParts exposed the exact 2011 335i DRIVE SHAFT category but returned no flex-disc candidate; no commerce link is approved for this recall repair.</x:v>
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or the approved recall over-the-air process. Do not order drivetrain or battery parts from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the remedy.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
         <x:v>0</x:v>
@@ -4999,21 +6497,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="17" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>bmw-i3-12v-battery-drain-2014</x:v>
+        <x:v>bmw-i5-heat-pump-drip-tube-thunking-clunking-noise</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>i3 12V Discharge Warning: ISTA Software-First Diagnosis</x:v>
+        <x:v>Early-Production G60 i5 Condensation-Drain Drum Noise</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>Read the Check Control Message and fault memory, run BMW ISTA Energy Diagnosis and test the 12V battery before replacing anything. For the Controller condition, BMW says not to replace the Controller; program the vehicle when the measured I-level and diagnostic result meet SIB 61 05 20. For the early REx condition, follow SIB 61 39 14. Replace and register a 12V battery only if separate testing proves it failed. ShowMeTheParts resolved the exact 2014 i3 model but exposed no battery category or defensible 12V candidate, so no commerce link is approved.</x:v>
+        <x:v>Confirm the production date and reproduce the rhythmic noise under the BMW bulletin conditions. If SIB 64 01 24 applies, an authorized high-voltage-qualified repair facility replaces the condensation-water drain with the optimized part; the procedure requires high-voltage battery removal. Do not cut or modify the drain. ShowMeTheParts resolved the exact 2024 i5 but returned no matching HVAC candidate, so no parts link is approved.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -5022,21 +6520,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="18" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>bmw-i3-12v-parasitic-drain-2014</x:v>
+        <x:v>bmw-i5-high-voltage-battery-module-insufficient-weld-seams</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2024-2024 | BMW | i5</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>12V Auxiliary Battery Parasitic Drain</x:v>
+        <x:v>Single-Vehicle 2024 i5 Battery-Weld Recall 24V-135</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Replace the 12V AGM battery with a fresh unit (OEM or high-quality AGM). Code the new battery using ISTA or BimmerCode to register it with the IBS (Intelligent Battery Sensor). Check for software updates that address module sleep behavior. Some owners install a battery tender for long-term parking.</x:v>
+        <x:v>Check the VIN for an open 24V-135 campaign. If included, follow BMW's instructions and have the affected high-voltage battery module replaced at no charge by an authorized high-voltage-qualified dealer. Do not open the battery pack or order modules independently; vehicles outside the campaign require separate fault-led diagnosis.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -5045,21 +6543,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="19" ht="528" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>bmw-i3-ac-compressor-black-death-2014</x:v>
+        <x:v>bmw-i5-integrated-brake-system-servomotor-weld-failure</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>Electric A/C Compressor Catastrophic Failure ("Black Death") - All I01</x:v>
+        <x:v>2024-2025 i5 Integrated-Brake Recall 24V-697</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>If caught early (noise but still functioning), replace compressor before catastrophic failure. Latest OEM compressor: BMW 64529496107 (supersedes 64529320855, 64529343806, 64529347662, 64529364868). FCP Euro price ~$1,756. If metal contamination has occurred, entire system including battery cooling channels must be replaced ($10,600+). MUST use POE (Polyolester) anti-electrostatic compressor oil - standard PAG oil will destroy EV compressors. Independent AC shops that understand EV compressors can save 60-80% vs dealer. RYC Automotive offers remanufactured compressor (RYC-i3-01) as budget option. Aftermarket Nissens condenser ($152) available vs OEM ($581 via FCP Euro).</x:v>
+        <x:v>Check the VIN for an open 24V-697 campaign. If included, have an authorized BMW dealer replace the integrated brake system at no charge. Do not buy pads, rotors, fluid or a generic actuator as a substitute. If a brake warning or changed pedal effort appears, stop driving when safe and arrange BMW assistance.</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -5068,21 +6566,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="20" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>bmw-i3-ac-compressor-failure-2014</x:v>
+        <x:v>bmw-i5-regen-braking-inconsistency-2024</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Electric AC Compressor Failure</x:v>
+        <x:v>Regenerative Braking Inconsistency in Cold Weather</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Replace the electric AC compressor assembly. This requires a certified HV-trained technician to safely de-energize the high-voltage system before working on the compressor. The system must be evacuated, the compressor replaced, and the system recharged with the correct amount of R-1234yf refrigerant.</x:v>
+        <x:v>Use the BMW departure timer to precondition the battery before driving — this warms the battery and restores full regen capability from the start. Set the regen level to "Adaptive" instead of "High" in winter, which provides smoother transitions. BMW software updates have improved regen ramping behavior. Rely more on friction brakes during the first 10-15 minutes of cold-weather driving until the battery warms.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
         <x:v>0</x:v>
@@ -5091,22 +6589,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="21" ht="66" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>bmw-i3-battery-degradation-2014</x:v>
+        <x:v>bmw-i5-software-glitches-2024</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2019-2021 | BMW | i3</x:v>
+        <x:v>2024-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>2019-2021 i3 High-Voltage Battery Cell Recall 22V-683</x:v>
-      </x:c>
-      <x:c r="E21" s="9" t="str">
-        <x:v>Check the VIN for an open 22V-683 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy; BMW instructs replacement of the affected battery cell module. Do not buy a battery module or use capacity estimates as a substitute for the VIN recall check. This high-voltage, recall-only path intentionally carries no commerce.</x:v>
-      </x:c>
+        <x:v>iDrive 8.5 Software Bugs and EV System Errors</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="str"/>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5114,22 +6610,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="22" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>bmw-i3-connectivity-module-2014</x:v>
+        <x:v>bmw-i5-software-updates-2025</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2025-2026 | BMW | i5</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>i3 ConnectedDrive 3G Sunset: VIN-Specific Eligibility Path</x:v>
-      </x:c>
-      <x:c r="E22" s="9" t="str">
-        <x:v>Check the VIN in BMW AIR/DCSnet or My Garage before choosing a remedy. An early 3G vehicle marked non-eligible cannot be restored by buying the frozen card’s used TCB part. A later campaign-eligible 4G vehicle should receive the BMW programming action that writes the IMS configuration. Confirm current service availability with BMW ConnectedDrive support; do not order a telematics module from model year alone.</x:v>
-      </x:c>
+        <x:v>iDrive 9 Software Updates and Calibration Issues</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="str"/>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5137,21 +6631,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="23" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>bmw-i3-dc-fast-charge-latch-2014</x:v>
+        <x:v>bmw-i5-steering-spindle-double-universal-joint-fracture</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2014-2014 | BMW | i3</x:v>
+        <x:v>2024-2025 | BMW | i5</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>2014 i3 Level 2 Charging Delay: KLE Campaign Check</x:v>
+        <x:v>2024-2025 i5 Steering-Spindle Recall 24V-714</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Check the VIN for the KLE service action and read charging and 12V faults with BMW diagnostics. For an open campaign, follow BMW’s KLE replacement and programming procedure. If the 12V battery is discharged, SIB 61 01 15 describes a controlled Level 2 recovery/programming path and says parts replacement does not solve its remaining intermittent delay. Do not drill or lubricate the charge port or buy a latch actuator based on this card.</x:v>
+        <x:v>Check the VIN for an open 24V-714 campaign. If included, have an authorized BMW dealer replace the steering spindle double universal joint at no charge. Do not order a steering joint from this card. If steering-column noise, notchy steering or increased effort appears, stop driving when safe and arrange BMW assistance.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -5160,22 +6654,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="24" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>bmw-i3-hvac-heater-2014</x:v>
+        <x:v>bmw-i7-air-suspension-calibration-2023</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3</x:v>
+        <x:v>2023-2026 | BMW | i7</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>Electric Heater &amp; HVAC System Failures - Range Impact</x:v>
-      </x:c>
-      <x:c r="E24" s="9" t="str">
-        <x:v>Electric heater element replacement ($800-1,500). Heat pump compressor replacement uses same compressor as AC system (64529496107) at $1,756-4,000. Blower motor replacement $300-600. HVAC control module reprogramming or replacement $500-1,000. Pre-conditioning the cabin while plugged in (before driving) reduces range impact significantly. Some owners install aftermarket heated seats and steering wheel to reduce HVAC load.</x:v>
-      </x:c>
+        <x:v>Air Suspension Calibration and Sensor Issues</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="str"/>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5183,21 +6675,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="726" hidden="0" customHeight="1">
+    <x:row r="25" ht="792" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>bmw-i3-rex-engine-issues-2014</x:v>
+        <x:v>bmw-i7-autonomous-system-updates-2025</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2014-2017 | BMW | i3 | W20 647cc</x:v>
+        <x:v>2023-2024 | BMW | i7</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>2014-2017 i3 REx Fuel-Vent-Line Recall 17V-088</x:v>
+        <x:v>G70 i7 ADCAM Assistance-Limit Diagnosis</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>Check the VIN for an open 17V-088 campaign with BMW/NHTSA. If included, arrange the free authorized-BMW remedy: inspect the fuel tank vent line, replace it if necessary and install the separating clip. Do not substitute a fuel-pump relay, injector cleaner or generic engine parts for the recall. ShowMeTheParts lists 2014 i3 fuel-system categories, but recall inclusion and remedy are VIN/dealer controlled, so no commerce link is approved.</x:v>
+        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather and traffic conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the operating limits in the owner manual. BMW states that parts replacement does not correct environmental system limitations.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -5206,21 +6698,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="26" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>bmw-i3-rex-stale-fuel-2014</x:v>
+        <x:v>bmw-i7-ota-update-failures-2025</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2014-2021 | BMW | i3 | W20 647cc</x:v>
+        <x:v>2023-2024 | BMW | i7</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>Range Extender Stale Fuel &amp; Engine Problems - I01 REx Only</x:v>
+        <x:v>G70 i7 Comfort-Access Faults after Remote Upgrade</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Preventive: Run the REx at least every 6 weeks for a minimum of 10-13 minutes to burn off moisture. Use fuel stabilizer (Sta-Bil) if vehicle sits for extended periods. Keep fuel tank above half to reduce vapor space. For fuel pump relay failure (most common), replace relay ($20-30). For injector issues, professional cleaning or replacement required. For coil failures, replace ignition coils. Maintain regular oil changes with BMW-approved oil despite low mileage. Some owners run premium fuel exclusively to reduce varnish formation.</x:v>
+        <x:v>Confirm that the complaint followed a BMW Remote Software Upgrade and read the exact BCP faults. Follow SIB 61 11 24 in ISTA to program and pair all FBD5/FBD5s remote-control receivers, clear faults and verify Comfort Access and Passive Go/Exit. Keep phones disconnected during receiver programming. BMW states that parts replacement will not solve this path. ShowMeTheParts resolves the exact 2023 i7 but has no software or receiver repair candidate, so all marketplace links are removed.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -5229,21 +6721,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="462" hidden="0" customHeight="1">
+    <x:row r="27" ht="528" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>bmw-i4-12v-battery-drain-2022</x:v>
+        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2015-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain</x:v>
+        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Ensure the latest software version is installed (BMW has released multiple OTA updates addressing sleep mode behavior). If the problem persists, have the dealer check for parasitic draw using ISTA diagnostics. In severe cases, the 12V battery may need replacement and proper registration.</x:v>
+        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -5252,21 +6744,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="28" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>bmw-i4-12v-battery-sleep-mode-2022</x:v>
+        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>12V Battery Drain - Sleep Mode Failure</x:v>
+        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>First check for latest software update - BMW has released updates to fix sleep mode bugs. If 12V battery has been deeply discharged, it may need replacement (60Ah AGM). Must register new battery using BimmerLink app (not BimmerCode - BimmerCode cannot register batteries). For vehicles that sit for extended periods, use a BMW-approved battery tender. If CCU is causing the issue, dealer diagnosis and CCU replacement under warranty. The DC-DC converter should maintain 12V charge from the HV battery, so persistent drain indicates a software or CCU hardware fault.</x:v>
+        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -5275,21 +6767,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="29" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>bmw-i4-brake-feel-regen-2022</x:v>
+        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8 | B38</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>Regenerative Braking Pedal Feel Complaints - Grabby/Aggressive</x:v>
+        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>This is a design characteristic of the blended braking system, not a defect per se. Adaptive approaches: Use "D" mode with Adaptive recuperation setting for the most natural brake feel - it adjusts regen based on traffic and road conditions. Avoid "B" mode unless you specifically want strong one-pedal driving. Practice feathering the brake pedal with very light, progressive pressure. Some owners report the brake feel improves slightly with software updates. If braking is truly abnormal (pulsating, grinding), have the integrated brake module checked as that could indicate a hardware issue covered under recall.</x:v>
+        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
         <x:v>0</x:v>
@@ -5298,21 +6790,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="594" hidden="0" customHeight="1">
+    <x:row r="30" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>bmw-i4-drivetrain-malfunction-2022</x:v>
+        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>2022-2025 i4 Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW’s free electric-drive-motor software update through the authorized dealer or the approved over-the-air recall process. Do not buy gear oil, gaskets or drivetrain parts as a substitute. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -5321,21 +6813,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="31" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>bmw-i4-heat-pump-cold-weather-2022</x:v>
+        <x:v>bmw-i8-charging-port-2014</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2022-2024 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>G26 i4 Coolant Changeover-Valve Leak Diagnosis</x:v>
+        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Check coolant level, read the exact BMW fault memory and inspect the G26 changeover valve for active or dried leakage. Follow SIB 17 01 24 and VIN-specific AIR/ETK instructions; replace the applicable older-production valve and bleed/test the cooling system with ISTA when the BMW criteria are met. ShowMeTheParts resolves exact 2022 i4 HVAC and water-pump categories but returned no changeover-valve candidate, so the frozen marketplace searches and generic coolant are removed.</x:v>
+        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -5344,21 +6836,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="32" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>bmw-i4-heat-pump-malfunction-2022</x:v>
+        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2014-2015 | BMW | i8</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>Heat Pump Malfunction in Cold Weather</x:v>
+        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>BMW has released software updates to improve heat pump operation in cold weather. Visit the dealer for the latest calibration. Some cases require heat pump valve replacement. Pre-conditioning the cabin while plugged in reduces the impact on driving range.</x:v>
+        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
       </x:c>
       <x:c r="F32" s="9" t="n">
         <x:v>0</x:v>
@@ -5367,21 +6859,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="33" ht="924" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>bmw-i4-idrive8-software-bugs-2022</x:v>
+        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>iDrive 8 Software Bugs - Screen Crashes, Reboots &amp; Freezing</x:v>
+        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Ensure vehicle has latest iDrive software via OTA update (Settings &gt; Software Update). Version .63 and later resolved many screen blank/reboot issues. For persistent crashes: Perform soft reset by holding volume knob/power button for 10+ seconds. For factory reset, use Settings &gt; General &gt; Reset to restore defaults. If issues persist after latest OTA, dealer can force-flash the head unit via ISTA. Some owners report that disconnecting phone from wireless CarPlay/Android Auto and using wired connection improves stability. BMW has released multiple major software updates addressing these issues.</x:v>
+        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -5390,21 +6882,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="34" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>bmw-i4-infotainment-glitches-2022</x:v>
+        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>iDrive 8 Software and Infotainment Glitches</x:v>
+        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Keep software up to date via OTA updates or dealer visit. For persistent issues, a full iDrive system reset (Settings &gt; General &gt; Reset) can resolve cached data problems. Some owners have needed the head unit replaced under warranty for hardware-level display faults.</x:v>
+        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -5413,21 +6905,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="35" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>bmw-i4-pedestrian-sound-2022</x:v>
+        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2022-2023 | BMW | i4</x:v>
+        <x:v>2014-2014 | BMW | i8</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>2022-2023 i4 eDrive40 Sound-Generator Recall 23V-026</x:v>
+        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-026 campaign. If included, arrange the free BMW programming remedy for the Receiver Audio Module/external artificial sound generator. Do not replace a speaker or module based only on a missing sound; if the VIN is outside the campaign, diagnose the exact warning and faults separately.</x:v>
+        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
         <x:v>0</x:v>
@@ -5436,21 +6928,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="36" ht="726" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>bmw-i5-12v-battery-drain-2024</x:v>
+        <x:v>bmw-i8-hv-system-faults-2014</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2014-2017 | BMW | i8</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain and Dead Car Syndrome</x:v>
+        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>Keep the i5 plugged in when parked for extended periods — the HV charger trickle-charges the 12V battery. Install a BMW-recommended battery maintainer connected to the 12V battery (accessible in the right side of the trunk). Update iDrive software to the latest version — BMW has released OTA updates that improve sleep-mode power management. If the 12V battery dies, the manual release cable under the hood allows emergency access.</x:v>
+        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -5459,21 +6951,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="37" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>bmw-i5-acoustic-pedestrian-warning-sound-generator-fault</x:v>
+        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>2024 i5 Pedestrian Sound Recall 23V-885</x:v>
+        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-885 campaign. If included, arrange BMW's free software programming remedy through the authorized dealer or the approved recall over-the-air process. Do not replace a speaker or module based only on a missing sound; diagnose vehicles outside the campaign separately.</x:v>
+        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -5482,21 +6974,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="38" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>bmw-i5-adaptive-suspension-calibration-2024</x:v>
+        <x:v>bmw-ix-air-suspension-2022</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>Adaptive Suspension Self-Leveling Calibration Errors</x:v>
+        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Perform a suspension calibration reset using BMW ISTA diagnostic software. If the issue persists, inspect the ride height sensors at each corner for damage or loose connectors. A dealer software update may also resolve the issue.</x:v>
+        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -5505,21 +6997,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="39" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>bmw-i5-c-wiring-harness-damaged-during-cabin-filter-service</x:v>
+        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>2024-2026 i5 A/C Harness Recall 26V-096</x:v>
+        <x:v>Air Suspension Calibration Errors</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>Check the VIN for an open 26V-096 campaign. If included, have an authorized BMW dealer inspect the air-conditioning wiring harness and repair or replace it as required at no charge. Do not probe, splice or order harness parts from this card. If smoke, burning odor or an electrical warning appears, stop using the vehicle and follow BMW emergency guidance.</x:v>
+        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -5528,21 +7020,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="40" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A40" s="40" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>bmw-i5-dc-fast-charge-throttling-loud-cooling-fans-repeated-session</x:v>
+        <x:v>bmw-ix-build-quality-2022</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5 | eDrive40, xDrive40, M60 xDrive</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>DC Fast-Charge Throttling and Loud Cooling Fans on Repeated Sessions</x:v>
+        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>Keep the i5 on the latest software, since BMW has released charging-curve/charging-management updates via OTA and dealer flashes. Precondition the battery before fast charging to reduce throttling, avoid back-to-back DC sessions when possible, and report persistent amp drops or skipped scheduled charges to the dealer (some cases were traced to software faults). Loud thermal-management fan noise is generally normal during/after DC charging.</x:v>
+        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
         <x:v>0</x:v>
@@ -5551,21 +7043,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="41" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A41" s="40" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>bmw-i5-electric-drive-motor-software-false-isolation-fault-causing</x:v>
+        <x:v>bmw-ix-charging-failures-2022</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>2024 i5 Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or the approved recall over-the-air process. Do not order drivetrain or battery parts from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the remedy.</x:v>
+        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
         <x:v>0</x:v>
@@ -5574,21 +7066,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="42" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A42" s="40" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>bmw-i5-heat-pump-drip-tube-thunking-clunking-noise</x:v>
+        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>Early-Production G60 i5 Condensation-Drain Drum Noise</x:v>
+        <x:v>DC Fast Charging Speed Inconsistency</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Confirm the production date and reproduce the rhythmic noise under the BMW bulletin conditions. If SIB 64 01 24 applies, an authorized high-voltage-qualified repair facility replaces the condensation-water drain with the optimized part; the procedure requires high-voltage battery removal. Do not cut or modify the drain. ShowMeTheParts resolved the exact 2024 i5 but returned no matching HVAC candidate, so no parts link is approved.</x:v>
+        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
         <x:v>0</x:v>
@@ -5597,21 +7089,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="43" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A43" s="40" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>bmw-i5-high-voltage-battery-module-insufficient-weld-seams</x:v>
+        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>Single-Vehicle 2024 i5 Battery-Weld Recall 24V-135</x:v>
+        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-135 campaign. If included, follow BMW's instructions and have the affected high-voltage battery module replaced at no charge by an authorized high-voltage-qualified dealer. Do not open the battery pack or order modules independently; vehicles outside the campaign require separate fault-led diagnosis.</x:v>
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
         <x:v>0</x:v>
@@ -5620,21 +7112,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="528" hidden="0" customHeight="1">
+    <x:row r="44" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A44" s="40" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>bmw-i5-integrated-brake-system-servomotor-weld-failure</x:v>
+        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>2024-2025 i5 Integrated-Brake Recall 24V-697</x:v>
+        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-697 campaign. If included, have an authorized BMW dealer replace the integrated brake system at no charge. Do not buy pads, rotors, fluid or a generic actuator as a substitute. If a brake warning or changed pedal effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
         <x:v>0</x:v>
@@ -5643,21 +7135,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="45" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A45" s="40" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>bmw-i5-regen-braking-inconsistency-2024</x:v>
+        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>Regenerative Braking Inconsistency in Cold Weather</x:v>
+        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
-        <x:v>Use the BMW departure timer to precondition the battery before driving — this warms the battery and restores full regen capability from the start. Set the regen level to "Adaptive" instead of "High" in winter, which provides smoother transitions. BMW software updates have improved regen ramping behavior. Rely more on friction brakes during the first 10-15 minutes of cold-weather driving until the battery warms.</x:v>
+        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
         <x:v>0</x:v>
@@ -5666,20 +7158,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="66" hidden="0" customHeight="1">
+    <x:row r="46" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A46" s="40" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>bmw-i5-software-glitches-2024</x:v>
+        <x:v>bmw-ix-phantom-braking-2022</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>iDrive 8.5 Software Bugs and EV System Errors</x:v>
-      </x:c>
-      <x:c r="E46" s="9" t="str"/>
+        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="str">
+        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
+      </x:c>
       <x:c r="F46" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5687,20 +7181,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="47" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A47" s="40" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>bmw-i5-software-updates-2025</x:v>
+        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>2025-2026 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>iDrive 9 Software Updates and Calibration Issues</x:v>
-      </x:c>
-      <x:c r="E47" s="9" t="str"/>
+        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
+      </x:c>
+      <x:c r="E47" s="9" t="str">
+        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
+      </x:c>
       <x:c r="F47" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5708,21 +7204,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="48" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A48" s="40" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>bmw-i5-steering-spindle-double-universal-joint-fracture</x:v>
+        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>2024-2025 i5 Steering-Spindle Recall 24V-714</x:v>
+        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-714 campaign. If included, have an authorized BMW dealer replace the steering spindle double universal joint at no charge. Do not order a steering joint from this card. If steering-column noise, notchy steering or increased effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
         <x:v>0</x:v>
@@ -5731,20 +7227,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="49" ht="660" hidden="0" customHeight="1">
       <x:c r="A49" s="40" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>bmw-i7-air-suspension-calibration-2023</x:v>
+        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
-        <x:v>2023-2026 | BMW | i7</x:v>
+        <x:v>2021-2021 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>Air Suspension Calibration and Sensor Issues</x:v>
-      </x:c>
-      <x:c r="E49" s="9" t="str"/>
+        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
+      </x:c>
+      <x:c r="E49" s="9" t="str">
+        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
+      </x:c>
       <x:c r="F49" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5752,21 +7250,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="792" hidden="0" customHeight="1">
+    <x:row r="50" ht="528" hidden="0" customHeight="1">
       <x:c r="A50" s="40" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>bmw-i7-autonomous-system-updates-2025</x:v>
+        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>2023-2024 | BMW | i7</x:v>
+        <x:v>2021-2021 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>G70 i7 ADCAM Assistance-Limit Diagnosis</x:v>
+        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather and traffic conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the operating limits in the owner manual. BMW states that parts replacement does not correct environmental system limitations.</x:v>
+        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
         <x:v>0</x:v>
@@ -5775,21 +7273,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="51" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A51" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>bmw-i7-ota-update-failures-2025</x:v>
+        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
-        <x:v>2023-2024 | BMW | i7</x:v>
+        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>G70 i7 Comfort-Access Faults after Remote Upgrade</x:v>
+        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
-        <x:v>Confirm that the complaint followed a BMW Remote Software Upgrade and read the exact BCP faults. Follow SIB 61 11 24 in ISTA to program and pair all FBD5/FBD5s remote-control receivers, clear faults and verify Comfort Access and Passive Go/Exit. Keep phones disconnected during receiver programming. BMW states that parts replacement will not solve this path. ShowMeTheParts resolves the exact 2023 i7 but has no software or receiver repair candidate, so all marketplace links are removed.</x:v>
+        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
         <x:v>0</x:v>
@@ -5798,21 +7296,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="528" hidden="0" customHeight="1">
+    <x:row r="52" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A52" s="40" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
+        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>2015-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
+        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
+        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
         <x:v>0</x:v>
@@ -5821,21 +7319,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="53" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A53" s="40" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
+        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
+        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
-        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
+        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
         <x:v>0</x:v>
@@ -5844,21 +7342,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="54" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A54" s="40" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
+        <x:v>bmw-m2-charge-pipe-2016</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8 | B38</x:v>
+        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
+        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
+        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
         <x:v>0</x:v>
@@ -5867,21 +7365,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="55" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A55" s="40" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
+        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2019-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
         <x:v>0</x:v>
@@ -5890,21 +7388,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="56" ht="726" hidden="0" customHeight="1">
       <x:c r="A56" s="40" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>bmw-i8-charging-port-2014</x:v>
+        <x:v>bmw-m2-cooling-system-2016</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2020 | BMW | M2 | S55</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
+        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
         <x:v>0</x:v>
@@ -5913,21 +7411,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="57" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A57" s="40" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
+        <x:v>bmw-m2-dct-clutch-2016</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>2014-2015 | BMW | i8</x:v>
+        <x:v>2016-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
+        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
       </x:c>
       <x:c r="F57" s="9" t="n">
         <x:v>0</x:v>
@@ -5936,21 +7434,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="924" hidden="0" customHeight="1">
+    <x:row r="58" ht="462" hidden="0" customHeight="1">
       <x:c r="A58" s="40" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
+        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2021 | BMW | M2</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
+        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
-        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
+        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
       </x:c>
       <x:c r="F58" s="9" t="n">
         <x:v>0</x:v>
@@ -5959,21 +7457,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="59" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A59" s="40" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
+        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2018 | BMW | M2 | N55</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
+        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
-        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
+        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
       </x:c>
       <x:c r="F59" s="9" t="n">
         <x:v>0</x:v>
@@ -5982,21 +7480,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="60" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A60" s="40" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
+        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>2014-2014 | BMW | i8</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
+        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
       </x:c>
       <x:c r="F60" s="9" t="n">
         <x:v>0</x:v>
@@ -6005,21 +7503,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="726" hidden="0" customHeight="1">
+    <x:row r="61" ht="858" hidden="0" customHeight="1">
       <x:c r="A61" s="40" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>bmw-i8-hv-system-faults-2014</x:v>
+        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>2014-2017 | BMW | i8</x:v>
+        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
+        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
-        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
+        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
       </x:c>
       <x:c r="F61" s="9" t="n">
         <x:v>0</x:v>
@@ -6028,21 +7526,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="62" ht="462" hidden="0" customHeight="1">
       <x:c r="A62" s="40" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
+        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
+        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
       </x:c>
       <x:c r="F62" s="9" t="n">
         <x:v>0</x:v>
@@ -6051,21 +7549,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="63" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A63" s="40" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-2022</x:v>
+        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
-        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
+        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
       </x:c>
       <x:c r="F63" s="9" t="n">
         <x:v>0</x:v>
@@ -6074,21 +7572,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="64" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A64" s="40" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
+        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>Air Suspension Calibration Errors</x:v>
+        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
-        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
+        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
       </x:c>
       <x:c r="F64" s="9" t="n">
         <x:v>0</x:v>
@@ -6097,21 +7595,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="65" ht="528" hidden="0" customHeight="1">
       <x:c r="A65" s="40" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>bmw-ix-build-quality-2022</x:v>
+        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
+        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
+        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
       </x:c>
       <x:c r="F65" s="9" t="n">
         <x:v>0</x:v>
@@ -6120,21 +7618,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="66" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A66" s="40" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>bmw-ix-charging-failures-2022</x:v>
+        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
+        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
+        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
       </x:c>
       <x:c r="F66" s="9" t="n">
         <x:v>0</x:v>
@@ -6143,21 +7641,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="67" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A67" s="40" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
+        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>DC Fast Charging Speed Inconsistency</x:v>
+        <x:v>Rear Subframe Mounting Point Cracking</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
-        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
+        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
       </x:c>
       <x:c r="F67" s="9" t="n">
         <x:v>0</x:v>
@@ -6166,21 +7664,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="68" ht="594" hidden="0" customHeight="1">
       <x:c r="A68" s="40" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
+        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
       </x:c>
       <x:c r="F68" s="9" t="n">
         <x:v>0</x:v>
@@ -6189,21 +7687,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="69" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A69" s="40" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
+        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
+        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
-        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
+        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
       </x:c>
       <x:c r="F69" s="9" t="n">
         <x:v>0</x:v>
@@ -6212,21 +7710,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="70" ht="396" hidden="0" customHeight="1">
       <x:c r="A70" s="40" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
+        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
+        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
+        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
       </x:c>
       <x:c r="F70" s="9" t="n">
         <x:v>0</x:v>
@@ -6235,21 +7733,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="71" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A71" s="40" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="9" t="str">
-        <x:v>bmw-ix-phantom-braking-2022</x:v>
+        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D71" s="9" t="str">
-        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
+        <x:v>EDC Electronic Damper Control System Failure</x:v>
       </x:c>
       <x:c r="E71" s="9" t="str">
-        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
+        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
       </x:c>
       <x:c r="F71" s="9" t="n">
         <x:v>0</x:v>
@@ -6258,21 +7756,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="72" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A72" s="40" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
+        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
+        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
       </x:c>
       <x:c r="E72" s="9" t="str">
-        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
+        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
       </x:c>
       <x:c r="F72" s="9" t="n">
         <x:v>0</x:v>
@@ -6281,21 +7779,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="73" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A73" s="40" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="9" t="str">
-        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
+        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D73" s="9" t="str">
-        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
+        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
-        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
+        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
       </x:c>
       <x:c r="F73" s="9" t="n">
         <x:v>0</x:v>
@@ -6304,21 +7802,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="660" hidden="0" customHeight="1">
+    <x:row r="74" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A74" s="40" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="9" t="str">
-        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
+        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
+        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
+        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
       </x:c>
       <x:c r="F74" s="9" t="n">
         <x:v>0</x:v>
@@ -6327,21 +7825,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="528" hidden="0" customHeight="1">
+    <x:row r="75" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A75" s="40" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="9" t="str">
-        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
+        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D75" s="9" t="str">
-        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
+        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E75" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
+        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
       </x:c>
       <x:c r="F75" s="9" t="n">
         <x:v>0</x:v>
@@ -6350,21 +7848,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="76" ht="660" hidden="0" customHeight="1">
       <x:c r="A76" s="40" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="9" t="str">
-        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
+        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
-        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D76" s="9" t="str">
-        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
+        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
       </x:c>
       <x:c r="E76" s="9" t="str">
-        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
+        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
       </x:c>
       <x:c r="F76" s="9" t="n">
         <x:v>0</x:v>
@@ -6373,21 +7871,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="77" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A77" s="40" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="9" t="str">
-        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
+        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
+        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
       </x:c>
       <x:c r="E77" s="9" t="str">
-        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
+        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
       </x:c>
       <x:c r="F77" s="9" t="n">
         <x:v>0</x:v>
@@ -6396,21 +7894,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="78" ht="726" hidden="0" customHeight="1">
       <x:c r="A78" s="40" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="9" t="str">
-        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
+        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
-        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
+        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
       </x:c>
       <x:c r="E78" s="9" t="str">
-        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
+        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
       </x:c>
       <x:c r="F78" s="9" t="n">
         <x:v>0</x:v>
@@ -6419,44 +7917,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="79" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A79" s="40" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="9" t="str">
-        <x:v>bmw-m2-charge-pipe-2016</x:v>
+        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
-        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
+        <x:v>2015-2018 | BMW | M3</x:v>
       </x:c>
       <x:c r="D79" s="9" t="str">
-        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
+        <x:v>Direct Fuel Injector Failure (S55)</x:v>
       </x:c>
       <x:c r="E79" s="9" t="str">
-        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
+        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
       </x:c>
       <x:c r="F79" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G79" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="80" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A80" s="40" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="9" t="str">
-        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
+        <x:v>bmw-m3-f80-water-pump-2015</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
-        <x:v>2019-2020 | BMW | M2</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
-        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
+        <x:v>Electric Water Pump Failure (S55)</x:v>
       </x:c>
       <x:c r="E80" s="9" t="str">
-        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
+        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
       </x:c>
       <x:c r="F80" s="9" t="n">
         <x:v>0</x:v>
@@ -6465,21 +7963,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="726" hidden="0" customHeight="1">
+    <x:row r="81" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A81" s="40" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="9" t="str">
-        <x:v>bmw-m2-cooling-system-2016</x:v>
+        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2 | S55</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
-        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
+        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
-        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
+        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
       </x:c>
       <x:c r="F81" s="9" t="n">
         <x:v>0</x:v>
@@ -6488,21 +7986,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="82" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A82" s="40" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>bmw-m2-dct-clutch-2016</x:v>
+        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
+        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
       </x:c>
       <x:c r="E82" s="9" t="str">
-        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
+        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
       </x:c>
       <x:c r="F82" s="9" t="n">
         <x:v>0</x:v>
@@ -6511,21 +8009,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="462" hidden="0" customHeight="1">
+    <x:row r="83" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A83" s="40" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
+        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
-        <x:v>2016-2021 | BMW | M2</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
+        <x:v>Coolant System Issues (S58)</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
+        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
       </x:c>
       <x:c r="F83" s="9" t="n">
         <x:v>0</x:v>
@@ -6534,21 +8032,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="84" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A84" s="40" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
+        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>2016-2018 | BMW | M2 | N55</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
-        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
+        <x:v>iDrive 8 Software/Electronics Issues</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
+        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
       </x:c>
       <x:c r="F84" s="9" t="n">
         <x:v>0</x:v>
@@ -6557,21 +8055,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="85" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A85" s="40" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="9" t="str">
-        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
+        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>2021-2021 | BMW | M3</x:v>
       </x:c>
       <x:c r="D85" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
+        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
       </x:c>
       <x:c r="E85" s="9" t="str">
-        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
+        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
       </x:c>
       <x:c r="F85" s="9" t="n">
         <x:v>0</x:v>
@@ -6580,21 +8078,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="858" hidden="0" customHeight="1">
+    <x:row r="86" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A86" s="40" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="9" t="str">
-        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
+        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
-        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
-        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
+        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
-        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
+        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
       </x:c>
       <x:c r="F86" s="9" t="n">
         <x:v>0</x:v>
@@ -6603,21 +8101,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="462" hidden="0" customHeight="1">
+    <x:row r="87" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A87" s="40" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
+        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>Power window regulator failure and interior trim rattles</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
-        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
+        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
       </x:c>
       <x:c r="F87" s="9" t="n">
         <x:v>0</x:v>
@@ -6626,21 +8124,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="88" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A88" s="40" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="9" t="str">
-        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
+        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D88" s="9" t="str">
-        <x:v>VANOS Solenoid O-Ring Failure</x:v>
+        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
       </x:c>
       <x:c r="E88" s="9" t="str">
-        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
+        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
       </x:c>
       <x:c r="F88" s="9" t="n">
         <x:v>0</x:v>
@@ -6649,21 +8147,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="89" ht="343.20001220703125" hidden="0" customHeight="1">
       <x:c r="A89" s="40" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
+        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
-        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
+        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
+        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
       </x:c>
       <x:c r="F89" s="9" t="n">
         <x:v>0</x:v>
@@ -6672,21 +8170,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="528" hidden="0" customHeight="1">
+    <x:row r="90" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A90" s="40" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" s="9" t="str">
-        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
+        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D90" s="9" t="str">
-        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
+        <x:v>S55 Crank Hub Slip/Failure</x:v>
       </x:c>
       <x:c r="E90" s="9" t="str">
-        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
+        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
       </x:c>
       <x:c r="F90" s="9" t="n">
         <x:v>0</x:v>
@@ -6695,21 +8193,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="91" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A91" s="40" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" s="9" t="str">
-        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
+        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
       </x:c>
       <x:c r="D91" s="9" t="str">
-        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
+        <x:v>S55/S58 Electric Water Pump Failure</x:v>
       </x:c>
       <x:c r="E91" s="9" t="str">
-        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
+        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
       </x:c>
       <x:c r="F91" s="9" t="n">
         <x:v>0</x:v>
@@ -6718,21 +8216,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="92" ht="462" hidden="0" customHeight="1">
       <x:c r="A92" s="40" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" s="9" t="str">
-        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
+        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracking</x:v>
+        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
       </x:c>
       <x:c r="E92" s="9" t="str">
-        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
+        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
       </x:c>
       <x:c r="F92" s="9" t="n">
         <x:v>0</x:v>
@@ -6741,21 +8239,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="594" hidden="0" customHeight="1">
+    <x:row r="93" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A93" s="40" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" s="9" t="str">
-        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
+        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
-        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
+        <x:v>S65 Throttle Body Actuator Failure</x:v>
       </x:c>
       <x:c r="E93" s="9" t="str">
-        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
+        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
       </x:c>
       <x:c r="F93" s="9" t="n">
         <x:v>0</x:v>
@@ -6764,21 +8262,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="94" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A94" s="40" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
+        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
+        <x:v>VANOS Solenoid Wear and Failure</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
-        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
+        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
       </x:c>
       <x:c r="F94" s="9" t="n">
         <x:v>0</x:v>
@@ -6787,21 +8285,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="396" hidden="0" customHeight="1">
+    <x:row r="95" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A95" s="40" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="9" t="str">
-        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
+        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D95" s="9" t="str">
-        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
+        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
       </x:c>
       <x:c r="E95" s="9" t="str">
-        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
+        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals, often combined with an anti-rattle kit that addresses the cam-gear/shaft play. DIY on the seal kit is common; specialists also offer fully rebuilt exchange units.</x:v>
       </x:c>
       <x:c r="F95" s="9" t="n">
         <x:v>0</x:v>
@@ -6810,21 +8308,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="96" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A96" s="40" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" s="9" t="str">
-        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
+        <x:v>bmw-m3-worn-rear-trailing-arm-bushings-suspension-mounts</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>EDC Electronic Damper Control System Failure</x:v>
+        <x:v>Worn rear trailing arm bushings (RTAB) and suspension mounts</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
-        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
+        <x:v>Replace the RTABs with genuine BMW rubber bushings or upgraded poly/spherical bushings; many owners add RTAB limiter kits to reduce deflection. Inspect and renew rear shock mounts and engine/transmission mounts at the same time. The RTAB job is a common DIY that can be done with the trailing arms on the car.</x:v>
       </x:c>
       <x:c r="F96" s="9" t="n">
         <x:v>0</x:v>
@@ -6833,21 +8331,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="97" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A97" s="40" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" s="9" t="str">
-        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
+        <x:v>bmw-m340i-12v-battery-drain-failure-battery-registration-issues</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
-        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
+        <x:v>2019-2024 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D97" s="9" t="str">
-        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
+        <x:v>12V Battery Drain and Failure / Battery Registration Issues</x:v>
       </x:c>
       <x:c r="E97" s="9" t="str">
-        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
+        <x:v>Test and replace the AGM battery with the correct OEM-spec unit, then register the new battery with BimmerLink/ISTA so the charging strategy adapts. Diagnose parasitic drain and a faulty IBS cable/sensor if discharge persists. Drive long enough to fully recharge between trips.</x:v>
       </x:c>
       <x:c r="F97" s="9" t="n">
         <x:v>0</x:v>
@@ -6856,21 +8354,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="884.4000244140625" hidden="0" customHeight="1">
+    <x:row r="98" ht="528" hidden="0" customHeight="1">
       <x:c r="A98" s="40" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" s="9" t="str">
-        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
+        <x:v>bmw-m340i-b58-carbon-buildup-2020</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D98" s="9" t="str">
-        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
+        <x:v>Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E98" s="9" t="str">
-        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
+        <x:v>Walnut blast the intake valves every 50,000-60,000 miles. This involves removing the intake manifold and blasting walnut shell media at the valve backs to remove carbon deposits. Some owners use catch cans to reduce oil vapor entering the intake. BMW's official position is that carbon buildup is normal for direct-injection engines.</x:v>
       </x:c>
       <x:c r="F98" s="9" t="n">
         <x:v>0</x:v>
@@ -6879,21 +8377,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="99" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A99" s="40" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" s="9" t="str">
-        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
+        <x:v>bmw-m340i-b58-coolant-loss-2020</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D99" s="9" t="str">
-        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
+        <x:v>Coolant Loss from Expansion Tank and Water Pump</x:v>
       </x:c>
       <x:c r="E99" s="9" t="str">
-        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
+        <x:v>Replace the coolant expansion tank at first sign of cracking. Proactively replace the electric water pump before 60,000 miles. Replace the coolant vent line per BMW TSB. Use only BMW-approved blue coolant. Monitor coolant level monthly and pressure test the cooling system at every major service.</x:v>
       </x:c>
       <x:c r="F99" s="9" t="n">
         <x:v>0</x:v>
@@ -6902,21 +8400,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="100" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A100" s="40" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" s="9" t="str">
-        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
+        <x:v>bmw-m340i-b58-hpfp-failure-2020</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D100" s="9" t="str">
-        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
       </x:c>
       <x:c r="E100" s="9" t="str">
-        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
+        <x:v>Replace the high-pressure fuel pump with the latest revised BMW part number. Verify the low-pressure fuel pump is providing adequate feed pressure. Use top-tier fuel and avoid running the tank below 1/4 to reduce strain on the fuel system. If under warranty, BMW will cover HPFP replacement.</x:v>
       </x:c>
       <x:c r="F100" s="9" t="n">
         <x:v>0</x:v>
@@ -6925,21 +8423,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="660" hidden="0" customHeight="1">
+    <x:row r="101" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A101" s="40" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" s="9" t="str">
-        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
+        <x:v>bmw-m340i-b58-oil-filter-disintegration-2020</x:v>
       </x:c>
       <x:c r="C101" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6, B58</x:v>
       </x:c>
       <x:c r="D101" s="9" t="str">
-        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
+        <x:v>Oil Filter Disintegration in Housing</x:v>
       </x:c>
       <x:c r="E101" s="9" t="str">
-        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
+        <x:v>Use only genuine BMW or Mann-branded oil filters (Mann is the OEM supplier). Change oil and filter every 5,000-7,000 miles rather than BMW's recommended 10,000-mile interval. When removing the old filter, inspect it carefully for signs of deterioration. If filter fragments are found in the housing, flush the housing thoroughly before installing the new filter.</x:v>
       </x:c>
       <x:c r="F101" s="9" t="n">
         <x:v>0</x:v>
@@ -6948,21 +8446,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="102" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A102" s="40" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B102" s="9" t="str">
-        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
+        <x:v>bmw-m340i-b58-wastegate-rattle-2020</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D102" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
+        <x:v>Turbo Wastegate Rattle at Idle</x:v>
       </x:c>
       <x:c r="E102" s="9" t="str">
-        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
+        <x:v>Have the wastegate actuator inspected for excessive play. Minor rattle without fault codes can be monitored. If boost control faults develop, replace the turbocharger wastegate actuator. In severe cases, the entire turbocharger assembly may need replacement. BMW may cover under warranty if fault codes are present.</x:v>
       </x:c>
       <x:c r="F102" s="9" t="n">
         <x:v>0</x:v>
@@ -6971,21 +8469,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="726" hidden="0" customHeight="1">
+    <x:row r="103" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A103" s="40" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B103" s="9" t="str">
-        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
+        <x:v>bmw-m340i-loss-brake-assist-from-brake-vacuum-pump-damage</x:v>
       </x:c>
       <x:c r="C103" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2020-2020 | BMW | M340i | B58 3.0L turbo inline-six</x:v>
       </x:c>
       <x:c r="D103" s="9" t="str">
-        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
+        <x:v>2020 M340i Brake-Assist Recall 21V-598</x:v>
       </x:c>
       <x:c r="E103" s="9" t="str">
-        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
+        <x:v>Check the VIN for an open 21V-598 campaign. An authorized BMW dealer updates the engine-management software free of charge and replaces the combined oil/vacuum pump if diagnosis shows it was already damaged. Do not order generic brake-vacuum parts from this card.</x:v>
       </x:c>
       <x:c r="F103" s="9" t="n">
         <x:v>0</x:v>
@@ -6994,44 +8492,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="104" ht="462" hidden="0" customHeight="1">
       <x:c r="A104" s="40" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
+        <x:v>bmw-m340i-seat-belt-warning-audio-failure</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3</x:v>
+        <x:v>2019-2022 | BMW | M340i</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
-        <x:v>Direct Fuel Injector Failure (S55)</x:v>
+        <x:v>2019-2022 M340i Seat-Belt Warning Recall 23V-584</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
-        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
+        <x:v>Check the VIN for an open 23V-584 campaign. An authorized BMW dealer installs updated Receiver Audio Module software free of charge; eligible vehicles may also receive the remedy by BMW Remote Software Upgrade. Always use the seat belt regardless of warning-chime behavior.</x:v>
       </x:c>
       <x:c r="F104" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G104" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="105" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A105" s="40" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B105" s="9" t="str">
-        <x:v>bmw-m3-f80-water-pump-2015</x:v>
+        <x:v>bmw-m340i-valve-cover-oil-filter-housing-gasket-oil-leaks</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D105" s="9" t="str">
-        <x:v>Electric Water Pump Failure (S55)</x:v>
+        <x:v>Valve Cover and Oil Filter Housing Gasket Oil Leaks (B58)</x:v>
       </x:c>
       <x:c r="E105" s="9" t="str">
-        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
+        <x:v>Replace the valve cover gasket and/or oil filter housing gasket. Many shops also replace the valve cover itself if it has warped. Clean any oil from spark-plug wells and inspect coils. Typical independent-shop cost is roughly $400-$900 depending on which gasket(s) and labor access.</x:v>
       </x:c>
       <x:c r="F105" s="9" t="n">
         <x:v>0</x:v>
@@ -7040,21 +8538,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="106" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A106" s="40" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B106" s="9" t="str">
-        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
+        <x:v>bmw-m340i-vanos-solenoid-o-ring-failure</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D106" s="9" t="str">
-        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E106" s="9" t="str">
-        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
+        <x:v>Diagnose with a scan tool (VANOS/camshaft position fault codes), then replace the affected intake/exhaust VANOS solenoid(s) and O-rings. Solenoids are relatively inexpensive parts; cost is mostly diagnosis and labor, typically a few hundred dollars.</x:v>
       </x:c>
       <x:c r="F106" s="9" t="n">
         <x:v>0</x:v>
@@ -7068,16 +8566,16 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B107" s="9" t="str">
-        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
+        <x:v>bmw-m340i-zf-8hp-harsh-jerky-low-speed-shifting-mechatronic-faults</x:v>
       </x:c>
       <x:c r="C107" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D107" s="9" t="str">
-        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
+        <x:v>ZF 8HP Harsh / Jerky Low-Speed Shifting and Mechatronic Faults</x:v>
       </x:c>
       <x:c r="E107" s="9" t="str">
-        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
+        <x:v>Perform the ZF 8-speed fluid-and-filter (pan) service rather than treating it as lifetime-fill; this resolves many shift-quality complaints. Let the drivetrain warm before hard driving. For persistent erratic shifting or warning lights, scan the transmission and repair/replace the mechatronic unit (valve body) as needed.</x:v>
       </x:c>
       <x:c r="F107" s="9" t="n">
         <x:v>0</x:v>
@@ -7086,21 +8584,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="108" ht="594" hidden="0" customHeight="1">
       <x:c r="A108" s="40" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B108" s="9" t="str">
-        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
+        <x:v>bmw-m3cs-idrive-software-2024</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D108" s="9" t="str">
-        <x:v>Coolant System Issues (S58)</x:v>
+        <x:v>iDrive 8 Software Glitches and Screen Blackouts</x:v>
       </x:c>
       <x:c r="E108" s="9" t="str">
-        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
+        <x:v>Check for and install the latest BMW iDrive 8 software updates, which can be delivered over-the-air or at a dealer. Perform a soft reset by holding the iDrive controller button for 30 seconds. If screen blackouts persist, the dealer may need to replace the head unit or update the gateway module firmware. Ensure the 12V battery is in good condition, as low voltage can trigger software instability.</x:v>
       </x:c>
       <x:c r="F108" s="9" t="n">
         <x:v>0</x:v>
@@ -7109,21 +8607,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="109" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A109" s="40" t="n">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B109" s="9" t="str">
-        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
+        <x:v>bmw-m3cs-s58-carbon-buildup-2024</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D109" s="9" t="str">
-        <x:v>iDrive 8 Software/Electronics Issues</x:v>
+        <x:v>S58 Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E109" s="9" t="str">
-        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
+        <x:v>Schedule walnut blast cleaning of the intake valves at 40,000-50,000 mile intervals. Install an oil catch can to reduce oil vapor entering the intake system. Use high-quality synthetic oil meeting BMW LL-01 specification and change at 5,000-7,000 mile intervals. Allow the engine to fully warm up before high-boost driving to ensure proper oil vapor management.</x:v>
       </x:c>
       <x:c r="F109" s="9" t="n">
         <x:v>0</x:v>
@@ -7132,21 +8630,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="110" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A110" s="40" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
+        <x:v>bmw-m3cs-s58-charge-pipe-crack-2024</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>2021-2021 | BMW | M3</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
+        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF. These direct-fit replacements handle higher temperatures and pressures without risk of cracking. If the car is under warranty and the failure occurs on stock tune, BMW should cover the repair. Inspect the charge pipe during every service and before track days.</x:v>
       </x:c>
       <x:c r="F110" s="9" t="n">
         <x:v>0</x:v>
@@ -7155,21 +8653,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="111" ht="396" hidden="0" customHeight="1">
       <x:c r="A111" s="40" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B111" s="9" t="str">
-        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
+        <x:v>bmw-m4-charge-pipe-blowoff-2015</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
-        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
+        <x:v>Plastic Charge Pipe Blow-Off Under Boost</x:v>
       </x:c>
       <x:c r="E111" s="9" t="str">
-        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
+        <x:v>Replace with an aluminum or silicone charge pipe. This is considered a must-do upgrade for any F82 M4. Many aftermarket options are direct bolt-on replacements. The job takes about 1-2 hours and requires removing the intake duct to access the charge pipe.</x:v>
       </x:c>
       <x:c r="F111" s="9" t="n">
         <x:v>0</x:v>
@@ -7178,21 +8676,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="112" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A112" s="40" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
+        <x:v>bmw-m4-convertible-top-2015</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>Power window regulator failure and interior trim rattles</x:v>
+        <x:v>Convertible Top Hydraulic Pump Failure - F83 M4 Convertible</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
-        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
+        <x:v>Diagnose specific failure: hydraulic pump motor, lines, microswitches, or latch mechanisms. Pump motor replacement is most common ($1,500-2,500). Check hydraulic fluid level and refill if low. Regular top cycling (minimum once per month) prevents seal degradation. Store with top UP to reduce strain on hydraulic system. Rebuilt hydraulic pumps available at lower cost than new OEM. Complex repair requiring specialized BMW knowledge.</x:v>
       </x:c>
       <x:c r="F112" s="9" t="n">
         <x:v>0</x:v>
@@ -7201,21 +8699,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="113" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A113" s="40" t="n">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B113" s="9" t="str">
-        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
+        <x:v>bmw-m4-cooling-track-2015</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
-        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
-        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
+        <x:v>Install comprehensive cooling upgrades for track use: CSF or Mishimoto high-capacity radiator, aftermarket oil cooler, upgraded intercoolers (Wagner, CSF), and transmission cooler. Remove kidney grille blockage for improved airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Total cooling system upgrade costs $3,000-5,000 but essential for serious track use. For street-only M4s, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F113" s="9" t="n">
         <x:v>0</x:v>
@@ -7224,21 +8722,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="114" ht="462" hidden="0" customHeight="1">
       <x:c r="A114" s="40" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B114" s="9" t="str">
-        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
+        <x:v>bmw-m4-crank-hub-bolt-2015</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
-        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
+        <x:v>S55 Crank Hub Bolt Loosening</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
-        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
+        <x:v>Replace with an upgraded aftermarket crank hub bolt (ARP or IND). The job requires removing the radiator fan, accessory belt, and harmonic balancer to access the bolt. Use proper torque specs for the upgraded bolt. This is a preventative maintenance item for any M4 owner.</x:v>
       </x:c>
       <x:c r="F114" s="9" t="n">
         <x:v>0</x:v>
@@ -7247,21 +8745,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="115" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A115" s="40" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B115" s="9" t="str">
-        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
+        <x:v>bmw-m4-dct-clutch-2015</x:v>
       </x:c>
       <x:c r="C115" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D115" s="9" t="str">
-        <x:v>S55 Crank Hub Slip/Failure</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E115" s="9" t="str">
-        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
+        <x:v>Replace DCT clutch pack when symptoms appear. BMW recommends replacing all clutches together. Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use (limit to special occasions). Transmission adaptation reset via BMW software may temporarily improve shift quality. Extended warranty highly recommended for DCT-equipped M4s. Labor-intensive repair requires transmission removal.</x:v>
       </x:c>
       <x:c r="F115" s="9" t="n">
         <x:v>0</x:v>
@@ -7270,21 +8768,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="116" ht="462" hidden="0" customHeight="1">
       <x:c r="A116" s="40" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B116" s="9" t="str">
-        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
+        <x:v>bmw-m4-rear-subframe-crack-2015</x:v>
       </x:c>
       <x:c r="C116" s="9" t="str">
-        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
+        <x:v>2015-2026 | BMW | M4</x:v>
       </x:c>
       <x:c r="D116" s="9" t="str">
-        <x:v>S55/S58 Electric Water Pump Failure</x:v>
+        <x:v>Rear Subframe Cracking From Track Use</x:v>
       </x:c>
       <x:c r="E116" s="9" t="str">
-        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
+        <x:v>Inspect subframe mounting points and welds regularly if the car sees track use. Reinforce with aftermarket subframe reinforcement plates or weld-in gussets. Severely cracked subframes must be replaced entirely. Upgraded subframe bushings (solid or reinforced) help distribute loads more evenly.</x:v>
       </x:c>
       <x:c r="F116" s="9" t="n">
         <x:v>0</x:v>
@@ -7293,21 +8791,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="462" hidden="0" customHeight="1">
+    <x:row r="117" ht="805.2000122070312" hidden="0" customHeight="1">
       <x:c r="A117" s="40" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B117" s="9" t="str">
-        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
+        <x:v>bmw-m4-s55-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
-        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
-        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway) that eliminates the slipping issue permanently. Installation requires crankshaft pulley removal and precise torque specs. This upgrade is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Cost is $1,200-2,500 installed vs. $20,000+ for engine replacement after failure.</x:v>
       </x:c>
       <x:c r="F117" s="9" t="n">
         <x:v>0</x:v>
@@ -7316,44 +8814,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="118" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A118" s="40" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B118" s="9" t="str">
-        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
+        <x:v>bmw-m4-s55-injector-2015</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
-        <x:v>S65 Throttle Body Actuator Failure</x:v>
+        <x:v>S55 High-Pressure Fuel Injector Failure - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
-        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
+        <x:v>Replace all 6 injectors together to prevent repeat repairs. Perform walnut blast carbon cleaning on intake valves while injectors are removed (labor overlap saves $400-600). Use Top Tier gasoline to minimize carbon buildup. Add fuel system cleaner (Liqui Moly Valve Clean) every 5,000 miles to reduce carbon deposits. BMW parts are expensive; some shops use OEM Bosch injectors at lower cost. Labor is 4-6 hours for injector replacement.</x:v>
       </x:c>
       <x:c r="F118" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G118" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="250.8000030517578" hidden="0" customHeight="1">
+    <x:row r="119" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A119" s="40" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B119" s="9" t="str">
-        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
+        <x:v>bmw-m4-s55-rod-bearing-2015</x:v>
       </x:c>
       <x:c r="C119" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>VANOS Solenoid Wear and Failure</x:v>
+        <x:v>S55 Rod Bearing Premature Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E119" s="9" t="str">
-        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
+        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles or before extensive track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability than OEM. Regular oil analysis (Blackstone Labs) every 5,000 miles to monitor bearing wear. Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max. Track-focused M4s should replace bearings every 50,000 miles. Labor is 8-12 hours, so many owners do this during clutch replacement.</x:v>
       </x:c>
       <x:c r="F119" s="9" t="n">
         <x:v>0</x:v>
@@ -7362,21 +8860,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="120" ht="660" hidden="0" customHeight="1">
       <x:c r="A120" s="40" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B120" s="9" t="str">
-        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
+        <x:v>bmw-m4cs-brake-wear-track-2024</x:v>
       </x:c>
       <x:c r="C120" s="9" t="str">
-        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D120" s="9" t="str">
-        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
+        <x:v>Rapid Brake Pad and Rotor Wear from Track Use</x:v>
       </x:c>
       <x:c r="E120" s="9" t="str">
-        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals, often combined with an anti-rattle kit that addresses the cam-gear/shaft play. DIY on the seal kit is common; specialists also offer fully rebuilt exchange units.</x:v>
+        <x:v>Inspect brake pads and rotors before and after every track day. Consider upgrading to aftermarket performance pads like Pagid RSC or Hawk DTC-70 for track use, and switch to street pads for daily driving. For frequent track users, the optional carbon ceramic brake package significantly extends rotor life. Use high-temperature brake fluid (DOT 5.1 or racing fluid) and flush before every track season.</x:v>
       </x:c>
       <x:c r="F120" s="9" t="n">
         <x:v>0</x:v>
@@ -7385,21 +8883,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="121" ht="462" hidden="0" customHeight="1">
       <x:c r="A121" s="40" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B121" s="9" t="str">
-        <x:v>bmw-m3-worn-rear-trailing-arm-bushings-suspension-mounts</x:v>
+        <x:v>bmw-m4cs-s58-carbon-buildup-2024</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
-        <x:v>Worn rear trailing arm bushings (RTAB) and suspension mounts</x:v>
+        <x:v>S58 Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
-        <x:v>Replace the RTABs with genuine BMW rubber bushings or upgraded poly/spherical bushings; many owners add RTAB limiter kits to reduce deflection. Inspect and renew rear shock mounts and engine/transmission mounts at the same time. The RTAB job is a common DIY that can be done with the trailing arms on the car.</x:v>
+        <x:v>Walnut blast the intake valves every 40,000-50,000 miles. Consider installing an oil catch can to reduce oil vapor ingestion. Maintain strict 5,000-7,000 mile oil change intervals with BMW LL-01 approved oil. Allow full engine warmup before spirited driving to ensure proper crankcase ventilation operation.</x:v>
       </x:c>
       <x:c r="F121" s="9" t="n">
         <x:v>0</x:v>
@@ -7408,21 +8906,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="122" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A122" s="40" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B122" s="9" t="str">
-        <x:v>bmw-m340i-12v-battery-drain-failure-battery-registration-issues</x:v>
+        <x:v>bmw-m4cs-s58-charge-pipe-crack-2024</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
-        <x:v>2019-2024 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D122" s="9" t="str">
-        <x:v>12V Battery Drain and Failure / Battery Registration Issues</x:v>
+        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
       </x:c>
       <x:c r="E122" s="9" t="str">
-        <x:v>Test and replace the AGM battery with the correct OEM-spec unit, then register the new battery with BimmerLink/ISTA so the charging strategy adapts. Diagnose parasitic drain and a faulty IBS cable/sensor if discharge persists. Drive long enough to fully recharge between trips.</x:v>
+        <x:v>Proactively replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF before any track use. These bolt-on replacements are rated for boost pressures well beyond what the S58 produces. Inspect the charge pipe at every service interval for signs of stress cracking or discoloration.</x:v>
       </x:c>
       <x:c r="F122" s="9" t="n">
         <x:v>0</x:v>
@@ -7431,21 +8929,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="528" hidden="0" customHeight="1">
+    <x:row r="123" ht="660" hidden="0" customHeight="1">
       <x:c r="A123" s="40" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B123" s="9" t="str">
-        <x:v>bmw-m340i-b58-carbon-buildup-2020</x:v>
+        <x:v>bmw-m5-absdsc-module-failure-triggering-2000</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D123" s="9" t="str">
-        <x:v>Intake Valve Carbon Buildup</x:v>
+        <x:v>ABS/DSC Module Failure Triggering ABS, Brake, and Traction Control Warning Lights</x:v>
       </x:c>
       <x:c r="E123" s="9" t="str">
-        <x:v>Walnut blast the intake valves every 50,000-60,000 miles. This involves removing the intake manifold and blasting walnut shell media at the valve backs to remove carbon deposits. Some owners use catch cans to reduce oil vapor entering the intake. BMW's official position is that carbon buildup is normal for direct-injection engines.</x:v>
+        <x:v>Diagnosis should begin with scanning the ABS/DSC module for communication or wheel-speed sensor faults and verifying power, ground, and sensor signals. If the module intermittently loses communication or shows implausible internal faults, the usual repair is module rebuild or replacement, followed by coding if required. Wheel speed sensors should only be replaced after confirming they are actually faulty.</x:v>
       </x:c>
       <x:c r="F123" s="9" t="n">
         <x:v>0</x:v>
@@ -7454,21 +8952,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="124" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A124" s="40" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B124" s="9" t="str">
-        <x:v>bmw-m340i-b58-coolant-loss-2020</x:v>
+        <x:v>bmw-m5-clutch-slave-cylinder-and-2000</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D124" s="9" t="str">
-        <x:v>Coolant Loss from Expansion Tank and Water Pump</x:v>
+        <x:v>Clutch Slave Cylinder and Hydraulic Line Failure Causing Soft Pedal and Shift Engagement Problems</x:v>
       </x:c>
       <x:c r="E124" s="9" t="str">
-        <x:v>Replace the coolant expansion tank at first sign of cracking. Proactively replace the electric water pump before 60,000 miles. Replace the coolant vent line per BMW TSB. Use only BMW-approved blue coolant. Monitor coolant level monthly and pressure test the cooling system at every major service.</x:v>
+        <x:v>Inspect the clutch hydraulic circuit for fluid leakage at the slave cylinder, master cylinder, and line connections, and verify brake/clutch fluid condition. Replace the failed slave cylinder and often the flexible hose, then bleed the system thoroughly; if symptoms persist, inspect the clutch, pressure plate, and pilot bearing.</x:v>
       </x:c>
       <x:c r="F124" s="9" t="n">
         <x:v>0</x:v>
@@ -7477,21 +8975,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="475.20001220703125" hidden="0" customHeight="1">
+    <x:row r="125" ht="1108.800048828125" hidden="0" customHeight="1">
       <x:c r="A125" s="40" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B125" s="9" t="str">
-        <x:v>bmw-m340i-b58-hpfp-failure-2020</x:v>
+        <x:v>bmw-m5-dct-clutch-2012</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2012-2016 | BMW | M5</x:v>
       </x:c>
       <x:c r="D125" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
+        <x:v>DCT Dual-Clutch Transmission Wear &amp; Judder - F10 M5</x:v>
       </x:c>
       <x:c r="E125" s="9" t="str">
-        <x:v>Replace the high-pressure fuel pump with the latest revised BMW part number. Verify the low-pressure fuel pump is providing adequate feed pressure. Use top-tier fuel and avoid running the tank below 1/4 to reduce strain on the fuel system. If under warranty, BMW will cover HPFP replacement.</x:v>
+        <x:v>PREVENTIVE: Replace DCT transmission fluid and filter every 30,000-50,000 miles (BMW says "lifetime" but this causes premature failure). Use ONLY BMW DCTF-1 specification fluid ($189-$253 service, DIY: $100-$150). For judder/jerkiness: try fluid change and software update FIRST before clutch replacement - many issues resolved this way. For severe clutch wear: replace dual-clutch assembly with OEM ($2,394-$2,567 typical, $3,000-$4,000 dealership) or upgraded performance clutch kit. Consider NRC TitanTec or CNS Racing upgraded DCT clutch packs for improved durability if used for performance driving/track. Complete DCT transmission replacement: $8,000-$12,000.</x:v>
       </x:c>
       <x:c r="F125" s="9" t="n">
         <x:v>0</x:v>
@@ -7500,21 +8998,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="126" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A126" s="40" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>bmw-m340i-b58-oil-filter-disintegration-2020</x:v>
+        <x:v>bmw-m5-door-vapor-barrier-and-2000</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6, B58</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
-        <x:v>Oil Filter Disintegration in Housing</x:v>
+        <x:v>Door Vapor Barrier and Sunroof Drain Leaks Causing Wet Carpets and Electrical Problems</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>Use only genuine BMW or Mann-branded oil filters (Mann is the OEM supplier). Change oil and filter every 5,000-7,000 miles rather than BMW's recommended 10,000-mile interval. When removing the old filter, inspect it carefully for signs of deterioration. If filter fragments are found in the housing, flush the housing thoroughly before installing the new filter.</x:v>
+        <x:v>Remove the door panel and inspect the vapor barrier seal, especially along the lower edge, and verify all sunroof drains flow freely and exit properly. Reseal the vapor barrier with butyl ribbon or equivalent body sealer, clear the drains, dry the carpet and padding thoroughly, and inspect under-carpet wiring/connectors for corrosion.</x:v>
       </x:c>
       <x:c r="F126" s="9" t="n">
         <x:v>0</x:v>
@@ -7523,21 +9021,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="127" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A127" s="40" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B127" s="9" t="str">
-        <x:v>bmw-m340i-b58-wastegate-rattle-2020</x:v>
+        <x:v>bmw-m5-e39-m5-vanos-solenoidseal-2000</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>Turbo Wastegate Rattle at Idle</x:v>
+        <x:v>E39 M5 VANOS Solenoid/Seal Failure Causing Rattle, Power Loss, and Check Engine Lights</x:v>
       </x:c>
       <x:c r="E127" s="9" t="str">
-        <x:v>Have the wastegate actuator inspected for excessive play. Minor rattle without fault codes can be monitored. If boost control faults develop, replace the turbocharger wastegate actuator. In severe cases, the entire turbocharger assembly may need replacement. BMW may cover under warranty if fault codes are present.</x:v>
+        <x:v>Diagnosis typically includes scanning for camshaft timing and VANOS activation faults, checking oil condition/pressure, and listening for startup rattle from the front of the engine. Repair usually involves rebuilding the VANOS units with upgraded seals, replacing failed solenoids or solenoid seals, and correcting any oil leaks or timing-related wear. Many owners address both banks preventively while the front of engine is apart.</x:v>
       </x:c>
       <x:c r="F127" s="9" t="n">
         <x:v>0</x:v>
@@ -7551,16 +9049,16 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B128" s="9" t="str">
-        <x:v>bmw-m340i-loss-brake-assist-from-brake-vacuum-pump-damage</x:v>
+        <x:v>bmw-m5-front-thrust-arm-bushing-2000</x:v>
       </x:c>
       <x:c r="C128" s="9" t="str">
-        <x:v>2020-2020 | BMW | M340i | B58 3.0L turbo inline-six</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D128" s="9" t="str">
-        <x:v>2020 M340i Brake-Assist Recall 21V-598</x:v>
+        <x:v>Front Thrust Arm Bushing Failure Causing 50-60 MPH Brake Shimmy and Steering Vibration</x:v>
       </x:c>
       <x:c r="E128" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-598 campaign. An authorized BMW dealer updates the engine-management software free of charge and replaces the combined oil/vacuum pump if diagnosis shows it was already damaged. Do not order generic brake-vacuum parts from this card.</x:v>
+        <x:v>Inspect the front thrust arms and control arms for bushing cracks, fluid leakage from hydro-bushings, and ball-joint play. Replace the thrust arms or complete front control arm set, then perform a proper alignment; if brake pulsation remains, inspect rotor runout and wheel balance.</x:v>
       </x:c>
       <x:c r="F128" s="9" t="n">
         <x:v>0</x:v>
@@ -7569,21 +9067,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="462" hidden="0" customHeight="1">
+    <x:row r="129" ht="594" hidden="0" customHeight="1">
       <x:c r="A129" s="40" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B129" s="9" t="str">
-        <x:v>bmw-m340i-seat-belt-warning-audio-failure</x:v>
+        <x:v>bmw-m5-getrag-420g-6-speed-synchro-2000</x:v>
       </x:c>
       <x:c r="C129" s="9" t="str">
-        <x:v>2019-2022 | BMW | M340i</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D129" s="9" t="str">
-        <x:v>2019-2022 M340i Seat-Belt Warning Recall 23V-584</x:v>
+        <x:v>Getrag 420G 6-Speed Synchro Wear and 2nd/3rd Gear Grinding</x:v>
       </x:c>
       <x:c r="E129" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-584 campaign. An authorized BMW dealer installs updated Receiver Audio Module software free of charge; eligible vehicles may also receive the remedy by BMW Remote Software Upgrade. Always use the seat belt regardless of warning-chime behavior.</x:v>
+        <x:v>Diagnosis involves road testing hot and cold, checking clutch release operation, and ruling out worn transmission mounts or old fluid before condemning the gearbox. Mild cases may improve with fresh fluid, but persistent grinding usually requires transmission rebuild with new synchros, bearings, and wear components. Clutch and shifter bushings are often serviced at the same time.</x:v>
       </x:c>
       <x:c r="F129" s="9" t="n">
         <x:v>0</x:v>
@@ -7592,21 +9090,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="130" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A130" s="40" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B130" s="9" t="str">
-        <x:v>bmw-m340i-valve-cover-oil-filter-housing-gasket-oil-leaks</x:v>
+        <x:v>bmw-m5-ignition-coils-2012</x:v>
       </x:c>
       <x:c r="C130" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2012-2023 | BMW | M5 | S63, S63TU</x:v>
       </x:c>
       <x:c r="D130" s="9" t="str">
-        <x:v>Valve Cover and Oil Filter Housing Gasket Oil Leaks (B58)</x:v>
+        <x:v>S63/S63TU Ignition Coil Premature Failure</x:v>
       </x:c>
       <x:c r="E130" s="9" t="str">
-        <x:v>Replace the valve cover gasket and/or oil filter housing gasket. Many shops also replace the valve cover itself if it has warped. Clean any oil from spark-plug wells and inspect coils. Typical independent-shop cost is roughly $400-$900 depending on which gasket(s) and labor access.</x:v>
+        <x:v>Replace failed ignition coil(s) immediately to prevent catalytic converter damage ($3,000-$5,000 additional). When one coil fails, M5Post recommends replacing all 8 coils as preventative maintenance ($600-$900 parts + labor) - they typically fail within similar timeframes and saves second service visit. Use OEM Bosch coils for best reliability ($50-$80 each) - aftermarket options fail even faster on S63 due to heat and electrical demands. Replace spark plugs simultaneously if mileage exceeds 30,000 miles ($280-$320 for 8 plugs). Labor: 1-2 hours. Single coil replacement: $179-$235.</x:v>
       </x:c>
       <x:c r="F130" s="9" t="n">
         <x:v>0</x:v>
@@ -7615,21 +9113,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="131" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A131" s="40" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B131" s="9" t="str">
-        <x:v>bmw-m340i-vanos-solenoid-o-ring-failure</x:v>
+        <x:v>bmw-m5-instrument-cluster-pixel-failure-2000</x:v>
       </x:c>
       <x:c r="C131" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D131" s="9" t="str">
-        <x:v>VANOS Solenoid O-Ring Failure</x:v>
+        <x:v>Instrument Cluster Pixel Failure and MID Display Dropout</x:v>
       </x:c>
       <x:c r="E131" s="9" t="str">
-        <x:v>Diagnose with a scan tool (VANOS/camshaft position fault codes), then replace the affected intake/exhaust VANOS solenoid(s) and O-rings. Solenoids are relatively inexpensive parts; cost is mostly diagnosis and labor, typically a few hundred dollars.</x:v>
+        <x:v>Diagnosis is usually visual, confirming missing display segments in the cluster or MID. Repair involves replacing or rebuilding the cluster/MID display ribbon and screen components, or sending the unit to a specialist rebuilder. Used replacement clusters require coding and mileage tamper considerations, so rebuild is often preferred.</x:v>
       </x:c>
       <x:c r="F131" s="9" t="n">
         <x:v>0</x:v>
@@ -7638,21 +9136,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="132" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A132" s="40" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B132" s="9" t="str">
-        <x:v>bmw-m340i-zf-8hp-harsh-jerky-low-speed-shifting-mechatronic-faults</x:v>
+        <x:v>bmw-m5-maf-sensor-degradation-causing-2000</x:v>
       </x:c>
       <x:c r="C132" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D132" s="9" t="str">
-        <x:v>ZF 8HP Harsh / Jerky Low-Speed Shifting and Mechatronic Faults</x:v>
+        <x:v>MAF Sensor Degradation Causing Lean Codes, Hesitation, and Reduced Power</x:v>
       </x:c>
       <x:c r="E132" s="9" t="str">
-        <x:v>Perform the ZF 8-speed fluid-and-filter (pan) service rather than treating it as lifetime-fill; this resolves many shift-quality complaints. Let the drivetrain warm before hard driving. For persistent erratic shifting or warning lights, scan the transmission and repair/replace the mechatronic unit (valve body) as needed.</x:v>
+        <x:v>Scan for fuel-trim and MAF-related faults, inspect for intake leaks first, then compare live airflow values bank-to-bank. If readings are implausible or one bank differs significantly, replace the affected MAF sensor(s) with OE-quality parts and clear adaptations; also inspect intake boots and air filter condition.</x:v>
       </x:c>
       <x:c r="F132" s="9" t="n">
         <x:v>0</x:v>
@@ -7661,21 +9159,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="594" hidden="0" customHeight="1">
+    <x:row r="133" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A133" s="40" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B133" s="9" t="str">
-        <x:v>bmw-m3cs-idrive-software-2024</x:v>
+        <x:v>bmw-m5-radiator-end-tank-and-2000</x:v>
       </x:c>
       <x:c r="C133" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D133" s="9" t="str">
-        <x:v>iDrive 8 Software Glitches and Screen Blackouts</x:v>
+        <x:v>Radiator End Tank and Expansion Tank Cracking Causing Sudden Coolant Loss and Overheating</x:v>
       </x:c>
       <x:c r="E133" s="9" t="str">
-        <x:v>Check for and install the latest BMW iDrive 8 software updates, which can be delivered over-the-air or at a dealer. Perform a soft reset by holding the iDrive controller button for 30 seconds. If screen blackouts persist, the dealer may need to replace the head unit or update the gateway module firmware. Ensure the 12V battery is in good condition, as low voltage can trigger software instability.</x:v>
+        <x:v>Diagnose with a cooling-system pressure test and inspect the radiator side tanks, expansion tank seams, level sensor area, upper hose neck, and bleed screw area for seepage or cracks. Repair typically involves replacing the failed tank or radiator, and many owners proactively refresh the full cooling system with hoses, cap, thermostat, water pump, and coolant to prevent repeat failures.</x:v>
       </x:c>
       <x:c r="F133" s="9" t="n">
         <x:v>0</x:v>
@@ -7689,16 +9187,16 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B134" s="9" t="str">
-        <x:v>bmw-m3cs-s58-carbon-buildup-2024</x:v>
+        <x:v>bmw-m5-rear-ball-joint-and-2000</x:v>
       </x:c>
       <x:c r="C134" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D134" s="9" t="str">
-        <x:v>S58 Intake Valve Carbon Buildup</x:v>
+        <x:v>Rear Ball Joint and Integral Link Wear Causing Clunks, Tire Wear, and Unstable Handling</x:v>
       </x:c>
       <x:c r="E134" s="9" t="str">
-        <x:v>Schedule walnut blast cleaning of the intake valves at 40,000-50,000 mile intervals. Install an oil catch can to reduce oil vapor entering the intake system. Use high-quality synthetic oil meeting BMW LL-01 specification and change at 5,000-7,000 mile intervals. Allow the engine to fully warm up before high-boost driving to ensure proper oil vapor management.</x:v>
+        <x:v>Diagnosis includes checking rear wheel play on a lift, inspecting ball joints and links for torn boots or looseness, and measuring alignment. Repair typically involves replacing worn rear ball joints and links in pairs, followed by a four-wheel alignment. Many owners refresh multiple rear suspension wear items together to restore the M5's original handling precision.</x:v>
       </x:c>
       <x:c r="F134" s="9" t="n">
         <x:v>0</x:v>
@@ -7707,21 +9205,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="135" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A135" s="40" t="n">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B135" s="9" t="str">
-        <x:v>bmw-m3cs-s58-charge-pipe-crack-2024</x:v>
+        <x:v>bmw-m5-s63-rod-bearing-2012</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2016 | BMW | M5 | S63</x:v>
       </x:c>
       <x:c r="D135" s="9" t="str">
-        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
+        <x:v>S63 Twin-Turbo V8 Rod Bearing Wear</x:v>
       </x:c>
       <x:c r="E135" s="9" t="str">
-        <x:v>Replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF. These direct-fit replacements handle higher temperatures and pressures without risk of cracking. If the car is under warranty and the failure occurs on stock tune, BMW should cover the repair. Inspect the charge pipe during every service and before track days.</x:v>
+        <x:v>Preventative rod bearing replacement with upgraded BE Bearings or ACL Race bearings every 60,000-80,000 miles. Requires oil pan removal and dropping the crankshaft to access all 8 rod bearings. Use strict 5,000-mile oil change intervals with BMW LL-01 approved 0W-40 oil.</x:v>
       </x:c>
       <x:c r="F135" s="9" t="n">
         <x:v>0</x:v>
@@ -7730,21 +9228,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="396" hidden="0" customHeight="1">
+    <x:row r="136" ht="1122" hidden="0" customHeight="1">
       <x:c r="A136" s="40" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B136" s="9" t="str">
-        <x:v>bmw-m4-charge-pipe-blowoff-2015</x:v>
+        <x:v>bmw-m5-s63-turbo-2012</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2012-2016 | BMW | M5 | S63</x:v>
       </x:c>
       <x:c r="D136" s="9" t="str">
-        <x:v>Plastic Charge Pipe Blow-Off Under Boost</x:v>
+        <x:v>S63 V8 Twin-Turbocharger Failure - F10 M5</x:v>
       </x:c>
       <x:c r="E136" s="9" t="str">
-        <x:v>Replace with an aluminum or silicone charge pipe. This is considered a must-do upgrade for any F82 M4. Many aftermarket options are direct bolt-on replacements. The job takes about 1-2 hours and requires removing the intake duct to access the charge pipe.</x:v>
+        <x:v>Replace failed turbocharger(s) with updated OEM units ($4,000-$6,000 per turbo, $8,000-$12,000 for both). Install BMW TSB heat insulators to protect turbo coolant and oil lines from excessive heat exposure ($200 preventive vs. $8,000+ turbo replacement). Use ONLY high-quality synthetic oil and maintain strict oil change intervals (5,000-7,500 miles MAX - NOT BMW's 10k recommendation). Avoid aggressive driving when engine cold - allow full warm-up before boost. For high-mileage vehicles (80,000+ miles), consider preventative turbo replacement or inspection. M5Post: when one turbo fails, seriously consider replacing both - labor overlap saves $2,000-$3,000 and other will likely fail soon.</x:v>
       </x:c>
       <x:c r="F136" s="9" t="n">
         <x:v>0</x:v>
@@ -7753,21 +9251,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="137" ht="1188" hidden="0" customHeight="1">
       <x:c r="A137" s="40" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B137" s="9" t="str">
-        <x:v>bmw-m4-convertible-top-2015</x:v>
+        <x:v>bmw-m5-s85-rod-bearing-2006</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D137" s="9" t="str">
-        <x:v>Convertible Top Hydraulic Pump Failure - F83 M4 Convertible</x:v>
+        <x:v>S85 V10 Rod Bearing Premature Failure (CATASTROPHIC) - E60 M5</x:v>
       </x:c>
       <x:c r="E137" s="9" t="str">
-        <x:v>Diagnose specific failure: hydraulic pump motor, lines, microswitches, or latch mechanisms. Pump motor replacement is most common ($1,500-2,500). Check hydraulic fluid level and refill if low. Regular top cycling (minimum once per month) prevents seal degradation. Store with top UP to reduce strain on hydraulic system. Rebuilt hydraulic pumps available at lower cost than new OEM. Complex repair requiring specialized BMW knowledge.</x:v>
+        <x:v>MANDATORY PREVENTATIVE: Replace rod bearings before 70,000 miles ($6,500-$8,600). Upgrade to BE Bearings, ACL Race, or VAC Motorsports high-performance bearings with increased clearances (0.0025" or greater) - DO NOT use OEM BMW bearings which have same design flaw. Perform regular oil analysis every 5,000 miles to detect early bearing wear. Use only BMW-approved 10W-60 synthetic oil with frequent oil changes (5,000-7,500 mile intervals). NEVER redline engine before reaching full operating temperature. Replace high-pressure VANOS line at same time as rod bearings (labor overlap saves $2,000-$3,000). If catastrophic failure occurs: Complete engine replacement required ($15,000-$32,000).</x:v>
       </x:c>
       <x:c r="F137" s="9" t="n">
         <x:v>0</x:v>
@@ -7776,21 +9274,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="138" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A138" s="40" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B138" s="9" t="str">
-        <x:v>bmw-m4-cooling-track-2015</x:v>
+        <x:v>bmw-m5-s85-throttle-actuator-2006</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D138" s="9" t="str">
-        <x:v>Cooling System Inadequacy Under Track Use - F82/F83 M4</x:v>
+        <x:v>S85 V10 Throttle Body Actuator Failure - E60 M5</x:v>
       </x:c>
       <x:c r="E138" s="9" t="str">
-        <x:v>Install comprehensive cooling upgrades for track use: CSF or Mishimoto high-capacity radiator, aftermarket oil cooler, upgraded intercoolers (Wagner, CSF), and transmission cooler. Remove kidney grille blockage for improved airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Total cooling system upgrade costs $3,000-5,000 but essential for serious track use. For street-only M4s, stock cooling is adequate.</x:v>
+        <x:v>Replace failed throttle actuator(s) with OEM units ($1,400-$1,700 each) or upgrade to Evolve Automotive uprated throttle actuators ($1,500-$1,800 each) for improved durability and increased lifespan - these have upgraded internal components that prevent repeat failure. ECU Testing and Euro Power Motorsports offer actuator rebuilds ($500-$800 per actuator) as cost-effective alternatives. M5Post consensus: when one actuator fails, replace both at same time to save labor costs since second will fail within 6-12 months. Labor: 3 hours professional / 4+ hours DIY.</x:v>
       </x:c>
       <x:c r="F138" s="9" t="n">
         <x:v>0</x:v>
@@ -7799,21 +9297,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="462" hidden="0" customHeight="1">
+    <x:row r="139" ht="1056" hidden="0" customHeight="1">
       <x:c r="A139" s="40" t="n">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B139" s="9" t="str">
-        <x:v>bmw-m4-crank-hub-bolt-2015</x:v>
+        <x:v>bmw-m5-s85-vanos-pump-2006</x:v>
       </x:c>
       <x:c r="C139" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2006-2010 | BMW | M5 | S85</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>S55 Crank Hub Bolt Loosening</x:v>
+        <x:v>VANOS High-Pressure Pump &amp; Line Failure (CATASTROPHIC) - E60 M5</x:v>
       </x:c>
       <x:c r="E139" s="9" t="str">
-        <x:v>Replace with an upgraded aftermarket crank hub bolt (ARP or IND). The job requires removing the radiator fan, accessory belt, and harmonic balancer to access the bolt. Use proper torque specs for the upgraded bolt. This is a preventative maintenance item for any M4 owner.</x:v>
+        <x:v>Replace high-pressure VANOS line with updated design that includes proper bend radius ($3,000 parts + labor). Replace VANOS high-pressure pump if showing signs of wear or contamination. DrVanos offers fully rebuilt S85 VANOS pumps ($1,800 + $400 core deposit) - M5Post gold standard for rebuilds. This repair is BEST performed simultaneously with rod bearing replacement to save on overlapping labor costs ($2,000-$4,000 savings). WARNING: DO NOT ignore VANOS line leaks - metal debris from failed pump circulates through entire lubrication system and can destroy engine. If catastrophic failure: engine replacement required ($32,000).</x:v>
       </x:c>
       <x:c r="F139" s="9" t="n">
         <x:v>0</x:v>
@@ -7822,21 +9320,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="140" ht="1188" hidden="0" customHeight="1">
       <x:c r="A140" s="40" t="n">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B140" s="9" t="str">
-        <x:v>bmw-m4-dct-clutch-2015</x:v>
+        <x:v>bmw-m5-smg-pump-2006</x:v>
       </x:c>
       <x:c r="C140" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D140" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F82/F83 M4</x:v>
+        <x:v>SMG III Hydraulic Pump Failure - E60 M5</x:v>
       </x:c>
       <x:c r="E140" s="9" t="str">
-        <x:v>Replace DCT clutch pack when symptoms appear. BMW recommends replacing all clutches together. Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use (limit to special occasions). Transmission adaptation reset via BMW software may temporarily improve shift quality. Extended warranty highly recommended for DCT-equipped M4s. Labor-intensive repair requires transmission removal.</x:v>
+        <x:v>DIAGNOSIS FIRST: Insist on proper diagnosis before pump replacement - accumulator failure has similar symptoms and costs $500 vs. $5,000. If pump confirmed failed: Try rebuild first - carbon buildup can often be cleaned for fraction of replacement cost. SMG Society and specialty shops offer pump rebuilds ($300 pump + labor + fluids = $1,500-$2,500). If rebuild unsuccessful: Replace SMG pump with OEM or remanufactured unit ($5,000-$7,700 dealership, $5,000-$6,500 independent specialist). Replace hydraulic accumulator at same time if vehicle has 60,000+ miles ($300-$500 additional). Flush and replace SMG hydraulic fluid and manual transmission fluid during pump replacement.</x:v>
       </x:c>
       <x:c r="F140" s="9" t="n">
         <x:v>0</x:v>
@@ -7845,21 +9343,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="462" hidden="0" customHeight="1">
+    <x:row r="141" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A141" s="40" t="n">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B141" s="9" t="str">
-        <x:v>bmw-m4-rear-subframe-crack-2015</x:v>
+        <x:v>bmw-m5-timing-chain-guide-wear-2000</x:v>
       </x:c>
       <x:c r="C141" s="9" t="str">
-        <x:v>2015-2026 | BMW | M4</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D141" s="9" t="str">
-        <x:v>Rear Subframe Cracking From Track Use</x:v>
+        <x:v>Timing Chain Guide Wear and Chain Tensioner Noise on the S62 V8</x:v>
       </x:c>
       <x:c r="E141" s="9" t="str">
-        <x:v>Inspect subframe mounting points and welds regularly if the car sees track use. Reinforce with aftermarket subframe reinforcement plates or weld-in gussets. Severely cracked subframes must be replaced entirely. Upgraded subframe bushings (solid or reinforced) help distribute loads more evenly.</x:v>
+        <x:v>Diagnosis includes listening for chain noise on cold start, inspecting oil/filter for plastic guide debris, and checking timing adaptation/fault data. Repair generally requires replacing timing chain guides, tensioners, related rails, gaskets, and often addressing front-engine seals while disassembled. Preventive service is often recommended once noise appears rather than waiting for a failure.</x:v>
       </x:c>
       <x:c r="F141" s="9" t="n">
         <x:v>0</x:v>
@@ -7868,21 +9366,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="805.2000122070312" hidden="0" customHeight="1">
+    <x:row r="142" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A142" s="40" t="n">
         <x:v>141</x:v>
       </x:c>
       <x:c r="B142" s="9" t="str">
-        <x:v>bmw-m4-s55-crank-hub-2015</x:v>
+        <x:v>bmw-m5-torque-converter-shudder-2018</x:v>
       </x:c>
       <x:c r="C142" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2018-2023 | BMW | M5</x:v>
       </x:c>
       <x:c r="D142" s="9" t="str">
-        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - F82/F83 M4</x:v>
+        <x:v>ZF 8HP Torque Converter Shudder</x:v>
       </x:c>
       <x:c r="E142" s="9" t="str">
-        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway) that eliminates the slipping issue permanently. Installation requires crankshaft pulley removal and precise torque specs. This upgrade is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Cost is $1,200-2,500 installed vs. $20,000+ for engine replacement after failure.</x:v>
+        <x:v>Perform a transmission fluid and filter change using genuine ZF LifeGuard 8 fluid. If the shudder persists, the torque converter must be replaced. BMW issued a service bulletin for some VINs. A software update for shift calibration may also help in mild cases.</x:v>
       </x:c>
       <x:c r="F142" s="9" t="n">
         <x:v>0</x:v>
@@ -7891,44 +9389,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="143" ht="1108.800048828125" hidden="0" customHeight="1">
       <x:c r="A143" s="40" t="n">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B143" s="9" t="str">
-        <x:v>bmw-m4-s55-injector-2015</x:v>
+        <x:v>bmw-m5-valve-stem-seals-2012</x:v>
       </x:c>
       <x:c r="C143" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2012-2023 | BMW | M5</x:v>
       </x:c>
       <x:c r="D143" s="9" t="str">
-        <x:v>S55 High-Pressure Fuel Injector Failure - F82/F83 M4</x:v>
+        <x:v>S63/S63TU Valve Stem Seal Failure &amp; Oil Consumption</x:v>
       </x:c>
       <x:c r="E143" s="9" t="str">
-        <x:v>Replace all 6 injectors together to prevent repeat repairs. Perform walnut blast carbon cleaning on intake valves while injectors are removed (labor overlap saves $400-600). Use Top Tier gasoline to minimize carbon buildup. Add fuel system cleaner (Liqui Moly Valve Clean) every 5,000 miles to reduce carbon deposits. BMW parts are expensive; some shops use OEM Bosch injectors at lower cost. Labor is 4-6 hours for injector replacement.</x:v>
+        <x:v>Replace valve stem seals with updated OEM or performance seals ($3,500-$10,000 depending on method). Labor-intensive repair requiring either cylinder head removal ($6,000-$10,000) or specialized valve spring compressor tools with heads on engine ($3,500-$6,000). Address issue EARLY to prevent catalytic converter damage from oil burning (adds $3,000-$5,000 to repair). Perform more frequent oil changes (5,000 miles) to minimize damage. Blue smoke test: let engine idle 30+ minutes until hot, then rev to redline briefly - big blue smoke plume = valve seals. Find shop that can replace valve seals with heads installed (specialized tools required) - saves $4,000+ in labor vs. full head removal.</x:v>
       </x:c>
       <x:c r="F143" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G143" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="144" ht="528" hidden="0" customHeight="1">
       <x:c r="A144" s="40" t="n">
         <x:v>143</x:v>
       </x:c>
       <x:c r="B144" s="9" t="str">
-        <x:v>bmw-m4-s55-rod-bearing-2015</x:v>
+        <x:v>bmw-m6-e63-e64-active-steering-steering-gear-play-knock</x:v>
       </x:c>
       <x:c r="C144" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
       </x:c>
       <x:c r="D144" s="9" t="str">
-        <x:v>S55 Rod Bearing Premature Wear - F82/F83 M4</x:v>
+        <x:v>E63/E64 Active Steering and Steering-Gear Play / Knock</x:v>
       </x:c>
       <x:c r="E144" s="9" t="str">
-        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles or before extensive track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability than OEM. Regular oil analysis (Blackstone Labs) every 5,000 miles to monitor bearing wear. Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max. Track-focused M4s should replace bearings every 50,000 miles. Labor is 8-12 hours, so many owners do this during clutch replacement.</x:v>
+        <x:v>Inspect the steering gear and front control-arm/thrust-arm bushings for play. Replace worn control-arm bushings/ball joints first as they are cheaper and frequently the source of the knock; if the steering rack/gear itself has internal play or leaks, it requires replacement (a significant cost) followed by an alignment.</x:v>
       </x:c>
       <x:c r="F144" s="9" t="n">
         <x:v>0</x:v>
@@ -7937,21 +9435,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="660" hidden="0" customHeight="1">
+    <x:row r="145" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A145" s="40" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B145" s="9" t="str">
-        <x:v>bmw-m4cs-brake-wear-track-2024</x:v>
+        <x:v>bmw-m6-f12-convertible-top-hydraulic-pump-relay-failure</x:v>
       </x:c>
       <x:c r="C145" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Convertible (F12) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D145" s="9" t="str">
-        <x:v>Rapid Brake Pad and Rotor Wear from Track Use</x:v>
+        <x:v>F12 Convertible Top Hydraulic Pump and Relay Failure</x:v>
       </x:c>
       <x:c r="E145" s="9" t="str">
-        <x:v>Inspect brake pads and rotors before and after every track day. Consider upgrading to aftermarket performance pads like Pagid RSC or Hawk DTC-70 for track use, and switch to street pads for daily driving. For frequent track users, the optional carbon ceramic brake package significantly extends rotor life. Use high-temperature brake fluid (DOT 5.1 or racing fluid) and flush before every track season.</x:v>
+        <x:v>Diagnose whether the fault is the pump's high-current relays (relatively cheap, often the cure), a pressure loss in the pump, a hydraulic leak, or a roof microswitch/sensor. Replace the relays first; if pressure loss persists, rebuild or replace the hydraulic pump unit (specialist rebuild services exist) and renew worn seals/sensors. Bleed and refill the hydraulic system after repair.</x:v>
       </x:c>
       <x:c r="F145" s="9" t="n">
         <x:v>0</x:v>
@@ -7960,21 +9458,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="462" hidden="0" customHeight="1">
+    <x:row r="146" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A146" s="40" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B146" s="9" t="str">
-        <x:v>bmw-m4cs-s58-carbon-buildup-2024</x:v>
+        <x:v>bmw-m6-f12-f13-7-speed-m-dct-mechatronic-clutch-pack-failure</x:v>
       </x:c>
       <x:c r="C146" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D146" s="9" t="str">
-        <x:v>S58 Intake Valve Carbon Buildup</x:v>
+        <x:v>F12/F13 7-Speed M-DCT Mechatronic and Clutch Pack Failure</x:v>
       </x:c>
       <x:c r="E146" s="9" t="str">
-        <x:v>Walnut blast the intake valves every 40,000-50,000 miles. Consider installing an oil catch can to reduce oil vapor ingestion. Maintain strict 5,000-7,000 mile oil change intervals with BMW LL-01 approved oil. Allow full engine warmup before spirited driving to ensure proper crankcase ventilation operation.</x:v>
+        <x:v>Scan for transmission codes to confirm whether the fault is the mechatronic unit or worn clutch packs. Mechatronic units can often be repaired/replaced and must be reprogrammed and adapted to the vehicle afterward. Worn clutch packs require a clutch replacement (dealer cost often $3,000-$5,000). Regular DCT fluid and filter changes help prevent premature wear; avoid prolonged clutch slip in traffic.</x:v>
       </x:c>
       <x:c r="F146" s="9" t="n">
         <x:v>0</x:v>
@@ -7983,21 +9481,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="147" ht="594" hidden="0" customHeight="1">
       <x:c r="A147" s="40" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B147" s="9" t="str">
-        <x:v>bmw-m4cs-s58-charge-pipe-crack-2024</x:v>
+        <x:v>bmw-m6-f12-f13-electric-water-pump-thermostat-failure</x:v>
       </x:c>
       <x:c r="C147" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D147" s="9" t="str">
-        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
+        <x:v>F12/F13 Electric Water Pump and Thermostat Failure</x:v>
       </x:c>
       <x:c r="E147" s="9" t="str">
-        <x:v>Proactively replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF before any track use. These bolt-on replacements are rated for boost pressures well beyond what the S58 produces. Inspect the charge pipe at every service interval for signs of stress cracking or discoloration.</x:v>
+        <x:v>Replace the failed electric water pump and/or electronic thermostat with OEM units; inspect the radiator end-tanks and expansion tank for cracks and replace as needed. Pressure-test the cooling system, refresh coolant, and treat the pump/thermostat as wear items given the heat load. Address any overheating event immediately to avoid secondary engine damage.</x:v>
       </x:c>
       <x:c r="F147" s="9" t="n">
         <x:v>0</x:v>
@@ -8006,21 +9504,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="660" hidden="0" customHeight="1">
+    <x:row r="148" ht="528" hidden="0" customHeight="1">
       <x:c r="A148" s="40" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B148" s="9" t="str">
-        <x:v>bmw-m5-absdsc-module-failure-triggering-2000</x:v>
+        <x:v>bmw-m6-f12-f13-turbocharger-wastegate-rattle-oil-starvation</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D148" s="9" t="str">
-        <x:v>ABS/DSC Module Failure Triggering ABS, Brake, and Traction Control Warning Lights</x:v>
+        <x:v>F12/F13 Turbocharger Wastegate Rattle and Oil Starvation</x:v>
       </x:c>
       <x:c r="E148" s="9" t="str">
-        <x:v>Diagnosis should begin with scanning the ABS/DSC module for communication or wheel-speed sensor faults and verifying power, ground, and sensor signals. If the module intermittently loses communication or shows implausible internal faults, the usual repair is module rebuild or replacement, followed by coding if required. Wheel speed sensors should only be replaced after confirming they are actually faulty.</x:v>
+        <x:v>Confirm wastegate rattle by listening at light throttle; worn actuators/linkages can be replaced or upgraded. For oil starvation, maintain strict oil-change intervals with the correct specification, allow proper cool-down after hard driving, and keep the cooling system healthy. Severely worn or whining turbos require rebuild or replacement.</x:v>
       </x:c>
       <x:c r="F148" s="9" t="n">
         <x:v>0</x:v>
@@ -8029,21 +9527,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="149" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A149" s="40" t="n">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B149" s="9" t="str">
-        <x:v>bmw-m5-clutch-slave-cylinder-and-2000</x:v>
+        <x:v>bmw-m6-rod-bearing-wear-2005</x:v>
       </x:c>
       <x:c r="C149" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2005-2019 | BMW | M6 | S65, S63</x:v>
       </x:c>
       <x:c r="D149" s="9" t="str">
-        <x:v>Clutch Slave Cylinder and Hydraulic Line Failure Causing Soft Pedal and Shift Engagement Problems</x:v>
+        <x:v>Rod Bearing Premature Wear (S65/S63 Engines)</x:v>
       </x:c>
       <x:c r="E149" s="9" t="str">
-        <x:v>Inspect the clutch hydraulic circuit for fluid leakage at the slave cylinder, master cylinder, and line connections, and verify brake/clutch fluid condition. Replace the failed slave cylinder and often the flexible hose, then bleed the system thoroughly; if symptoms persist, inspect the clutch, pressure plate, and pilot bearing.</x:v>
+        <x:v>Perform a preventive rod bearing replacement between 60,000-80,000 miles on S65 engines, and inspect by 80,000-100,000 miles on S63 engines. Use upgraded ACL or King XP bearings with coated surfaces. Cut and send used oil filter for analysis — bearing material particles indicate wear progression. The job requires engine-out on the S65 (approximately 20 hours labor) or can be done in-car on the S63 with the oil pan dropped.</x:v>
       </x:c>
       <x:c r="F149" s="9" t="n">
         <x:v>0</x:v>
@@ -8052,21 +9550,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="150" ht="528" hidden="0" customHeight="1">
       <x:c r="A150" s="40" t="n">
         <x:v>149</x:v>
       </x:c>
       <x:c r="B150" s="9" t="str">
-        <x:v>bmw-m5-dct-clutch-2012</x:v>
+        <x:v>bmw-m6-s63-carbon-buildup-intake-valves</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D150" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Wear &amp; Judder - F10 M5</x:v>
+        <x:v>S63 Carbon Buildup on Intake Valves (Direct Injection)</x:v>
       </x:c>
       <x:c r="E150" s="9" t="str">
-        <x:v>PREVENTIVE: Replace DCT transmission fluid and filter every 30,000-50,000 miles (BMW says "lifetime" but this causes premature failure). Use ONLY BMW DCTF-1 specification fluid ($189-$253 service, DIY: $100-$150). For judder/jerkiness: try fluid change and software update FIRST before clutch replacement - many issues resolved this way. For severe clutch wear: replace dual-clutch assembly with OEM ($2,394-$2,567 typical, $3,000-$4,000 dealership) or upgraded performance clutch kit. Consider NRC TitanTec or CNS Racing upgraded DCT clutch packs for improved durability if used for performance driving/track. Complete DCT transmission replacement: $8,000-$12,000.</x:v>
+        <x:v>Have the intake valves walnut-blasted (media-blast cleaning) to remove carbon deposits without removing the cylinder heads. Many owners do this every 50,000-70,000 km. A properly functioning PCV/crankcase ventilation system and quality oil reduce deposit rate. An oil-catch can is sometimes fitted to slow accumulation.</x:v>
       </x:c>
       <x:c r="F150" s="9" t="n">
         <x:v>0</x:v>
@@ -8075,21 +9573,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="151" ht="528" hidden="0" customHeight="1">
       <x:c r="A151" s="40" t="n">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B151" s="9" t="str">
-        <x:v>bmw-m5-door-vapor-barrier-and-2000</x:v>
+        <x:v>bmw-m6-s63-high-pressure-fuel-pump-fuel-injector-cold-start-misfire</x:v>
       </x:c>
       <x:c r="C151" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D151" s="9" t="str">
-        <x:v>Door Vapor Barrier and Sunroof Drain Leaks Causing Wet Carpets and Electrical Problems</x:v>
+        <x:v>S63 High-Pressure Fuel Pump / Fuel Injector Cold-Start Misfire</x:v>
       </x:c>
       <x:c r="E151" s="9" t="str">
-        <x:v>Remove the door panel and inspect the vapor barrier seal, especially along the lower edge, and verify all sunroof drains flow freely and exit properly. Reseal the vapor barrier with butyl ribbon or equivalent body sealer, clear the drains, dry the carpet and padding thoroughly, and inspect under-carpet wiring/connectors for corrosion.</x:v>
+        <x:v>Scan for misfire and fuel-system codes and test cold-start fuel-rail pressure. Replace a failing HPFP; for injector faults, replace the affected injector(s) with units of the correct matching index code (do not mix injector indexes on a bank) and re-code them. Address per the relevant BMW technical service bulletin for the N63/S63.</x:v>
       </x:c>
       <x:c r="F151" s="9" t="n">
         <x:v>0</x:v>
@@ -8098,21 +9596,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="152" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A152" s="40" t="n">
         <x:v>151</x:v>
       </x:c>
       <x:c r="B152" s="9" t="str">
-        <x:v>bmw-m5-e39-m5-vanos-solenoidseal-2000</x:v>
+        <x:v>bmw-m6-s63-rod-bearing-2013</x:v>
       </x:c>
       <x:c r="C152" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2013-2018 | BMW | M6 | S63</x:v>
       </x:c>
       <x:c r="D152" s="9" t="str">
-        <x:v>E39 M5 VANOS Solenoid/Seal Failure Causing Rattle, Power Loss, and Check Engine Lights</x:v>
+        <x:v>S63 Twin-Turbo V8 Rod Bearing Concerns (F06/F12/F13 M6)</x:v>
       </x:c>
       <x:c r="E152" s="9" t="str">
-        <x:v>Diagnosis typically includes scanning for camshaft timing and VANOS activation faults, checking oil condition/pressure, and listening for startup rattle from the front of the engine. Repair usually involves rebuilding the VANOS units with upgraded seals, replacing failed solenoids or solenoid seals, and correcting any oil leaks or timing-related wear. Many owners address both banks preventively while the front of engine is apart.</x:v>
+        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles using ACL Race Rod Bearings 8B1578HX-STD ($150-250), King Bearings SV Series, or WPC-treated bearings from Lang Racing. Cost: $4,000-7,000 for preventive replacement. Oil changes every 5,000-7,500 miles mandatory (ignore BMW's 10,000-mile recommendation). Use Blackstone Labs oil analysis ($30/test) every 5,000 miles to monitor bearing wear metals. Preventive replacement recommended for peace of mind, especially on cars used for track days or spirited driving.</x:v>
       </x:c>
       <x:c r="F152" s="9" t="n">
         <x:v>0</x:v>
@@ -8121,21 +9619,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="153" ht="1069.199951171875" hidden="0" customHeight="1">
       <x:c r="A153" s="40" t="n">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B153" s="9" t="str">
-        <x:v>bmw-m5-front-thrust-arm-bushing-2000</x:v>
+        <x:v>bmw-m6-s85-rod-bearing-2006</x:v>
       </x:c>
       <x:c r="C153" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2006-2010 | BMW | M6 | S85</x:v>
       </x:c>
       <x:c r="D153" s="9" t="str">
-        <x:v>Front Thrust Arm Bushing Failure Causing 50-60 MPH Brake Shimmy and Steering Vibration</x:v>
+        <x:v>S85 V10 Rod Bearing Failure (Catastrophic Engine Destruction)</x:v>
       </x:c>
       <x:c r="E153" s="9" t="str">
-        <x:v>Inspect the front thrust arms and control arms for bushing cracks, fluid leakage from hydro-bushings, and ball-joint play. Replace the thrust arms or complete front control arm set, then perform a proper alignment; if brake pulsation remains, inspect rotor runout and wheel balance.</x:v>
+        <x:v>MANDATORY PREVENTIVE REPLACEMENT before 70,000 miles: Replace all 10 rod bearings with ACL Race Bearings 10B1580HX-STD (+0.001" clearance, $200-350) or WPC-treated bearings from Lang Racing, or VAC Motorsports kit VAC-HPRBK-S85, or Turner kit TMS222798, or FCP Euro kit 11247841703KT3. ALSO replace VANOS line 11367838669 and use ARP rod bolts (included in most kits). Cost: $6,500-9,500 preventive. If engine is destroyed from bearing failure: $15,000-32,000 for engine replacement or rebuild. NEVER use OEM bearings as replacements. Use Blackstone Labs oil analysis every 5,000 miles ($30/test) to monitor bearing wear metals.</x:v>
       </x:c>
       <x:c r="F153" s="9" t="n">
         <x:v>0</x:v>
@@ -8144,21 +9642,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="594" hidden="0" customHeight="1">
+    <x:row r="154" ht="924" hidden="0" customHeight="1">
       <x:c r="A154" s="40" t="n">
         <x:v>153</x:v>
       </x:c>
       <x:c r="B154" s="9" t="str">
-        <x:v>bmw-m5-getrag-420g-6-speed-synchro-2000</x:v>
+        <x:v>bmw-m6-s85-throttle-actuator-2006</x:v>
       </x:c>
       <x:c r="C154" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2006-2010 | BMW | M6 | S85</x:v>
       </x:c>
       <x:c r="D154" s="9" t="str">
-        <x:v>Getrag 420G 6-Speed Synchro Wear and 2nd/3rd Gear Grinding</x:v>
+        <x:v>S85 V10 Throttle Actuator Failure (Plastic Gear Stripping)</x:v>
       </x:c>
       <x:c r="E154" s="9" t="str">
-        <x:v>Diagnosis involves road testing hot and cold, checking clutch release operation, and ruling out worn transmission mounts or old fluid before condemning the gearbox. Mild cases may improve with fresh fluid, but persistent grinding usually requires transmission rebuild with new synchros, bearings, and wear components. Clutch and shifter bushings are often serviced at the same time.</x:v>
+        <x:v>Rebuild throttle actuators using Beisan Systems BS101 sintered metal gear kit ($250/set, need 2 sets for both actuators) for permanent fix. Beisan BS102 full rebuild service available ($300). Alternatively, rebuilt actuators from Euro Power Motorsports ($500-800 each). OEM replacement actuators from BMW cost $2,000-4,500. Total cost: $500-4,500 depending on approach. Beisan Systems sintered metal gears are THE permanent fix - they replace the weak plastic PPA gears with metal gears that will not strip. Always rebuild both actuators simultaneously.</x:v>
       </x:c>
       <x:c r="F154" s="9" t="n">
         <x:v>0</x:v>
@@ -8167,21 +9665,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="155" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A155" s="40" t="n">
         <x:v>154</x:v>
       </x:c>
       <x:c r="B155" s="9" t="str">
-        <x:v>bmw-m5-ignition-coils-2012</x:v>
+        <x:v>bmw-m6-s85-v10-vanos-high-pressure-oil-pump-failure</x:v>
       </x:c>
       <x:c r="C155" s="9" t="str">
-        <x:v>2012-2023 | BMW | M5 | S63, S63TU</x:v>
+        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
       </x:c>
       <x:c r="D155" s="9" t="str">
-        <x:v>S63/S63TU Ignition Coil Premature Failure</x:v>
+        <x:v>S85 V10 VANOS High-Pressure Oil Pump Failure</x:v>
       </x:c>
       <x:c r="E155" s="9" t="str">
-        <x:v>Replace failed ignition coil(s) immediately to prevent catalytic converter damage ($3,000-$5,000 additional). When one coil fails, M5Post recommends replacing all 8 coils as preventative maintenance ($600-$900 parts + labor) - they typically fail within similar timeframes and saves second service visit. Use OEM Bosch coils for best reliability ($50-$80 each) - aftermarket options fail even faster on S63 due to heat and electrical demands. Replace spark plugs simultaneously if mileage exceeds 30,000 miles ($280-$320 for 8 plugs). Labor: 1-2 hours. Single coil replacement: $179-$235.</x:v>
+        <x:v>Perform an oil-pressure test on the VANOS circuit at the first sign of cold-start knocking. Replace or professionally rebuild the high-pressure VANOS pump and renew the high-pressure lines/seals. Many owners do the VANOS pump preventively at the same time as the rod-bearing service since the oil pan is already removed. Use only BMW-spec oil and strict change intervals to prolong pump life.</x:v>
       </x:c>
       <x:c r="F155" s="9" t="n">
         <x:v>0</x:v>
@@ -8190,21 +9688,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="156" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A156" s="40" t="n">
         <x:v>155</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>bmw-m5-instrument-cluster-pixel-failure-2000</x:v>
+        <x:v>bmw-m6-smg-pump-failure-2005</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2005-2010 | BMW | M6</x:v>
       </x:c>
       <x:c r="D156" s="9" t="str">
-        <x:v>Instrument Cluster Pixel Failure and MID Display Dropout</x:v>
+        <x:v>SMG Hydraulic Pump and Clutch Actuator Failure</x:v>
       </x:c>
       <x:c r="E156" s="9" t="str">
-        <x:v>Diagnosis is usually visual, confirming missing display segments in the cluster or MID. Repair involves replacing or rebuilding the cluster/MID display ribbon and screen components, or sending the unit to a specialist rebuilder. Used replacement clusters require coding and mileage tamper considerations, so rebuild is often preferred.</x:v>
+        <x:v>Replace the SMG hydraulic pump and pressure accumulator. Bleed and refill the SMG hydraulic system with Pentosin CHF 11S fluid. Many owners convert to a traditional 6-speed manual swap using an aftermarket kit from companies like OS Giken or using the E90 M3 6MT parts. Budget $2,000-4,000 for SMG repair or $5,000-8,000 for a manual conversion.</x:v>
       </x:c>
       <x:c r="F156" s="9" t="n">
         <x:v>0</x:v>
@@ -8213,21 +9711,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="157" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A157" s="40" t="n">
         <x:v>156</x:v>
       </x:c>
       <x:c r="B157" s="9" t="str">
-        <x:v>bmw-m5-maf-sensor-degradation-causing-2000</x:v>
+        <x:v>bmw-m8-adaptive-suspension-leak-2020</x:v>
       </x:c>
       <x:c r="C157" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2020-2025 | BMW | M8</x:v>
       </x:c>
       <x:c r="D157" s="9" t="str">
-        <x:v>MAF Sensor Degradation Causing Lean Codes, Hesitation, and Reduced Power</x:v>
+        <x:v>Adaptive Suspension Damper Leaks</x:v>
       </x:c>
       <x:c r="E157" s="9" t="str">
-        <x:v>Scan for fuel-trim and MAF-related faults, inspect for intake leaks first, then compare live airflow values bank-to-bank. If readings are implausible or one bank differs significantly, replace the affected MAF sensor(s) with OE-quality parts and clear adaptations; also inspect intake boots and air filter condition.</x:v>
+        <x:v>Replace the leaking damper(s). BMW adaptive dampers must be replaced as complete units — they cannot be rebuilt. After replacement, a suspension calibration via ISTA is required to integrate the new damper into the adaptive system. Replacing in pairs (front or rear axle) is recommended.</x:v>
       </x:c>
       <x:c r="F157" s="9" t="n">
         <x:v>0</x:v>
@@ -8236,21 +9734,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="158" ht="990" hidden="0" customHeight="1">
       <x:c r="A158" s="40" t="n">
         <x:v>157</x:v>
       </x:c>
       <x:c r="B158" s="9" t="str">
-        <x:v>bmw-m5-radiator-end-tank-and-2000</x:v>
+        <x:v>bmw-m8-carbon-ceramic-brakes-2020</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2020-2024 | BMW | M8</x:v>
       </x:c>
       <x:c r="D158" s="9" t="str">
-        <x:v>Radiator End Tank and Expansion Tank Cracking Causing Sudden Coolant Loss and Overheating</x:v>
+        <x:v>M8 Carbon Ceramic Brake (CCB) Issues</x:v>
       </x:c>
       <x:c r="E158" s="9" t="str">
-        <x:v>Diagnose with a cooling-system pressure test and inspect the radiator side tanks, expansion tank seams, level sensor area, upper hose neck, and bleed screw area for seepage or cracks. Repair typically involves replacing the failed tank or radiator, and many owners proactively refresh the full cooling system with hoses, cap, thermostat, water pump, and coolant to prevent repeat failures.</x:v>
+        <x:v>Replace damaged CCB rotors ($3,000-$4,000 per corner, $12,000-$16,000 for all four). CCB rotors cannot be resurfaced - replacement is only option. Alternatively, convert to iron rotors using BimmerWorld CCB-to-iron conversion kit ($3,000-$5,000 total for all four corners) for dramatically lower running costs. PREVENTION: Avoid driving through standing water with hot brakes (thermal shock cracks rotors). Avoid aggressive braking over potholes or road debris. Squealing at low speed is normal for CCB material - not a defect. If only using car for street driving, iron conversion is more practical and cost-effective.</x:v>
       </x:c>
       <x:c r="F158" s="9" t="n">
         <x:v>0</x:v>
@@ -8259,21 +9757,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="159" ht="396" hidden="0" customHeight="1">
       <x:c r="A159" s="40" t="n">
         <x:v>158</x:v>
       </x:c>
       <x:c r="B159" s="9" t="str">
-        <x:v>bmw-m5-rear-ball-joint-and-2000</x:v>
+        <x:v>bmw-m8-s63tu4-oil-consumption-2020</x:v>
       </x:c>
       <x:c r="C159" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2020-2025 | BMW | M8 | S63TU4</x:v>
       </x:c>
       <x:c r="D159" s="9" t="str">
-        <x:v>Rear Ball Joint and Integral Link Wear Causing Clunks, Tire Wear, and Unstable Handling</x:v>
+        <x:v>S63TU4 V8 Excessive Oil Consumption</x:v>
       </x:c>
       <x:c r="E159" s="9" t="str">
-        <x:v>Diagnosis includes checking rear wheel play on a lift, inspecting ball joints and links for torn boots or looseness, and measuring alignment. Repair typically involves replacing worn rear ball joints and links in pairs, followed by a four-wheel alignment. Many owners refresh multiple rear suspension wear items together to restore the M5's original handling precision.</x:v>
+        <x:v>Monitor oil level regularly using iDrive oil level check. For excessive consumption beyond BMW's threshold, valve stem seal replacement may be warranted under warranty. Updated piston rings are available for severe cases. Always keep oil topped up between changes.</x:v>
       </x:c>
       <x:c r="F159" s="9" t="n">
         <x:v>0</x:v>
@@ -8282,21 +9780,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="160" ht="858" hidden="0" customHeight="1">
       <x:c r="A160" s="40" t="n">
         <x:v>159</x:v>
       </x:c>
       <x:c r="B160" s="9" t="str">
-        <x:v>bmw-m5-s63-rod-bearing-2012</x:v>
+        <x:v>bmw-m8-s63tu4-rod-bearing-2020</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5 | S63</x:v>
+        <x:v>2020-2024 | BMW | M8</x:v>
       </x:c>
       <x:c r="D160" s="9" t="str">
-        <x:v>S63 Twin-Turbo V8 Rod Bearing Wear</x:v>
+        <x:v>S63TU4 Rod Bearing Wear (M8/M8 Competition)</x:v>
       </x:c>
       <x:c r="E160" s="9" t="str">
-        <x:v>Preventative rod bearing replacement with upgraded BE Bearings or ACL Race bearings every 60,000-80,000 miles. Requires oil pan removal and dropping the crankshaft to access all 8 rod bearings. Use strict 5,000-mile oil change intervals with BMW LL-01 approved 0W-40 oil.</x:v>
+        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles or sooner if tracked ($5,000-$8,000). Use ACL Race bearings 8B1578HX-STD ($200-350) which have wider clearance tolerances than OEM for better oil film protection. Monitor bearing health with Blackstone Labs oil analysis ($30/sample) every oil change - elevated copper/lead indicates bearing wear starting. If bearings have failed: engine replacement required ($20,000-$40,000). CRITICAL: If you hear any knocking from bottom end, stop driving immediately and tow to shop.</x:v>
       </x:c>
       <x:c r="F160" s="9" t="n">
         <x:v>0</x:v>
@@ -8305,21 +9803,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="1122" hidden="0" customHeight="1">
+    <x:row r="161" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A161" s="40" t="n">
         <x:v>160</x:v>
       </x:c>
       <x:c r="B161" s="9" t="str">
-        <x:v>bmw-m5-s63-turbo-2012</x:v>
+        <x:v>bmw-n54-hpfp</x:v>
       </x:c>
       <x:c r="C161" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5 | S63</x:v>
+        <x:v>2007-2010 | BMW | 3 Series | N54</x:v>
       </x:c>
       <x:c r="D161" s="9" t="str">
-        <x:v>S63 V8 Twin-Turbocharger Failure - F10 M5</x:v>
+        <x:v>N54 Long Crank or Power Loss Requires Fuel-Pressure Diagnosis</x:v>
       </x:c>
       <x:c r="E161" s="9" t="str">
-        <x:v>Replace failed turbocharger(s) with updated OEM units ($4,000-$6,000 per turbo, $8,000-$12,000 for both). Install BMW TSB heat insulators to protect turbo coolant and oil lines from excessive heat exposure ($200 preventive vs. $8,000+ turbo replacement). Use ONLY high-quality synthetic oil and maintain strict oil change intervals (5,000-7,500 miles MAX - NOT BMW's 10k recommendation). Avoid aggressive driving when engine cold - allow full warm-up before boost. For high-mileage vehicles (80,000+ miles), consider preventative turbo replacement or inspection. M5Post: when one turbo fails, seriously consider replacing both - labor overlap saves $2,000-$3,000 and other will likely fail soon.</x:v>
+        <x:v>Have a BMW-qualified technician read fault memory and follow the bulletin pressure tests for 2FBF, 29DC, 29F1 or 29F2 before replacing the pump. The historical ten-year/120,000-mile emissions-warranty extension has expired for this population and is not a current coverage promise. ShowMeTheParts resolved three 2009 335i fuel-pump candidates, but catalog fitment is not diagnosis or remedy proof and no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F161" s="9" t="n">
         <x:v>0</x:v>
@@ -8328,21 +9826,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="1188" hidden="0" customHeight="1">
+    <x:row r="162" ht="290.3999938964844" hidden="0" customHeight="1">
       <x:c r="A162" s="40" t="n">
         <x:v>161</x:v>
       </x:c>
       <x:c r="B162" s="9" t="str">
-        <x:v>bmw-m5-s85-rod-bearing-2006</x:v>
+        <x:v>bmw-n55-boost-solenoid-2012</x:v>
       </x:c>
       <x:c r="C162" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
       </x:c>
       <x:c r="D162" s="9" t="str">
-        <x:v>S85 V10 Rod Bearing Premature Failure (CATASTROPHIC) - E60 M5</x:v>
+        <x:v>Wastegate/Boost Solenoid Issues</x:v>
       </x:c>
       <x:c r="E162" s="9" t="str">
-        <x:v>MANDATORY PREVENTATIVE: Replace rod bearings before 70,000 miles ($6,500-$8,600). Upgrade to BE Bearings, ACL Race, or VAC Motorsports high-performance bearings with increased clearances (0.0025" or greater) - DO NOT use OEM BMW bearings which have same design flaw. Perform regular oil analysis every 5,000 miles to detect early bearing wear. Use only BMW-approved 10W-60 synthetic oil with frequent oil changes (5,000-7,500 mile intervals). NEVER redline engine before reaching full operating temperature. Replace high-pressure VANOS line at same time as rod bearings (labor overlap saves $2,000-$3,000). If catastrophic failure occurs: Complete engine replacement required ($15,000-$32,000).</x:v>
+        <x:v>Diagnose boost system for proper operation. Replace wastegate actuator or boost solenoid as needed. Check vacuum lines for leaks. Software update may address some issues.</x:v>
       </x:c>
       <x:c r="F162" s="9" t="n">
         <x:v>0</x:v>
@@ -8351,21 +9849,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="163" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A163" s="40" t="n">
         <x:v>162</x:v>
       </x:c>
       <x:c r="B163" s="9" t="str">
-        <x:v>bmw-m5-s85-throttle-actuator-2006</x:v>
+        <x:v>bmw-n55-carbon-buildup-2012</x:v>
       </x:c>
       <x:c r="C163" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
       </x:c>
       <x:c r="D163" s="9" t="str">
-        <x:v>S85 V10 Throttle Body Actuator Failure - E60 M5</x:v>
+        <x:v>Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E163" s="9" t="str">
-        <x:v>Replace failed throttle actuator(s) with OEM units ($1,400-$1,700 each) or upgrade to Evolve Automotive uprated throttle actuators ($1,500-$1,800 each) for improved durability and increased lifespan - these have upgraded internal components that prevent repeat failure. ECU Testing and Euro Power Motorsports offer actuator rebuilds ($500-$800 per actuator) as cost-effective alternatives. M5Post consensus: when one actuator fails, replace both at same time to save labor costs since second will fail within 6-12 months. Labor: 3 hours professional / 4+ hours DIY.</x:v>
+        <x:v>Walnut blast cleaning of intake valves every 50,000-70,000 miles. Install catch can to reduce oil vapor. Use quality fuel. BMW port injection on later engines helps reduce this issue.</x:v>
       </x:c>
       <x:c r="F163" s="9" t="n">
         <x:v>0</x:v>
@@ -8374,21 +9872,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="1056" hidden="0" customHeight="1">
+    <x:row r="164" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A164" s="40" t="n">
         <x:v>163</x:v>
       </x:c>
       <x:c r="B164" s="9" t="str">
-        <x:v>bmw-m5-s85-vanos-pump-2006</x:v>
+        <x:v>bmw-n55-charge-pipe-2012</x:v>
       </x:c>
       <x:c r="C164" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5 | S85</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D164" s="9" t="str">
-        <x:v>VANOS High-Pressure Pump &amp; Line Failure (CATASTROPHIC) - E60 M5</x:v>
+        <x:v>Charge Pipe Failure/Cracking</x:v>
       </x:c>
       <x:c r="E164" s="9" t="str">
-        <x:v>Replace high-pressure VANOS line with updated design that includes proper bend radius ($3,000 parts + labor). Replace VANOS high-pressure pump if showing signs of wear or contamination. DrVanos offers fully rebuilt S85 VANOS pumps ($1,800 + $400 core deposit) - M5Post gold standard for rebuilds. This repair is BEST performed simultaneously with rod bearing replacement to save on overlapping labor costs ($2,000-$4,000 savings). WARNING: DO NOT ignore VANOS line leaks - metal debris from failed pump circulates through entire lubrication system and can destroy engine. If catastrophic failure: engine replacement required ($32,000).</x:v>
+        <x:v>Replace with upgraded aluminum charge pipe for reliability. If keeping stock, inspect regularly for cracks. Upgraded pipe is recommended for any tuned vehicle. Installation is relatively straightforward.</x:v>
       </x:c>
       <x:c r="F164" s="9" t="n">
         <x:v>0</x:v>
@@ -8397,21 +9895,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="1188" hidden="0" customHeight="1">
+    <x:row r="165" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A165" s="40" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B165" s="9" t="str">
-        <x:v>bmw-m5-smg-pump-2006</x:v>
+        <x:v>bmw-n55-injector-2012</x:v>
       </x:c>
       <x:c r="C165" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D165" s="9" t="str">
-        <x:v>SMG III Hydraulic Pump Failure - E60 M5</x:v>
+        <x:v>High-Pressure Fuel Injector Issues</x:v>
       </x:c>
       <x:c r="E165" s="9" t="str">
-        <x:v>DIAGNOSIS FIRST: Insist on proper diagnosis before pump replacement - accumulator failure has similar symptoms and costs $500 vs. $5,000. If pump confirmed failed: Try rebuild first - carbon buildup can often be cleaned for fraction of replacement cost. SMG Society and specialty shops offer pump rebuilds ($300 pump + labor + fluids = $1,500-$2,500). If rebuild unsuccessful: Replace SMG pump with OEM or remanufactured unit ($5,000-$7,700 dealership, $5,000-$6,500 independent specialist). Replace hydraulic accumulator at same time if vehicle has 60,000+ miles ($300-$500 additional). Flush and replace SMG hydraulic fluid and manual transmission fluid during pump replacement.</x:v>
+        <x:v>Replace failed injector(s) with correct index version. Consider cleaning service for carbon buildup. Use quality fuel. All injectors should be same index for proper operation.</x:v>
       </x:c>
       <x:c r="F165" s="9" t="n">
         <x:v>0</x:v>
@@ -8420,21 +9918,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="166" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A166" s="40" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B166" s="9" t="str">
-        <x:v>bmw-m5-timing-chain-guide-wear-2000</x:v>
+        <x:v>bmw-n55-oil-filter-housing-2012</x:v>
       </x:c>
       <x:c r="C166" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D166" s="9" t="str">
-        <x:v>Timing Chain Guide Wear and Chain Tensioner Noise on the S62 V8</x:v>
+        <x:v>Certain 2012 F30 N55 Vehicles Need an Oil-Filter-Housing Campaign Check</x:v>
       </x:c>
       <x:c r="E166" s="9" t="str">
-        <x:v>Diagnosis includes listening for chain noise on cold start, inspecting oil/filter for plastic guide debris, and checking timing adaptation/fault data. Repair generally requires replacing timing chain guides, tensioners, related rails, gaskets, and often addressing front-engine seals while disassembled. Preventive service is often recommended once noise appears rather than waiting for a failure.</x:v>
+        <x:v>Check the VIN and service-action history, then have a BMW-qualified technician inspect the housing material and leak source. Under the bulletin, the black plastic housing is replaced while the silver aluminum housing is left in place. ShowMeTheParts returned no exact 2012 335i oil-filter-housing candidate, and the former generic gasket links were removed.</x:v>
       </x:c>
       <x:c r="F166" s="9" t="n">
         <x:v>0</x:v>
@@ -8443,21 +9941,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="167" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A167" s="40" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B167" s="9" t="str">
-        <x:v>bmw-m5-torque-converter-shudder-2018</x:v>
+        <x:v>bmw-n55-valve-cover-2012</x:v>
       </x:c>
       <x:c r="C167" s="9" t="str">
-        <x:v>2018-2023 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D167" s="9" t="str">
-        <x:v>ZF 8HP Torque Converter Shudder</x:v>
+        <x:v>Valve Cover/Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E167" s="9" t="str">
-        <x:v>Perform a transmission fluid and filter change using genuine ZF LifeGuard 8 fluid. If the shudder persists, the torque converter must be replaced. BMW issued a service bulletin for some VINs. A software update for shift calibration may also help in mild cases.</x:v>
+        <x:v>Replace valve cover and gasket as an assembly (PCV valve is integrated). Clean oil from exhaust manifold. Monitor for leaks after repair. This is a common maintenance item at higher mileage.</x:v>
       </x:c>
       <x:c r="F167" s="9" t="n">
         <x:v>0</x:v>
@@ -8466,21 +9964,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="168" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A168" s="40" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B168" s="9" t="str">
-        <x:v>bmw-m5-valve-stem-seals-2012</x:v>
+        <x:v>bmw-n55-vanos-2012</x:v>
       </x:c>
       <x:c r="C168" s="9" t="str">
-        <x:v>2012-2023 | BMW | M5</x:v>
+        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D168" s="9" t="str">
-        <x:v>S63/S63TU Valve Stem Seal Failure &amp; Oil Consumption</x:v>
+        <x:v>Certain 2012 N55 3 Series Need a VANOS Gear-Bolt Recall Check</x:v>
       </x:c>
       <x:c r="E168" s="9" t="str">
-        <x:v>Replace valve stem seals with updated OEM or performance seals ($3,500-$10,000 depending on method). Labor-intensive repair requiring either cylinder head removal ($6,000-$10,000) or specialized valve spring compressor tools with heads on engine ($3,500-$6,000). Address issue EARLY to prevent catalytic converter damage from oil burning (adds $3,000-$5,000 to repair). Perform more frequent oil changes (5,000 miles) to minimize damage. Blue smoke test: let engine idle 30+ minutes until hot, then rev to redline briefly - big blue smoke plume = valve seals. Find shop that can replace valve seals with heads installed (specialized tools required) - saves $4,000+ in labor vs. full head removal.</x:v>
+        <x:v>Check the VIN for campaign 14V-176 before ordering VANOS solenoids or gears. For an affected vehicle, BMW specifies replacing the VANOS gear bolts and inspecting for loose or broken bolts, with additional gear work only when the campaign procedure requires it. Recall work belongs with an authorized BMW center, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F168" s="9" t="n">
         <x:v>0</x:v>
@@ -8489,21 +9987,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="528" hidden="0" customHeight="1">
+    <x:row r="169" ht="660" hidden="0" customHeight="1">
       <x:c r="A169" s="40" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B169" s="9" t="str">
-        <x:v>bmw-m6-e63-e64-active-steering-steering-gear-play-knock</x:v>
+        <x:v>bmw-n55-water-pump-2012</x:v>
       </x:c>
       <x:c r="C169" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
+        <x:v>2012-2013 | BMW | 3 Series | N54T, N55</x:v>
       </x:c>
       <x:c r="D169" s="9" t="str">
-        <x:v>E63/E64 Active Steering and Steering-Gear Play / Knock</x:v>
+        <x:v>2012-2013 335i/335is Overheat Warnings Need Coolant-Pump Diagnosis</x:v>
       </x:c>
       <x:c r="E169" s="9" t="str">
-        <x:v>Inspect the steering gear and front control-arm/thrust-arm bushings for play. Replace worn control-arm bushings/ball joints first as they are cheaper and frequently the source of the knock; if the steering rack/gear itself has internal play or leaks, it requires replacement (a significant cost) followed by an alignment.</x:v>
+        <x:v>Stop safely if an overheat warning appears and avoid continued operation until the cooling system is checked. Verify the chassis, engine and VIN, read fault memory and follow the current coolant-pump test plan before replacement. Settlement benefits were time-limited. ShowMeTheParts resolved five 2012 335i water-pump candidates, but fitment does not prove failure or remedy, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F169" s="9" t="n">
         <x:v>0</x:v>
@@ -8512,21 +10010,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="170" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A170" s="40" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B170" s="9" t="str">
-        <x:v>bmw-m6-f12-convertible-top-hydraulic-pump-relay-failure</x:v>
+        <x:v>bmw-x1-coolant-leak-2016</x:v>
       </x:c>
       <x:c r="C170" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Convertible (F12) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2016-2023 | BMW | X1 | B-series</x:v>
       </x:c>
       <x:c r="D170" s="9" t="str">
-        <x:v>F12 Convertible Top Hydraulic Pump and Relay Failure</x:v>
+        <x:v>Coolant Leaks - Water Pump &amp; Thermostat - F48 X1</x:v>
       </x:c>
       <x:c r="E170" s="9" t="str">
-        <x:v>Diagnose whether the fault is the pump's high-current relays (relatively cheap, often the cure), a pressure loss in the pump, a hydraulic leak, or a roof microswitch/sensor. Replace the relays first; if pressure loss persists, rebuild or replace the hydraulic pump unit (specialist rebuild services exist) and renew worn seals/sensors. Bleed and refill the hydraulic system after repair.</x:v>
+        <x:v>Replace failed water pump or thermostat housing. Electric water pump replacement is 2-3 hours labor. Thermostat housing is 1-2 hours. Always use BMW-approved coolant (blue or orange, do not mix). Properly bleed cooling system after repair to prevent air pockets. Inspect all coolant hoses during repair and replace if cracked. Preventive replacement of water pump at 80,000 miles recommended.</x:v>
       </x:c>
       <x:c r="F170" s="9" t="n">
         <x:v>0</x:v>
@@ -8535,21 +10033,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="171" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A171" s="40" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B171" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-7-speed-m-dct-mechatronic-clutch-pack-failure</x:v>
+        <x:v>bmw-x1-n20-timing-chain-2013</x:v>
       </x:c>
       <x:c r="C171" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2015 | BMW | X1 | N20</x:v>
       </x:c>
       <x:c r="D171" s="9" t="str">
-        <x:v>F12/F13 7-Speed M-DCT Mechatronic and Clutch Pack Failure</x:v>
+        <x:v>Lower-Engine Whine Requires X1 N20 Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E171" s="9" t="str">
-        <x:v>Scan for transmission codes to confirm whether the fault is the mechatronic unit or worn clutch packs. Mechatronic units can often be repaired/replaced and must be reprogrammed and adapted to the vehicle afterward. Worn clutch packs require a clutch replacement (dealer cost often $3,000-$5,000). Regular DCT fluid and filter changes help prevent premature wear; avoid prolonged clutch slip in traffic.</x:v>
+        <x:v>Confirm the exact model, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F171" s="9" t="n">
         <x:v>0</x:v>
@@ -8558,21 +10056,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="594" hidden="0" customHeight="1">
+    <x:row r="172" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A172" s="40" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B172" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-electric-water-pump-thermostat-failure</x:v>
+        <x:v>bmw-x1-n20-timing-chain-guide-2013</x:v>
       </x:c>
       <x:c r="C172" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2015 | BMW | X1 | N20</x:v>
       </x:c>
       <x:c r="D172" s="9" t="str">
-        <x:v>F12/F13 Electric Water Pump and Thermostat Failure</x:v>
+        <x:v>N20 Timing Chain Guide Failure</x:v>
       </x:c>
       <x:c r="E172" s="9" t="str">
-        <x:v>Replace the failed electric water pump and/or electronic thermostat with OEM units; inspect the radiator end-tanks and expansion tank for cracks and replace as needed. Pressure-test the cooling system, refresh coolant, and treat the pump/thermostat as wear items given the heat load. Address any overheating event immediately to avoid secondary engine damage.</x:v>
+        <x:v>Replace timing chain, guides, tensioner, and both sprockets as a complete kit. The repair requires removing the front of the engine and is labor-intensive. Updated guide materials are available. Preventive replacement at 80,000 miles is recommended for high-mileage N20 engines.</x:v>
       </x:c>
       <x:c r="F172" s="9" t="n">
         <x:v>0</x:v>
@@ -8581,44 +10079,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="528" hidden="0" customHeight="1">
+    <x:row r="173" ht="396" hidden="0" customHeight="1">
       <x:c r="A173" s="40" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B173" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-turbocharger-wastegate-rattle-oil-starvation</x:v>
+        <x:v>bmw-x1-oil-filter-housing-gasket-2013</x:v>
       </x:c>
       <x:c r="C173" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2022 | BMW | X1 | N20, B48</x:v>
       </x:c>
       <x:c r="D173" s="9" t="str">
-        <x:v>F12/F13 Turbocharger Wastegate Rattle and Oil Starvation</x:v>
+        <x:v>Oil Filter Housing Gasket Leak</x:v>
       </x:c>
       <x:c r="E173" s="9" t="str">
-        <x:v>Confirm wastegate rattle by listening at light throttle; worn actuators/linkages can be replaced or upgraded. For oil starvation, maintain strict oil-change intervals with the correct specification, allow proper cool-down after hard driving, and keep the cooling system healthy. Severely worn or whining turbos require rebuild or replacement.</x:v>
+        <x:v>Replace the oil filter housing gasket and clean all affected surfaces. Also inspect and replace the oil cooler gasket if present. Use only OEM-quality gaskets as aftermarket gaskets tend to fail prematurely. Typical repair takes 2-3 hours.</x:v>
       </x:c>
       <x:c r="F173" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G173" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="174" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A174" s="40" t="n">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B174" s="9" t="str">
-        <x:v>bmw-m6-rod-bearing-wear-2005</x:v>
+        <x:v>bmw-x1-oil-leak-2016</x:v>
       </x:c>
       <x:c r="C174" s="9" t="str">
-        <x:v>2005-2019 | BMW | M6 | S65, S63</x:v>
+        <x:v>2016-2023 | BMW | X1 | B46, B48</x:v>
       </x:c>
       <x:c r="D174" s="9" t="str">
-        <x:v>Rod Bearing Premature Wear (S65/S63 Engines)</x:v>
+        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - F48 X1</x:v>
       </x:c>
       <x:c r="E174" s="9" t="str">
-        <x:v>Perform a preventive rod bearing replacement between 60,000-80,000 miles on S65 engines, and inspect by 80,000-100,000 miles on S63 engines. Use upgraded ACL or King XP bearings with coated surfaces. Cut and send used oil filter for analysis — bearing material particles indicate wear progression. The job requires engine-out on the S65 (approximately 20 hours labor) or can be done in-car on the S63 with the oil pan dropped.</x:v>
+        <x:v>Replace valve cover gasket and/or oil filter housing gasket as needed. Valve cover replacement is 2-3 hours labor. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on B-series engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
       </x:c>
       <x:c r="F174" s="9" t="n">
         <x:v>0</x:v>
@@ -8627,21 +10125,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="528" hidden="0" customHeight="1">
+    <x:row r="175" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A175" s="40" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B175" s="9" t="str">
-        <x:v>bmw-m6-s63-carbon-buildup-intake-valves</x:v>
+        <x:v>bmw-x1-suspension-bushing-2016</x:v>
       </x:c>
       <x:c r="C175" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2016-2023 | BMW | X1</x:v>
       </x:c>
       <x:c r="D175" s="9" t="str">
-        <x:v>S63 Carbon Buildup on Intake Valves (Direct Injection)</x:v>
+        <x:v>Front Suspension Bushing &amp; Control Arm Wear - F48 X1</x:v>
       </x:c>
       <x:c r="E175" s="9" t="str">
-        <x:v>Have the intake valves walnut-blasted (media-blast cleaning) to remove carbon deposits without removing the cylinder heads. Many owners do this every 50,000-70,000 km. A properly functioning PCV/crankcase ventilation system and quality oil reduce deposit rate. An oil-catch can is sometimes fitted to slow accumulation.</x:v>
+        <x:v>Replace worn control arms or bushings. Most shops replace complete control arms (with integrated bushings) rather than pressing in new bushings alone. Alignment required after replacement. Inspect all suspension components while vehicle is lifted. Consider replacing both sides even if only one shows symptoms to avoid repeat labor costs. Use OEM or quality aftermarket parts (Lemforder, Meyle HD) for longevity.</x:v>
       </x:c>
       <x:c r="F175" s="9" t="n">
         <x:v>0</x:v>
@@ -8650,21 +10148,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="528" hidden="0" customHeight="1">
+    <x:row r="176" ht="660" hidden="0" customHeight="1">
       <x:c r="A176" s="40" t="n">
         <x:v>175</x:v>
       </x:c>
       <x:c r="B176" s="9" t="str">
-        <x:v>bmw-m6-s63-high-pressure-fuel-pump-fuel-injector-cold-start-misfire</x:v>
+        <x:v>bmw-x1-transfer-case-2013</x:v>
       </x:c>
       <x:c r="C176" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2023 | BMW | X1</x:v>
       </x:c>
       <x:c r="D176" s="9" t="str">
-        <x:v>S63 High-Pressure Fuel Pump / Fuel Injector Cold-Start Misfire</x:v>
+        <x:v>Transfer Case Failure - xDrive Models E84/F48 X1</x:v>
       </x:c>
       <x:c r="E176" s="9" t="str">
-        <x:v>Scan for misfire and fuel-system codes and test cold-start fuel-rail pressure. Replace a failing HPFP; for injector faults, replace the affected injector(s) with units of the correct matching index code (do not mix injector indexes on a bank) and re-code them. Address per the relevant BMW technical service bulletin for the N63/S63.</x:v>
+        <x:v>Diagnose specific failure point. Transfer case actuator motor can be replaced separately ($800-1,200) if caught early. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors for better durability. Common wear item on high-mileage xDrive models.</x:v>
       </x:c>
       <x:c r="F176" s="9" t="n">
         <x:v>0</x:v>
@@ -8673,21 +10171,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="177" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A177" s="40" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B177" s="9" t="str">
-        <x:v>bmw-m6-s63-rod-bearing-2013</x:v>
+        <x:v>bmw-x1-transfer-case-actuator-2013</x:v>
       </x:c>
       <x:c r="C177" s="9" t="str">
-        <x:v>2013-2018 | BMW | M6 | S63</x:v>
+        <x:v>2013-2022 | BMW | X1</x:v>
       </x:c>
       <x:c r="D177" s="9" t="str">
-        <x:v>S63 Twin-Turbo V8 Rod Bearing Concerns (F06/F12/F13 M6)</x:v>
+        <x:v>Transfer Case Actuator Motor Failure</x:v>
       </x:c>
       <x:c r="E177" s="9" t="str">
-        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles using ACL Race Rod Bearings 8B1578HX-STD ($150-250), King Bearings SV Series, or WPC-treated bearings from Lang Racing. Cost: $4,000-7,000 for preventive replacement. Oil changes every 5,000-7,500 miles mandatory (ignore BMW's 10,000-mile recommendation). Use Blackstone Labs oil analysis ($30/test) every 5,000 miles to monitor bearing wear metals. Preventive replacement recommended for peace of mind, especially on cars used for track days or spirited driving.</x:v>
+        <x:v>Replace the transfer case actuator motor (also called the servo motor). The transfer case itself usually does not need replacement. Ensure the transfer case fluid is changed at the same time. Some owners report success with rebuilt actuators at lower cost.</x:v>
       </x:c>
       <x:c r="F177" s="9" t="n">
         <x:v>0</x:v>
@@ -8696,21 +10194,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="1069.199951171875" hidden="0" customHeight="1">
+    <x:row r="178" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A178" s="40" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B178" s="9" t="str">
-        <x:v>bmw-m6-s85-rod-bearing-2006</x:v>
+        <x:v>bmw-x2-b48-timing-chain-tensioner-2018</x:v>
       </x:c>
       <x:c r="C178" s="9" t="str">
-        <x:v>2006-2010 | BMW | M6 | S85</x:v>
+        <x:v>2018-2023 | BMW | X2 | B48</x:v>
       </x:c>
       <x:c r="D178" s="9" t="str">
-        <x:v>S85 V10 Rod Bearing Failure (Catastrophic Engine Destruction)</x:v>
+        <x:v>B48 Timing Chain Tensioner Weakness</x:v>
       </x:c>
       <x:c r="E178" s="9" t="str">
-        <x:v>MANDATORY PREVENTIVE REPLACEMENT before 70,000 miles: Replace all 10 rod bearings with ACL Race Bearings 10B1580HX-STD (+0.001" clearance, $200-350) or WPC-treated bearings from Lang Racing, or VAC Motorsports kit VAC-HPRBK-S85, or Turner kit TMS222798, or FCP Euro kit 11247841703KT3. ALSO replace VANOS line 11367838669 and use ARP rod bolts (included in most kits). Cost: $6,500-9,500 preventive. If engine is destroyed from bearing failure: $15,000-32,000 for engine replacement or rebuild. NEVER use OEM bearings as replacements. Use Blackstone Labs oil analysis every 5,000 miles ($30/test) to monitor bearing wear metals.</x:v>
+        <x:v>Replace the timing chain tensioner and inspect the chain and guides. If the chain has stretched beyond specification, replace the full timing chain kit. Updated tensioner design from BMW addresses the oil pressure retention issue.</x:v>
       </x:c>
       <x:c r="F178" s="9" t="n">
         <x:v>0</x:v>
@@ -8719,21 +10217,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="179" ht="924" hidden="0" customHeight="1">
+    <x:row r="179" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A179" s="40" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B179" s="9" t="str">
-        <x:v>bmw-m6-s85-throttle-actuator-2006</x:v>
+        <x:v>bmw-x2-crankshaft-sensor-recall-2018</x:v>
       </x:c>
       <x:c r="C179" s="9" t="str">
-        <x:v>2006-2010 | BMW | M6 | S85</x:v>
+        <x:v>2018-2018 | BMW | X2</x:v>
       </x:c>
       <x:c r="D179" s="9" t="str">
-        <x:v>S85 V10 Throttle Actuator Failure (Plastic Gear Stripping)</x:v>
+        <x:v>2018 X2 Crankshaft Sensor Safety Recall 18V-465</x:v>
       </x:c>
       <x:c r="E179" s="9" t="str">
-        <x:v>Rebuild throttle actuators using Beisan Systems BS101 sintered metal gear kit ($250/set, need 2 sets for both actuators) for permanent fix. Beisan BS102 full rebuild service available ($300). Alternatively, rebuilt actuators from Euro Power Motorsports ($500-800 each). OEM replacement actuators from BMW cost $2,000-4,500. Total cost: $500-4,500 depending on approach. Beisan Systems sintered metal gears are THE permanent fix - they replace the weak plastic PPA gears with metal gears that will not strip. Always rebuild both actuators simultaneously.</x:v>
+        <x:v>Check the VIN for an open 18V-465 campaign. If open, an authorized BMW dealer replaces the crankshaft sensor free of charge. A stall or sudden loss of power requires moving to a safe location and arranging BMW assistance; do not order a sensor from this card. ShowMeTheParts resolved exact X2 category fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F179" s="9" t="n">
         <x:v>0</x:v>
@@ -8742,21 +10240,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="180" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A180" s="40" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B180" s="9" t="str">
-        <x:v>bmw-m6-s85-v10-vanos-high-pressure-oil-pump-failure</x:v>
+        <x:v>bmw-x2-front-control-arm-bushings-2018</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
+        <x:v>2018-2023 | BMW | X2</x:v>
       </x:c>
       <x:c r="D180" s="9" t="str">
-        <x:v>S85 V10 VANOS High-Pressure Oil Pump Failure</x:v>
+        <x:v>Front Control Arm Bushing Premature Wear</x:v>
       </x:c>
       <x:c r="E180" s="9" t="str">
-        <x:v>Perform an oil-pressure test on the VANOS circuit at the first sign of cold-start knocking. Replace or professionally rebuild the high-pressure VANOS pump and renew the high-pressure lines/seals. Many owners do the VANOS pump preventively at the same time as the rod-bearing service since the oil pan is already removed. Use only BMW-spec oil and strict change intervals to prolong pump life.</x:v>
+        <x:v>Replace front control arms with new bushings (sold as complete assemblies by BMW). Aftermarket options with upgraded polyurethane bushings are available for longer life. Perform a four-wheel alignment after replacement.</x:v>
       </x:c>
       <x:c r="F180" s="9" t="n">
         <x:v>0</x:v>
@@ -8765,21 +10263,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="181" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A181" s="40" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B181" s="9" t="str">
-        <x:v>bmw-m6-smg-pump-failure-2005</x:v>
+        <x:v>bmw-x2-oil-filter-housing-2018</x:v>
       </x:c>
       <x:c r="C181" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6</x:v>
+        <x:v>2018-2023 | BMW | X2 | sDrive28i, xDrive28i | B48</x:v>
       </x:c>
       <x:c r="D181" s="9" t="str">
-        <x:v>SMG Hydraulic Pump and Clutch Actuator Failure</x:v>
+        <x:v>B48 Oil Filter Housing Gasket Leak/Cracking</x:v>
       </x:c>
       <x:c r="E181" s="9" t="str">
-        <x:v>Replace the SMG hydraulic pump and pressure accumulator. Bleed and refill the SMG hydraulic system with Pentosin CHF 11S fluid. Many owners convert to a traditional 6-speed manual swap using an aftermarket kit from companies like OS Giken or using the E90 M3 6MT parts. Budget $2,000-4,000 for SMG repair or $5,000-8,000 for a manual conversion.</x:v>
+        <x:v>Replace the cracked oil filter housing. OEM plastic housing replacement (BMW 11428596283, $412 dealer) will eventually crack again. RECOMMENDED: Install aftermarket aluminum upgrade housing ($250-350) which permanently eliminates the heat-cycling crack issue. FCP Euro kit 11428596283KT ($450) includes all gaskets and seals. If coolant and oil have mixed, perform complete oil flush and coolant system flush before installing new housing. Check for engine damage if contamination was prolonged.</x:v>
       </x:c>
       <x:c r="F181" s="9" t="n">
         <x:v>0</x:v>
@@ -8788,21 +10286,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="182" ht="330" hidden="0" customHeight="1">
       <x:c r="A182" s="40" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B182" s="9" t="str">
-        <x:v>bmw-m8-adaptive-suspension-leak-2020</x:v>
+        <x:v>bmw-x2-oil-filter-housing-gasket-2018</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
-        <x:v>2020-2025 | BMW | M8</x:v>
+        <x:v>2018-2023 | BMW | X2 | B48</x:v>
       </x:c>
       <x:c r="D182" s="9" t="str">
-        <x:v>Adaptive Suspension Damper Leaks</x:v>
+        <x:v>Oil Filter Housing Gasket Leak</x:v>
       </x:c>
       <x:c r="E182" s="9" t="str">
-        <x:v>Replace the leaking damper(s). BMW adaptive dampers must be replaced as complete units — they cannot be rebuilt. After replacement, a suspension calibration via ISTA is required to integrate the new damper into the adaptive system. Replacing in pairs (front or rear axle) is recommended.</x:v>
+        <x:v>Replace the oil filter housing gasket. Clean all oil-contaminated surfaces and inspect the serpentine belt for oil damage. Replace belt if oil-soaked. Use OEM-quality gasket material for longevity.</x:v>
       </x:c>
       <x:c r="F182" s="9" t="n">
         <x:v>0</x:v>
@@ -8811,21 +10309,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="990" hidden="0" customHeight="1">
+    <x:row r="183" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A183" s="40" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B183" s="9" t="str">
-        <x:v>bmw-m8-carbon-ceramic-brakes-2020</x:v>
+        <x:v>bmw-x2-tie-rod-recall-2019</x:v>
       </x:c>
       <x:c r="C183" s="9" t="str">
-        <x:v>2020-2024 | BMW | M8</x:v>
+        <x:v>2019-2019 | BMW | X2</x:v>
       </x:c>
       <x:c r="D183" s="9" t="str">
-        <x:v>M8 Carbon Ceramic Brake (CCB) Issues</x:v>
+        <x:v>2019 X2 Steering Tie-Rod Safety Recall 19V-601</x:v>
       </x:c>
       <x:c r="E183" s="9" t="str">
-        <x:v>Replace damaged CCB rotors ($3,000-$4,000 per corner, $12,000-$16,000 for all four). CCB rotors cannot be resurfaced - replacement is only option. Alternatively, convert to iron rotors using BimmerWorld CCB-to-iron conversion kit ($3,000-$5,000 total for all four corners) for dramatically lower running costs. PREVENTION: Avoid driving through standing water with hot brakes (thermal shock cracks rotors). Avoid aggressive braking over potholes or road debris. Squealing at low speed is normal for CCB material - not a defect. If only using car for street driving, iron conversion is more practical and cost-effective.</x:v>
+        <x:v>Check the VIN in BMW AIR or NHTSA for an open 19V-601 campaign. If open, an authorized BMW dealer checks both tie rods and replaces the tie rods and ball joints as necessary free of charge. Do not infer recall eligibility from model year alone or order steering parts from this card.</x:v>
       </x:c>
       <x:c r="F183" s="9" t="n">
         <x:v>0</x:v>
@@ -8834,21 +10332,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="396" hidden="0" customHeight="1">
+    <x:row r="184" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A184" s="40" t="n">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B184" s="9" t="str">
-        <x:v>bmw-m8-s63tu4-oil-consumption-2020</x:v>
+        <x:v>bmw-x2-transmission-jerking-2018</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
-        <x:v>2020-2025 | BMW | M8 | S63TU4</x:v>
+        <x:v>2018-2020 | BMW | X2</x:v>
       </x:c>
       <x:c r="D184" s="9" t="str">
-        <x:v>S63TU4 V8 Excessive Oil Consumption</x:v>
+        <x:v>Aisin 8-Speed Transmission Jerking</x:v>
       </x:c>
       <x:c r="E184" s="9" t="str">
-        <x:v>Monitor oil level regularly using iDrive oil level check. For excessive consumption beyond BMW's threshold, valve stem seal replacement may be warranted under warranty. Updated piston rings are available for severe cases. Always keep oil topped up between changes.</x:v>
+        <x:v>Start with transmission software recalibration at BMW dealer ($200-500) which may resolve calibration-related shifting issues. If software update does not resolve, transmission may require oil pump replacement or internal repair ($2,000-5,000). In severe cases with extensive oil pump neck wear, complete transmission replacement required ($5,000-7,000). Reference TSB GBSEL-SELP24 when visiting dealer.</x:v>
       </x:c>
       <x:c r="F184" s="9" t="n">
         <x:v>0</x:v>
@@ -8857,21 +10355,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="858" hidden="0" customHeight="1">
+    <x:row r="185" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A185" s="40" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B185" s="9" t="str">
-        <x:v>bmw-m8-s63tu4-rod-bearing-2020</x:v>
+        <x:v>bmw-x2-valve-cover-gasket-2018</x:v>
       </x:c>
       <x:c r="C185" s="9" t="str">
-        <x:v>2020-2024 | BMW | M8</x:v>
+        <x:v>2018-2023 | BMW | X2</x:v>
       </x:c>
       <x:c r="D185" s="9" t="str">
-        <x:v>S63TU4 Rod Bearing Wear (M8/M8 Competition)</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E185" s="9" t="str">
-        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles or sooner if tracked ($5,000-$8,000). Use ACL Race bearings 8B1578HX-STD ($200-350) which have wider clearance tolerances than OEM for better oil film protection. Monitor bearing health with Blackstone Labs oil analysis ($30/sample) every oil change - elevated copper/lead indicates bearing wear starting. If bearings have failed: engine replacement required ($20,000-$40,000). CRITICAL: If you hear any knocking from bottom end, stop driving immediately and tow to shop.</x:v>
+        <x:v>Replace valve cover gasket. Genuine BMW valve cover assembly 11127611278 ($200-350) includes integrated gasket. Labor typically 2-3 hours ($300-500). Total cost $700-1,000 at shop. DIY possible with basic tools to save $300-500 in labor. Replace spark plug tube seals at same time if applicable - labor overlap saves money. Monitor oil level between repairs.</x:v>
       </x:c>
       <x:c r="F185" s="9" t="n">
         <x:v>0</x:v>
@@ -8880,21 +10378,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="186" ht="990" hidden="0" customHeight="1">
       <x:c r="A186" s="40" t="n">
         <x:v>185</x:v>
       </x:c>
       <x:c r="B186" s="9" t="str">
-        <x:v>bmw-n54-hpfp</x:v>
+        <x:v>bmw-x3-coolant-expansion-tank-2004</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
-        <x:v>2007-2010 | BMW | 3 Series | N54</x:v>
+        <x:v>2004-2023 | BMW | X3</x:v>
       </x:c>
       <x:c r="D186" s="9" t="str">
-        <x:v>N54 Long Crank or Power Loss Requires Fuel-Pressure Diagnosis</x:v>
+        <x:v>Coolant Expansion Tank Cracking</x:v>
       </x:c>
       <x:c r="E186" s="9" t="str">
-        <x:v>Have a BMW-qualified technician read fault memory and follow the bulletin pressure tests for 2FBF, 29DC, 29F1 or 29F2 before replacing the pump. The historical ten-year/120,000-mile emissions-warranty extension has expired for this population and is not a current coverage promise. ShowMeTheParts resolved three 2009 335i fuel-pump candidates, but catalog fitment is not diagnosis or remedy proof and no commerce link is approved.</x:v>
+        <x:v>Replace expansion tank and coolant ($50-100 DIY parts, $200-400 independent shop, $400-580 dealer). Very simple DIY repair taking 30 minutes - drain coolant, unbolt old tank, install new tank, refill with BMW-spec coolant (blue or pink/orange premix). Use Behr or OEM BMW expansion tank - Dorman aftermarket tanks may fail prematurely. YouTube and Pelicanparts have detailed DIY guides. PREVENTIVE: Replace every 5-7 years or 80-100k miles before cracks develop. Check tank regularly for hairline cracks. Don't ignore coolant leaks - can lead to catastrophic overheating and head gasket failure.</x:v>
       </x:c>
       <x:c r="F186" s="9" t="n">
         <x:v>0</x:v>
@@ -8903,44 +10401,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="290.3999938964844" hidden="0" customHeight="1">
+    <x:row r="187" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A187" s="40" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B187" s="9" t="str">
-        <x:v>bmw-n55-boost-solenoid-2012</x:v>
+        <x:v>bmw-x3-electric-water-pump-2011</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
+        <x:v>2011-2026 | BMW | X3</x:v>
       </x:c>
       <x:c r="D187" s="9" t="str">
-        <x:v>Wastegate/Boost Solenoid Issues</x:v>
+        <x:v>Electric Water Pump Failure</x:v>
       </x:c>
       <x:c r="E187" s="9" t="str">
-        <x:v>Diagnose boost system for proper operation. Replace wastegate actuator or boost solenoid as needed. Check vacuum lines for leaks. Software update may address some issues.</x:v>
+        <x:v>Replace the electric water pump and thermostat together, as they are part of the same cooling circuit and the thermostat often fails concurrently. Bleed the cooling system thoroughly after replacement. Some owners carry a spare pump due to the sudden failure nature.</x:v>
       </x:c>
       <x:c r="F187" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G187" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="188" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A188" s="40" t="n">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B188" s="9" t="str">
-        <x:v>bmw-n55-carbon-buildup-2012</x:v>
+        <x:v>bmw-x3-m-electric-wastegate-actuator-adaptation-fault-boost-cutout-ea</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
+        <x:v>2020-2020 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D188" s="9" t="str">
-        <x:v>Intake Valve Carbon Buildup</x:v>
+        <x:v>2020 X3 M Wastegate Adaptation Faults Require Software Diagnosis</x:v>
       </x:c>
       <x:c r="E188" s="9" t="str">
-        <x:v>Walnut blast cleaning of intake valves every 50,000-70,000 miles. Install catch can to reduce oil vapor. Use quality fuel. BMW port injection on later engines helps reduce this issue.</x:v>
+        <x:v>Confirm the production date, fault codes and current vehicle integration level. If the I-level is below S15A-20-03-510, a BMW-qualified repairer follows the bulletin and programs the vehicle with the specified or newer approved ISTA level. Diagnose unrelated mechanical noise separately; do not replace an actuator or turbocharger from this card.</x:v>
       </x:c>
       <x:c r="F188" s="9" t="n">
         <x:v>0</x:v>
@@ -8949,21 +10447,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="189" ht="462" hidden="0" customHeight="1">
       <x:c r="A189" s="40" t="n">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B189" s="9" t="str">
-        <x:v>bmw-n55-charge-pipe-2012</x:v>
+        <x:v>bmw-x3-m-fuel-tank-inlet-check-valve-weld-failure-2021-x3-m</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2021-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D189" s="9" t="str">
-        <x:v>Charge Pipe Failure/Cracking</x:v>
+        <x:v>2021 X3 M Fuel-Tank Safety Recall 21V-199</x:v>
       </x:c>
       <x:c r="E189" s="9" t="str">
-        <x:v>Replace with upgraded aluminum charge pipe for reliability. If keeping stock, inspect regularly for cracks. Upgraded pipe is recommended for any tuned vehicle. Installation is relatively straightforward.</x:v>
+        <x:v>Check the VIN for an open 21V-199 campaign. If open, an authorized BMW dealer replaces the fuel tank free of charge. If fuel odor or leakage appears, move safely away from traffic, stop, have occupants exit and contact BMW roadside assistance; do not continue driving or order a tank from this card.</x:v>
       </x:c>
       <x:c r="F189" s="9" t="n">
         <x:v>0</x:v>
@@ -8972,21 +10470,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="277.20001220703125" hidden="0" customHeight="1">
+    <x:row r="190" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A190" s="40" t="n">
         <x:v>189</x:v>
       </x:c>
       <x:c r="B190" s="9" t="str">
-        <x:v>bmw-n55-injector-2012</x:v>
+        <x:v>bmw-x3-m-idrive-control-display-blank-screen-infotainment-glitches-f9</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2020-2021 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D190" s="9" t="str">
-        <x:v>High-Pressure Fuel Injector Issues</x:v>
+        <x:v>iDrive Control Display Blank Screen and Infotainment Glitches - F97 X3 M (2019-2021)</x:v>
       </x:c>
       <x:c r="E190" s="9" t="str">
-        <x:v>Replace failed injector(s) with correct index version. Consider cleaning service for carbon buildup. Use quality fuel. All injectors should be same index for proper operation.</x:v>
+        <x:v>First try the latest iDrive/head-unit software update at the dealer, which resolves many of the early glitches, reboots, and camera issues. If the display panel hardware has failed (lines, persistent blank screen with backlight off), the control display/screen assembly is replaced. A soft reset (press-and-hold volume/power) can temporarily clear a frozen screen.</x:v>
       </x:c>
       <x:c r="F190" s="9" t="n">
         <x:v>0</x:v>
@@ -8995,21 +10493,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="191" ht="462" hidden="0" customHeight="1">
       <x:c r="A191" s="40" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="B191" s="9" t="str">
-        <x:v>bmw-n55-oil-filter-housing-2012</x:v>
+        <x:v>bmw-x3-m-improperly-welded-front-seat-frame-2019-2021-x3-m</x:v>
       </x:c>
       <x:c r="C191" s="9" t="str">
-        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
+        <x:v>2021-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D191" s="9" t="str">
-        <x:v>Certain 2012 F30 N55 Vehicles Need an Oil-Filter-Housing Campaign Check</x:v>
+        <x:v>2021 X3 M Front Seat-Frame Safety Recall 23V-211</x:v>
       </x:c>
       <x:c r="E191" s="9" t="str">
-        <x:v>Check the VIN and service-action history, then have a BMW-qualified technician inspect the housing material and leak source. Under the bulletin, the black plastic housing is replaced while the silver aluminum housing is left in place. ShowMeTheParts returned no exact 2012 335i oil-filter-housing candidate, and the former generic gasket links were removed.</x:v>
+        <x:v>Check the VIN for an open 23V-211 campaign. If open, an authorized BMW dealer replaces the affected front seat frame and backrest free of charge using VIN-selected parts. Contact BMW promptly if a front seat vibrates or makes abnormal noise; do not order seat components from this card.</x:v>
       </x:c>
       <x:c r="F191" s="9" t="n">
         <x:v>0</x:v>
@@ -9018,21 +10516,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="192" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A192" s="40" t="n">
         <x:v>191</x:v>
       </x:c>
       <x:c r="B192" s="9" t="str">
-        <x:v>bmw-n55-valve-cover-2012</x:v>
+        <x:v>bmw-x3-m-low-mounted-engine-oil-cooler-vulnerable-to-road-debris-punc</x:v>
       </x:c>
       <x:c r="C192" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D192" s="9" t="str">
-        <x:v>Valve Cover/Gasket Oil Leak</x:v>
+        <x:v>Low-Mounted Engine Oil Cooler Vulnerable to Road-Debris Puncture - F97 X3 M (S58)</x:v>
       </x:c>
       <x:c r="E192" s="9" t="str">
-        <x:v>Replace valve cover and gasket as an assembly (PCV valve is integrated). Clean oil from exhaust manifold. Monitor for leaks after repair. This is a common maintenance item at higher mileage.</x:v>
+        <x:v>Inspect the oil cooler periodically for stone damage and weeping; fit a protective mesh/guard in front of the cooler as preventive insurance (popular among track and spirited-use owners). If punctured, stop driving immediately and replace the oil cooler and refill with the correct oil; verify no bearing damage occurred from any oil starvation.</x:v>
       </x:c>
       <x:c r="F192" s="9" t="n">
         <x:v>0</x:v>
@@ -9041,21 +10539,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="193" ht="594" hidden="0" customHeight="1">
       <x:c r="A193" s="40" t="n">
         <x:v>192</x:v>
       </x:c>
       <x:c r="B193" s="9" t="str">
-        <x:v>bmw-n55-vanos-2012</x:v>
+        <x:v>bmw-x3-m-oem-plastic-charge-pipe-cracking-blow-off-under-boost-f97-x3</x:v>
       </x:c>
       <x:c r="C193" s="9" t="str">
-        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
+        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D193" s="9" t="str">
-        <x:v>Certain 2012 N55 3 Series Need a VANOS Gear-Bolt Recall Check</x:v>
+        <x:v>OEM Plastic Charge Pipe Cracking / Blow-Off Under Boost - F97 X3 M (S58)</x:v>
       </x:c>
       <x:c r="E193" s="9" t="str">
-        <x:v>Check the VIN for campaign 14V-176 before ordering VANOS solenoids or gears. For an affected vehicle, BMW specifies replacing the VANOS gear bolts and inspecting for loose or broken bolts, with additional gear work only when the campaign procedure requires it. Recall work belongs with an authorized BMW center, so no commerce link is approved.</x:v>
+        <x:v>Replace the OEM plastic charge pipe with an aluminum (or reinforced) aftermarket charge pipe from suppliers such as FTP, Racing Dynamics, or Kies; this is the standard durable fix and is strongly recommended before or alongside any tune. A failed OEM pipe can be re-fitted with a new OEM unit but the same failure mode tends to recur, especially on modified cars.</x:v>
       </x:c>
       <x:c r="F193" s="9" t="n">
         <x:v>0</x:v>
@@ -9064,21 +10562,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="660" hidden="0" customHeight="1">
+    <x:row r="194" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A194" s="40" t="n">
         <x:v>193</x:v>
       </x:c>
       <x:c r="B194" s="9" t="str">
-        <x:v>bmw-n55-water-pump-2012</x:v>
+        <x:v>bmw-x3-n20-timing-chain-2011</x:v>
       </x:c>
       <x:c r="C194" s="9" t="str">
-        <x:v>2012-2013 | BMW | 3 Series | N54T, N55</x:v>
+        <x:v>2011-2017 | BMW | X3 | N20</x:v>
       </x:c>
       <x:c r="D194" s="9" t="str">
-        <x:v>2012-2013 335i/335is Overheat Warnings Need Coolant-Pump Diagnosis</x:v>
+        <x:v>N20 Timing Chain Guide Failure</x:v>
       </x:c>
       <x:c r="E194" s="9" t="str">
-        <x:v>Stop safely if an overheat warning appears and avoid continued operation until the cooling system is checked. Verify the chassis, engine and VIN, read fault memory and follow the current coolant-pump test plan before replacement. Settlement benefits were time-limited. ShowMeTheParts resolved five 2012 335i water-pump candidates, but fitment does not prove failure or remedy, so no commerce link is approved.</x:v>
+        <x:v>Replace the complete timing chain kit including chain, guides, tensioner, and sprockets. Preventive replacement is strongly recommended at 80,000 miles before failure occurs. The updated guide design uses more durable materials.</x:v>
       </x:c>
       <x:c r="F194" s="9" t="n">
         <x:v>0</x:v>
@@ -9092,16 +10590,16 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="B195" s="9" t="str">
-        <x:v>bmw-x1-coolant-leak-2016</x:v>
+        <x:v>bmw-x3-n20-timing-chain-2012</x:v>
       </x:c>
       <x:c r="C195" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1 | B-series</x:v>
+        <x:v>2013-2015 | BMW | X3 | N20</x:v>
       </x:c>
       <x:c r="D195" s="9" t="str">
-        <x:v>Coolant Leaks - Water Pump &amp; Thermostat - F48 X1</x:v>
+        <x:v>Lower-Engine Whine Requires X3 N20 Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E195" s="9" t="str">
-        <x:v>Replace failed water pump or thermostat housing. Electric water pump replacement is 2-3 hours labor. Thermostat housing is 1-2 hours. Always use BMW-approved coolant (blue or orange, do not mix). Properly bleed cooling system after repair to prevent air pockets. Inspect all coolant hoses during repair and replace if cracked. Preventive replacement of water pump at 80,000 miles recommended.</x:v>
+        <x:v>Confirm the exact X3 variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F195" s="9" t="n">
         <x:v>0</x:v>
@@ -9110,21 +10608,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="196" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A196" s="40" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="B196" s="9" t="str">
-        <x:v>bmw-x1-n20-timing-chain-2013</x:v>
+        <x:v>bmw-x3-oil-filter-housing-gasket-2007</x:v>
       </x:c>
       <x:c r="C196" s="9" t="str">
-        <x:v>2013-2015 | BMW | X1 | N20</x:v>
+        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
       </x:c>
       <x:c r="D196" s="9" t="str">
-        <x:v>Lower-Engine Whine Requires X1 N20 Timing-Chain Diagnosis</x:v>
+        <x:v>Oil Filter Housing Gasket Leak (N52, N20 Engines)</x:v>
       </x:c>
       <x:c r="E196" s="9" t="str">
-        <x:v>Confirm the exact model, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Replace oil filter housing gasket and oil cooler gasket ($40-80 DIY repair kit, $300-500 independent shop, $500-800 dealer). Requires draining some coolant and oil, removing housing, replacing gaskets, reassembling. Moderate DIY difficulty - Pelicanparts and YouTube have detailed model-specific guides. Use Victor Reinz or OEM BMW gasket kit for long-lasting seal - cheap gaskets leak within 20k miles. Address leak early before oil damages serpentine belt or alternator.</x:v>
       </x:c>
       <x:c r="F196" s="9" t="n">
         <x:v>0</x:v>
@@ -9133,21 +10631,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="197" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A197" s="40" t="n">
         <x:v>196</x:v>
       </x:c>
       <x:c r="B197" s="9" t="str">
-        <x:v>bmw-x1-n20-timing-chain-guide-2013</x:v>
+        <x:v>bmw-x3-transfer-case-actuator-2004</x:v>
       </x:c>
       <x:c r="C197" s="9" t="str">
-        <x:v>2013-2015 | BMW | X1 | N20</x:v>
+        <x:v>2004-2023 | BMW | X3</x:v>
       </x:c>
       <x:c r="D197" s="9" t="str">
-        <x:v>N20 Timing Chain Guide Failure</x:v>
+        <x:v>Transfer Case Actuator Motor Failure (xDrive AWD System)</x:v>
       </x:c>
       <x:c r="E197" s="9" t="str">
-        <x:v>Replace timing chain, guides, tensioner, and both sprockets as a complete kit. The repair requires removing the front of the engine and is labor-intensive. Updated guide materials are available. Preventive replacement at 80,000 miles is recommended for high-mileage N20 engines.</x:v>
+        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket repair kit. DIY repair kits cost $100-150 and include replacement plastic gears, clips, and seals - straightforward installation saves $1,200+. Complete actuator motor replacement costs $540 for the assembly if DIY, or $1,500-2,200 at dealer. If transfer case itself is damaged from prolonged actuator failure, complete transfer case replacement costs $1,400-3,300. PREVENTIVE: If buying used X3 over 80k miles, budget for this repair - it's "when not if" on xDrive models. Check for clicking noise when shutting off ignition.</x:v>
       </x:c>
       <x:c r="F197" s="9" t="n">
         <x:v>0</x:v>
@@ -9161,85 +10659,85 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="B198" s="9" t="str">
-        <x:v>bmw-x1-oil-filter-housing-gasket-2013</x:v>
+        <x:v>bmw-x3-transfer-case-actuator-2011</x:v>
       </x:c>
       <x:c r="C198" s="9" t="str">
-        <x:v>2013-2022 | BMW | X1 | N20, B48</x:v>
+        <x:v>2011-2026 | BMW | X3</x:v>
       </x:c>
       <x:c r="D198" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak</x:v>
+        <x:v>Transfer Case Actuator Motor Failure</x:v>
       </x:c>
       <x:c r="E198" s="9" t="str">
-        <x:v>Replace the oil filter housing gasket and clean all affected surfaces. Also inspect and replace the oil cooler gasket if present. Use only OEM-quality gaskets as aftermarket gaskets tend to fail prematurely. Typical repair takes 2-3 hours.</x:v>
+        <x:v>Replace the transfer case actuator motor. Change the transfer case fluid at the same time. The actuator can be replaced without removing the entire transfer case. Rebuilt units are available at lower cost but OEM is recommended for reliability.</x:v>
       </x:c>
       <x:c r="F198" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G198" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="199" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A199" s="40" t="n">
         <x:v>198</x:v>
       </x:c>
       <x:c r="B199" s="9" t="str">
-        <x:v>bmw-x1-oil-leak-2016</x:v>
+        <x:v>bmw-x3-valve-cover-gasket-2004</x:v>
       </x:c>
       <x:c r="C199" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1 | B46, B48</x:v>
+        <x:v>2004-2017 | BMW | X3 | 2.5i, 3.0i, 3.0si | M54, N52</x:v>
       </x:c>
       <x:c r="D199" s="9" t="str">
-        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - F48 X1</x:v>
+        <x:v>Valve Cover Gasket Oil Leaks (M54, N52 Engines)</x:v>
       </x:c>
       <x:c r="E199" s="9" t="str">
-        <x:v>Replace valve cover gasket and/or oil filter housing gasket as needed. Valve cover replacement is 2-3 hours labor. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on B-series engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
+        <x:v>Replace valve cover gasket and VANOS solenoid o-rings ($300-500 independent shop, $700-1,000 dealer, $80-150 DIY parts). On M54 engines, also replace ignition coil boots if contaminated by oil ($50 additional). Use OEM BMW gasket or Victor Reinz brand - aftermarket quality matters for long-term seal. Relatively straightforward DIY repair - saves $200-400 in labor. YouTube and Bimmerfest have detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage).</x:v>
       </x:c>
       <x:c r="F199" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G199" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="200" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A200" s="40" t="n">
         <x:v>199</x:v>
       </x:c>
       <x:c r="B200" s="9" t="str">
-        <x:v>bmw-x1-suspension-bushing-2016</x:v>
+        <x:v>bmw-x3-valve-cover-gasket-2011</x:v>
       </x:c>
       <x:c r="C200" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1</x:v>
+        <x:v>2011-2022 | BMW | X3 | N20, B48</x:v>
       </x:c>
       <x:c r="D200" s="9" t="str">
-        <x:v>Front Suspension Bushing &amp; Control Arm Wear - F48 X1</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E200" s="9" t="str">
-        <x:v>Replace worn control arms or bushings. Most shops replace complete control arms (with integrated bushings) rather than pressing in new bushings alone. Alignment required after replacement. Inspect all suspension components while vehicle is lifted. Consider replacing both sides even if only one shows symptoms to avoid repeat labor costs. Use OEM or quality aftermarket parts (Lemforder, Meyle HD) for longevity.</x:v>
+        <x:v>Replace the valve cover gasket. Inspect the valve cover for warping or cracks — if damaged, replace the entire cover assembly. Clean all oil residue from surrounding components. Use a torque wrench to prevent over-tightening which causes cover warping.</x:v>
       </x:c>
       <x:c r="F200" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G200" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="660" hidden="0" customHeight="1">
+    <x:row r="201" ht="858" hidden="0" customHeight="1">
       <x:c r="A201" s="40" t="n">
         <x:v>200</x:v>
       </x:c>
       <x:c r="B201" s="9" t="str">
-        <x:v>bmw-x1-transfer-case-2013</x:v>
+        <x:v>bmw-x3-vanos-solenoid-2007</x:v>
       </x:c>
       <x:c r="C201" s="9" t="str">
-        <x:v>2013-2023 | BMW | X1</x:v>
+        <x:v>2007-2017 | BMW | X3 | M40i, M50, xDrive35i | N52, N55</x:v>
       </x:c>
       <x:c r="D201" s="9" t="str">
-        <x:v>Transfer Case Failure - xDrive Models E84/F48 X1</x:v>
+        <x:v>VANOS Solenoid Failure (N52, N55 Engines)</x:v>
       </x:c>
       <x:c r="E201" s="9" t="str">
-        <x:v>Diagnose specific failure point. Transfer case actuator motor can be replaced separately ($800-1,200) if caught early. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors for better durability. Common wear item on high-mileage xDrive models.</x:v>
+        <x:v>Replace VANOS solenoids and seals ($250-400 European shops, $729-882 US average). Use high-quality oil (5W-30 or 0W-40 BMW LL-01 spec) and change every 5,000-7,000 miles to prevent future failures - cheap oil or extended intervals kill VANOS solenoids. Some cases may require complete VANOS unit rebuild ($1,500-2,500). PREVENTIVE: Replace VANOS solenoids and seals every 50k miles as maintenance - much cheaper than waiting for failure. On F25 X3 with N52/N55, check TSB SI B12 14 10 for VANOS gear assembly bolt issue.</x:v>
       </x:c>
       <x:c r="F201" s="9" t="n">
         <x:v>0</x:v>
@@ -9248,21 +10746,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="202" ht="1016.4000244140625" hidden="0" customHeight="1">
       <x:c r="A202" s="40" t="n">
         <x:v>201</x:v>
       </x:c>
       <x:c r="B202" s="9" t="str">
-        <x:v>bmw-x1-transfer-case-actuator-2013</x:v>
+        <x:v>bmw-x3-wastegate-rattle-2011</x:v>
       </x:c>
       <x:c r="C202" s="9" t="str">
-        <x:v>2013-2022 | BMW | X1</x:v>
+        <x:v>2011-2023 | BMW | X3 | M40i, M50, sDrive30i, xDrive28i, xDrive30i, xDrive35i</x:v>
       </x:c>
       <x:c r="D202" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure</x:v>
+        <x:v>Turbocharger Wastegate Rattle (N55, N20, B58 Engines)</x:v>
       </x:c>
       <x:c r="E202" s="9" t="str">
-        <x:v>Replace the transfer case actuator motor (also called the servo motor). The transfer case itself usually does not need replacement. Ensure the transfer case fluid is changed at the same time. Some owners report success with rebuilt actuators at lower cost.</x:v>
+        <x:v>Replace wastegate actuator ($400-800) or use aftermarket wastegate repair kit with upgraded stainless steel bushings ($150-300). Some cases require complete turbocharger replacement ($2,000-$4,000). VTT (Vargas Turbo Technologies) repair kits popular on forums - upgraded materials prevent future rattle. MONITORING: Early wastegate rattle may be harmless (annoying but no performance loss). If car boosts normally and no underboost codes, can monitor rattle without urgent repair. However, if check engine light appears with code 30FF or boost pressure drops, repair immediately to prevent turbo damage.</x:v>
       </x:c>
       <x:c r="F202" s="9" t="n">
         <x:v>0</x:v>
@@ -9271,21 +10769,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="203" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A203" s="40" t="n">
         <x:v>202</x:v>
       </x:c>
       <x:c r="B203" s="9" t="str">
-        <x:v>bmw-x2-b48-timing-chain-tensioner-2018</x:v>
+        <x:v>bmw-x3-water-pump-2007</x:v>
       </x:c>
       <x:c r="C203" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | B48</x:v>
+        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
       </x:c>
       <x:c r="D203" s="9" t="str">
-        <x:v>B48 Timing Chain Tensioner Weakness</x:v>
+        <x:v>Electric Water Pump Failure (N52, N20 Engines)</x:v>
       </x:c>
       <x:c r="E203" s="9" t="str">
-        <x:v>Replace the timing chain tensioner and inspect the chain and guides. If the chain has stretched beyond specification, replace the full timing chain kit. Updated tensioner design from BMW addresses the oil pressure retention issue.</x:v>
+        <x:v>Replace electric water pump at first sign of failure ($800 parts + labor). Consider preventative replacement at 70-80k miles to avoid being stranded ($400 parts, DIY-able). CRITICAL: If you own 2013-2017 X3 28i, verify recall repair (protective shield installation) has been completed to prevent fire risk - check with BMW dealer using VIN. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps cylinder heads ($4,000+ repair). Call tow truck.</x:v>
       </x:c>
       <x:c r="F203" s="9" t="n">
         <x:v>0</x:v>
@@ -9294,21 +10792,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="204" ht="1240.800048828125" hidden="0" customHeight="1">
       <x:c r="A204" s="40" t="n">
         <x:v>203</x:v>
       </x:c>
       <x:c r="B204" s="9" t="str">
-        <x:v>bmw-x2-crankshaft-sensor-recall-2018</x:v>
+        <x:v>bmw-x3m-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C204" s="9" t="str">
-        <x:v>2018-2018 | BMW | X2</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D204" s="9" t="str">
-        <x:v>2018 X2 Crankshaft Sensor Safety Recall 18V-465</x:v>
+        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E204" s="9" t="str">
-        <x:v>Check the VIN for an open 18V-465 campaign. If open, an authorized BMW dealer replaces the crankshaft sensor free of charge. A stall or sudden loss of power requires moving to a safe location and arranging BMW assistance; do not order a sensor from this card. ShowMeTheParts resolved exact X2 category fitment only, so no commerce link is approved.</x:v>
+        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
       </x:c>
       <x:c r="F204" s="9" t="n">
         <x:v>0</x:v>
@@ -9317,21 +10815,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="205" ht="1188" hidden="0" customHeight="1">
       <x:c r="A205" s="40" t="n">
         <x:v>204</x:v>
       </x:c>
       <x:c r="B205" s="9" t="str">
-        <x:v>bmw-x2-front-control-arm-bushings-2018</x:v>
+        <x:v>bmw-x3m-cooling-track-use-2020</x:v>
       </x:c>
       <x:c r="C205" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D205" s="9" t="str">
-        <x:v>Front Control Arm Bushing Premature Wear</x:v>
+        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E205" s="9" t="str">
-        <x:v>Replace front control arms with new bushings (sold as complete assemblies by BMW). Aftermarket options with upgraded polyurethane bushings are available for longer life. Perform a four-wheel alignment after replacement.</x:v>
+        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
       </x:c>
       <x:c r="F205" s="9" t="n">
         <x:v>0</x:v>
@@ -9340,21 +10838,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="206" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A206" s="40" t="n">
         <x:v>205</x:v>
       </x:c>
       <x:c r="B206" s="9" t="str">
-        <x:v>bmw-x2-oil-filter-housing-2018</x:v>
+        <x:v>bmw-x3m-differential-bolt-2020</x:v>
       </x:c>
       <x:c r="C206" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | sDrive28i, xDrive28i | B48</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D206" s="9" t="str">
-        <x:v>B48 Oil Filter Housing Gasket Leak/Cracking</x:v>
+        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E206" s="9" t="str">
-        <x:v>Replace the cracked oil filter housing. OEM plastic housing replacement (BMW 11428596283, $412 dealer) will eventually crack again. RECOMMENDED: Install aftermarket aluminum upgrade housing ($250-350) which permanently eliminates the heat-cycling crack issue. FCP Euro kit 11428596283KT ($450) includes all gaskets and seals. If coolant and oil have mixed, perform complete oil flush and coolant system flush before installing new housing. Check for engine damage if contamination was prolonged.</x:v>
+        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
       </x:c>
       <x:c r="F206" s="9" t="n">
         <x:v>0</x:v>
@@ -9363,21 +10861,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" ht="330" hidden="0" customHeight="1">
+    <x:row r="207" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A207" s="40" t="n">
         <x:v>206</x:v>
       </x:c>
       <x:c r="B207" s="9" t="str">
-        <x:v>bmw-x2-oil-filter-housing-gasket-2018</x:v>
+        <x:v>bmw-x3m-s58-bearing-recall-2020</x:v>
       </x:c>
       <x:c r="C207" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | B48</x:v>
+        <x:v>2020-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D207" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak</x:v>
+        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E207" s="9" t="str">
-        <x:v>Replace the oil filter housing gasket. Clean all oil-contaminated surfaces and inspect the serpentine belt for oil damage. Replace belt if oil-soaked. Use OEM-quality gasket material for longevity.</x:v>
+        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
       </x:c>
       <x:c r="F207" s="9" t="n">
         <x:v>0</x:v>
@@ -9386,21 +10884,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="208" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="208" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A208" s="40" t="n">
         <x:v>207</x:v>
       </x:c>
       <x:c r="B208" s="9" t="str">
-        <x:v>bmw-x2-tie-rod-recall-2019</x:v>
+        <x:v>bmw-x3m-transfer-case-2020</x:v>
       </x:c>
       <x:c r="C208" s="9" t="str">
-        <x:v>2019-2019 | BMW | X2</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D208" s="9" t="str">
-        <x:v>2019 X2 Steering Tie-Rod Safety Recall 19V-601</x:v>
+        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E208" s="9" t="str">
-        <x:v>Check the VIN in BMW AIR or NHTSA for an open 19V-601 campaign. If open, an authorized BMW dealer checks both tie rods and replaces the tie rods and ball joints as necessary free of charge. Do not infer recall eligibility from model year alone or order steering parts from this card.</x:v>
+        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
       </x:c>
       <x:c r="F208" s="9" t="n">
         <x:v>0</x:v>
@@ -9409,21 +10907,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="209" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A209" s="40" t="n">
         <x:v>208</x:v>
       </x:c>
       <x:c r="B209" s="9" t="str">
-        <x:v>bmw-x2-transmission-jerking-2018</x:v>
+        <x:v>bmw-x4-n20-timing-chain-2015</x:v>
       </x:c>
       <x:c r="C209" s="9" t="str">
-        <x:v>2018-2020 | BMW | X2</x:v>
+        <x:v>2015-2016 | BMW | X4 | xDrive28i, xDrive30i</x:v>
       </x:c>
       <x:c r="D209" s="9" t="str">
-        <x:v>Aisin 8-Speed Transmission Jerking</x:v>
+        <x:v>N20 Timing Chain Premature Failure - F26 X4 xDrive28i</x:v>
       </x:c>
       <x:c r="E209" s="9" t="str">
-        <x:v>Start with transmission software recalibration at BMW dealer ($200-500) which may resolve calibration-related shifting issues. If software update does not resolve, transmission may require oil pump replacement or internal repair ($2,000-5,000). In severe cases with extensive oil pump neck wear, complete transmission replacement required ($5,000-7,000). Reference TSB GBSEL-SELP24 when visiting dealer.</x:v>
+        <x:v>Complete timing chain kit replacement including chain, guides, tensioner, and sprockets. Must be performed by experienced BMW technician. Preventive replacement recommended at 60,000-80,000 miles. BMW extended warranty to 8 years/100,000 miles under class action settlement. Upgraded reinforced chain kit available from aftermarket. Labor is 10-14 hours for X4 due to AWD and tight engine bay.</x:v>
       </x:c>
       <x:c r="F209" s="9" t="n">
         <x:v>0</x:v>
@@ -9432,21 +10930,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="210" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A210" s="40" t="n">
         <x:v>209</x:v>
       </x:c>
       <x:c r="B210" s="9" t="str">
-        <x:v>bmw-x2-valve-cover-gasket-2018</x:v>
+        <x:v>bmw-x4-n20-timing-chain-guide-2015</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2</x:v>
+        <x:v>2015-2015 | BMW | X4 | N20</x:v>
       </x:c>
       <x:c r="D210" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>2015 X4 N20 Lower-Engine Whine Requires Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E210" s="9" t="str">
-        <x:v>Replace valve cover gasket. Genuine BMW valve cover assembly 11127611278 ($200-350) includes integrated gasket. Labor typically 2-3 hours ($300-500). Total cost $700-1,000 at shop. DIY possible with basic tools to save $300-500 in labor. Replace spark plug tube seals at same time if applicable - labor overlap saves money. Monitor oil level between repairs.</x:v>
+        <x:v>Confirm the exact xDrive28i variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F210" s="9" t="n">
         <x:v>0</x:v>
@@ -9455,21 +10953,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="211" ht="990" hidden="0" customHeight="1">
+    <x:row r="211" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A211" s="40" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="B211" s="9" t="str">
-        <x:v>bmw-x3-coolant-expansion-tank-2004</x:v>
+        <x:v>bmw-x4-oil-leak-2015</x:v>
       </x:c>
       <x:c r="C211" s="9" t="str">
-        <x:v>2004-2023 | BMW | X3</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D211" s="9" t="str">
-        <x:v>Coolant Expansion Tank Cracking</x:v>
+        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - All Models</x:v>
       </x:c>
       <x:c r="E211" s="9" t="str">
-        <x:v>Replace expansion tank and coolant ($50-100 DIY parts, $200-400 independent shop, $400-580 dealer). Very simple DIY repair taking 30 minutes - drain coolant, unbolt old tank, install new tank, refill with BMW-spec coolant (blue or pink/orange premix). Use Behr or OEM BMW expansion tank - Dorman aftermarket tanks may fail prematurely. YouTube and Pelicanparts have detailed DIY guides. PREVENTIVE: Replace every 5-7 years or 80-100k miles before cracks develop. Check tank regularly for hairline cracks. Don't ignore coolant leaks - can lead to catastrophic overheating and head gasket failure.</x:v>
+        <x:v>Replace valve cover gasket and/or oil filter housing gasket. Valve cover replacement is 3-4 hours labor on X4. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on BMW turbo engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
       </x:c>
       <x:c r="F211" s="9" t="n">
         <x:v>0</x:v>
@@ -9478,44 +10976,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="212" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="212" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A212" s="40" t="n">
         <x:v>211</x:v>
       </x:c>
       <x:c r="B212" s="9" t="str">
-        <x:v>bmw-x3-electric-water-pump-2011</x:v>
+        <x:v>bmw-x4-rear-differential-mount-2015</x:v>
       </x:c>
       <x:c r="C212" s="9" t="str">
-        <x:v>2011-2026 | BMW | X3</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D212" s="9" t="str">
-        <x:v>Electric Water Pump Failure</x:v>
+        <x:v>Rear Differential Mount Bushing Failure</x:v>
       </x:c>
       <x:c r="E212" s="9" t="str">
-        <x:v>Replace the electric water pump and thermostat together, as they are part of the same cooling circuit and the thermostat often fails concurrently. Bleed the cooling system thoroughly after replacement. Some owners carry a spare pump due to the sudden failure nature.</x:v>
+        <x:v>Replace rear differential mount bushings. Both front and rear differential bushings should be inspected and replaced as a set. Upgraded aftermarket bushings with stiffer rubber or polyurethane are available for longer service life.</x:v>
       </x:c>
       <x:c r="F212" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G212" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="213" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="213" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A213" s="40" t="n">
         <x:v>212</x:v>
       </x:c>
       <x:c r="B213" s="9" t="str">
-        <x:v>bmw-x3-m-electric-wastegate-actuator-adaptation-fault-boost-cutout-ea</x:v>
+        <x:v>bmw-x4-transfer-case-2015</x:v>
       </x:c>
       <x:c r="C213" s="9" t="str">
-        <x:v>2020-2020 | BMW | X3 M | S58</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D213" s="9" t="str">
-        <x:v>2020 X3 M Wastegate Adaptation Faults Require Software Diagnosis</x:v>
+        <x:v>Transfer Case Actuator Motor Failure - All xDrive X4</x:v>
       </x:c>
       <x:c r="E213" s="9" t="str">
-        <x:v>Confirm the production date, fault codes and current vehicle integration level. If the I-level is below S15A-20-03-510, a BMW-qualified repairer follows the bulletin and programs the vehicle with the specified or newer approved ISTA level. Diagnose unrelated mechanical noise separately; do not replace an actuator or turbocharger from this card.</x:v>
+        <x:v>Diagnose specific failure. Transfer case actuator motor replacement ($800-1,200) is most common. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors. Common wear item on high-mileage xDrive BMW models.</x:v>
       </x:c>
       <x:c r="F213" s="9" t="n">
         <x:v>0</x:v>
@@ -9524,21 +11022,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="214" ht="462" hidden="0" customHeight="1">
+    <x:row r="214" ht="1240.800048828125" hidden="0" customHeight="1">
       <x:c r="A214" s="40" t="n">
         <x:v>213</x:v>
       </x:c>
       <x:c r="B214" s="9" t="str">
-        <x:v>bmw-x3-m-fuel-tank-inlet-check-valve-weld-failure-2021-x3-m</x:v>
+        <x:v>bmw-x4m-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C214" s="9" t="str">
-        <x:v>2021-2021 | BMW | X3 M</x:v>
+        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
       </x:c>
       <x:c r="D214" s="9" t="str">
-        <x:v>2021 X3 M Fuel-Tank Safety Recall 21V-199</x:v>
+        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E214" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-199 campaign. If open, an authorized BMW dealer replaces the fuel tank free of charge. If fuel odor or leakage appears, move safely away from traffic, stop, have occupants exit and contact BMW roadside assistance; do not continue driving or order a tank from this card.</x:v>
+        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
       </x:c>
       <x:c r="F214" s="9" t="n">
         <x:v>0</x:v>
@@ -9547,21 +11045,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="215" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="215" ht="1188" hidden="0" customHeight="1">
       <x:c r="A215" s="40" t="n">
         <x:v>214</x:v>
       </x:c>
       <x:c r="B215" s="9" t="str">
-        <x:v>bmw-x3-m-idrive-control-display-blank-screen-infotainment-glitches-f9</x:v>
+        <x:v>bmw-x4m-cooling-track-use-2020</x:v>
       </x:c>
       <x:c r="C215" s="9" t="str">
-        <x:v>2020-2021 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2023 | BMW | X4 M</x:v>
       </x:c>
       <x:c r="D215" s="9" t="str">
-        <x:v>iDrive Control Display Blank Screen and Infotainment Glitches - F97 X3 M (2019-2021)</x:v>
+        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E215" s="9" t="str">
-        <x:v>First try the latest iDrive/head-unit software update at the dealer, which resolves many of the early glitches, reboots, and camera issues. If the display panel hardware has failed (lines, persistent blank screen with backlight off), the control display/screen assembly is replaced. A soft reset (press-and-hold volume/power) can temporarily clear a frozen screen.</x:v>
+        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
       </x:c>
       <x:c r="F215" s="9" t="n">
         <x:v>0</x:v>
@@ -9570,21 +11068,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="216" ht="462" hidden="0" customHeight="1">
+    <x:row r="216" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A216" s="40" t="n">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B216" s="9" t="str">
-        <x:v>bmw-x3-m-improperly-welded-front-seat-frame-2019-2021-x3-m</x:v>
+        <x:v>bmw-x4m-differential-bolt-2020</x:v>
       </x:c>
       <x:c r="C216" s="9" t="str">
-        <x:v>2021-2021 | BMW | X3 M</x:v>
+        <x:v>2020-2023 | BMW | X4 M</x:v>
       </x:c>
       <x:c r="D216" s="9" t="str">
-        <x:v>2021 X3 M Front Seat-Frame Safety Recall 23V-211</x:v>
+        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E216" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-211 campaign. If open, an authorized BMW dealer replaces the affected front seat frame and backrest free of charge using VIN-selected parts. Contact BMW promptly if a front seat vibrates or makes abnormal noise; do not order seat components from this card.</x:v>
+        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
       </x:c>
       <x:c r="F216" s="9" t="n">
         <x:v>0</x:v>
@@ -9593,21 +11091,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="217" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="217" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A217" s="40" t="n">
         <x:v>216</x:v>
       </x:c>
       <x:c r="B217" s="9" t="str">
-        <x:v>bmw-x3-m-low-mounted-engine-oil-cooler-vulnerable-to-road-debris-punc</x:v>
+        <x:v>bmw-x4m-s58-bearing-recall-2020</x:v>
       </x:c>
       <x:c r="C217" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2021 | BMW | X4 M | M40i, xDrive35i | S58</x:v>
       </x:c>
       <x:c r="D217" s="9" t="str">
-        <x:v>Low-Mounted Engine Oil Cooler Vulnerable to Road-Debris Puncture - F97 X3 M (S58)</x:v>
+        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E217" s="9" t="str">
-        <x:v>Inspect the oil cooler periodically for stone damage and weeping; fit a protective mesh/guard in front of the cooler as preventive insurance (popular among track and spirited-use owners). If punctured, stop driving immediately and replace the oil cooler and refill with the correct oil; verify no bearing damage occurred from any oil starvation.</x:v>
+        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
       </x:c>
       <x:c r="F217" s="9" t="n">
         <x:v>0</x:v>
@@ -9616,21 +11114,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="218" ht="594" hidden="0" customHeight="1">
+    <x:row r="218" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A218" s="40" t="n">
         <x:v>217</x:v>
       </x:c>
       <x:c r="B218" s="9" t="str">
-        <x:v>bmw-x3-m-oem-plastic-charge-pipe-cracking-blow-off-under-boost-f97-x3</x:v>
+        <x:v>bmw-x4m-transfer-case-2020</x:v>
       </x:c>
       <x:c r="C218" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
       </x:c>
       <x:c r="D218" s="9" t="str">
-        <x:v>OEM Plastic Charge Pipe Cracking / Blow-Off Under Boost - F97 X3 M (S58)</x:v>
+        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E218" s="9" t="str">
-        <x:v>Replace the OEM plastic charge pipe with an aluminum (or reinforced) aftermarket charge pipe from suppliers such as FTP, Racing Dynamics, or Kies; this is the standard durable fix and is strongly recommended before or alongside any tune. A failed OEM pipe can be re-fitted with a new OEM unit but the same failure mode tends to recur, especially on modified cars.</x:v>
+        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
       </x:c>
       <x:c r="F218" s="9" t="n">
         <x:v>0</x:v>
@@ -9639,21 +11137,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="219" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="219" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A219" s="40" t="n">
         <x:v>218</x:v>
       </x:c>
       <x:c r="B219" s="9" t="str">
-        <x:v>bmw-x3-n20-timing-chain-2011</x:v>
+        <x:v>bmw-x5-air-suspension-2007</x:v>
       </x:c>
       <x:c r="C219" s="9" t="str">
-        <x:v>2011-2017 | BMW | X3 | N20</x:v>
+        <x:v>2019-2026 | BMW | X5</x:v>
       </x:c>
       <x:c r="D219" s="9" t="str">
-        <x:v>N20 Timing Chain Guide Failure</x:v>
+        <x:v>G05 Suspension Warning: Check Faults and Campaigns Before Parts</x:v>
       </x:c>
       <x:c r="E219" s="9" t="str">
-        <x:v>Replace the complete timing chain kit including chain, guides, tensioner, and sprockets. Preventive replacement is strongly recommended at 80,000 miles before failure occurs. The updated guide design uses more durable materials.</x:v>
+        <x:v>Start with the VIN build/options, open-campaign status, exact warning, complete fault memory, and BMW ISTA test plan. If the VIN and production date match a BMW action, follow that bulletin: inspect the specified sensor-link holders, apply the specified software correction, or inspect the affected air line as directed. For other vehicles, test the particular system shown by the VIN and fault path before selecting any component. Do not buy a compressor, strut, spring, or conversion kit until the failed part and its VIN-specific number are established. This article intentionally has no retail link because no single part repairs all of these conditions.</x:v>
       </x:c>
       <x:c r="F219" s="9" t="n">
         <x:v>0</x:v>
@@ -9662,44 +11160,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="220" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="220" ht="1148.4000244140625" hidden="0" customHeight="1">
       <x:c r="A220" s="40" t="n">
         <x:v>219</x:v>
       </x:c>
       <x:c r="B220" s="9" t="str">
-        <x:v>bmw-x3-n20-timing-chain-2012</x:v>
+        <x:v>bmw-x5-air-suspension-compressor-2007</x:v>
       </x:c>
       <x:c r="C220" s="9" t="str">
-        <x:v>2013-2015 | BMW | X3 | N20</x:v>
+        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive35i, xDrive48i, xDrive50i, X5 M | N52, N62, M57, N55, N63, S63</x:v>
       </x:c>
       <x:c r="D220" s="9" t="str">
-        <x:v>Lower-Engine Whine Requires X3 N20 Timing-Chain Diagnosis</x:v>
+        <x:v>E70 Rear Air-Supply Unit: Diagnose the Self-Leveling System First</x:v>
       </x:c>
       <x:c r="E220" s="9" t="str">
-        <x:v>Confirm the exact X3 variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Read the EHC fault memory and run the applicable BMW ISTA test plan before ordering a compressor. Confirm the vehicle is equipped with rear self-leveling suspension, compare left/right ride height, check system power and wiring, inspect the height-sensor links, and leak-test the air springs, lines, and valve system. Test the air supply only after those checks isolate it. If BMW ETK/AIR selects the E70 air-supply system for the VIN and diagnosis confirms that assembly, replace it with current part 37-20-6-859-714, follow the BMW repair procedure, clear faults, and perform the required ride-height calibration. Do not install a generic compressor or a coil-conversion kit from symptoms alone.</x:v>
       </x:c>
       <x:c r="F220" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G220" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="221" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="221" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A221" s="40" t="n">
         <x:v>220</x:v>
       </x:c>
       <x:c r="B221" s="9" t="str">
-        <x:v>bmw-x3-oil-filter-housing-gasket-2007</x:v>
+        <x:v>bmw-x5-carbon-buildup-2007</x:v>
       </x:c>
       <x:c r="C221" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
+        <x:v>2011-2018 | BMW | X5 | xDrive35i, xDrive50i | N55, N63, N63TU1</x:v>
       </x:c>
       <x:c r="D221" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak (N52, N20 Engines)</x:v>
+        <x:v>Possible Intake-Valve Deposits on Direct-Injected Gasoline Engines</x:v>
       </x:c>
       <x:c r="E221" s="9" t="str">
-        <x:v>Replace oil filter housing gasket and oil cooler gasket ($40-80 DIY repair kit, $300-500 independent shop, $500-800 dealer). Requires draining some coolant and oil, removing housing, replacing gaskets, reassembling. Moderate DIY difficulty - Pelicanparts and YouTube have detailed model-specific guides. Use Victor Reinz or OEM BMW gasket kit for long-lasting seal - cheap gaskets leak within 20k miles. Address leak early before oil damages serpentine belt or alternator.</x:v>
+        <x:v>Diagnose the actual symptom before authorizing cleaning: read BMW-specific faults and misfire counters, check ignition and fueling, smoke-test the intake where indicated, verify crankcase ventilation operation, and inspect the intake valves with a borescope or by removing the intake manifold when the test plan supports it. If substantial deposits are confirmed and match the complaint, use an engine-specific professional mechanical-cleaning procedure that protects closed valves and removes all blasting media before reassembly. Do not present a universal catch can, chemical spray, fuel brand, short oil interval, or high-RPM driving as a proven repair. Any crankcase-ventilation modification also requires engine-specific fitment and emissions-law review.</x:v>
       </x:c>
       <x:c r="F221" s="9" t="n">
         <x:v>0</x:v>
@@ -9708,90 +11206,90 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="222" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="222" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A222" s="40" t="n">
         <x:v>221</x:v>
       </x:c>
       <x:c r="B222" s="9" t="str">
-        <x:v>bmw-x3-transfer-case-actuator-2004</x:v>
+        <x:v>bmw-x5-coolant-pipe-leak-2007</x:v>
       </x:c>
       <x:c r="C222" s="9" t="str">
-        <x:v>2004-2023 | BMW | X3</x:v>
+        <x:v>2007-2010 | BMW | X5 | 4.8i, xDrive48i | N62, N62TU</x:v>
       </x:c>
       <x:c r="D222" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure (xDrive AWD System)</x:v>
+        <x:v>E70 N62 Coolant Transfer Pipe Leak (Pressure-Test First)</x:v>
       </x:c>
       <x:c r="E222" s="9" t="str">
-        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket repair kit. DIY repair kits cost $100-150 and include replacement plastic gears, clips, and seals - straightforward installation saves $1,200+. Complete actuator motor replacement costs $540 for the assembly if DIY, or $1,500-2,200 at dealer. If transfer case itself is damaged from prolonged actuator failure, complete transfer case replacement costs $1,400-3,300. PREVENTIVE: If buying used X3 over 80k miles, budget for this repair - it's "when not if" on xDrive models. Check for clicking noise when shutting off ignition.</x:v>
+        <x:v>Pressure-test the cooling system cold and inspect the engine valley and all accessible connections to identify the exact leak before ordering parts. If inspection confirms the N62 transfer pipe and BMW ETK/AIR selects it for the VIN, replace pipe 11-14-1-439-975 with the required seals and one-time-use hardware from the VIN-specific repair diagram. Refill and bleed the cooling system with the specified coolant, repeat the pressure test, and verify stable temperature. Do not automatically replace an N63 pipe, thermostat, or unrelated hoses from this article.</x:v>
       </x:c>
       <x:c r="F222" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G222" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="223" ht="396" hidden="0" customHeight="1">
+    <x:row r="223" ht="1082.4000244140625" hidden="0" customHeight="1">
       <x:c r="A223" s="40" t="n">
         <x:v>222</x:v>
       </x:c>
       <x:c r="B223" s="9" t="str">
-        <x:v>bmw-x3-transfer-case-actuator-2011</x:v>
+        <x:v>bmw-x5-n63-timing-chain-2008</x:v>
       </x:c>
       <x:c r="C223" s="9" t="str">
-        <x:v>2011-2026 | BMW | X3</x:v>
+        <x:v>2010-2013 | BMW | X5 | xDrive50i | N63</x:v>
       </x:c>
       <x:c r="D223" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure</x:v>
+        <x:v>Early N63 Timing-Chain Wear Check: ISTA Test Before Repair</x:v>
       </x:c>
       <x:c r="E223" s="9" t="str">
-        <x:v>Replace the transfer case actuator motor. Change the transfer case fluid at the same time. The actuator can be replaced without removing the entire transfer case. Rebuilt units are available at lower cost but OEM is recommended for reliability.</x:v>
+        <x:v>Check the VIN and service history with a BMW center, diagnose stored VANOS/camshaft faults first, and run BMW's ISTA timing-chain elongation test. If the result is 'Timing chain is OK,' do not replace parts on this claim. If it is 'not OK,' BMW SIB 11 16 14 directs replacement of both timing chains under the VIN-specific repair instruction, followed by the required oil/filter service, priming steps, programming, and shorter oil-service interval. A single tensioner 11-31-7-557-741 or a generic Cloyes kit is not the complete repair and must not be presented as what the owner needs. Tow the vehicle rather than driving it when severe mechanical noise, oil-pressure warnings, or loss of timing is present.</x:v>
       </x:c>
       <x:c r="F223" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G223" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="224" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="224" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A224" s="40" t="n">
         <x:v>223</x:v>
       </x:c>
       <x:c r="B224" s="9" t="str">
-        <x:v>bmw-x3-valve-cover-gasket-2004</x:v>
+        <x:v>bmw-x5-n63-wastegate-2008</x:v>
       </x:c>
       <x:c r="C224" s="9" t="str">
-        <x:v>2004-2017 | BMW | X3 | 2.5i, 3.0i, 3.0si | M54, N52</x:v>
+        <x:v>2010-2018 | BMW | X5 | xDrive50i | N63, N63TU</x:v>
       </x:c>
       <x:c r="D224" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leaks (M54, N52 Engines)</x:v>
+        <x:v>N63/N63TU Low Boost or Turbo Rattle: Diagnose Vacuum Control First</x:v>
       </x:c>
       <x:c r="E224" s="9" t="str">
-        <x:v>Replace valve cover gasket and VANOS solenoid o-rings ($300-500 independent shop, $700-1,000 dealer, $80-150 DIY parts). On M54 engines, also replace ignition coil boots if contaminated by oil ($50 additional). Use OEM BMW gasket or Victor Reinz brand - aftermarket quality matters for long-term seal. Relatively straightforward DIY repair - saves $200-400 in labor. YouTube and Bimmerfest have detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage).</x:v>
+        <x:v>Read all DME faults and compare requested versus actual boost under the BMW test plan. Pressure- or smoke-test the intake and charge-air path, verify vacuum supply from the pump and reservoir, inspect both banks' hoses and pressure converters, and test actuator movement before condemning a turbocharger. Identify the engine generation, failed bank, and exact hardware in BMW ETK/AIR. Check a 2010-2013 E70 VIN for the N63 Customer Care Package only as applicable; its published six-point scope includes air-mass sensors, injectors, vacuum pump, low-pressure fuel sensor/feed line, fresh-air turbo seals, and crankcase-ventilation lines, not an automatic wastegate replacement. No retail link is published until diagnosis selects a VIN-specific component.</x:v>
       </x:c>
       <x:c r="F224" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G224" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="225" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="225" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A225" s="40" t="n">
         <x:v>224</x:v>
       </x:c>
       <x:c r="B225" s="9" t="str">
-        <x:v>bmw-x3-valve-cover-gasket-2011</x:v>
+        <x:v>bmw-x5-oil-leaks-2000</x:v>
       </x:c>
       <x:c r="C225" s="9" t="str">
-        <x:v>2011-2022 | BMW | X3 | N20, B48</x:v>
+        <x:v>2003-2006 | BMW | X5 | 3.0i | M54</x:v>
       </x:c>
       <x:c r="D225" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>E53 3.0i M54 Valve-Cover Gasket Leak (Confirm the Source)</x:v>
       </x:c>
       <x:c r="E225" s="9" t="str">
-        <x:v>Replace the valve cover gasket. Inspect the valve cover for warping or cracks — if damaged, replace the entire cover assembly. Clean all oil residue from surrounding components. Use a torque wrench to prevent over-tightening which causes cover warping.</x:v>
+        <x:v>Clean the engine and trace the highest fresh-oil source before ordering a gasket. If the leak is at the M54 cylinder-head-cover perimeter or spark-plug-well seals, inspect the plastic cover for cracks, warpage, damaged fastener grommets, and crankcase-ventilation faults. Reuse the cover only if it passes inspection, then install VIN/production-confirmed gasket set 11-12-0-030-496 with the BMW-specified grommets and sealant locations and torque sequence. If the cover or another oil circuit is the source, select that separate repair instead.</x:v>
       </x:c>
       <x:c r="F225" s="9" t="n">
         <x:v>1</x:v>
@@ -9800,113 +11298,113 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="226" ht="858" hidden="0" customHeight="1">
+    <x:row r="226" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A226" s="40" t="n">
         <x:v>225</x:v>
       </x:c>
       <x:c r="B226" s="9" t="str">
-        <x:v>bmw-x3-vanos-solenoid-2007</x:v>
+        <x:v>bmw-x5-transfer-case-actuator-2000</x:v>
       </x:c>
       <x:c r="C226" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | M40i, M50, xDrive35i | N52, N55</x:v>
+        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive48i, X5 M | N52, N62, M57, S63</x:v>
       </x:c>
       <x:c r="D226" s="9" t="str">
-        <x:v>VANOS Solenoid Failure (N52, N55 Engines)</x:v>
+        <x:v>E70 ATC700 Transfer-Case Positioning Motor (Diagnosis Required)</x:v>
       </x:c>
       <x:c r="E226" s="9" t="str">
-        <x:v>Replace VANOS solenoids and seals ($250-400 European shops, $729-882 US average). Use high-quality oil (5W-30 or 0W-40 BMW LL-01 spec) and change every 5,000-7,000 miles to prevent future failures - cheap oil or extended intervals kill VANOS solenoids. Some cases may require complete VANOS unit rebuild ($1,500-2,500). PREVENTIVE: Replace VANOS solenoids and seals every 50k miles as maintenance - much cheaper than waiting for failure. On F25 X3 with N52/N55, check TSB SI B12 14 10 for VANOS gear assembly bolt issue.</x:v>
+        <x:v>Read BMW VTG/DSC faults and run the applicable ISTA transfer-case test plan before buying a motor. Confirm tire sizes and wear, battery voltage, wiring, transfer-case type, fluid condition, calibration, and—especially after differential or transfer-case replacement—the VIN-correct front and rear gear ratios. If testing confirms the ATC700 positioning motor and BMW ETK/AIR selects this application for the VIN, current BMW exchange servomotor 27-10-2-449-709 supersedes 27-10-7-568-267. Install the correct classification resistor/hardware supplied or specified for the VIN and perform the required VTG initialization/calibration. A generic gear-only kit is not a universal BMW repair and should not be ordered without opening and confirming the exact motor failure.</x:v>
       </x:c>
       <x:c r="F226" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G226" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" ht="1016.4000244140625" hidden="0" customHeight="1">
+    <x:row r="227" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A227" s="40" t="n">
         <x:v>226</x:v>
       </x:c>
       <x:c r="B227" s="9" t="str">
-        <x:v>bmw-x3-wastegate-rattle-2011</x:v>
+        <x:v>bmw-x5-transfer-case-actuator-2007</x:v>
       </x:c>
       <x:c r="C227" s="9" t="str">
-        <x:v>2011-2023 | BMW | X3 | M40i, M50, sDrive30i, xDrive28i, xDrive30i, xDrive35i</x:v>
+        <x:v>2019-2026 | BMW | X5</x:v>
       </x:c>
       <x:c r="D227" s="9" t="str">
-        <x:v>Turbocharger Wastegate Rattle (N55, N20, B58 Engines)</x:v>
+        <x:v>G05/F95 Transfer-Case Shudder: Tires and Fluid Diagnosis First</x:v>
       </x:c>
       <x:c r="E227" s="9" t="str">
-        <x:v>Replace wastegate actuator ($400-800) or use aftermarket wastegate repair kit with upgraded stainless steel bushings ($150-300). Some cases require complete turbocharger replacement ($2,000-$4,000). VTT (Vargas Turbo Technologies) repair kits popular on forums - upgraded materials prevent future rattle. MONITORING: Early wastegate rattle may be harmless (annoying but no performance loss). If car boosts normally and no underboost codes, can monitor rattle without urgent repair. However, if check engine light appears with code 30FF or boost pressure drops, repair immediately to prevent turbo damage.</x:v>
+        <x:v>Follow BMW SIB 27 02 20 in order: verify all four tires for VIN-correct size, brand/application, axle placement, and wear; diagnose any powertrain faults; then use ISTA to temporarily deactivate the transfer-case clutch and road-test the complaint. Only if the shudder disappears with the VTG deactivated does BMW direct an ATX13-X oil change with DTF-1, followed by VTG calibration. The clutch plates can require up to 125 miles after the service to become fully saturated and smooth out. If the symptom remains, continue diagnosis rather than buying an actuator or transfer case. Part numbers for any further repair must be selected by VIN in ETK/AIR.</x:v>
       </x:c>
       <x:c r="F227" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G227" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="228" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="228" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A228" s="40" t="n">
         <x:v>227</x:v>
       </x:c>
       <x:c r="B228" s="9" t="str">
-        <x:v>bmw-x3-water-pump-2007</x:v>
+        <x:v>bmw-x5-vanos-solenoid-2000</x:v>
       </x:c>
       <x:c r="C228" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
+        <x:v>2010-2013 | BMW | X5 | xDrive30i, xDrive35i | N51, N52K, N52T, N55</x:v>
       </x:c>
       <x:c r="D228" s="9" t="str">
-        <x:v>Electric Water Pump Failure (N52, N20 Engines)</x:v>
+        <x:v>VANOS Adjustment-Unit Bolt Recall 23V-707 (E70 Inline-Six)</x:v>
       </x:c>
       <x:c r="E228" s="9" t="str">
-        <x:v>Replace electric water pump at first sign of failure ($800 parts + labor). Consider preventative replacement at 70-80k miles to avoid being stranded ($400 parts, DIY-able). CRITICAL: If you own 2013-2017 X3 28i, verify recall repair (protective shield installation) has been completed to prevent fire risk - check with BMW dealer using VIN. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps cylinder heads ($4,000+ repair). Call tow truck.</x:v>
+        <x:v>Enter the VIN in BMW's official recall lookup and have an authorized BMW center complete recall 23V-707 if it is open. BMW's procedure is inspection-dependent: intact affected bolts are replaced; if bolts are loose or broken, the affected VANOS adjustment unit is replaced, and missing fragments must be recovered. The recall repair is free, so do not buy a solenoid or VANOS part first. If the VIN is outside the recall or a fault remains after the remedy, use BMW-capable diagnostics to test oil supply and pressure, wiring, sensors, control solenoids, adjustment units, and mechanical timing before selecting a part. If the engine runs roughly, makes unusual mechanical noise, loses power, or stalls, move out of traffic safely, stop driving, and contact BMW for transport guidance.</x:v>
       </x:c>
       <x:c r="F228" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G228" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="229" ht="1240.800048828125" hidden="0" customHeight="1">
+    <x:row r="229" ht="1148.4000244140625" hidden="0" customHeight="1">
       <x:c r="A229" s="40" t="n">
         <x:v>228</x:v>
       </x:c>
       <x:c r="B229" s="9" t="str">
-        <x:v>bmw-x3m-brake-wear-2020</x:v>
+        <x:v>bmw-x5-water-pump-2007</x:v>
       </x:c>
       <x:c r="C229" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2011-2013 | BMW | X5 | xDrive35i | N55</x:v>
       </x:c>
       <x:c r="D229" s="9" t="str">
-        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F97 X3 M / F98 X4 M</x:v>
+        <x:v>E70 xDrive35i N55 Electric Coolant Pump (Fault-Confirmed)</x:v>
       </x:c>
       <x:c r="E229" s="9" t="str">
-        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
+        <x:v>If the engine-temperature warning appears, stop safely, shut the engine off, and tow the vehicle if normal temperature cannot be confirmed. When cool, check coolant level and leaks, read BMW-specific faults, verify pump power/ground and communication, and run the ISTA coolant-pump activation/test plan. If those tests confirm the pump and BMW ETK/AIR selects 11-51-5-A05-704 for the VIN, replace it using the BMW procedure, select the thermostat separately only if testing or preventive planning justifies it, vacuum-fill or bleed the system as specified, and verify commanded pump operation and stable temperature. Do not use a fixed-mileage rule or this part number for an N52, N63, or F15 without VIN confirmation.</x:v>
       </x:c>
       <x:c r="F229" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G229" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="230" ht="1188" hidden="0" customHeight="1">
+    <x:row r="230" ht="1056" hidden="0" customHeight="1">
       <x:c r="A230" s="40" t="n">
         <x:v>229</x:v>
       </x:c>
       <x:c r="B230" s="9" t="str">
-        <x:v>bmw-x3m-cooling-track-use-2020</x:v>
+        <x:v>bmw-x5m-brake-system-2010</x:v>
       </x:c>
       <x:c r="C230" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D230" s="9" t="str">
-        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F97 X3 M / F98 X4 M</x:v>
+        <x:v>Heavy-Duty Brake System Accelerated Wear - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E230" s="9" t="str">
-        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
+        <x:v>E70 X5 M brakes: OEM front pads 34116799964 ($150-$250), rear pads 34216794879 ($120-$200). F85 X5 M front brake rotors: 34112284101/34112284102 with 6-pot caliper 34117845747/34117845748 and pads 34112284869. F85 rear: 385mm x 24mm perforated rotors 34212284903/34212284904 with 4-pot Brembo caliper and Textar pads. Budget $1,500-$2,500 per axle for complete brake service. For track use: EBC Yellowstuff or Hawk HPS 5.0 pads ($200-$350 per axle) with StopTech slotted rotors for improved heat management. Use Motul RBF 660 or ATE Typ 200 brake fluid - flush every 12 months. Budget $3,000-$5,000 per year for brake maintenance if driving spiritedly.</x:v>
       </x:c>
       <x:c r="F230" s="9" t="n">
         <x:v>0</x:v>
@@ -9915,21 +11413,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="231" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="231" ht="1122" hidden="0" customHeight="1">
       <x:c r="A231" s="40" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="B231" s="9" t="str">
-        <x:v>bmw-x3m-differential-bolt-2020</x:v>
+        <x:v>bmw-x5m-rear-differential-2010</x:v>
       </x:c>
       <x:c r="C231" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M | S63</x:v>
       </x:c>
       <x:c r="D231" s="9" t="str">
-        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F97 X3 M / F98 X4 M</x:v>
+        <x:v>Rear Differential Wear &amp; Fluid Degradation - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E231" s="9" t="str">
-        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
+        <x:v>Change rear differential fluid every 30,000 miles (ignore BMW "lifetime fill" claim). E70 X5 M: No drain plug - fluid must be extracted through fill port with hand pump or suction device. Recommended fluid: Royal Purple 75W-140 GL5 synthetic or Red Line 75W-140 GL5 ($40-$60 per fill). Capacity approximately 1.2 liters. For limited-slip diff, ensure fluid is GL5 rated with limited-slip additive. If differential is making whining/howling noise: have a limited-slip differential specialist inspect internals (not generic BMW shop). Diff rebuild: $1,500-$3,000 at specialist. Complete differential replacement: $3,000-$5,500 + labor. Labor for fluid change: $150-$300 at independent shop.</x:v>
       </x:c>
       <x:c r="F231" s="9" t="n">
         <x:v>0</x:v>
@@ -9938,21 +11436,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="232" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="232" ht="1386" hidden="0" customHeight="1">
       <x:c r="A232" s="40" t="n">
         <x:v>231</x:v>
       </x:c>
       <x:c r="B232" s="9" t="str">
-        <x:v>bmw-x3m-s58-bearing-recall-2020</x:v>
+        <x:v>bmw-x5m-s63-cooling-system-2010</x:v>
       </x:c>
       <x:c r="C232" s="9" t="str">
-        <x:v>2020-2021 | BMW | X3 M</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D232" s="9" t="str">
-        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F97 X3 M / F98 X4 M</x:v>
+        <x:v>S63 Cooling System Component Failures - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E232" s="9" t="str">
-        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
+        <x:v>PROACTIVE MAINTENANCE SCHEDULE: Replace electric water pump at 60,000 miles ($400-$700 + labor). Replace thermostat at same time ($150-$250). Replace expansion tank at 60,000-80,000 miles ($100-$200). Inspect all coolant hoses at every oil change - replace any that are soft, bulging, or showing surface cracks. E70 X5 M expansion tank vent hose: 17128627119 ($30-$50). Flush coolant system every 2 years or 30,000 miles (more frequent than BMW's 4-year recommendation). Use ONLY BMW coolant mixed 50/50 with distilled water. For E70 hot-V turbo coolant lines: GRYPHONTEK repair kit eliminates plastic T-fitting failure (see separate issue entry). Budget $1,500-$2,500 for complete cooling system refresh at 60,000 miles. This prevents catastrophic overheating that can destroy the S63 engine ($15,000-$34,000 engine replacement).</x:v>
       </x:c>
       <x:c r="F232" s="9" t="n">
         <x:v>0</x:v>
@@ -9961,21 +11459,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="233" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="233" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A233" s="40" t="n">
         <x:v>232</x:v>
       </x:c>
       <x:c r="B233" s="9" t="str">
-        <x:v>bmw-x3m-transfer-case-2020</x:v>
+        <x:v>bmw-x5m-s63-oil-leaks-2010</x:v>
       </x:c>
       <x:c r="C233" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D233" s="9" t="str">
-        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F97 X3 M / F98 X4 M</x:v>
+        <x:v>S63 V8 Chronic Oil Leaks (Valve Cover, Oil Pan, Turbo Lines) - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E233" s="9" t="str">
-        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
+        <x:v>Valve cover gasket replacement (both sides): $1,200-$2,500 with labor. BMW plastic valve covers can crack and must be replaced entirely (not just gasket) - inspect during service. Oil filter housing gasket: $400-$800 with labor. Oil pan gasket: $2,000-$3,500 (requires engine/subframe drop). Turbo oil feed/return lines: replace with GRYPHONTEK or MAMBA upgraded silicone/braided lines during any turbo service ($200-$400). VANOS solenoid seals: $100-$200 (DIY-friendly). For comprehensive oil leak repair at 80,000+ miles: budget $3,000-$5,000 to address all common leak points simultaneously. Valve cover bolt torque is CRITICAL - too tight cracks the cover ($800-$1,200 per cover), too loose and it leaks.</x:v>
       </x:c>
       <x:c r="F233" s="9" t="n">
         <x:v>0</x:v>
@@ -9984,21 +11482,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="234" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="234" ht="1412.4000244140625" hidden="0" customHeight="1">
       <x:c r="A234" s="40" t="n">
         <x:v>233</x:v>
       </x:c>
       <x:c r="B234" s="9" t="str">
-        <x:v>bmw-x4-n20-timing-chain-2015</x:v>
+        <x:v>bmw-x5m-s63-rod-bearing-2010</x:v>
       </x:c>
       <x:c r="C234" s="9" t="str">
-        <x:v>2015-2016 | BMW | X4 | xDrive28i, xDrive30i</x:v>
+        <x:v>2010-2018 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i</x:v>
       </x:c>
       <x:c r="D234" s="9" t="str">
-        <x:v>N20 Timing Chain Premature Failure - F26 X4 xDrive28i</x:v>
+        <x:v>S63 V8 Rod Bearing Premature Wear &amp; Failure - E70/F85 X5 M</x:v>
       </x:c>
       <x:c r="E234" s="9" t="str">
-        <x:v>Complete timing chain kit replacement including chain, guides, tensioner, and sprockets. Must be performed by experienced BMW technician. Preventive replacement recommended at 60,000-80,000 miles. BMW extended warranty to 8 years/100,000 miles under class action settlement. Upgraded reinforced chain kit available from aftermarket. Labor is 10-14 hours for X4 due to AWD and tight engine bay.</x:v>
+        <x:v>PREVENTIVE: For track-driven X5 M, replace rod bearings proactively at 60,000-80,000 miles. ACL Race Series rod bearings (8B1578HX-STD for S63B44, +0.001" extra oil clearance) are the community gold standard ($200-$350 for bearing set). WPC surface-treated bearings from Lang Racing are the premium choice ($400-$600 set). Total cost for preventive rod bearing service: $4,500-$8,500 depending on shop. Oil analysis every 5,000 miles through Blackstone Labs ($30/test) to monitor bearing wear metals (lead and copper). Use only BMW 10W-60 synthetic oil with 5,000-7,500 mile oil change intervals. Never track the car on cold oil. Mporium BMW offers specialized S63 rod bearing service starting at $4,499. If catastrophic failure: rebuilt S63 engine from RK Autowerks (~$8,500 + installation), new BMW engine (~$34,000), or complete engine rebuild ($12,000-$18,000).</x:v>
       </x:c>
       <x:c r="F234" s="9" t="n">
         <x:v>0</x:v>
@@ -10007,21 +11505,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="235" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A235" s="40" t="n">
         <x:v>234</x:v>
       </x:c>
       <x:c r="B235" s="9" t="str">
-        <x:v>bmw-x4-n20-timing-chain-guide-2015</x:v>
+        <x:v>bmw-x5m-s63-turbo-coolant-line-2010</x:v>
       </x:c>
       <x:c r="C235" s="9" t="str">
-        <x:v>2015-2015 | BMW | X4 | N20</x:v>
+        <x:v>2010-2013 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D235" s="9" t="str">
-        <x:v>2015 X4 N20 Lower-Engine Whine Requires Timing-Chain Diagnosis</x:v>
+        <x:v>S63 Turbo Coolant Line Plastic T-Fitting Failure (Hot-V Design) - E70 X5 M</x:v>
       </x:c>
       <x:c r="E235" s="9" t="str">
-        <x:v>Confirm the exact xDrive28i variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Replace ALL factory plastic turbo coolant T-fittings and hoses with GRYPHONTEK S63 Turbo Coolant Line Repair Kit ($200-$400). Kit includes pre-shaped multi-layer reinforced silicone hoses, brass T-fittings (replacing factory plastic), and all necessary hose clamps. Direct bolt-on installation designed for the E70/E71 S63 engine bay. MAMBA Turbo also offers a reinforced turbo coolant line kit with brass and silicone components ($150-$350). This is a PROACTIVE replacement - do not wait for failure. Replace at first sign of coolant weeping or during any turbo service. Labor: $800-$1,500 due to tight access in hot-V engine valley. If turbo bearings are damaged from overheating: turbo replacement $3,000-$5,000 per unit.</x:v>
       </x:c>
       <x:c r="F235" s="9" t="n">
         <x:v>0</x:v>
@@ -10030,21 +11528,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="236" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="236" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A236" s="40" t="n">
         <x:v>235</x:v>
       </x:c>
       <x:c r="B236" s="9" t="str">
-        <x:v>bmw-x4-oil-leak-2015</x:v>
+        <x:v>bmw-x5m-s63-vanos-solenoid-2010</x:v>
       </x:c>
       <x:c r="C236" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D236" s="9" t="str">
-        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - All Models</x:v>
+        <x:v>S63 VANOS Solenoid Failure - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E236" s="9" t="str">
-        <x:v>Replace valve cover gasket and/or oil filter housing gasket. Valve cover replacement is 3-4 hours labor on X4. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on BMW turbo engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
+        <x:v>Replace all 4 VANOS solenoids simultaneously - they are same age and if one has failed, others are close behind. Pierburg 11368605123 (OEM supplier) at $30-$50 each from Turner Motorsport or BimmerWorld. Genuine BMW 11368482268 for S63TU applications at $50-$70 each. Total parts cost: $120-$280 for all 4 solenoids. Also replace VANOS solenoid O-rings and filter screens during service. Labor: 1-2 hours professional ($150-$400 labor). This is one of the easier S63 repairs - accessible from top of engine without removing intake manifold. Natafox and Febi also offer quality aftermarket VANOS solenoids at lower cost ($20-$35 each). Clean VANOS system with fresh oil change immediately after solenoid replacement.</x:v>
       </x:c>
       <x:c r="F236" s="9" t="n">
         <x:v>0</x:v>
@@ -10053,21 +11551,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="237" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="237" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A237" s="40" t="n">
         <x:v>236</x:v>
       </x:c>
       <x:c r="B237" s="9" t="str">
-        <x:v>bmw-x4-rear-differential-mount-2015</x:v>
+        <x:v>bmw-x5m-s63-wastegate-rattle-2010</x:v>
       </x:c>
       <x:c r="C237" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2010-2018 | BMW | X5 M | S63</x:v>
       </x:c>
       <x:c r="D237" s="9" t="str">
-        <x:v>Rear Differential Mount Bushing Failure</x:v>
+        <x:v>S63 Twin Turbo Wastegate Rattle - E70/F85 X5 M</x:v>
       </x:c>
       <x:c r="E237" s="9" t="str">
-        <x:v>Replace rear differential mount bushings. Both front and rear differential bushings should be inspected and replaced as a set. Upgraded aftermarket bushings with stiffer rubber or polyurethane are available for longer service life.</x:v>
+        <x:v>Option 1 (Most cost-effective): MAMBA SUS316 stainless steel wastegate rattle flapper repair kit for S63 MGT2260 (part 077-0024, replaces 790463-2 / 790484-3), approximately $150-$300 per turbo. Requires turbo removal for installation. Option 2: Lskioer turbo wastegate rattle flapper repair kit for S63/S63TU MGT2260DSL ($80-$150 per kit on Amazon). Option 3: Replace turbo wastegate actuators with new OEM units ($300-$500 each). Option 4: Full turbocharger replacement with new or remanufactured units ($3,000-$5,000 per turbo + labor). Labor for turbo removal and reinstallation: $2,000-$3,500 for both turbos. While turbos are out: replace turbo oil feed/return lines, coolant lines, and all gaskets (GRYPHONTEK turbo coolant line repair kit for E70 X5M, ~$200-$400).</x:v>
       </x:c>
       <x:c r="F237" s="9" t="n">
         <x:v>0</x:v>
@@ -10076,21 +11574,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="238" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="238" ht="1069.199951171875" hidden="0" customHeight="1">
       <x:c r="A238" s="40" t="n">
         <x:v>237</x:v>
       </x:c>
       <x:c r="B238" s="9" t="str">
-        <x:v>bmw-x4-transfer-case-2015</x:v>
+        <x:v>bmw-x5m-transfer-case-actuator-2010</x:v>
       </x:c>
       <x:c r="C238" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2010-2023 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D238" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure - All xDrive X4</x:v>
+        <x:v>xDrive Transfer Case Actuator Motor Failure - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E238" s="9" t="str">
-        <x:v>Diagnose specific failure. Transfer case actuator motor replacement ($800-1,200) is most common. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors. Common wear item on high-mileage xDrive BMW models.</x:v>
+        <x:v>Replace transfer case actuator motor. E70 X5 M: BMW 27107566296 or equivalent ($250-$450 for actuator motor). F85 X5 M: BMW 27608643153 or equivalent ($300-$500). F95 X5 M: check VIN-specific part number with dealer. FCP Euro has an excellent DIY guide for BMW transfer case actuator repair - the actuator can be replaced without removing the entire transfer case. Labor: 2-3 hours at specialist shop ($300-$600 labor). Change transfer case fluid at same time with BMW DTF-1 specification fluid. XeMODeX offers remanufactured transfer case actuator motors at reduced cost ($200-$350). For complete transfer case failure: $3,500-$6,000 for replacement unit + labor.</x:v>
       </x:c>
       <x:c r="F238" s="9" t="n">
         <x:v>0</x:v>
@@ -10099,21 +11597,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" ht="1240.800048828125" hidden="0" customHeight="1">
+    <x:row r="239" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A239" s="40" t="n">
         <x:v>238</x:v>
       </x:c>
       <x:c r="B239" s="9" t="str">
-        <x:v>bmw-x4m-brake-wear-2020</x:v>
+        <x:v>bmw-x6-adaptive-drive-malfunction-2008</x:v>
       </x:c>
       <x:c r="C239" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
+        <x:v>2008-2019 | BMW | X6</x:v>
       </x:c>
       <x:c r="D239" s="9" t="str">
-        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F98 X4 M / F98 X4 M</x:v>
+        <x:v>Adaptive Drive System Malfunction</x:v>
       </x:c>
       <x:c r="E239" s="9" t="str">
-        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
+        <x:v>Diagnose specific Adaptive Drive component failure using BMW ISTA diagnostics. Replace the failed component — most commonly the hydraulic pump or valve block. If repair cost is prohibitive, some owners convert to conventional anti-roll bars as a permanent fix at lower cost.</x:v>
       </x:c>
       <x:c r="F239" s="9" t="n">
         <x:v>0</x:v>
@@ -10122,21 +11620,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="1188" hidden="0" customHeight="1">
+    <x:row r="240" ht="858" hidden="0" customHeight="1">
       <x:c r="A240" s="40" t="n">
         <x:v>239</x:v>
       </x:c>
       <x:c r="B240" s="9" t="str">
-        <x:v>bmw-x4m-cooling-track-use-2020</x:v>
+        <x:v>bmw-x6-air-suspension-2008</x:v>
       </x:c>
       <x:c r="C240" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M</x:v>
+        <x:v>2008-2023 | BMW | X6</x:v>
       </x:c>
       <x:c r="D240" s="9" t="str">
-        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F98 X4 M / F98 X4 M</x:v>
+        <x:v>Air Suspension Compressor &amp; Strut Failure</x:v>
       </x:c>
       <x:c r="E240" s="9" t="str">
-        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
+        <x:v>Replace failed air springs or compressor. Arnott rear air spring A-2642 ($200-300 each). OEM F16 spring 37126795013 ($200). Arnott compressor P-2655 ($599). Or convert to coil springs: Strutmasters BB2RBM conversion kit ($1,200-1,800) permanently eliminates air suspension issues. Conversion is cheaper long-term than continued air suspension repairs. If keeping air suspension: inspect air springs at 60,000-80,000 miles for cracks/leaks before compressor damage occurs. Replace both air springs on same axle simultaneously.</x:v>
       </x:c>
       <x:c r="F240" s="9" t="n">
         <x:v>0</x:v>
@@ -10145,21 +11643,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="241" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="241" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A241" s="40" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="B241" s="9" t="str">
-        <x:v>bmw-x4m-differential-bolt-2020</x:v>
+        <x:v>bmw-x6-ibs-brake-recall-2023</x:v>
       </x:c>
       <x:c r="C241" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M</x:v>
+        <x:v>2024-2024 | BMW | X6</x:v>
       </x:c>
       <x:c r="D241" s="9" t="str">
-        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F98 X4 M / F98 X4 M</x:v>
+        <x:v>2024 X6 Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E241" s="9" t="str">
-        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
       </x:c>
       <x:c r="F241" s="9" t="n">
         <x:v>0</x:v>
@@ -10168,21 +11666,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="242" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="242" ht="924" hidden="0" customHeight="1">
       <x:c r="A242" s="40" t="n">
         <x:v>241</x:v>
       </x:c>
       <x:c r="B242" s="9" t="str">
-        <x:v>bmw-x4m-s58-bearing-recall-2020</x:v>
+        <x:v>bmw-x6-n63-timing-chain-2008</x:v>
       </x:c>
       <x:c r="C242" s="9" t="str">
-        <x:v>2020-2021 | BMW | X4 M | M40i, xDrive35i | S58</x:v>
+        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
       </x:c>
       <x:c r="D242" s="9" t="str">
-        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F98 X4 M / F98 X4 M</x:v>
+        <x:v>N63 Timing Chain Stretch &amp; Guide Failure (E71/F16 xDrive50i)</x:v>
       </x:c>
       <x:c r="E242" s="9" t="str">
-        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: If you own 2008-2014 E71 xDrive50i with N63, replace timing chain guides and tensioners IMMEDIATELY at 60,000-80,000 miles ($4,000-6,000) BEFORE failure. IWIS timing chain kit 90001521 ($800-1,200) or Turner kit 11317594899KT recommended. Replace lower chain guide 11147574373 at same time. If chain has already failed: complete engine replacement required ($15,000-25,000). Check VIN with BMW dealer for extended warranty eligibility. 2015+ N63TU engines have improved timing components but still require monitoring.</x:v>
       </x:c>
       <x:c r="F242" s="9" t="n">
         <x:v>0</x:v>
@@ -10191,21 +11689,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="243" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="243" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A243" s="40" t="n">
         <x:v>242</x:v>
       </x:c>
       <x:c r="B243" s="9" t="str">
-        <x:v>bmw-x4m-transfer-case-2020</x:v>
+        <x:v>bmw-x6-n63-valve-stem-seal-wear-2008</x:v>
       </x:c>
       <x:c r="C243" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
+        <x:v>2008-2019 | BMW | X6 | N63</x:v>
       </x:c>
       <x:c r="D243" s="9" t="str">
-        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F98 X4 M / F98 X4 M</x:v>
+        <x:v>N63 Valve Stem Seal Degradation and Oil Burning</x:v>
       </x:c>
       <x:c r="E243" s="9" t="str">
-        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
+        <x:v>Replace all intake and exhaust valve stem seals. This is a major job requiring head work. Also replace turbo oil return lines and update engine software per BMW N63 Customer Care Package specifications. Ensure proper oil grade (BMW LL-01) is used.</x:v>
       </x:c>
       <x:c r="F243" s="9" t="n">
         <x:v>0</x:v>
@@ -10214,21 +11712,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="244" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="244" ht="858" hidden="0" customHeight="1">
       <x:c r="A244" s="40" t="n">
         <x:v>243</x:v>
       </x:c>
       <x:c r="B244" s="9" t="str">
-        <x:v>bmw-x5-air-suspension-2007</x:v>
+        <x:v>bmw-x6-n63-valve-stem-seals-2008</x:v>
       </x:c>
       <x:c r="C244" s="9" t="str">
-        <x:v>2019-2026 | BMW | X5</x:v>
+        <x:v>2008-2023 | BMW | X6 | M50i, xDrive50i | N63</x:v>
       </x:c>
       <x:c r="D244" s="9" t="str">
-        <x:v>G05 Suspension Warning: Check Faults and Campaigns Before Parts</x:v>
+        <x:v>N63 Valve Stem Seal / Oil Consumption (xDrive50i)</x:v>
       </x:c>
       <x:c r="E244" s="9" t="str">
-        <x:v>Start with the VIN build/options, open-campaign status, exact warning, complete fault memory, and BMW ISTA test plan. If the VIN and production date match a BMW action, follow that bulletin: inspect the specified sensor-link holders, apply the specified software correction, or inspect the affected air line as directed. For other vehicles, test the particular system shown by the VIN and fault path before selecting any component. Do not buy a compressor, strut, spring, or conversion kit until the failed part and its VIN-specific number are established. This article intentionally has no retail link because no single part repairs all of these conditions.</x:v>
+        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 ($80-120/set of 16, need 2 sets for V8). 5150 AutoSport Viton upgraded seals ($150-200) are recommended for better heat resistance in hot-vee configuration. AGA Tools kit AGA-N63-VSK-K ($500-800) includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Some owners monitor oil levels and add as needed rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil.</x:v>
       </x:c>
       <x:c r="F244" s="9" t="n">
         <x:v>0</x:v>
@@ -10237,44 +11735,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="245" ht="1148.4000244140625" hidden="0" customHeight="1">
+    <x:row r="245" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A245" s="40" t="n">
         <x:v>244</x:v>
       </x:c>
       <x:c r="B245" s="9" t="str">
-        <x:v>bmw-x5-air-suspension-compressor-2007</x:v>
+        <x:v>bmw-x6-n63-wastegate-2008</x:v>
       </x:c>
       <x:c r="C245" s="9" t="str">
-        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive35i, xDrive48i, xDrive50i, X5 M | N52, N62, M57, N55, N63, S63</x:v>
+        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
       </x:c>
       <x:c r="D245" s="9" t="str">
-        <x:v>E70 Rear Air-Supply Unit: Diagnose the Self-Leveling System First</x:v>
+        <x:v>N63 Turbo Wastegate Rattle (xDrive50i)</x:v>
       </x:c>
       <x:c r="E245" s="9" t="str">
-        <x:v>Read the EHC fault memory and run the applicable BMW ISTA test plan before ordering a compressor. Confirm the vehicle is equipped with rear self-leveling suspension, compare left/right ride height, check system power and wiring, inspect the height-sensor links, and leak-test the air springs, lines, and valve system. Test the air supply only after those checks isolate it. If BMW ETK/AIR selects the E70 air-supply system for the VIN and diagnosis confirms that assembly, replace it with current part 37-20-6-859-714, follow the BMW repair procedure, clear faults, and perform the required ride-height calibration. Do not install a generic compressor or a coil-conversion kit from symptoms alone.</x:v>
+        <x:v>Repair options range from flapper repair kits ($50-100/turbo) to complete turbocharger replacement ($4,000-8,000 for both). Garrett MGT2256S flapper repair kit ($50-100 per turbo) is cheapest fix. MAMBA adjustable actuator kit ($150-300) provides more durable solution. OEM actuators 11657646093 available from BMW. Complete turbo replacement $2,000-4,000 per turbo. MONITORING: Wastegate rattle is early warning - address before complete turbo failure to avoid $8,000+ repair.</x:v>
       </x:c>
       <x:c r="F245" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G245" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="246" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="246" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A246" s="40" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="B246" s="9" t="str">
-        <x:v>bmw-x5-carbon-buildup-2007</x:v>
+        <x:v>bmw-x6-rear-differential-bushing-2008</x:v>
       </x:c>
       <x:c r="C246" s="9" t="str">
-        <x:v>2011-2018 | BMW | X5 | xDrive35i, xDrive50i | N55, N63, N63TU1</x:v>
+        <x:v>2008-2026 | BMW | X6</x:v>
       </x:c>
       <x:c r="D246" s="9" t="str">
-        <x:v>Possible Intake-Valve Deposits on Direct-Injected Gasoline Engines</x:v>
+        <x:v>Rear Differential Bushing Deterioration</x:v>
       </x:c>
       <x:c r="E246" s="9" t="str">
-        <x:v>Diagnose the actual symptom before authorizing cleaning: read BMW-specific faults and misfire counters, check ignition and fueling, smoke-test the intake where indicated, verify crankcase ventilation operation, and inspect the intake valves with a borescope or by removing the intake manifold when the test plan supports it. If substantial deposits are confirmed and match the complaint, use an engine-specific professional mechanical-cleaning procedure that protects closed valves and removes all blasting media before reassembly. Do not present a universal catch can, chemical spray, fuel brand, short oil interval, or high-RPM driving as a proven repair. Any crankcase-ventilation modification also requires engine-specific fitment and emissions-law review.</x:v>
+        <x:v>Replace all rear differential mount bushings. Use OEM or equivalent quality bushings (Lemforder is the OEM supplier). Inspect the differential housing for any damage from excessive movement. Perform subframe alignment check after bushing replacement.</x:v>
       </x:c>
       <x:c r="F246" s="9" t="n">
         <x:v>0</x:v>
@@ -10283,67 +11781,67 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="247" ht="884.4000244140625" hidden="0" customHeight="1">
+    <x:row r="247" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A247" s="40" t="n">
         <x:v>246</x:v>
       </x:c>
       <x:c r="B247" s="9" t="str">
-        <x:v>bmw-x5-coolant-pipe-leak-2007</x:v>
+        <x:v>bmw-x6-transfer-case-2008</x:v>
       </x:c>
       <x:c r="C247" s="9" t="str">
-        <x:v>2007-2010 | BMW | X5 | 4.8i, xDrive48i | N62, N62TU</x:v>
+        <x:v>2008-2023 | BMW | X6</x:v>
       </x:c>
       <x:c r="D247" s="9" t="str">
-        <x:v>E70 N62 Coolant Transfer Pipe Leak (Pressure-Test First)</x:v>
+        <x:v>Transfer Case Actuator Motor Failure (All xDrive Models)</x:v>
       </x:c>
       <x:c r="E247" s="9" t="str">
-        <x:v>Pressure-test the cooling system cold and inspect the engine valley and all accessible connections to identify the exact leak before ordering parts. If inspection confirms the N62 transfer pipe and BMW ETK/AIR selects it for the VIN, replace pipe 11-14-1-439-975 with the required seals and one-time-use hardware from the VIN-specific repair diagram. Refill and bleed the cooling system with the specified coolant, repeat the pressure test, and verify stable temperature. Do not automatically replace an N63 pipe, thermostat, or unrelated hoses from this article.</x:v>
+        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket gear repair kit ($100-150). G06 actuator motor 27609469023 ($400-600) for complete replacement. DIY gear repair kits are straightforward and save $1,200+ over dealer replacement. Complete transfer case replacement if internal damage occurred: $1,400-3,300. PREVENTIVE: If buying used X6 over 80k miles, budget for this repair and listen for clicking noise when shutting off ignition.</x:v>
       </x:c>
       <x:c r="F247" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G247" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="248" ht="1082.4000244140625" hidden="0" customHeight="1">
+    <x:row r="248" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A248" s="40" t="n">
         <x:v>247</x:v>
       </x:c>
       <x:c r="B248" s="9" t="str">
-        <x:v>bmw-x5-n63-timing-chain-2008</x:v>
+        <x:v>bmw-x6m-front-thrust-arm-bushing-2015</x:v>
       </x:c>
       <x:c r="C248" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 | xDrive50i | N63</x:v>
+        <x:v>2015-2025 | BMW | X6 M</x:v>
       </x:c>
       <x:c r="D248" s="9" t="str">
-        <x:v>Early N63 Timing-Chain Wear Check: ISTA Test Before Repair</x:v>
+        <x:v>Front Thrust Arm Bushing (Tension Strut) Premature Wear</x:v>
       </x:c>
       <x:c r="E248" s="9" t="str">
-        <x:v>Check the VIN and service history with a BMW center, diagnose stored VANOS/camshaft faults first, and run BMW's ISTA timing-chain elongation test. If the result is 'Timing chain is OK,' do not replace parts on this claim. If it is 'not OK,' BMW SIB 11 16 14 directs replacement of both timing chains under the VIN-specific repair instruction, followed by the required oil/filter service, priming steps, programming, and shorter oil-service interval. A single tensioner 11-31-7-557-741 or a generic Cloyes kit is not the complete repair and must not be presented as what the owner needs. Tow the vehicle rather than driving it when severe mechanical noise, oil-pressure warnings, or loss of timing is present.</x:v>
+        <x:v>Replace both front thrust arms as complete assemblies (the bushings are not serviceable separately). Use genuine BMW M-spec parts or Lemforder equivalents. Perform a 4-wheel alignment immediately after replacement. Upgrade to Powerflex polyurethane thrust arm bushings for extended lifespan, especially on tracked cars.</x:v>
       </x:c>
       <x:c r="F248" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G248" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="249" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="249" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A249" s="40" t="n">
         <x:v>248</x:v>
       </x:c>
       <x:c r="B249" s="9" t="str">
-        <x:v>bmw-x5-n63-wastegate-2008</x:v>
+        <x:v>bmw-x6m-s63-rod-bearing-2010</x:v>
       </x:c>
       <x:c r="C249" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 | xDrive50i | N63, N63TU</x:v>
+        <x:v>2010-2023 | BMW | X6 M | M50i, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D249" s="9" t="str">
-        <x:v>N63/N63TU Low Boost or Turbo Rattle: Diagnose Vacuum Control First</x:v>
+        <x:v>S63 Rod Bearing Failure (X6 M)</x:v>
       </x:c>
       <x:c r="E249" s="9" t="str">
-        <x:v>Read all DME faults and compare requested versus actual boost under the BMW test plan. Pressure- or smoke-test the intake and charge-air path, verify vacuum supply from the pump and reservoir, inspect both banks' hoses and pressure converters, and test actuator movement before condemning a turbocharger. Identify the engine generation, failed bank, and exact hardware in BMW ETK/AIR. Check a 2010-2013 E70 VIN for the N63 Customer Care Package only as applicable; its published six-point scope includes air-mass sensors, injectors, vacuum pump, low-pressure fuel sensor/feed line, fresh-air turbo seals, and crankcase-ventilation lines, not an automatic wastegate replacement. No retail link is published until diagnosis selects a VIN-specific component.</x:v>
+        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles ($2,500-5,000 labor-intensive job). Use ACL Race 8B1578HX-STD ($150-250) or King CR8049SV ($120-200) upgraded bearings - these are stronger than OEM and provide better durability under high loads. Send oil samples for analysis (Blackstone Labs ~$30) every 5,000 miles to monitor bearing wear metals. If bearings have already failed: engine replacement required ($15,000-30,000). DO NOT buy used X6 M without documented bearing replacement history or fresh oil analysis.</x:v>
       </x:c>
       <x:c r="F249" s="9" t="n">
         <x:v>0</x:v>
@@ -10352,136 +11850,136 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="250" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="250" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A250" s="40" t="n">
         <x:v>249</x:v>
       </x:c>
       <x:c r="B250" s="9" t="str">
-        <x:v>bmw-x5-oil-leaks-2000</x:v>
+        <x:v>bmw-x6m-vanos-solenoid-2015</x:v>
       </x:c>
       <x:c r="C250" s="9" t="str">
-        <x:v>2003-2006 | BMW | X5 | 3.0i | M54</x:v>
+        <x:v>2015-2021 | BMW | X6 M | S63</x:v>
       </x:c>
       <x:c r="D250" s="9" t="str">
-        <x:v>E53 3.0i M54 Valve-Cover Gasket Leak (Confirm the Source)</x:v>
+        <x:v>VANOS Solenoid Oil Sludge Buildup</x:v>
       </x:c>
       <x:c r="E250" s="9" t="str">
-        <x:v>Clean the engine and trace the highest fresh-oil source before ordering a gasket. If the leak is at the M54 cylinder-head-cover perimeter or spark-plug-well seals, inspect the plastic cover for cracks, warpage, damaged fastener grommets, and crankcase-ventilation faults. Reuse the cover only if it passes inspection, then install VIN/production-confirmed gasket set 11-12-0-030-496 with the BMW-specified grommets and sealant locations and torque sequence. If the cover or another oil circuit is the source, select that separate repair instead.</x:v>
+        <x:v>Remove and clean or replace the VANOS solenoids. Perform an engine oil flush. Strictly follow 7,500-mile oil change intervals with BMW LL-01 rated 0W-40 synthetic oil.</x:v>
       </x:c>
       <x:c r="F250" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G250" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="251" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="251" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A251" s="40" t="n">
         <x:v>250</x:v>
       </x:c>
       <x:c r="B251" s="9" t="str">
-        <x:v>bmw-x5-transfer-case-actuator-2000</x:v>
+        <x:v>bmw-x7-48v-battery-2020</x:v>
       </x:c>
       <x:c r="C251" s="9" t="str">
-        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive48i, X5 M | N52, N62, M57, S63</x:v>
+        <x:v>2020-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D251" s="9" t="str">
-        <x:v>E70 ATC700 Transfer-Case Positioning Motor (Diagnosis Required)</x:v>
+        <x:v>48V Mild Hybrid Battery Issues</x:v>
       </x:c>
       <x:c r="E251" s="9" t="str">
-        <x:v>Read BMW VTG/DSC faults and run the applicable ISTA transfer-case test plan before buying a motor. Confirm tire sizes and wear, battery voltage, wiring, transfer-case type, fluid condition, calibration, and—especially after differential or transfer-case replacement—the VIN-correct front and rear gear ratios. If testing confirms the ATC700 positioning motor and BMW ETK/AIR selects this application for the VIN, current BMW exchange servomotor 27-10-2-449-709 supersedes 27-10-7-568-267. Install the correct classification resistor/hardware supplied or specified for the VIN and perform the required VTG initialization/calibration. A generic gear-only kit is not a universal BMW repair and should not be ordered without opening and confirming the exact motor failure.</x:v>
+        <x:v>Replace the 48V mild hybrid battery ($1,000-2,000 at dealer). Requires dealer-level diagnostic tools and coding after installation - this is NOT a DIY repair. The 48V battery is separate from the main 12V battery. No aftermarket alternatives currently available. Check if vehicle is still under BMW warranty or extended warranty coverage. Some owners choose to live with the failed auto start-stop rather than pay for replacement.</x:v>
       </x:c>
       <x:c r="F251" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G251" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="252" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="252" ht="726" hidden="0" customHeight="1">
       <x:c r="A252" s="40" t="n">
         <x:v>251</x:v>
       </x:c>
       <x:c r="B252" s="9" t="str">
-        <x:v>bmw-x5-transfer-case-actuator-2007</x:v>
+        <x:v>bmw-x7-air-suspension-2019</x:v>
       </x:c>
       <x:c r="C252" s="9" t="str">
-        <x:v>2019-2026 | BMW | X5</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D252" s="9" t="str">
-        <x:v>G05/F95 Transfer-Case Shudder: Tires and Fluid Diagnosis First</x:v>
+        <x:v>Air Suspension Compressor &amp; Strut Failure (Standard Equipment)</x:v>
       </x:c>
       <x:c r="E252" s="9" t="str">
-        <x:v>Follow BMW SIB 27 02 20 in order: verify all four tires for VIN-correct size, brand/application, axle placement, and wear; diagnose any powertrain faults; then use ISTA to temporarily deactivate the transfer-case clutch and road-test the complaint. Only if the shudder disappears with the VTG deactivated does BMW direct an ATX13-X oil change with DTF-1, followed by VTG calibration. The clutch plates can require up to 125 miles after the service to become fully saturated and smooth out. If the symptom remains, continue diagnosis rather than buying an actuator or transfer case. Part numbers for any further repair must be selected by VIN in ETK/AIR.</x:v>
+        <x:v>Replace failed air struts and/or compressor. Front strut left 37106869035 ($1,500-2,000), right 37106869036 ($1,500-2,000), rear 37106869039 ($1,000-1,500). Compressor 37206861882 ($800-1,200). RebuildMasterTech rebuilt struts ($600-900 each) are a more affordable alternative. Total repair can reach $2,180-5,000+ depending on which components have failed. Replace both struts on same axle simultaneously. Inspect at 50,000 miles for early signs of leaking.</x:v>
       </x:c>
       <x:c r="F252" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G252" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="253" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A253" s="40" t="n">
         <x:v>252</x:v>
       </x:c>
       <x:c r="B253" s="9" t="str">
-        <x:v>bmw-x5-vanos-solenoid-2000</x:v>
+        <x:v>bmw-x7-air-suspension-compressor-2019</x:v>
       </x:c>
       <x:c r="C253" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 | xDrive30i, xDrive35i | N51, N52K, N52T, N55</x:v>
+        <x:v>2019-2026 | BMW | X7</x:v>
       </x:c>
       <x:c r="D253" s="9" t="str">
-        <x:v>VANOS Adjustment-Unit Bolt Recall 23V-707 (E70 Inline-Six)</x:v>
+        <x:v>Air Suspension Compressor Failure</x:v>
       </x:c>
       <x:c r="E253" s="9" t="str">
-        <x:v>Enter the VIN in BMW's official recall lookup and have an authorized BMW center complete recall 23V-707 if it is open. BMW's procedure is inspection-dependent: intact affected bolts are replaced; if bolts are loose or broken, the affected VANOS adjustment unit is replaced, and missing fragments must be recovered. The recall repair is free, so do not buy a solenoid or VANOS part first. If the VIN is outside the recall or a fault remains after the remedy, use BMW-capable diagnostics to test oil supply and pressure, wiring, sensors, control solenoids, adjustment units, and mechanical timing before selecting a part. If the engine runs roughly, makes unusual mechanical noise, loses power, or stalls, move out of traffic safely, stop driving, and contact BMW for transport guidance.</x:v>
+        <x:v>Replace the air suspension compressor. Inspect all four air springs for leaks using soapy water solution. Replace any leaking air springs to prevent repeated compressor failure. Check the valve block for proper operation. The compressor is located under the rear of the vehicle.</x:v>
       </x:c>
       <x:c r="F253" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G253" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="254" ht="1148.4000244140625" hidden="0" customHeight="1">
+    <x:row r="254" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A254" s="40" t="n">
         <x:v>253</x:v>
       </x:c>
       <x:c r="B254" s="9" t="str">
-        <x:v>bmw-x5-water-pump-2007</x:v>
+        <x:v>bmw-x7-b58-coolant-2019</x:v>
       </x:c>
       <x:c r="C254" s="9" t="str">
-        <x:v>2011-2013 | BMW | X5 | xDrive35i | N55</x:v>
+        <x:v>2019-2023 | BMW | X7 | xDrive40i | B58</x:v>
       </x:c>
       <x:c r="D254" s="9" t="str">
-        <x:v>E70 xDrive35i N55 Electric Coolant Pump (Fault-Confirmed)</x:v>
+        <x:v>B58 Coolant System Failures (xDrive40i)</x:v>
       </x:c>
       <x:c r="E254" s="9" t="str">
-        <x:v>If the engine-temperature warning appears, stop safely, shut the engine off, and tow the vehicle if normal temperature cannot be confirmed. When cool, check coolant level and leaks, read BMW-specific faults, verify pump power/ground and communication, and run the ISTA coolant-pump activation/test plan. If those tests confirm the pump and BMW ETK/AIR selects 11-51-5-A05-704 for the VIN, replace it using the BMW procedure, select the thermostat separately only if testing or preventive planning justifies it, vacuum-fill or bleed the system as specified, and verify commanded pump operation and stable temperature. Do not use a fixed-mileage rule or this part number for an N52, N63, or F15 without VIN confirmation.</x:v>
+        <x:v>Replace failed coolant system components. Water pump 11518482250 ($300-400). Thermostat 11537644811 ($150-250). Replace expansion tank and all plastic coolant connections when performing repair to prevent cascading failures. For 2023+ models, check VIN for recall 24V-608 coverage for coolant pump connector. Total repair $500-2,500 depending on extent of damage. PREVENTIVE: Replace thermostat and water pump at 60,000-70,000 miles before failure. Inspect coolant hoses and connections at every oil change after 50k miles.</x:v>
       </x:c>
       <x:c r="F254" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G254" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" ht="1056" hidden="0" customHeight="1">
+    <x:row r="255" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A255" s="40" t="n">
         <x:v>254</x:v>
       </x:c>
       <x:c r="B255" s="9" t="str">
-        <x:v>bmw-x5m-brake-system-2010</x:v>
+        <x:v>bmw-x7-b58-coolant-expansion-tank-2019</x:v>
       </x:c>
       <x:c r="C255" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M</x:v>
+        <x:v>2019-2026 | BMW | X7 | B58</x:v>
       </x:c>
       <x:c r="D255" s="9" t="str">
-        <x:v>Heavy-Duty Brake System Accelerated Wear - E70/F85/F95 X5 M</x:v>
+        <x:v>B58 Coolant Expansion Tank Crack</x:v>
       </x:c>
       <x:c r="E255" s="9" t="str">
-        <x:v>E70 X5 M brakes: OEM front pads 34116799964 ($150-$250), rear pads 34216794879 ($120-$200). F85 X5 M front brake rotors: 34112284101/34112284102 with 6-pot caliper 34117845747/34117845748 and pads 34112284869. F85 rear: 385mm x 24mm perforated rotors 34212284903/34212284904 with 4-pot Brembo caliper and Textar pads. Budget $1,500-$2,500 per axle for complete brake service. For track use: EBC Yellowstuff or Hawk HPS 5.0 pads ($200-$350 per axle) with StopTech slotted rotors for improved heat management. Use Motul RBF 660 or ATE Typ 200 brake fluid - flush every 12 months. Budget $3,000-$5,000 per year for brake maintenance if driving spiritedly.</x:v>
+        <x:v>Replace the coolant expansion tank with an updated BMW part that uses improved plastic composition. Also replace the cap and inspect all coolant hoses. Flush and refill the cooling system with BMW-approved coolant. Check for coolant contamination from the old tank.</x:v>
       </x:c>
       <x:c r="F255" s="9" t="n">
         <x:v>0</x:v>
@@ -10490,21 +11988,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="256" ht="1122" hidden="0" customHeight="1">
+    <x:row r="256" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A256" s="40" t="n">
         <x:v>255</x:v>
       </x:c>
       <x:c r="B256" s="9" t="str">
-        <x:v>bmw-x5m-rear-differential-2010</x:v>
+        <x:v>bmw-x7-ibs-brake-recall-2023</x:v>
       </x:c>
       <x:c r="C256" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | S63</x:v>
+        <x:v>2023-2025 | BMW | X7</x:v>
       </x:c>
       <x:c r="D256" s="9" t="str">
-        <x:v>Rear Differential Wear &amp; Fluid Degradation - E70/F85/F95 X5 M</x:v>
+        <x:v>2023-2025 X7 Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E256" s="9" t="str">
-        <x:v>Change rear differential fluid every 30,000 miles (ignore BMW "lifetime fill" claim). E70 X5 M: No drain plug - fluid must be extracted through fill port with hand pump or suction device. Recommended fluid: Royal Purple 75W-140 GL5 synthetic or Red Line 75W-140 GL5 ($40-$60 per fill). Capacity approximately 1.2 liters. For limited-slip diff, ensure fluid is GL5 rated with limited-slip additive. If differential is making whining/howling noise: have a limited-slip differential specialist inspect internals (not generic BMW shop). Diff rebuild: $1,500-$3,000 at specialist. Complete differential replacement: $3,000-$5,500 + labor. Labor for fluid change: $150-$300 at independent shop.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
       </x:c>
       <x:c r="F256" s="9" t="n">
         <x:v>0</x:v>
@@ -10513,21 +12011,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" ht="1386" hidden="0" customHeight="1">
+    <x:row r="257" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A257" s="40" t="n">
         <x:v>256</x:v>
       </x:c>
       <x:c r="B257" s="9" t="str">
-        <x:v>bmw-x5m-s63-cooling-system-2010</x:v>
+        <x:v>bmw-x7-n63-oil-consumption-2019</x:v>
       </x:c>
       <x:c r="C257" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2019-2023 | BMW | X7 | M50i, M60i, xDrive50i | N63TU3</x:v>
       </x:c>
       <x:c r="D257" s="9" t="str">
-        <x:v>S63 Cooling System Component Failures - E70/F85/F95 X5 M</x:v>
+        <x:v>N63TU3 Oil Consumption &amp; Valve Stem Seal Degradation (xDrive50i/M50i/M60i)</x:v>
       </x:c>
       <x:c r="E257" s="9" t="str">
-        <x:v>PROACTIVE MAINTENANCE SCHEDULE: Replace electric water pump at 60,000 miles ($400-$700 + labor). Replace thermostat at same time ($150-$250). Replace expansion tank at 60,000-80,000 miles ($100-$200). Inspect all coolant hoses at every oil change - replace any that are soft, bulging, or showing surface cracks. E70 X5 M expansion tank vent hose: 17128627119 ($30-$50). Flush coolant system every 2 years or 30,000 miles (more frequent than BMW's 4-year recommendation). Use ONLY BMW coolant mixed 50/50 with distilled water. For E70 hot-V turbo coolant lines: GRYPHONTEK repair kit eliminates plastic T-fitting failure (see separate issue entry). Budget $1,500-$2,500 for complete cooling system refresh at 60,000 miles. This prevents catastrophic overheating that can destroy the S63 engine ($15,000-$34,000 engine replacement).</x:v>
+        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 for OEM spec. 5150 AutoSport Viton upgraded seals ($150-200) recommended for better heat resistance. AGA Tools kit includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Check eligibility for class action settlement coverage. Some owners monitor oil levels and top off rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil and check level every 500-1,000 miles.</x:v>
       </x:c>
       <x:c r="F257" s="9" t="n">
         <x:v>0</x:v>
@@ -10536,21 +12034,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="258" ht="1135.199951171875" hidden="0" customHeight="1">
+    <x:row r="258" ht="396" hidden="0" customHeight="1">
       <x:c r="A258" s="40" t="n">
         <x:v>257</x:v>
       </x:c>
       <x:c r="B258" s="9" t="str">
-        <x:v>bmw-x5m-s63-oil-leaks-2010</x:v>
+        <x:v>bmw-x7-panoramic-roof-rattle-2019</x:v>
       </x:c>
       <x:c r="C258" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2019-2026 | BMW | X7</x:v>
       </x:c>
       <x:c r="D258" s="9" t="str">
-        <x:v>S63 V8 Chronic Oil Leaks (Valve Cover, Oil Pan, Turbo Lines) - E70/F85/F95 X5 M</x:v>
+        <x:v>Panoramic Sunroof Rattle and Creak</x:v>
       </x:c>
       <x:c r="E258" s="9" t="str">
-        <x:v>Valve cover gasket replacement (both sides): $1,200-$2,500 with labor. BMW plastic valve covers can crack and must be replaced entirely (not just gasket) - inspect during service. Oil filter housing gasket: $400-$800 with labor. Oil pan gasket: $2,000-$3,500 (requires engine/subframe drop). Turbo oil feed/return lines: replace with GRYPHONTEK or MAMBA upgraded silicone/braided lines during any turbo service ($200-$400). VANOS solenoid seals: $100-$200 (DIY-friendly). For comprehensive oil leak repair at 80,000+ miles: budget $3,000-$5,000 to address all common leak points simultaneously. Valve cover bolt torque is CRITICAL - too tight cracks the cover ($800-$1,200 per cover), too loose and it leaks.</x:v>
+        <x:v>Apply BMW-approved felt tape or lubricant to sunroof guide rails. Replace worn guide rail bushings. In severe cases, the sunroof cassette or seal may need replacement under warranty. BMW has issued updated guide rail components for early production vehicles.</x:v>
       </x:c>
       <x:c r="F258" s="9" t="n">
         <x:v>0</x:v>
@@ -10559,21 +12057,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" ht="1412.4000244140625" hidden="0" customHeight="1">
+    <x:row r="259" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A259" s="40" t="n">
         <x:v>258</x:v>
       </x:c>
       <x:c r="B259" s="9" t="str">
-        <x:v>bmw-x5m-s63-rod-bearing-2010</x:v>
+        <x:v>bmw-x7-sunroof-leak-2019</x:v>
       </x:c>
       <x:c r="C259" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D259" s="9" t="str">
-        <x:v>S63 V8 Rod Bearing Premature Wear &amp; Failure - E70/F85 X5 M</x:v>
+        <x:v>Panoramic Sunroof Water Leak</x:v>
       </x:c>
       <x:c r="E259" s="9" t="str">
-        <x:v>PREVENTIVE: For track-driven X5 M, replace rod bearings proactively at 60,000-80,000 miles. ACL Race Series rod bearings (8B1578HX-STD for S63B44, +0.001" extra oil clearance) are the community gold standard ($200-$350 for bearing set). WPC surface-treated bearings from Lang Racing are the premium choice ($400-$600 set). Total cost for preventive rod bearing service: $4,500-$8,500 depending on shop. Oil analysis every 5,000 miles through Blackstone Labs ($30/test) to monitor bearing wear metals (lead and copper). Use only BMW 10W-60 synthetic oil with 5,000-7,500 mile oil change intervals. Never track the car on cold oil. Mporium BMW offers specialized S63 rod bearing service starting at $4,499. If catastrophic failure: rebuilt S63 engine from RK Autowerks (~$8,500 + installation), new BMW engine (~$34,000), or complete engine rebuild ($12,000-$18,000).</x:v>
+        <x:v>Clear clogged sunroof drain tubes ($100-300 at shop). Reference TSB SIB 54 11 19 when visiting dealer. For persistent leaks, drain tube connections or sunroof seal may need replacement ($500-1,500). If water has damaged interior electronics, repair costs can reach $3,000. PREVENTIVE: Clear sunroof drains annually, especially in areas with heavy tree debris. Run compressed air or flexible drain snake through drain tubes during oil changes. Keep sunroof track clean of debris.</x:v>
       </x:c>
       <x:c r="F259" s="9" t="n">
         <x:v>0</x:v>
@@ -10582,21 +12080,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="260" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="260" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A260" s="40" t="n">
         <x:v>259</x:v>
       </x:c>
       <x:c r="B260" s="9" t="str">
-        <x:v>bmw-x5m-s63-turbo-coolant-line-2010</x:v>
+        <x:v>bmw-x7-tire-wear-2019</x:v>
       </x:c>
       <x:c r="C260" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 M</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D260" s="9" t="str">
-        <x:v>S63 Turbo Coolant Line Plastic T-Fitting Failure (Hot-V Design) - E70 X5 M</x:v>
+        <x:v>Premature Tire Wear (Especially 21"/22" Wheels)</x:v>
       </x:c>
       <x:c r="E260" s="9" t="str">
-        <x:v>Replace ALL factory plastic turbo coolant T-fittings and hoses with GRYPHONTEK S63 Turbo Coolant Line Repair Kit ($200-$400). Kit includes pre-shaped multi-layer reinforced silicone hoses, brass T-fittings (replacing factory plastic), and all necessary hose clamps. Direct bolt-on installation designed for the E70/E71 S63 engine bay. MAMBA Turbo also offers a reinforced turbo coolant line kit with brass and silicone components ($150-$350). This is a PROACTIVE replacement - do not wait for failure. Replace at first sign of coolant weeping or during any turbo service. Labor: $800-$1,500 due to tight access in hot-V engine valley. If turbo bearings are damaged from overheating: turbo replacement $3,000-$5,000 per unit.</x:v>
+        <x:v>Have alignment adjusted to reduce aggressive camber settings ($200-400). Switch to quality tires designed for heavy SUVs: Michelin Pilot Sport 4S or Continental PremiumContact 6 are recommended. If possible, avoid 22" wheels and opt for 21" or smaller for better tire longevity and ride comfort. Alignment adjustment can extend tire life from 15,000 to 30,000+ miles. Total cost $200-2,000 depending on tire replacement needs. Check alignment every 10,000 miles.</x:v>
       </x:c>
       <x:c r="F260" s="9" t="n">
         <x:v>0</x:v>
@@ -10605,21 +12103,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="261" ht="1135.199951171875" hidden="0" customHeight="1">
+    <x:row r="261" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A261" s="40" t="n">
         <x:v>260</x:v>
       </x:c>
       <x:c r="B261" s="9" t="str">
-        <x:v>bmw-x5m-s63-vanos-solenoid-2010</x:v>
+        <x:v>bmw-xm-airbag-passenger-knee-recall-2023</x:v>
       </x:c>
       <x:c r="C261" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2023-2023 | BMW | XM</x:v>
       </x:c>
       <x:c r="D261" s="9" t="str">
-        <x:v>S63 VANOS Solenoid Failure - E70/F85/F95 X5 M</x:v>
+        <x:v>2023 XM Front-Passenger Knee-Airbag Recall 23V-622</x:v>
       </x:c>
       <x:c r="E261" s="9" t="str">
-        <x:v>Replace all 4 VANOS solenoids simultaneously - they are same age and if one has failed, others are close behind. Pierburg 11368605123 (OEM supplier) at $30-$50 each from Turner Motorsport or BimmerWorld. Genuine BMW 11368482268 for S63TU applications at $50-$70 each. Total parts cost: $120-$280 for all 4 solenoids. Also replace VANOS solenoid O-rings and filter screens during service. Labor: 1-2 hours professional ($150-$400 labor). This is one of the easier S63 repairs - accessible from top of engine without removing intake manifold. Natafox and Febi also offer quality aftermarket VANOS solenoids at lower cost ($20-$35 each). Clean VANOS system with fresh oil change immediately after solenoid replacement.</x:v>
+        <x:v>Check the VIN for an open 23V-622 campaign. If open, an authorized BMW dealer replaces the front-passenger knee airbag free of charge. Do not attempt airbag diagnosis or order a clock spring or airbag module from this card; supplemental-restraint work requires trained personnel and VIN-selected parts.</x:v>
       </x:c>
       <x:c r="F261" s="9" t="n">
         <x:v>0</x:v>
@@ -10628,21 +12126,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="262" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="262" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A262" s="40" t="n">
         <x:v>261</x:v>
       </x:c>
       <x:c r="B262" s="9" t="str">
-        <x:v>bmw-x5m-s63-wastegate-rattle-2010</x:v>
+        <x:v>bmw-xm-hybrid-drivetrain-hesitation-2023</x:v>
       </x:c>
       <x:c r="C262" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 M | S63</x:v>
+        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid, S68</x:v>
       </x:c>
       <x:c r="D262" s="9" t="str">
-        <x:v>S63 Twin Turbo Wastegate Rattle - E70/F85 X5 M</x:v>
+        <x:v>Hybrid Drivetrain Hesitation and Power Delivery Lag</x:v>
       </x:c>
       <x:c r="E262" s="9" t="str">
-        <x:v>Option 1 (Most cost-effective): MAMBA SUS316 stainless steel wastegate rattle flapper repair kit for S63 MGT2260 (part 077-0024, replaces 790463-2 / 790484-3), approximately $150-$300 per turbo. Requires turbo removal for installation. Option 2: Lskioer turbo wastegate rattle flapper repair kit for S63/S63TU MGT2260DSL ($80-$150 per kit on Amazon). Option 3: Replace turbo wastegate actuators with new OEM units ($300-$500 each). Option 4: Full turbocharger replacement with new or remanufactured units ($3,000-$5,000 per turbo + labor). Labor for turbo removal and reinstallation: $2,000-$3,500 for both turbos. While turbos are out: replace turbo oil feed/return lines, coolant lines, and all gaskets (GRYPHONTEK turbo coolant line repair kit for E70 X5M, ~$200-$400).</x:v>
+        <x:v>Visit the dealer for the latest transmission and hybrid system software calibration updates. Select Sport or Sport Plus mode for more consistent power delivery. The latest software revisions significantly improve the electric-to-V8 handoff smoothness. If hesitation persists after updates, the dealer can reset the transmission adaptation values to relearn driving patterns.</x:v>
       </x:c>
       <x:c r="F262" s="9" t="n">
         <x:v>0</x:v>
@@ -10651,21 +12149,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="263" ht="1069.199951171875" hidden="0" customHeight="1">
+    <x:row r="263" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A263" s="40" t="n">
         <x:v>262</x:v>
       </x:c>
       <x:c r="B263" s="9" t="str">
-        <x:v>bmw-x5m-transfer-case-actuator-2010</x:v>
+        <x:v>bmw-xm-integrated-brake-system-recall-2023</x:v>
       </x:c>
       <x:c r="C263" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M</x:v>
+        <x:v>2023-2024 | BMW | XM</x:v>
       </x:c>
       <x:c r="D263" s="9" t="str">
-        <x:v>xDrive Transfer Case Actuator Motor Failure - E70/F85/F95 X5 M</x:v>
+        <x:v>2023-2024 XM Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E263" s="9" t="str">
-        <x:v>Replace transfer case actuator motor. E70 X5 M: BMW 27107566296 or equivalent ($250-$450 for actuator motor). F85 X5 M: BMW 27608643153 or equivalent ($300-$500). F95 X5 M: check VIN-specific part number with dealer. FCP Euro has an excellent DIY guide for BMW transfer case actuator repair - the actuator can be replaced without removing the entire transfer case. Labor: 2-3 hours at specialist shop ($300-$600 labor). Change transfer case fluid at same time with BMW DTF-1 specification fluid. XeMODeX offers remanufactured transfer case actuator motors at reduced cost ($200-$350). For complete transfer case failure: $3,500-$6,000 for replacement unit + labor.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; wheel-speed sensors are not the recall remedy.</x:v>
       </x:c>
       <x:c r="F263" s="9" t="n">
         <x:v>0</x:v>
@@ -10674,21 +12172,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="264" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="264" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A264" s="40" t="n">
         <x:v>263</x:v>
       </x:c>
       <x:c r="B264" s="9" t="str">
-        <x:v>bmw-x6-adaptive-drive-malfunction-2008</x:v>
+        <x:v>bmw-xm-suspension-ride-quality-2023</x:v>
       </x:c>
       <x:c r="C264" s="9" t="str">
-        <x:v>2008-2019 | BMW | X6</x:v>
+        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid</x:v>
       </x:c>
       <x:c r="D264" s="9" t="str">
-        <x:v>Adaptive Drive System Malfunction</x:v>
+        <x:v>Harsh Ride Quality and Suspension Stiffness</x:v>
       </x:c>
       <x:c r="E264" s="9" t="str">
-        <x:v>Diagnose specific Adaptive Drive component failure using BMW ISTA diagnostics. Replace the failed component — most commonly the hydraulic pump or valve block. If repair cost is prohibitive, some owners convert to conventional anti-roll bars as a permanent fix at lower cost.</x:v>
+        <x:v>Check tire pressures regularly - overinflated tires significantly worsen the harsh ride. Some owners report improved comfort by switching to a tire with a taller sidewall profile (if available for the XM's wheel size). Use Comfort mode for daily driving. Unfortunately, no aftermarket spring or damper solution currently exists to significantly improve the ride without compromising the handling needed for the XM's weight.</x:v>
       </x:c>
       <x:c r="F264" s="9" t="n">
         <x:v>0</x:v>
@@ -10697,21 +12195,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="265" ht="858" hidden="0" customHeight="1">
+    <x:row r="265" ht="528" hidden="0" customHeight="1">
       <x:c r="A265" s="40" t="n">
         <x:v>264</x:v>
       </x:c>
       <x:c r="B265" s="9" t="str">
-        <x:v>bmw-x6-air-suspension-2008</x:v>
+        <x:v>bmw-z3-convertible-top-rear-window-cracking-clouding-bead-separatio</x:v>
       </x:c>
       <x:c r="C265" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D265" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure</x:v>
+        <x:v>Convertible Top Rear Window Cracking, Clouding, and Bead Separation</x:v>
       </x:c>
       <x:c r="E265" s="9" t="str">
-        <x:v>Replace failed air springs or compressor. Arnott rear air spring A-2642 ($200-300 each). OEM F16 spring 37126795013 ($200). Arnott compressor P-2655 ($599). Or convert to coil springs: Strutmasters BB2RBM conversion kit ($1,200-1,800) permanently eliminates air suspension issues. Conversion is cheaper long-term than continued air suspension repairs. If keeping air suspension: inspect air springs at 60,000-80,000 miles for cracks/leaks before compressor damage occurs. Replace both air springs on same axle simultaneously.</x:v>
+        <x:v>Replace the rear window panel only — BMW used a zipper system so the clouded/cracked window unzips and a new window zips/tapes in without disturbing the fabric top. Re-gluing separated bead trim rarely holds, so window replacement is the durable fix. Job is a DIY-feasible 1-1.5 hours; replace the whole top only if the fabric is also degraded.</x:v>
       </x:c>
       <x:c r="F265" s="9" t="n">
         <x:v>0</x:v>
@@ -10720,22 +12218,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="266" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="266" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A266" s="40" t="n">
         <x:v>265</x:v>
       </x:c>
       <x:c r="B266" s="9" t="str">
-        <x:v>bmw-x6-ibs-brake-recall-2023</x:v>
+        <x:v>bmw-z3-cooling-system-failure-1996</x:v>
       </x:c>
       <x:c r="C266" s="9" t="str">
-        <x:v>2024-2024 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D266" s="9" t="str">
-        <x:v>2024 X6 Integrated Brake System Recall 26V-422</x:v>
-      </x:c>
-      <x:c r="E266" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
-      </x:c>
+        <x:v>Cooling System Component Failures</x:v>
+      </x:c>
+      <x:c r="E266" s="9" t="str"/>
       <x:c r="F266" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -10743,21 +12239,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="267" ht="924" hidden="0" customHeight="1">
+    <x:row r="267" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A267" s="40" t="n">
         <x:v>266</x:v>
       </x:c>
       <x:c r="B267" s="9" t="str">
-        <x:v>bmw-x6-n63-timing-chain-2008</x:v>
+        <x:v>bmw-z3-cracked-exhaust-manifold-1-9l-4-cylinder</x:v>
       </x:c>
       <x:c r="C267" s="9" t="str">
-        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
+        <x:v>1996-2002 | BMW | Z3 | 1.9, 1.9i, Z3 1.9 | 1.9L M44 4-cylinder, 1.9L M43TU 4-cylinder</x:v>
       </x:c>
       <x:c r="D267" s="9" t="str">
-        <x:v>N63 Timing Chain Stretch &amp; Guide Failure (E71/F16 xDrive50i)</x:v>
+        <x:v>Cracked Exhaust Manifold on 1.9L 4-Cylinder (M44/M43)</x:v>
       </x:c>
       <x:c r="E267" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: If you own 2008-2014 E71 xDrive50i with N63, replace timing chain guides and tensioners IMMEDIATELY at 60,000-80,000 miles ($4,000-6,000) BEFORE failure. IWIS timing chain kit 90001521 ($800-1,200) or Turner kit 11317594899KT recommended. Replace lower chain guide 11147574373 at same time. If chain has already failed: complete engine replacement required ($15,000-25,000). Check VIN with BMW dealer for extended warranty eligibility. 2015+ N63TU engines have improved timing components but still require monitoring.</x:v>
+        <x:v>Inspect the manifold for hairline cracks (a cold-engine listen or smoke test confirms the leak). Replace the cracked manifold with a used OE unit or an aftermarket stainless tubular header, and renew the manifold gasket and hardware. Allow roughly 3-4 hours labor.</x:v>
       </x:c>
       <x:c r="F267" s="9" t="n">
         <x:v>0</x:v>
@@ -10766,21 +12262,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="268" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="268" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A268" s="40" t="n">
         <x:v>267</x:v>
       </x:c>
       <x:c r="B268" s="9" t="str">
-        <x:v>bmw-x6-n63-valve-stem-seal-wear-2008</x:v>
+        <x:v>bmw-z3-differential-mount-ear-trunk-floor-pan-tearing</x:v>
       </x:c>
       <x:c r="C268" s="9" t="str">
-        <x:v>2008-2019 | BMW | X6 | N63</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D268" s="9" t="str">
-        <x:v>N63 Valve Stem Seal Degradation and Oil Burning</x:v>
+        <x:v>Differential Mount Ear and Trunk Floor Pan Tearing</x:v>
       </x:c>
       <x:c r="E268" s="9" t="str">
-        <x:v>Replace all intake and exhaust valve stem seals. This is a major job requiring head work. Also replace turbo oil return lines and update engine software per BMW N63 Customer Care Package specifications. Ensure proper oil grade (BMW LL-01) is used.</x:v>
+        <x:v>Inspect the trunk floor around the differential mount and rear subframe pickup points for cracks, torn metal, and broken spot welds. Repair requires welding and a reinforcement/re-fabrication plate kit to tie the diff mount/subframe back into the floor. Switching the diff carrier bushings to polyurethane reduces carrier movement and the stress that causes the tearing. Catching it early greatly limits the repair scope.</x:v>
       </x:c>
       <x:c r="F268" s="9" t="n">
         <x:v>0</x:v>
@@ -10789,21 +12285,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="269" ht="858" hidden="0" customHeight="1">
+    <x:row r="269" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A269" s="40" t="n">
         <x:v>268</x:v>
       </x:c>
       <x:c r="B269" s="9" t="str">
-        <x:v>bmw-x6-n63-valve-stem-seals-2008</x:v>
+        <x:v>bmw-z3-door-window-regulator-clip-mounting-tab-failure</x:v>
       </x:c>
       <x:c r="C269" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6 | M50i, xDrive50i | N63</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D269" s="9" t="str">
-        <x:v>N63 Valve Stem Seal / Oil Consumption (xDrive50i)</x:v>
+        <x:v>Door Window Regulator Clip / Mounting Tab Failure</x:v>
       </x:c>
       <x:c r="E269" s="9" t="str">
-        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 ($80-120/set of 16, need 2 sets for V8). 5150 AutoSport Viton upgraded seals ($150-200) are recommended for better heat resistance in hot-vee configuration. AGA Tools kit AGA-N63-VSK-K ($500-800) includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Some owners monitor oil levels and add as needed rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil.</x:v>
+        <x:v>Replace the broken plastic regulator clips, or replace the regulator assembly if the cable or mechanism is also worn. If the welded mounting tab/anchor has torn from the door frame, it must be re-welded or reinforced before fitting a new regulator. Lubricate the window channels to reduce drag on the new parts.</x:v>
       </x:c>
       <x:c r="F269" s="9" t="n">
         <x:v>0</x:v>
@@ -10812,21 +12308,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="270" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="270" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A270" s="40" t="n">
         <x:v>269</x:v>
       </x:c>
       <x:c r="B270" s="9" t="str">
-        <x:v>bmw-x6-n63-wastegate-2008</x:v>
+        <x:v>bmw-z3-fuel-level-sender-failure-causing-erratic-dead-fuel-gauge</x:v>
       </x:c>
       <x:c r="C270" s="9" t="str">
-        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D270" s="9" t="str">
-        <x:v>N63 Turbo Wastegate Rattle (xDrive50i)</x:v>
+        <x:v>Fuel Level Sender Failure Causing Erratic or Dead Fuel Gauge</x:v>
       </x:c>
       <x:c r="E270" s="9" t="str">
-        <x:v>Repair options range from flapper repair kits ($50-100/turbo) to complete turbocharger replacement ($4,000-8,000 for both). Garrett MGT2256S flapper repair kit ($50-100 per turbo) is cheapest fix. MAMBA adjustable actuator kit ($150-300) provides more durable solution. OEM actuators 11657646093 available from BMW. Complete turbo replacement $2,000-4,000 per turbo. MONITORING: Wastegate rattle is early warning - address before complete turbo failure to avoid $8,000+ repair.</x:v>
+        <x:v>Remove the access panel behind the seats and inspect the sender. A dirty or lightly worn ceramic/resistor plate can sometimes be cleaned, but a cracked plate or worn brushes requires replacing the sender unit (or the complete fuel-pump/sender carrier assembly). Also check the tank vent valve, as tank vacuum can deform the float arm. Confirm wiring/ground integrity before condemning the sender.</x:v>
       </x:c>
       <x:c r="F270" s="9" t="n">
         <x:v>0</x:v>
@@ -10835,21 +12331,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="271" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="271" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A271" s="40" t="n">
         <x:v>270</x:v>
       </x:c>
       <x:c r="B271" s="9" t="str">
-        <x:v>bmw-x6-rear-differential-bushing-2008</x:v>
+        <x:v>bmw-z3-hvac-blower-final-stage-resistor-failure</x:v>
       </x:c>
       <x:c r="C271" s="9" t="str">
-        <x:v>2008-2026 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D271" s="9" t="str">
-        <x:v>Rear Differential Bushing Deterioration</x:v>
+        <x:v>HVAC Blower Final Stage Resistor Failure (Fan Only Works on Max)</x:v>
       </x:c>
       <x:c r="E271" s="9" t="str">
-        <x:v>Replace all rear differential mount bushings. Use OEM or equivalent quality bushings (Lemforder is the OEM supplier). Inspect the differential housing for any damage from excessive movement. Perform subframe alignment check after bushing replacement.</x:v>
+        <x:v>Replace the blower final stage resistor (A/C cars: part under the scuttle/cowl; non-A/C cars: behind the passenger footwell panel). If a new resistor does not restore all speeds, test the blower motor itself, which may also be worn. Inspect for corrosion/water intrusion at the cowl on A/C cars.</x:v>
       </x:c>
       <x:c r="F271" s="9" t="n">
         <x:v>0</x:v>
@@ -10858,21 +12354,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="272" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="272" ht="1584" hidden="0" customHeight="1">
       <x:c r="A272" s="40" t="n">
         <x:v>271</x:v>
       </x:c>
       <x:c r="B272" s="9" t="str">
-        <x:v>bmw-x6-transfer-case-2008</x:v>
+        <x:v>bmw-z3-rear-subframe-crack-1996</x:v>
       </x:c>
       <x:c r="C272" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D272" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure (All xDrive Models)</x:v>
+        <x:v>Rear Subframe Mounting Point Cracking</x:v>
       </x:c>
       <x:c r="E272" s="9" t="str">
-        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket gear repair kit ($100-150). G06 actuator motor 27609469023 ($400-600) for complete replacement. DIY gear repair kits are straightforward and save $1,200+ over dealer replacement. Complete transfer case replacement if internal damage occurred: $1,400-3,300. PREVENTIVE: If buying used X6 over 80k miles, budget for this repair and listen for clicking noise when shutting off ignition.</x:v>
+        <x:v>Inspect the trunk floor, differential mount area, and all rear subframe mounting points from above and below the car for spot-weld separation, torn sheet metal, and cracked seams; a dye penetrant test or removing trunk trim/seam sealer may be needed to reveal early damage. If cracking is present, the proper repair is to drop the rear axle carrier/subframe, weld and reinforce the damaged unibody mounting points and trunk floor with a reinforcement kit (commonly Randy Forbes-style dual-ear/differential mount reinforcement or equivalent), then reinstall with new subframe bushings, differential mount bushings, and perform a 4-wheel alignment. Minor early cracks may be repairable before major deformation, but advanced damage often requires fabrication and extensive welding by a chassis/body specialist; typical cost ranges from about $2,000-$3,500 for early reinforcement repairs and can exceed $4,000-$6,000 if the floor is torn or multiple mounting points are damaged.</x:v>
       </x:c>
       <x:c r="F272" s="9" t="n">
         <x:v>0</x:v>
@@ -10881,22 +12377,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="273" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="273" ht="66" hidden="0" customHeight="1">
       <x:c r="A273" s="40" t="n">
         <x:v>272</x:v>
       </x:c>
       <x:c r="B273" s="9" t="str">
-        <x:v>bmw-x6m-front-thrust-arm-bushing-2015</x:v>
+        <x:v>bmw-z3-rear-subframe-cracking-1996</x:v>
       </x:c>
       <x:c r="C273" s="9" t="str">
-        <x:v>2015-2025 | BMW | X6 M</x:v>
+        <x:v>1996-2002 | BMW | Z3 | M52, M54</x:v>
       </x:c>
       <x:c r="D273" s="9" t="str">
-        <x:v>Front Thrust Arm Bushing (Tension Strut) Premature Wear</x:v>
-      </x:c>
-      <x:c r="E273" s="9" t="str">
-        <x:v>Replace both front thrust arms as complete assemblies (the bushings are not serviceable separately). Use genuine BMW M-spec parts or Lemforder equivalents. Perform a 4-wheel alignment immediately after replacement. Upgrade to Powerflex polyurethane thrust arm bushings for extended lifespan, especially on tracked cars.</x:v>
-      </x:c>
+        <x:v>Rear Subframe Mounting Point Cracks</x:v>
+      </x:c>
+      <x:c r="E273" s="9" t="str"/>
       <x:c r="F273" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -10904,21 +12398,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="274" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="274" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A274" s="40" t="n">
         <x:v>273</x:v>
       </x:c>
       <x:c r="B274" s="9" t="str">
-        <x:v>bmw-x6m-s63-rod-bearing-2010</x:v>
+        <x:v>bmw-z3-valve-cover-gasket-oil-leak</x:v>
       </x:c>
       <x:c r="C274" s="9" t="str">
-        <x:v>2010-2023 | BMW | X6 M | M50i, xDrive50i | S63</x:v>
+        <x:v>1997-2002 | BMW | Z3 | 2.3, 2.5i, 2.8, 3.0i | M52 2.8, M52TU 2.5/2.8, M54 2.5/3.0</x:v>
       </x:c>
       <x:c r="D274" s="9" t="str">
-        <x:v>S63 Rod Bearing Failure (X6 M)</x:v>
+        <x:v>Valve Cover Gasket Oil Leak (M52/M54 6-Cylinder)</x:v>
       </x:c>
       <x:c r="E274" s="9" t="str">
-        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles ($2,500-5,000 labor-intensive job). Use ACL Race 8B1578HX-STD ($150-250) or King CR8049SV ($120-200) upgraded bearings - these are stronger than OEM and provide better durability under high loads. Send oil samples for analysis (Blackstone Labs ~$30) every 5,000 miles to monitor bearing wear metals. If bearings have already failed: engine replacement required ($15,000-30,000). DO NOT buy used X6 M without documented bearing replacement history or fresh oil analysis.</x:v>
+        <x:v>Replace the valve cover gasket, the spark-plug-well/grommet seals, and the cover bolt seals. On M54 engines also clean oil from the plug wells and replace any oil-contaminated coil boots/coils. Use the correct torque sequence to avoid re-leaking. Inspect the cover for warping or cracks while it is off.</x:v>
       </x:c>
       <x:c r="F274" s="9" t="n">
         <x:v>0</x:v>
@@ -10927,21 +12421,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="275" ht="277.20001220703125" hidden="0" customHeight="1">
+    <x:row r="275" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A275" s="40" t="n">
         <x:v>274</x:v>
       </x:c>
       <x:c r="B275" s="9" t="str">
-        <x:v>bmw-x6m-vanos-solenoid-2015</x:v>
+        <x:v>bmw-z3-vanos-seals-1999</x:v>
       </x:c>
       <x:c r="C275" s="9" t="str">
-        <x:v>2015-2021 | BMW | X6 M | S63</x:v>
+        <x:v>1999-2002 | BMW | Z3 | M52, M54, S52</x:v>
       </x:c>
       <x:c r="D275" s="9" t="str">
-        <x:v>VANOS Solenoid Oil Sludge Buildup</x:v>
+        <x:v>VANOS Seal Failure (M52/M54/S52)</x:v>
       </x:c>
       <x:c r="E275" s="9" t="str">
-        <x:v>Remove and clean or replace the VANOS solenoids. Perform an engine oil flush. Strictly follow 7,500-mile oil change intervals with BMW LL-01 rated 0W-40 synthetic oil.</x:v>
+        <x:v>Confirm the fault by checking for cold-start VANOS rattle, rough idle, hesitation, and scanning for cam timing or mixture-related fault codes; on M52TU/M54/S52 engines, inspect VANOS operation and rule out vacuum leaks before disassembly. Repair typically involves removing the valve cover and VANOS unit, replacing the internal piston seals/O-rings with updated Viton/Teflon seals, renewing the valve cover gasket and VANOS oil line sealing washers, and then re-timing the cams to BMW specifications if required. If the unit still rattles after resealing, the VANOS bearing/anti-rattle components or the complete VANOS assembly may need replacement. Typical cost is about $60-$150 in seals/gaskets for DIY repair, $300-$700 for an independent shop reseal, or $800-$1,500+ if a rebuilt/replacement VANOS unit is installed.</x:v>
       </x:c>
       <x:c r="F275" s="9" t="n">
         <x:v>0</x:v>
@@ -10950,21 +12444,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="276" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="276" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A276" s="40" t="n">
         <x:v>275</x:v>
       </x:c>
       <x:c r="B276" s="9" t="str">
-        <x:v>bmw-x7-48v-battery-2020</x:v>
+        <x:v>bmw-z4-b58-coolant-tank-2019</x:v>
       </x:c>
       <x:c r="C276" s="9" t="str">
-        <x:v>2020-2023 | BMW | X7</x:v>
+        <x:v>2019-2026 | BMW | Z4 | B58</x:v>
       </x:c>
       <x:c r="D276" s="9" t="str">
-        <x:v>48V Mild Hybrid Battery Issues</x:v>
+        <x:v>B58 Coolant Expansion Tank Cracking</x:v>
       </x:c>
       <x:c r="E276" s="9" t="str">
-        <x:v>Replace the 48V mild hybrid battery ($1,000-2,000 at dealer). Requires dealer-level diagnostic tools and coding after installation - this is NOT a DIY repair. The 48V battery is separate from the main 12V battery. No aftermarket alternatives currently available. Check if vehicle is still under BMW warranty or extended warranty coverage. Some owners choose to live with the failed auto start-stop rather than pay for replacement.</x:v>
+        <x:v>Replace the coolant expansion tank with an updated BMW part or aftermarket aluminum tank. Inspect the tank and cap regularly for signs of cracking, discoloration, or seepage. When replacing, also replace the cap and check all coolant hoses for brittleness. Flush and refill with BMW-approved coolant.</x:v>
       </x:c>
       <x:c r="F276" s="9" t="n">
         <x:v>0</x:v>
@@ -10973,21 +12467,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="277" ht="726" hidden="0" customHeight="1">
+    <x:row r="277" ht="1306.800048828125" hidden="0" customHeight="1">
       <x:c r="A277" s="40" t="n">
         <x:v>276</x:v>
       </x:c>
       <x:c r="B277" s="9" t="str">
-        <x:v>bmw-x7-air-suspension-2019</x:v>
+        <x:v>bmw-z4-e85-convertible-top-hydraulic-2003</x:v>
       </x:c>
       <x:c r="C277" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>2003-2008 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D277" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure (Standard Equipment)</x:v>
+        <x:v>Convertible Top Hydraulic Pump Motor Failure - E85 Z4</x:v>
       </x:c>
       <x:c r="E277" s="9" t="str">
-        <x:v>Replace failed air struts and/or compressor. Front strut left 37106869035 ($1,500-2,000), right 37106869036 ($1,500-2,000), rear 37106869039 ($1,000-1,500). Compressor 37206861882 ($800-1,200). RebuildMasterTech rebuilt struts ($600-900 each) are a more affordable alternative. Total repair can reach $2,180-5,000+ depending on which components have failed. Replace both struts on same axle simultaneously. Inspect at 50,000 miles for early signs of leaking.</x:v>
+        <x:v>Replace hydraulic pump motor assembly (BMW 54347193448 / supersedes 54347119633). OEM Genuine BMW pump: $800-$1,200. Aftermarket alternatives available on Amazon for $150-$300 but quality varies significantly. Dealer labor is $1,500-$2,500+ as BMW procedure requires full top removal. ZRoadster.org members have documented a motor relocation to the boot/trunk area which allows much easier future access. Hydraulic fluid: use Aral Vitamol ZHM or BMW 54340394395 hydraulic oil. PREVENTION: Clean drain holes annually, ensure rubber bungs are properly seated, and check for water intrusion in pump area at every service. Some owners have had success with pump motor rebuilds from roofmotors.co.uk ($300-$500) but quality of rebuilds varies.</x:v>
       </x:c>
       <x:c r="F277" s="9" t="n">
         <x:v>0</x:v>
@@ -10996,21 +12490,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="278" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="278" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A278" s="40" t="n">
         <x:v>277</x:v>
       </x:c>
       <x:c r="B278" s="9" t="str">
-        <x:v>bmw-x7-air-suspension-compressor-2019</x:v>
+        <x:v>bmw-z4-e85-window-regulator-2003</x:v>
       </x:c>
       <x:c r="C278" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7</x:v>
+        <x:v>2003-2008 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D278" s="9" t="str">
-        <x:v>Air Suspension Compressor Failure</x:v>
+        <x:v>Power Window Regulator Failure - E85 Z4</x:v>
       </x:c>
       <x:c r="E278" s="9" t="str">
-        <x:v>Replace the air suspension compressor. Inspect all four air springs for leaks using soapy water solution. Replace any leaking air springs to prevent repeated compressor failure. Check the valve block for proper operation. The compressor is located under the rear of the vehicle.</x:v>
+        <x:v>Option 1 (Budget): Window regulator repair kit - replacement cables and rollers for ~$18-$25 from eBay/Amazon (BWR974 for left/driver side). Requires removing door panel and threading new cables through existing regulator frame. DIY-friendly with Z4-forum.com guides. Option 2 (Recommended): Full window regulator replacement. Driver side: BMW 51337198909 ($180-$280 OEM, $80-$150 aftermarket). Passenger side: BMW 51337198910 ($180-$280 OEM, $80-$150 aftermarket). Labor: $200-$400 at independent shop, $500-$700+ at dealer. DIY: 2-3 hours with door panel removal guide from Pelican Parts. ZRoadster.org recommends full replacement over repair kit for long-term reliability.</x:v>
       </x:c>
       <x:c r="F278" s="9" t="n">
         <x:v>0</x:v>
@@ -11019,21 +12513,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="279" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="279" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A279" s="40" t="n">
         <x:v>278</x:v>
       </x:c>
       <x:c r="B279" s="9" t="str">
-        <x:v>bmw-x7-b58-coolant-2019</x:v>
+        <x:v>bmw-z4-electric-steering-rack-2003</x:v>
       </x:c>
       <x:c r="C279" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7 | xDrive40i | B58</x:v>
+        <x:v>2012-2012 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D279" s="9" t="str">
-        <x:v>B58 Coolant System Failures (xDrive40i)</x:v>
+        <x:v>2012 Z4 Electric Power-Steering Recall 12V-302</x:v>
       </x:c>
       <x:c r="E279" s="9" t="str">
-        <x:v>Replace failed coolant system components. Water pump 11518482250 ($300-400). Thermostat 11537644811 ($150-250). Replace expansion tank and all plastic coolant connections when performing repair to prevent cascading failures. For 2023+ models, check VIN for recall 24V-608 coverage for coolant pump connector. Total repair $500-2,500 depending on extent of damage. PREVENTIVE: Replace thermostat and water pump at 60,000-70,000 miles before failure. Inspect coolant hoses and connections at every oil change after 50k miles.</x:v>
+        <x:v>Check the VIN for an open 12V-302 campaign. If open, an authorized BMW dealer replaces the steering-assistance module free of charge. If the steering warning and audible alert occur, maintain control, reduce speed, stop safely and arrange dealer or roadside assistance; do not replace a steering rack from this card.</x:v>
       </x:c>
       <x:c r="F279" s="9" t="n">
         <x:v>0</x:v>
@@ -11042,21 +12536,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="280" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="280" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A280" s="40" t="n">
         <x:v>279</x:v>
       </x:c>
       <x:c r="B280" s="9" t="str">
-        <x:v>bmw-x7-b58-coolant-expansion-tank-2019</x:v>
+        <x:v>bmw-z4-electric-water-pump-2006</x:v>
       </x:c>
       <x:c r="C280" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7 | B58</x:v>
+        <x:v>2012-2016 | BMW | Z4 | N20</x:v>
       </x:c>
       <x:c r="D280" s="9" t="str">
-        <x:v>B58 Coolant Expansion Tank Crack</x:v>
+        <x:v>2012-2016 Z4 sDrive28i Water-Pump Connector Recall 24V-608</x:v>
       </x:c>
       <x:c r="E280" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with an updated BMW part that uses improved plastic composition. Also replace the cap and inspect all coolant hoses. Flush and refill the cooling system with BMW-approved coolant. Check for coolant contamination from the old tank.</x:v>
+        <x:v>Check the VIN for an open 24V-608 campaign. If open, an authorized BMW dealer inspects the water pump and connector, replaces them if necessary, and installs the protective shield free of charge. If smoke appears from the engine compartment, stop safely, switch off the vehicle, have occupants exit, move away from traffic and call emergency or roadside assistance; do not order a pump from this card.</x:v>
       </x:c>
       <x:c r="F280" s="9" t="n">
         <x:v>0</x:v>
@@ -11065,44 +12559,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="281" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="281" ht="1359.5999755859375" hidden="0" customHeight="1">
       <x:c r="A281" s="40" t="n">
         <x:v>280</x:v>
       </x:c>
       <x:c r="B281" s="9" t="str">
-        <x:v>bmw-x7-ibs-brake-recall-2023</x:v>
+        <x:v>bmw-z4-g29-b58-water-pump-2019</x:v>
       </x:c>
       <x:c r="C281" s="9" t="str">
-        <x:v>2023-2025 | BMW | X7</x:v>
+        <x:v>2019-2025 | BMW | Z4 | M40i, sDrive35i, sDrive35is | B48, B58</x:v>
       </x:c>
       <x:c r="D281" s="9" t="str">
-        <x:v>2023-2025 X7 Integrated Brake System Recall 26V-422</x:v>
+        <x:v>B48/B58 Electric Water Pump &amp; Thermostat Failure - G29 Z4</x:v>
       </x:c>
       <x:c r="E281" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
+        <x:v>Preventative replacement recommended at 60,000 miles. Always replace water pump and thermostat together - they share labor overlap and frequently fail concurrently. B48 sDrive30i: Water pump BMW 11518632586 ($300-$450), Thermostat BMW 11538685978 ($100-$150). B58 M40i: Water pump BMW 11518650986 ($350-$500), Thermostat BMW 11538685978 ($100-$150). Mishimoto offers performance water pump alternatives for B58 with improved impeller design. Replace 3 O-rings between thermostat and pump housing, plus 2 O-rings on coolant tube to head. Must replace water pump mounting bolts (torque-to-yield). Labor: 3-4 hours. FCP Euro lifetime warranty kits available. Also inspect plastic cylinder head coolant outlet adapter - known to shear off causing massive coolant leak.</x:v>
       </x:c>
       <x:c r="F281" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G281" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="282" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="282" ht="1122" hidden="0" customHeight="1">
       <x:c r="A282" s="40" t="n">
         <x:v>281</x:v>
       </x:c>
       <x:c r="B282" s="9" t="str">
-        <x:v>bmw-x7-n63-oil-consumption-2019</x:v>
+        <x:v>bmw-z4-n54-hpfp-2009</x:v>
       </x:c>
       <x:c r="C282" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7 | M50i, M60i, xDrive50i | N63TU3</x:v>
+        <x:v>2009-2011 | BMW | Z4 | M40i, sDrive35i, sDrive35is | N54</x:v>
       </x:c>
       <x:c r="D282" s="9" t="str">
-        <x:v>N63TU3 Oil Consumption &amp; Valve Stem Seal Degradation (xDrive50i/M50i/M60i)</x:v>
+        <x:v>N54 High Pressure Fuel Pump (HPFP) Failure - E89 Z4 sDrive35i/35is</x:v>
       </x:c>
       <x:c r="E282" s="9" t="str">
-        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 for OEM spec. 5150 AutoSport Viton upgraded seals ($150-200) recommended for better heat resistance. AGA Tools kit includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Check eligibility for class action settlement coverage. Some owners monitor oil levels and top off rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil and check level every 500-1,000 miles.</x:v>
+        <x:v>Replace HPFP with latest revision Genuine BMW unit. The pump went through multiple revisions - ONLY install the latest version. Part number evolution: Original -&gt; 13517592881 (Index 10, TSB fix) -&gt; 13517616170 (latest revision, most reliable). Genuine BMW 13517616170 is the definitive fix ($350-$550 for pump). Replacement is straightforward DIY (1-2 hours) with basic tools. Also available as complete kit from FCP Euro with lifetime warranty. BMW extended warranty coverage to 10 years/120,000 miles under customer care package for original owners - check VIN eligibility. Replace low-pressure fuel sensor at same time (13537537319) as it may have been damaged by pressure fluctuations ($35-$55).</x:v>
       </x:c>
       <x:c r="F282" s="9" t="n">
         <x:v>0</x:v>
@@ -11111,21 +12605,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="283" ht="396" hidden="0" customHeight="1">
+    <x:row r="283" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A283" s="40" t="n">
         <x:v>282</x:v>
       </x:c>
       <x:c r="B283" s="9" t="str">
-        <x:v>bmw-x7-panoramic-roof-rattle-2019</x:v>
+        <x:v>bmw-z4-n54-wastegate-rattle-2009</x:v>
       </x:c>
       <x:c r="C283" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7</x:v>
+        <x:v>2009-2010 | BMW | Z4 | N54</x:v>
       </x:c>
       <x:c r="D283" s="9" t="str">
-        <x:v>Panoramic Sunroof Rattle and Creak</x:v>
+        <x:v>2009-2010 Z4 sDrive35i N54 Wastegate Diagnosis</x:v>
       </x:c>
       <x:c r="E283" s="9" t="str">
-        <x:v>Apply BMW-approved felt tape or lubricant to sunroof guide rails. Replace worn guide rail bushings. In severe cases, the sunroof cassette or seal may need replacement under warranty. BMW has issued updated guide rail components for early production vehicles.</x:v>
+        <x:v>Confirm the VIN, engine, production date, DME faults, boost-control data and noise source using current BMW diagnostic information. Check VIN-specific coverage history with BMW, recognizing that the bulletin's time/mileage window may have expired. Do not replace a turbocharger, actuator or wastegate from this card without the required diagnosis.</x:v>
       </x:c>
       <x:c r="F283" s="9" t="n">
         <x:v>0</x:v>
@@ -11134,21 +12628,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="284" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="284" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A284" s="40" t="n">
         <x:v>283</x:v>
       </x:c>
       <x:c r="B284" s="9" t="str">
-        <x:v>bmw-x7-sunroof-leak-2019</x:v>
+        <x:v>bmw-z4-soft-top-hydraulic-2003</x:v>
       </x:c>
       <x:c r="C284" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>2009-2016 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D284" s="9" t="str">
-        <x:v>Panoramic Sunroof Water Leak</x:v>
+        <x:v>Retractable Hard Top Hydraulic Mechanism Failure</x:v>
       </x:c>
       <x:c r="E284" s="9" t="str">
-        <x:v>Clear clogged sunroof drain tubes ($100-300 at shop). Reference TSB SIB 54 11 19 when visiting dealer. For persistent leaks, drain tube connections or sunroof seal may need replacement ($500-1,500). If water has damaged interior electronics, repair costs can reach $3,000. PREVENTIVE: Clear sunroof drains annually, especially in areas with heavy tree debris. Run compressed air or flexible drain snake through drain tubes during oil changes. Keep sunroof track clean of debris.</x:v>
+        <x:v>Diagnose the leak location and replace the failed component. Common failure points are the main hydraulic cylinders (left and right), the hydraulic pump motor, and the flexible hoses. The hydraulic fluid should be flushed and replaced with BMW-approved CHF 11S fluid. A full system bleed is required after any repair.</x:v>
       </x:c>
       <x:c r="F284" s="9" t="n">
         <x:v>0</x:v>
@@ -11157,21 +12651,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="285" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="285" ht="1188" hidden="0" customHeight="1">
       <x:c r="A285" s="40" t="n">
         <x:v>284</x:v>
       </x:c>
       <x:c r="B285" s="9" t="str">
-        <x:v>bmw-x7-tire-wear-2019</x:v>
+        <x:v>bmw-z4-vanos-solenoid-2003</x:v>
       </x:c>
       <x:c r="C285" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>2003-2016 | BMW | Z4 | 2.5i, 3.0i, 3.0si, M40i, sDrive28i, sDrive30i, sDrive35i, sDrive35is | M54, N52, N54, N20</x:v>
       </x:c>
       <x:c r="D285" s="9" t="str">
-        <x:v>Premature Tire Wear (Especially 21"/22" Wheels)</x:v>
+        <x:v>VANOS Solenoid &amp; System Failure - E85/E89 Z4 (All Engines)</x:v>
       </x:c>
       <x:c r="E285" s="9" t="str">
-        <x:v>Have alignment adjusted to reduce aggressive camber settings ($200-400). Switch to quality tires designed for heavy SUVs: Michelin Pilot Sport 4S or Continental PremiumContact 6 are recommended. If possible, avoid 22" wheels and opt for 21" or smaller for better tire longevity and ride comfort. Alignment adjustment can extend tire life from 15,000 to 30,000+ miles. Total cost $200-2,000 depending on tire replacement needs. Check alignment every 10,000 miles.</x:v>
+        <x:v>Replace VANOS solenoids - inexpensive and straightforward repair. M54 (E85 2003-2005): 2 solenoids required, BMW 11361707323 ($35-$65 each). N52 (E85 2006-2008 / E89 2009-2011 28i): 2 solenoids, BMW 11367585425 ($40-$70 each). N54 (E89 35i/35is): 2 solenoids, BMW 11367585425 ($40-$70 each). N20 (E89 sDrive28i 2012-2016): 2 solenoids, BMW 11367585425 ($40-$70 each). Labor: under 1 hour for experienced mechanic, 2-3 hours DIY. Replace all solenoids at once even if only one has failed - the others are same age and will fail soon. Also replace VANOS solenoid O-rings and sealing plates during service. Clean VANOS system with Beisan Systems VANOS cleaning procedure for best results.</x:v>
       </x:c>
       <x:c r="F285" s="9" t="n">
         <x:v>0</x:v>
@@ -11180,597 +12674,26 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="286" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A286" s="40" t="n">
+    <x:row r="286" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A286" s="42" t="n">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="B286" s="9" t="str">
-        <x:v>bmw-xm-airbag-passenger-knee-recall-2023</x:v>
-      </x:c>
-      <x:c r="C286" s="9" t="str">
-        <x:v>2023-2023 | BMW | XM</x:v>
-      </x:c>
-      <x:c r="D286" s="9" t="str">
-        <x:v>2023 XM Front-Passenger Knee-Airbag Recall 23V-622</x:v>
-      </x:c>
-      <x:c r="E286" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-622 campaign. If open, an authorized BMW dealer replaces the front-passenger knee airbag free of charge. Do not attempt airbag diagnosis or order a clock spring or airbag module from this card; supplemental-restraint work requires trained personnel and VIN-selected parts.</x:v>
-      </x:c>
-      <x:c r="F286" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G286" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="287" ht="567.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A287" s="40" t="n">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="B287" s="9" t="str">
-        <x:v>bmw-xm-hybrid-drivetrain-hesitation-2023</x:v>
-      </x:c>
-      <x:c r="C287" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid, S68</x:v>
-      </x:c>
-      <x:c r="D287" s="9" t="str">
-        <x:v>Hybrid Drivetrain Hesitation and Power Delivery Lag</x:v>
-      </x:c>
-      <x:c r="E287" s="9" t="str">
-        <x:v>Visit the dealer for the latest transmission and hybrid system software calibration updates. Select Sport or Sport Plus mode for more consistent power delivery. The latest software revisions significantly improve the electric-to-V8 handoff smoothness. If hesitation persists after updates, the dealer can reset the transmission adaptation values to relearn driving patterns.</x:v>
-      </x:c>
-      <x:c r="F287" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G287" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="288" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A288" s="40" t="n">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="B288" s="9" t="str">
-        <x:v>bmw-xm-integrated-brake-system-recall-2023</x:v>
-      </x:c>
-      <x:c r="C288" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM</x:v>
-      </x:c>
-      <x:c r="D288" s="9" t="str">
-        <x:v>2023-2024 XM Integrated Brake System Recall 26V-422</x:v>
-      </x:c>
-      <x:c r="E288" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; wheel-speed sensors are not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F288" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G288" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="289" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A289" s="40" t="n">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="B289" s="9" t="str">
-        <x:v>bmw-xm-suspension-ride-quality-2023</x:v>
-      </x:c>
-      <x:c r="C289" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid</x:v>
-      </x:c>
-      <x:c r="D289" s="9" t="str">
-        <x:v>Harsh Ride Quality and Suspension Stiffness</x:v>
-      </x:c>
-      <x:c r="E289" s="9" t="str">
-        <x:v>Check tire pressures regularly - overinflated tires significantly worsen the harsh ride. Some owners report improved comfort by switching to a tire with a taller sidewall profile (if available for the XM's wheel size). Use Comfort mode for daily driving. Unfortunately, no aftermarket spring or damper solution currently exists to significantly improve the ride without compromising the handling needed for the XM's weight.</x:v>
-      </x:c>
-      <x:c r="F289" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G289" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="290" ht="528" hidden="0" customHeight="1">
-      <x:c r="A290" s="40" t="n">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="B290" s="9" t="str">
-        <x:v>bmw-z3-convertible-top-rear-window-cracking-clouding-bead-separatio</x:v>
-      </x:c>
-      <x:c r="C290" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D290" s="9" t="str">
-        <x:v>Convertible Top Rear Window Cracking, Clouding, and Bead Separation</x:v>
-      </x:c>
-      <x:c r="E290" s="9" t="str">
-        <x:v>Replace the rear window panel only — BMW used a zipper system so the clouded/cracked window unzips and a new window zips/tapes in without disturbing the fabric top. Re-gluing separated bead trim rarely holds, so window replacement is the durable fix. Job is a DIY-feasible 1-1.5 hours; replace the whole top only if the fabric is also degraded.</x:v>
-      </x:c>
-      <x:c r="F290" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G290" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="291" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A291" s="40" t="n">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="B291" s="9" t="str">
-        <x:v>bmw-z3-cooling-system-failure-1996</x:v>
-      </x:c>
-      <x:c r="C291" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D291" s="9" t="str">
-        <x:v>Cooling System Component Failures</x:v>
-      </x:c>
-      <x:c r="E291" s="9" t="str"/>
-      <x:c r="F291" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G291" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="292" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A292" s="40" t="n">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="B292" s="9" t="str">
-        <x:v>bmw-z3-cracked-exhaust-manifold-1-9l-4-cylinder</x:v>
-      </x:c>
-      <x:c r="C292" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3 | 1.9, 1.9i, Z3 1.9 | 1.9L M44 4-cylinder, 1.9L M43TU 4-cylinder</x:v>
-      </x:c>
-      <x:c r="D292" s="9" t="str">
-        <x:v>Cracked Exhaust Manifold on 1.9L 4-Cylinder (M44/M43)</x:v>
-      </x:c>
-      <x:c r="E292" s="9" t="str">
-        <x:v>Inspect the manifold for hairline cracks (a cold-engine listen or smoke test confirms the leak). Replace the cracked manifold with a used OE unit or an aftermarket stainless tubular header, and renew the manifold gasket and hardware. Allow roughly 3-4 hours labor.</x:v>
-      </x:c>
-      <x:c r="F292" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G292" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="293" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A293" s="40" t="n">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="B293" s="9" t="str">
-        <x:v>bmw-z3-differential-mount-ear-trunk-floor-pan-tearing</x:v>
-      </x:c>
-      <x:c r="C293" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D293" s="9" t="str">
-        <x:v>Differential Mount Ear and Trunk Floor Pan Tearing</x:v>
-      </x:c>
-      <x:c r="E293" s="9" t="str">
-        <x:v>Inspect the trunk floor around the differential mount and rear subframe pickup points for cracks, torn metal, and broken spot welds. Repair requires welding and a reinforcement/re-fabrication plate kit to tie the diff mount/subframe back into the floor. Switching the diff carrier bushings to polyurethane reduces carrier movement and the stress that causes the tearing. Catching it early greatly limits the repair scope.</x:v>
-      </x:c>
-      <x:c r="F293" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G293" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="294" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A294" s="40" t="n">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="B294" s="9" t="str">
-        <x:v>bmw-z3-door-window-regulator-clip-mounting-tab-failure</x:v>
-      </x:c>
-      <x:c r="C294" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D294" s="9" t="str">
-        <x:v>Door Window Regulator Clip / Mounting Tab Failure</x:v>
-      </x:c>
-      <x:c r="E294" s="9" t="str">
-        <x:v>Replace the broken plastic regulator clips, or replace the regulator assembly if the cable or mechanism is also worn. If the welded mounting tab/anchor has torn from the door frame, it must be re-welded or reinforced before fitting a new regulator. Lubricate the window channels to reduce drag on the new parts.</x:v>
-      </x:c>
-      <x:c r="F294" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G294" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="295" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A295" s="40" t="n">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="B295" s="9" t="str">
-        <x:v>bmw-z3-fuel-level-sender-failure-causing-erratic-dead-fuel-gauge</x:v>
-      </x:c>
-      <x:c r="C295" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D295" s="9" t="str">
-        <x:v>Fuel Level Sender Failure Causing Erratic or Dead Fuel Gauge</x:v>
-      </x:c>
-      <x:c r="E295" s="9" t="str">
-        <x:v>Remove the access panel behind the seats and inspect the sender. A dirty or lightly worn ceramic/resistor plate can sometimes be cleaned, but a cracked plate or worn brushes requires replacing the sender unit (or the complete fuel-pump/sender carrier assembly). Also check the tank vent valve, as tank vacuum can deform the float arm. Confirm wiring/ground integrity before condemning the sender.</x:v>
-      </x:c>
-      <x:c r="F295" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G295" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="296" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A296" s="40" t="n">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="B296" s="9" t="str">
-        <x:v>bmw-z3-hvac-blower-final-stage-resistor-failure</x:v>
-      </x:c>
-      <x:c r="C296" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D296" s="9" t="str">
-        <x:v>HVAC Blower Final Stage Resistor Failure (Fan Only Works on Max)</x:v>
-      </x:c>
-      <x:c r="E296" s="9" t="str">
-        <x:v>Replace the blower final stage resistor (A/C cars: part under the scuttle/cowl; non-A/C cars: behind the passenger footwell panel). If a new resistor does not restore all speeds, test the blower motor itself, which may also be worn. Inspect for corrosion/water intrusion at the cowl on A/C cars.</x:v>
-      </x:c>
-      <x:c r="F296" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G296" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="297" ht="1584" hidden="0" customHeight="1">
-      <x:c r="A297" s="40" t="n">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="B297" s="9" t="str">
-        <x:v>bmw-z3-rear-subframe-crack-1996</x:v>
-      </x:c>
-      <x:c r="C297" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D297" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracking</x:v>
-      </x:c>
-      <x:c r="E297" s="9" t="str">
-        <x:v>Inspect the trunk floor, differential mount area, and all rear subframe mounting points from above and below the car for spot-weld separation, torn sheet metal, and cracked seams; a dye penetrant test or removing trunk trim/seam sealer may be needed to reveal early damage. If cracking is present, the proper repair is to drop the rear axle carrier/subframe, weld and reinforce the damaged unibody mounting points and trunk floor with a reinforcement kit (commonly Randy Forbes-style dual-ear/differential mount reinforcement or equivalent), then reinstall with new subframe bushings, differential mount bushings, and perform a 4-wheel alignment. Minor early cracks may be repairable before major deformation, but advanced damage often requires fabrication and extensive welding by a chassis/body specialist; typical cost ranges from about $2,000-$3,500 for early reinforcement repairs and can exceed $4,000-$6,000 if the floor is torn or multiple mounting points are damaged.</x:v>
-      </x:c>
-      <x:c r="F297" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G297" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="298" ht="66" hidden="0" customHeight="1">
-      <x:c r="A298" s="40" t="n">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="B298" s="9" t="str">
-        <x:v>bmw-z3-rear-subframe-cracking-1996</x:v>
-      </x:c>
-      <x:c r="C298" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3 | M52, M54</x:v>
-      </x:c>
-      <x:c r="D298" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracks</x:v>
-      </x:c>
-      <x:c r="E298" s="9" t="str"/>
-      <x:c r="F298" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G298" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="299" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A299" s="40" t="n">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="B299" s="9" t="str">
-        <x:v>bmw-z3-valve-cover-gasket-oil-leak</x:v>
-      </x:c>
-      <x:c r="C299" s="9" t="str">
-        <x:v>1997-2002 | BMW | Z3 | 2.3, 2.5i, 2.8, 3.0i | M52 2.8, M52TU 2.5/2.8, M54 2.5/3.0</x:v>
-      </x:c>
-      <x:c r="D299" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak (M52/M54 6-Cylinder)</x:v>
-      </x:c>
-      <x:c r="E299" s="9" t="str">
-        <x:v>Replace the valve cover gasket, the spark-plug-well/grommet seals, and the cover bolt seals. On M54 engines also clean oil from the plug wells and replace any oil-contaminated coil boots/coils. Use the correct torque sequence to avoid re-leaking. Inspect the cover for warping or cracks while it is off.</x:v>
-      </x:c>
-      <x:c r="F299" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G299" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="300" ht="1293.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A300" s="40" t="n">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="B300" s="9" t="str">
-        <x:v>bmw-z3-vanos-seals-1999</x:v>
-      </x:c>
-      <x:c r="C300" s="9" t="str">
-        <x:v>1999-2002 | BMW | Z3 | M52, M54, S52</x:v>
-      </x:c>
-      <x:c r="D300" s="9" t="str">
-        <x:v>VANOS Seal Failure (M52/M54/S52)</x:v>
-      </x:c>
-      <x:c r="E300" s="9" t="str">
-        <x:v>Confirm the fault by checking for cold-start VANOS rattle, rough idle, hesitation, and scanning for cam timing or mixture-related fault codes; on M52TU/M54/S52 engines, inspect VANOS operation and rule out vacuum leaks before disassembly. Repair typically involves removing the valve cover and VANOS unit, replacing the internal piston seals/O-rings with updated Viton/Teflon seals, renewing the valve cover gasket and VANOS oil line sealing washers, and then re-timing the cams to BMW specifications if required. If the unit still rattles after resealing, the VANOS bearing/anti-rattle components or the complete VANOS assembly may need replacement. Typical cost is about $60-$150 in seals/gaskets for DIY repair, $300-$700 for an independent shop reseal, or $800-$1,500+ if a rebuilt/replacement VANOS unit is installed.</x:v>
-      </x:c>
-      <x:c r="F300" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G300" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="301" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A301" s="40" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="B301" s="9" t="str">
-        <x:v>bmw-z4-b58-coolant-tank-2019</x:v>
-      </x:c>
-      <x:c r="C301" s="9" t="str">
-        <x:v>2019-2026 | BMW | Z4 | B58</x:v>
-      </x:c>
-      <x:c r="D301" s="9" t="str">
-        <x:v>B58 Coolant Expansion Tank Cracking</x:v>
-      </x:c>
-      <x:c r="E301" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with an updated BMW part or aftermarket aluminum tank. Inspect the tank and cap regularly for signs of cracking, discoloration, or seepage. When replacing, also replace the cap and check all coolant hoses for brittleness. Flush and refill with BMW-approved coolant.</x:v>
-      </x:c>
-      <x:c r="F301" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G301" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="302" ht="1306.800048828125" hidden="0" customHeight="1">
-      <x:c r="A302" s="40" t="n">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="B302" s="9" t="str">
-        <x:v>bmw-z4-e85-convertible-top-hydraulic-2003</x:v>
-      </x:c>
-      <x:c r="C302" s="9" t="str">
-        <x:v>2003-2008 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D302" s="9" t="str">
-        <x:v>Convertible Top Hydraulic Pump Motor Failure - E85 Z4</x:v>
-      </x:c>
-      <x:c r="E302" s="9" t="str">
-        <x:v>Replace hydraulic pump motor assembly (BMW 54347193448 / supersedes 54347119633). OEM Genuine BMW pump: $800-$1,200. Aftermarket alternatives available on Amazon for $150-$300 but quality varies significantly. Dealer labor is $1,500-$2,500+ as BMW procedure requires full top removal. ZRoadster.org members have documented a motor relocation to the boot/trunk area which allows much easier future access. Hydraulic fluid: use Aral Vitamol ZHM or BMW 54340394395 hydraulic oil. PREVENTION: Clean drain holes annually, ensure rubber bungs are properly seated, and check for water intrusion in pump area at every service. Some owners have had success with pump motor rebuilds from roofmotors.co.uk ($300-$500) but quality of rebuilds varies.</x:v>
-      </x:c>
-      <x:c r="F302" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G302" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="303" ht="1135.199951171875" hidden="0" customHeight="1">
-      <x:c r="A303" s="40" t="n">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="B303" s="9" t="str">
-        <x:v>bmw-z4-e85-window-regulator-2003</x:v>
-      </x:c>
-      <x:c r="C303" s="9" t="str">
-        <x:v>2003-2008 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D303" s="9" t="str">
-        <x:v>Power Window Regulator Failure - E85 Z4</x:v>
-      </x:c>
-      <x:c r="E303" s="9" t="str">
-        <x:v>Option 1 (Budget): Window regulator repair kit - replacement cables and rollers for ~$18-$25 from eBay/Amazon (BWR974 for left/driver side). Requires removing door panel and threading new cables through existing regulator frame. DIY-friendly with Z4-forum.com guides. Option 2 (Recommended): Full window regulator replacement. Driver side: BMW 51337198909 ($180-$280 OEM, $80-$150 aftermarket). Passenger side: BMW 51337198910 ($180-$280 OEM, $80-$150 aftermarket). Labor: $200-$400 at independent shop, $500-$700+ at dealer. DIY: 2-3 hours with door panel removal guide from Pelican Parts. ZRoadster.org recommends full replacement over repair kit for long-term reliability.</x:v>
-      </x:c>
-      <x:c r="F303" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G303" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="304" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A304" s="40" t="n">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="B304" s="9" t="str">
-        <x:v>bmw-z4-electric-steering-rack-2003</x:v>
-      </x:c>
-      <x:c r="C304" s="9" t="str">
-        <x:v>2012-2012 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D304" s="9" t="str">
-        <x:v>2012 Z4 Electric Power-Steering Recall 12V-302</x:v>
-      </x:c>
-      <x:c r="E304" s="9" t="str">
-        <x:v>Check the VIN for an open 12V-302 campaign. If open, an authorized BMW dealer replaces the steering-assistance module free of charge. If the steering warning and audible alert occur, maintain control, reduce speed, stop safely and arrange dealer or roadside assistance; do not replace a steering rack from this card.</x:v>
-      </x:c>
-      <x:c r="F304" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G304" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="305" ht="633.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A305" s="40" t="n">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="B305" s="9" t="str">
-        <x:v>bmw-z4-electric-water-pump-2006</x:v>
-      </x:c>
-      <x:c r="C305" s="9" t="str">
-        <x:v>2012-2016 | BMW | Z4 | N20</x:v>
-      </x:c>
-      <x:c r="D305" s="9" t="str">
-        <x:v>2012-2016 Z4 sDrive28i Water-Pump Connector Recall 24V-608</x:v>
-      </x:c>
-      <x:c r="E305" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-608 campaign. If open, an authorized BMW dealer inspects the water pump and connector, replaces them if necessary, and installs the protective shield free of charge. If smoke appears from the engine compartment, stop safely, switch off the vehicle, have occupants exit, move away from traffic and call emergency or roadside assistance; do not order a pump from this card.</x:v>
-      </x:c>
-      <x:c r="F305" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G305" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="306" ht="1359.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A306" s="40" t="n">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="B306" s="9" t="str">
-        <x:v>bmw-z4-g29-b58-water-pump-2019</x:v>
-      </x:c>
-      <x:c r="C306" s="9" t="str">
-        <x:v>2019-2025 | BMW | Z4 | M40i, sDrive35i, sDrive35is | B48, B58</x:v>
-      </x:c>
-      <x:c r="D306" s="9" t="str">
-        <x:v>B48/B58 Electric Water Pump &amp; Thermostat Failure - G29 Z4</x:v>
-      </x:c>
-      <x:c r="E306" s="9" t="str">
-        <x:v>Preventative replacement recommended at 60,000 miles. Always replace water pump and thermostat together - they share labor overlap and frequently fail concurrently. B48 sDrive30i: Water pump BMW 11518632586 ($300-$450), Thermostat BMW 11538685978 ($100-$150). B58 M40i: Water pump BMW 11518650986 ($350-$500), Thermostat BMW 11538685978 ($100-$150). Mishimoto offers performance water pump alternatives for B58 with improved impeller design. Replace 3 O-rings between thermostat and pump housing, plus 2 O-rings on coolant tube to head. Must replace water pump mounting bolts (torque-to-yield). Labor: 3-4 hours. FCP Euro lifetime warranty kits available. Also inspect plastic cylinder head coolant outlet adapter - known to shear off causing massive coolant leak.</x:v>
-      </x:c>
-      <x:c r="F306" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G306" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="307" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A307" s="40" t="n">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="B307" s="9" t="str">
-        <x:v>bmw-z4-n54-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C307" s="9" t="str">
-        <x:v>2009-2011 | BMW | Z4 | M40i, sDrive35i, sDrive35is | N54</x:v>
-      </x:c>
-      <x:c r="D307" s="9" t="str">
-        <x:v>N54 High Pressure Fuel Pump (HPFP) Failure - E89 Z4 sDrive35i/35is</x:v>
-      </x:c>
-      <x:c r="E307" s="9" t="str">
-        <x:v>Replace HPFP with latest revision Genuine BMW unit. The pump went through multiple revisions - ONLY install the latest version. Part number evolution: Original -&gt; 13517592881 (Index 10, TSB fix) -&gt; 13517616170 (latest revision, most reliable). Genuine BMW 13517616170 is the definitive fix ($350-$550 for pump). Replacement is straightforward DIY (1-2 hours) with basic tools. Also available as complete kit from FCP Euro with lifetime warranty. BMW extended warranty coverage to 10 years/120,000 miles under customer care package for original owners - check VIN eligibility. Replace low-pressure fuel sensor at same time (13537537319) as it may have been damaged by pressure fluctuations ($35-$55).</x:v>
-      </x:c>
-      <x:c r="F307" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G307" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="308" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A308" s="40" t="n">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="B308" s="9" t="str">
-        <x:v>bmw-z4-n54-wastegate-rattle-2009</x:v>
-      </x:c>
-      <x:c r="C308" s="9" t="str">
-        <x:v>2009-2010 | BMW | Z4 | N54</x:v>
-      </x:c>
-      <x:c r="D308" s="9" t="str">
-        <x:v>2009-2010 Z4 sDrive35i N54 Wastegate Diagnosis</x:v>
-      </x:c>
-      <x:c r="E308" s="9" t="str">
-        <x:v>Confirm the VIN, engine, production date, DME faults, boost-control data and noise source using current BMW diagnostic information. Check VIN-specific coverage history with BMW, recognizing that the bulletin's time/mileage window may have expired. Do not replace a turbocharger, actuator or wastegate from this card without the required diagnosis.</x:v>
-      </x:c>
-      <x:c r="F308" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G308" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="309" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A309" s="40" t="n">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="B309" s="9" t="str">
-        <x:v>bmw-z4-soft-top-hydraulic-2003</x:v>
-      </x:c>
-      <x:c r="C309" s="9" t="str">
-        <x:v>2009-2016 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D309" s="9" t="str">
-        <x:v>Retractable Hard Top Hydraulic Mechanism Failure</x:v>
-      </x:c>
-      <x:c r="E309" s="9" t="str">
-        <x:v>Diagnose the leak location and replace the failed component. Common failure points are the main hydraulic cylinders (left and right), the hydraulic pump motor, and the flexible hoses. The hydraulic fluid should be flushed and replaced with BMW-approved CHF 11S fluid. A full system bleed is required after any repair.</x:v>
-      </x:c>
-      <x:c r="F309" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G309" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="310" ht="1188" hidden="0" customHeight="1">
-      <x:c r="A310" s="40" t="n">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="B310" s="9" t="str">
-        <x:v>bmw-z4-vanos-solenoid-2003</x:v>
-      </x:c>
-      <x:c r="C310" s="9" t="str">
-        <x:v>2003-2016 | BMW | Z4 | 2.5i, 3.0i, 3.0si, M40i, sDrive28i, sDrive30i, sDrive35i, sDrive35is | M54, N52, N54, N20</x:v>
-      </x:c>
-      <x:c r="D310" s="9" t="str">
-        <x:v>VANOS Solenoid &amp; System Failure - E85/E89 Z4 (All Engines)</x:v>
-      </x:c>
-      <x:c r="E310" s="9" t="str">
-        <x:v>Replace VANOS solenoids - inexpensive and straightforward repair. M54 (E85 2003-2005): 2 solenoids required, BMW 11361707323 ($35-$65 each). N52 (E85 2006-2008 / E89 2009-2011 28i): 2 solenoids, BMW 11367585425 ($40-$70 each). N54 (E89 35i/35is): 2 solenoids, BMW 11367585425 ($40-$70 each). N20 (E89 sDrive28i 2012-2016): 2 solenoids, BMW 11367585425 ($40-$70 each). Labor: under 1 hour for experienced mechanic, 2-3 hours DIY. Replace all solenoids at once even if only one has failed - the others are same age and will fail soon. Also replace VANOS solenoid O-rings and sealing plates during service. Clean VANOS system with Beisan Systems VANOS cleaning procedure for best results.</x:v>
-      </x:c>
-      <x:c r="F310" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G310" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="311" ht="554.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A311" s="42" t="n">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="B311" s="43" t="str">
+      <x:c r="B286" s="43" t="str">
         <x:v>bmw-z8-soft-top-mechanism-2000</x:v>
       </x:c>
-      <x:c r="C311" s="43" t="str">
+      <x:c r="C286" s="43" t="str">
         <x:v>2000-2003 | BMW | Z8</x:v>
       </x:c>
-      <x:c r="D311" s="43" t="str">
+      <x:c r="D286" s="43" t="str">
         <x:v>Power Soft Top Hydraulic System and Cable Failure</x:v>
       </x:c>
-      <x:c r="E311" s="43" t="str">
+      <x:c r="E286" s="43" t="str">
         <x:v>Rebuild the hydraulic cylinders with new seals rather than replacing ($200 vs $2,000+). Inspect and replace frayed cables. Adjust or replace the microswitch sensors at the windshield header latch. Lubricate the top mechanism pivot points with silicone grease annually. Store the car with the top up to reduce stress on the hydraulic system.</x:v>
       </x:c>
-      <x:c r="F311" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G311" s="44" t="str">
+      <x:c r="F286" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G286" s="44" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>

--- a/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
+++ b/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R281e99e7ac6442ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="Rb9d83947515940a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R57a2076393cb4f26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="Re3ed6452063147e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2c17cda81a7d4bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="R0d753f5f65c04068"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R36276f2dc1604ce6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R1ec443a6e9e64a8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>285</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>100</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>148</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -565,10 +565,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="29" t="str">
-        <x:v>Source snapshot hash</x:v>
-      </x:c>
-      <x:c r="B11" s="13" t="str">
-        <x:v>9c5acba63181f1d3d714c4d0090380ab656767ee3836b4056dfe3873dadc67e0</x:v>
+        <x:v>Missing How to Fix</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C11" s="11"/>
       <x:c r="D11" s="11"/>
@@ -578,8 +578,12 @@
       <x:c r="H11" s="28"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="27"/>
-      <x:c r="B12" s="11"/>
+      <x:c r="A12" s="29" t="str">
+        <x:v>Source snapshot hash</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>9c5acba63181f1d3d714c4d0090380ab656767ee3836b4056dfe3873dadc67e0</x:v>
+      </x:c>
       <x:c r="C12" s="11"/>
       <x:c r="D12" s="11"/>
       <x:c r="E12" s="11"/>
@@ -588,31 +592,31 @@
       <x:c r="H12" s="28"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="30" t="str">
+      <x:c r="A13" s="27"/>
+      <x:c r="B13" s="11"/>
+      <x:c r="C13" s="11"/>
+      <x:c r="D13" s="11"/>
+      <x:c r="E13" s="11"/>
+      <x:c r="F13" s="11"/>
+      <x:c r="G13" s="11"/>
+      <x:c r="H13" s="28"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="30" t="str">
         <x:v>Interpretation</x:v>
       </x:c>
-      <x:c r="B13" s="14"/>
-      <x:c r="C13" s="14"/>
-      <x:c r="D13" s="14"/>
-      <x:c r="E13" s="14"/>
-      <x:c r="F13" s="14"/>
-      <x:c r="G13" s="14"/>
-      <x:c r="H13" s="31"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="32" t="str">
-        <x:v>This workbook is a local review artifact. Every completed row was evaluated from its full How to Fix text. A product is approved only for the exact verified scope; diagnosis, recall, coverage, software, and ambiguous-fitment issues use service/official destinations. DTCs did not create scanner links.</x:v>
-      </x:c>
-      <x:c r="B14" s="15"/>
-      <x:c r="C14" s="15"/>
-      <x:c r="D14" s="15"/>
-      <x:c r="E14" s="15"/>
-      <x:c r="F14" s="15"/>
-      <x:c r="G14" s="15"/>
-      <x:c r="H14" s="33"/>
+      <x:c r="B14" s="14"/>
+      <x:c r="C14" s="14"/>
+      <x:c r="D14" s="14"/>
+      <x:c r="E14" s="14"/>
+      <x:c r="F14" s="14"/>
+      <x:c r="G14" s="14"/>
+      <x:c r="H14" s="31"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="32"/>
+      <x:c r="A15" s="32" t="str">
+        <x:v>This workbook is a local review artifact. Every completed row with source instructions was evaluated from its full How to Fix text; blank source instructions are explicitly flagged and receive no inferred link. A product is approved only for the exact verified scope; diagnosis, recall, coverage, software, and ambiguous-fitment issues use service/official destinations. DTCs did not create scanner links.</x:v>
+      </x:c>
       <x:c r="B15" s="15"/>
       <x:c r="C15" s="15"/>
       <x:c r="D15" s="15"/>
@@ -632,20 +636,30 @@
       <x:c r="H16" s="33"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="34"/>
-      <x:c r="B17" s="35"/>
-      <x:c r="C17" s="35"/>
-      <x:c r="D17" s="35"/>
-      <x:c r="E17" s="35"/>
-      <x:c r="F17" s="35"/>
-      <x:c r="G17" s="35"/>
-      <x:c r="H17" s="36"/>
+      <x:c r="A17" s="32"/>
+      <x:c r="B17" s="15"/>
+      <x:c r="C17" s="15"/>
+      <x:c r="D17" s="15"/>
+      <x:c r="E17" s="15"/>
+      <x:c r="F17" s="15"/>
+      <x:c r="G17" s="15"/>
+      <x:c r="H17" s="33"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="34"/>
+      <x:c r="B18" s="35"/>
+      <x:c r="C18" s="35"/>
+      <x:c r="D18" s="35"/>
+      <x:c r="E18" s="35"/>
+      <x:c r="F18" s="35"/>
+      <x:c r="G18" s="35"/>
+      <x:c r="H18" s="36"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A13:H13"/>
-    <x:mergeCell ref="A14:H17"/>
+    <x:mergeCell ref="A14:H14"/>
+    <x:mergeCell ref="A15:H18"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6088,28 +6102,1340 @@
       <x:c r="N148" s="41" t="str"/>
     </x:row>
     <x:row r="149" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A149" s="42" t="str"/>
-      <x:c r="B149" s="43" t="str"/>
-      <x:c r="C149" s="43" t="str"/>
-      <x:c r="D149" s="43" t="str"/>
-      <x:c r="E149" s="43" t="str"/>
-      <x:c r="F149" s="43" t="str"/>
-      <x:c r="G149" s="43" t="str"/>
-      <x:c r="H149" s="43" t="str">
+      <x:c r="A149" s="40" t="str"/>
+      <x:c r="B149" s="9" t="str"/>
+      <x:c r="C149" s="9" t="str"/>
+      <x:c r="D149" s="9" t="str"/>
+      <x:c r="E149" s="9" t="str"/>
+      <x:c r="F149" s="9" t="str"/>
+      <x:c r="G149" s="9" t="str"/>
+      <x:c r="H149" s="9" t="str">
         <x:v>BMW dealer locator</x:v>
       </x:c>
-      <x:c r="I149" s="43" t="str">
+      <x:c r="I149" s="9" t="str">
         <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
       </x:c>
-      <x:c r="J149" s="43" t="str">
+      <x:c r="J149" s="9" t="str">
         <x:v>REx fuel/ignition diagnosis and injector service</x:v>
       </x:c>
-      <x:c r="K149" s="43" t="str">
+      <x:c r="K149" s="9" t="str">
         <x:v>diagnostic service</x:v>
       </x:c>
-      <x:c r="L149" s="43" t="str"/>
-      <x:c r="M149" s="43" t="str"/>
-      <x:c r="N149" s="44" t="str"/>
+      <x:c r="L149" s="9" t="str"/>
+      <x:c r="M149" s="9" t="str"/>
+      <x:c r="N149" s="41" t="str"/>
+    </x:row>
+    <x:row r="150" ht="462" hidden="0" customHeight="1">
+      <x:c r="A150" s="40" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B150" s="9" t="str">
+        <x:v>bmw-i4-12v-battery-drain-2022</x:v>
+      </x:c>
+      <x:c r="C150" s="9" t="str">
+        <x:v>2022-2026 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D150" s="9" t="str">
+        <x:v>12V Auxiliary Battery Drain</x:v>
+      </x:c>
+      <x:c r="E150" s="9" t="str">
+        <x:v>Ensure the latest software version is installed (BMW has released multiple OTA updates addressing sleep mode behavior). If the problem persists, have the dealer check for parasitic draw using ISTA diagnostics. In severe cases, the 12V battery may need replacement and proper registration.</x:v>
+      </x:c>
+      <x:c r="F150" s="9" t="str">
+        <x:v>Latest vehicle software; ISTA energy/parasitic-draw diagnosis; battery test; VIN-specific 12V battery and registration only if failed</x:v>
+      </x:c>
+      <x:c r="G150" s="9" t="str">
+        <x:v>SOFTWARE/DIAGNOSIS FIRST / NO UNIVERSAL BATTERY</x:v>
+      </x:c>
+      <x:c r="H150" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I150" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J150" s="9" t="str">
+        <x:v>2022-2026 i4 software, energy diagnosis, battery test and registration</x:v>
+      </x:c>
+      <x:c r="K150" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L150" s="9" t="str"/>
+      <x:c r="M150" s="9" t="str">
+        <x:v>The row does not identify battery chemistry, capacity, production split or part number, and software/parasitic draw must be checked before replacement.</x:v>
+      </x:c>
+      <x:c r="N150" s="41" t="str">
+        <x:v>Add trim, production date and VIN-specific battery specification before a product link; do not imply every auxiliary-battery warning is battery failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="937.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A151" s="40" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B151" s="9" t="str">
+        <x:v>bmw-i4-12v-battery-sleep-mode-2022</x:v>
+      </x:c>
+      <x:c r="C151" s="9" t="str">
+        <x:v>2022-2025 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D151" s="9" t="str">
+        <x:v>12V Battery Drain - Sleep Mode Failure</x:v>
+      </x:c>
+      <x:c r="E151" s="9" t="str">
+        <x:v>First check for latest software update - BMW has released updates to fix sleep mode bugs. If 12V battery has been deeply discharged, it may need replacement (60Ah AGM). Must register new battery using BimmerLink app (not BimmerCode - BimmerCode cannot register batteries). For vehicles that sit for extended periods, use a BMW-approved battery tender. If CCU is causing the issue, dealer diagnosis and CCU replacement under warranty. The DC-DC converter should maintain 12V charge from the HV battery, so persistent drain indicates a software or CCU hardware fault.</x:v>
+      </x:c>
+      <x:c r="F151" s="9" t="str">
+        <x:v>Software/CCU and parasitic-draw diagnosis; load-test exact 12V battery; VIN-specific replacement and supported registration procedure only if failed</x:v>
+      </x:c>
+      <x:c r="G151" s="9" t="str">
+        <x:v>SOFTWARE/DIAGNOSIS FIRST / BATTERY SPEC UNVERIFIED</x:v>
+      </x:c>
+      <x:c r="H151" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I151" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J151" s="9" t="str">
+        <x:v>2022-2025 i4 CCU/sleep diagnosis, battery specification and registration</x:v>
+      </x:c>
+      <x:c r="K151" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L151" s="9" t="str">
+        <x:v>https://bmwtechinfo.bmwgroup.com/sib_attachments/B611523.pdf</x:v>
+      </x:c>
+      <x:c r="M151" s="9" t="str">
+        <x:v>BMW service information says to identify whether the installed 12V battery is lithium or lead before charging; the row's blanket 60Ah AGM claim is not VIN-verified.</x:v>
+      </x:c>
+      <x:c r="N151" s="41" t="str">
+        <x:v>Remove the universal 60Ah AGM and charger claims. Verify whether the exact vehicle uses Li or Pb/AGM and verify the supported registration tool before linking products.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="937.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A152" s="40" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B152" s="9" t="str">
+        <x:v>bmw-i4-brake-feel-regen-2022</x:v>
+      </x:c>
+      <x:c r="C152" s="9" t="str">
+        <x:v>2022-2025 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D152" s="9" t="str">
+        <x:v>Regenerative Braking Pedal Feel Complaints - Grabby/Aggressive</x:v>
+      </x:c>
+      <x:c r="E152" s="9" t="str">
+        <x:v>This is a design characteristic of the blended braking system, not a defect per se. Adaptive approaches: Use "D" mode with Adaptive recuperation setting for the most natural brake feel - it adjusts regen based on traffic and road conditions. Avoid "B" mode unless you specifically want strong one-pedal driving. Practice feathering the brake pedal with very light, progressive pressure. Some owners report the brake feel improves slightly with software updates. If braking is truly abnormal (pulsating, grinding), have the integrated brake module checked as that could indicate a hardware issue covered under recall.</x:v>
+      </x:c>
+      <x:c r="F152" s="9" t="str">
+        <x:v>Explain selectable recuperation behavior; software check; physical/integrated-brake diagnosis only for abnormal pulsation, grinding, warning or changed pedal effort</x:v>
+      </x:c>
+      <x:c r="G152" s="9" t="str">
+        <x:v>EDUCATION/SOFTWARE FIRST / NO PART</x:v>
+      </x:c>
+      <x:c r="H152" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I152" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J152" s="9" t="str">
+        <x:v>2022-2025 i4 abnormal blended-brake or integrated-brake diagnosis</x:v>
+      </x:c>
+      <x:c r="K152" s="9" t="str">
+        <x:v>brake diagnostic service</x:v>
+      </x:c>
+      <x:c r="L152" s="9" t="str"/>
+      <x:c r="M152" s="9" t="str">
+        <x:v>The source describes a normal operating characteristic unless objective abnormal symptoms are present; no failed part is identified.</x:v>
+      </x:c>
+      <x:c r="N152" s="41" t="str">
+        <x:v>Do not imply Adaptive recuperation exists on every configuration or mention a recall without a VIN-specific campaign reference.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="594" hidden="0" customHeight="1">
+      <x:c r="A153" s="40" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B153" s="9" t="str">
+        <x:v>bmw-i4-drivetrain-malfunction-2022</x:v>
+      </x:c>
+      <x:c r="C153" s="9" t="str">
+        <x:v>2022-2025 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D153" s="9" t="str">
+        <x:v>2022-2025 i4 Propulsion-Loss Recall 25V-395</x:v>
+      </x:c>
+      <x:c r="E153" s="9" t="str">
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW’s free electric-drive-motor software update through the authorized dealer or the approved over-the-air recall process. Do not buy gear oil, gaskets or drivetrain parts as a substitute. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+      </x:c>
+      <x:c r="F153" s="9" t="str">
+        <x:v>VIN check for 25V-395; authorized/approved OTA electric-drive-motor software remedy; separate diagnosis if warning remains</x:v>
+      </x:c>
+      <x:c r="G153" s="9" t="str">
+        <x:v>RECALL/SOFTWARE ONLY / NO DRIVETRAIN PART</x:v>
+      </x:c>
+      <x:c r="H153" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I153" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J153" s="9" t="str">
+        <x:v>2022-2025 i4; VIN required for 25V-395</x:v>
+      </x:c>
+      <x:c r="K153" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L153" s="9" t="str"/>
+      <x:c r="M153" s="9" t="str">
+        <x:v>The source explicitly rejects gear oil, gaskets and drivetrain parts as substitutes for the software recall.</x:v>
+      </x:c>
+      <x:c r="N153" s="41" t="str">
+        <x:v>Keep this as a VIN-controlled propulsion-loss recall, not a generic drivetrain-malfunction parts page.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A154" s="40" t="str"/>
+      <x:c r="B154" s="9" t="str"/>
+      <x:c r="C154" s="9" t="str"/>
+      <x:c r="D154" s="9" t="str"/>
+      <x:c r="E154" s="9" t="str"/>
+      <x:c r="F154" s="9" t="str"/>
+      <x:c r="G154" s="9" t="str"/>
+      <x:c r="H154" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I154" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J154" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K154" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L154" s="9" t="str"/>
+      <x:c r="M154" s="9" t="str"/>
+      <x:c r="N154" s="41" t="str"/>
+    </x:row>
+    <x:row r="155" ht="818.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A155" s="40" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B155" s="9" t="str">
+        <x:v>bmw-i4-heat-pump-cold-weather-2022</x:v>
+      </x:c>
+      <x:c r="C155" s="9" t="str">
+        <x:v>2022-2024 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D155" s="9" t="str">
+        <x:v>G26 i4 Coolant Changeover-Valve Leak Diagnosis</x:v>
+      </x:c>
+      <x:c r="E155" s="9" t="str">
+        <x:v>Check coolant level, read the exact BMW fault memory and inspect the G26 changeover valve for active or dried leakage. Follow SIB 17 01 24 and VIN-specific AIR/ETK instructions; replace the applicable older-production valve and bleed/test the cooling system with ISTA when the BMW criteria are met. ShowMeTheParts resolves exact 2022 i4 HVAC and water-pump categories but returned no changeover-valve candidate, so the frozen marketplace searches and generic coolant are removed.</x:v>
+      </x:c>
+      <x:c r="F155" s="9" t="str">
+        <x:v>Coolant level/fault memory; inspect G26 coolant changeover valve for active/dried leakage; production/VIN-specific valve and ISTA bleed/test only when bulletin criteria are met</x:v>
+      </x:c>
+      <x:c r="G155" s="9" t="str">
+        <x:v>BULLETIN DIAGNOSIS FIRST / NO CATALOG CANDIDATE</x:v>
+      </x:c>
+      <x:c r="H155" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I155" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J155" s="9" t="str">
+        <x:v>2022-2024 G26 i4 SIB 17 01 24 diagnosis, ETK valve selection and ISTA bleed</x:v>
+      </x:c>
+      <x:c r="K155" s="9" t="str">
+        <x:v>diagnostic/HV cooling service</x:v>
+      </x:c>
+      <x:c r="L155" s="9" t="str"/>
+      <x:c r="M155" s="9" t="str">
+        <x:v>The corrected How to Fix reports no changeover-valve catalog candidate and requires production-specific AIR/ETK instructions.</x:v>
+      </x:c>
+      <x:c r="N155" s="41" t="str">
+        <x:v>Rename this to the coolant changeover-valve leak condition; do not link generic coolant, water pumps or a scanner.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A156" s="40" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B156" s="9" t="str">
+        <x:v>bmw-i4-heat-pump-malfunction-2022</x:v>
+      </x:c>
+      <x:c r="C156" s="9" t="str">
+        <x:v>2022-2026 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D156" s="9" t="str">
+        <x:v>Heat Pump Malfunction in Cold Weather</x:v>
+      </x:c>
+      <x:c r="E156" s="9" t="str">
+        <x:v>BMW has released software updates to improve heat pump operation in cold weather. Visit the dealer for the latest calibration. Some cases require heat pump valve replacement. Pre-conditioning the cabin while plugged in reduces the impact on driving range.</x:v>
+      </x:c>
+      <x:c r="F156" s="9" t="str">
+        <x:v>Latest calibration; exact HVAC fault diagnosis; heat-pump valve only when fault and VIN/ETK part are confirmed</x:v>
+      </x:c>
+      <x:c r="G156" s="9" t="str">
+        <x:v>SOFTWARE/DIAGNOSIS FIRST / NO UNIVERSAL VALVE</x:v>
+      </x:c>
+      <x:c r="H156" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I156" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J156" s="9" t="str">
+        <x:v>2022-2026 i4 HVAC software and heat-pump diagnosis</x:v>
+      </x:c>
+      <x:c r="K156" s="9" t="str">
+        <x:v>HV HVAC service</x:v>
+      </x:c>
+      <x:c r="L156" s="9" t="str"/>
+      <x:c r="M156" s="9" t="str">
+        <x:v>The row combines software and unspecified valve faults without part number, production split or confirmed symptom.</x:v>
+      </x:c>
+      <x:c r="N156" s="41" t="str">
+        <x:v>Split software-only cold-weather behavior from a diagnosed leaking/failed valve before adding a product link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="976.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A157" s="40" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B157" s="9" t="str">
+        <x:v>bmw-i4-idrive8-software-bugs-2022</x:v>
+      </x:c>
+      <x:c r="C157" s="9" t="str">
+        <x:v>2022-2025 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D157" s="9" t="str">
+        <x:v>iDrive 8 Software Bugs - Screen Crashes, Reboots &amp; Freezing</x:v>
+      </x:c>
+      <x:c r="E157" s="9" t="str">
+        <x:v>Ensure vehicle has latest iDrive software via OTA update (Settings &gt; Software Update). Version .63 and later resolved many screen blank/reboot issues. For persistent crashes: Perform soft reset by holding volume knob/power button for 10+ seconds. For factory reset, use Settings &gt; General &gt; Reset to restore defaults. If issues persist after latest OTA, dealer can force-flash the head unit via ISTA. Some owners report that disconnecting phone from wireless CarPlay/Android Auto and using wired connection improves stability. BMW has released multiple major software updates addressing these issues.</x:v>
+      </x:c>
+      <x:c r="F157" s="9" t="str">
+        <x:v>Current Remote Software Upgrade; supported soft/factory reset; ISTA programming only for persistent faults; hardware only after diagnosis</x:v>
+      </x:c>
+      <x:c r="G157" s="9" t="str">
+        <x:v>SOFTWARE/SUPPORT LINKS ONLY</x:v>
+      </x:c>
+      <x:c r="H157" s="9" t="str">
+        <x:v>My BMW Garage</x:v>
+      </x:c>
+      <x:c r="I157" s="9" t="str">
+        <x:v>https://mygarage.bmwusa.com/</x:v>
+      </x:c>
+      <x:c r="J157" s="9" t="str">
+        <x:v>VIN-linked software and vehicle information</x:v>
+      </x:c>
+      <x:c r="K157" s="9" t="str">
+        <x:v>official software route</x:v>
+      </x:c>
+      <x:c r="L157" s="9" t="str"/>
+      <x:c r="M157" s="9" t="str">
+        <x:v>The fix is software/reset driven and does not identify a failed head unit or retail part.</x:v>
+      </x:c>
+      <x:c r="N157" s="41" t="str">
+        <x:v>Remove hard-coded '.63 and later' unless tied to the exact BMW software train; avoid unverified phone-workaround guarantees.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A158" s="40" t="str"/>
+      <x:c r="B158" s="9" t="str"/>
+      <x:c r="C158" s="9" t="str"/>
+      <x:c r="D158" s="9" t="str"/>
+      <x:c r="E158" s="9" t="str"/>
+      <x:c r="F158" s="9" t="str"/>
+      <x:c r="G158" s="9" t="str"/>
+      <x:c r="H158" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I158" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J158" s="9" t="str">
+        <x:v>Persistent iDrive 8 crash diagnosis and ISTA programming</x:v>
+      </x:c>
+      <x:c r="K158" s="9" t="str">
+        <x:v>programming service</x:v>
+      </x:c>
+      <x:c r="L158" s="9" t="str"/>
+      <x:c r="M158" s="9" t="str"/>
+      <x:c r="N158" s="41" t="str"/>
+    </x:row>
+    <x:row r="159" ht="435.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A159" s="40" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B159" s="9" t="str">
+        <x:v>bmw-i4-infotainment-glitches-2022</x:v>
+      </x:c>
+      <x:c r="C159" s="9" t="str">
+        <x:v>2022-2026 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D159" s="9" t="str">
+        <x:v>iDrive 8 Software and Infotainment Glitches</x:v>
+      </x:c>
+      <x:c r="E159" s="9" t="str">
+        <x:v>Keep software up to date via OTA updates or dealer visit. For persistent issues, a full iDrive system reset (Settings &gt; General &gt; Reset) can resolve cached data problems. Some owners have needed the head unit replaced under warranty for hardware-level display faults.</x:v>
+      </x:c>
+      <x:c r="F159" s="9" t="str">
+        <x:v>OTA/dealer software update; supported iDrive reset; head-unit diagnosis and warranty replacement only for confirmed hardware fault</x:v>
+      </x:c>
+      <x:c r="G159" s="9" t="str">
+        <x:v>SOFTWARE/WARRANTY FIRST / NO RETAIL HEAD UNIT</x:v>
+      </x:c>
+      <x:c r="H159" s="9" t="str">
+        <x:v>My BMW Garage</x:v>
+      </x:c>
+      <x:c r="I159" s="9" t="str">
+        <x:v>https://mygarage.bmwusa.com/</x:v>
+      </x:c>
+      <x:c r="J159" s="9" t="str">
+        <x:v>VIN-linked software information</x:v>
+      </x:c>
+      <x:c r="K159" s="9" t="str">
+        <x:v>official software route</x:v>
+      </x:c>
+      <x:c r="L159" s="9" t="str"/>
+      <x:c r="M159" s="9" t="str">
+        <x:v>The row supplies no head-unit generation or part number and says hardware replacement is only for confirmed display faults.</x:v>
+      </x:c>
+      <x:c r="N159" s="41" t="str">
+        <x:v>Combine or distinguish this row from the adjacent iDrive 8 software-bugs issue to avoid duplicate generic content.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A160" s="40" t="str"/>
+      <x:c r="B160" s="9" t="str"/>
+      <x:c r="C160" s="9" t="str"/>
+      <x:c r="D160" s="9" t="str"/>
+      <x:c r="E160" s="9" t="str"/>
+      <x:c r="F160" s="9" t="str"/>
+      <x:c r="G160" s="9" t="str"/>
+      <x:c r="H160" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I160" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J160" s="9" t="str">
+        <x:v>Persistent infotainment diagnosis, programming and warranty review</x:v>
+      </x:c>
+      <x:c r="K160" s="9" t="str">
+        <x:v>diagnostic/programming service</x:v>
+      </x:c>
+      <x:c r="L160" s="9" t="str"/>
+      <x:c r="M160" s="9" t="str"/>
+      <x:c r="N160" s="41" t="str"/>
+    </x:row>
+    <x:row r="161" ht="514.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A161" s="40" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B161" s="9" t="str">
+        <x:v>bmw-i4-pedestrian-sound-2022</x:v>
+      </x:c>
+      <x:c r="C161" s="9" t="str">
+        <x:v>2022-2023 | BMW | i4</x:v>
+      </x:c>
+      <x:c r="D161" s="9" t="str">
+        <x:v>2022-2023 i4 eDrive40 Sound-Generator Recall 23V-026</x:v>
+      </x:c>
+      <x:c r="E161" s="9" t="str">
+        <x:v>Check the VIN for an open 23V-026 campaign. If included, arrange the free BMW programming remedy for the Receiver Audio Module/external artificial sound generator. Do not replace a speaker or module based only on a missing sound; if the VIN is outside the campaign, diagnose the exact warning and faults separately.</x:v>
+      </x:c>
+      <x:c r="F161" s="9" t="str">
+        <x:v>VIN check for 23V-026; authorized programming of Receiver Audio Module/external sound generator; separate diagnosis outside recall</x:v>
+      </x:c>
+      <x:c r="G161" s="9" t="str">
+        <x:v>RECALL/PROGRAMMING ONLY / NO SPEAKER PART</x:v>
+      </x:c>
+      <x:c r="H161" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I161" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J161" s="9" t="str">
+        <x:v>2022-2023 i4 eDrive40; VIN required for 23V-026</x:v>
+      </x:c>
+      <x:c r="K161" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L161" s="9" t="str"/>
+      <x:c r="M161" s="9" t="str">
+        <x:v>The free programming remedy controls and the source explicitly says not to replace a speaker or module based only on missing sound.</x:v>
+      </x:c>
+      <x:c r="N161" s="41" t="str">
+        <x:v>Keep eDrive40/VIN scope visible and separate non-recall faults.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A162" s="40" t="str"/>
+      <x:c r="B162" s="9" t="str"/>
+      <x:c r="C162" s="9" t="str"/>
+      <x:c r="D162" s="9" t="str"/>
+      <x:c r="E162" s="9" t="str"/>
+      <x:c r="F162" s="9" t="str"/>
+      <x:c r="G162" s="9" t="str"/>
+      <x:c r="H162" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I162" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J162" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K162" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L162" s="9" t="str"/>
+      <x:c r="M162" s="9" t="str"/>
+      <x:c r="N162" s="41" t="str"/>
+    </x:row>
+    <x:row r="163" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A163" s="40" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B163" s="9" t="str">
+        <x:v>bmw-i5-12v-battery-drain-2024</x:v>
+      </x:c>
+      <x:c r="C163" s="9" t="str">
+        <x:v>2024-2025 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D163" s="9" t="str">
+        <x:v>12V Auxiliary Battery Drain and Dead Car Syndrome</x:v>
+      </x:c>
+      <x:c r="E163" s="9" t="str">
+        <x:v>Keep the i5 plugged in when parked for extended periods — the HV charger trickle-charges the 12V battery. Install a BMW-recommended battery maintainer connected to the 12V battery (accessible in the right side of the trunk). Update iDrive software to the latest version — BMW has released OTA updates that improve sleep-mode power management. If the 12V battery dies, the manual release cable under the hood allows emergency access.</x:v>
+      </x:c>
+      <x:c r="F163" s="9" t="str">
+        <x:v>Software and energy/parasitic-draw diagnosis; exact battery chemistry/capacity test; approved maintainer only after BMW connection/chemistry confirmation</x:v>
+      </x:c>
+      <x:c r="G163" s="9" t="str">
+        <x:v>SOFTWARE/DIAGNOSIS FIRST / MAINTAINER HELD</x:v>
+      </x:c>
+      <x:c r="H163" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I163" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J163" s="9" t="str">
+        <x:v>2024-2025 i5 energy diagnosis, exact 12V battery specification and safe charging guidance</x:v>
+      </x:c>
+      <x:c r="K163" s="9" t="str">
+        <x:v>diagnostic service</x:v>
+      </x:c>
+      <x:c r="L163" s="9" t="str">
+        <x:v>https://bmwtechinfo.bmwgroup.com/sib_attachments/B611523.pdf</x:v>
+      </x:c>
+      <x:c r="M163" s="9" t="str">
+        <x:v>The current BMW charger part found in US retail was discontinued/unavailable, and the row does not identify whether the installed 12V battery is Li or Pb/AGM.</x:v>
+      </x:c>
+      <x:c r="N163" s="41" t="str">
+        <x:v>Do not assert that plugging in always trickle-charges the 12V battery or direct charger connection without the i5 procedure and battery chemistry.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="501.6000061035156" hidden="0" customHeight="1">
+      <x:c r="A164" s="40" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B164" s="9" t="str">
+        <x:v>bmw-i5-acoustic-pedestrian-warning-sound-generator-fault</x:v>
+      </x:c>
+      <x:c r="C164" s="9" t="str">
+        <x:v>2024-2024 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D164" s="9" t="str">
+        <x:v>2024 i5 Pedestrian Sound Recall 23V-885</x:v>
+      </x:c>
+      <x:c r="E164" s="9" t="str">
+        <x:v>Check the VIN for an open 23V-885 campaign. If included, arrange BMW's free software programming remedy through the authorized dealer or the approved recall over-the-air process. Do not replace a speaker or module based only on a missing sound; diagnose vehicles outside the campaign separately.</x:v>
+      </x:c>
+      <x:c r="F164" s="9" t="str">
+        <x:v>VIN check for 23V-885; authorized dealer or approved OTA programming remedy; separate diagnosis outside campaign</x:v>
+      </x:c>
+      <x:c r="G164" s="9" t="str">
+        <x:v>RECALL/PROGRAMMING ONLY / NO SPEAKER PART</x:v>
+      </x:c>
+      <x:c r="H164" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I164" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J164" s="9" t="str">
+        <x:v>2024 i5; VIN required for 23V-885</x:v>
+      </x:c>
+      <x:c r="K164" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L164" s="9" t="str"/>
+      <x:c r="M164" s="9" t="str">
+        <x:v>The recall remedy is programming and the source explicitly rejects replacing a speaker or module from the symptom alone.</x:v>
+      </x:c>
+      <x:c r="N164" s="41" t="str">
+        <x:v>Keep non-recall missing-sound diagnosis separate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A165" s="40" t="str"/>
+      <x:c r="B165" s="9" t="str"/>
+      <x:c r="C165" s="9" t="str"/>
+      <x:c r="D165" s="9" t="str"/>
+      <x:c r="E165" s="9" t="str"/>
+      <x:c r="F165" s="9" t="str"/>
+      <x:c r="G165" s="9" t="str"/>
+      <x:c r="H165" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I165" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J165" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K165" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L165" s="9" t="str"/>
+      <x:c r="M165" s="9" t="str"/>
+      <x:c r="N165" s="41" t="str"/>
+    </x:row>
+    <x:row r="166" ht="356.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A166" s="40" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B166" s="9" t="str">
+        <x:v>bmw-i5-adaptive-suspension-calibration-2024</x:v>
+      </x:c>
+      <x:c r="C166" s="9" t="str">
+        <x:v>2024-2026 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D166" s="9" t="str">
+        <x:v>Adaptive Suspension Self-Leveling Calibration Errors</x:v>
+      </x:c>
+      <x:c r="E166" s="9" t="str">
+        <x:v>Perform a suspension calibration reset using BMW ISTA diagnostic software. If the issue persists, inspect the ride height sensors at each corner for damage or loose connectors. A dealer software update may also resolve the issue.</x:v>
+      </x:c>
+      <x:c r="F166" s="9" t="str">
+        <x:v>ISTA calibration; inspect each ride-height sensor/connector; software update; exact sensor only after corner and part-number diagnosis</x:v>
+      </x:c>
+      <x:c r="G166" s="9" t="str">
+        <x:v>CALIBRATION/DIAGNOSIS FIRST / NO SENSOR LINK</x:v>
+      </x:c>
+      <x:c r="H166" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I166" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J166" s="9" t="str">
+        <x:v>2024-2026 i5 suspension calibration, sensor inspection and software</x:v>
+      </x:c>
+      <x:c r="K166" s="9" t="str">
+        <x:v>calibration service</x:v>
+      </x:c>
+      <x:c r="L166" s="9" t="str"/>
+      <x:c r="M166" s="9" t="str">
+        <x:v>The row provides no trim, suspension option, corner, sensor part number or confirmed physical failure.</x:v>
+      </x:c>
+      <x:c r="N166" s="41" t="str">
+        <x:v>Split software/calibration error from a damaged ride-height sensor and identify axle/side before adding parts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A167" s="40" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B167" s="9" t="str">
+        <x:v>bmw-i5-c-wiring-harness-damaged-during-cabin-filter-service</x:v>
+      </x:c>
+      <x:c r="C167" s="9" t="str">
+        <x:v>2024-2026 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D167" s="9" t="str">
+        <x:v>2024-2026 i5 A/C Harness Recall 26V-096</x:v>
+      </x:c>
+      <x:c r="E167" s="9" t="str">
+        <x:v>Check the VIN for an open 26V-096 campaign. If included, have an authorized BMW dealer inspect the air-conditioning wiring harness and repair or replace it as required at no charge. Do not probe, splice or order harness parts from this card. If smoke, burning odor or an electrical warning appears, stop using the vehicle and follow BMW emergency guidance.</x:v>
+      </x:c>
+      <x:c r="F167" s="9" t="str">
+        <x:v>VIN check for 26V-096; dealer inspection and repair/replacement of A/C harness; emergency response for smoke/burning odor</x:v>
+      </x:c>
+      <x:c r="G167" s="9" t="str">
+        <x:v>RECALL ONLY / NO HARNESS PART</x:v>
+      </x:c>
+      <x:c r="H167" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I167" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J167" s="9" t="str">
+        <x:v>2024-2026 i5; VIN required for 26V-096</x:v>
+      </x:c>
+      <x:c r="K167" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L167" s="9" t="str"/>
+      <x:c r="M167" s="9" t="str">
+        <x:v>This is a current VIN-controlled safety recall and the source prohibits probing, splicing or ordering harness parts from the card.</x:v>
+      </x:c>
+      <x:c r="N167" s="41" t="str">
+        <x:v>Keep the recall number and emergency guidance prominent.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A168" s="40" t="str"/>
+      <x:c r="B168" s="9" t="str"/>
+      <x:c r="C168" s="9" t="str"/>
+      <x:c r="D168" s="9" t="str"/>
+      <x:c r="E168" s="9" t="str"/>
+      <x:c r="F168" s="9" t="str"/>
+      <x:c r="G168" s="9" t="str"/>
+      <x:c r="H168" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I168" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J168" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K168" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L168" s="9" t="str"/>
+      <x:c r="M168" s="9" t="str"/>
+      <x:c r="N168" s="41" t="str"/>
+    </x:row>
+    <x:row r="169" ht="712.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A169" s="40" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B169" s="9" t="str">
+        <x:v>bmw-i5-dc-fast-charge-throttling-loud-cooling-fans-repeated-session</x:v>
+      </x:c>
+      <x:c r="C169" s="9" t="str">
+        <x:v>2024-2025 | BMW | i5 | eDrive40, xDrive40, M60 xDrive</x:v>
+      </x:c>
+      <x:c r="D169" s="9" t="str">
+        <x:v>DC Fast-Charge Throttling and Loud Cooling Fans on Repeated Sessions</x:v>
+      </x:c>
+      <x:c r="E169" s="9" t="str">
+        <x:v>Keep the i5 on the latest software, since BMW has released charging-curve/charging-management updates via OTA and dealer flashes. Precondition the battery before fast charging to reduce throttling, avoid back-to-back DC sessions when possible, and report persistent amp drops or skipped scheduled charges to the dealer (some cases were traced to software faults). Loud thermal-management fan noise is generally normal during/after DC charging.</x:v>
+      </x:c>
+      <x:c r="F169" s="9" t="str">
+        <x:v>Latest charging-management software; battery preconditioning; charging-session observation; dealer diagnosis for persistent abnormal power drops or schedule failures</x:v>
+      </x:c>
+      <x:c r="G169" s="9" t="str">
+        <x:v>SOFTWARE/OPERATING GUIDANCE / NO PART</x:v>
+      </x:c>
+      <x:c r="H169" s="9" t="str">
+        <x:v>My BMW Garage</x:v>
+      </x:c>
+      <x:c r="I169" s="9" t="str">
+        <x:v>https://mygarage.bmwusa.com/</x:v>
+      </x:c>
+      <x:c r="J169" s="9" t="str">
+        <x:v>VIN-linked software information</x:v>
+      </x:c>
+      <x:c r="K169" s="9" t="str">
+        <x:v>official software route</x:v>
+      </x:c>
+      <x:c r="L169" s="9" t="str"/>
+      <x:c r="M169" s="9" t="str">
+        <x:v>Loud fan operation can be normal thermal management and the source identifies software/usage rather than a failed cooling component.</x:v>
+      </x:c>
+      <x:c r="N169" s="41" t="str">
+        <x:v>Do not present normal repeated-session throttling as a part failure; document charger, ambient temperature, state of charge and preconditioning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A170" s="40" t="str"/>
+      <x:c r="B170" s="9" t="str"/>
+      <x:c r="C170" s="9" t="str"/>
+      <x:c r="D170" s="9" t="str"/>
+      <x:c r="E170" s="9" t="str"/>
+      <x:c r="F170" s="9" t="str"/>
+      <x:c r="G170" s="9" t="str"/>
+      <x:c r="H170" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I170" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J170" s="9" t="str">
+        <x:v>Persistent i5 charging-management diagnosis</x:v>
+      </x:c>
+      <x:c r="K170" s="9" t="str">
+        <x:v>EV diagnostic service</x:v>
+      </x:c>
+      <x:c r="L170" s="9" t="str"/>
+      <x:c r="M170" s="9" t="str"/>
+      <x:c r="N170" s="41" t="str"/>
+    </x:row>
+    <x:row r="171" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A171" s="40" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B171" s="9" t="str">
+        <x:v>bmw-i5-electric-drive-motor-software-false-isolation-fault-causing</x:v>
+      </x:c>
+      <x:c r="C171" s="9" t="str">
+        <x:v>2024-2024 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D171" s="9" t="str">
+        <x:v>2024 i5 Propulsion-Loss Recall 25V-395</x:v>
+      </x:c>
+      <x:c r="E171" s="9" t="str">
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or the approved recall over-the-air process. Do not order drivetrain or battery parts from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the remedy.</x:v>
+      </x:c>
+      <x:c r="F171" s="9" t="str">
+        <x:v>VIN check for 25V-395; authorized/approved OTA electric-drive-motor software remedy; separate diagnosis if fault persists</x:v>
+      </x:c>
+      <x:c r="G171" s="9" t="str">
+        <x:v>RECALL/SOFTWARE ONLY / NO DRIVETRAIN PART</x:v>
+      </x:c>
+      <x:c r="H171" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I171" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J171" s="9" t="str">
+        <x:v>2024 i5; VIN required for 25V-395</x:v>
+      </x:c>
+      <x:c r="K171" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L171" s="9" t="str"/>
+      <x:c r="M171" s="9" t="str">
+        <x:v>The source explicitly rejects drivetrain and battery parts as substitutes for the software recall.</x:v>
+      </x:c>
+      <x:c r="N171" s="41" t="str">
+        <x:v>Keep this VIN-controlled and avoid claiming every isolation fault is the recall condition.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A172" s="40" t="str"/>
+      <x:c r="B172" s="9" t="str"/>
+      <x:c r="C172" s="9" t="str"/>
+      <x:c r="D172" s="9" t="str"/>
+      <x:c r="E172" s="9" t="str"/>
+      <x:c r="F172" s="9" t="str"/>
+      <x:c r="G172" s="9" t="str"/>
+      <x:c r="H172" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I172" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J172" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K172" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L172" s="9" t="str"/>
+      <x:c r="M172" s="9" t="str"/>
+      <x:c r="N172" s="41" t="str"/>
+    </x:row>
+    <x:row r="173" ht="699.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A173" s="40" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B173" s="9" t="str">
+        <x:v>bmw-i5-heat-pump-drip-tube-thunking-clunking-noise</x:v>
+      </x:c>
+      <x:c r="C173" s="9" t="str">
+        <x:v>2024-2024 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D173" s="9" t="str">
+        <x:v>Early-Production G60 i5 Condensation-Drain Drum Noise</x:v>
+      </x:c>
+      <x:c r="E173" s="9" t="str">
+        <x:v>Confirm the production date and reproduce the rhythmic noise under the BMW bulletin conditions. If SIB 64 01 24 applies, an authorized high-voltage-qualified repair facility replaces the condensation-water drain with the optimized part; the procedure requires high-voltage battery removal. Do not cut or modify the drain. ShowMeTheParts resolved the exact 2024 i5 but returned no matching HVAC candidate, so no parts link is approved.</x:v>
+      </x:c>
+      <x:c r="F173" s="9" t="str">
+        <x:v>Production-date and bulletin-condition verification; optimized condensation drain installed by HV-qualified facility with HV battery removal</x:v>
+      </x:c>
+      <x:c r="G173" s="9" t="str">
+        <x:v>HV BULLETIN SERVICE / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H173" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I173" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J173" s="9" t="str">
+        <x:v>Early-production 2024 G60 i5 SIB 64 01 24 diagnosis and HV-qualified drain replacement</x:v>
+      </x:c>
+      <x:c r="K173" s="9" t="str">
+        <x:v>HV HVAC service</x:v>
+      </x:c>
+      <x:c r="L173" s="9" t="str"/>
+      <x:c r="M173" s="9" t="str">
+        <x:v>The source found no matching catalog HVAC candidate and the repair requires HV battery removal.</x:v>
+      </x:c>
+      <x:c r="N173" s="41" t="str">
+        <x:v>Do not cut or modify the drain and do not link generic tubing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A174" s="40" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B174" s="9" t="str">
+        <x:v>bmw-i5-high-voltage-battery-module-insufficient-weld-seams</x:v>
+      </x:c>
+      <x:c r="C174" s="9" t="str">
+        <x:v>2024-2024 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D174" s="9" t="str">
+        <x:v>Single-Vehicle 2024 i5 Battery-Weld Recall 24V-135</x:v>
+      </x:c>
+      <x:c r="E174" s="9" t="str">
+        <x:v>Check the VIN for an open 24V-135 campaign. If included, follow BMW's instructions and have the affected high-voltage battery module replaced at no charge by an authorized high-voltage-qualified dealer. Do not open the battery pack or order modules independently; vehicles outside the campaign require separate fault-led diagnosis.</x:v>
+      </x:c>
+      <x:c r="F174" s="9" t="str">
+        <x:v>VIN check for 24V-135; dealer replacement of affected HV battery module</x:v>
+      </x:c>
+      <x:c r="G174" s="9" t="str">
+        <x:v>HIGH-VOLTAGE RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H174" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I174" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J174" s="9" t="str">
+        <x:v>Single affected 2024 i5; VIN required for 24V-135</x:v>
+      </x:c>
+      <x:c r="K174" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L174" s="9" t="str"/>
+      <x:c r="M174" s="9" t="str">
+        <x:v>This single-vehicle high-voltage recall cannot support any retail battery-module link.</x:v>
+      </x:c>
+      <x:c r="N174" s="41" t="str">
+        <x:v>Keep the exceptionally narrow VIN scope visible.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A175" s="40" t="str"/>
+      <x:c r="B175" s="9" t="str"/>
+      <x:c r="C175" s="9" t="str"/>
+      <x:c r="D175" s="9" t="str"/>
+      <x:c r="E175" s="9" t="str"/>
+      <x:c r="F175" s="9" t="str"/>
+      <x:c r="G175" s="9" t="str"/>
+      <x:c r="H175" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I175" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J175" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K175" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L175" s="9" t="str"/>
+      <x:c r="M175" s="9" t="str"/>
+      <x:c r="N175" s="41" t="str"/>
+    </x:row>
+    <x:row r="176" ht="528" hidden="0" customHeight="1">
+      <x:c r="A176" s="40" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B176" s="9" t="str">
+        <x:v>bmw-i5-integrated-brake-system-servomotor-weld-failure</x:v>
+      </x:c>
+      <x:c r="C176" s="9" t="str">
+        <x:v>2024-2025 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D176" s="9" t="str">
+        <x:v>2024-2025 i5 Integrated-Brake Recall 24V-697</x:v>
+      </x:c>
+      <x:c r="E176" s="9" t="str">
+        <x:v>Check the VIN for an open 24V-697 campaign. If included, have an authorized BMW dealer replace the integrated brake system at no charge. Do not buy pads, rotors, fluid or a generic actuator as a substitute. If a brake warning or changed pedal effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+      </x:c>
+      <x:c r="F176" s="9" t="str">
+        <x:v>VIN check for 24V-697; authorized integrated-brake-system replacement; immediate service for warnings or changed pedal effort</x:v>
+      </x:c>
+      <x:c r="G176" s="9" t="str">
+        <x:v>BRAKE RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H176" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I176" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J176" s="9" t="str">
+        <x:v>2024-2025 i5; VIN required for 24V-697</x:v>
+      </x:c>
+      <x:c r="K176" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L176" s="9" t="str"/>
+      <x:c r="M176" s="9" t="str">
+        <x:v>Pads, rotors, fluid and generic actuators do not substitute for the recall remedy.</x:v>
+      </x:c>
+      <x:c r="N176" s="41" t="str">
+        <x:v>Do not add routine brake products to this safety recall card.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A177" s="40" t="str"/>
+      <x:c r="B177" s="9" t="str"/>
+      <x:c r="C177" s="9" t="str"/>
+      <x:c r="D177" s="9" t="str"/>
+      <x:c r="E177" s="9" t="str"/>
+      <x:c r="F177" s="9" t="str"/>
+      <x:c r="G177" s="9" t="str"/>
+      <x:c r="H177" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I177" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J177" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K177" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L177" s="9" t="str"/>
+      <x:c r="M177" s="9" t="str"/>
+      <x:c r="N177" s="41" t="str"/>
+    </x:row>
+    <x:row r="178" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A178" s="40" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B178" s="9" t="str">
+        <x:v>bmw-i5-regen-braking-inconsistency-2024</x:v>
+      </x:c>
+      <x:c r="C178" s="9" t="str">
+        <x:v>2024-2025 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D178" s="9" t="str">
+        <x:v>Regenerative Braking Inconsistency in Cold Weather</x:v>
+      </x:c>
+      <x:c r="E178" s="9" t="str">
+        <x:v>Use the BMW departure timer to precondition the battery before driving — this warms the battery and restores full regen capability from the start. Set the regen level to "Adaptive" instead of "High" in winter, which provides smoother transitions. BMW software updates have improved regen ramping behavior. Rely more on friction brakes during the first 10-15 minutes of cold-weather driving until the battery warms.</x:v>
+      </x:c>
+      <x:c r="F178" s="9" t="str">
+        <x:v>Battery/cabin preconditioning; selectable recuperation use; software update; friction-brake/regen diagnosis only for objective abnormal behavior</x:v>
+      </x:c>
+      <x:c r="G178" s="9" t="str">
+        <x:v>OPERATING GUIDANCE/SOFTWARE FIRST</x:v>
+      </x:c>
+      <x:c r="H178" s="9" t="str">
+        <x:v>My BMW Garage</x:v>
+      </x:c>
+      <x:c r="I178" s="9" t="str">
+        <x:v>https://mygarage.bmwusa.com/</x:v>
+      </x:c>
+      <x:c r="J178" s="9" t="str">
+        <x:v>VIN-linked software information</x:v>
+      </x:c>
+      <x:c r="K178" s="9" t="str">
+        <x:v>official software route</x:v>
+      </x:c>
+      <x:c r="L178" s="9" t="str"/>
+      <x:c r="M178" s="9" t="str">
+        <x:v>Cold-battery regen limits can be an operating characteristic; no failed part is identified.</x:v>
+      </x:c>
+      <x:c r="N178" s="41" t="str">
+        <x:v>Do not hard-code '10-15 minutes' or specific menu labels across all software versions without owner-manual support.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A179" s="40" t="str"/>
+      <x:c r="B179" s="9" t="str"/>
+      <x:c r="C179" s="9" t="str"/>
+      <x:c r="D179" s="9" t="str"/>
+      <x:c r="E179" s="9" t="str"/>
+      <x:c r="F179" s="9" t="str"/>
+      <x:c r="G179" s="9" t="str"/>
+      <x:c r="H179" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I179" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J179" s="9" t="str">
+        <x:v>Persistent abnormal i5 regen/blended-brake diagnosis</x:v>
+      </x:c>
+      <x:c r="K179" s="9" t="str">
+        <x:v>EV brake diagnostic service</x:v>
+      </x:c>
+      <x:c r="L179" s="9" t="str"/>
+      <x:c r="M179" s="9" t="str"/>
+      <x:c r="N179" s="41" t="str"/>
+    </x:row>
+    <x:row r="180" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A180" s="40" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B180" s="9" t="str">
+        <x:v>bmw-i5-software-glitches-2024</x:v>
+      </x:c>
+      <x:c r="C180" s="9" t="str">
+        <x:v>2024-2026 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D180" s="9" t="str">
+        <x:v>iDrive 8.5 Software Bugs and EV System Errors</x:v>
+      </x:c>
+      <x:c r="E180" s="9" t="str"/>
+      <x:c r="F180" s="9" t="str">
+        <x:v>No repair instructions supplied in source</x:v>
+      </x:c>
+      <x:c r="G180" s="9" t="str">
+        <x:v>SOURCE HOW-TO-FIX REQUIRED / NO LINK</x:v>
+      </x:c>
+      <x:c r="H180" s="9" t="str"/>
+      <x:c r="I180" s="9" t="str"/>
+      <x:c r="J180" s="9" t="str"/>
+      <x:c r="K180" s="9" t="str"/>
+      <x:c r="L180" s="9" t="str"/>
+      <x:c r="M180" s="9" t="str">
+        <x:v>The How to Fix field is empty, so there is no named repair, service or product to verify.</x:v>
+      </x:c>
+      <x:c r="N180" s="41" t="str">
+        <x:v>Author a symptom-specific diagnostic and software path before adding OTA, dealer or hardware destinations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A181" s="40" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B181" s="9" t="str">
+        <x:v>bmw-i5-software-updates-2025</x:v>
+      </x:c>
+      <x:c r="C181" s="9" t="str">
+        <x:v>2025-2026 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D181" s="9" t="str">
+        <x:v>iDrive 9 Software Updates and Calibration Issues</x:v>
+      </x:c>
+      <x:c r="E181" s="9" t="str"/>
+      <x:c r="F181" s="9" t="str">
+        <x:v>No repair instructions supplied in source</x:v>
+      </x:c>
+      <x:c r="G181" s="9" t="str">
+        <x:v>SOURCE HOW-TO-FIX REQUIRED / NO LINK</x:v>
+      </x:c>
+      <x:c r="H181" s="9" t="str"/>
+      <x:c r="I181" s="9" t="str"/>
+      <x:c r="J181" s="9" t="str"/>
+      <x:c r="K181" s="9" t="str"/>
+      <x:c r="L181" s="9" t="str"/>
+      <x:c r="M181" s="9" t="str">
+        <x:v>The How to Fix field is empty and the title alone does not establish an actionable repair.</x:v>
+      </x:c>
+      <x:c r="N181" s="41" t="str">
+        <x:v>Add exact symptoms, software/version verification, reset/programming steps and escalation criteria first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A182" s="40" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B182" s="9" t="str">
+        <x:v>bmw-i5-steering-spindle-double-universal-joint-fracture</x:v>
+      </x:c>
+      <x:c r="C182" s="9" t="str">
+        <x:v>2024-2025 | BMW | i5</x:v>
+      </x:c>
+      <x:c r="D182" s="9" t="str">
+        <x:v>2024-2025 i5 Steering-Spindle Recall 24V-714</x:v>
+      </x:c>
+      <x:c r="E182" s="9" t="str">
+        <x:v>Check the VIN for an open 24V-714 campaign. If included, have an authorized BMW dealer replace the steering spindle double universal joint at no charge. Do not order a steering joint from this card. If steering-column noise, notchy steering or increased effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+      </x:c>
+      <x:c r="F182" s="9" t="str">
+        <x:v>VIN check for 24V-714; authorized steering-spindle double-universal-joint replacement; immediate service for notchy/increased-effort steering</x:v>
+      </x:c>
+      <x:c r="G182" s="9" t="str">
+        <x:v>STEERING RECALL ONLY / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H182" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I182" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J182" s="9" t="str">
+        <x:v>2024-2025 i5; VIN required for 24V-714</x:v>
+      </x:c>
+      <x:c r="K182" s="9" t="str">
+        <x:v>official recall check</x:v>
+      </x:c>
+      <x:c r="L182" s="9" t="str"/>
+      <x:c r="M182" s="9" t="str">
+        <x:v>The free safety-recall remedy controls and the source explicitly says not to order the steering joint from the card.</x:v>
+      </x:c>
+      <x:c r="N182" s="41" t="str">
+        <x:v>Keep emergency steering guidance and VIN scope prominent.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A183" s="40" t="str"/>
+      <x:c r="B183" s="9" t="str"/>
+      <x:c r="C183" s="9" t="str"/>
+      <x:c r="D183" s="9" t="str"/>
+      <x:c r="E183" s="9" t="str"/>
+      <x:c r="F183" s="9" t="str"/>
+      <x:c r="G183" s="9" t="str"/>
+      <x:c r="H183" s="9" t="str">
+        <x:v>NHTSA VIN recall lookup</x:v>
+      </x:c>
+      <x:c r="I183" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J183" s="9" t="str">
+        <x:v>US VIN confirmation</x:v>
+      </x:c>
+      <x:c r="K183" s="9" t="str">
+        <x:v>government recall check</x:v>
+      </x:c>
+      <x:c r="L183" s="9" t="str"/>
+      <x:c r="M183" s="9" t="str"/>
+      <x:c r="N183" s="41" t="str"/>
+    </x:row>
+    <x:row r="184" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A184" s="40" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B184" s="9" t="str">
+        <x:v>bmw-i7-air-suspension-calibration-2023</x:v>
+      </x:c>
+      <x:c r="C184" s="9" t="str">
+        <x:v>2023-2026 | BMW | i7</x:v>
+      </x:c>
+      <x:c r="D184" s="9" t="str">
+        <x:v>Air Suspension Calibration and Sensor Issues</x:v>
+      </x:c>
+      <x:c r="E184" s="9" t="str"/>
+      <x:c r="F184" s="9" t="str">
+        <x:v>No repair instructions supplied in source</x:v>
+      </x:c>
+      <x:c r="G184" s="9" t="str">
+        <x:v>SOURCE HOW-TO-FIX REQUIRED / NO LINK</x:v>
+      </x:c>
+      <x:c r="H184" s="9" t="str"/>
+      <x:c r="I184" s="9" t="str"/>
+      <x:c r="J184" s="9" t="str"/>
+      <x:c r="K184" s="9" t="str"/>
+      <x:c r="L184" s="9" t="str"/>
+      <x:c r="M184" s="9" t="str">
+        <x:v>The How to Fix field is empty; title alone cannot distinguish calibration, sensor, leak, strut or compressor faults.</x:v>
+      </x:c>
+      <x:c r="N184" s="41" t="str">
+        <x:v>Add ISTA fault/calibration steps and exact component criteria before any service or part destination.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="792" hidden="0" customHeight="1">
+      <x:c r="A185" s="40" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B185" s="9" t="str">
+        <x:v>bmw-i7-autonomous-system-updates-2025</x:v>
+      </x:c>
+      <x:c r="C185" s="9" t="str">
+        <x:v>2023-2024 | BMW | i7</x:v>
+      </x:c>
+      <x:c r="D185" s="9" t="str">
+        <x:v>G70 i7 ADCAM Assistance-Limit Diagnosis</x:v>
+      </x:c>
+      <x:c r="E185" s="9" t="str">
+        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather and traffic conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the operating limits in the owner manual. BMW states that parts replacement does not correct environmental system limitations.</x:v>
+      </x:c>
+      <x:c r="F185" s="9" t="str">
+        <x:v>ADCam fault memory; clean/inspect camera area and wipers; verify holder/windshield installation; ISTA calibration after replacement; explain environmental limits</x:v>
+      </x:c>
+      <x:c r="G185" s="9" t="str">
+        <x:v>DIAGNOSIS/CALIBRATION SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H185" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I185" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J185" s="9" t="str">
+        <x:v>2023-2024 G70 i7 ADCAM diagnosis and windshield-camera calibration</x:v>
+      </x:c>
+      <x:c r="K185" s="9" t="str">
+        <x:v>ADAS calibration service</x:v>
+      </x:c>
+      <x:c r="L185" s="9" t="str"/>
+      <x:c r="M185" s="9" t="str">
+        <x:v>BMW says parts replacement does not correct environmental operating limits; calibration is conditional on the fault and windshield work.</x:v>
+      </x:c>
+      <x:c r="N185" s="41" t="str">
+        <x:v>Rename the issue to ADCAM assistance-limit diagnosis rather than autonomous-system updates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="778.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A186" s="42" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B186" s="43" t="str">
+        <x:v>bmw-i7-ota-update-failures-2025</x:v>
+      </x:c>
+      <x:c r="C186" s="43" t="str">
+        <x:v>2023-2024 | BMW | i7</x:v>
+      </x:c>
+      <x:c r="D186" s="43" t="str">
+        <x:v>G70 i7 Comfort-Access Faults after Remote Upgrade</x:v>
+      </x:c>
+      <x:c r="E186" s="43" t="str">
+        <x:v>Confirm that the complaint followed a BMW Remote Software Upgrade and read the exact BCP faults. Follow SIB 61 11 24 in ISTA to program and pair all FBD5/FBD5s remote-control receivers, clear faults and verify Comfort Access and Passive Go/Exit. Keep phones disconnected during receiver programming. BMW states that parts replacement will not solve this path. ShowMeTheParts resolves the exact 2023 i7 but has no software or receiver repair candidate, so all marketplace links are removed.</x:v>
+      </x:c>
+      <x:c r="F186" s="43" t="str">
+        <x:v>Confirm complaint followed Remote Software Upgrade; read BCP faults; ISTA programming/pairing of all FBD5/FBD5s receivers; verify Comfort Access and Passive Go/Exit</x:v>
+      </x:c>
+      <x:c r="G186" s="43" t="str">
+        <x:v>SOFTWARE/PAIRING SERVICE / NO RECEIVER PART</x:v>
+      </x:c>
+      <x:c r="H186" s="43" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I186" s="43" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J186" s="43" t="str">
+        <x:v>2023-2024 G70 i7 SIB 61 11 24 programming and receiver pairing</x:v>
+      </x:c>
+      <x:c r="K186" s="43" t="str">
+        <x:v>programming service</x:v>
+      </x:c>
+      <x:c r="L186" s="43" t="str"/>
+      <x:c r="M186" s="43" t="str">
+        <x:v>The source reports no software/receiver catalog candidate and states that parts replacement will not solve this path.</x:v>
+      </x:c>
+      <x:c r="N186" s="44" t="str">
+        <x:v>Rename this to Comfort Access faults after Remote Upgrade and do not link receivers or scanners.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6152,21 +7478,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="462" hidden="0" customHeight="1">
+    <x:row r="2" ht="528" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>bmw-i4-12v-battery-drain-2022</x:v>
+        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2015-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain</x:v>
+        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Ensure the latest software version is installed (BMW has released multiple OTA updates addressing sleep mode behavior). If the problem persists, have the dealer check for parasitic draw using ISTA diagnostics. In severe cases, the 12V battery may need replacement and proper registration.</x:v>
+        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -6175,21 +7501,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="3" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>bmw-i4-12v-battery-sleep-mode-2022</x:v>
+        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>12V Battery Drain - Sleep Mode Failure</x:v>
+        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>First check for latest software update - BMW has released updates to fix sleep mode bugs. If 12V battery has been deeply discharged, it may need replacement (60Ah AGM). Must register new battery using BimmerLink app (not BimmerCode - BimmerCode cannot register batteries). For vehicles that sit for extended periods, use a BMW-approved battery tender. If CCU is causing the issue, dealer diagnosis and CCU replacement under warranty. The DC-DC converter should maintain 12V charge from the HV battery, so persistent drain indicates a software or CCU hardware fault.</x:v>
+        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -6198,21 +7524,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="4" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>bmw-i4-brake-feel-regen-2022</x:v>
+        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8 | B38</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>Regenerative Braking Pedal Feel Complaints - Grabby/Aggressive</x:v>
+        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>This is a design characteristic of the blended braking system, not a defect per se. Adaptive approaches: Use "D" mode with Adaptive recuperation setting for the most natural brake feel - it adjusts regen based on traffic and road conditions. Avoid "B" mode unless you specifically want strong one-pedal driving. Practice feathering the brake pedal with very light, progressive pressure. Some owners report the brake feel improves slightly with software updates. If braking is truly abnormal (pulsating, grinding), have the integrated brake module checked as that could indicate a hardware issue covered under recall.</x:v>
+        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -6221,21 +7547,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="594" hidden="0" customHeight="1">
+    <x:row r="5" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>bmw-i4-drivetrain-malfunction-2022</x:v>
+        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>2022-2025 i4 Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW’s free electric-drive-motor software update through the authorized dealer or the approved over-the-air recall process. Do not buy gear oil, gaskets or drivetrain parts as a substitute. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -6244,21 +7570,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="6" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>bmw-i4-heat-pump-cold-weather-2022</x:v>
+        <x:v>bmw-i8-charging-port-2014</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2022-2024 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>G26 i4 Coolant Changeover-Valve Leak Diagnosis</x:v>
+        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Check coolant level, read the exact BMW fault memory and inspect the G26 changeover valve for active or dried leakage. Follow SIB 17 01 24 and VIN-specific AIR/ETK instructions; replace the applicable older-production valve and bleed/test the cooling system with ISTA when the BMW criteria are met. ShowMeTheParts resolves exact 2022 i4 HVAC and water-pump categories but returned no changeover-valve candidate, so the frozen marketplace searches and generic coolant are removed.</x:v>
+        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -6267,21 +7593,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="7" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>bmw-i4-heat-pump-malfunction-2022</x:v>
+        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2014-2015 | BMW | i8</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>Heat Pump Malfunction in Cold Weather</x:v>
+        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>BMW has released software updates to improve heat pump operation in cold weather. Visit the dealer for the latest calibration. Some cases require heat pump valve replacement. Pre-conditioning the cabin while plugged in reduces the impact on driving range.</x:v>
+        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -6290,21 +7616,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="8" ht="924" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>bmw-i4-idrive8-software-bugs-2022</x:v>
+        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2022-2025 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>iDrive 8 Software Bugs - Screen Crashes, Reboots &amp; Freezing</x:v>
+        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Ensure vehicle has latest iDrive software via OTA update (Settings &gt; Software Update). Version .63 and later resolved many screen blank/reboot issues. For persistent crashes: Perform soft reset by holding volume knob/power button for 10+ seconds. For factory reset, use Settings &gt; General &gt; Reset to restore defaults. If issues persist after latest OTA, dealer can force-flash the head unit via ISTA. Some owners report that disconnecting phone from wireless CarPlay/Android Auto and using wired connection improves stability. BMW has released multiple major software updates addressing these issues.</x:v>
+        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
@@ -6313,21 +7639,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="9" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>bmw-i4-infotainment-glitches-2022</x:v>
+        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2022-2026 | BMW | i4</x:v>
+        <x:v>2014-2020 | BMW | i8</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>iDrive 8 Software and Infotainment Glitches</x:v>
+        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Keep software up to date via OTA updates or dealer visit. For persistent issues, a full iDrive system reset (Settings &gt; General &gt; Reset) can resolve cached data problems. Some owners have needed the head unit replaced under warranty for hardware-level display faults.</x:v>
+        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -6336,21 +7662,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="10" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A10" s="40" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>bmw-i4-pedestrian-sound-2022</x:v>
+        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2022-2023 | BMW | i4</x:v>
+        <x:v>2014-2014 | BMW | i8</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>2022-2023 i4 eDrive40 Sound-Generator Recall 23V-026</x:v>
+        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-026 campaign. If included, arrange the free BMW programming remedy for the Receiver Audio Module/external artificial sound generator. Do not replace a speaker or module based only on a missing sound; if the VIN is outside the campaign, diagnose the exact warning and faults separately.</x:v>
+        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
         <x:v>0</x:v>
@@ -6359,21 +7685,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="11" ht="726" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>bmw-i5-12v-battery-drain-2024</x:v>
+        <x:v>bmw-i8-hv-system-faults-2014</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2014-2017 | BMW | i8</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain and Dead Car Syndrome</x:v>
+        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Keep the i5 plugged in when parked for extended periods — the HV charger trickle-charges the 12V battery. Install a BMW-recommended battery maintainer connected to the 12V battery (accessible in the right side of the trunk). Update iDrive software to the latest version — BMW has released OTA updates that improve sleep-mode power management. If the 12V battery dies, the manual release cable under the hood allows emergency access.</x:v>
+        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -6382,21 +7708,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="12" ht="963.5999755859375" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>bmw-i5-acoustic-pedestrian-warning-sound-generator-fault</x:v>
+        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>2024 i5 Pedestrian Sound Recall 23V-885</x:v>
+        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-885 campaign. If included, arrange BMW's free software programming remedy through the authorized dealer or the approved recall over-the-air process. Do not replace a speaker or module based only on a missing sound; diagnose vehicles outside the campaign separately.</x:v>
+        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -6405,21 +7731,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="13" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>bmw-i5-adaptive-suspension-calibration-2024</x:v>
+        <x:v>bmw-ix-air-suspension-2022</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>Adaptive Suspension Self-Leveling Calibration Errors</x:v>
+        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Perform a suspension calibration reset using BMW ISTA diagnostic software. If the issue persists, inspect the ride height sensors at each corner for damage or loose connectors. A dealer software update may also resolve the issue.</x:v>
+        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -6428,21 +7754,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="14" ht="422.3999938964844" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>bmw-i5-c-wiring-harness-damaged-during-cabin-filter-service</x:v>
+        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>2024-2026 i5 A/C Harness Recall 26V-096</x:v>
+        <x:v>Air Suspension Calibration Errors</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Check the VIN for an open 26V-096 campaign. If included, have an authorized BMW dealer inspect the air-conditioning wiring harness and repair or replace it as required at no charge. Do not probe, splice or order harness parts from this card. If smoke, burning odor or an electrical warning appears, stop using the vehicle and follow BMW emergency guidance.</x:v>
+        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -6451,21 +7777,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="15" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>bmw-i5-dc-fast-charge-throttling-loud-cooling-fans-repeated-session</x:v>
+        <x:v>bmw-ix-build-quality-2022</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5 | eDrive40, xDrive40, M60 xDrive</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>DC Fast-Charge Throttling and Loud Cooling Fans on Repeated Sessions</x:v>
+        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Keep the i5 on the latest software, since BMW has released charging-curve/charging-management updates via OTA and dealer flashes. Precondition the battery before fast charging to reduce throttling, avoid back-to-back DC sessions when possible, and report persistent amp drops or skipped scheduled charges to the dealer (some cases were traced to software faults). Loud thermal-management fan noise is generally normal during/after DC charging.</x:v>
+        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -6474,21 +7800,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="16" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>bmw-i5-electric-drive-motor-software-false-isolation-fault-causing</x:v>
+        <x:v>bmw-ix-charging-failures-2022</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>2024 i5 Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or the approved recall over-the-air process. Do not order drivetrain or battery parts from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the remedy.</x:v>
+        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
         <x:v>0</x:v>
@@ -6497,21 +7823,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="17" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>bmw-i5-heat-pump-drip-tube-thunking-clunking-noise</x:v>
+        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>Early-Production G60 i5 Condensation-Drain Drum Noise</x:v>
+        <x:v>DC Fast Charging Speed Inconsistency</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>Confirm the production date and reproduce the rhythmic noise under the BMW bulletin conditions. If SIB 64 01 24 applies, an authorized high-voltage-qualified repair facility replaces the condensation-water drain with the optimized part; the procedure requires high-voltage battery removal. Do not cut or modify the drain. ShowMeTheParts resolved the exact 2024 i5 but returned no matching HVAC candidate, so no parts link is approved.</x:v>
+        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -6520,21 +7846,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="18" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>bmw-i5-high-voltage-battery-module-insufficient-weld-seams</x:v>
+        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2024-2024 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>Single-Vehicle 2024 i5 Battery-Weld Recall 24V-135</x:v>
+        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-135 campaign. If included, follow BMW's instructions and have the affected high-voltage battery module replaced at no charge by an authorized high-voltage-qualified dealer. Do not open the battery pack or order modules independently; vehicles outside the campaign require separate fault-led diagnosis.</x:v>
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -6543,21 +7869,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="528" hidden="0" customHeight="1">
+    <x:row r="19" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>bmw-i5-integrated-brake-system-servomotor-weld-failure</x:v>
+        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2022-2025 | BMW | iX</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>2024-2025 i5 Integrated-Brake Recall 24V-697</x:v>
+        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-697 campaign. If included, have an authorized BMW dealer replace the integrated brake system at no charge. Do not buy pads, rotors, fluid or a generic actuator as a substitute. If a brake warning or changed pedal effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -6566,21 +7892,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="20" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>bmw-i5-regen-braking-inconsistency-2024</x:v>
+        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2022-2026 | BMW | iX</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Regenerative Braking Inconsistency in Cold Weather</x:v>
+        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Use the BMW departure timer to precondition the battery before driving — this warms the battery and restores full regen capability from the start. Set the regen level to "Adaptive" instead of "High" in winter, which provides smoother transitions. BMW software updates have improved regen ramping behavior. Rely more on friction brakes during the first 10-15 minutes of cold-weather driving until the battery warms.</x:v>
+        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
         <x:v>0</x:v>
@@ -6589,20 +7915,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="66" hidden="0" customHeight="1">
+    <x:row r="21" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>bmw-i5-software-glitches-2024</x:v>
+        <x:v>bmw-ix-phantom-braking-2022</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2024-2026 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>iDrive 8.5 Software Bugs and EV System Errors</x:v>
-      </x:c>
-      <x:c r="E21" s="9" t="str"/>
+        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="str">
+        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
+      </x:c>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6610,20 +7938,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="22" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>bmw-i5-software-updates-2025</x:v>
+        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2025-2026 | BMW | i5</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>iDrive 9 Software Updates and Calibration Issues</x:v>
-      </x:c>
-      <x:c r="E22" s="9" t="str"/>
+        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="str">
+        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
+      </x:c>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6631,21 +7961,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="23" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>bmw-i5-steering-spindle-double-universal-joint-fracture</x:v>
+        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2024-2025 | BMW | i5</x:v>
+        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>2024-2025 i5 Steering-Spindle Recall 24V-714</x:v>
+        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-714 campaign. If included, have an authorized BMW dealer replace the steering spindle double universal joint at no charge. Do not order a steering joint from this card. If steering-column noise, notchy steering or increased effort appears, stop driving when safe and arrange BMW assistance.</x:v>
+        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -6654,20 +7984,22 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="24" ht="660" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>bmw-i7-air-suspension-calibration-2023</x:v>
+        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2023-2026 | BMW | i7</x:v>
+        <x:v>2021-2021 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>Air Suspension Calibration and Sensor Issues</x:v>
-      </x:c>
-      <x:c r="E24" s="9" t="str"/>
+        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="str">
+        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
+      </x:c>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6675,21 +8007,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="792" hidden="0" customHeight="1">
+    <x:row r="25" ht="528" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>bmw-i7-autonomous-system-updates-2025</x:v>
+        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2023-2024 | BMW | i7</x:v>
+        <x:v>2021-2021 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>G70 i7 ADCAM Assistance-Limit Diagnosis</x:v>
+        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather and traffic conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the operating limits in the owner manual. BMW states that parts replacement does not correct environmental system limitations.</x:v>
+        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -6698,21 +8030,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="26" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>bmw-i7-ota-update-failures-2025</x:v>
+        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2023-2024 | BMW | i7</x:v>
+        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>G70 i7 Comfort-Access Faults after Remote Upgrade</x:v>
+        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Confirm that the complaint followed a BMW Remote Software Upgrade and read the exact BCP faults. Follow SIB 61 11 24 in ISTA to program and pair all FBD5/FBD5s remote-control receivers, clear faults and verify Comfort Access and Passive Go/Exit. Keep phones disconnected during receiver programming. BMW states that parts replacement will not solve this path. ShowMeTheParts resolves the exact 2023 i7 but has no software or receiver repair candidate, so all marketplace links are removed.</x:v>
+        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -6721,21 +8053,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="528" hidden="0" customHeight="1">
+    <x:row r="27" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
+        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2015-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
+        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
+        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -6744,21 +8076,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="28" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
+        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
+        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
+        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -6767,21 +8099,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="29" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
+        <x:v>bmw-m2-charge-pipe-2016</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8 | B38</x:v>
+        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
+        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
+        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
         <x:v>0</x:v>
@@ -6790,21 +8122,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="30" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
+        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2019-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -6813,21 +8145,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="31" ht="726" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>bmw-i8-charging-port-2014</x:v>
+        <x:v>bmw-m2-cooling-system-2016</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2020 | BMW | M2 | S55</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
+        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -6836,21 +8168,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="32" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
+        <x:v>bmw-m2-dct-clutch-2016</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2014-2015 | BMW | i8</x:v>
+        <x:v>2016-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
+        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
       </x:c>
       <x:c r="F32" s="9" t="n">
         <x:v>0</x:v>
@@ -6859,21 +8191,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="924" hidden="0" customHeight="1">
+    <x:row r="33" ht="462" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
+        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2021 | BMW | M2</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
+        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
+        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -6882,21 +8214,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="34" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
+        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2018 | BMW | M2 | N55</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
+        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
+        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -6905,21 +8237,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="35" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
+        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2014-2014 | BMW | i8</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
+        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
         <x:v>0</x:v>
@@ -6928,21 +8260,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="726" hidden="0" customHeight="1">
+    <x:row r="36" ht="858" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>bmw-i8-hv-system-faults-2014</x:v>
+        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2014-2017 | BMW | i8</x:v>
+        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
+        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
+        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -6951,21 +8283,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="37" ht="462" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
+        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
+        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -6974,21 +8306,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="38" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-2022</x:v>
+        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
+        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -6997,21 +8329,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="39" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
+        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>Air Suspension Calibration Errors</x:v>
+        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
+        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -7020,21 +8352,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="40" ht="528" hidden="0" customHeight="1">
       <x:c r="A40" s="40" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>bmw-ix-build-quality-2022</x:v>
+        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
+        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
+        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
         <x:v>0</x:v>
@@ -7043,21 +8375,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="41" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A41" s="40" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>bmw-ix-charging-failures-2022</x:v>
+        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
+        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
-        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
+        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
         <x:v>0</x:v>
@@ -7066,21 +8398,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="42" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A42" s="40" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
+        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>DC Fast Charging Speed Inconsistency</x:v>
+        <x:v>Rear Subframe Mounting Point Cracking</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
+        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
         <x:v>0</x:v>
@@ -7089,21 +8421,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="43" ht="594" hidden="0" customHeight="1">
       <x:c r="A43" s="40" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
+        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
         <x:v>0</x:v>
@@ -7112,21 +8444,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="44" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A44" s="40" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
+        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
+        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
+        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
         <x:v>0</x:v>
@@ -7135,21 +8467,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="45" ht="396" hidden="0" customHeight="1">
       <x:c r="A45" s="40" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
+        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
+        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
-        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
+        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
         <x:v>0</x:v>
@@ -7158,21 +8490,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="46" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A46" s="40" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>bmw-ix-phantom-braking-2022</x:v>
+        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
+        <x:v>EDC Electronic Damper Control System Failure</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
+        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
       </x:c>
       <x:c r="F46" s="9" t="n">
         <x:v>0</x:v>
@@ -7181,21 +8513,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="47" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A47" s="40" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
+        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
+        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
+        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
       </x:c>
       <x:c r="F47" s="9" t="n">
         <x:v>0</x:v>
@@ -7204,21 +8536,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="48" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A48" s="40" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
+        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
+        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
+        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
         <x:v>0</x:v>
@@ -7227,21 +8559,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="660" hidden="0" customHeight="1">
+    <x:row r="49" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A49" s="40" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
+        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
+        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E49" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
+        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
       </x:c>
       <x:c r="F49" s="9" t="n">
         <x:v>0</x:v>
@@ -7250,21 +8582,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="528" hidden="0" customHeight="1">
+    <x:row r="50" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A50" s="40" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
+        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
+        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
+        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
         <x:v>0</x:v>
@@ -7273,21 +8605,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="51" ht="660" hidden="0" customHeight="1">
       <x:c r="A51" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
+        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
-        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
+        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
-        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
+        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
         <x:v>0</x:v>
@@ -7296,21 +8628,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="52" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A52" s="40" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
+        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
+        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
+        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
         <x:v>0</x:v>
@@ -7319,21 +8651,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="53" ht="726" hidden="0" customHeight="1">
       <x:c r="A53" s="40" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
+        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
+        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
-        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
+        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
         <x:v>0</x:v>
@@ -7342,44 +8674,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="54" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A54" s="40" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>bmw-m2-charge-pipe-2016</x:v>
+        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
+        <x:v>2015-2018 | BMW | M3</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
+        <x:v>Direct Fuel Injector Failure (S55)</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
+        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G54" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="55" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A55" s="40" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
+        <x:v>bmw-m3-f80-water-pump-2015</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>2019-2020 | BMW | M2</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
+        <x:v>Electric Water Pump Failure (S55)</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
+        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
         <x:v>0</x:v>
@@ -7388,21 +8720,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="726" hidden="0" customHeight="1">
+    <x:row r="56" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A56" s="40" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>bmw-m2-cooling-system-2016</x:v>
+        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2 | S55</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
+        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
+        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
         <x:v>0</x:v>
@@ -7411,21 +8743,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="57" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A57" s="40" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>bmw-m2-dct-clutch-2016</x:v>
+        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
+        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
+        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
       </x:c>
       <x:c r="F57" s="9" t="n">
         <x:v>0</x:v>
@@ -7434,21 +8766,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="462" hidden="0" customHeight="1">
+    <x:row r="58" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A58" s="40" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
+        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>2016-2021 | BMW | M2</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
+        <x:v>Coolant System Issues (S58)</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
-        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
+        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
       </x:c>
       <x:c r="F58" s="9" t="n">
         <x:v>0</x:v>
@@ -7457,21 +8789,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="59" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A59" s="40" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
+        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>2016-2018 | BMW | M2 | N55</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
+        <x:v>iDrive 8 Software/Electronics Issues</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
-        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
+        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
       </x:c>
       <x:c r="F59" s="9" t="n">
         <x:v>0</x:v>
@@ -7480,21 +8812,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="60" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A60" s="40" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
+        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>2021-2021 | BMW | M3</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
+        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
+        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
       </x:c>
       <x:c r="F60" s="9" t="n">
         <x:v>0</x:v>
@@ -7503,21 +8835,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="858" hidden="0" customHeight="1">
+    <x:row r="61" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A61" s="40" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
+        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
+        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
-        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
+        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
       </x:c>
       <x:c r="F61" s="9" t="n">
         <x:v>0</x:v>
@@ -7526,21 +8858,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="462" hidden="0" customHeight="1">
+    <x:row r="62" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A62" s="40" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
+        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>Power window regulator failure and interior trim rattles</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
+        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
       </x:c>
       <x:c r="F62" s="9" t="n">
         <x:v>0</x:v>
@@ -7549,21 +8881,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="63" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A63" s="40" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
+        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>VANOS Solenoid O-Ring Failure</x:v>
+        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
-        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
+        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
       </x:c>
       <x:c r="F63" s="9" t="n">
         <x:v>0</x:v>
@@ -7572,21 +8904,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="64" ht="343.20001220703125" hidden="0" customHeight="1">
       <x:c r="A64" s="40" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
+        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
+        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
-        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
+        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
       </x:c>
       <x:c r="F64" s="9" t="n">
         <x:v>0</x:v>
@@ -7595,21 +8927,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="528" hidden="0" customHeight="1">
+    <x:row r="65" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A65" s="40" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
+        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
+        <x:v>S55 Crank Hub Slip/Failure</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
+        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
       </x:c>
       <x:c r="F65" s="9" t="n">
         <x:v>0</x:v>
@@ -7618,21 +8950,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="66" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A66" s="40" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
+        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
+        <x:v>S55/S58 Electric Water Pump Failure</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
+        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
       </x:c>
       <x:c r="F66" s="9" t="n">
         <x:v>0</x:v>
@@ -7641,21 +8973,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="67" ht="462" hidden="0" customHeight="1">
       <x:c r="A67" s="40" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
+        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracking</x:v>
+        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
-        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
+        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
       </x:c>
       <x:c r="F67" s="9" t="n">
         <x:v>0</x:v>
@@ -7664,21 +8996,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="594" hidden="0" customHeight="1">
+    <x:row r="68" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A68" s="40" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
+        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
+        <x:v>S65 Throttle Body Actuator Failure</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
+        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
       </x:c>
       <x:c r="F68" s="9" t="n">
         <x:v>0</x:v>
@@ -7687,21 +9019,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="69" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A69" s="40" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
+        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
+        <x:v>VANOS Solenoid Wear and Failure</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
-        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
+        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
       </x:c>
       <x:c r="F69" s="9" t="n">
         <x:v>0</x:v>
@@ -7710,21 +9042,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="396" hidden="0" customHeight="1">
+    <x:row r="70" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A70" s="40" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
+        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
+        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
+        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals, often combined with an anti-rattle kit that addresses the cam-gear/shaft play. DIY on the seal kit is common; specialists also offer fully rebuilt exchange units.</x:v>
       </x:c>
       <x:c r="F70" s="9" t="n">
         <x:v>0</x:v>
@@ -7733,21 +9065,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="71" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A71" s="40" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="9" t="str">
-        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
+        <x:v>bmw-m3-worn-rear-trailing-arm-bushings-suspension-mounts</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D71" s="9" t="str">
-        <x:v>EDC Electronic Damper Control System Failure</x:v>
+        <x:v>Worn rear trailing arm bushings (RTAB) and suspension mounts</x:v>
       </x:c>
       <x:c r="E71" s="9" t="str">
-        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
+        <x:v>Replace the RTABs with genuine BMW rubber bushings or upgraded poly/spherical bushings; many owners add RTAB limiter kits to reduce deflection. Inspect and renew rear shock mounts and engine/transmission mounts at the same time. The RTAB job is a common DIY that can be done with the trailing arms on the car.</x:v>
       </x:c>
       <x:c r="F71" s="9" t="n">
         <x:v>0</x:v>
@@ -7756,21 +9088,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="72" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A72" s="40" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="9" t="str">
-        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
+        <x:v>bmw-m340i-12v-battery-drain-failure-battery-registration-issues</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
-        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
+        <x:v>2019-2024 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D72" s="9" t="str">
-        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
+        <x:v>12V Battery Drain and Failure / Battery Registration Issues</x:v>
       </x:c>
       <x:c r="E72" s="9" t="str">
-        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
+        <x:v>Test and replace the AGM battery with the correct OEM-spec unit, then register the new battery with BimmerLink/ISTA so the charging strategy adapts. Diagnose parasitic drain and a faulty IBS cable/sensor if discharge persists. Drive long enough to fully recharge between trips.</x:v>
       </x:c>
       <x:c r="F72" s="9" t="n">
         <x:v>0</x:v>
@@ -7779,21 +9111,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="884.4000244140625" hidden="0" customHeight="1">
+    <x:row r="73" ht="528" hidden="0" customHeight="1">
       <x:c r="A73" s="40" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B73" s="9" t="str">
-        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
+        <x:v>bmw-m340i-b58-carbon-buildup-2020</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D73" s="9" t="str">
-        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
+        <x:v>Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E73" s="9" t="str">
-        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
+        <x:v>Walnut blast the intake valves every 50,000-60,000 miles. This involves removing the intake manifold and blasting walnut shell media at the valve backs to remove carbon deposits. Some owners use catch cans to reduce oil vapor entering the intake. BMW's official position is that carbon buildup is normal for direct-injection engines.</x:v>
       </x:c>
       <x:c r="F73" s="9" t="n">
         <x:v>0</x:v>
@@ -7802,21 +9134,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="74" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A74" s="40" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B74" s="9" t="str">
-        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
+        <x:v>bmw-m340i-b58-coolant-loss-2020</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D74" s="9" t="str">
-        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
+        <x:v>Coolant Loss from Expansion Tank and Water Pump</x:v>
       </x:c>
       <x:c r="E74" s="9" t="str">
-        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
+        <x:v>Replace the coolant expansion tank at first sign of cracking. Proactively replace the electric water pump before 60,000 miles. Replace the coolant vent line per BMW TSB. Use only BMW-approved blue coolant. Monitor coolant level monthly and pressure test the cooling system at every major service.</x:v>
       </x:c>
       <x:c r="F74" s="9" t="n">
         <x:v>0</x:v>
@@ -7825,21 +9157,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="75" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A75" s="40" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B75" s="9" t="str">
-        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
+        <x:v>bmw-m340i-b58-hpfp-failure-2020</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D75" s="9" t="str">
-        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
       </x:c>
       <x:c r="E75" s="9" t="str">
-        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
+        <x:v>Replace the high-pressure fuel pump with the latest revised BMW part number. Verify the low-pressure fuel pump is providing adequate feed pressure. Use top-tier fuel and avoid running the tank below 1/4 to reduce strain on the fuel system. If under warranty, BMW will cover HPFP replacement.</x:v>
       </x:c>
       <x:c r="F75" s="9" t="n">
         <x:v>0</x:v>
@@ -7848,21 +9180,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="660" hidden="0" customHeight="1">
+    <x:row r="76" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A76" s="40" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B76" s="9" t="str">
-        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
+        <x:v>bmw-m340i-b58-oil-filter-disintegration-2020</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6, B58</x:v>
       </x:c>
       <x:c r="D76" s="9" t="str">
-        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
+        <x:v>Oil Filter Disintegration in Housing</x:v>
       </x:c>
       <x:c r="E76" s="9" t="str">
-        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
+        <x:v>Use only genuine BMW or Mann-branded oil filters (Mann is the OEM supplier). Change oil and filter every 5,000-7,000 miles rather than BMW's recommended 10,000-mile interval. When removing the old filter, inspect it carefully for signs of deterioration. If filter fragments are found in the housing, flush the housing thoroughly before installing the new filter.</x:v>
       </x:c>
       <x:c r="F76" s="9" t="n">
         <x:v>0</x:v>
@@ -7871,21 +9203,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="77" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A77" s="40" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B77" s="9" t="str">
-        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
+        <x:v>bmw-m340i-b58-wastegate-rattle-2020</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D77" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
+        <x:v>Turbo Wastegate Rattle at Idle</x:v>
       </x:c>
       <x:c r="E77" s="9" t="str">
-        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
+        <x:v>Have the wastegate actuator inspected for excessive play. Minor rattle without fault codes can be monitored. If boost control faults develop, replace the turbocharger wastegate actuator. In severe cases, the entire turbocharger assembly may need replacement. BMW may cover under warranty if fault codes are present.</x:v>
       </x:c>
       <x:c r="F77" s="9" t="n">
         <x:v>0</x:v>
@@ -7894,21 +9226,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="726" hidden="0" customHeight="1">
+    <x:row r="78" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A78" s="40" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B78" s="9" t="str">
-        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
+        <x:v>bmw-m340i-loss-brake-assist-from-brake-vacuum-pump-damage</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2020-2020 | BMW | M340i | B58 3.0L turbo inline-six</x:v>
       </x:c>
       <x:c r="D78" s="9" t="str">
-        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
+        <x:v>2020 M340i Brake-Assist Recall 21V-598</x:v>
       </x:c>
       <x:c r="E78" s="9" t="str">
-        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
+        <x:v>Check the VIN for an open 21V-598 campaign. An authorized BMW dealer updates the engine-management software free of charge and replaces the combined oil/vacuum pump if diagnosis shows it was already damaged. Do not order generic brake-vacuum parts from this card.</x:v>
       </x:c>
       <x:c r="F78" s="9" t="n">
         <x:v>0</x:v>
@@ -7917,44 +9249,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="79" ht="462" hidden="0" customHeight="1">
       <x:c r="A79" s="40" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B79" s="9" t="str">
-        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
+        <x:v>bmw-m340i-seat-belt-warning-audio-failure</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3</x:v>
+        <x:v>2019-2022 | BMW | M340i</x:v>
       </x:c>
       <x:c r="D79" s="9" t="str">
-        <x:v>Direct Fuel Injector Failure (S55)</x:v>
+        <x:v>2019-2022 M340i Seat-Belt Warning Recall 23V-584</x:v>
       </x:c>
       <x:c r="E79" s="9" t="str">
-        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
+        <x:v>Check the VIN for an open 23V-584 campaign. An authorized BMW dealer installs updated Receiver Audio Module software free of charge; eligible vehicles may also receive the remedy by BMW Remote Software Upgrade. Always use the seat belt regardless of warning-chime behavior.</x:v>
       </x:c>
       <x:c r="F79" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G79" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="80" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A80" s="40" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B80" s="9" t="str">
-        <x:v>bmw-m3-f80-water-pump-2015</x:v>
+        <x:v>bmw-m340i-valve-cover-oil-filter-housing-gasket-oil-leaks</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D80" s="9" t="str">
-        <x:v>Electric Water Pump Failure (S55)</x:v>
+        <x:v>Valve Cover and Oil Filter Housing Gasket Oil Leaks (B58)</x:v>
       </x:c>
       <x:c r="E80" s="9" t="str">
-        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
+        <x:v>Replace the valve cover gasket and/or oil filter housing gasket. Many shops also replace the valve cover itself if it has warped. Clean any oil from spark-plug wells and inspect coils. Typical independent-shop cost is roughly $400-$900 depending on which gasket(s) and labor access.</x:v>
       </x:c>
       <x:c r="F80" s="9" t="n">
         <x:v>0</x:v>
@@ -7963,21 +9295,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="81" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A81" s="40" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B81" s="9" t="str">
-        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
+        <x:v>bmw-m340i-vanos-solenoid-o-ring-failure</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D81" s="9" t="str">
-        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E81" s="9" t="str">
-        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
+        <x:v>Diagnose with a scan tool (VANOS/camshaft position fault codes), then replace the affected intake/exhaust VANOS solenoid(s) and O-rings. Solenoids are relatively inexpensive parts; cost is mostly diagnosis and labor, typically a few hundred dollars.</x:v>
       </x:c>
       <x:c r="F81" s="9" t="n">
         <x:v>0</x:v>
@@ -7991,16 +9323,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B82" s="9" t="str">
-        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
+        <x:v>bmw-m340i-zf-8hp-harsh-jerky-low-speed-shifting-mechatronic-faults</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D82" s="9" t="str">
-        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
+        <x:v>ZF 8HP Harsh / Jerky Low-Speed Shifting and Mechatronic Faults</x:v>
       </x:c>
       <x:c r="E82" s="9" t="str">
-        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
+        <x:v>Perform the ZF 8-speed fluid-and-filter (pan) service rather than treating it as lifetime-fill; this resolves many shift-quality complaints. Let the drivetrain warm before hard driving. For persistent erratic shifting or warning lights, scan the transmission and repair/replace the mechatronic unit (valve body) as needed.</x:v>
       </x:c>
       <x:c r="F82" s="9" t="n">
         <x:v>0</x:v>
@@ -8009,21 +9341,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="83" ht="594" hidden="0" customHeight="1">
       <x:c r="A83" s="40" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B83" s="9" t="str">
-        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
+        <x:v>bmw-m3cs-idrive-software-2024</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D83" s="9" t="str">
-        <x:v>Coolant System Issues (S58)</x:v>
+        <x:v>iDrive 8 Software Glitches and Screen Blackouts</x:v>
       </x:c>
       <x:c r="E83" s="9" t="str">
-        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
+        <x:v>Check for and install the latest BMW iDrive 8 software updates, which can be delivered over-the-air or at a dealer. Perform a soft reset by holding the iDrive controller button for 30 seconds. If screen blackouts persist, the dealer may need to replace the head unit or update the gateway module firmware. Ensure the 12V battery is in good condition, as low voltage can trigger software instability.</x:v>
       </x:c>
       <x:c r="F83" s="9" t="n">
         <x:v>0</x:v>
@@ -8032,21 +9364,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="84" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A84" s="40" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B84" s="9" t="str">
-        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
+        <x:v>bmw-m3cs-s58-carbon-buildup-2024</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D84" s="9" t="str">
-        <x:v>iDrive 8 Software/Electronics Issues</x:v>
+        <x:v>S58 Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E84" s="9" t="str">
-        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
+        <x:v>Schedule walnut blast cleaning of the intake valves at 40,000-50,000 mile intervals. Install an oil catch can to reduce oil vapor entering the intake system. Use high-quality synthetic oil meeting BMW LL-01 specification and change at 5,000-7,000 mile intervals. Allow the engine to fully warm up before high-boost driving to ensure proper oil vapor management.</x:v>
       </x:c>
       <x:c r="F84" s="9" t="n">
         <x:v>0</x:v>
@@ -8055,21 +9387,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="85" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A85" s="40" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B85" s="9" t="str">
-        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
+        <x:v>bmw-m3cs-s58-charge-pipe-crack-2024</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
-        <x:v>2021-2021 | BMW | M3</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D85" s="9" t="str">
-        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
+        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
       </x:c>
       <x:c r="E85" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF. These direct-fit replacements handle higher temperatures and pressures without risk of cracking. If the car is under warranty and the failure occurs on stock tune, BMW should cover the repair. Inspect the charge pipe during every service and before track days.</x:v>
       </x:c>
       <x:c r="F85" s="9" t="n">
         <x:v>0</x:v>
@@ -8078,21 +9410,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="86" ht="396" hidden="0" customHeight="1">
       <x:c r="A86" s="40" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B86" s="9" t="str">
-        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
+        <x:v>bmw-m4-charge-pipe-blowoff-2015</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D86" s="9" t="str">
-        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
+        <x:v>Plastic Charge Pipe Blow-Off Under Boost</x:v>
       </x:c>
       <x:c r="E86" s="9" t="str">
-        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
+        <x:v>Replace with an aluminum or silicone charge pipe. This is considered a must-do upgrade for any F82 M4. Many aftermarket options are direct bolt-on replacements. The job takes about 1-2 hours and requires removing the intake duct to access the charge pipe.</x:v>
       </x:c>
       <x:c r="F86" s="9" t="n">
         <x:v>0</x:v>
@@ -8101,21 +9433,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="87" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A87" s="40" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B87" s="9" t="str">
-        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
+        <x:v>bmw-m4-convertible-top-2015</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D87" s="9" t="str">
-        <x:v>Power window regulator failure and interior trim rattles</x:v>
+        <x:v>Convertible Top Hydraulic Pump Failure - F83 M4 Convertible</x:v>
       </x:c>
       <x:c r="E87" s="9" t="str">
-        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
+        <x:v>Diagnose specific failure: hydraulic pump motor, lines, microswitches, or latch mechanisms. Pump motor replacement is most common ($1,500-2,500). Check hydraulic fluid level and refill if low. Regular top cycling (minimum once per month) prevents seal degradation. Store with top UP to reduce strain on hydraulic system. Rebuilt hydraulic pumps available at lower cost than new OEM. Complex repair requiring specialized BMW knowledge.</x:v>
       </x:c>
       <x:c r="F87" s="9" t="n">
         <x:v>0</x:v>
@@ -8124,21 +9456,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="88" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A88" s="40" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B88" s="9" t="str">
-        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
+        <x:v>bmw-m4-cooling-track-2015</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D88" s="9" t="str">
-        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E88" s="9" t="str">
-        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
+        <x:v>Install comprehensive cooling upgrades for track use: CSF or Mishimoto high-capacity radiator, aftermarket oil cooler, upgraded intercoolers (Wagner, CSF), and transmission cooler. Remove kidney grille blockage for improved airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Total cooling system upgrade costs $3,000-5,000 but essential for serious track use. For street-only M4s, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F88" s="9" t="n">
         <x:v>0</x:v>
@@ -8147,21 +9479,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="89" ht="462" hidden="0" customHeight="1">
       <x:c r="A89" s="40" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B89" s="9" t="str">
-        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
+        <x:v>bmw-m4-crank-hub-bolt-2015</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D89" s="9" t="str">
-        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
+        <x:v>S55 Crank Hub Bolt Loosening</x:v>
       </x:c>
       <x:c r="E89" s="9" t="str">
-        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
+        <x:v>Replace with an upgraded aftermarket crank hub bolt (ARP or IND). The job requires removing the radiator fan, accessory belt, and harmonic balancer to access the bolt. Use proper torque specs for the upgraded bolt. This is a preventative maintenance item for any M4 owner.</x:v>
       </x:c>
       <x:c r="F89" s="9" t="n">
         <x:v>0</x:v>
@@ -8170,21 +9502,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="90" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A90" s="40" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B90" s="9" t="str">
-        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
+        <x:v>bmw-m4-dct-clutch-2015</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D90" s="9" t="str">
-        <x:v>S55 Crank Hub Slip/Failure</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E90" s="9" t="str">
-        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
+        <x:v>Replace DCT clutch pack when symptoms appear. BMW recommends replacing all clutches together. Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use (limit to special occasions). Transmission adaptation reset via BMW software may temporarily improve shift quality. Extended warranty highly recommended for DCT-equipped M4s. Labor-intensive repair requires transmission removal.</x:v>
       </x:c>
       <x:c r="F90" s="9" t="n">
         <x:v>0</x:v>
@@ -8193,21 +9525,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="91" ht="462" hidden="0" customHeight="1">
       <x:c r="A91" s="40" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B91" s="9" t="str">
-        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
+        <x:v>bmw-m4-rear-subframe-crack-2015</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
-        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
+        <x:v>2015-2026 | BMW | M4</x:v>
       </x:c>
       <x:c r="D91" s="9" t="str">
-        <x:v>S55/S58 Electric Water Pump Failure</x:v>
+        <x:v>Rear Subframe Cracking From Track Use</x:v>
       </x:c>
       <x:c r="E91" s="9" t="str">
-        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
+        <x:v>Inspect subframe mounting points and welds regularly if the car sees track use. Reinforce with aftermarket subframe reinforcement plates or weld-in gussets. Severely cracked subframes must be replaced entirely. Upgraded subframe bushings (solid or reinforced) help distribute loads more evenly.</x:v>
       </x:c>
       <x:c r="F91" s="9" t="n">
         <x:v>0</x:v>
@@ -8216,21 +9548,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="462" hidden="0" customHeight="1">
+    <x:row r="92" ht="805.2000122070312" hidden="0" customHeight="1">
       <x:c r="A92" s="40" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B92" s="9" t="str">
-        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
+        <x:v>bmw-m4-s55-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D92" s="9" t="str">
-        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E92" s="9" t="str">
-        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway) that eliminates the slipping issue permanently. Installation requires crankshaft pulley removal and precise torque specs. This upgrade is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Cost is $1,200-2,500 installed vs. $20,000+ for engine replacement after failure.</x:v>
       </x:c>
       <x:c r="F92" s="9" t="n">
         <x:v>0</x:v>
@@ -8239,44 +9571,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="93" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A93" s="40" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B93" s="9" t="str">
-        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
+        <x:v>bmw-m4-s55-injector-2015</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D93" s="9" t="str">
-        <x:v>S65 Throttle Body Actuator Failure</x:v>
+        <x:v>S55 High-Pressure Fuel Injector Failure - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E93" s="9" t="str">
-        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
+        <x:v>Replace all 6 injectors together to prevent repeat repairs. Perform walnut blast carbon cleaning on intake valves while injectors are removed (labor overlap saves $400-600). Use Top Tier gasoline to minimize carbon buildup. Add fuel system cleaner (Liqui Moly Valve Clean) every 5,000 miles to reduce carbon deposits. BMW parts are expensive; some shops use OEM Bosch injectors at lower cost. Labor is 4-6 hours for injector replacement.</x:v>
       </x:c>
       <x:c r="F93" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G93" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="250.8000030517578" hidden="0" customHeight="1">
+    <x:row r="94" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A94" s="40" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B94" s="9" t="str">
-        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
+        <x:v>bmw-m4-s55-rod-bearing-2015</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D94" s="9" t="str">
-        <x:v>VANOS Solenoid Wear and Failure</x:v>
+        <x:v>S55 Rod Bearing Premature Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E94" s="9" t="str">
-        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
+        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles or before extensive track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability than OEM. Regular oil analysis (Blackstone Labs) every 5,000 miles to monitor bearing wear. Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max. Track-focused M4s should replace bearings every 50,000 miles. Labor is 8-12 hours, so many owners do this during clutch replacement.</x:v>
       </x:c>
       <x:c r="F94" s="9" t="n">
         <x:v>0</x:v>
@@ -8285,21 +9617,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="95" ht="660" hidden="0" customHeight="1">
       <x:c r="A95" s="40" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="9" t="str">
-        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
+        <x:v>bmw-m4cs-brake-wear-track-2024</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
-        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D95" s="9" t="str">
-        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
+        <x:v>Rapid Brake Pad and Rotor Wear from Track Use</x:v>
       </x:c>
       <x:c r="E95" s="9" t="str">
-        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals, often combined with an anti-rattle kit that addresses the cam-gear/shaft play. DIY on the seal kit is common; specialists also offer fully rebuilt exchange units.</x:v>
+        <x:v>Inspect brake pads and rotors before and after every track day. Consider upgrading to aftermarket performance pads like Pagid RSC or Hawk DTC-70 for track use, and switch to street pads for daily driving. For frequent track users, the optional carbon ceramic brake package significantly extends rotor life. Use high-temperature brake fluid (DOT 5.1 or racing fluid) and flush before every track season.</x:v>
       </x:c>
       <x:c r="F95" s="9" t="n">
         <x:v>0</x:v>
@@ -8308,21 +9640,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="96" ht="462" hidden="0" customHeight="1">
       <x:c r="A96" s="40" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B96" s="9" t="str">
-        <x:v>bmw-m3-worn-rear-trailing-arm-bushings-suspension-mounts</x:v>
+        <x:v>bmw-m4cs-s58-carbon-buildup-2024</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D96" s="9" t="str">
-        <x:v>Worn rear trailing arm bushings (RTAB) and suspension mounts</x:v>
+        <x:v>S58 Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E96" s="9" t="str">
-        <x:v>Replace the RTABs with genuine BMW rubber bushings or upgraded poly/spherical bushings; many owners add RTAB limiter kits to reduce deflection. Inspect and renew rear shock mounts and engine/transmission mounts at the same time. The RTAB job is a common DIY that can be done with the trailing arms on the car.</x:v>
+        <x:v>Walnut blast the intake valves every 40,000-50,000 miles. Consider installing an oil catch can to reduce oil vapor ingestion. Maintain strict 5,000-7,000 mile oil change intervals with BMW LL-01 approved oil. Allow full engine warmup before spirited driving to ensure proper crankcase ventilation operation.</x:v>
       </x:c>
       <x:c r="F96" s="9" t="n">
         <x:v>0</x:v>
@@ -8331,21 +9663,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="97" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A97" s="40" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B97" s="9" t="str">
-        <x:v>bmw-m340i-12v-battery-drain-failure-battery-registration-issues</x:v>
+        <x:v>bmw-m4cs-s58-charge-pipe-crack-2024</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
-        <x:v>2019-2024 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D97" s="9" t="str">
-        <x:v>12V Battery Drain and Failure / Battery Registration Issues</x:v>
+        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
       </x:c>
       <x:c r="E97" s="9" t="str">
-        <x:v>Test and replace the AGM battery with the correct OEM-spec unit, then register the new battery with BimmerLink/ISTA so the charging strategy adapts. Diagnose parasitic drain and a faulty IBS cable/sensor if discharge persists. Drive long enough to fully recharge between trips.</x:v>
+        <x:v>Proactively replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF before any track use. These bolt-on replacements are rated for boost pressures well beyond what the S58 produces. Inspect the charge pipe at every service interval for signs of stress cracking or discoloration.</x:v>
       </x:c>
       <x:c r="F97" s="9" t="n">
         <x:v>0</x:v>
@@ -8354,21 +9686,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="528" hidden="0" customHeight="1">
+    <x:row r="98" ht="660" hidden="0" customHeight="1">
       <x:c r="A98" s="40" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B98" s="9" t="str">
-        <x:v>bmw-m340i-b58-carbon-buildup-2020</x:v>
+        <x:v>bmw-m5-absdsc-module-failure-triggering-2000</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D98" s="9" t="str">
-        <x:v>Intake Valve Carbon Buildup</x:v>
+        <x:v>ABS/DSC Module Failure Triggering ABS, Brake, and Traction Control Warning Lights</x:v>
       </x:c>
       <x:c r="E98" s="9" t="str">
-        <x:v>Walnut blast the intake valves every 50,000-60,000 miles. This involves removing the intake manifold and blasting walnut shell media at the valve backs to remove carbon deposits. Some owners use catch cans to reduce oil vapor entering the intake. BMW's official position is that carbon buildup is normal for direct-injection engines.</x:v>
+        <x:v>Diagnosis should begin with scanning the ABS/DSC module for communication or wheel-speed sensor faults and verifying power, ground, and sensor signals. If the module intermittently loses communication or shows implausible internal faults, the usual repair is module rebuild or replacement, followed by coding if required. Wheel speed sensors should only be replaced after confirming they are actually faulty.</x:v>
       </x:c>
       <x:c r="F98" s="9" t="n">
         <x:v>0</x:v>
@@ -8377,21 +9709,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="99" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A99" s="40" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B99" s="9" t="str">
-        <x:v>bmw-m340i-b58-coolant-loss-2020</x:v>
+        <x:v>bmw-m5-clutch-slave-cylinder-and-2000</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D99" s="9" t="str">
-        <x:v>Coolant Loss from Expansion Tank and Water Pump</x:v>
+        <x:v>Clutch Slave Cylinder and Hydraulic Line Failure Causing Soft Pedal and Shift Engagement Problems</x:v>
       </x:c>
       <x:c r="E99" s="9" t="str">
-        <x:v>Replace the coolant expansion tank at first sign of cracking. Proactively replace the electric water pump before 60,000 miles. Replace the coolant vent line per BMW TSB. Use only BMW-approved blue coolant. Monitor coolant level monthly and pressure test the cooling system at every major service.</x:v>
+        <x:v>Inspect the clutch hydraulic circuit for fluid leakage at the slave cylinder, master cylinder, and line connections, and verify brake/clutch fluid condition. Replace the failed slave cylinder and often the flexible hose, then bleed the system thoroughly; if symptoms persist, inspect the clutch, pressure plate, and pilot bearing.</x:v>
       </x:c>
       <x:c r="F99" s="9" t="n">
         <x:v>0</x:v>
@@ -8400,21 +9732,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="475.20001220703125" hidden="0" customHeight="1">
+    <x:row r="100" ht="1108.800048828125" hidden="0" customHeight="1">
       <x:c r="A100" s="40" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B100" s="9" t="str">
-        <x:v>bmw-m340i-b58-hpfp-failure-2020</x:v>
+        <x:v>bmw-m5-dct-clutch-2012</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2012-2016 | BMW | M5</x:v>
       </x:c>
       <x:c r="D100" s="9" t="str">
-        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
+        <x:v>DCT Dual-Clutch Transmission Wear &amp; Judder - F10 M5</x:v>
       </x:c>
       <x:c r="E100" s="9" t="str">
-        <x:v>Replace the high-pressure fuel pump with the latest revised BMW part number. Verify the low-pressure fuel pump is providing adequate feed pressure. Use top-tier fuel and avoid running the tank below 1/4 to reduce strain on the fuel system. If under warranty, BMW will cover HPFP replacement.</x:v>
+        <x:v>PREVENTIVE: Replace DCT transmission fluid and filter every 30,000-50,000 miles (BMW says "lifetime" but this causes premature failure). Use ONLY BMW DCTF-1 specification fluid ($189-$253 service, DIY: $100-$150). For judder/jerkiness: try fluid change and software update FIRST before clutch replacement - many issues resolved this way. For severe clutch wear: replace dual-clutch assembly with OEM ($2,394-$2,567 typical, $3,000-$4,000 dealership) or upgraded performance clutch kit. Consider NRC TitanTec or CNS Racing upgraded DCT clutch packs for improved durability if used for performance driving/track. Complete DCT transmission replacement: $8,000-$12,000.</x:v>
       </x:c>
       <x:c r="F100" s="9" t="n">
         <x:v>0</x:v>
@@ -8423,21 +9755,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="101" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A101" s="40" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B101" s="9" t="str">
-        <x:v>bmw-m340i-b58-oil-filter-disintegration-2020</x:v>
+        <x:v>bmw-m5-door-vapor-barrier-and-2000</x:v>
       </x:c>
       <x:c r="C101" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6, B58</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D101" s="9" t="str">
-        <x:v>Oil Filter Disintegration in Housing</x:v>
+        <x:v>Door Vapor Barrier and Sunroof Drain Leaks Causing Wet Carpets and Electrical Problems</x:v>
       </x:c>
       <x:c r="E101" s="9" t="str">
-        <x:v>Use only genuine BMW or Mann-branded oil filters (Mann is the OEM supplier). Change oil and filter every 5,000-7,000 miles rather than BMW's recommended 10,000-mile interval. When removing the old filter, inspect it carefully for signs of deterioration. If filter fragments are found in the housing, flush the housing thoroughly before installing the new filter.</x:v>
+        <x:v>Remove the door panel and inspect the vapor barrier seal, especially along the lower edge, and verify all sunroof drains flow freely and exit properly. Reseal the vapor barrier with butyl ribbon or equivalent body sealer, clear the drains, dry the carpet and padding thoroughly, and inspect under-carpet wiring/connectors for corrosion.</x:v>
       </x:c>
       <x:c r="F101" s="9" t="n">
         <x:v>0</x:v>
@@ -8446,21 +9778,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="102" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A102" s="40" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B102" s="9" t="str">
-        <x:v>bmw-m340i-b58-wastegate-rattle-2020</x:v>
+        <x:v>bmw-m5-e39-m5-vanos-solenoidseal-2000</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
-        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D102" s="9" t="str">
-        <x:v>Turbo Wastegate Rattle at Idle</x:v>
+        <x:v>E39 M5 VANOS Solenoid/Seal Failure Causing Rattle, Power Loss, and Check Engine Lights</x:v>
       </x:c>
       <x:c r="E102" s="9" t="str">
-        <x:v>Have the wastegate actuator inspected for excessive play. Minor rattle without fault codes can be monitored. If boost control faults develop, replace the turbocharger wastegate actuator. In severe cases, the entire turbocharger assembly may need replacement. BMW may cover under warranty if fault codes are present.</x:v>
+        <x:v>Diagnosis typically includes scanning for camshaft timing and VANOS activation faults, checking oil condition/pressure, and listening for startup rattle from the front of the engine. Repair usually involves rebuilding the VANOS units with upgraded seals, replacing failed solenoids or solenoid seals, and correcting any oil leaks or timing-related wear. Many owners address both banks preventively while the front of engine is apart.</x:v>
       </x:c>
       <x:c r="F102" s="9" t="n">
         <x:v>0</x:v>
@@ -8474,16 +9806,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B103" s="9" t="str">
-        <x:v>bmw-m340i-loss-brake-assist-from-brake-vacuum-pump-damage</x:v>
+        <x:v>bmw-m5-front-thrust-arm-bushing-2000</x:v>
       </x:c>
       <x:c r="C103" s="9" t="str">
-        <x:v>2020-2020 | BMW | M340i | B58 3.0L turbo inline-six</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D103" s="9" t="str">
-        <x:v>2020 M340i Brake-Assist Recall 21V-598</x:v>
+        <x:v>Front Thrust Arm Bushing Failure Causing 50-60 MPH Brake Shimmy and Steering Vibration</x:v>
       </x:c>
       <x:c r="E103" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-598 campaign. An authorized BMW dealer updates the engine-management software free of charge and replaces the combined oil/vacuum pump if diagnosis shows it was already damaged. Do not order generic brake-vacuum parts from this card.</x:v>
+        <x:v>Inspect the front thrust arms and control arms for bushing cracks, fluid leakage from hydro-bushings, and ball-joint play. Replace the thrust arms or complete front control arm set, then perform a proper alignment; if brake pulsation remains, inspect rotor runout and wheel balance.</x:v>
       </x:c>
       <x:c r="F103" s="9" t="n">
         <x:v>0</x:v>
@@ -8492,21 +9824,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="462" hidden="0" customHeight="1">
+    <x:row r="104" ht="594" hidden="0" customHeight="1">
       <x:c r="A104" s="40" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B104" s="9" t="str">
-        <x:v>bmw-m340i-seat-belt-warning-audio-failure</x:v>
+        <x:v>bmw-m5-getrag-420g-6-speed-synchro-2000</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
-        <x:v>2019-2022 | BMW | M340i</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D104" s="9" t="str">
-        <x:v>2019-2022 M340i Seat-Belt Warning Recall 23V-584</x:v>
+        <x:v>Getrag 420G 6-Speed Synchro Wear and 2nd/3rd Gear Grinding</x:v>
       </x:c>
       <x:c r="E104" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-584 campaign. An authorized BMW dealer installs updated Receiver Audio Module software free of charge; eligible vehicles may also receive the remedy by BMW Remote Software Upgrade. Always use the seat belt regardless of warning-chime behavior.</x:v>
+        <x:v>Diagnosis involves road testing hot and cold, checking clutch release operation, and ruling out worn transmission mounts or old fluid before condemning the gearbox. Mild cases may improve with fresh fluid, but persistent grinding usually requires transmission rebuild with new synchros, bearings, and wear components. Clutch and shifter bushings are often serviced at the same time.</x:v>
       </x:c>
       <x:c r="F104" s="9" t="n">
         <x:v>0</x:v>
@@ -8515,21 +9847,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="105" ht="976.7999877929688" hidden="0" customHeight="1">
       <x:c r="A105" s="40" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B105" s="9" t="str">
-        <x:v>bmw-m340i-valve-cover-oil-filter-housing-gasket-oil-leaks</x:v>
+        <x:v>bmw-m5-ignition-coils-2012</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2012-2023 | BMW | M5 | S63, S63TU</x:v>
       </x:c>
       <x:c r="D105" s="9" t="str">
-        <x:v>Valve Cover and Oil Filter Housing Gasket Oil Leaks (B58)</x:v>
+        <x:v>S63/S63TU Ignition Coil Premature Failure</x:v>
       </x:c>
       <x:c r="E105" s="9" t="str">
-        <x:v>Replace the valve cover gasket and/or oil filter housing gasket. Many shops also replace the valve cover itself if it has warped. Clean any oil from spark-plug wells and inspect coils. Typical independent-shop cost is roughly $400-$900 depending on which gasket(s) and labor access.</x:v>
+        <x:v>Replace failed ignition coil(s) immediately to prevent catalytic converter damage ($3,000-$5,000 additional). When one coil fails, M5Post recommends replacing all 8 coils as preventative maintenance ($600-$900 parts + labor) - they typically fail within similar timeframes and saves second service visit. Use OEM Bosch coils for best reliability ($50-$80 each) - aftermarket options fail even faster on S63 due to heat and electrical demands. Replace spark plugs simultaneously if mileage exceeds 30,000 miles ($280-$320 for 8 plugs). Labor: 1-2 hours. Single coil replacement: $179-$235.</x:v>
       </x:c>
       <x:c r="F105" s="9" t="n">
         <x:v>0</x:v>
@@ -8538,21 +9870,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="106" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A106" s="40" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B106" s="9" t="str">
-        <x:v>bmw-m340i-vanos-solenoid-o-ring-failure</x:v>
+        <x:v>bmw-m5-instrument-cluster-pixel-failure-2000</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D106" s="9" t="str">
-        <x:v>VANOS Solenoid O-Ring Failure</x:v>
+        <x:v>Instrument Cluster Pixel Failure and MID Display Dropout</x:v>
       </x:c>
       <x:c r="E106" s="9" t="str">
-        <x:v>Diagnose with a scan tool (VANOS/camshaft position fault codes), then replace the affected intake/exhaust VANOS solenoid(s) and O-rings. Solenoids are relatively inexpensive parts; cost is mostly diagnosis and labor, typically a few hundred dollars.</x:v>
+        <x:v>Diagnosis is usually visual, confirming missing display segments in the cluster or MID. Repair involves replacing or rebuilding the cluster/MID display ribbon and screen components, or sending the unit to a specialist rebuilder. Used replacement clusters require coding and mileage tamper considerations, so rebuild is often preferred.</x:v>
       </x:c>
       <x:c r="F106" s="9" t="n">
         <x:v>0</x:v>
@@ -8561,21 +9893,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="107" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A107" s="40" t="n">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B107" s="9" t="str">
-        <x:v>bmw-m340i-zf-8hp-harsh-jerky-low-speed-shifting-mechatronic-faults</x:v>
+        <x:v>bmw-m5-maf-sensor-degradation-causing-2000</x:v>
       </x:c>
       <x:c r="C107" s="9" t="str">
-        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D107" s="9" t="str">
-        <x:v>ZF 8HP Harsh / Jerky Low-Speed Shifting and Mechatronic Faults</x:v>
+        <x:v>MAF Sensor Degradation Causing Lean Codes, Hesitation, and Reduced Power</x:v>
       </x:c>
       <x:c r="E107" s="9" t="str">
-        <x:v>Perform the ZF 8-speed fluid-and-filter (pan) service rather than treating it as lifetime-fill; this resolves many shift-quality complaints. Let the drivetrain warm before hard driving. For persistent erratic shifting or warning lights, scan the transmission and repair/replace the mechatronic unit (valve body) as needed.</x:v>
+        <x:v>Scan for fuel-trim and MAF-related faults, inspect for intake leaks first, then compare live airflow values bank-to-bank. If readings are implausible or one bank differs significantly, replace the affected MAF sensor(s) with OE-quality parts and clear adaptations; also inspect intake boots and air filter condition.</x:v>
       </x:c>
       <x:c r="F107" s="9" t="n">
         <x:v>0</x:v>
@@ -8584,21 +9916,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="594" hidden="0" customHeight="1">
+    <x:row r="108" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A108" s="40" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B108" s="9" t="str">
-        <x:v>bmw-m3cs-idrive-software-2024</x:v>
+        <x:v>bmw-m5-radiator-end-tank-and-2000</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D108" s="9" t="str">
-        <x:v>iDrive 8 Software Glitches and Screen Blackouts</x:v>
+        <x:v>Radiator End Tank and Expansion Tank Cracking Causing Sudden Coolant Loss and Overheating</x:v>
       </x:c>
       <x:c r="E108" s="9" t="str">
-        <x:v>Check for and install the latest BMW iDrive 8 software updates, which can be delivered over-the-air or at a dealer. Perform a soft reset by holding the iDrive controller button for 30 seconds. If screen blackouts persist, the dealer may need to replace the head unit or update the gateway module firmware. Ensure the 12V battery is in good condition, as low voltage can trigger software instability.</x:v>
+        <x:v>Diagnose with a cooling-system pressure test and inspect the radiator side tanks, expansion tank seams, level sensor area, upper hose neck, and bleed screw area for seepage or cracks. Repair typically involves replacing the failed tank or radiator, and many owners proactively refresh the full cooling system with hoses, cap, thermostat, water pump, and coolant to prevent repeat failures.</x:v>
       </x:c>
       <x:c r="F108" s="9" t="n">
         <x:v>0</x:v>
@@ -8612,16 +9944,16 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B109" s="9" t="str">
-        <x:v>bmw-m3cs-s58-carbon-buildup-2024</x:v>
+        <x:v>bmw-m5-rear-ball-joint-and-2000</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D109" s="9" t="str">
-        <x:v>S58 Intake Valve Carbon Buildup</x:v>
+        <x:v>Rear Ball Joint and Integral Link Wear Causing Clunks, Tire Wear, and Unstable Handling</x:v>
       </x:c>
       <x:c r="E109" s="9" t="str">
-        <x:v>Schedule walnut blast cleaning of the intake valves at 40,000-50,000 mile intervals. Install an oil catch can to reduce oil vapor entering the intake system. Use high-quality synthetic oil meeting BMW LL-01 specification and change at 5,000-7,000 mile intervals. Allow the engine to fully warm up before high-boost driving to ensure proper oil vapor management.</x:v>
+        <x:v>Diagnosis includes checking rear wheel play on a lift, inspecting ball joints and links for torn boots or looseness, and measuring alignment. Repair typically involves replacing worn rear ball joints and links in pairs, followed by a four-wheel alignment. Many owners refresh multiple rear suspension wear items together to restore the M5's original handling precision.</x:v>
       </x:c>
       <x:c r="F109" s="9" t="n">
         <x:v>0</x:v>
@@ -8630,21 +9962,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="110" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A110" s="40" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B110" s="9" t="str">
-        <x:v>bmw-m3cs-s58-charge-pipe-crack-2024</x:v>
+        <x:v>bmw-m5-s63-rod-bearing-2012</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2016 | BMW | M5 | S63</x:v>
       </x:c>
       <x:c r="D110" s="9" t="str">
-        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
+        <x:v>S63 Twin-Turbo V8 Rod Bearing Wear</x:v>
       </x:c>
       <x:c r="E110" s="9" t="str">
-        <x:v>Replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF. These direct-fit replacements handle higher temperatures and pressures without risk of cracking. If the car is under warranty and the failure occurs on stock tune, BMW should cover the repair. Inspect the charge pipe during every service and before track days.</x:v>
+        <x:v>Preventative rod bearing replacement with upgraded BE Bearings or ACL Race bearings every 60,000-80,000 miles. Requires oil pan removal and dropping the crankshaft to access all 8 rod bearings. Use strict 5,000-mile oil change intervals with BMW LL-01 approved 0W-40 oil.</x:v>
       </x:c>
       <x:c r="F110" s="9" t="n">
         <x:v>0</x:v>
@@ -8653,21 +9985,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="396" hidden="0" customHeight="1">
+    <x:row r="111" ht="1122" hidden="0" customHeight="1">
       <x:c r="A111" s="40" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B111" s="9" t="str">
-        <x:v>bmw-m4-charge-pipe-blowoff-2015</x:v>
+        <x:v>bmw-m5-s63-turbo-2012</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2012-2016 | BMW | M5 | S63</x:v>
       </x:c>
       <x:c r="D111" s="9" t="str">
-        <x:v>Plastic Charge Pipe Blow-Off Under Boost</x:v>
+        <x:v>S63 V8 Twin-Turbocharger Failure - F10 M5</x:v>
       </x:c>
       <x:c r="E111" s="9" t="str">
-        <x:v>Replace with an aluminum or silicone charge pipe. This is considered a must-do upgrade for any F82 M4. Many aftermarket options are direct bolt-on replacements. The job takes about 1-2 hours and requires removing the intake duct to access the charge pipe.</x:v>
+        <x:v>Replace failed turbocharger(s) with updated OEM units ($4,000-$6,000 per turbo, $8,000-$12,000 for both). Install BMW TSB heat insulators to protect turbo coolant and oil lines from excessive heat exposure ($200 preventive vs. $8,000+ turbo replacement). Use ONLY high-quality synthetic oil and maintain strict oil change intervals (5,000-7,500 miles MAX - NOT BMW's 10k recommendation). Avoid aggressive driving when engine cold - allow full warm-up before boost. For high-mileage vehicles (80,000+ miles), consider preventative turbo replacement or inspection. M5Post: when one turbo fails, seriously consider replacing both - labor overlap saves $2,000-$3,000 and other will likely fail soon.</x:v>
       </x:c>
       <x:c r="F111" s="9" t="n">
         <x:v>0</x:v>
@@ -8676,21 +10008,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="112" ht="1188" hidden="0" customHeight="1">
       <x:c r="A112" s="40" t="n">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B112" s="9" t="str">
-        <x:v>bmw-m4-convertible-top-2015</x:v>
+        <x:v>bmw-m5-s85-rod-bearing-2006</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D112" s="9" t="str">
-        <x:v>Convertible Top Hydraulic Pump Failure - F83 M4 Convertible</x:v>
+        <x:v>S85 V10 Rod Bearing Premature Failure (CATASTROPHIC) - E60 M5</x:v>
       </x:c>
       <x:c r="E112" s="9" t="str">
-        <x:v>Diagnose specific failure: hydraulic pump motor, lines, microswitches, or latch mechanisms. Pump motor replacement is most common ($1,500-2,500). Check hydraulic fluid level and refill if low. Regular top cycling (minimum once per month) prevents seal degradation. Store with top UP to reduce strain on hydraulic system. Rebuilt hydraulic pumps available at lower cost than new OEM. Complex repair requiring specialized BMW knowledge.</x:v>
+        <x:v>MANDATORY PREVENTATIVE: Replace rod bearings before 70,000 miles ($6,500-$8,600). Upgrade to BE Bearings, ACL Race, or VAC Motorsports high-performance bearings with increased clearances (0.0025" or greater) - DO NOT use OEM BMW bearings which have same design flaw. Perform regular oil analysis every 5,000 miles to detect early bearing wear. Use only BMW-approved 10W-60 synthetic oil with frequent oil changes (5,000-7,500 mile intervals). NEVER redline engine before reaching full operating temperature. Replace high-pressure VANOS line at same time as rod bearings (labor overlap saves $2,000-$3,000). If catastrophic failure occurs: Complete engine replacement required ($15,000-$32,000).</x:v>
       </x:c>
       <x:c r="F112" s="9" t="n">
         <x:v>0</x:v>
@@ -8699,21 +10031,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="113" ht="937.2000122070312" hidden="0" customHeight="1">
       <x:c r="A113" s="40" t="n">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B113" s="9" t="str">
-        <x:v>bmw-m4-cooling-track-2015</x:v>
+        <x:v>bmw-m5-s85-throttle-actuator-2006</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D113" s="9" t="str">
-        <x:v>Cooling System Inadequacy Under Track Use - F82/F83 M4</x:v>
+        <x:v>S85 V10 Throttle Body Actuator Failure - E60 M5</x:v>
       </x:c>
       <x:c r="E113" s="9" t="str">
-        <x:v>Install comprehensive cooling upgrades for track use: CSF or Mishimoto high-capacity radiator, aftermarket oil cooler, upgraded intercoolers (Wagner, CSF), and transmission cooler. Remove kidney grille blockage for improved airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Total cooling system upgrade costs $3,000-5,000 but essential for serious track use. For street-only M4s, stock cooling is adequate.</x:v>
+        <x:v>Replace failed throttle actuator(s) with OEM units ($1,400-$1,700 each) or upgrade to Evolve Automotive uprated throttle actuators ($1,500-$1,800 each) for improved durability and increased lifespan - these have upgraded internal components that prevent repeat failure. ECU Testing and Euro Power Motorsports offer actuator rebuilds ($500-$800 per actuator) as cost-effective alternatives. M5Post consensus: when one actuator fails, replace both at same time to save labor costs since second will fail within 6-12 months. Labor: 3 hours professional / 4+ hours DIY.</x:v>
       </x:c>
       <x:c r="F113" s="9" t="n">
         <x:v>0</x:v>
@@ -8722,21 +10054,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="462" hidden="0" customHeight="1">
+    <x:row r="114" ht="1056" hidden="0" customHeight="1">
       <x:c r="A114" s="40" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B114" s="9" t="str">
-        <x:v>bmw-m4-crank-hub-bolt-2015</x:v>
+        <x:v>bmw-m5-s85-vanos-pump-2006</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2006-2010 | BMW | M5 | S85</x:v>
       </x:c>
       <x:c r="D114" s="9" t="str">
-        <x:v>S55 Crank Hub Bolt Loosening</x:v>
+        <x:v>VANOS High-Pressure Pump &amp; Line Failure (CATASTROPHIC) - E60 M5</x:v>
       </x:c>
       <x:c r="E114" s="9" t="str">
-        <x:v>Replace with an upgraded aftermarket crank hub bolt (ARP or IND). The job requires removing the radiator fan, accessory belt, and harmonic balancer to access the bolt. Use proper torque specs for the upgraded bolt. This is a preventative maintenance item for any M4 owner.</x:v>
+        <x:v>Replace high-pressure VANOS line with updated design that includes proper bend radius ($3,000 parts + labor). Replace VANOS high-pressure pump if showing signs of wear or contamination. DrVanos offers fully rebuilt S85 VANOS pumps ($1,800 + $400 core deposit) - M5Post gold standard for rebuilds. This repair is BEST performed simultaneously with rod bearing replacement to save on overlapping labor costs ($2,000-$4,000 savings). WARNING: DO NOT ignore VANOS line leaks - metal debris from failed pump circulates through entire lubrication system and can destroy engine. If catastrophic failure: engine replacement required ($32,000).</x:v>
       </x:c>
       <x:c r="F114" s="9" t="n">
         <x:v>0</x:v>
@@ -8745,21 +10077,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="115" ht="1188" hidden="0" customHeight="1">
       <x:c r="A115" s="40" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B115" s="9" t="str">
-        <x:v>bmw-m4-dct-clutch-2015</x:v>
+        <x:v>bmw-m5-smg-pump-2006</x:v>
       </x:c>
       <x:c r="C115" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4</x:v>
+        <x:v>2006-2010 | BMW | M5</x:v>
       </x:c>
       <x:c r="D115" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F82/F83 M4</x:v>
+        <x:v>SMG III Hydraulic Pump Failure - E60 M5</x:v>
       </x:c>
       <x:c r="E115" s="9" t="str">
-        <x:v>Replace DCT clutch pack when symptoms appear. BMW recommends replacing all clutches together. Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use (limit to special occasions). Transmission adaptation reset via BMW software may temporarily improve shift quality. Extended warranty highly recommended for DCT-equipped M4s. Labor-intensive repair requires transmission removal.</x:v>
+        <x:v>DIAGNOSIS FIRST: Insist on proper diagnosis before pump replacement - accumulator failure has similar symptoms and costs $500 vs. $5,000. If pump confirmed failed: Try rebuild first - carbon buildup can often be cleaned for fraction of replacement cost. SMG Society and specialty shops offer pump rebuilds ($300 pump + labor + fluids = $1,500-$2,500). If rebuild unsuccessful: Replace SMG pump with OEM or remanufactured unit ($5,000-$7,700 dealership, $5,000-$6,500 independent specialist). Replace hydraulic accumulator at same time if vehicle has 60,000+ miles ($300-$500 additional). Flush and replace SMG hydraulic fluid and manual transmission fluid during pump replacement.</x:v>
       </x:c>
       <x:c r="F115" s="9" t="n">
         <x:v>0</x:v>
@@ -8768,21 +10100,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="462" hidden="0" customHeight="1">
+    <x:row r="116" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A116" s="40" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B116" s="9" t="str">
-        <x:v>bmw-m4-rear-subframe-crack-2015</x:v>
+        <x:v>bmw-m5-timing-chain-guide-wear-2000</x:v>
       </x:c>
       <x:c r="C116" s="9" t="str">
-        <x:v>2015-2026 | BMW | M4</x:v>
+        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
       </x:c>
       <x:c r="D116" s="9" t="str">
-        <x:v>Rear Subframe Cracking From Track Use</x:v>
+        <x:v>Timing Chain Guide Wear and Chain Tensioner Noise on the S62 V8</x:v>
       </x:c>
       <x:c r="E116" s="9" t="str">
-        <x:v>Inspect subframe mounting points and welds regularly if the car sees track use. Reinforce with aftermarket subframe reinforcement plates or weld-in gussets. Severely cracked subframes must be replaced entirely. Upgraded subframe bushings (solid or reinforced) help distribute loads more evenly.</x:v>
+        <x:v>Diagnosis includes listening for chain noise on cold start, inspecting oil/filter for plastic guide debris, and checking timing adaptation/fault data. Repair generally requires replacing timing chain guides, tensioners, related rails, gaskets, and often addressing front-engine seals while disassembled. Preventive service is often recommended once noise appears rather than waiting for a failure.</x:v>
       </x:c>
       <x:c r="F116" s="9" t="n">
         <x:v>0</x:v>
@@ -8791,21 +10123,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="805.2000122070312" hidden="0" customHeight="1">
+    <x:row r="117" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A117" s="40" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B117" s="9" t="str">
-        <x:v>bmw-m4-s55-crank-hub-2015</x:v>
+        <x:v>bmw-m5-torque-converter-shudder-2018</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2018-2023 | BMW | M5</x:v>
       </x:c>
       <x:c r="D117" s="9" t="str">
-        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - F82/F83 M4</x:v>
+        <x:v>ZF 8HP Torque Converter Shudder</x:v>
       </x:c>
       <x:c r="E117" s="9" t="str">
-        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway) that eliminates the slipping issue permanently. Installation requires crankshaft pulley removal and precise torque specs. This upgrade is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Cost is $1,200-2,500 installed vs. $20,000+ for engine replacement after failure.</x:v>
+        <x:v>Perform a transmission fluid and filter change using genuine ZF LifeGuard 8 fluid. If the shudder persists, the torque converter must be replaced. BMW issued a service bulletin for some VINs. A software update for shift calibration may also help in mild cases.</x:v>
       </x:c>
       <x:c r="F117" s="9" t="n">
         <x:v>0</x:v>
@@ -8814,44 +10146,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="118" ht="1108.800048828125" hidden="0" customHeight="1">
       <x:c r="A118" s="40" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B118" s="9" t="str">
-        <x:v>bmw-m4-s55-injector-2015</x:v>
+        <x:v>bmw-m5-valve-stem-seals-2012</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2012-2023 | BMW | M5</x:v>
       </x:c>
       <x:c r="D118" s="9" t="str">
-        <x:v>S55 High-Pressure Fuel Injector Failure - F82/F83 M4</x:v>
+        <x:v>S63/S63TU Valve Stem Seal Failure &amp; Oil Consumption</x:v>
       </x:c>
       <x:c r="E118" s="9" t="str">
-        <x:v>Replace all 6 injectors together to prevent repeat repairs. Perform walnut blast carbon cleaning on intake valves while injectors are removed (labor overlap saves $400-600). Use Top Tier gasoline to minimize carbon buildup. Add fuel system cleaner (Liqui Moly Valve Clean) every 5,000 miles to reduce carbon deposits. BMW parts are expensive; some shops use OEM Bosch injectors at lower cost. Labor is 4-6 hours for injector replacement.</x:v>
+        <x:v>Replace valve stem seals with updated OEM or performance seals ($3,500-$10,000 depending on method). Labor-intensive repair requiring either cylinder head removal ($6,000-$10,000) or specialized valve spring compressor tools with heads on engine ($3,500-$6,000). Address issue EARLY to prevent catalytic converter damage from oil burning (adds $3,000-$5,000 to repair). Perform more frequent oil changes (5,000 miles) to minimize damage. Blue smoke test: let engine idle 30+ minutes until hot, then rev to redline briefly - big blue smoke plume = valve seals. Find shop that can replace valve seals with heads installed (specialized tools required) - saves $4,000+ in labor vs. full head removal.</x:v>
       </x:c>
       <x:c r="F118" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G118" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="119" ht="528" hidden="0" customHeight="1">
       <x:c r="A119" s="40" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B119" s="9" t="str">
-        <x:v>bmw-m4-s55-rod-bearing-2015</x:v>
+        <x:v>bmw-m6-e63-e64-active-steering-steering-gear-play-knock</x:v>
       </x:c>
       <x:c r="C119" s="9" t="str">
-        <x:v>2015-2020 | BMW | M4 | S55</x:v>
+        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>S55 Rod Bearing Premature Wear - F82/F83 M4</x:v>
+        <x:v>E63/E64 Active Steering and Steering-Gear Play / Knock</x:v>
       </x:c>
       <x:c r="E119" s="9" t="str">
-        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles or before extensive track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability than OEM. Regular oil analysis (Blackstone Labs) every 5,000 miles to monitor bearing wear. Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max. Track-focused M4s should replace bearings every 50,000 miles. Labor is 8-12 hours, so many owners do this during clutch replacement.</x:v>
+        <x:v>Inspect the steering gear and front control-arm/thrust-arm bushings for play. Replace worn control-arm bushings/ball joints first as they are cheaper and frequently the source of the knock; if the steering rack/gear itself has internal play or leaks, it requires replacement (a significant cost) followed by an alignment.</x:v>
       </x:c>
       <x:c r="F119" s="9" t="n">
         <x:v>0</x:v>
@@ -8860,21 +10192,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="660" hidden="0" customHeight="1">
+    <x:row r="120" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A120" s="40" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B120" s="9" t="str">
-        <x:v>bmw-m4cs-brake-wear-track-2024</x:v>
+        <x:v>bmw-m6-f12-convertible-top-hydraulic-pump-relay-failure</x:v>
       </x:c>
       <x:c r="C120" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Convertible (F12) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D120" s="9" t="str">
-        <x:v>Rapid Brake Pad and Rotor Wear from Track Use</x:v>
+        <x:v>F12 Convertible Top Hydraulic Pump and Relay Failure</x:v>
       </x:c>
       <x:c r="E120" s="9" t="str">
-        <x:v>Inspect brake pads and rotors before and after every track day. Consider upgrading to aftermarket performance pads like Pagid RSC or Hawk DTC-70 for track use, and switch to street pads for daily driving. For frequent track users, the optional carbon ceramic brake package significantly extends rotor life. Use high-temperature brake fluid (DOT 5.1 or racing fluid) and flush before every track season.</x:v>
+        <x:v>Diagnose whether the fault is the pump's high-current relays (relatively cheap, often the cure), a pressure loss in the pump, a hydraulic leak, or a roof microswitch/sensor. Replace the relays first; if pressure loss persists, rebuild or replace the hydraulic pump unit (specialist rebuild services exist) and renew worn seals/sensors. Bleed and refill the hydraulic system after repair.</x:v>
       </x:c>
       <x:c r="F120" s="9" t="n">
         <x:v>0</x:v>
@@ -8883,21 +10215,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="462" hidden="0" customHeight="1">
+    <x:row r="121" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A121" s="40" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B121" s="9" t="str">
-        <x:v>bmw-m4cs-s58-carbon-buildup-2024</x:v>
+        <x:v>bmw-m6-f12-f13-7-speed-m-dct-mechatronic-clutch-pack-failure</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
-        <x:v>S58 Intake Valve Carbon Buildup</x:v>
+        <x:v>F12/F13 7-Speed M-DCT Mechatronic and Clutch Pack Failure</x:v>
       </x:c>
       <x:c r="E121" s="9" t="str">
-        <x:v>Walnut blast the intake valves every 40,000-50,000 miles. Consider installing an oil catch can to reduce oil vapor ingestion. Maintain strict 5,000-7,000 mile oil change intervals with BMW LL-01 approved oil. Allow full engine warmup before spirited driving to ensure proper crankcase ventilation operation.</x:v>
+        <x:v>Scan for transmission codes to confirm whether the fault is the mechatronic unit or worn clutch packs. Mechatronic units can often be repaired/replaced and must be reprogrammed and adapted to the vehicle afterward. Worn clutch packs require a clutch replacement (dealer cost often $3,000-$5,000). Regular DCT fluid and filter changes help prevent premature wear; avoid prolonged clutch slip in traffic.</x:v>
       </x:c>
       <x:c r="F121" s="9" t="n">
         <x:v>0</x:v>
@@ -8906,21 +10238,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="122" ht="594" hidden="0" customHeight="1">
       <x:c r="A122" s="40" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B122" s="9" t="str">
-        <x:v>bmw-m4cs-s58-charge-pipe-crack-2024</x:v>
+        <x:v>bmw-m6-f12-f13-electric-water-pump-thermostat-failure</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
-        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D122" s="9" t="str">
-        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
+        <x:v>F12/F13 Electric Water Pump and Thermostat Failure</x:v>
       </x:c>
       <x:c r="E122" s="9" t="str">
-        <x:v>Proactively replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF before any track use. These bolt-on replacements are rated for boost pressures well beyond what the S58 produces. Inspect the charge pipe at every service interval for signs of stress cracking or discoloration.</x:v>
+        <x:v>Replace the failed electric water pump and/or electronic thermostat with OEM units; inspect the radiator end-tanks and expansion tank for cracks and replace as needed. Pressure-test the cooling system, refresh coolant, and treat the pump/thermostat as wear items given the heat load. Address any overheating event immediately to avoid secondary engine damage.</x:v>
       </x:c>
       <x:c r="F122" s="9" t="n">
         <x:v>0</x:v>
@@ -8929,21 +10261,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="660" hidden="0" customHeight="1">
+    <x:row r="123" ht="528" hidden="0" customHeight="1">
       <x:c r="A123" s="40" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B123" s="9" t="str">
-        <x:v>bmw-m5-absdsc-module-failure-triggering-2000</x:v>
+        <x:v>bmw-m6-f12-f13-turbocharger-wastegate-rattle-oil-starvation</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D123" s="9" t="str">
-        <x:v>ABS/DSC Module Failure Triggering ABS, Brake, and Traction Control Warning Lights</x:v>
+        <x:v>F12/F13 Turbocharger Wastegate Rattle and Oil Starvation</x:v>
       </x:c>
       <x:c r="E123" s="9" t="str">
-        <x:v>Diagnosis should begin with scanning the ABS/DSC module for communication or wheel-speed sensor faults and verifying power, ground, and sensor signals. If the module intermittently loses communication or shows implausible internal faults, the usual repair is module rebuild or replacement, followed by coding if required. Wheel speed sensors should only be replaced after confirming they are actually faulty.</x:v>
+        <x:v>Confirm wastegate rattle by listening at light throttle; worn actuators/linkages can be replaced or upgraded. For oil starvation, maintain strict oil-change intervals with the correct specification, allow proper cool-down after hard driving, and keep the cooling system healthy. Severely worn or whining turbos require rebuild or replacement.</x:v>
       </x:c>
       <x:c r="F123" s="9" t="n">
         <x:v>0</x:v>
@@ -8952,21 +10284,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="124" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A124" s="40" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B124" s="9" t="str">
-        <x:v>bmw-m5-clutch-slave-cylinder-and-2000</x:v>
+        <x:v>bmw-m6-rod-bearing-wear-2005</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2005-2019 | BMW | M6 | S65, S63</x:v>
       </x:c>
       <x:c r="D124" s="9" t="str">
-        <x:v>Clutch Slave Cylinder and Hydraulic Line Failure Causing Soft Pedal and Shift Engagement Problems</x:v>
+        <x:v>Rod Bearing Premature Wear (S65/S63 Engines)</x:v>
       </x:c>
       <x:c r="E124" s="9" t="str">
-        <x:v>Inspect the clutch hydraulic circuit for fluid leakage at the slave cylinder, master cylinder, and line connections, and verify brake/clutch fluid condition. Replace the failed slave cylinder and often the flexible hose, then bleed the system thoroughly; if symptoms persist, inspect the clutch, pressure plate, and pilot bearing.</x:v>
+        <x:v>Perform a preventive rod bearing replacement between 60,000-80,000 miles on S65 engines, and inspect by 80,000-100,000 miles on S63 engines. Use upgraded ACL or King XP bearings with coated surfaces. Cut and send used oil filter for analysis — bearing material particles indicate wear progression. The job requires engine-out on the S65 (approximately 20 hours labor) or can be done in-car on the S63 with the oil pan dropped.</x:v>
       </x:c>
       <x:c r="F124" s="9" t="n">
         <x:v>0</x:v>
@@ -8975,21 +10307,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="125" ht="528" hidden="0" customHeight="1">
       <x:c r="A125" s="40" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B125" s="9" t="str">
-        <x:v>bmw-m5-dct-clutch-2012</x:v>
+        <x:v>bmw-m6-s63-carbon-buildup-intake-valves</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D125" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Wear &amp; Judder - F10 M5</x:v>
+        <x:v>S63 Carbon Buildup on Intake Valves (Direct Injection)</x:v>
       </x:c>
       <x:c r="E125" s="9" t="str">
-        <x:v>PREVENTIVE: Replace DCT transmission fluid and filter every 30,000-50,000 miles (BMW says "lifetime" but this causes premature failure). Use ONLY BMW DCTF-1 specification fluid ($189-$253 service, DIY: $100-$150). For judder/jerkiness: try fluid change and software update FIRST before clutch replacement - many issues resolved this way. For severe clutch wear: replace dual-clutch assembly with OEM ($2,394-$2,567 typical, $3,000-$4,000 dealership) or upgraded performance clutch kit. Consider NRC TitanTec or CNS Racing upgraded DCT clutch packs for improved durability if used for performance driving/track. Complete DCT transmission replacement: $8,000-$12,000.</x:v>
+        <x:v>Have the intake valves walnut-blasted (media-blast cleaning) to remove carbon deposits without removing the cylinder heads. Many owners do this every 50,000-70,000 km. A properly functioning PCV/crankcase ventilation system and quality oil reduce deposit rate. An oil-catch can is sometimes fitted to slow accumulation.</x:v>
       </x:c>
       <x:c r="F125" s="9" t="n">
         <x:v>0</x:v>
@@ -8998,21 +10330,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="126" ht="528" hidden="0" customHeight="1">
       <x:c r="A126" s="40" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B126" s="9" t="str">
-        <x:v>bmw-m5-door-vapor-barrier-and-2000</x:v>
+        <x:v>bmw-m6-s63-high-pressure-fuel-pump-fuel-injector-cold-start-misfire</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
       </x:c>
       <x:c r="D126" s="9" t="str">
-        <x:v>Door Vapor Barrier and Sunroof Drain Leaks Causing Wet Carpets and Electrical Problems</x:v>
+        <x:v>S63 High-Pressure Fuel Pump / Fuel Injector Cold-Start Misfire</x:v>
       </x:c>
       <x:c r="E126" s="9" t="str">
-        <x:v>Remove the door panel and inspect the vapor barrier seal, especially along the lower edge, and verify all sunroof drains flow freely and exit properly. Reseal the vapor barrier with butyl ribbon or equivalent body sealer, clear the drains, dry the carpet and padding thoroughly, and inspect under-carpet wiring/connectors for corrosion.</x:v>
+        <x:v>Scan for misfire and fuel-system codes and test cold-start fuel-rail pressure. Replace a failing HPFP; for injector faults, replace the affected injector(s) with units of the correct matching index code (do not mix injector indexes on a bank) and re-code them. Address per the relevant BMW technical service bulletin for the N63/S63.</x:v>
       </x:c>
       <x:c r="F126" s="9" t="n">
         <x:v>0</x:v>
@@ -9021,21 +10353,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="127" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A127" s="40" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B127" s="9" t="str">
-        <x:v>bmw-m5-e39-m5-vanos-solenoidseal-2000</x:v>
+        <x:v>bmw-m6-s63-rod-bearing-2013</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2013-2018 | BMW | M6 | S63</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>E39 M5 VANOS Solenoid/Seal Failure Causing Rattle, Power Loss, and Check Engine Lights</x:v>
+        <x:v>S63 Twin-Turbo V8 Rod Bearing Concerns (F06/F12/F13 M6)</x:v>
       </x:c>
       <x:c r="E127" s="9" t="str">
-        <x:v>Diagnosis typically includes scanning for camshaft timing and VANOS activation faults, checking oil condition/pressure, and listening for startup rattle from the front of the engine. Repair usually involves rebuilding the VANOS units with upgraded seals, replacing failed solenoids or solenoid seals, and correcting any oil leaks or timing-related wear. Many owners address both banks preventively while the front of engine is apart.</x:v>
+        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles using ACL Race Rod Bearings 8B1578HX-STD ($150-250), King Bearings SV Series, or WPC-treated bearings from Lang Racing. Cost: $4,000-7,000 for preventive replacement. Oil changes every 5,000-7,500 miles mandatory (ignore BMW's 10,000-mile recommendation). Use Blackstone Labs oil analysis ($30/test) every 5,000 miles to monitor bearing wear metals. Preventive replacement recommended for peace of mind, especially on cars used for track days or spirited driving.</x:v>
       </x:c>
       <x:c r="F127" s="9" t="n">
         <x:v>0</x:v>
@@ -9044,21 +10376,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="128" ht="1069.199951171875" hidden="0" customHeight="1">
       <x:c r="A128" s="40" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B128" s="9" t="str">
-        <x:v>bmw-m5-front-thrust-arm-bushing-2000</x:v>
+        <x:v>bmw-m6-s85-rod-bearing-2006</x:v>
       </x:c>
       <x:c r="C128" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2006-2010 | BMW | M6 | S85</x:v>
       </x:c>
       <x:c r="D128" s="9" t="str">
-        <x:v>Front Thrust Arm Bushing Failure Causing 50-60 MPH Brake Shimmy and Steering Vibration</x:v>
+        <x:v>S85 V10 Rod Bearing Failure (Catastrophic Engine Destruction)</x:v>
       </x:c>
       <x:c r="E128" s="9" t="str">
-        <x:v>Inspect the front thrust arms and control arms for bushing cracks, fluid leakage from hydro-bushings, and ball-joint play. Replace the thrust arms or complete front control arm set, then perform a proper alignment; if brake pulsation remains, inspect rotor runout and wheel balance.</x:v>
+        <x:v>MANDATORY PREVENTIVE REPLACEMENT before 70,000 miles: Replace all 10 rod bearings with ACL Race Bearings 10B1580HX-STD (+0.001" clearance, $200-350) or WPC-treated bearings from Lang Racing, or VAC Motorsports kit VAC-HPRBK-S85, or Turner kit TMS222798, or FCP Euro kit 11247841703KT3. ALSO replace VANOS line 11367838669 and use ARP rod bolts (included in most kits). Cost: $6,500-9,500 preventive. If engine is destroyed from bearing failure: $15,000-32,000 for engine replacement or rebuild. NEVER use OEM bearings as replacements. Use Blackstone Labs oil analysis every 5,000 miles ($30/test) to monitor bearing wear metals.</x:v>
       </x:c>
       <x:c r="F128" s="9" t="n">
         <x:v>0</x:v>
@@ -9067,21 +10399,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="594" hidden="0" customHeight="1">
+    <x:row r="129" ht="924" hidden="0" customHeight="1">
       <x:c r="A129" s="40" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B129" s="9" t="str">
-        <x:v>bmw-m5-getrag-420g-6-speed-synchro-2000</x:v>
+        <x:v>bmw-m6-s85-throttle-actuator-2006</x:v>
       </x:c>
       <x:c r="C129" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2006-2010 | BMW | M6 | S85</x:v>
       </x:c>
       <x:c r="D129" s="9" t="str">
-        <x:v>Getrag 420G 6-Speed Synchro Wear and 2nd/3rd Gear Grinding</x:v>
+        <x:v>S85 V10 Throttle Actuator Failure (Plastic Gear Stripping)</x:v>
       </x:c>
       <x:c r="E129" s="9" t="str">
-        <x:v>Diagnosis involves road testing hot and cold, checking clutch release operation, and ruling out worn transmission mounts or old fluid before condemning the gearbox. Mild cases may improve with fresh fluid, but persistent grinding usually requires transmission rebuild with new synchros, bearings, and wear components. Clutch and shifter bushings are often serviced at the same time.</x:v>
+        <x:v>Rebuild throttle actuators using Beisan Systems BS101 sintered metal gear kit ($250/set, need 2 sets for both actuators) for permanent fix. Beisan BS102 full rebuild service available ($300). Alternatively, rebuilt actuators from Euro Power Motorsports ($500-800 each). OEM replacement actuators from BMW cost $2,000-4,500. Total cost: $500-4,500 depending on approach. Beisan Systems sintered metal gears are THE permanent fix - they replace the weak plastic PPA gears with metal gears that will not strip. Always rebuild both actuators simultaneously.</x:v>
       </x:c>
       <x:c r="F129" s="9" t="n">
         <x:v>0</x:v>
@@ -9090,21 +10422,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="130" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A130" s="40" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B130" s="9" t="str">
-        <x:v>bmw-m5-ignition-coils-2012</x:v>
+        <x:v>bmw-m6-s85-v10-vanos-high-pressure-oil-pump-failure</x:v>
       </x:c>
       <x:c r="C130" s="9" t="str">
-        <x:v>2012-2023 | BMW | M5 | S63, S63TU</x:v>
+        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
       </x:c>
       <x:c r="D130" s="9" t="str">
-        <x:v>S63/S63TU Ignition Coil Premature Failure</x:v>
+        <x:v>S85 V10 VANOS High-Pressure Oil Pump Failure</x:v>
       </x:c>
       <x:c r="E130" s="9" t="str">
-        <x:v>Replace failed ignition coil(s) immediately to prevent catalytic converter damage ($3,000-$5,000 additional). When one coil fails, M5Post recommends replacing all 8 coils as preventative maintenance ($600-$900 parts + labor) - they typically fail within similar timeframes and saves second service visit. Use OEM Bosch coils for best reliability ($50-$80 each) - aftermarket options fail even faster on S63 due to heat and electrical demands. Replace spark plugs simultaneously if mileage exceeds 30,000 miles ($280-$320 for 8 plugs). Labor: 1-2 hours. Single coil replacement: $179-$235.</x:v>
+        <x:v>Perform an oil-pressure test on the VANOS circuit at the first sign of cold-start knocking. Replace or professionally rebuild the high-pressure VANOS pump and renew the high-pressure lines/seals. Many owners do the VANOS pump preventively at the same time as the rod-bearing service since the oil pan is already removed. Use only BMW-spec oil and strict change intervals to prolong pump life.</x:v>
       </x:c>
       <x:c r="F130" s="9" t="n">
         <x:v>0</x:v>
@@ -9113,21 +10445,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="131" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A131" s="40" t="n">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B131" s="9" t="str">
-        <x:v>bmw-m5-instrument-cluster-pixel-failure-2000</x:v>
+        <x:v>bmw-m6-smg-pump-failure-2005</x:v>
       </x:c>
       <x:c r="C131" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2005-2010 | BMW | M6</x:v>
       </x:c>
       <x:c r="D131" s="9" t="str">
-        <x:v>Instrument Cluster Pixel Failure and MID Display Dropout</x:v>
+        <x:v>SMG Hydraulic Pump and Clutch Actuator Failure</x:v>
       </x:c>
       <x:c r="E131" s="9" t="str">
-        <x:v>Diagnosis is usually visual, confirming missing display segments in the cluster or MID. Repair involves replacing or rebuilding the cluster/MID display ribbon and screen components, or sending the unit to a specialist rebuilder. Used replacement clusters require coding and mileage tamper considerations, so rebuild is often preferred.</x:v>
+        <x:v>Replace the SMG hydraulic pump and pressure accumulator. Bleed and refill the SMG hydraulic system with Pentosin CHF 11S fluid. Many owners convert to a traditional 6-speed manual swap using an aftermarket kit from companies like OS Giken or using the E90 M3 6MT parts. Budget $2,000-4,000 for SMG repair or $5,000-8,000 for a manual conversion.</x:v>
       </x:c>
       <x:c r="F131" s="9" t="n">
         <x:v>0</x:v>
@@ -9136,21 +10468,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="501.6000061035156" hidden="0" customHeight="1">
+    <x:row r="132" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A132" s="40" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B132" s="9" t="str">
-        <x:v>bmw-m5-maf-sensor-degradation-causing-2000</x:v>
+        <x:v>bmw-m8-adaptive-suspension-leak-2020</x:v>
       </x:c>
       <x:c r="C132" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2020-2025 | BMW | M8</x:v>
       </x:c>
       <x:c r="D132" s="9" t="str">
-        <x:v>MAF Sensor Degradation Causing Lean Codes, Hesitation, and Reduced Power</x:v>
+        <x:v>Adaptive Suspension Damper Leaks</x:v>
       </x:c>
       <x:c r="E132" s="9" t="str">
-        <x:v>Scan for fuel-trim and MAF-related faults, inspect for intake leaks first, then compare live airflow values bank-to-bank. If readings are implausible or one bank differs significantly, replace the affected MAF sensor(s) with OE-quality parts and clear adaptations; also inspect intake boots and air filter condition.</x:v>
+        <x:v>Replace the leaking damper(s). BMW adaptive dampers must be replaced as complete units — they cannot be rebuilt. After replacement, a suspension calibration via ISTA is required to integrate the new damper into the adaptive system. Replacing in pairs (front or rear axle) is recommended.</x:v>
       </x:c>
       <x:c r="F132" s="9" t="n">
         <x:v>0</x:v>
@@ -9159,21 +10491,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="133" ht="990" hidden="0" customHeight="1">
       <x:c r="A133" s="40" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B133" s="9" t="str">
-        <x:v>bmw-m5-radiator-end-tank-and-2000</x:v>
+        <x:v>bmw-m8-carbon-ceramic-brakes-2020</x:v>
       </x:c>
       <x:c r="C133" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2020-2024 | BMW | M8</x:v>
       </x:c>
       <x:c r="D133" s="9" t="str">
-        <x:v>Radiator End Tank and Expansion Tank Cracking Causing Sudden Coolant Loss and Overheating</x:v>
+        <x:v>M8 Carbon Ceramic Brake (CCB) Issues</x:v>
       </x:c>
       <x:c r="E133" s="9" t="str">
-        <x:v>Diagnose with a cooling-system pressure test and inspect the radiator side tanks, expansion tank seams, level sensor area, upper hose neck, and bleed screw area for seepage or cracks. Repair typically involves replacing the failed tank or radiator, and many owners proactively refresh the full cooling system with hoses, cap, thermostat, water pump, and coolant to prevent repeat failures.</x:v>
+        <x:v>Replace damaged CCB rotors ($3,000-$4,000 per corner, $12,000-$16,000 for all four). CCB rotors cannot be resurfaced - replacement is only option. Alternatively, convert to iron rotors using BimmerWorld CCB-to-iron conversion kit ($3,000-$5,000 total for all four corners) for dramatically lower running costs. PREVENTION: Avoid driving through standing water with hot brakes (thermal shock cracks rotors). Avoid aggressive braking over potholes or road debris. Squealing at low speed is normal for CCB material - not a defect. If only using car for street driving, iron conversion is more practical and cost-effective.</x:v>
       </x:c>
       <x:c r="F133" s="9" t="n">
         <x:v>0</x:v>
@@ -9182,21 +10514,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="134" ht="396" hidden="0" customHeight="1">
       <x:c r="A134" s="40" t="n">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B134" s="9" t="str">
-        <x:v>bmw-m5-rear-ball-joint-and-2000</x:v>
+        <x:v>bmw-m8-s63tu4-oil-consumption-2020</x:v>
       </x:c>
       <x:c r="C134" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2020-2025 | BMW | M8 | S63TU4</x:v>
       </x:c>
       <x:c r="D134" s="9" t="str">
-        <x:v>Rear Ball Joint and Integral Link Wear Causing Clunks, Tire Wear, and Unstable Handling</x:v>
+        <x:v>S63TU4 V8 Excessive Oil Consumption</x:v>
       </x:c>
       <x:c r="E134" s="9" t="str">
-        <x:v>Diagnosis includes checking rear wheel play on a lift, inspecting ball joints and links for torn boots or looseness, and measuring alignment. Repair typically involves replacing worn rear ball joints and links in pairs, followed by a four-wheel alignment. Many owners refresh multiple rear suspension wear items together to restore the M5's original handling precision.</x:v>
+        <x:v>Monitor oil level regularly using iDrive oil level check. For excessive consumption beyond BMW's threshold, valve stem seal replacement may be warranted under warranty. Updated piston rings are available for severe cases. Always keep oil topped up between changes.</x:v>
       </x:c>
       <x:c r="F134" s="9" t="n">
         <x:v>0</x:v>
@@ -9205,21 +10537,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="135" ht="858" hidden="0" customHeight="1">
       <x:c r="A135" s="40" t="n">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B135" s="9" t="str">
-        <x:v>bmw-m5-s63-rod-bearing-2012</x:v>
+        <x:v>bmw-m8-s63tu4-rod-bearing-2020</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5 | S63</x:v>
+        <x:v>2020-2024 | BMW | M8</x:v>
       </x:c>
       <x:c r="D135" s="9" t="str">
-        <x:v>S63 Twin-Turbo V8 Rod Bearing Wear</x:v>
+        <x:v>S63TU4 Rod Bearing Wear (M8/M8 Competition)</x:v>
       </x:c>
       <x:c r="E135" s="9" t="str">
-        <x:v>Preventative rod bearing replacement with upgraded BE Bearings or ACL Race bearings every 60,000-80,000 miles. Requires oil pan removal and dropping the crankshaft to access all 8 rod bearings. Use strict 5,000-mile oil change intervals with BMW LL-01 approved 0W-40 oil.</x:v>
+        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles or sooner if tracked ($5,000-$8,000). Use ACL Race bearings 8B1578HX-STD ($200-350) which have wider clearance tolerances than OEM for better oil film protection. Monitor bearing health with Blackstone Labs oil analysis ($30/sample) every oil change - elevated copper/lead indicates bearing wear starting. If bearings have failed: engine replacement required ($20,000-$40,000). CRITICAL: If you hear any knocking from bottom end, stop driving immediately and tow to shop.</x:v>
       </x:c>
       <x:c r="F135" s="9" t="n">
         <x:v>0</x:v>
@@ -9228,21 +10560,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="1122" hidden="0" customHeight="1">
+    <x:row r="136" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A136" s="40" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B136" s="9" t="str">
-        <x:v>bmw-m5-s63-turbo-2012</x:v>
+        <x:v>bmw-n54-hpfp</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
-        <x:v>2012-2016 | BMW | M5 | S63</x:v>
+        <x:v>2007-2010 | BMW | 3 Series | N54</x:v>
       </x:c>
       <x:c r="D136" s="9" t="str">
-        <x:v>S63 V8 Twin-Turbocharger Failure - F10 M5</x:v>
+        <x:v>N54 Long Crank or Power Loss Requires Fuel-Pressure Diagnosis</x:v>
       </x:c>
       <x:c r="E136" s="9" t="str">
-        <x:v>Replace failed turbocharger(s) with updated OEM units ($4,000-$6,000 per turbo, $8,000-$12,000 for both). Install BMW TSB heat insulators to protect turbo coolant and oil lines from excessive heat exposure ($200 preventive vs. $8,000+ turbo replacement). Use ONLY high-quality synthetic oil and maintain strict oil change intervals (5,000-7,500 miles MAX - NOT BMW's 10k recommendation). Avoid aggressive driving when engine cold - allow full warm-up before boost. For high-mileage vehicles (80,000+ miles), consider preventative turbo replacement or inspection. M5Post: when one turbo fails, seriously consider replacing both - labor overlap saves $2,000-$3,000 and other will likely fail soon.</x:v>
+        <x:v>Have a BMW-qualified technician read fault memory and follow the bulletin pressure tests for 2FBF, 29DC, 29F1 or 29F2 before replacing the pump. The historical ten-year/120,000-mile emissions-warranty extension has expired for this population and is not a current coverage promise. ShowMeTheParts resolved three 2009 335i fuel-pump candidates, but catalog fitment is not diagnosis or remedy proof and no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F136" s="9" t="n">
         <x:v>0</x:v>
@@ -9251,21 +10583,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="1188" hidden="0" customHeight="1">
+    <x:row r="137" ht="290.3999938964844" hidden="0" customHeight="1">
       <x:c r="A137" s="40" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B137" s="9" t="str">
-        <x:v>bmw-m5-s85-rod-bearing-2006</x:v>
+        <x:v>bmw-n55-boost-solenoid-2012</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
       </x:c>
       <x:c r="D137" s="9" t="str">
-        <x:v>S85 V10 Rod Bearing Premature Failure (CATASTROPHIC) - E60 M5</x:v>
+        <x:v>Wastegate/Boost Solenoid Issues</x:v>
       </x:c>
       <x:c r="E137" s="9" t="str">
-        <x:v>MANDATORY PREVENTATIVE: Replace rod bearings before 70,000 miles ($6,500-$8,600). Upgrade to BE Bearings, ACL Race, or VAC Motorsports high-performance bearings with increased clearances (0.0025" or greater) - DO NOT use OEM BMW bearings which have same design flaw. Perform regular oil analysis every 5,000 miles to detect early bearing wear. Use only BMW-approved 10W-60 synthetic oil with frequent oil changes (5,000-7,500 mile intervals). NEVER redline engine before reaching full operating temperature. Replace high-pressure VANOS line at same time as rod bearings (labor overlap saves $2,000-$3,000). If catastrophic failure occurs: Complete engine replacement required ($15,000-$32,000).</x:v>
+        <x:v>Diagnose boost system for proper operation. Replace wastegate actuator or boost solenoid as needed. Check vacuum lines for leaks. Software update may address some issues.</x:v>
       </x:c>
       <x:c r="F137" s="9" t="n">
         <x:v>0</x:v>
@@ -9274,21 +10606,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="138" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A138" s="40" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B138" s="9" t="str">
-        <x:v>bmw-m5-s85-throttle-actuator-2006</x:v>
+        <x:v>bmw-n55-carbon-buildup-2012</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
       </x:c>
       <x:c r="D138" s="9" t="str">
-        <x:v>S85 V10 Throttle Body Actuator Failure - E60 M5</x:v>
+        <x:v>Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E138" s="9" t="str">
-        <x:v>Replace failed throttle actuator(s) with OEM units ($1,400-$1,700 each) or upgrade to Evolve Automotive uprated throttle actuators ($1,500-$1,800 each) for improved durability and increased lifespan - these have upgraded internal components that prevent repeat failure. ECU Testing and Euro Power Motorsports offer actuator rebuilds ($500-$800 per actuator) as cost-effective alternatives. M5Post consensus: when one actuator fails, replace both at same time to save labor costs since second will fail within 6-12 months. Labor: 3 hours professional / 4+ hours DIY.</x:v>
+        <x:v>Walnut blast cleaning of intake valves every 50,000-70,000 miles. Install catch can to reduce oil vapor. Use quality fuel. BMW port injection on later engines helps reduce this issue.</x:v>
       </x:c>
       <x:c r="F138" s="9" t="n">
         <x:v>0</x:v>
@@ -9297,21 +10629,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="1056" hidden="0" customHeight="1">
+    <x:row r="139" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A139" s="40" t="n">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B139" s="9" t="str">
-        <x:v>bmw-m5-s85-vanos-pump-2006</x:v>
+        <x:v>bmw-n55-charge-pipe-2012</x:v>
       </x:c>
       <x:c r="C139" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5 | S85</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>VANOS High-Pressure Pump &amp; Line Failure (CATASTROPHIC) - E60 M5</x:v>
+        <x:v>Charge Pipe Failure/Cracking</x:v>
       </x:c>
       <x:c r="E139" s="9" t="str">
-        <x:v>Replace high-pressure VANOS line with updated design that includes proper bend radius ($3,000 parts + labor). Replace VANOS high-pressure pump if showing signs of wear or contamination. DrVanos offers fully rebuilt S85 VANOS pumps ($1,800 + $400 core deposit) - M5Post gold standard for rebuilds. This repair is BEST performed simultaneously with rod bearing replacement to save on overlapping labor costs ($2,000-$4,000 savings). WARNING: DO NOT ignore VANOS line leaks - metal debris from failed pump circulates through entire lubrication system and can destroy engine. If catastrophic failure: engine replacement required ($32,000).</x:v>
+        <x:v>Replace with upgraded aluminum charge pipe for reliability. If keeping stock, inspect regularly for cracks. Upgraded pipe is recommended for any tuned vehicle. Installation is relatively straightforward.</x:v>
       </x:c>
       <x:c r="F139" s="9" t="n">
         <x:v>0</x:v>
@@ -9320,21 +10652,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="1188" hidden="0" customHeight="1">
+    <x:row r="140" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A140" s="40" t="n">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B140" s="9" t="str">
-        <x:v>bmw-m5-smg-pump-2006</x:v>
+        <x:v>bmw-n55-injector-2012</x:v>
       </x:c>
       <x:c r="C140" s="9" t="str">
-        <x:v>2006-2010 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D140" s="9" t="str">
-        <x:v>SMG III Hydraulic Pump Failure - E60 M5</x:v>
+        <x:v>High-Pressure Fuel Injector Issues</x:v>
       </x:c>
       <x:c r="E140" s="9" t="str">
-        <x:v>DIAGNOSIS FIRST: Insist on proper diagnosis before pump replacement - accumulator failure has similar symptoms and costs $500 vs. $5,000. If pump confirmed failed: Try rebuild first - carbon buildup can often be cleaned for fraction of replacement cost. SMG Society and specialty shops offer pump rebuilds ($300 pump + labor + fluids = $1,500-$2,500). If rebuild unsuccessful: Replace SMG pump with OEM or remanufactured unit ($5,000-$7,700 dealership, $5,000-$6,500 independent specialist). Replace hydraulic accumulator at same time if vehicle has 60,000+ miles ($300-$500 additional). Flush and replace SMG hydraulic fluid and manual transmission fluid during pump replacement.</x:v>
+        <x:v>Replace failed injector(s) with correct index version. Consider cleaning service for carbon buildup. Use quality fuel. All injectors should be same index for proper operation.</x:v>
       </x:c>
       <x:c r="F140" s="9" t="n">
         <x:v>0</x:v>
@@ -9343,21 +10675,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="141" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A141" s="40" t="n">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B141" s="9" t="str">
-        <x:v>bmw-m5-timing-chain-guide-wear-2000</x:v>
+        <x:v>bmw-n55-oil-filter-housing-2012</x:v>
       </x:c>
       <x:c r="C141" s="9" t="str">
-        <x:v>2000-2003 | BMW | M5 | 4.9L S62 V8</x:v>
+        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D141" s="9" t="str">
-        <x:v>Timing Chain Guide Wear and Chain Tensioner Noise on the S62 V8</x:v>
+        <x:v>Certain 2012 F30 N55 Vehicles Need an Oil-Filter-Housing Campaign Check</x:v>
       </x:c>
       <x:c r="E141" s="9" t="str">
-        <x:v>Diagnosis includes listening for chain noise on cold start, inspecting oil/filter for plastic guide debris, and checking timing adaptation/fault data. Repair generally requires replacing timing chain guides, tensioners, related rails, gaskets, and often addressing front-engine seals while disassembled. Preventive service is often recommended once noise appears rather than waiting for a failure.</x:v>
+        <x:v>Check the VIN and service-action history, then have a BMW-qualified technician inspect the housing material and leak source. Under the bulletin, the black plastic housing is replaced while the silver aluminum housing is left in place. ShowMeTheParts returned no exact 2012 335i oil-filter-housing candidate, and the former generic gasket links were removed.</x:v>
       </x:c>
       <x:c r="F141" s="9" t="n">
         <x:v>0</x:v>
@@ -9366,21 +10698,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="142" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A142" s="40" t="n">
         <x:v>141</x:v>
       </x:c>
       <x:c r="B142" s="9" t="str">
-        <x:v>bmw-m5-torque-converter-shudder-2018</x:v>
+        <x:v>bmw-n55-valve-cover-2012</x:v>
       </x:c>
       <x:c r="C142" s="9" t="str">
-        <x:v>2018-2023 | BMW | M5</x:v>
+        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D142" s="9" t="str">
-        <x:v>ZF 8HP Torque Converter Shudder</x:v>
+        <x:v>Valve Cover/Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E142" s="9" t="str">
-        <x:v>Perform a transmission fluid and filter change using genuine ZF LifeGuard 8 fluid. If the shudder persists, the torque converter must be replaced. BMW issued a service bulletin for some VINs. A software update for shift calibration may also help in mild cases.</x:v>
+        <x:v>Replace valve cover and gasket as an assembly (PCV valve is integrated). Clean oil from exhaust manifold. Monitor for leaks after repair. This is a common maintenance item at higher mileage.</x:v>
       </x:c>
       <x:c r="F142" s="9" t="n">
         <x:v>0</x:v>
@@ -9389,21 +10721,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="1108.800048828125" hidden="0" customHeight="1">
+    <x:row r="143" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A143" s="40" t="n">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B143" s="9" t="str">
-        <x:v>bmw-m5-valve-stem-seals-2012</x:v>
+        <x:v>bmw-n55-vanos-2012</x:v>
       </x:c>
       <x:c r="C143" s="9" t="str">
-        <x:v>2012-2023 | BMW | M5</x:v>
+        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
       </x:c>
       <x:c r="D143" s="9" t="str">
-        <x:v>S63/S63TU Valve Stem Seal Failure &amp; Oil Consumption</x:v>
+        <x:v>Certain 2012 N55 3 Series Need a VANOS Gear-Bolt Recall Check</x:v>
       </x:c>
       <x:c r="E143" s="9" t="str">
-        <x:v>Replace valve stem seals with updated OEM or performance seals ($3,500-$10,000 depending on method). Labor-intensive repair requiring either cylinder head removal ($6,000-$10,000) or specialized valve spring compressor tools with heads on engine ($3,500-$6,000). Address issue EARLY to prevent catalytic converter damage from oil burning (adds $3,000-$5,000 to repair). Perform more frequent oil changes (5,000 miles) to minimize damage. Blue smoke test: let engine idle 30+ minutes until hot, then rev to redline briefly - big blue smoke plume = valve seals. Find shop that can replace valve seals with heads installed (specialized tools required) - saves $4,000+ in labor vs. full head removal.</x:v>
+        <x:v>Check the VIN for campaign 14V-176 before ordering VANOS solenoids or gears. For an affected vehicle, BMW specifies replacing the VANOS gear bolts and inspecting for loose or broken bolts, with additional gear work only when the campaign procedure requires it. Recall work belongs with an authorized BMW center, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F143" s="9" t="n">
         <x:v>0</x:v>
@@ -9412,21 +10744,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="528" hidden="0" customHeight="1">
+    <x:row r="144" ht="660" hidden="0" customHeight="1">
       <x:c r="A144" s="40" t="n">
         <x:v>143</x:v>
       </x:c>
       <x:c r="B144" s="9" t="str">
-        <x:v>bmw-m6-e63-e64-active-steering-steering-gear-play-knock</x:v>
+        <x:v>bmw-n55-water-pump-2012</x:v>
       </x:c>
       <x:c r="C144" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
+        <x:v>2012-2013 | BMW | 3 Series | N54T, N55</x:v>
       </x:c>
       <x:c r="D144" s="9" t="str">
-        <x:v>E63/E64 Active Steering and Steering-Gear Play / Knock</x:v>
+        <x:v>2012-2013 335i/335is Overheat Warnings Need Coolant-Pump Diagnosis</x:v>
       </x:c>
       <x:c r="E144" s="9" t="str">
-        <x:v>Inspect the steering gear and front control-arm/thrust-arm bushings for play. Replace worn control-arm bushings/ball joints first as they are cheaper and frequently the source of the knock; if the steering rack/gear itself has internal play or leaks, it requires replacement (a significant cost) followed by an alignment.</x:v>
+        <x:v>Stop safely if an overheat warning appears and avoid continued operation until the cooling system is checked. Verify the chassis, engine and VIN, read fault memory and follow the current coolant-pump test plan before replacement. Settlement benefits were time-limited. ShowMeTheParts resolved five 2012 335i water-pump candidates, but fitment does not prove failure or remedy, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F144" s="9" t="n">
         <x:v>0</x:v>
@@ -9435,21 +10767,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="145" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A145" s="40" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B145" s="9" t="str">
-        <x:v>bmw-m6-f12-convertible-top-hydraulic-pump-relay-failure</x:v>
+        <x:v>bmw-x1-coolant-leak-2016</x:v>
       </x:c>
       <x:c r="C145" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Convertible (F12) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2016-2023 | BMW | X1 | B-series</x:v>
       </x:c>
       <x:c r="D145" s="9" t="str">
-        <x:v>F12 Convertible Top Hydraulic Pump and Relay Failure</x:v>
+        <x:v>Coolant Leaks - Water Pump &amp; Thermostat - F48 X1</x:v>
       </x:c>
       <x:c r="E145" s="9" t="str">
-        <x:v>Diagnose whether the fault is the pump's high-current relays (relatively cheap, often the cure), a pressure loss in the pump, a hydraulic leak, or a roof microswitch/sensor. Replace the relays first; if pressure loss persists, rebuild or replace the hydraulic pump unit (specialist rebuild services exist) and renew worn seals/sensors. Bleed and refill the hydraulic system after repair.</x:v>
+        <x:v>Replace failed water pump or thermostat housing. Electric water pump replacement is 2-3 hours labor. Thermostat housing is 1-2 hours. Always use BMW-approved coolant (blue or orange, do not mix). Properly bleed cooling system after repair to prevent air pockets. Inspect all coolant hoses during repair and replace if cracked. Preventive replacement of water pump at 80,000 miles recommended.</x:v>
       </x:c>
       <x:c r="F145" s="9" t="n">
         <x:v>0</x:v>
@@ -9458,21 +10790,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="146" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A146" s="40" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B146" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-7-speed-m-dct-mechatronic-clutch-pack-failure</x:v>
+        <x:v>bmw-x1-n20-timing-chain-2013</x:v>
       </x:c>
       <x:c r="C146" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2015 | BMW | X1 | N20</x:v>
       </x:c>
       <x:c r="D146" s="9" t="str">
-        <x:v>F12/F13 7-Speed M-DCT Mechatronic and Clutch Pack Failure</x:v>
+        <x:v>Lower-Engine Whine Requires X1 N20 Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E146" s="9" t="str">
-        <x:v>Scan for transmission codes to confirm whether the fault is the mechatronic unit or worn clutch packs. Mechatronic units can often be repaired/replaced and must be reprogrammed and adapted to the vehicle afterward. Worn clutch packs require a clutch replacement (dealer cost often $3,000-$5,000). Regular DCT fluid and filter changes help prevent premature wear; avoid prolonged clutch slip in traffic.</x:v>
+        <x:v>Confirm the exact model, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F146" s="9" t="n">
         <x:v>0</x:v>
@@ -9481,21 +10813,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="594" hidden="0" customHeight="1">
+    <x:row r="147" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A147" s="40" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B147" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-electric-water-pump-thermostat-failure</x:v>
+        <x:v>bmw-x1-n20-timing-chain-guide-2013</x:v>
       </x:c>
       <x:c r="C147" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2015 | BMW | X1 | N20</x:v>
       </x:c>
       <x:c r="D147" s="9" t="str">
-        <x:v>F12/F13 Electric Water Pump and Thermostat Failure</x:v>
+        <x:v>N20 Timing Chain Guide Failure</x:v>
       </x:c>
       <x:c r="E147" s="9" t="str">
-        <x:v>Replace the failed electric water pump and/or electronic thermostat with OEM units; inspect the radiator end-tanks and expansion tank for cracks and replace as needed. Pressure-test the cooling system, refresh coolant, and treat the pump/thermostat as wear items given the heat load. Address any overheating event immediately to avoid secondary engine damage.</x:v>
+        <x:v>Replace timing chain, guides, tensioner, and both sprockets as a complete kit. The repair requires removing the front of the engine and is labor-intensive. Updated guide materials are available. Preventive replacement at 80,000 miles is recommended for high-mileage N20 engines.</x:v>
       </x:c>
       <x:c r="F147" s="9" t="n">
         <x:v>0</x:v>
@@ -9504,44 +10836,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="528" hidden="0" customHeight="1">
+    <x:row r="148" ht="396" hidden="0" customHeight="1">
       <x:c r="A148" s="40" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B148" s="9" t="str">
-        <x:v>bmw-m6-f12-f13-turbocharger-wastegate-rattle-oil-starvation</x:v>
+        <x:v>bmw-x1-oil-filter-housing-gasket-2013</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2022 | BMW | X1 | N20, B48</x:v>
       </x:c>
       <x:c r="D148" s="9" t="str">
-        <x:v>F12/F13 Turbocharger Wastegate Rattle and Oil Starvation</x:v>
+        <x:v>Oil Filter Housing Gasket Leak</x:v>
       </x:c>
       <x:c r="E148" s="9" t="str">
-        <x:v>Confirm wastegate rattle by listening at light throttle; worn actuators/linkages can be replaced or upgraded. For oil starvation, maintain strict oil-change intervals with the correct specification, allow proper cool-down after hard driving, and keep the cooling system healthy. Severely worn or whining turbos require rebuild or replacement.</x:v>
+        <x:v>Replace the oil filter housing gasket and clean all affected surfaces. Also inspect and replace the oil cooler gasket if present. Use only OEM-quality gaskets as aftermarket gaskets tend to fail prematurely. Typical repair takes 2-3 hours.</x:v>
       </x:c>
       <x:c r="F148" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G148" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="149" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A149" s="40" t="n">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B149" s="9" t="str">
-        <x:v>bmw-m6-rod-bearing-wear-2005</x:v>
+        <x:v>bmw-x1-oil-leak-2016</x:v>
       </x:c>
       <x:c r="C149" s="9" t="str">
-        <x:v>2005-2019 | BMW | M6 | S65, S63</x:v>
+        <x:v>2016-2023 | BMW | X1 | B46, B48</x:v>
       </x:c>
       <x:c r="D149" s="9" t="str">
-        <x:v>Rod Bearing Premature Wear (S65/S63 Engines)</x:v>
+        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - F48 X1</x:v>
       </x:c>
       <x:c r="E149" s="9" t="str">
-        <x:v>Perform a preventive rod bearing replacement between 60,000-80,000 miles on S65 engines, and inspect by 80,000-100,000 miles on S63 engines. Use upgraded ACL or King XP bearings with coated surfaces. Cut and send used oil filter for analysis — bearing material particles indicate wear progression. The job requires engine-out on the S65 (approximately 20 hours labor) or can be done in-car on the S63 with the oil pan dropped.</x:v>
+        <x:v>Replace valve cover gasket and/or oil filter housing gasket as needed. Valve cover replacement is 2-3 hours labor. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on B-series engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
       </x:c>
       <x:c r="F149" s="9" t="n">
         <x:v>0</x:v>
@@ -9550,21 +10882,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="528" hidden="0" customHeight="1">
+    <x:row r="150" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A150" s="40" t="n">
         <x:v>149</x:v>
       </x:c>
       <x:c r="B150" s="9" t="str">
-        <x:v>bmw-m6-s63-carbon-buildup-intake-valves</x:v>
+        <x:v>bmw-x1-suspension-bushing-2016</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2016-2023 | BMW | X1</x:v>
       </x:c>
       <x:c r="D150" s="9" t="str">
-        <x:v>S63 Carbon Buildup on Intake Valves (Direct Injection)</x:v>
+        <x:v>Front Suspension Bushing &amp; Control Arm Wear - F48 X1</x:v>
       </x:c>
       <x:c r="E150" s="9" t="str">
-        <x:v>Have the intake valves walnut-blasted (media-blast cleaning) to remove carbon deposits without removing the cylinder heads. Many owners do this every 50,000-70,000 km. A properly functioning PCV/crankcase ventilation system and quality oil reduce deposit rate. An oil-catch can is sometimes fitted to slow accumulation.</x:v>
+        <x:v>Replace worn control arms or bushings. Most shops replace complete control arms (with integrated bushings) rather than pressing in new bushings alone. Alignment required after replacement. Inspect all suspension components while vehicle is lifted. Consider replacing both sides even if only one shows symptoms to avoid repeat labor costs. Use OEM or quality aftermarket parts (Lemforder, Meyle HD) for longevity.</x:v>
       </x:c>
       <x:c r="F150" s="9" t="n">
         <x:v>0</x:v>
@@ -9573,21 +10905,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="528" hidden="0" customHeight="1">
+    <x:row r="151" ht="660" hidden="0" customHeight="1">
       <x:c r="A151" s="40" t="n">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B151" s="9" t="str">
-        <x:v>bmw-m6-s63-high-pressure-fuel-pump-fuel-injector-cold-start-misfire</x:v>
+        <x:v>bmw-x1-transfer-case-2013</x:v>
       </x:c>
       <x:c r="C151" s="9" t="str">
-        <x:v>2012-2019 | BMW | M6 | M6 Coupe (F13), M6 Convertible (F12), M6 Gran Coupe (F06) | S63 4.4L twin-turbo V8 (S63TU)</x:v>
+        <x:v>2013-2023 | BMW | X1</x:v>
       </x:c>
       <x:c r="D151" s="9" t="str">
-        <x:v>S63 High-Pressure Fuel Pump / Fuel Injector Cold-Start Misfire</x:v>
+        <x:v>Transfer Case Failure - xDrive Models E84/F48 X1</x:v>
       </x:c>
       <x:c r="E151" s="9" t="str">
-        <x:v>Scan for misfire and fuel-system codes and test cold-start fuel-rail pressure. Replace a failing HPFP; for injector faults, replace the affected injector(s) with units of the correct matching index code (do not mix injector indexes on a bank) and re-code them. Address per the relevant BMW technical service bulletin for the N63/S63.</x:v>
+        <x:v>Diagnose specific failure point. Transfer case actuator motor can be replaced separately ($800-1,200) if caught early. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors for better durability. Common wear item on high-mileage xDrive models.</x:v>
       </x:c>
       <x:c r="F151" s="9" t="n">
         <x:v>0</x:v>
@@ -9596,21 +10928,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="152" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A152" s="40" t="n">
         <x:v>151</x:v>
       </x:c>
       <x:c r="B152" s="9" t="str">
-        <x:v>bmw-m6-s63-rod-bearing-2013</x:v>
+        <x:v>bmw-x1-transfer-case-actuator-2013</x:v>
       </x:c>
       <x:c r="C152" s="9" t="str">
-        <x:v>2013-2018 | BMW | M6 | S63</x:v>
+        <x:v>2013-2022 | BMW | X1</x:v>
       </x:c>
       <x:c r="D152" s="9" t="str">
-        <x:v>S63 Twin-Turbo V8 Rod Bearing Concerns (F06/F12/F13 M6)</x:v>
+        <x:v>Transfer Case Actuator Motor Failure</x:v>
       </x:c>
       <x:c r="E152" s="9" t="str">
-        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles using ACL Race Rod Bearings 8B1578HX-STD ($150-250), King Bearings SV Series, or WPC-treated bearings from Lang Racing. Cost: $4,000-7,000 for preventive replacement. Oil changes every 5,000-7,500 miles mandatory (ignore BMW's 10,000-mile recommendation). Use Blackstone Labs oil analysis ($30/test) every 5,000 miles to monitor bearing wear metals. Preventive replacement recommended for peace of mind, especially on cars used for track days or spirited driving.</x:v>
+        <x:v>Replace the transfer case actuator motor (also called the servo motor). The transfer case itself usually does not need replacement. Ensure the transfer case fluid is changed at the same time. Some owners report success with rebuilt actuators at lower cost.</x:v>
       </x:c>
       <x:c r="F152" s="9" t="n">
         <x:v>0</x:v>
@@ -9619,21 +10951,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="1069.199951171875" hidden="0" customHeight="1">
+    <x:row r="153" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A153" s="40" t="n">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B153" s="9" t="str">
-        <x:v>bmw-m6-s85-rod-bearing-2006</x:v>
+        <x:v>bmw-x2-b48-timing-chain-tensioner-2018</x:v>
       </x:c>
       <x:c r="C153" s="9" t="str">
-        <x:v>2006-2010 | BMW | M6 | S85</x:v>
+        <x:v>2018-2023 | BMW | X2 | B48</x:v>
       </x:c>
       <x:c r="D153" s="9" t="str">
-        <x:v>S85 V10 Rod Bearing Failure (Catastrophic Engine Destruction)</x:v>
+        <x:v>B48 Timing Chain Tensioner Weakness</x:v>
       </x:c>
       <x:c r="E153" s="9" t="str">
-        <x:v>MANDATORY PREVENTIVE REPLACEMENT before 70,000 miles: Replace all 10 rod bearings with ACL Race Bearings 10B1580HX-STD (+0.001" clearance, $200-350) or WPC-treated bearings from Lang Racing, or VAC Motorsports kit VAC-HPRBK-S85, or Turner kit TMS222798, or FCP Euro kit 11247841703KT3. ALSO replace VANOS line 11367838669 and use ARP rod bolts (included in most kits). Cost: $6,500-9,500 preventive. If engine is destroyed from bearing failure: $15,000-32,000 for engine replacement or rebuild. NEVER use OEM bearings as replacements. Use Blackstone Labs oil analysis every 5,000 miles ($30/test) to monitor bearing wear metals.</x:v>
+        <x:v>Replace the timing chain tensioner and inspect the chain and guides. If the chain has stretched beyond specification, replace the full timing chain kit. Updated tensioner design from BMW addresses the oil pressure retention issue.</x:v>
       </x:c>
       <x:c r="F153" s="9" t="n">
         <x:v>0</x:v>
@@ -9642,21 +10974,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="924" hidden="0" customHeight="1">
+    <x:row r="154" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A154" s="40" t="n">
         <x:v>153</x:v>
       </x:c>
       <x:c r="B154" s="9" t="str">
-        <x:v>bmw-m6-s85-throttle-actuator-2006</x:v>
+        <x:v>bmw-x2-crankshaft-sensor-recall-2018</x:v>
       </x:c>
       <x:c r="C154" s="9" t="str">
-        <x:v>2006-2010 | BMW | M6 | S85</x:v>
+        <x:v>2018-2018 | BMW | X2</x:v>
       </x:c>
       <x:c r="D154" s="9" t="str">
-        <x:v>S85 V10 Throttle Actuator Failure (Plastic Gear Stripping)</x:v>
+        <x:v>2018 X2 Crankshaft Sensor Safety Recall 18V-465</x:v>
       </x:c>
       <x:c r="E154" s="9" t="str">
-        <x:v>Rebuild throttle actuators using Beisan Systems BS101 sintered metal gear kit ($250/set, need 2 sets for both actuators) for permanent fix. Beisan BS102 full rebuild service available ($300). Alternatively, rebuilt actuators from Euro Power Motorsports ($500-800 each). OEM replacement actuators from BMW cost $2,000-4,500. Total cost: $500-4,500 depending on approach. Beisan Systems sintered metal gears are THE permanent fix - they replace the weak plastic PPA gears with metal gears that will not strip. Always rebuild both actuators simultaneously.</x:v>
+        <x:v>Check the VIN for an open 18V-465 campaign. If open, an authorized BMW dealer replaces the crankshaft sensor free of charge. A stall or sudden loss of power requires moving to a safe location and arranging BMW assistance; do not order a sensor from this card. ShowMeTheParts resolved exact X2 category fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F154" s="9" t="n">
         <x:v>0</x:v>
@@ -9665,21 +10997,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="155" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A155" s="40" t="n">
         <x:v>154</x:v>
       </x:c>
       <x:c r="B155" s="9" t="str">
-        <x:v>bmw-m6-s85-v10-vanos-high-pressure-oil-pump-failure</x:v>
+        <x:v>bmw-x2-front-control-arm-bushings-2018</x:v>
       </x:c>
       <x:c r="C155" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6 | M6 Coupe, M6 Convertible | S85 5.0L V10 (S85B50)</x:v>
+        <x:v>2018-2023 | BMW | X2</x:v>
       </x:c>
       <x:c r="D155" s="9" t="str">
-        <x:v>S85 V10 VANOS High-Pressure Oil Pump Failure</x:v>
+        <x:v>Front Control Arm Bushing Premature Wear</x:v>
       </x:c>
       <x:c r="E155" s="9" t="str">
-        <x:v>Perform an oil-pressure test on the VANOS circuit at the first sign of cold-start knocking. Replace or professionally rebuild the high-pressure VANOS pump and renew the high-pressure lines/seals. Many owners do the VANOS pump preventively at the same time as the rod-bearing service since the oil pan is already removed. Use only BMW-spec oil and strict change intervals to prolong pump life.</x:v>
+        <x:v>Replace front control arms with new bushings (sold as complete assemblies by BMW). Aftermarket options with upgraded polyurethane bushings are available for longer life. Perform a four-wheel alignment after replacement.</x:v>
       </x:c>
       <x:c r="F155" s="9" t="n">
         <x:v>0</x:v>
@@ -9688,21 +11020,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="156" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A156" s="40" t="n">
         <x:v>155</x:v>
       </x:c>
       <x:c r="B156" s="9" t="str">
-        <x:v>bmw-m6-smg-pump-failure-2005</x:v>
+        <x:v>bmw-x2-oil-filter-housing-2018</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
-        <x:v>2005-2010 | BMW | M6</x:v>
+        <x:v>2018-2023 | BMW | X2 | sDrive28i, xDrive28i | B48</x:v>
       </x:c>
       <x:c r="D156" s="9" t="str">
-        <x:v>SMG Hydraulic Pump and Clutch Actuator Failure</x:v>
+        <x:v>B48 Oil Filter Housing Gasket Leak/Cracking</x:v>
       </x:c>
       <x:c r="E156" s="9" t="str">
-        <x:v>Replace the SMG hydraulic pump and pressure accumulator. Bleed and refill the SMG hydraulic system with Pentosin CHF 11S fluid. Many owners convert to a traditional 6-speed manual swap using an aftermarket kit from companies like OS Giken or using the E90 M3 6MT parts. Budget $2,000-4,000 for SMG repair or $5,000-8,000 for a manual conversion.</x:v>
+        <x:v>Replace the cracked oil filter housing. OEM plastic housing replacement (BMW 11428596283, $412 dealer) will eventually crack again. RECOMMENDED: Install aftermarket aluminum upgrade housing ($250-350) which permanently eliminates the heat-cycling crack issue. FCP Euro kit 11428596283KT ($450) includes all gaskets and seals. If coolant and oil have mixed, perform complete oil flush and coolant system flush before installing new housing. Check for engine damage if contamination was prolonged.</x:v>
       </x:c>
       <x:c r="F156" s="9" t="n">
         <x:v>0</x:v>
@@ -9711,21 +11043,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="157" ht="330" hidden="0" customHeight="1">
       <x:c r="A157" s="40" t="n">
         <x:v>156</x:v>
       </x:c>
       <x:c r="B157" s="9" t="str">
-        <x:v>bmw-m8-adaptive-suspension-leak-2020</x:v>
+        <x:v>bmw-x2-oil-filter-housing-gasket-2018</x:v>
       </x:c>
       <x:c r="C157" s="9" t="str">
-        <x:v>2020-2025 | BMW | M8</x:v>
+        <x:v>2018-2023 | BMW | X2 | B48</x:v>
       </x:c>
       <x:c r="D157" s="9" t="str">
-        <x:v>Adaptive Suspension Damper Leaks</x:v>
+        <x:v>Oil Filter Housing Gasket Leak</x:v>
       </x:c>
       <x:c r="E157" s="9" t="str">
-        <x:v>Replace the leaking damper(s). BMW adaptive dampers must be replaced as complete units — they cannot be rebuilt. After replacement, a suspension calibration via ISTA is required to integrate the new damper into the adaptive system. Replacing in pairs (front or rear axle) is recommended.</x:v>
+        <x:v>Replace the oil filter housing gasket. Clean all oil-contaminated surfaces and inspect the serpentine belt for oil damage. Replace belt if oil-soaked. Use OEM-quality gasket material for longevity.</x:v>
       </x:c>
       <x:c r="F157" s="9" t="n">
         <x:v>0</x:v>
@@ -9734,21 +11066,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="990" hidden="0" customHeight="1">
+    <x:row r="158" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A158" s="40" t="n">
         <x:v>157</x:v>
       </x:c>
       <x:c r="B158" s="9" t="str">
-        <x:v>bmw-m8-carbon-ceramic-brakes-2020</x:v>
+        <x:v>bmw-x2-tie-rod-recall-2019</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
-        <x:v>2020-2024 | BMW | M8</x:v>
+        <x:v>2019-2019 | BMW | X2</x:v>
       </x:c>
       <x:c r="D158" s="9" t="str">
-        <x:v>M8 Carbon Ceramic Brake (CCB) Issues</x:v>
+        <x:v>2019 X2 Steering Tie-Rod Safety Recall 19V-601</x:v>
       </x:c>
       <x:c r="E158" s="9" t="str">
-        <x:v>Replace damaged CCB rotors ($3,000-$4,000 per corner, $12,000-$16,000 for all four). CCB rotors cannot be resurfaced - replacement is only option. Alternatively, convert to iron rotors using BimmerWorld CCB-to-iron conversion kit ($3,000-$5,000 total for all four corners) for dramatically lower running costs. PREVENTION: Avoid driving through standing water with hot brakes (thermal shock cracks rotors). Avoid aggressive braking over potholes or road debris. Squealing at low speed is normal for CCB material - not a defect. If only using car for street driving, iron conversion is more practical and cost-effective.</x:v>
+        <x:v>Check the VIN in BMW AIR or NHTSA for an open 19V-601 campaign. If open, an authorized BMW dealer checks both tie rods and replaces the tie rods and ball joints as necessary free of charge. Do not infer recall eligibility from model year alone or order steering parts from this card.</x:v>
       </x:c>
       <x:c r="F158" s="9" t="n">
         <x:v>0</x:v>
@@ -9757,21 +11089,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="396" hidden="0" customHeight="1">
+    <x:row r="159" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A159" s="40" t="n">
         <x:v>158</x:v>
       </x:c>
       <x:c r="B159" s="9" t="str">
-        <x:v>bmw-m8-s63tu4-oil-consumption-2020</x:v>
+        <x:v>bmw-x2-transmission-jerking-2018</x:v>
       </x:c>
       <x:c r="C159" s="9" t="str">
-        <x:v>2020-2025 | BMW | M8 | S63TU4</x:v>
+        <x:v>2018-2020 | BMW | X2</x:v>
       </x:c>
       <x:c r="D159" s="9" t="str">
-        <x:v>S63TU4 V8 Excessive Oil Consumption</x:v>
+        <x:v>Aisin 8-Speed Transmission Jerking</x:v>
       </x:c>
       <x:c r="E159" s="9" t="str">
-        <x:v>Monitor oil level regularly using iDrive oil level check. For excessive consumption beyond BMW's threshold, valve stem seal replacement may be warranted under warranty. Updated piston rings are available for severe cases. Always keep oil topped up between changes.</x:v>
+        <x:v>Start with transmission software recalibration at BMW dealer ($200-500) which may resolve calibration-related shifting issues. If software update does not resolve, transmission may require oil pump replacement or internal repair ($2,000-5,000). In severe cases with extensive oil pump neck wear, complete transmission replacement required ($5,000-7,000). Reference TSB GBSEL-SELP24 when visiting dealer.</x:v>
       </x:c>
       <x:c r="F159" s="9" t="n">
         <x:v>0</x:v>
@@ -9780,21 +11112,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="858" hidden="0" customHeight="1">
+    <x:row r="160" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A160" s="40" t="n">
         <x:v>159</x:v>
       </x:c>
       <x:c r="B160" s="9" t="str">
-        <x:v>bmw-m8-s63tu4-rod-bearing-2020</x:v>
+        <x:v>bmw-x2-valve-cover-gasket-2018</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
-        <x:v>2020-2024 | BMW | M8</x:v>
+        <x:v>2018-2023 | BMW | X2</x:v>
       </x:c>
       <x:c r="D160" s="9" t="str">
-        <x:v>S63TU4 Rod Bearing Wear (M8/M8 Competition)</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E160" s="9" t="str">
-        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles or sooner if tracked ($5,000-$8,000). Use ACL Race bearings 8B1578HX-STD ($200-350) which have wider clearance tolerances than OEM for better oil film protection. Monitor bearing health with Blackstone Labs oil analysis ($30/sample) every oil change - elevated copper/lead indicates bearing wear starting. If bearings have failed: engine replacement required ($20,000-$40,000). CRITICAL: If you hear any knocking from bottom end, stop driving immediately and tow to shop.</x:v>
+        <x:v>Replace valve cover gasket. Genuine BMW valve cover assembly 11127611278 ($200-350) includes integrated gasket. Labor typically 2-3 hours ($300-500). Total cost $700-1,000 at shop. DIY possible with basic tools to save $300-500 in labor. Replace spark plug tube seals at same time if applicable - labor overlap saves money. Monitor oil level between repairs.</x:v>
       </x:c>
       <x:c r="F160" s="9" t="n">
         <x:v>0</x:v>
@@ -9803,21 +11135,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="161" ht="990" hidden="0" customHeight="1">
       <x:c r="A161" s="40" t="n">
         <x:v>160</x:v>
       </x:c>
       <x:c r="B161" s="9" t="str">
-        <x:v>bmw-n54-hpfp</x:v>
+        <x:v>bmw-x3-coolant-expansion-tank-2004</x:v>
       </x:c>
       <x:c r="C161" s="9" t="str">
-        <x:v>2007-2010 | BMW | 3 Series | N54</x:v>
+        <x:v>2004-2023 | BMW | X3</x:v>
       </x:c>
       <x:c r="D161" s="9" t="str">
-        <x:v>N54 Long Crank or Power Loss Requires Fuel-Pressure Diagnosis</x:v>
+        <x:v>Coolant Expansion Tank Cracking</x:v>
       </x:c>
       <x:c r="E161" s="9" t="str">
-        <x:v>Have a BMW-qualified technician read fault memory and follow the bulletin pressure tests for 2FBF, 29DC, 29F1 or 29F2 before replacing the pump. The historical ten-year/120,000-mile emissions-warranty extension has expired for this population and is not a current coverage promise. ShowMeTheParts resolved three 2009 335i fuel-pump candidates, but catalog fitment is not diagnosis or remedy proof and no commerce link is approved.</x:v>
+        <x:v>Replace expansion tank and coolant ($50-100 DIY parts, $200-400 independent shop, $400-580 dealer). Very simple DIY repair taking 30 minutes - drain coolant, unbolt old tank, install new tank, refill with BMW-spec coolant (blue or pink/orange premix). Use Behr or OEM BMW expansion tank - Dorman aftermarket tanks may fail prematurely. YouTube and Pelicanparts have detailed DIY guides. PREVENTIVE: Replace every 5-7 years or 80-100k miles before cracks develop. Check tank regularly for hairline cracks. Don't ignore coolant leaks - can lead to catastrophic overheating and head gasket failure.</x:v>
       </x:c>
       <x:c r="F161" s="9" t="n">
         <x:v>0</x:v>
@@ -9826,44 +11158,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="290.3999938964844" hidden="0" customHeight="1">
+    <x:row r="162" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A162" s="40" t="n">
         <x:v>161</x:v>
       </x:c>
       <x:c r="B162" s="9" t="str">
-        <x:v>bmw-n55-boost-solenoid-2012</x:v>
+        <x:v>bmw-x3-electric-water-pump-2011</x:v>
       </x:c>
       <x:c r="C162" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
+        <x:v>2011-2026 | BMW | X3</x:v>
       </x:c>
       <x:c r="D162" s="9" t="str">
-        <x:v>Wastegate/Boost Solenoid Issues</x:v>
+        <x:v>Electric Water Pump Failure</x:v>
       </x:c>
       <x:c r="E162" s="9" t="str">
-        <x:v>Diagnose boost system for proper operation. Replace wastegate actuator or boost solenoid as needed. Check vacuum lines for leaks. Software update may address some issues.</x:v>
+        <x:v>Replace the electric water pump and thermostat together, as they are part of the same cooling circuit and the thermostat often fails concurrently. Bleed the cooling system thoroughly after replacement. Some owners carry a spare pump due to the sudden failure nature.</x:v>
       </x:c>
       <x:c r="F162" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G162" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="163" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A163" s="40" t="n">
         <x:v>162</x:v>
       </x:c>
       <x:c r="B163" s="9" t="str">
-        <x:v>bmw-n55-carbon-buildup-2012</x:v>
+        <x:v>bmw-x3-m-electric-wastegate-actuator-adaptation-fault-boost-cutout-ea</x:v>
       </x:c>
       <x:c r="C163" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | 335d, 335i, 340i, M340i | N55</x:v>
+        <x:v>2020-2020 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D163" s="9" t="str">
-        <x:v>Intake Valve Carbon Buildup</x:v>
+        <x:v>2020 X3 M Wastegate Adaptation Faults Require Software Diagnosis</x:v>
       </x:c>
       <x:c r="E163" s="9" t="str">
-        <x:v>Walnut blast cleaning of intake valves every 50,000-70,000 miles. Install catch can to reduce oil vapor. Use quality fuel. BMW port injection on later engines helps reduce this issue.</x:v>
+        <x:v>Confirm the production date, fault codes and current vehicle integration level. If the I-level is below S15A-20-03-510, a BMW-qualified repairer follows the bulletin and programs the vehicle with the specified or newer approved ISTA level. Diagnose unrelated mechanical noise separately; do not replace an actuator or turbocharger from this card.</x:v>
       </x:c>
       <x:c r="F163" s="9" t="n">
         <x:v>0</x:v>
@@ -9872,21 +11204,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="164" ht="462" hidden="0" customHeight="1">
       <x:c r="A164" s="40" t="n">
         <x:v>163</x:v>
       </x:c>
       <x:c r="B164" s="9" t="str">
-        <x:v>bmw-n55-charge-pipe-2012</x:v>
+        <x:v>bmw-x3-m-fuel-tank-inlet-check-valve-weld-failure-2021-x3-m</x:v>
       </x:c>
       <x:c r="C164" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2021-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D164" s="9" t="str">
-        <x:v>Charge Pipe Failure/Cracking</x:v>
+        <x:v>2021 X3 M Fuel-Tank Safety Recall 21V-199</x:v>
       </x:c>
       <x:c r="E164" s="9" t="str">
-        <x:v>Replace with upgraded aluminum charge pipe for reliability. If keeping stock, inspect regularly for cracks. Upgraded pipe is recommended for any tuned vehicle. Installation is relatively straightforward.</x:v>
+        <x:v>Check the VIN for an open 21V-199 campaign. If open, an authorized BMW dealer replaces the fuel tank free of charge. If fuel odor or leakage appears, move safely away from traffic, stop, have occupants exit and contact BMW roadside assistance; do not continue driving or order a tank from this card.</x:v>
       </x:c>
       <x:c r="F164" s="9" t="n">
         <x:v>0</x:v>
@@ -9895,21 +11227,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="277.20001220703125" hidden="0" customHeight="1">
+    <x:row r="165" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A165" s="40" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B165" s="9" t="str">
-        <x:v>bmw-n55-injector-2012</x:v>
+        <x:v>bmw-x3-m-idrive-control-display-blank-screen-infotainment-glitches-f9</x:v>
       </x:c>
       <x:c r="C165" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2020-2021 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D165" s="9" t="str">
-        <x:v>High-Pressure Fuel Injector Issues</x:v>
+        <x:v>iDrive Control Display Blank Screen and Infotainment Glitches - F97 X3 M (2019-2021)</x:v>
       </x:c>
       <x:c r="E165" s="9" t="str">
-        <x:v>Replace failed injector(s) with correct index version. Consider cleaning service for carbon buildup. Use quality fuel. All injectors should be same index for proper operation.</x:v>
+        <x:v>First try the latest iDrive/head-unit software update at the dealer, which resolves many of the early glitches, reboots, and camera issues. If the display panel hardware has failed (lines, persistent blank screen with backlight off), the control display/screen assembly is replaced. A soft reset (press-and-hold volume/power) can temporarily clear a frozen screen.</x:v>
       </x:c>
       <x:c r="F165" s="9" t="n">
         <x:v>0</x:v>
@@ -9918,21 +11250,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="166" ht="462" hidden="0" customHeight="1">
       <x:c r="A166" s="40" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B166" s="9" t="str">
-        <x:v>bmw-n55-oil-filter-housing-2012</x:v>
+        <x:v>bmw-x3-m-improperly-welded-front-seat-frame-2019-2021-x3-m</x:v>
       </x:c>
       <x:c r="C166" s="9" t="str">
-        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
+        <x:v>2021-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D166" s="9" t="str">
-        <x:v>Certain 2012 F30 N55 Vehicles Need an Oil-Filter-Housing Campaign Check</x:v>
+        <x:v>2021 X3 M Front Seat-Frame Safety Recall 23V-211</x:v>
       </x:c>
       <x:c r="E166" s="9" t="str">
-        <x:v>Check the VIN and service-action history, then have a BMW-qualified technician inspect the housing material and leak source. Under the bulletin, the black plastic housing is replaced while the silver aluminum housing is left in place. ShowMeTheParts returned no exact 2012 335i oil-filter-housing candidate, and the former generic gasket links were removed.</x:v>
+        <x:v>Check the VIN for an open 23V-211 campaign. If open, an authorized BMW dealer replaces the affected front seat frame and backrest free of charge using VIN-selected parts. Contact BMW promptly if a front seat vibrates or makes abnormal noise; do not order seat components from this card.</x:v>
       </x:c>
       <x:c r="F166" s="9" t="n">
         <x:v>0</x:v>
@@ -9941,21 +11273,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="167" ht="541.2000122070312" hidden="0" customHeight="1">
       <x:c r="A167" s="40" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B167" s="9" t="str">
-        <x:v>bmw-n55-valve-cover-2012</x:v>
+        <x:v>bmw-x3-m-low-mounted-engine-oil-cooler-vulnerable-to-road-debris-punc</x:v>
       </x:c>
       <x:c r="C167" s="9" t="str">
-        <x:v>2012-2018 | BMW | 3 Series | N55</x:v>
+        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D167" s="9" t="str">
-        <x:v>Valve Cover/Gasket Oil Leak</x:v>
+        <x:v>Low-Mounted Engine Oil Cooler Vulnerable to Road-Debris Puncture - F97 X3 M (S58)</x:v>
       </x:c>
       <x:c r="E167" s="9" t="str">
-        <x:v>Replace valve cover and gasket as an assembly (PCV valve is integrated). Clean oil from exhaust manifold. Monitor for leaks after repair. This is a common maintenance item at higher mileage.</x:v>
+        <x:v>Inspect the oil cooler periodically for stone damage and weeping; fit a protective mesh/guard in front of the cooler as preventive insurance (popular among track and spirited-use owners). If punctured, stop driving immediately and replace the oil cooler and refill with the correct oil; verify no bearing damage occurred from any oil starvation.</x:v>
       </x:c>
       <x:c r="F167" s="9" t="n">
         <x:v>0</x:v>
@@ -9964,21 +11296,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="168" ht="594" hidden="0" customHeight="1">
       <x:c r="A168" s="40" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B168" s="9" t="str">
-        <x:v>bmw-n55-vanos-2012</x:v>
+        <x:v>bmw-x3-m-oem-plastic-charge-pipe-cracking-blow-off-under-boost-f97-x3</x:v>
       </x:c>
       <x:c r="C168" s="9" t="str">
-        <x:v>2012-2012 | BMW | 3 Series | N55</x:v>
+        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
       </x:c>
       <x:c r="D168" s="9" t="str">
-        <x:v>Certain 2012 N55 3 Series Need a VANOS Gear-Bolt Recall Check</x:v>
+        <x:v>OEM Plastic Charge Pipe Cracking / Blow-Off Under Boost - F97 X3 M (S58)</x:v>
       </x:c>
       <x:c r="E168" s="9" t="str">
-        <x:v>Check the VIN for campaign 14V-176 before ordering VANOS solenoids or gears. For an affected vehicle, BMW specifies replacing the VANOS gear bolts and inspecting for loose or broken bolts, with additional gear work only when the campaign procedure requires it. Recall work belongs with an authorized BMW center, so no commerce link is approved.</x:v>
+        <x:v>Replace the OEM plastic charge pipe with an aluminum (or reinforced) aftermarket charge pipe from suppliers such as FTP, Racing Dynamics, or Kies; this is the standard durable fix and is strongly recommended before or alongside any tune. A failed OEM pipe can be re-fitted with a new OEM unit but the same failure mode tends to recur, especially on modified cars.</x:v>
       </x:c>
       <x:c r="F168" s="9" t="n">
         <x:v>0</x:v>
@@ -9987,21 +11319,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="660" hidden="0" customHeight="1">
+    <x:row r="169" ht="382.79998779296875" hidden="0" customHeight="1">
       <x:c r="A169" s="40" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B169" s="9" t="str">
-        <x:v>bmw-n55-water-pump-2012</x:v>
+        <x:v>bmw-x3-n20-timing-chain-2011</x:v>
       </x:c>
       <x:c r="C169" s="9" t="str">
-        <x:v>2012-2013 | BMW | 3 Series | N54T, N55</x:v>
+        <x:v>2011-2017 | BMW | X3 | N20</x:v>
       </x:c>
       <x:c r="D169" s="9" t="str">
-        <x:v>2012-2013 335i/335is Overheat Warnings Need Coolant-Pump Diagnosis</x:v>
+        <x:v>N20 Timing Chain Guide Failure</x:v>
       </x:c>
       <x:c r="E169" s="9" t="str">
-        <x:v>Stop safely if an overheat warning appears and avoid continued operation until the cooling system is checked. Verify the chassis, engine and VIN, read fault memory and follow the current coolant-pump test plan before replacement. Settlement benefits were time-limited. ShowMeTheParts resolved five 2012 335i water-pump candidates, but fitment does not prove failure or remedy, so no commerce link is approved.</x:v>
+        <x:v>Replace the complete timing chain kit including chain, guides, tensioner, and sprockets. Preventive replacement is strongly recommended at 80,000 miles before failure occurs. The updated guide design uses more durable materials.</x:v>
       </x:c>
       <x:c r="F169" s="9" t="n">
         <x:v>0</x:v>
@@ -10015,16 +11347,16 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B170" s="9" t="str">
-        <x:v>bmw-x1-coolant-leak-2016</x:v>
+        <x:v>bmw-x3-n20-timing-chain-2012</x:v>
       </x:c>
       <x:c r="C170" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1 | B-series</x:v>
+        <x:v>2013-2015 | BMW | X3 | N20</x:v>
       </x:c>
       <x:c r="D170" s="9" t="str">
-        <x:v>Coolant Leaks - Water Pump &amp; Thermostat - F48 X1</x:v>
+        <x:v>Lower-Engine Whine Requires X3 N20 Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E170" s="9" t="str">
-        <x:v>Replace failed water pump or thermostat housing. Electric water pump replacement is 2-3 hours labor. Thermostat housing is 1-2 hours. Always use BMW-approved coolant (blue or orange, do not mix). Properly bleed cooling system after repair to prevent air pockets. Inspect all coolant hoses during repair and replace if cracked. Preventive replacement of water pump at 80,000 miles recommended.</x:v>
+        <x:v>Confirm the exact X3 variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F170" s="9" t="n">
         <x:v>0</x:v>
@@ -10033,21 +11365,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="171" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A171" s="40" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B171" s="9" t="str">
-        <x:v>bmw-x1-n20-timing-chain-2013</x:v>
+        <x:v>bmw-x3-oil-filter-housing-gasket-2007</x:v>
       </x:c>
       <x:c r="C171" s="9" t="str">
-        <x:v>2013-2015 | BMW | X1 | N20</x:v>
+        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
       </x:c>
       <x:c r="D171" s="9" t="str">
-        <x:v>Lower-Engine Whine Requires X1 N20 Timing-Chain Diagnosis</x:v>
+        <x:v>Oil Filter Housing Gasket Leak (N52, N20 Engines)</x:v>
       </x:c>
       <x:c r="E171" s="9" t="str">
-        <x:v>Confirm the exact model, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Replace oil filter housing gasket and oil cooler gasket ($40-80 DIY repair kit, $300-500 independent shop, $500-800 dealer). Requires draining some coolant and oil, removing housing, replacing gaskets, reassembling. Moderate DIY difficulty - Pelicanparts and YouTube have detailed model-specific guides. Use Victor Reinz or OEM BMW gasket kit for long-lasting seal - cheap gaskets leak within 20k miles. Address leak early before oil damages serpentine belt or alternator.</x:v>
       </x:c>
       <x:c r="F171" s="9" t="n">
         <x:v>0</x:v>
@@ -10056,21 +11388,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="172" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A172" s="40" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B172" s="9" t="str">
-        <x:v>bmw-x1-n20-timing-chain-guide-2013</x:v>
+        <x:v>bmw-x3-transfer-case-actuator-2004</x:v>
       </x:c>
       <x:c r="C172" s="9" t="str">
-        <x:v>2013-2015 | BMW | X1 | N20</x:v>
+        <x:v>2004-2023 | BMW | X3</x:v>
       </x:c>
       <x:c r="D172" s="9" t="str">
-        <x:v>N20 Timing Chain Guide Failure</x:v>
+        <x:v>Transfer Case Actuator Motor Failure (xDrive AWD System)</x:v>
       </x:c>
       <x:c r="E172" s="9" t="str">
-        <x:v>Replace timing chain, guides, tensioner, and both sprockets as a complete kit. The repair requires removing the front of the engine and is labor-intensive. Updated guide materials are available. Preventive replacement at 80,000 miles is recommended for high-mileage N20 engines.</x:v>
+        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket repair kit. DIY repair kits cost $100-150 and include replacement plastic gears, clips, and seals - straightforward installation saves $1,200+. Complete actuator motor replacement costs $540 for the assembly if DIY, or $1,500-2,200 at dealer. If transfer case itself is damaged from prolonged actuator failure, complete transfer case replacement costs $1,400-3,300. PREVENTIVE: If buying used X3 over 80k miles, budget for this repair - it's "when not if" on xDrive models. Check for clicking noise when shutting off ignition.</x:v>
       </x:c>
       <x:c r="F172" s="9" t="n">
         <x:v>0</x:v>
@@ -10084,85 +11416,85 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B173" s="9" t="str">
-        <x:v>bmw-x1-oil-filter-housing-gasket-2013</x:v>
+        <x:v>bmw-x3-transfer-case-actuator-2011</x:v>
       </x:c>
       <x:c r="C173" s="9" t="str">
-        <x:v>2013-2022 | BMW | X1 | N20, B48</x:v>
+        <x:v>2011-2026 | BMW | X3</x:v>
       </x:c>
       <x:c r="D173" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak</x:v>
+        <x:v>Transfer Case Actuator Motor Failure</x:v>
       </x:c>
       <x:c r="E173" s="9" t="str">
-        <x:v>Replace the oil filter housing gasket and clean all affected surfaces. Also inspect and replace the oil cooler gasket if present. Use only OEM-quality gaskets as aftermarket gaskets tend to fail prematurely. Typical repair takes 2-3 hours.</x:v>
+        <x:v>Replace the transfer case actuator motor. Change the transfer case fluid at the same time. The actuator can be replaced without removing the entire transfer case. Rebuilt units are available at lower cost but OEM is recommended for reliability.</x:v>
       </x:c>
       <x:c r="F173" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G173" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="174" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A174" s="40" t="n">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B174" s="9" t="str">
-        <x:v>bmw-x1-oil-leak-2016</x:v>
+        <x:v>bmw-x3-valve-cover-gasket-2004</x:v>
       </x:c>
       <x:c r="C174" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1 | B46, B48</x:v>
+        <x:v>2004-2017 | BMW | X3 | 2.5i, 3.0i, 3.0si | M54, N52</x:v>
       </x:c>
       <x:c r="D174" s="9" t="str">
-        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - F48 X1</x:v>
+        <x:v>Valve Cover Gasket Oil Leaks (M54, N52 Engines)</x:v>
       </x:c>
       <x:c r="E174" s="9" t="str">
-        <x:v>Replace valve cover gasket and/or oil filter housing gasket as needed. Valve cover replacement is 2-3 hours labor. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on B-series engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
+        <x:v>Replace valve cover gasket and VANOS solenoid o-rings ($300-500 independent shop, $700-1,000 dealer, $80-150 DIY parts). On M54 engines, also replace ignition coil boots if contaminated by oil ($50 additional). Use OEM BMW gasket or Victor Reinz brand - aftermarket quality matters for long-term seal. Relatively straightforward DIY repair - saves $200-400 in labor. YouTube and Bimmerfest have detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage).</x:v>
       </x:c>
       <x:c r="F174" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G174" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="175" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A175" s="40" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B175" s="9" t="str">
-        <x:v>bmw-x1-suspension-bushing-2016</x:v>
+        <x:v>bmw-x3-valve-cover-gasket-2011</x:v>
       </x:c>
       <x:c r="C175" s="9" t="str">
-        <x:v>2016-2023 | BMW | X1</x:v>
+        <x:v>2011-2022 | BMW | X3 | N20, B48</x:v>
       </x:c>
       <x:c r="D175" s="9" t="str">
-        <x:v>Front Suspension Bushing &amp; Control Arm Wear - F48 X1</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E175" s="9" t="str">
-        <x:v>Replace worn control arms or bushings. Most shops replace complete control arms (with integrated bushings) rather than pressing in new bushings alone. Alignment required after replacement. Inspect all suspension components while vehicle is lifted. Consider replacing both sides even if only one shows symptoms to avoid repeat labor costs. Use OEM or quality aftermarket parts (Lemforder, Meyle HD) for longevity.</x:v>
+        <x:v>Replace the valve cover gasket. Inspect the valve cover for warping or cracks — if damaged, replace the entire cover assembly. Clean all oil residue from surrounding components. Use a torque wrench to prevent over-tightening which causes cover warping.</x:v>
       </x:c>
       <x:c r="F175" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G175" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="660" hidden="0" customHeight="1">
+    <x:row r="176" ht="858" hidden="0" customHeight="1">
       <x:c r="A176" s="40" t="n">
         <x:v>175</x:v>
       </x:c>
       <x:c r="B176" s="9" t="str">
-        <x:v>bmw-x1-transfer-case-2013</x:v>
+        <x:v>bmw-x3-vanos-solenoid-2007</x:v>
       </x:c>
       <x:c r="C176" s="9" t="str">
-        <x:v>2013-2023 | BMW | X1</x:v>
+        <x:v>2007-2017 | BMW | X3 | M40i, M50, xDrive35i | N52, N55</x:v>
       </x:c>
       <x:c r="D176" s="9" t="str">
-        <x:v>Transfer Case Failure - xDrive Models E84/F48 X1</x:v>
+        <x:v>VANOS Solenoid Failure (N52, N55 Engines)</x:v>
       </x:c>
       <x:c r="E176" s="9" t="str">
-        <x:v>Diagnose specific failure point. Transfer case actuator motor can be replaced separately ($800-1,200) if caught early. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors for better durability. Common wear item on high-mileage xDrive models.</x:v>
+        <x:v>Replace VANOS solenoids and seals ($250-400 European shops, $729-882 US average). Use high-quality oil (5W-30 or 0W-40 BMW LL-01 spec) and change every 5,000-7,000 miles to prevent future failures - cheap oil or extended intervals kill VANOS solenoids. Some cases may require complete VANOS unit rebuild ($1,500-2,500). PREVENTIVE: Replace VANOS solenoids and seals every 50k miles as maintenance - much cheaper than waiting for failure. On F25 X3 with N52/N55, check TSB SI B12 14 10 for VANOS gear assembly bolt issue.</x:v>
       </x:c>
       <x:c r="F176" s="9" t="n">
         <x:v>0</x:v>
@@ -10171,21 +11503,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="177" ht="1016.4000244140625" hidden="0" customHeight="1">
       <x:c r="A177" s="40" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B177" s="9" t="str">
-        <x:v>bmw-x1-transfer-case-actuator-2013</x:v>
+        <x:v>bmw-x3-wastegate-rattle-2011</x:v>
       </x:c>
       <x:c r="C177" s="9" t="str">
-        <x:v>2013-2022 | BMW | X1</x:v>
+        <x:v>2011-2023 | BMW | X3 | M40i, M50, sDrive30i, xDrive28i, xDrive30i, xDrive35i</x:v>
       </x:c>
       <x:c r="D177" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure</x:v>
+        <x:v>Turbocharger Wastegate Rattle (N55, N20, B58 Engines)</x:v>
       </x:c>
       <x:c r="E177" s="9" t="str">
-        <x:v>Replace the transfer case actuator motor (also called the servo motor). The transfer case itself usually does not need replacement. Ensure the transfer case fluid is changed at the same time. Some owners report success with rebuilt actuators at lower cost.</x:v>
+        <x:v>Replace wastegate actuator ($400-800) or use aftermarket wastegate repair kit with upgraded stainless steel bushings ($150-300). Some cases require complete turbocharger replacement ($2,000-$4,000). VTT (Vargas Turbo Technologies) repair kits popular on forums - upgraded materials prevent future rattle. MONITORING: Early wastegate rattle may be harmless (annoying but no performance loss). If car boosts normally and no underboost codes, can monitor rattle without urgent repair. However, if check engine light appears with code 30FF or boost pressure drops, repair immediately to prevent turbo damage.</x:v>
       </x:c>
       <x:c r="F177" s="9" t="n">
         <x:v>0</x:v>
@@ -10194,21 +11526,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="178" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A178" s="40" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B178" s="9" t="str">
-        <x:v>bmw-x2-b48-timing-chain-tensioner-2018</x:v>
+        <x:v>bmw-x3-water-pump-2007</x:v>
       </x:c>
       <x:c r="C178" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | B48</x:v>
+        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
       </x:c>
       <x:c r="D178" s="9" t="str">
-        <x:v>B48 Timing Chain Tensioner Weakness</x:v>
+        <x:v>Electric Water Pump Failure (N52, N20 Engines)</x:v>
       </x:c>
       <x:c r="E178" s="9" t="str">
-        <x:v>Replace the timing chain tensioner and inspect the chain and guides. If the chain has stretched beyond specification, replace the full timing chain kit. Updated tensioner design from BMW addresses the oil pressure retention issue.</x:v>
+        <x:v>Replace electric water pump at first sign of failure ($800 parts + labor). Consider preventative replacement at 70-80k miles to avoid being stranded ($400 parts, DIY-able). CRITICAL: If you own 2013-2017 X3 28i, verify recall repair (protective shield installation) has been completed to prevent fire risk - check with BMW dealer using VIN. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps cylinder heads ($4,000+ repair). Call tow truck.</x:v>
       </x:c>
       <x:c r="F178" s="9" t="n">
         <x:v>0</x:v>
@@ -10217,21 +11549,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="179" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="179" ht="1240.800048828125" hidden="0" customHeight="1">
       <x:c r="A179" s="40" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B179" s="9" t="str">
-        <x:v>bmw-x2-crankshaft-sensor-recall-2018</x:v>
+        <x:v>bmw-x3m-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C179" s="9" t="str">
-        <x:v>2018-2018 | BMW | X2</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D179" s="9" t="str">
-        <x:v>2018 X2 Crankshaft Sensor Safety Recall 18V-465</x:v>
+        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E179" s="9" t="str">
-        <x:v>Check the VIN for an open 18V-465 campaign. If open, an authorized BMW dealer replaces the crankshaft sensor free of charge. A stall or sudden loss of power requires moving to a safe location and arranging BMW assistance; do not order a sensor from this card. ShowMeTheParts resolved exact X2 category fitment only, so no commerce link is approved.</x:v>
+        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
       </x:c>
       <x:c r="F179" s="9" t="n">
         <x:v>0</x:v>
@@ -10240,21 +11572,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="180" ht="1188" hidden="0" customHeight="1">
       <x:c r="A180" s="40" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B180" s="9" t="str">
-        <x:v>bmw-x2-front-control-arm-bushings-2018</x:v>
+        <x:v>bmw-x3m-cooling-track-use-2020</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D180" s="9" t="str">
-        <x:v>Front Control Arm Bushing Premature Wear</x:v>
+        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E180" s="9" t="str">
-        <x:v>Replace front control arms with new bushings (sold as complete assemblies by BMW). Aftermarket options with upgraded polyurethane bushings are available for longer life. Perform a four-wheel alignment after replacement.</x:v>
+        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
       </x:c>
       <x:c r="F180" s="9" t="n">
         <x:v>0</x:v>
@@ -10263,21 +11595,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="181" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A181" s="40" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B181" s="9" t="str">
-        <x:v>bmw-x2-oil-filter-housing-2018</x:v>
+        <x:v>bmw-x3m-differential-bolt-2020</x:v>
       </x:c>
       <x:c r="C181" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | sDrive28i, xDrive28i | B48</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D181" s="9" t="str">
-        <x:v>B48 Oil Filter Housing Gasket Leak/Cracking</x:v>
+        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E181" s="9" t="str">
-        <x:v>Replace the cracked oil filter housing. OEM plastic housing replacement (BMW 11428596283, $412 dealer) will eventually crack again. RECOMMENDED: Install aftermarket aluminum upgrade housing ($250-350) which permanently eliminates the heat-cycling crack issue. FCP Euro kit 11428596283KT ($450) includes all gaskets and seals. If coolant and oil have mixed, perform complete oil flush and coolant system flush before installing new housing. Check for engine damage if contamination was prolonged.</x:v>
+        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
       </x:c>
       <x:c r="F181" s="9" t="n">
         <x:v>0</x:v>
@@ -10286,21 +11618,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="330" hidden="0" customHeight="1">
+    <x:row r="182" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A182" s="40" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B182" s="9" t="str">
-        <x:v>bmw-x2-oil-filter-housing-gasket-2018</x:v>
+        <x:v>bmw-x3m-s58-bearing-recall-2020</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2 | B48</x:v>
+        <x:v>2020-2021 | BMW | X3 M</x:v>
       </x:c>
       <x:c r="D182" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak</x:v>
+        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E182" s="9" t="str">
-        <x:v>Replace the oil filter housing gasket. Clean all oil-contaminated surfaces and inspect the serpentine belt for oil damage. Replace belt if oil-soaked. Use OEM-quality gasket material for longevity.</x:v>
+        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
       </x:c>
       <x:c r="F182" s="9" t="n">
         <x:v>0</x:v>
@@ -10309,21 +11641,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="183" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A183" s="40" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B183" s="9" t="str">
-        <x:v>bmw-x2-tie-rod-recall-2019</x:v>
+        <x:v>bmw-x3m-transfer-case-2020</x:v>
       </x:c>
       <x:c r="C183" s="9" t="str">
-        <x:v>2019-2019 | BMW | X2</x:v>
+        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
       </x:c>
       <x:c r="D183" s="9" t="str">
-        <x:v>2019 X2 Steering Tie-Rod Safety Recall 19V-601</x:v>
+        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F97 X3 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E183" s="9" t="str">
-        <x:v>Check the VIN in BMW AIR or NHTSA for an open 19V-601 campaign. If open, an authorized BMW dealer checks both tie rods and replaces the tie rods and ball joints as necessary free of charge. Do not infer recall eligibility from model year alone or order steering parts from this card.</x:v>
+        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
       </x:c>
       <x:c r="F183" s="9" t="n">
         <x:v>0</x:v>
@@ -10332,21 +11664,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="184" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A184" s="40" t="n">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B184" s="9" t="str">
-        <x:v>bmw-x2-transmission-jerking-2018</x:v>
+        <x:v>bmw-x4-n20-timing-chain-2015</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
-        <x:v>2018-2020 | BMW | X2</x:v>
+        <x:v>2015-2016 | BMW | X4 | xDrive28i, xDrive30i</x:v>
       </x:c>
       <x:c r="D184" s="9" t="str">
-        <x:v>Aisin 8-Speed Transmission Jerking</x:v>
+        <x:v>N20 Timing Chain Premature Failure - F26 X4 xDrive28i</x:v>
       </x:c>
       <x:c r="E184" s="9" t="str">
-        <x:v>Start with transmission software recalibration at BMW dealer ($200-500) which may resolve calibration-related shifting issues. If software update does not resolve, transmission may require oil pump replacement or internal repair ($2,000-5,000). In severe cases with extensive oil pump neck wear, complete transmission replacement required ($5,000-7,000). Reference TSB GBSEL-SELP24 when visiting dealer.</x:v>
+        <x:v>Complete timing chain kit replacement including chain, guides, tensioner, and sprockets. Must be performed by experienced BMW technician. Preventive replacement recommended at 60,000-80,000 miles. BMW extended warranty to 8 years/100,000 miles under class action settlement. Upgraded reinforced chain kit available from aftermarket. Labor is 10-14 hours for X4 due to AWD and tight engine bay.</x:v>
       </x:c>
       <x:c r="F184" s="9" t="n">
         <x:v>0</x:v>
@@ -10355,21 +11687,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="185" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A185" s="40" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B185" s="9" t="str">
-        <x:v>bmw-x2-valve-cover-gasket-2018</x:v>
+        <x:v>bmw-x4-n20-timing-chain-guide-2015</x:v>
       </x:c>
       <x:c r="C185" s="9" t="str">
-        <x:v>2018-2023 | BMW | X2</x:v>
+        <x:v>2015-2015 | BMW | X4 | N20</x:v>
       </x:c>
       <x:c r="D185" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>2015 X4 N20 Lower-Engine Whine Requires Timing-Chain Diagnosis</x:v>
       </x:c>
       <x:c r="E185" s="9" t="str">
-        <x:v>Replace valve cover gasket. Genuine BMW valve cover assembly 11127611278 ($200-350) includes integrated gasket. Labor typically 2-3 hours ($300-500). Total cost $700-1,000 at shop. DIY possible with basic tools to save $300-500 in labor. Replace spark plug tube seals at same time if applicable - labor overlap saves money. Monitor oil level between repairs.</x:v>
+        <x:v>Confirm the exact xDrive28i variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
       </x:c>
       <x:c r="F185" s="9" t="n">
         <x:v>0</x:v>
@@ -10378,21 +11710,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="990" hidden="0" customHeight="1">
+    <x:row r="186" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A186" s="40" t="n">
         <x:v>185</x:v>
       </x:c>
       <x:c r="B186" s="9" t="str">
-        <x:v>bmw-x3-coolant-expansion-tank-2004</x:v>
+        <x:v>bmw-x4-oil-leak-2015</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
-        <x:v>2004-2023 | BMW | X3</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D186" s="9" t="str">
-        <x:v>Coolant Expansion Tank Cracking</x:v>
+        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - All Models</x:v>
       </x:c>
       <x:c r="E186" s="9" t="str">
-        <x:v>Replace expansion tank and coolant ($50-100 DIY parts, $200-400 independent shop, $400-580 dealer). Very simple DIY repair taking 30 minutes - drain coolant, unbolt old tank, install new tank, refill with BMW-spec coolant (blue or pink/orange premix). Use Behr or OEM BMW expansion tank - Dorman aftermarket tanks may fail prematurely. YouTube and Pelicanparts have detailed DIY guides. PREVENTIVE: Replace every 5-7 years or 80-100k miles before cracks develop. Check tank regularly for hairline cracks. Don't ignore coolant leaks - can lead to catastrophic overheating and head gasket failure.</x:v>
+        <x:v>Replace valve cover gasket and/or oil filter housing gasket. Valve cover replacement is 3-4 hours labor on X4. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on BMW turbo engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
       </x:c>
       <x:c r="F186" s="9" t="n">
         <x:v>0</x:v>
@@ -10401,44 +11733,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="187" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A187" s="40" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B187" s="9" t="str">
-        <x:v>bmw-x3-electric-water-pump-2011</x:v>
+        <x:v>bmw-x4-rear-differential-mount-2015</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
-        <x:v>2011-2026 | BMW | X3</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D187" s="9" t="str">
-        <x:v>Electric Water Pump Failure</x:v>
+        <x:v>Rear Differential Mount Bushing Failure</x:v>
       </x:c>
       <x:c r="E187" s="9" t="str">
-        <x:v>Replace the electric water pump and thermostat together, as they are part of the same cooling circuit and the thermostat often fails concurrently. Bleed the cooling system thoroughly after replacement. Some owners carry a spare pump due to the sudden failure nature.</x:v>
+        <x:v>Replace rear differential mount bushings. Both front and rear differential bushings should be inspected and replaced as a set. Upgraded aftermarket bushings with stiffer rubber or polyurethane are available for longer service life.</x:v>
       </x:c>
       <x:c r="F187" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G187" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="188" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A188" s="40" t="n">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B188" s="9" t="str">
-        <x:v>bmw-x3-m-electric-wastegate-actuator-adaptation-fault-boost-cutout-ea</x:v>
+        <x:v>bmw-x4-transfer-case-2015</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
-        <x:v>2020-2020 | BMW | X3 M | S58</x:v>
+        <x:v>2015-2023 | BMW | X4</x:v>
       </x:c>
       <x:c r="D188" s="9" t="str">
-        <x:v>2020 X3 M Wastegate Adaptation Faults Require Software Diagnosis</x:v>
+        <x:v>Transfer Case Actuator Motor Failure - All xDrive X4</x:v>
       </x:c>
       <x:c r="E188" s="9" t="str">
-        <x:v>Confirm the production date, fault codes and current vehicle integration level. If the I-level is below S15A-20-03-510, a BMW-qualified repairer follows the bulletin and programs the vehicle with the specified or newer approved ISTA level. Diagnose unrelated mechanical noise separately; do not replace an actuator or turbocharger from this card.</x:v>
+        <x:v>Diagnose specific failure. Transfer case actuator motor replacement ($800-1,200) is most common. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors. Common wear item on high-mileage xDrive BMW models.</x:v>
       </x:c>
       <x:c r="F188" s="9" t="n">
         <x:v>0</x:v>
@@ -10447,21 +11779,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" ht="462" hidden="0" customHeight="1">
+    <x:row r="189" ht="1240.800048828125" hidden="0" customHeight="1">
       <x:c r="A189" s="40" t="n">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B189" s="9" t="str">
-        <x:v>bmw-x3-m-fuel-tank-inlet-check-valve-weld-failure-2021-x3-m</x:v>
+        <x:v>bmw-x4m-brake-wear-2020</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
-        <x:v>2021-2021 | BMW | X3 M</x:v>
+        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
       </x:c>
       <x:c r="D189" s="9" t="str">
-        <x:v>2021 X3 M Fuel-Tank Safety Recall 21V-199</x:v>
+        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E189" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-199 campaign. If open, an authorized BMW dealer replaces the fuel tank free of charge. If fuel odor or leakage appears, move safely away from traffic, stop, have occupants exit and contact BMW roadside assistance; do not continue driving or order a tank from this card.</x:v>
+        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
       </x:c>
       <x:c r="F189" s="9" t="n">
         <x:v>0</x:v>
@@ -10470,21 +11802,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="190" ht="1188" hidden="0" customHeight="1">
       <x:c r="A190" s="40" t="n">
         <x:v>189</x:v>
       </x:c>
       <x:c r="B190" s="9" t="str">
-        <x:v>bmw-x3-m-idrive-control-display-blank-screen-infotainment-glitches-f9</x:v>
+        <x:v>bmw-x4m-cooling-track-use-2020</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
-        <x:v>2020-2021 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2023 | BMW | X4 M</x:v>
       </x:c>
       <x:c r="D190" s="9" t="str">
-        <x:v>iDrive Control Display Blank Screen and Infotainment Glitches - F97 X3 M (2019-2021)</x:v>
+        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E190" s="9" t="str">
-        <x:v>First try the latest iDrive/head-unit software update at the dealer, which resolves many of the early glitches, reboots, and camera issues. If the display panel hardware has failed (lines, persistent blank screen with backlight off), the control display/screen assembly is replaced. A soft reset (press-and-hold volume/power) can temporarily clear a frozen screen.</x:v>
+        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
       </x:c>
       <x:c r="F190" s="9" t="n">
         <x:v>0</x:v>
@@ -10493,21 +11825,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="462" hidden="0" customHeight="1">
+    <x:row r="191" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A191" s="40" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="B191" s="9" t="str">
-        <x:v>bmw-x3-m-improperly-welded-front-seat-frame-2019-2021-x3-m</x:v>
+        <x:v>bmw-x4m-differential-bolt-2020</x:v>
       </x:c>
       <x:c r="C191" s="9" t="str">
-        <x:v>2021-2021 | BMW | X3 M</x:v>
+        <x:v>2020-2023 | BMW | X4 M</x:v>
       </x:c>
       <x:c r="D191" s="9" t="str">
-        <x:v>2021 X3 M Front Seat-Frame Safety Recall 23V-211</x:v>
+        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E191" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-211 campaign. If open, an authorized BMW dealer replaces the affected front seat frame and backrest free of charge using VIN-selected parts. Contact BMW promptly if a front seat vibrates or makes abnormal noise; do not order seat components from this card.</x:v>
+        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
       </x:c>
       <x:c r="F191" s="9" t="n">
         <x:v>0</x:v>
@@ -10516,21 +11848,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="192" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A192" s="40" t="n">
         <x:v>191</x:v>
       </x:c>
       <x:c r="B192" s="9" t="str">
-        <x:v>bmw-x3-m-low-mounted-engine-oil-cooler-vulnerable-to-road-debris-punc</x:v>
+        <x:v>bmw-x4m-s58-bearing-recall-2020</x:v>
       </x:c>
       <x:c r="C192" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2021 | BMW | X4 M | M40i, xDrive35i | S58</x:v>
       </x:c>
       <x:c r="D192" s="9" t="str">
-        <x:v>Low-Mounted Engine Oil Cooler Vulnerable to Road-Debris Puncture - F97 X3 M (S58)</x:v>
+        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E192" s="9" t="str">
-        <x:v>Inspect the oil cooler periodically for stone damage and weeping; fit a protective mesh/guard in front of the cooler as preventive insurance (popular among track and spirited-use owners). If punctured, stop driving immediately and replace the oil cooler and refill with the correct oil; verify no bearing damage occurred from any oil starvation.</x:v>
+        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
       </x:c>
       <x:c r="F192" s="9" t="n">
         <x:v>0</x:v>
@@ -10539,21 +11871,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="594" hidden="0" customHeight="1">
+    <x:row r="193" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A193" s="40" t="n">
         <x:v>192</x:v>
       </x:c>
       <x:c r="B193" s="9" t="str">
-        <x:v>bmw-x3-m-oem-plastic-charge-pipe-cracking-blow-off-under-boost-f97-x3</x:v>
+        <x:v>bmw-x4m-transfer-case-2020</x:v>
       </x:c>
       <x:c r="C193" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | X3 M, X3 M Competition | S58, S58B30</x:v>
+        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
       </x:c>
       <x:c r="D193" s="9" t="str">
-        <x:v>OEM Plastic Charge Pipe Cracking / Blow-Off Under Boost - F97 X3 M (S58)</x:v>
+        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F98 X4 M / F98 X4 M</x:v>
       </x:c>
       <x:c r="E193" s="9" t="str">
-        <x:v>Replace the OEM plastic charge pipe with an aluminum (or reinforced) aftermarket charge pipe from suppliers such as FTP, Racing Dynamics, or Kies; this is the standard durable fix and is strongly recommended before or alongside any tune. A failed OEM pipe can be re-fitted with a new OEM unit but the same failure mode tends to recur, especially on modified cars.</x:v>
+        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
       </x:c>
       <x:c r="F193" s="9" t="n">
         <x:v>0</x:v>
@@ -10562,21 +11894,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="382.79998779296875" hidden="0" customHeight="1">
+    <x:row r="194" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A194" s="40" t="n">
         <x:v>193</x:v>
       </x:c>
       <x:c r="B194" s="9" t="str">
-        <x:v>bmw-x3-n20-timing-chain-2011</x:v>
+        <x:v>bmw-x5-air-suspension-2007</x:v>
       </x:c>
       <x:c r="C194" s="9" t="str">
-        <x:v>2011-2017 | BMW | X3 | N20</x:v>
+        <x:v>2019-2026 | BMW | X5</x:v>
       </x:c>
       <x:c r="D194" s="9" t="str">
-        <x:v>N20 Timing Chain Guide Failure</x:v>
+        <x:v>G05 Suspension Warning: Check Faults and Campaigns Before Parts</x:v>
       </x:c>
       <x:c r="E194" s="9" t="str">
-        <x:v>Replace the complete timing chain kit including chain, guides, tensioner, and sprockets. Preventive replacement is strongly recommended at 80,000 miles before failure occurs. The updated guide design uses more durable materials.</x:v>
+        <x:v>Start with the VIN build/options, open-campaign status, exact warning, complete fault memory, and BMW ISTA test plan. If the VIN and production date match a BMW action, follow that bulletin: inspect the specified sensor-link holders, apply the specified software correction, or inspect the affected air line as directed. For other vehicles, test the particular system shown by the VIN and fault path before selecting any component. Do not buy a compressor, strut, spring, or conversion kit until the failed part and its VIN-specific number are established. This article intentionally has no retail link because no single part repairs all of these conditions.</x:v>
       </x:c>
       <x:c r="F194" s="9" t="n">
         <x:v>0</x:v>
@@ -10585,44 +11917,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="195" ht="1148.4000244140625" hidden="0" customHeight="1">
       <x:c r="A195" s="40" t="n">
         <x:v>194</x:v>
       </x:c>
       <x:c r="B195" s="9" t="str">
-        <x:v>bmw-x3-n20-timing-chain-2012</x:v>
+        <x:v>bmw-x5-air-suspension-compressor-2007</x:v>
       </x:c>
       <x:c r="C195" s="9" t="str">
-        <x:v>2013-2015 | BMW | X3 | N20</x:v>
+        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive35i, xDrive48i, xDrive50i, X5 M | N52, N62, M57, N55, N63, S63</x:v>
       </x:c>
       <x:c r="D195" s="9" t="str">
-        <x:v>Lower-Engine Whine Requires X3 N20 Timing-Chain Diagnosis</x:v>
+        <x:v>E70 Rear Air-Supply Unit: Diagnose the Self-Leveling System First</x:v>
       </x:c>
       <x:c r="E195" s="9" t="str">
-        <x:v>Confirm the exact X3 variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Read the EHC fault memory and run the applicable BMW ISTA test plan before ordering a compressor. Confirm the vehicle is equipped with rear self-leveling suspension, compare left/right ride height, check system power and wiring, inspect the height-sensor links, and leak-test the air springs, lines, and valve system. Test the air supply only after those checks isolate it. If BMW ETK/AIR selects the E70 air-supply system for the VIN and diagnosis confirms that assembly, replace it with current part 37-20-6-859-714, follow the BMW repair procedure, clear faults, and perform the required ride-height calibration. Do not install a generic compressor or a coil-conversion kit from symptoms alone.</x:v>
       </x:c>
       <x:c r="F195" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G195" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="196" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A196" s="40" t="n">
         <x:v>195</x:v>
       </x:c>
       <x:c r="B196" s="9" t="str">
-        <x:v>bmw-x3-oil-filter-housing-gasket-2007</x:v>
+        <x:v>bmw-x5-carbon-buildup-2007</x:v>
       </x:c>
       <x:c r="C196" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
+        <x:v>2011-2018 | BMW | X5 | xDrive35i, xDrive50i | N55, N63, N63TU1</x:v>
       </x:c>
       <x:c r="D196" s="9" t="str">
-        <x:v>Oil Filter Housing Gasket Leak (N52, N20 Engines)</x:v>
+        <x:v>Possible Intake-Valve Deposits on Direct-Injected Gasoline Engines</x:v>
       </x:c>
       <x:c r="E196" s="9" t="str">
-        <x:v>Replace oil filter housing gasket and oil cooler gasket ($40-80 DIY repair kit, $300-500 independent shop, $500-800 dealer). Requires draining some coolant and oil, removing housing, replacing gaskets, reassembling. Moderate DIY difficulty - Pelicanparts and YouTube have detailed model-specific guides. Use Victor Reinz or OEM BMW gasket kit for long-lasting seal - cheap gaskets leak within 20k miles. Address leak early before oil damages serpentine belt or alternator.</x:v>
+        <x:v>Diagnose the actual symptom before authorizing cleaning: read BMW-specific faults and misfire counters, check ignition and fueling, smoke-test the intake where indicated, verify crankcase ventilation operation, and inspect the intake valves with a borescope or by removing the intake manifold when the test plan supports it. If substantial deposits are confirmed and match the complaint, use an engine-specific professional mechanical-cleaning procedure that protects closed valves and removes all blasting media before reassembly. Do not present a universal catch can, chemical spray, fuel brand, short oil interval, or high-RPM driving as a proven repair. Any crankcase-ventilation modification also requires engine-specific fitment and emissions-law review.</x:v>
       </x:c>
       <x:c r="F196" s="9" t="n">
         <x:v>0</x:v>
@@ -10631,90 +11963,90 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="197" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A197" s="40" t="n">
         <x:v>196</x:v>
       </x:c>
       <x:c r="B197" s="9" t="str">
-        <x:v>bmw-x3-transfer-case-actuator-2004</x:v>
+        <x:v>bmw-x5-coolant-pipe-leak-2007</x:v>
       </x:c>
       <x:c r="C197" s="9" t="str">
-        <x:v>2004-2023 | BMW | X3</x:v>
+        <x:v>2007-2010 | BMW | X5 | 4.8i, xDrive48i | N62, N62TU</x:v>
       </x:c>
       <x:c r="D197" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure (xDrive AWD System)</x:v>
+        <x:v>E70 N62 Coolant Transfer Pipe Leak (Pressure-Test First)</x:v>
       </x:c>
       <x:c r="E197" s="9" t="str">
-        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket repair kit. DIY repair kits cost $100-150 and include replacement plastic gears, clips, and seals - straightforward installation saves $1,200+. Complete actuator motor replacement costs $540 for the assembly if DIY, or $1,500-2,200 at dealer. If transfer case itself is damaged from prolonged actuator failure, complete transfer case replacement costs $1,400-3,300. PREVENTIVE: If buying used X3 over 80k miles, budget for this repair - it's "when not if" on xDrive models. Check for clicking noise when shutting off ignition.</x:v>
+        <x:v>Pressure-test the cooling system cold and inspect the engine valley and all accessible connections to identify the exact leak before ordering parts. If inspection confirms the N62 transfer pipe and BMW ETK/AIR selects it for the VIN, replace pipe 11-14-1-439-975 with the required seals and one-time-use hardware from the VIN-specific repair diagram. Refill and bleed the cooling system with the specified coolant, repeat the pressure test, and verify stable temperature. Do not automatically replace an N63 pipe, thermostat, or unrelated hoses from this article.</x:v>
       </x:c>
       <x:c r="F197" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G197" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" ht="396" hidden="0" customHeight="1">
+    <x:row r="198" ht="1082.4000244140625" hidden="0" customHeight="1">
       <x:c r="A198" s="40" t="n">
         <x:v>197</x:v>
       </x:c>
       <x:c r="B198" s="9" t="str">
-        <x:v>bmw-x3-transfer-case-actuator-2011</x:v>
+        <x:v>bmw-x5-n63-timing-chain-2008</x:v>
       </x:c>
       <x:c r="C198" s="9" t="str">
-        <x:v>2011-2026 | BMW | X3</x:v>
+        <x:v>2010-2013 | BMW | X5 | xDrive50i | N63</x:v>
       </x:c>
       <x:c r="D198" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure</x:v>
+        <x:v>Early N63 Timing-Chain Wear Check: ISTA Test Before Repair</x:v>
       </x:c>
       <x:c r="E198" s="9" t="str">
-        <x:v>Replace the transfer case actuator motor. Change the transfer case fluid at the same time. The actuator can be replaced without removing the entire transfer case. Rebuilt units are available at lower cost but OEM is recommended for reliability.</x:v>
+        <x:v>Check the VIN and service history with a BMW center, diagnose stored VANOS/camshaft faults first, and run BMW's ISTA timing-chain elongation test. If the result is 'Timing chain is OK,' do not replace parts on this claim. If it is 'not OK,' BMW SIB 11 16 14 directs replacement of both timing chains under the VIN-specific repair instruction, followed by the required oil/filter service, priming steps, programming, and shorter oil-service interval. A single tensioner 11-31-7-557-741 or a generic Cloyes kit is not the complete repair and must not be presented as what the owner needs. Tow the vehicle rather than driving it when severe mechanical noise, oil-pressure warnings, or loss of timing is present.</x:v>
       </x:c>
       <x:c r="F198" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G198" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="199" ht="1227.5999755859375" hidden="0" customHeight="1">
       <x:c r="A199" s="40" t="n">
         <x:v>198</x:v>
       </x:c>
       <x:c r="B199" s="9" t="str">
-        <x:v>bmw-x3-valve-cover-gasket-2004</x:v>
+        <x:v>bmw-x5-n63-wastegate-2008</x:v>
       </x:c>
       <x:c r="C199" s="9" t="str">
-        <x:v>2004-2017 | BMW | X3 | 2.5i, 3.0i, 3.0si | M54, N52</x:v>
+        <x:v>2010-2018 | BMW | X5 | xDrive50i | N63, N63TU</x:v>
       </x:c>
       <x:c r="D199" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leaks (M54, N52 Engines)</x:v>
+        <x:v>N63/N63TU Low Boost or Turbo Rattle: Diagnose Vacuum Control First</x:v>
       </x:c>
       <x:c r="E199" s="9" t="str">
-        <x:v>Replace valve cover gasket and VANOS solenoid o-rings ($300-500 independent shop, $700-1,000 dealer, $80-150 DIY parts). On M54 engines, also replace ignition coil boots if contaminated by oil ($50 additional). Use OEM BMW gasket or Victor Reinz brand - aftermarket quality matters for long-term seal. Relatively straightforward DIY repair - saves $200-400 in labor. YouTube and Bimmerfest have detailed model-specific guides. Monitor oil level weekly and top off as needed (1 quart low is OK, 2+ quarts low risks engine damage).</x:v>
+        <x:v>Read all DME faults and compare requested versus actual boost under the BMW test plan. Pressure- or smoke-test the intake and charge-air path, verify vacuum supply from the pump and reservoir, inspect both banks' hoses and pressure converters, and test actuator movement before condemning a turbocharger. Identify the engine generation, failed bank, and exact hardware in BMW ETK/AIR. Check a 2010-2013 E70 VIN for the N63 Customer Care Package only as applicable; its published six-point scope includes air-mass sensors, injectors, vacuum pump, low-pressure fuel sensor/feed line, fresh-air turbo seals, and crankcase-ventilation lines, not an automatic wastegate replacement. No retail link is published until diagnosis selects a VIN-specific component.</x:v>
       </x:c>
       <x:c r="F199" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G199" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="200" ht="844.7999877929688" hidden="0" customHeight="1">
       <x:c r="A200" s="40" t="n">
         <x:v>199</x:v>
       </x:c>
       <x:c r="B200" s="9" t="str">
-        <x:v>bmw-x3-valve-cover-gasket-2011</x:v>
+        <x:v>bmw-x5-oil-leaks-2000</x:v>
       </x:c>
       <x:c r="C200" s="9" t="str">
-        <x:v>2011-2022 | BMW | X3 | N20, B48</x:v>
+        <x:v>2003-2006 | BMW | X5 | 3.0i | M54</x:v>
       </x:c>
       <x:c r="D200" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>E53 3.0i M54 Valve-Cover Gasket Leak (Confirm the Source)</x:v>
       </x:c>
       <x:c r="E200" s="9" t="str">
-        <x:v>Replace the valve cover gasket. Inspect the valve cover for warping or cracks — if damaged, replace the entire cover assembly. Clean all oil residue from surrounding components. Use a torque wrench to prevent over-tightening which causes cover warping.</x:v>
+        <x:v>Clean the engine and trace the highest fresh-oil source before ordering a gasket. If the leak is at the M54 cylinder-head-cover perimeter or spark-plug-well seals, inspect the plastic cover for cracks, warpage, damaged fastener grommets, and crankcase-ventilation faults. Reuse the cover only if it passes inspection, then install VIN/production-confirmed gasket set 11-12-0-030-496 with the BMW-specified grommets and sealant locations and torque sequence. If the cover or another oil circuit is the source, select that separate repair instead.</x:v>
       </x:c>
       <x:c r="F200" s="9" t="n">
         <x:v>1</x:v>
@@ -10723,113 +12055,113 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="858" hidden="0" customHeight="1">
+    <x:row r="201" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A201" s="40" t="n">
         <x:v>200</x:v>
       </x:c>
       <x:c r="B201" s="9" t="str">
-        <x:v>bmw-x3-vanos-solenoid-2007</x:v>
+        <x:v>bmw-x5-transfer-case-actuator-2000</x:v>
       </x:c>
       <x:c r="C201" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | M40i, M50, xDrive35i | N52, N55</x:v>
+        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive48i, X5 M | N52, N62, M57, S63</x:v>
       </x:c>
       <x:c r="D201" s="9" t="str">
-        <x:v>VANOS Solenoid Failure (N52, N55 Engines)</x:v>
+        <x:v>E70 ATC700 Transfer-Case Positioning Motor (Diagnosis Required)</x:v>
       </x:c>
       <x:c r="E201" s="9" t="str">
-        <x:v>Replace VANOS solenoids and seals ($250-400 European shops, $729-882 US average). Use high-quality oil (5W-30 or 0W-40 BMW LL-01 spec) and change every 5,000-7,000 miles to prevent future failures - cheap oil or extended intervals kill VANOS solenoids. Some cases may require complete VANOS unit rebuild ($1,500-2,500). PREVENTIVE: Replace VANOS solenoids and seals every 50k miles as maintenance - much cheaper than waiting for failure. On F25 X3 with N52/N55, check TSB SI B12 14 10 for VANOS gear assembly bolt issue.</x:v>
+        <x:v>Read BMW VTG/DSC faults and run the applicable ISTA transfer-case test plan before buying a motor. Confirm tire sizes and wear, battery voltage, wiring, transfer-case type, fluid condition, calibration, and—especially after differential or transfer-case replacement—the VIN-correct front and rear gear ratios. If testing confirms the ATC700 positioning motor and BMW ETK/AIR selects this application for the VIN, current BMW exchange servomotor 27-10-2-449-709 supersedes 27-10-7-568-267. Install the correct classification resistor/hardware supplied or specified for the VIN and perform the required VTG initialization/calibration. A generic gear-only kit is not a universal BMW repair and should not be ordered without opening and confirming the exact motor failure.</x:v>
       </x:c>
       <x:c r="F201" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G201" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="1016.4000244140625" hidden="0" customHeight="1">
+    <x:row r="202" ht="1042.800048828125" hidden="0" customHeight="1">
       <x:c r="A202" s="40" t="n">
         <x:v>201</x:v>
       </x:c>
       <x:c r="B202" s="9" t="str">
-        <x:v>bmw-x3-wastegate-rattle-2011</x:v>
+        <x:v>bmw-x5-transfer-case-actuator-2007</x:v>
       </x:c>
       <x:c r="C202" s="9" t="str">
-        <x:v>2011-2023 | BMW | X3 | M40i, M50, sDrive30i, xDrive28i, xDrive30i, xDrive35i</x:v>
+        <x:v>2019-2026 | BMW | X5</x:v>
       </x:c>
       <x:c r="D202" s="9" t="str">
-        <x:v>Turbocharger Wastegate Rattle (N55, N20, B58 Engines)</x:v>
+        <x:v>G05/F95 Transfer-Case Shudder: Tires and Fluid Diagnosis First</x:v>
       </x:c>
       <x:c r="E202" s="9" t="str">
-        <x:v>Replace wastegate actuator ($400-800) or use aftermarket wastegate repair kit with upgraded stainless steel bushings ($150-300). Some cases require complete turbocharger replacement ($2,000-$4,000). VTT (Vargas Turbo Technologies) repair kits popular on forums - upgraded materials prevent future rattle. MONITORING: Early wastegate rattle may be harmless (annoying but no performance loss). If car boosts normally and no underboost codes, can monitor rattle without urgent repair. However, if check engine light appears with code 30FF or boost pressure drops, repair immediately to prevent turbo damage.</x:v>
+        <x:v>Follow BMW SIB 27 02 20 in order: verify all four tires for VIN-correct size, brand/application, axle placement, and wear; diagnose any powertrain faults; then use ISTA to temporarily deactivate the transfer-case clutch and road-test the complaint. Only if the shudder disappears with the VTG deactivated does BMW direct an ATX13-X oil change with DTF-1, followed by VTG calibration. The clutch plates can require up to 125 miles after the service to become fully saturated and smooth out. If the symptom remains, continue diagnosis rather than buying an actuator or transfer case. Part numbers for any further repair must be selected by VIN in ETK/AIR.</x:v>
       </x:c>
       <x:c r="F202" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G202" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="203" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A203" s="40" t="n">
         <x:v>202</x:v>
       </x:c>
       <x:c r="B203" s="9" t="str">
-        <x:v>bmw-x3-water-pump-2007</x:v>
+        <x:v>bmw-x5-vanos-solenoid-2000</x:v>
       </x:c>
       <x:c r="C203" s="9" t="str">
-        <x:v>2007-2017 | BMW | X3 | sDrive30i, xDrive28i, xDrive30i | N52, N20</x:v>
+        <x:v>2010-2013 | BMW | X5 | xDrive30i, xDrive35i | N51, N52K, N52T, N55</x:v>
       </x:c>
       <x:c r="D203" s="9" t="str">
-        <x:v>Electric Water Pump Failure (N52, N20 Engines)</x:v>
+        <x:v>VANOS Adjustment-Unit Bolt Recall 23V-707 (E70 Inline-Six)</x:v>
       </x:c>
       <x:c r="E203" s="9" t="str">
-        <x:v>Replace electric water pump at first sign of failure ($800 parts + labor). Consider preventative replacement at 70-80k miles to avoid being stranded ($400 parts, DIY-able). CRITICAL: If you own 2013-2017 X3 28i, verify recall repair (protective shield installation) has been completed to prevent fire risk - check with BMW dealer using VIN. If engine overheats, PULL OVER IMMEDIATELY and shut off - driving with overheating warps cylinder heads ($4,000+ repair). Call tow truck.</x:v>
+        <x:v>Enter the VIN in BMW's official recall lookup and have an authorized BMW center complete recall 23V-707 if it is open. BMW's procedure is inspection-dependent: intact affected bolts are replaced; if bolts are loose or broken, the affected VANOS adjustment unit is replaced, and missing fragments must be recovered. The recall repair is free, so do not buy a solenoid or VANOS part first. If the VIN is outside the recall or a fault remains after the remedy, use BMW-capable diagnostics to test oil supply and pressure, wiring, sensors, control solenoids, adjustment units, and mechanical timing before selecting a part. If the engine runs roughly, makes unusual mechanical noise, loses power, or stalls, move out of traffic safely, stop driving, and contact BMW for transport guidance.</x:v>
       </x:c>
       <x:c r="F203" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G203" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="1240.800048828125" hidden="0" customHeight="1">
+    <x:row r="204" ht="1148.4000244140625" hidden="0" customHeight="1">
       <x:c r="A204" s="40" t="n">
         <x:v>203</x:v>
       </x:c>
       <x:c r="B204" s="9" t="str">
-        <x:v>bmw-x3m-brake-wear-2020</x:v>
+        <x:v>bmw-x5-water-pump-2007</x:v>
       </x:c>
       <x:c r="C204" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2011-2013 | BMW | X5 | xDrive35i | N55</x:v>
       </x:c>
       <x:c r="D204" s="9" t="str">
-        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F97 X3 M / F98 X4 M</x:v>
+        <x:v>E70 xDrive35i N55 Electric Coolant Pump (Fault-Confirmed)</x:v>
       </x:c>
       <x:c r="E204" s="9" t="str">
-        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
+        <x:v>If the engine-temperature warning appears, stop safely, shut the engine off, and tow the vehicle if normal temperature cannot be confirmed. When cool, check coolant level and leaks, read BMW-specific faults, verify pump power/ground and communication, and run the ISTA coolant-pump activation/test plan. If those tests confirm the pump and BMW ETK/AIR selects 11-51-5-A05-704 for the VIN, replace it using the BMW procedure, select the thermostat separately only if testing or preventive planning justifies it, vacuum-fill or bleed the system as specified, and verify commanded pump operation and stable temperature. Do not use a fixed-mileage rule or this part number for an N52, N63, or F15 without VIN confirmation.</x:v>
       </x:c>
       <x:c r="F204" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G204" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="1188" hidden="0" customHeight="1">
+    <x:row r="205" ht="1056" hidden="0" customHeight="1">
       <x:c r="A205" s="40" t="n">
         <x:v>204</x:v>
       </x:c>
       <x:c r="B205" s="9" t="str">
-        <x:v>bmw-x3m-cooling-track-use-2020</x:v>
+        <x:v>bmw-x5m-brake-system-2010</x:v>
       </x:c>
       <x:c r="C205" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D205" s="9" t="str">
-        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F97 X3 M / F98 X4 M</x:v>
+        <x:v>Heavy-Duty Brake System Accelerated Wear - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E205" s="9" t="str">
-        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
+        <x:v>E70 X5 M brakes: OEM front pads 34116799964 ($150-$250), rear pads 34216794879 ($120-$200). F85 X5 M front brake rotors: 34112284101/34112284102 with 6-pot caliper 34117845747/34117845748 and pads 34112284869. F85 rear: 385mm x 24mm perforated rotors 34212284903/34212284904 with 4-pot Brembo caliper and Textar pads. Budget $1,500-$2,500 per axle for complete brake service. For track use: EBC Yellowstuff or Hawk HPS 5.0 pads ($200-$350 per axle) with StopTech slotted rotors for improved heat management. Use Motul RBF 660 or ATE Typ 200 brake fluid - flush every 12 months. Budget $3,000-$5,000 per year for brake maintenance if driving spiritedly.</x:v>
       </x:c>
       <x:c r="F205" s="9" t="n">
         <x:v>0</x:v>
@@ -10838,21 +12170,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="206" ht="1122" hidden="0" customHeight="1">
       <x:c r="A206" s="40" t="n">
         <x:v>205</x:v>
       </x:c>
       <x:c r="B206" s="9" t="str">
-        <x:v>bmw-x3m-differential-bolt-2020</x:v>
+        <x:v>bmw-x5m-rear-differential-2010</x:v>
       </x:c>
       <x:c r="C206" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M | S63</x:v>
       </x:c>
       <x:c r="D206" s="9" t="str">
-        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F97 X3 M / F98 X4 M</x:v>
+        <x:v>Rear Differential Wear &amp; Fluid Degradation - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E206" s="9" t="str">
-        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
+        <x:v>Change rear differential fluid every 30,000 miles (ignore BMW "lifetime fill" claim). E70 X5 M: No drain plug - fluid must be extracted through fill port with hand pump or suction device. Recommended fluid: Royal Purple 75W-140 GL5 synthetic or Red Line 75W-140 GL5 ($40-$60 per fill). Capacity approximately 1.2 liters. For limited-slip diff, ensure fluid is GL5 rated with limited-slip additive. If differential is making whining/howling noise: have a limited-slip differential specialist inspect internals (not generic BMW shop). Diff rebuild: $1,500-$3,000 at specialist. Complete differential replacement: $3,000-$5,500 + labor. Labor for fluid change: $150-$300 at independent shop.</x:v>
       </x:c>
       <x:c r="F206" s="9" t="n">
         <x:v>0</x:v>
@@ -10861,21 +12193,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="207" ht="1386" hidden="0" customHeight="1">
       <x:c r="A207" s="40" t="n">
         <x:v>206</x:v>
       </x:c>
       <x:c r="B207" s="9" t="str">
-        <x:v>bmw-x3m-s58-bearing-recall-2020</x:v>
+        <x:v>bmw-x5m-s63-cooling-system-2010</x:v>
       </x:c>
       <x:c r="C207" s="9" t="str">
-        <x:v>2020-2021 | BMW | X3 M</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D207" s="9" t="str">
-        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F97 X3 M / F98 X4 M</x:v>
+        <x:v>S63 Cooling System Component Failures - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E207" s="9" t="str">
-        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
+        <x:v>PROACTIVE MAINTENANCE SCHEDULE: Replace electric water pump at 60,000 miles ($400-$700 + labor). Replace thermostat at same time ($150-$250). Replace expansion tank at 60,000-80,000 miles ($100-$200). Inspect all coolant hoses at every oil change - replace any that are soft, bulging, or showing surface cracks. E70 X5 M expansion tank vent hose: 17128627119 ($30-$50). Flush coolant system every 2 years or 30,000 miles (more frequent than BMW's 4-year recommendation). Use ONLY BMW coolant mixed 50/50 with distilled water. For E70 hot-V turbo coolant lines: GRYPHONTEK repair kit eliminates plastic T-fitting failure (see separate issue entry). Budget $1,500-$2,500 for complete cooling system refresh at 60,000 miles. This prevents catastrophic overheating that can destroy the S63 engine ($15,000-$34,000 engine replacement).</x:v>
       </x:c>
       <x:c r="F207" s="9" t="n">
         <x:v>0</x:v>
@@ -10884,21 +12216,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="208" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="208" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A208" s="40" t="n">
         <x:v>207</x:v>
       </x:c>
       <x:c r="B208" s="9" t="str">
-        <x:v>bmw-x3m-transfer-case-2020</x:v>
+        <x:v>bmw-x5m-s63-oil-leaks-2010</x:v>
       </x:c>
       <x:c r="C208" s="9" t="str">
-        <x:v>2020-2023 | BMW | X3 M | S58</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D208" s="9" t="str">
-        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F97 X3 M / F98 X4 M</x:v>
+        <x:v>S63 V8 Chronic Oil Leaks (Valve Cover, Oil Pan, Turbo Lines) - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E208" s="9" t="str">
-        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
+        <x:v>Valve cover gasket replacement (both sides): $1,200-$2,500 with labor. BMW plastic valve covers can crack and must be replaced entirely (not just gasket) - inspect during service. Oil filter housing gasket: $400-$800 with labor. Oil pan gasket: $2,000-$3,500 (requires engine/subframe drop). Turbo oil feed/return lines: replace with GRYPHONTEK or MAMBA upgraded silicone/braided lines during any turbo service ($200-$400). VANOS solenoid seals: $100-$200 (DIY-friendly). For comprehensive oil leak repair at 80,000+ miles: budget $3,000-$5,000 to address all common leak points simultaneously. Valve cover bolt torque is CRITICAL - too tight cracks the cover ($800-$1,200 per cover), too loose and it leaks.</x:v>
       </x:c>
       <x:c r="F208" s="9" t="n">
         <x:v>0</x:v>
@@ -10907,21 +12239,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="209" ht="1412.4000244140625" hidden="0" customHeight="1">
       <x:c r="A209" s="40" t="n">
         <x:v>208</x:v>
       </x:c>
       <x:c r="B209" s="9" t="str">
-        <x:v>bmw-x4-n20-timing-chain-2015</x:v>
+        <x:v>bmw-x5m-s63-rod-bearing-2010</x:v>
       </x:c>
       <x:c r="C209" s="9" t="str">
-        <x:v>2015-2016 | BMW | X4 | xDrive28i, xDrive30i</x:v>
+        <x:v>2010-2018 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i</x:v>
       </x:c>
       <x:c r="D209" s="9" t="str">
-        <x:v>N20 Timing Chain Premature Failure - F26 X4 xDrive28i</x:v>
+        <x:v>S63 V8 Rod Bearing Premature Wear &amp; Failure - E70/F85 X5 M</x:v>
       </x:c>
       <x:c r="E209" s="9" t="str">
-        <x:v>Complete timing chain kit replacement including chain, guides, tensioner, and sprockets. Must be performed by experienced BMW technician. Preventive replacement recommended at 60,000-80,000 miles. BMW extended warranty to 8 years/100,000 miles under class action settlement. Upgraded reinforced chain kit available from aftermarket. Labor is 10-14 hours for X4 due to AWD and tight engine bay.</x:v>
+        <x:v>PREVENTIVE: For track-driven X5 M, replace rod bearings proactively at 60,000-80,000 miles. ACL Race Series rod bearings (8B1578HX-STD for S63B44, +0.001" extra oil clearance) are the community gold standard ($200-$350 for bearing set). WPC surface-treated bearings from Lang Racing are the premium choice ($400-$600 set). Total cost for preventive rod bearing service: $4,500-$8,500 depending on shop. Oil analysis every 5,000 miles through Blackstone Labs ($30/test) to monitor bearing wear metals (lead and copper). Use only BMW 10W-60 synthetic oil with 5,000-7,500 mile oil change intervals. Never track the car on cold oil. Mporium BMW offers specialized S63 rod bearing service starting at $4,499. If catastrophic failure: rebuilt S63 engine from RK Autowerks (~$8,500 + installation), new BMW engine (~$34,000), or complete engine rebuild ($12,000-$18,000).</x:v>
       </x:c>
       <x:c r="F209" s="9" t="n">
         <x:v>0</x:v>
@@ -10930,21 +12262,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="210" ht="1214.4000244140625" hidden="0" customHeight="1">
       <x:c r="A210" s="40" t="n">
         <x:v>209</x:v>
       </x:c>
       <x:c r="B210" s="9" t="str">
-        <x:v>bmw-x4-n20-timing-chain-guide-2015</x:v>
+        <x:v>bmw-x5m-s63-turbo-coolant-line-2010</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
-        <x:v>2015-2015 | BMW | X4 | N20</x:v>
+        <x:v>2010-2013 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D210" s="9" t="str">
-        <x:v>2015 X4 N20 Lower-Engine Whine Requires Timing-Chain Diagnosis</x:v>
+        <x:v>S63 Turbo Coolant Line Plastic T-Fitting Failure (Hot-V Design) - E70 X5 M</x:v>
       </x:c>
       <x:c r="E210" s="9" t="str">
-        <x:v>Confirm the exact xDrive28i variant, N20 engine, production date and VIN eligibility, then have a BMW-qualified technician reproduce the noise and follow current BMW diagnosis before replacing anything. The historical seven-year/70,000-mile coverage was a limited warranty extension, not a recall, and is not a current coverage promise. ShowMeTheParts established category-level fitment only, so no commerce link is approved.</x:v>
+        <x:v>Replace ALL factory plastic turbo coolant T-fittings and hoses with GRYPHONTEK S63 Turbo Coolant Line Repair Kit ($200-$400). Kit includes pre-shaped multi-layer reinforced silicone hoses, brass T-fittings (replacing factory plastic), and all necessary hose clamps. Direct bolt-on installation designed for the E70/E71 S63 engine bay. MAMBA Turbo also offers a reinforced turbo coolant line kit with brass and silicone components ($150-$350). This is a PROACTIVE replacement - do not wait for failure. Replace at first sign of coolant weeping or during any turbo service. Labor: $800-$1,500 due to tight access in hot-V engine valley. If turbo bearings are damaged from overheating: turbo replacement $3,000-$5,000 per unit.</x:v>
       </x:c>
       <x:c r="F210" s="9" t="n">
         <x:v>0</x:v>
@@ -10953,21 +12285,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="211" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="211" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A211" s="40" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="B211" s="9" t="str">
-        <x:v>bmw-x4-oil-leak-2015</x:v>
+        <x:v>bmw-x5m-s63-vanos-solenoid-2010</x:v>
       </x:c>
       <x:c r="C211" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D211" s="9" t="str">
-        <x:v>Oil Leaks - Valve Cover &amp; Oil Filter Housing - All Models</x:v>
+        <x:v>S63 VANOS Solenoid Failure - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E211" s="9" t="str">
-        <x:v>Replace valve cover gasket and/or oil filter housing gasket. Valve cover replacement is 3-4 hours labor on X4. Oil filter housing gasket is 1-2 hours. Both are routine maintenance items on BMW turbo engines. Use OEM gaskets for best longevity. Clean oil residue from engine bay after repair. Monitor oil level regularly to catch leaks early.</x:v>
+        <x:v>Replace all 4 VANOS solenoids simultaneously - they are same age and if one has failed, others are close behind. Pierburg 11368605123 (OEM supplier) at $30-$50 each from Turner Motorsport or BimmerWorld. Genuine BMW 11368482268 for S63TU applications at $50-$70 each. Total parts cost: $120-$280 for all 4 solenoids. Also replace VANOS solenoid O-rings and filter screens during service. Labor: 1-2 hours professional ($150-$400 labor). This is one of the easier S63 repairs - accessible from top of engine without removing intake manifold. Natafox and Febi also offer quality aftermarket VANOS solenoids at lower cost ($20-$35 each). Clean VANOS system with fresh oil change immediately after solenoid replacement.</x:v>
       </x:c>
       <x:c r="F211" s="9" t="n">
         <x:v>0</x:v>
@@ -10976,21 +12308,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="212" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="212" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A212" s="40" t="n">
         <x:v>211</x:v>
       </x:c>
       <x:c r="B212" s="9" t="str">
-        <x:v>bmw-x4-rear-differential-mount-2015</x:v>
+        <x:v>bmw-x5m-s63-wastegate-rattle-2010</x:v>
       </x:c>
       <x:c r="C212" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2010-2018 | BMW | X5 M | S63</x:v>
       </x:c>
       <x:c r="D212" s="9" t="str">
-        <x:v>Rear Differential Mount Bushing Failure</x:v>
+        <x:v>S63 Twin Turbo Wastegate Rattle - E70/F85 X5 M</x:v>
       </x:c>
       <x:c r="E212" s="9" t="str">
-        <x:v>Replace rear differential mount bushings. Both front and rear differential bushings should be inspected and replaced as a set. Upgraded aftermarket bushings with stiffer rubber or polyurethane are available for longer service life.</x:v>
+        <x:v>Option 1 (Most cost-effective): MAMBA SUS316 stainless steel wastegate rattle flapper repair kit for S63 MGT2260 (part 077-0024, replaces 790463-2 / 790484-3), approximately $150-$300 per turbo. Requires turbo removal for installation. Option 2: Lskioer turbo wastegate rattle flapper repair kit for S63/S63TU MGT2260DSL ($80-$150 per kit on Amazon). Option 3: Replace turbo wastegate actuators with new OEM units ($300-$500 each). Option 4: Full turbocharger replacement with new or remanufactured units ($3,000-$5,000 per turbo + labor). Labor for turbo removal and reinstallation: $2,000-$3,500 for both turbos. While turbos are out: replace turbo oil feed/return lines, coolant lines, and all gaskets (GRYPHONTEK turbo coolant line repair kit for E70 X5M, ~$200-$400).</x:v>
       </x:c>
       <x:c r="F212" s="9" t="n">
         <x:v>0</x:v>
@@ -10999,21 +12331,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="213" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="213" ht="1069.199951171875" hidden="0" customHeight="1">
       <x:c r="A213" s="40" t="n">
         <x:v>212</x:v>
       </x:c>
       <x:c r="B213" s="9" t="str">
-        <x:v>bmw-x4-transfer-case-2015</x:v>
+        <x:v>bmw-x5m-transfer-case-actuator-2010</x:v>
       </x:c>
       <x:c r="C213" s="9" t="str">
-        <x:v>2015-2023 | BMW | X4</x:v>
+        <x:v>2010-2023 | BMW | X5 M</x:v>
       </x:c>
       <x:c r="D213" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure - All xDrive X4</x:v>
+        <x:v>xDrive Transfer Case Actuator Motor Failure - E70/F85/F95 X5 M</x:v>
       </x:c>
       <x:c r="E213" s="9" t="str">
-        <x:v>Diagnose specific failure. Transfer case actuator motor replacement ($800-1,200) is most common. Complete transfer case replacement required for internal failures ($2,500-4,000). Regular transfer case fluid changes every 50,000 miles may extend life. Some owners install aftermarket upgraded actuator motors. Common wear item on high-mileage xDrive BMW models.</x:v>
+        <x:v>Replace transfer case actuator motor. E70 X5 M: BMW 27107566296 or equivalent ($250-$450 for actuator motor). F85 X5 M: BMW 27608643153 or equivalent ($300-$500). F95 X5 M: check VIN-specific part number with dealer. FCP Euro has an excellent DIY guide for BMW transfer case actuator repair - the actuator can be replaced without removing the entire transfer case. Labor: 2-3 hours at specialist shop ($300-$600 labor). Change transfer case fluid at same time with BMW DTF-1 specification fluid. XeMODeX offers remanufactured transfer case actuator motors at reduced cost ($200-$350). For complete transfer case failure: $3,500-$6,000 for replacement unit + labor.</x:v>
       </x:c>
       <x:c r="F213" s="9" t="n">
         <x:v>0</x:v>
@@ -11022,21 +12354,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="214" ht="1240.800048828125" hidden="0" customHeight="1">
+    <x:row r="214" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A214" s="40" t="n">
         <x:v>213</x:v>
       </x:c>
       <x:c r="B214" s="9" t="str">
-        <x:v>bmw-x4m-brake-wear-2020</x:v>
+        <x:v>bmw-x6-adaptive-drive-malfunction-2008</x:v>
       </x:c>
       <x:c r="C214" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
+        <x:v>2008-2019 | BMW | X6</x:v>
       </x:c>
       <x:c r="D214" s="9" t="str">
-        <x:v>Accelerated Brake Pad &amp; Rotor Wear from Vehicle Weight - F98 X4 M / F98 X4 M</x:v>
+        <x:v>Adaptive Drive System Malfunction</x:v>
       </x:c>
       <x:c r="E214" s="9" t="str">
-        <x:v>Front brake replacement: OEM front rotor (34118054825 left, matching right) with OEM M compound pads. Complete OEM front brake kit available from BimmerWorld (34108064561K1, ~$800-$1,000). Rear brake kit similarly priced. For track use: Upgrade to Brembo GT brake pad set (BM8 compound) for improved heat resistance and longer pad life. EBC Yellowstuff or Hawk HPS 5.0 pads are popular street/track compromise choices ($150-$250 per axle). StopTech slotted rotors offer improved heat dissipation. For dedicated track cars: Brembo GT big brake kit with 412x38mm discs available ($4,000-$6,000 installed). Budget $2,000-$3,000 per year for brake maintenance if driving spiritedly. Use high-temperature brake fluid (Motul RBF 660 or ATE Typ 200) and flush every 12 months.</x:v>
+        <x:v>Diagnose specific Adaptive Drive component failure using BMW ISTA diagnostics. Replace the failed component — most commonly the hydraulic pump or valve block. If repair cost is prohibitive, some owners convert to conventional anti-roll bars as a permanent fix at lower cost.</x:v>
       </x:c>
       <x:c r="F214" s="9" t="n">
         <x:v>0</x:v>
@@ -11045,21 +12377,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="215" ht="1188" hidden="0" customHeight="1">
+    <x:row r="215" ht="858" hidden="0" customHeight="1">
       <x:c r="A215" s="40" t="n">
         <x:v>214</x:v>
       </x:c>
       <x:c r="B215" s="9" t="str">
-        <x:v>bmw-x4m-cooling-track-use-2020</x:v>
+        <x:v>bmw-x6-air-suspension-2008</x:v>
       </x:c>
       <x:c r="C215" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M</x:v>
+        <x:v>2008-2023 | BMW | X6</x:v>
       </x:c>
       <x:c r="D215" s="9" t="str">
-        <x:v>Cooling System Heat Soak During Track/Spirited Driving - F98 X4 M / F98 X4 M</x:v>
+        <x:v>Air Suspension Compressor &amp; Strut Failure</x:v>
       </x:c>
       <x:c r="E215" s="9" t="str">
-        <x:v>For track use: Upgrade intercooler to do88 front-mount intercooler ($1,200-$1,800) - the community standard for S58 heat management. Add CSF high-performance radiator ($600-$900) for sustained track work. Dinan or VRSF also offer intercooler upgrades in the $1,000-$1,500 range. For street/canyon driving: Stock cooling is adequate but ensure coolant flush every 2 years/30,000 miles and inspect expansion tank for cracks. Replace coolant expansion tank preemptively at 60,000 miles if car is driven hard. For all X3 M/X4 M: Use BMW coolant only (mixed 50/50 with distilled water), replace thermostat at 80,000 miles preventatively, inspect all coolant hoses for bulging or softening at every oil change.</x:v>
+        <x:v>Replace failed air springs or compressor. Arnott rear air spring A-2642 ($200-300 each). OEM F16 spring 37126795013 ($200). Arnott compressor P-2655 ($599). Or convert to coil springs: Strutmasters BB2RBM conversion kit ($1,200-1,800) permanently eliminates air suspension issues. Conversion is cheaper long-term than continued air suspension repairs. If keeping air suspension: inspect air springs at 60,000-80,000 miles for cracks/leaks before compressor damage occurs. Replace both air springs on same axle simultaneously.</x:v>
       </x:c>
       <x:c r="F215" s="9" t="n">
         <x:v>0</x:v>
@@ -11068,21 +12400,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="216" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="216" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A216" s="40" t="n">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B216" s="9" t="str">
-        <x:v>bmw-x4m-differential-bolt-2020</x:v>
+        <x:v>bmw-x6-ibs-brake-recall-2023</x:v>
       </x:c>
       <x:c r="C216" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M</x:v>
+        <x:v>2024-2024 | BMW | X6</x:v>
       </x:c>
       <x:c r="D216" s="9" t="str">
-        <x:v>Rear Differential Mounting Bolt &amp; Bush Failure - F98 X4 M / F98 X4 M</x:v>
+        <x:v>2024 X6 Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E216" s="9" t="str">
-        <x:v>Replace factory differential bolt, bush, and collar with FJ Motorwerkes uprated diff bolt and collar upgrade kit. The FJ kit uses premium CNC-machined stainless steel components that can handle 170,000 PSI (39% stronger than BMW's revised bolt). Kit price approximately $255 (GBP). Available from FJ Motorwerkes directly, BMG Performance, AM Tuning, and H4ck Performance. Installation is straightforward - rear differential does not need to be fully removed. Budget $400-$600 total including labor. This upgrade is considered MANDATORY by the X3 M/X4 M community for any car making stock or above power. JXB Performance also offers a driveshaft carrier bearing upgrade for cars experiencing propshaft vibration as a companion fix.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
       </x:c>
       <x:c r="F216" s="9" t="n">
         <x:v>0</x:v>
@@ -11091,21 +12423,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="217" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="217" ht="924" hidden="0" customHeight="1">
       <x:c r="A217" s="40" t="n">
         <x:v>216</x:v>
       </x:c>
       <x:c r="B217" s="9" t="str">
-        <x:v>bmw-x4m-s58-bearing-recall-2020</x:v>
+        <x:v>bmw-x6-n63-timing-chain-2008</x:v>
       </x:c>
       <x:c r="C217" s="9" t="str">
-        <x:v>2020-2021 | BMW | X4 M | M40i, xDrive35i | S58</x:v>
+        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
       </x:c>
       <x:c r="D217" s="9" t="str">
-        <x:v>S58 Engine Main Bearing Shell Recall / Stop Sale - F98 X4 M / F98 X4 M</x:v>
+        <x:v>N63 Timing Chain Stretch &amp; Guide Failure (E71/F16 xDrive50i)</x:v>
       </x:c>
       <x:c r="E217" s="9" t="str">
-        <x:v>Check VIN immediately against BMW recall database at bmwusa.com or contact your BMW dealer. If your vehicle is within the affected production date range, BMW will inspect and replace main bearing shells at no cost under the Tech Campaign. The repair requires removing the cylinder head and oil pan to access and replace all main bearing shells - this is a major repair (8-12 hours labor) but fully covered by BMW. Do NOT drive the vehicle if knocking is present. For S58 vehicles outside the recall range: Proactive rod bearing inspection is recommended at 60,000 miles for track-driven vehicles. ACL Race Series rod bearings 6B1510H-STD are the aftermarket upgrade choice on Bimmerpost for preventive replacement ($150-$250 for bearing set, $3,000-$5,000 total with labor).</x:v>
+        <x:v>PREVENTIVE REPLACEMENT: If you own 2008-2014 E71 xDrive50i with N63, replace timing chain guides and tensioners IMMEDIATELY at 60,000-80,000 miles ($4,000-6,000) BEFORE failure. IWIS timing chain kit 90001521 ($800-1,200) or Turner kit 11317594899KT recommended. Replace lower chain guide 11147574373 at same time. If chain has already failed: complete engine replacement required ($15,000-25,000). Check VIN with BMW dealer for extended warranty eligibility. 2015+ N63TU engines have improved timing components but still require monitoring.</x:v>
       </x:c>
       <x:c r="F217" s="9" t="n">
         <x:v>0</x:v>
@@ -11114,21 +12446,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="218" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="218" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A218" s="40" t="n">
         <x:v>217</x:v>
       </x:c>
       <x:c r="B218" s="9" t="str">
-        <x:v>bmw-x4m-transfer-case-2020</x:v>
+        <x:v>bmw-x6-n63-valve-stem-seal-wear-2008</x:v>
       </x:c>
       <x:c r="C218" s="9" t="str">
-        <x:v>2020-2023 | BMW | X4 M | S58</x:v>
+        <x:v>2008-2019 | BMW | X6 | N63</x:v>
       </x:c>
       <x:c r="D218" s="9" t="str">
-        <x:v>xDrive Transfer Case Stress &amp; Fluid Degradation - F98 X4 M / F98 X4 M</x:v>
+        <x:v>N63 Valve Stem Seal Degradation and Oil Burning</x:v>
       </x:c>
       <x:c r="E218" s="9" t="str">
-        <x:v>Change transfer case fluid every 30,000 miles (BMW says "lifetime fill" - this is NOT correct for M vehicles driven hard). Use BMW DTF-1 transfer case fluid or equivalent high-quality synthetic. Check tire tread depth at every service - all 4 tires must be within 2/32" of each other to prevent transfer case stress. Rotate tires every 5,000-7,000 miles. If transfer case actuator motor fails: FCP Euro guide for BMW transfer case actuator repair (part number varies by production date, ~$300-$600). For tuned cars: Consider transfer case brace/reinforcement and shortened fluid change intervals (every 15,000 miles). Complete transfer case replacement if internals are damaged: $3,000-$5,500 at independent specialist, $5,000-$8,000+ at dealer.</x:v>
+        <x:v>Replace all intake and exhaust valve stem seals. This is a major job requiring head work. Also replace turbo oil return lines and update engine software per BMW N63 Customer Care Package specifications. Ensure proper oil grade (BMW LL-01) is used.</x:v>
       </x:c>
       <x:c r="F218" s="9" t="n">
         <x:v>0</x:v>
@@ -11137,21 +12469,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="219" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="219" ht="858" hidden="0" customHeight="1">
       <x:c r="A219" s="40" t="n">
         <x:v>218</x:v>
       </x:c>
       <x:c r="B219" s="9" t="str">
-        <x:v>bmw-x5-air-suspension-2007</x:v>
+        <x:v>bmw-x6-n63-valve-stem-seals-2008</x:v>
       </x:c>
       <x:c r="C219" s="9" t="str">
-        <x:v>2019-2026 | BMW | X5</x:v>
+        <x:v>2008-2023 | BMW | X6 | M50i, xDrive50i | N63</x:v>
       </x:c>
       <x:c r="D219" s="9" t="str">
-        <x:v>G05 Suspension Warning: Check Faults and Campaigns Before Parts</x:v>
+        <x:v>N63 Valve Stem Seal / Oil Consumption (xDrive50i)</x:v>
       </x:c>
       <x:c r="E219" s="9" t="str">
-        <x:v>Start with the VIN build/options, open-campaign status, exact warning, complete fault memory, and BMW ISTA test plan. If the VIN and production date match a BMW action, follow that bulletin: inspect the specified sensor-link holders, apply the specified software correction, or inspect the affected air line as directed. For other vehicles, test the particular system shown by the VIN and fault path before selecting any component. Do not buy a compressor, strut, spring, or conversion kit until the failed part and its VIN-specific number are established. This article intentionally has no retail link because no single part repairs all of these conditions.</x:v>
+        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 ($80-120/set of 16, need 2 sets for V8). 5150 AutoSport Viton upgraded seals ($150-200) are recommended for better heat resistance in hot-vee configuration. AGA Tools kit AGA-N63-VSK-K ($500-800) includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Some owners monitor oil levels and add as needed rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil.</x:v>
       </x:c>
       <x:c r="F219" s="9" t="n">
         <x:v>0</x:v>
@@ -11160,44 +12492,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="220" ht="1148.4000244140625" hidden="0" customHeight="1">
+    <x:row r="220" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A220" s="40" t="n">
         <x:v>219</x:v>
       </x:c>
       <x:c r="B220" s="9" t="str">
-        <x:v>bmw-x5-air-suspension-compressor-2007</x:v>
+        <x:v>bmw-x6-n63-wastegate-2008</x:v>
       </x:c>
       <x:c r="C220" s="9" t="str">
-        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive35i, xDrive48i, xDrive50i, X5 M | N52, N62, M57, N55, N63, S63</x:v>
+        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
       </x:c>
       <x:c r="D220" s="9" t="str">
-        <x:v>E70 Rear Air-Supply Unit: Diagnose the Self-Leveling System First</x:v>
+        <x:v>N63 Turbo Wastegate Rattle (xDrive50i)</x:v>
       </x:c>
       <x:c r="E220" s="9" t="str">
-        <x:v>Read the EHC fault memory and run the applicable BMW ISTA test plan before ordering a compressor. Confirm the vehicle is equipped with rear self-leveling suspension, compare left/right ride height, check system power and wiring, inspect the height-sensor links, and leak-test the air springs, lines, and valve system. Test the air supply only after those checks isolate it. If BMW ETK/AIR selects the E70 air-supply system for the VIN and diagnosis confirms that assembly, replace it with current part 37-20-6-859-714, follow the BMW repair procedure, clear faults, and perform the required ride-height calibration. Do not install a generic compressor or a coil-conversion kit from symptoms alone.</x:v>
+        <x:v>Repair options range from flapper repair kits ($50-100/turbo) to complete turbocharger replacement ($4,000-8,000 for both). Garrett MGT2256S flapper repair kit ($50-100 per turbo) is cheapest fix. MAMBA adjustable actuator kit ($150-300) provides more durable solution. OEM actuators 11657646093 available from BMW. Complete turbo replacement $2,000-4,000 per turbo. MONITORING: Wastegate rattle is early warning - address before complete turbo failure to avoid $8,000+ repair.</x:v>
       </x:c>
       <x:c r="F220" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G220" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="221" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="221" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A221" s="40" t="n">
         <x:v>220</x:v>
       </x:c>
       <x:c r="B221" s="9" t="str">
-        <x:v>bmw-x5-carbon-buildup-2007</x:v>
+        <x:v>bmw-x6-rear-differential-bushing-2008</x:v>
       </x:c>
       <x:c r="C221" s="9" t="str">
-        <x:v>2011-2018 | BMW | X5 | xDrive35i, xDrive50i | N55, N63, N63TU1</x:v>
+        <x:v>2008-2026 | BMW | X6</x:v>
       </x:c>
       <x:c r="D221" s="9" t="str">
-        <x:v>Possible Intake-Valve Deposits on Direct-Injected Gasoline Engines</x:v>
+        <x:v>Rear Differential Bushing Deterioration</x:v>
       </x:c>
       <x:c r="E221" s="9" t="str">
-        <x:v>Diagnose the actual symptom before authorizing cleaning: read BMW-specific faults and misfire counters, check ignition and fueling, smoke-test the intake where indicated, verify crankcase ventilation operation, and inspect the intake valves with a borescope or by removing the intake manifold when the test plan supports it. If substantial deposits are confirmed and match the complaint, use an engine-specific professional mechanical-cleaning procedure that protects closed valves and removes all blasting media before reassembly. Do not present a universal catch can, chemical spray, fuel brand, short oil interval, or high-RPM driving as a proven repair. Any crankcase-ventilation modification also requires engine-specific fitment and emissions-law review.</x:v>
+        <x:v>Replace all rear differential mount bushings. Use OEM or equivalent quality bushings (Lemforder is the OEM supplier). Inspect the differential housing for any damage from excessive movement. Perform subframe alignment check after bushing replacement.</x:v>
       </x:c>
       <x:c r="F221" s="9" t="n">
         <x:v>0</x:v>
@@ -11206,67 +12538,67 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="222" ht="884.4000244140625" hidden="0" customHeight="1">
+    <x:row r="222" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A222" s="40" t="n">
         <x:v>221</x:v>
       </x:c>
       <x:c r="B222" s="9" t="str">
-        <x:v>bmw-x5-coolant-pipe-leak-2007</x:v>
+        <x:v>bmw-x6-transfer-case-2008</x:v>
       </x:c>
       <x:c r="C222" s="9" t="str">
-        <x:v>2007-2010 | BMW | X5 | 4.8i, xDrive48i | N62, N62TU</x:v>
+        <x:v>2008-2023 | BMW | X6</x:v>
       </x:c>
       <x:c r="D222" s="9" t="str">
-        <x:v>E70 N62 Coolant Transfer Pipe Leak (Pressure-Test First)</x:v>
+        <x:v>Transfer Case Actuator Motor Failure (All xDrive Models)</x:v>
       </x:c>
       <x:c r="E222" s="9" t="str">
-        <x:v>Pressure-test the cooling system cold and inspect the engine valley and all accessible connections to identify the exact leak before ordering parts. If inspection confirms the N62 transfer pipe and BMW ETK/AIR selects it for the VIN, replace pipe 11-14-1-439-975 with the required seals and one-time-use hardware from the VIN-specific repair diagram. Refill and bleed the cooling system with the specified coolant, repeat the pressure test, and verify stable temperature. Do not automatically replace an N63 pipe, thermostat, or unrelated hoses from this article.</x:v>
+        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket gear repair kit ($100-150). G06 actuator motor 27609469023 ($400-600) for complete replacement. DIY gear repair kits are straightforward and save $1,200+ over dealer replacement. Complete transfer case replacement if internal damage occurred: $1,400-3,300. PREVENTIVE: If buying used X6 over 80k miles, budget for this repair and listen for clicking noise when shutting off ignition.</x:v>
       </x:c>
       <x:c r="F222" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G222" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="223" ht="1082.4000244140625" hidden="0" customHeight="1">
+    <x:row r="223" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A223" s="40" t="n">
         <x:v>222</x:v>
       </x:c>
       <x:c r="B223" s="9" t="str">
-        <x:v>bmw-x5-n63-timing-chain-2008</x:v>
+        <x:v>bmw-x6m-front-thrust-arm-bushing-2015</x:v>
       </x:c>
       <x:c r="C223" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 | xDrive50i | N63</x:v>
+        <x:v>2015-2025 | BMW | X6 M</x:v>
       </x:c>
       <x:c r="D223" s="9" t="str">
-        <x:v>Early N63 Timing-Chain Wear Check: ISTA Test Before Repair</x:v>
+        <x:v>Front Thrust Arm Bushing (Tension Strut) Premature Wear</x:v>
       </x:c>
       <x:c r="E223" s="9" t="str">
-        <x:v>Check the VIN and service history with a BMW center, diagnose stored VANOS/camshaft faults first, and run BMW's ISTA timing-chain elongation test. If the result is 'Timing chain is OK,' do not replace parts on this claim. If it is 'not OK,' BMW SIB 11 16 14 directs replacement of both timing chains under the VIN-specific repair instruction, followed by the required oil/filter service, priming steps, programming, and shorter oil-service interval. A single tensioner 11-31-7-557-741 or a generic Cloyes kit is not the complete repair and must not be presented as what the owner needs. Tow the vehicle rather than driving it when severe mechanical noise, oil-pressure warnings, or loss of timing is present.</x:v>
+        <x:v>Replace both front thrust arms as complete assemblies (the bushings are not serviceable separately). Use genuine BMW M-spec parts or Lemforder equivalents. Perform a 4-wheel alignment immediately after replacement. Upgrade to Powerflex polyurethane thrust arm bushings for extended lifespan, especially on tracked cars.</x:v>
       </x:c>
       <x:c r="F223" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G223" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="224" ht="1227.5999755859375" hidden="0" customHeight="1">
+    <x:row r="224" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A224" s="40" t="n">
         <x:v>223</x:v>
       </x:c>
       <x:c r="B224" s="9" t="str">
-        <x:v>bmw-x5-n63-wastegate-2008</x:v>
+        <x:v>bmw-x6m-s63-rod-bearing-2010</x:v>
       </x:c>
       <x:c r="C224" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 | xDrive50i | N63, N63TU</x:v>
+        <x:v>2010-2023 | BMW | X6 M | M50i, xDrive50i | S63</x:v>
       </x:c>
       <x:c r="D224" s="9" t="str">
-        <x:v>N63/N63TU Low Boost or Turbo Rattle: Diagnose Vacuum Control First</x:v>
+        <x:v>S63 Rod Bearing Failure (X6 M)</x:v>
       </x:c>
       <x:c r="E224" s="9" t="str">
-        <x:v>Read all DME faults and compare requested versus actual boost under the BMW test plan. Pressure- or smoke-test the intake and charge-air path, verify vacuum supply from the pump and reservoir, inspect both banks' hoses and pressure converters, and test actuator movement before condemning a turbocharger. Identify the engine generation, failed bank, and exact hardware in BMW ETK/AIR. Check a 2010-2013 E70 VIN for the N63 Customer Care Package only as applicable; its published six-point scope includes air-mass sensors, injectors, vacuum pump, low-pressure fuel sensor/feed line, fresh-air turbo seals, and crankcase-ventilation lines, not an automatic wastegate replacement. No retail link is published until diagnosis selects a VIN-specific component.</x:v>
+        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles ($2,500-5,000 labor-intensive job). Use ACL Race 8B1578HX-STD ($150-250) or King CR8049SV ($120-200) upgraded bearings - these are stronger than OEM and provide better durability under high loads. Send oil samples for analysis (Blackstone Labs ~$30) every 5,000 miles to monitor bearing wear metals. If bearings have already failed: engine replacement required ($15,000-30,000). DO NOT buy used X6 M without documented bearing replacement history or fresh oil analysis.</x:v>
       </x:c>
       <x:c r="F224" s="9" t="n">
         <x:v>0</x:v>
@@ -11275,136 +12607,136 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="225" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="225" ht="277.20001220703125" hidden="0" customHeight="1">
       <x:c r="A225" s="40" t="n">
         <x:v>224</x:v>
       </x:c>
       <x:c r="B225" s="9" t="str">
-        <x:v>bmw-x5-oil-leaks-2000</x:v>
+        <x:v>bmw-x6m-vanos-solenoid-2015</x:v>
       </x:c>
       <x:c r="C225" s="9" t="str">
-        <x:v>2003-2006 | BMW | X5 | 3.0i | M54</x:v>
+        <x:v>2015-2021 | BMW | X6 M | S63</x:v>
       </x:c>
       <x:c r="D225" s="9" t="str">
-        <x:v>E53 3.0i M54 Valve-Cover Gasket Leak (Confirm the Source)</x:v>
+        <x:v>VANOS Solenoid Oil Sludge Buildup</x:v>
       </x:c>
       <x:c r="E225" s="9" t="str">
-        <x:v>Clean the engine and trace the highest fresh-oil source before ordering a gasket. If the leak is at the M54 cylinder-head-cover perimeter or spark-plug-well seals, inspect the plastic cover for cracks, warpage, damaged fastener grommets, and crankcase-ventilation faults. Reuse the cover only if it passes inspection, then install VIN/production-confirmed gasket set 11-12-0-030-496 with the BMW-specified grommets and sealant locations and torque sequence. If the cover or another oil circuit is the source, select that separate repair instead.</x:v>
+        <x:v>Remove and clean or replace the VANOS solenoids. Perform an engine oil flush. Strictly follow 7,500-mile oil change intervals with BMW LL-01 rated 0W-40 synthetic oil.</x:v>
       </x:c>
       <x:c r="F225" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G225" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="226" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="226" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A226" s="40" t="n">
         <x:v>225</x:v>
       </x:c>
       <x:c r="B226" s="9" t="str">
-        <x:v>bmw-x5-transfer-case-actuator-2000</x:v>
+        <x:v>bmw-x7-48v-battery-2020</x:v>
       </x:c>
       <x:c r="C226" s="9" t="str">
-        <x:v>2007-2013 | BMW | X5 | 3.0si, 4.8i, xDrive30i, xDrive35d, xDrive48i, X5 M | N52, N62, M57, S63</x:v>
+        <x:v>2020-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D226" s="9" t="str">
-        <x:v>E70 ATC700 Transfer-Case Positioning Motor (Diagnosis Required)</x:v>
+        <x:v>48V Mild Hybrid Battery Issues</x:v>
       </x:c>
       <x:c r="E226" s="9" t="str">
-        <x:v>Read BMW VTG/DSC faults and run the applicable ISTA transfer-case test plan before buying a motor. Confirm tire sizes and wear, battery voltage, wiring, transfer-case type, fluid condition, calibration, and—especially after differential or transfer-case replacement—the VIN-correct front and rear gear ratios. If testing confirms the ATC700 positioning motor and BMW ETK/AIR selects this application for the VIN, current BMW exchange servomotor 27-10-2-449-709 supersedes 27-10-7-568-267. Install the correct classification resistor/hardware supplied or specified for the VIN and perform the required VTG initialization/calibration. A generic gear-only kit is not a universal BMW repair and should not be ordered without opening and confirming the exact motor failure.</x:v>
+        <x:v>Replace the 48V mild hybrid battery ($1,000-2,000 at dealer). Requires dealer-level diagnostic tools and coding after installation - this is NOT a DIY repair. The 48V battery is separate from the main 12V battery. No aftermarket alternatives currently available. Check if vehicle is still under BMW warranty or extended warranty coverage. Some owners choose to live with the failed auto start-stop rather than pay for replacement.</x:v>
       </x:c>
       <x:c r="F226" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G226" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="227" ht="726" hidden="0" customHeight="1">
       <x:c r="A227" s="40" t="n">
         <x:v>226</x:v>
       </x:c>
       <x:c r="B227" s="9" t="str">
-        <x:v>bmw-x5-transfer-case-actuator-2007</x:v>
+        <x:v>bmw-x7-air-suspension-2019</x:v>
       </x:c>
       <x:c r="C227" s="9" t="str">
-        <x:v>2019-2026 | BMW | X5</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D227" s="9" t="str">
-        <x:v>G05/F95 Transfer-Case Shudder: Tires and Fluid Diagnosis First</x:v>
+        <x:v>Air Suspension Compressor &amp; Strut Failure (Standard Equipment)</x:v>
       </x:c>
       <x:c r="E227" s="9" t="str">
-        <x:v>Follow BMW SIB 27 02 20 in order: verify all four tires for VIN-correct size, brand/application, axle placement, and wear; diagnose any powertrain faults; then use ISTA to temporarily deactivate the transfer-case clutch and road-test the complaint. Only if the shudder disappears with the VTG deactivated does BMW direct an ATX13-X oil change with DTF-1, followed by VTG calibration. The clutch plates can require up to 125 miles after the service to become fully saturated and smooth out. If the symptom remains, continue diagnosis rather than buying an actuator or transfer case. Part numbers for any further repair must be selected by VIN in ETK/AIR.</x:v>
+        <x:v>Replace failed air struts and/or compressor. Front strut left 37106869035 ($1,500-2,000), right 37106869036 ($1,500-2,000), rear 37106869039 ($1,000-1,500). Compressor 37206861882 ($800-1,200). RebuildMasterTech rebuilt struts ($600-900 each) are a more affordable alternative. Total repair can reach $2,180-5,000+ depending on which components have failed. Replace both struts on same axle simultaneously. Inspect at 50,000 miles for early signs of leaking.</x:v>
       </x:c>
       <x:c r="F227" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G227" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="228" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="228" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A228" s="40" t="n">
         <x:v>227</x:v>
       </x:c>
       <x:c r="B228" s="9" t="str">
-        <x:v>bmw-x5-vanos-solenoid-2000</x:v>
+        <x:v>bmw-x7-air-suspension-compressor-2019</x:v>
       </x:c>
       <x:c r="C228" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 | xDrive30i, xDrive35i | N51, N52K, N52T, N55</x:v>
+        <x:v>2019-2026 | BMW | X7</x:v>
       </x:c>
       <x:c r="D228" s="9" t="str">
-        <x:v>VANOS Adjustment-Unit Bolt Recall 23V-707 (E70 Inline-Six)</x:v>
+        <x:v>Air Suspension Compressor Failure</x:v>
       </x:c>
       <x:c r="E228" s="9" t="str">
-        <x:v>Enter the VIN in BMW's official recall lookup and have an authorized BMW center complete recall 23V-707 if it is open. BMW's procedure is inspection-dependent: intact affected bolts are replaced; if bolts are loose or broken, the affected VANOS adjustment unit is replaced, and missing fragments must be recovered. The recall repair is free, so do not buy a solenoid or VANOS part first. If the VIN is outside the recall or a fault remains after the remedy, use BMW-capable diagnostics to test oil supply and pressure, wiring, sensors, control solenoids, adjustment units, and mechanical timing before selecting a part. If the engine runs roughly, makes unusual mechanical noise, loses power, or stalls, move out of traffic safely, stop driving, and contact BMW for transport guidance.</x:v>
+        <x:v>Replace the air suspension compressor. Inspect all four air springs for leaks using soapy water solution. Replace any leaking air springs to prevent repeated compressor failure. Check the valve block for proper operation. The compressor is located under the rear of the vehicle.</x:v>
       </x:c>
       <x:c r="F228" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G228" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="229" ht="1148.4000244140625" hidden="0" customHeight="1">
+    <x:row r="229" ht="871.2000122070312" hidden="0" customHeight="1">
       <x:c r="A229" s="40" t="n">
         <x:v>228</x:v>
       </x:c>
       <x:c r="B229" s="9" t="str">
-        <x:v>bmw-x5-water-pump-2007</x:v>
+        <x:v>bmw-x7-b58-coolant-2019</x:v>
       </x:c>
       <x:c r="C229" s="9" t="str">
-        <x:v>2011-2013 | BMW | X5 | xDrive35i | N55</x:v>
+        <x:v>2019-2023 | BMW | X7 | xDrive40i | B58</x:v>
       </x:c>
       <x:c r="D229" s="9" t="str">
-        <x:v>E70 xDrive35i N55 Electric Coolant Pump (Fault-Confirmed)</x:v>
+        <x:v>B58 Coolant System Failures (xDrive40i)</x:v>
       </x:c>
       <x:c r="E229" s="9" t="str">
-        <x:v>If the engine-temperature warning appears, stop safely, shut the engine off, and tow the vehicle if normal temperature cannot be confirmed. When cool, check coolant level and leaks, read BMW-specific faults, verify pump power/ground and communication, and run the ISTA coolant-pump activation/test plan. If those tests confirm the pump and BMW ETK/AIR selects 11-51-5-A05-704 for the VIN, replace it using the BMW procedure, select the thermostat separately only if testing or preventive planning justifies it, vacuum-fill or bleed the system as specified, and verify commanded pump operation and stable temperature. Do not use a fixed-mileage rule or this part number for an N52, N63, or F15 without VIN confirmation.</x:v>
+        <x:v>Replace failed coolant system components. Water pump 11518482250 ($300-400). Thermostat 11537644811 ($150-250). Replace expansion tank and all plastic coolant connections when performing repair to prevent cascading failures. For 2023+ models, check VIN for recall 24V-608 coverage for coolant pump connector. Total repair $500-2,500 depending on extent of damage. PREVENTIVE: Replace thermostat and water pump at 60,000-70,000 miles before failure. Inspect coolant hoses and connections at every oil change after 50k miles.</x:v>
       </x:c>
       <x:c r="F229" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G229" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="230" ht="1056" hidden="0" customHeight="1">
+    <x:row r="230" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A230" s="40" t="n">
         <x:v>229</x:v>
       </x:c>
       <x:c r="B230" s="9" t="str">
-        <x:v>bmw-x5m-brake-system-2010</x:v>
+        <x:v>bmw-x7-b58-coolant-expansion-tank-2019</x:v>
       </x:c>
       <x:c r="C230" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M</x:v>
+        <x:v>2019-2026 | BMW | X7 | B58</x:v>
       </x:c>
       <x:c r="D230" s="9" t="str">
-        <x:v>Heavy-Duty Brake System Accelerated Wear - E70/F85/F95 X5 M</x:v>
+        <x:v>B58 Coolant Expansion Tank Crack</x:v>
       </x:c>
       <x:c r="E230" s="9" t="str">
-        <x:v>E70 X5 M brakes: OEM front pads 34116799964 ($150-$250), rear pads 34216794879 ($120-$200). F85 X5 M front brake rotors: 34112284101/34112284102 with 6-pot caliper 34117845747/34117845748 and pads 34112284869. F85 rear: 385mm x 24mm perforated rotors 34212284903/34212284904 with 4-pot Brembo caliper and Textar pads. Budget $1,500-$2,500 per axle for complete brake service. For track use: EBC Yellowstuff or Hawk HPS 5.0 pads ($200-$350 per axle) with StopTech slotted rotors for improved heat management. Use Motul RBF 660 or ATE Typ 200 brake fluid - flush every 12 months. Budget $3,000-$5,000 per year for brake maintenance if driving spiritedly.</x:v>
+        <x:v>Replace the coolant expansion tank with an updated BMW part that uses improved plastic composition. Also replace the cap and inspect all coolant hoses. Flush and refill the cooling system with BMW-approved coolant. Check for coolant contamination from the old tank.</x:v>
       </x:c>
       <x:c r="F230" s="9" t="n">
         <x:v>0</x:v>
@@ -11413,21 +12745,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="231" ht="1122" hidden="0" customHeight="1">
+    <x:row r="231" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A231" s="40" t="n">
         <x:v>230</x:v>
       </x:c>
       <x:c r="B231" s="9" t="str">
-        <x:v>bmw-x5m-rear-differential-2010</x:v>
+        <x:v>bmw-x7-ibs-brake-recall-2023</x:v>
       </x:c>
       <x:c r="C231" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | S63</x:v>
+        <x:v>2023-2025 | BMW | X7</x:v>
       </x:c>
       <x:c r="D231" s="9" t="str">
-        <x:v>Rear Differential Wear &amp; Fluid Degradation - E70/F85/F95 X5 M</x:v>
+        <x:v>2023-2025 X7 Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E231" s="9" t="str">
-        <x:v>Change rear differential fluid every 30,000 miles (ignore BMW "lifetime fill" claim). E70 X5 M: No drain plug - fluid must be extracted through fill port with hand pump or suction device. Recommended fluid: Royal Purple 75W-140 GL5 synthetic or Red Line 75W-140 GL5 ($40-$60 per fill). Capacity approximately 1.2 liters. For limited-slip diff, ensure fluid is GL5 rated with limited-slip additive. If differential is making whining/howling noise: have a limited-slip differential specialist inspect internals (not generic BMW shop). Diff rebuild: $1,500-$3,000 at specialist. Complete differential replacement: $3,000-$5,500 + labor. Labor for fluid change: $150-$300 at independent shop.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
       </x:c>
       <x:c r="F231" s="9" t="n">
         <x:v>0</x:v>
@@ -11436,21 +12768,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="232" ht="1386" hidden="0" customHeight="1">
+    <x:row r="232" ht="897.5999755859375" hidden="0" customHeight="1">
       <x:c r="A232" s="40" t="n">
         <x:v>231</x:v>
       </x:c>
       <x:c r="B232" s="9" t="str">
-        <x:v>bmw-x5m-s63-cooling-system-2010</x:v>
+        <x:v>bmw-x7-n63-oil-consumption-2019</x:v>
       </x:c>
       <x:c r="C232" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2019-2023 | BMW | X7 | M50i, M60i, xDrive50i | N63TU3</x:v>
       </x:c>
       <x:c r="D232" s="9" t="str">
-        <x:v>S63 Cooling System Component Failures - E70/F85/F95 X5 M</x:v>
+        <x:v>N63TU3 Oil Consumption &amp; Valve Stem Seal Degradation (xDrive50i/M50i/M60i)</x:v>
       </x:c>
       <x:c r="E232" s="9" t="str">
-        <x:v>PROACTIVE MAINTENANCE SCHEDULE: Replace electric water pump at 60,000 miles ($400-$700 + labor). Replace thermostat at same time ($150-$250). Replace expansion tank at 60,000-80,000 miles ($100-$200). Inspect all coolant hoses at every oil change - replace any that are soft, bulging, or showing surface cracks. E70 X5 M expansion tank vent hose: 17128627119 ($30-$50). Flush coolant system every 2 years or 30,000 miles (more frequent than BMW's 4-year recommendation). Use ONLY BMW coolant mixed 50/50 with distilled water. For E70 hot-V turbo coolant lines: GRYPHONTEK repair kit eliminates plastic T-fitting failure (see separate issue entry). Budget $1,500-$2,500 for complete cooling system refresh at 60,000 miles. This prevents catastrophic overheating that can destroy the S63 engine ($15,000-$34,000 engine replacement).</x:v>
+        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 for OEM spec. 5150 AutoSport Viton upgraded seals ($150-200) recommended for better heat resistance. AGA Tools kit includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Check eligibility for class action settlement coverage. Some owners monitor oil levels and top off rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil and check level every 500-1,000 miles.</x:v>
       </x:c>
       <x:c r="F232" s="9" t="n">
         <x:v>0</x:v>
@@ -11459,21 +12791,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="233" ht="1135.199951171875" hidden="0" customHeight="1">
+    <x:row r="233" ht="396" hidden="0" customHeight="1">
       <x:c r="A233" s="40" t="n">
         <x:v>232</x:v>
       </x:c>
       <x:c r="B233" s="9" t="str">
-        <x:v>bmw-x5m-s63-oil-leaks-2010</x:v>
+        <x:v>bmw-x7-panoramic-roof-rattle-2019</x:v>
       </x:c>
       <x:c r="C233" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2019-2026 | BMW | X7</x:v>
       </x:c>
       <x:c r="D233" s="9" t="str">
-        <x:v>S63 V8 Chronic Oil Leaks (Valve Cover, Oil Pan, Turbo Lines) - E70/F85/F95 X5 M</x:v>
+        <x:v>Panoramic Sunroof Rattle and Creak</x:v>
       </x:c>
       <x:c r="E233" s="9" t="str">
-        <x:v>Valve cover gasket replacement (both sides): $1,200-$2,500 with labor. BMW plastic valve covers can crack and must be replaced entirely (not just gasket) - inspect during service. Oil filter housing gasket: $400-$800 with labor. Oil pan gasket: $2,000-$3,500 (requires engine/subframe drop). Turbo oil feed/return lines: replace with GRYPHONTEK or MAMBA upgraded silicone/braided lines during any turbo service ($200-$400). VANOS solenoid seals: $100-$200 (DIY-friendly). For comprehensive oil leak repair at 80,000+ miles: budget $3,000-$5,000 to address all common leak points simultaneously. Valve cover bolt torque is CRITICAL - too tight cracks the cover ($800-$1,200 per cover), too loose and it leaks.</x:v>
+        <x:v>Apply BMW-approved felt tape or lubricant to sunroof guide rails. Replace worn guide rail bushings. In severe cases, the sunroof cassette or seal may need replacement under warranty. BMW has issued updated guide rail components for early production vehicles.</x:v>
       </x:c>
       <x:c r="F233" s="9" t="n">
         <x:v>0</x:v>
@@ -11482,21 +12814,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="234" ht="1412.4000244140625" hidden="0" customHeight="1">
+    <x:row r="234" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A234" s="40" t="n">
         <x:v>233</x:v>
       </x:c>
       <x:c r="B234" s="9" t="str">
-        <x:v>bmw-x5m-s63-rod-bearing-2010</x:v>
+        <x:v>bmw-x7-sunroof-leak-2019</x:v>
       </x:c>
       <x:c r="C234" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D234" s="9" t="str">
-        <x:v>S63 V8 Rod Bearing Premature Wear &amp; Failure - E70/F85 X5 M</x:v>
+        <x:v>Panoramic Sunroof Water Leak</x:v>
       </x:c>
       <x:c r="E234" s="9" t="str">
-        <x:v>PREVENTIVE: For track-driven X5 M, replace rod bearings proactively at 60,000-80,000 miles. ACL Race Series rod bearings (8B1578HX-STD for S63B44, +0.001" extra oil clearance) are the community gold standard ($200-$350 for bearing set). WPC surface-treated bearings from Lang Racing are the premium choice ($400-$600 set). Total cost for preventive rod bearing service: $4,500-$8,500 depending on shop. Oil analysis every 5,000 miles through Blackstone Labs ($30/test) to monitor bearing wear metals (lead and copper). Use only BMW 10W-60 synthetic oil with 5,000-7,500 mile oil change intervals. Never track the car on cold oil. Mporium BMW offers specialized S63 rod bearing service starting at $4,499. If catastrophic failure: rebuilt S63 engine from RK Autowerks (~$8,500 + installation), new BMW engine (~$34,000), or complete engine rebuild ($12,000-$18,000).</x:v>
+        <x:v>Clear clogged sunroof drain tubes ($100-300 at shop). Reference TSB SIB 54 11 19 when visiting dealer. For persistent leaks, drain tube connections or sunroof seal may need replacement ($500-1,500). If water has damaged interior electronics, repair costs can reach $3,000. PREVENTIVE: Clear sunroof drains annually, especially in areas with heavy tree debris. Run compressed air or flexible drain snake through drain tubes during oil changes. Keep sunroof track clean of debris.</x:v>
       </x:c>
       <x:c r="F234" s="9" t="n">
         <x:v>0</x:v>
@@ -11505,21 +12837,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="1214.4000244140625" hidden="0" customHeight="1">
+    <x:row r="235" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A235" s="40" t="n">
         <x:v>234</x:v>
       </x:c>
       <x:c r="B235" s="9" t="str">
-        <x:v>bmw-x5m-s63-turbo-coolant-line-2010</x:v>
+        <x:v>bmw-x7-tire-wear-2019</x:v>
       </x:c>
       <x:c r="C235" s="9" t="str">
-        <x:v>2010-2013 | BMW | X5 M</x:v>
+        <x:v>2019-2023 | BMW | X7</x:v>
       </x:c>
       <x:c r="D235" s="9" t="str">
-        <x:v>S63 Turbo Coolant Line Plastic T-Fitting Failure (Hot-V Design) - E70 X5 M</x:v>
+        <x:v>Premature Tire Wear (Especially 21"/22" Wheels)</x:v>
       </x:c>
       <x:c r="E235" s="9" t="str">
-        <x:v>Replace ALL factory plastic turbo coolant T-fittings and hoses with GRYPHONTEK S63 Turbo Coolant Line Repair Kit ($200-$400). Kit includes pre-shaped multi-layer reinforced silicone hoses, brass T-fittings (replacing factory plastic), and all necessary hose clamps. Direct bolt-on installation designed for the E70/E71 S63 engine bay. MAMBA Turbo also offers a reinforced turbo coolant line kit with brass and silicone components ($150-$350). This is a PROACTIVE replacement - do not wait for failure. Replace at first sign of coolant weeping or during any turbo service. Labor: $800-$1,500 due to tight access in hot-V engine valley. If turbo bearings are damaged from overheating: turbo replacement $3,000-$5,000 per unit.</x:v>
+        <x:v>Have alignment adjusted to reduce aggressive camber settings ($200-400). Switch to quality tires designed for heavy SUVs: Michelin Pilot Sport 4S or Continental PremiumContact 6 are recommended. If possible, avoid 22" wheels and opt for 21" or smaller for better tire longevity and ride comfort. Alignment adjustment can extend tire life from 15,000 to 30,000+ miles. Total cost $200-2,000 depending on tire replacement needs. Check alignment every 10,000 miles.</x:v>
       </x:c>
       <x:c r="F235" s="9" t="n">
         <x:v>0</x:v>
@@ -11528,21 +12860,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="236" ht="1135.199951171875" hidden="0" customHeight="1">
+    <x:row r="236" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A236" s="40" t="n">
         <x:v>235</x:v>
       </x:c>
       <x:c r="B236" s="9" t="str">
-        <x:v>bmw-x5m-s63-vanos-solenoid-2010</x:v>
+        <x:v>bmw-xm-airbag-passenger-knee-recall-2023</x:v>
       </x:c>
       <x:c r="C236" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M | 4.4i, 4.6is, 4.8is, M50i, M60i, xDrive48i, xDrive50e, xDrive50i | S63</x:v>
+        <x:v>2023-2023 | BMW | XM</x:v>
       </x:c>
       <x:c r="D236" s="9" t="str">
-        <x:v>S63 VANOS Solenoid Failure - E70/F85/F95 X5 M</x:v>
+        <x:v>2023 XM Front-Passenger Knee-Airbag Recall 23V-622</x:v>
       </x:c>
       <x:c r="E236" s="9" t="str">
-        <x:v>Replace all 4 VANOS solenoids simultaneously - they are same age and if one has failed, others are close behind. Pierburg 11368605123 (OEM supplier) at $30-$50 each from Turner Motorsport or BimmerWorld. Genuine BMW 11368482268 for S63TU applications at $50-$70 each. Total parts cost: $120-$280 for all 4 solenoids. Also replace VANOS solenoid O-rings and filter screens during service. Labor: 1-2 hours professional ($150-$400 labor). This is one of the easier S63 repairs - accessible from top of engine without removing intake manifold. Natafox and Febi also offer quality aftermarket VANOS solenoids at lower cost ($20-$35 each). Clean VANOS system with fresh oil change immediately after solenoid replacement.</x:v>
+        <x:v>Check the VIN for an open 23V-622 campaign. If open, an authorized BMW dealer replaces the front-passenger knee airbag free of charge. Do not attempt airbag diagnosis or order a clock spring or airbag module from this card; supplemental-restraint work requires trained personnel and VIN-selected parts.</x:v>
       </x:c>
       <x:c r="F236" s="9" t="n">
         <x:v>0</x:v>
@@ -11551,21 +12883,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="237" ht="1293.5999755859375" hidden="0" customHeight="1">
+    <x:row r="237" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A237" s="40" t="n">
         <x:v>236</x:v>
       </x:c>
       <x:c r="B237" s="9" t="str">
-        <x:v>bmw-x5m-s63-wastegate-rattle-2010</x:v>
+        <x:v>bmw-xm-hybrid-drivetrain-hesitation-2023</x:v>
       </x:c>
       <x:c r="C237" s="9" t="str">
-        <x:v>2010-2018 | BMW | X5 M | S63</x:v>
+        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid, S68</x:v>
       </x:c>
       <x:c r="D237" s="9" t="str">
-        <x:v>S63 Twin Turbo Wastegate Rattle - E70/F85 X5 M</x:v>
+        <x:v>Hybrid Drivetrain Hesitation and Power Delivery Lag</x:v>
       </x:c>
       <x:c r="E237" s="9" t="str">
-        <x:v>Option 1 (Most cost-effective): MAMBA SUS316 stainless steel wastegate rattle flapper repair kit for S63 MGT2260 (part 077-0024, replaces 790463-2 / 790484-3), approximately $150-$300 per turbo. Requires turbo removal for installation. Option 2: Lskioer turbo wastegate rattle flapper repair kit for S63/S63TU MGT2260DSL ($80-$150 per kit on Amazon). Option 3: Replace turbo wastegate actuators with new OEM units ($300-$500 each). Option 4: Full turbocharger replacement with new or remanufactured units ($3,000-$5,000 per turbo + labor). Labor for turbo removal and reinstallation: $2,000-$3,500 for both turbos. While turbos are out: replace turbo oil feed/return lines, coolant lines, and all gaskets (GRYPHONTEK turbo coolant line repair kit for E70 X5M, ~$200-$400).</x:v>
+        <x:v>Visit the dealer for the latest transmission and hybrid system software calibration updates. Select Sport or Sport Plus mode for more consistent power delivery. The latest software revisions significantly improve the electric-to-V8 handoff smoothness. If hesitation persists after updates, the dealer can reset the transmission adaptation values to relearn driving patterns.</x:v>
       </x:c>
       <x:c r="F237" s="9" t="n">
         <x:v>0</x:v>
@@ -11574,21 +12906,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="238" ht="1069.199951171875" hidden="0" customHeight="1">
+    <x:row r="238" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A238" s="40" t="n">
         <x:v>237</x:v>
       </x:c>
       <x:c r="B238" s="9" t="str">
-        <x:v>bmw-x5m-transfer-case-actuator-2010</x:v>
+        <x:v>bmw-xm-integrated-brake-system-recall-2023</x:v>
       </x:c>
       <x:c r="C238" s="9" t="str">
-        <x:v>2010-2023 | BMW | X5 M</x:v>
+        <x:v>2023-2024 | BMW | XM</x:v>
       </x:c>
       <x:c r="D238" s="9" t="str">
-        <x:v>xDrive Transfer Case Actuator Motor Failure - E70/F85/F95 X5 M</x:v>
+        <x:v>2023-2024 XM Integrated Brake System Recall 26V-422</x:v>
       </x:c>
       <x:c r="E238" s="9" t="str">
-        <x:v>Replace transfer case actuator motor. E70 X5 M: BMW 27107566296 or equivalent ($250-$450 for actuator motor). F85 X5 M: BMW 27608643153 or equivalent ($300-$500). F95 X5 M: check VIN-specific part number with dealer. FCP Euro has an excellent DIY guide for BMW transfer case actuator repair - the actuator can be replaced without removing the entire transfer case. Labor: 2-3 hours at specialist shop ($300-$600 labor). Change transfer case fluid at same time with BMW DTF-1 specification fluid. XeMODeX offers remanufactured transfer case actuator motors at reduced cost ($200-$350). For complete transfer case failure: $3,500-$6,000 for replacement unit + labor.</x:v>
+        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; wheel-speed sensors are not the recall remedy.</x:v>
       </x:c>
       <x:c r="F238" s="9" t="n">
         <x:v>0</x:v>
@@ -11597,21 +12929,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="239" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="239" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A239" s="40" t="n">
         <x:v>238</x:v>
       </x:c>
       <x:c r="B239" s="9" t="str">
-        <x:v>bmw-x6-adaptive-drive-malfunction-2008</x:v>
+        <x:v>bmw-xm-suspension-ride-quality-2023</x:v>
       </x:c>
       <x:c r="C239" s="9" t="str">
-        <x:v>2008-2019 | BMW | X6</x:v>
+        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid</x:v>
       </x:c>
       <x:c r="D239" s="9" t="str">
-        <x:v>Adaptive Drive System Malfunction</x:v>
+        <x:v>Harsh Ride Quality and Suspension Stiffness</x:v>
       </x:c>
       <x:c r="E239" s="9" t="str">
-        <x:v>Diagnose specific Adaptive Drive component failure using BMW ISTA diagnostics. Replace the failed component — most commonly the hydraulic pump or valve block. If repair cost is prohibitive, some owners convert to conventional anti-roll bars as a permanent fix at lower cost.</x:v>
+        <x:v>Check tire pressures regularly - overinflated tires significantly worsen the harsh ride. Some owners report improved comfort by switching to a tire with a taller sidewall profile (if available for the XM's wheel size). Use Comfort mode for daily driving. Unfortunately, no aftermarket spring or damper solution currently exists to significantly improve the ride without compromising the handling needed for the XM's weight.</x:v>
       </x:c>
       <x:c r="F239" s="9" t="n">
         <x:v>0</x:v>
@@ -11620,21 +12952,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="858" hidden="0" customHeight="1">
+    <x:row r="240" ht="528" hidden="0" customHeight="1">
       <x:c r="A240" s="40" t="n">
         <x:v>239</x:v>
       </x:c>
       <x:c r="B240" s="9" t="str">
-        <x:v>bmw-x6-air-suspension-2008</x:v>
+        <x:v>bmw-z3-convertible-top-rear-window-cracking-clouding-bead-separatio</x:v>
       </x:c>
       <x:c r="C240" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D240" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure</x:v>
+        <x:v>Convertible Top Rear Window Cracking, Clouding, and Bead Separation</x:v>
       </x:c>
       <x:c r="E240" s="9" t="str">
-        <x:v>Replace failed air springs or compressor. Arnott rear air spring A-2642 ($200-300 each). OEM F16 spring 37126795013 ($200). Arnott compressor P-2655 ($599). Or convert to coil springs: Strutmasters BB2RBM conversion kit ($1,200-1,800) permanently eliminates air suspension issues. Conversion is cheaper long-term than continued air suspension repairs. If keeping air suspension: inspect air springs at 60,000-80,000 miles for cracks/leaks before compressor damage occurs. Replace both air springs on same axle simultaneously.</x:v>
+        <x:v>Replace the rear window panel only — BMW used a zipper system so the clouded/cracked window unzips and a new window zips/tapes in without disturbing the fabric top. Re-gluing separated bead trim rarely holds, so window replacement is the durable fix. Job is a DIY-feasible 1-1.5 hours; replace the whole top only if the fabric is also degraded.</x:v>
       </x:c>
       <x:c r="F240" s="9" t="n">
         <x:v>0</x:v>
@@ -11643,22 +12975,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="241" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="241" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A241" s="40" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="B241" s="9" t="str">
-        <x:v>bmw-x6-ibs-brake-recall-2023</x:v>
+        <x:v>bmw-z3-cooling-system-failure-1996</x:v>
       </x:c>
       <x:c r="C241" s="9" t="str">
-        <x:v>2024-2024 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D241" s="9" t="str">
-        <x:v>2024 X6 Integrated Brake System Recall 26V-422</x:v>
-      </x:c>
-      <x:c r="E241" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
-      </x:c>
+        <x:v>Cooling System Component Failures</x:v>
+      </x:c>
+      <x:c r="E241" s="9" t="str"/>
       <x:c r="F241" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -11666,21 +12996,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="242" ht="924" hidden="0" customHeight="1">
+    <x:row r="242" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A242" s="40" t="n">
         <x:v>241</x:v>
       </x:c>
       <x:c r="B242" s="9" t="str">
-        <x:v>bmw-x6-n63-timing-chain-2008</x:v>
+        <x:v>bmw-z3-cracked-exhaust-manifold-1-9l-4-cylinder</x:v>
       </x:c>
       <x:c r="C242" s="9" t="str">
-        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
+        <x:v>1996-2002 | BMW | Z3 | 1.9, 1.9i, Z3 1.9 | 1.9L M44 4-cylinder, 1.9L M43TU 4-cylinder</x:v>
       </x:c>
       <x:c r="D242" s="9" t="str">
-        <x:v>N63 Timing Chain Stretch &amp; Guide Failure (E71/F16 xDrive50i)</x:v>
+        <x:v>Cracked Exhaust Manifold on 1.9L 4-Cylinder (M44/M43)</x:v>
       </x:c>
       <x:c r="E242" s="9" t="str">
-        <x:v>PREVENTIVE REPLACEMENT: If you own 2008-2014 E71 xDrive50i with N63, replace timing chain guides and tensioners IMMEDIATELY at 60,000-80,000 miles ($4,000-6,000) BEFORE failure. IWIS timing chain kit 90001521 ($800-1,200) or Turner kit 11317594899KT recommended. Replace lower chain guide 11147574373 at same time. If chain has already failed: complete engine replacement required ($15,000-25,000). Check VIN with BMW dealer for extended warranty eligibility. 2015+ N63TU engines have improved timing components but still require monitoring.</x:v>
+        <x:v>Inspect the manifold for hairline cracks (a cold-engine listen or smoke test confirms the leak). Replace the cracked manifold with a used OE unit or an aftermarket stainless tubular header, and renew the manifold gasket and hardware. Allow roughly 3-4 hours labor.</x:v>
       </x:c>
       <x:c r="F242" s="9" t="n">
         <x:v>0</x:v>
@@ -11689,21 +13019,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="243" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="243" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A243" s="40" t="n">
         <x:v>242</x:v>
       </x:c>
       <x:c r="B243" s="9" t="str">
-        <x:v>bmw-x6-n63-valve-stem-seal-wear-2008</x:v>
+        <x:v>bmw-z3-differential-mount-ear-trunk-floor-pan-tearing</x:v>
       </x:c>
       <x:c r="C243" s="9" t="str">
-        <x:v>2008-2019 | BMW | X6 | N63</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D243" s="9" t="str">
-        <x:v>N63 Valve Stem Seal Degradation and Oil Burning</x:v>
+        <x:v>Differential Mount Ear and Trunk Floor Pan Tearing</x:v>
       </x:c>
       <x:c r="E243" s="9" t="str">
-        <x:v>Replace all intake and exhaust valve stem seals. This is a major job requiring head work. Also replace turbo oil return lines and update engine software per BMW N63 Customer Care Package specifications. Ensure proper oil grade (BMW LL-01) is used.</x:v>
+        <x:v>Inspect the trunk floor around the differential mount and rear subframe pickup points for cracks, torn metal, and broken spot welds. Repair requires welding and a reinforcement/re-fabrication plate kit to tie the diff mount/subframe back into the floor. Switching the diff carrier bushings to polyurethane reduces carrier movement and the stress that causes the tearing. Catching it early greatly limits the repair scope.</x:v>
       </x:c>
       <x:c r="F243" s="9" t="n">
         <x:v>0</x:v>
@@ -11712,21 +13042,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="244" ht="858" hidden="0" customHeight="1">
+    <x:row r="244" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A244" s="40" t="n">
         <x:v>243</x:v>
       </x:c>
       <x:c r="B244" s="9" t="str">
-        <x:v>bmw-x6-n63-valve-stem-seals-2008</x:v>
+        <x:v>bmw-z3-door-window-regulator-clip-mounting-tab-failure</x:v>
       </x:c>
       <x:c r="C244" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6 | M50i, xDrive50i | N63</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D244" s="9" t="str">
-        <x:v>N63 Valve Stem Seal / Oil Consumption (xDrive50i)</x:v>
+        <x:v>Door Window Regulator Clip / Mounting Tab Failure</x:v>
       </x:c>
       <x:c r="E244" s="9" t="str">
-        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 ($80-120/set of 16, need 2 sets for V8). 5150 AutoSport Viton upgraded seals ($150-200) are recommended for better heat resistance in hot-vee configuration. AGA Tools kit AGA-N63-VSK-K ($500-800) includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Some owners monitor oil levels and add as needed rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil.</x:v>
+        <x:v>Replace the broken plastic regulator clips, or replace the regulator assembly if the cable or mechanism is also worn. If the welded mounting tab/anchor has torn from the door frame, it must be re-welded or reinforced before fitting a new regulator. Lubricate the window channels to reduce drag on the new parts.</x:v>
       </x:c>
       <x:c r="F244" s="9" t="n">
         <x:v>0</x:v>
@@ -11735,21 +13065,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="245" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="245" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A245" s="40" t="n">
         <x:v>244</x:v>
       </x:c>
       <x:c r="B245" s="9" t="str">
-        <x:v>bmw-x6-n63-wastegate-2008</x:v>
+        <x:v>bmw-z3-fuel-level-sender-failure-causing-erratic-dead-fuel-gauge</x:v>
       </x:c>
       <x:c r="C245" s="9" t="str">
-        <x:v>2008-2018 | BMW | X6 | M50i, xDrive50i</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D245" s="9" t="str">
-        <x:v>N63 Turbo Wastegate Rattle (xDrive50i)</x:v>
+        <x:v>Fuel Level Sender Failure Causing Erratic or Dead Fuel Gauge</x:v>
       </x:c>
       <x:c r="E245" s="9" t="str">
-        <x:v>Repair options range from flapper repair kits ($50-100/turbo) to complete turbocharger replacement ($4,000-8,000 for both). Garrett MGT2256S flapper repair kit ($50-100 per turbo) is cheapest fix. MAMBA adjustable actuator kit ($150-300) provides more durable solution. OEM actuators 11657646093 available from BMW. Complete turbo replacement $2,000-4,000 per turbo. MONITORING: Wastegate rattle is early warning - address before complete turbo failure to avoid $8,000+ repair.</x:v>
+        <x:v>Remove the access panel behind the seats and inspect the sender. A dirty or lightly worn ceramic/resistor plate can sometimes be cleaned, but a cracked plate or worn brushes requires replacing the sender unit (or the complete fuel-pump/sender carrier assembly). Also check the tank vent valve, as tank vacuum can deform the float arm. Confirm wiring/ground integrity before condemning the sender.</x:v>
       </x:c>
       <x:c r="F245" s="9" t="n">
         <x:v>0</x:v>
@@ -11758,21 +13088,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="246" ht="409.20001220703125" hidden="0" customHeight="1">
+    <x:row r="246" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A246" s="40" t="n">
         <x:v>245</x:v>
       </x:c>
       <x:c r="B246" s="9" t="str">
-        <x:v>bmw-x6-rear-differential-bushing-2008</x:v>
+        <x:v>bmw-z3-hvac-blower-final-stage-resistor-failure</x:v>
       </x:c>
       <x:c r="C246" s="9" t="str">
-        <x:v>2008-2026 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D246" s="9" t="str">
-        <x:v>Rear Differential Bushing Deterioration</x:v>
+        <x:v>HVAC Blower Final Stage Resistor Failure (Fan Only Works on Max)</x:v>
       </x:c>
       <x:c r="E246" s="9" t="str">
-        <x:v>Replace all rear differential mount bushings. Use OEM or equivalent quality bushings (Lemforder is the OEM supplier). Inspect the differential housing for any damage from excessive movement. Perform subframe alignment check after bushing replacement.</x:v>
+        <x:v>Replace the blower final stage resistor (A/C cars: part under the scuttle/cowl; non-A/C cars: behind the passenger footwell panel). If a new resistor does not restore all speeds, test the blower motor itself, which may also be worn. Inspect for corrosion/water intrusion at the cowl on A/C cars.</x:v>
       </x:c>
       <x:c r="F246" s="9" t="n">
         <x:v>0</x:v>
@@ -11781,21 +13111,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="247" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="247" ht="1584" hidden="0" customHeight="1">
       <x:c r="A247" s="40" t="n">
         <x:v>246</x:v>
       </x:c>
       <x:c r="B247" s="9" t="str">
-        <x:v>bmw-x6-transfer-case-2008</x:v>
+        <x:v>bmw-z3-rear-subframe-crack-1996</x:v>
       </x:c>
       <x:c r="C247" s="9" t="str">
-        <x:v>2008-2023 | BMW | X6</x:v>
+        <x:v>1996-2002 | BMW | Z3</x:v>
       </x:c>
       <x:c r="D247" s="9" t="str">
-        <x:v>Transfer Case Actuator Motor Failure (All xDrive Models)</x:v>
+        <x:v>Rear Subframe Mounting Point Cracking</x:v>
       </x:c>
       <x:c r="E247" s="9" t="str">
-        <x:v>Replace the actuator motor assembly or rebuild using an aftermarket gear repair kit ($100-150). G06 actuator motor 27609469023 ($400-600) for complete replacement. DIY gear repair kits are straightforward and save $1,200+ over dealer replacement. Complete transfer case replacement if internal damage occurred: $1,400-3,300. PREVENTIVE: If buying used X6 over 80k miles, budget for this repair and listen for clicking noise when shutting off ignition.</x:v>
+        <x:v>Inspect the trunk floor, differential mount area, and all rear subframe mounting points from above and below the car for spot-weld separation, torn sheet metal, and cracked seams; a dye penetrant test or removing trunk trim/seam sealer may be needed to reveal early damage. If cracking is present, the proper repair is to drop the rear axle carrier/subframe, weld and reinforce the damaged unibody mounting points and trunk floor with a reinforcement kit (commonly Randy Forbes-style dual-ear/differential mount reinforcement or equivalent), then reinstall with new subframe bushings, differential mount bushings, and perform a 4-wheel alignment. Minor early cracks may be repairable before major deformation, but advanced damage often requires fabrication and extensive welding by a chassis/body specialist; typical cost ranges from about $2,000-$3,500 for early reinforcement repairs and can exceed $4,000-$6,000 if the floor is torn or multiple mounting points are damaged.</x:v>
       </x:c>
       <x:c r="F247" s="9" t="n">
         <x:v>0</x:v>
@@ -11804,22 +13134,20 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="248" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="248" ht="66" hidden="0" customHeight="1">
       <x:c r="A248" s="40" t="n">
         <x:v>247</x:v>
       </x:c>
       <x:c r="B248" s="9" t="str">
-        <x:v>bmw-x6m-front-thrust-arm-bushing-2015</x:v>
+        <x:v>bmw-z3-rear-subframe-cracking-1996</x:v>
       </x:c>
       <x:c r="C248" s="9" t="str">
-        <x:v>2015-2025 | BMW | X6 M</x:v>
+        <x:v>1996-2002 | BMW | Z3 | M52, M54</x:v>
       </x:c>
       <x:c r="D248" s="9" t="str">
-        <x:v>Front Thrust Arm Bushing (Tension Strut) Premature Wear</x:v>
-      </x:c>
-      <x:c r="E248" s="9" t="str">
-        <x:v>Replace both front thrust arms as complete assemblies (the bushings are not serviceable separately). Use genuine BMW M-spec parts or Lemforder equivalents. Perform a 4-wheel alignment immediately after replacement. Upgrade to Powerflex polyurethane thrust arm bushings for extended lifespan, especially on tracked cars.</x:v>
-      </x:c>
+        <x:v>Rear Subframe Mounting Point Cracks</x:v>
+      </x:c>
+      <x:c r="E248" s="9" t="str"/>
       <x:c r="F248" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -11827,21 +13155,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="249" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="249" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A249" s="40" t="n">
         <x:v>248</x:v>
       </x:c>
       <x:c r="B249" s="9" t="str">
-        <x:v>bmw-x6m-s63-rod-bearing-2010</x:v>
+        <x:v>bmw-z3-valve-cover-gasket-oil-leak</x:v>
       </x:c>
       <x:c r="C249" s="9" t="str">
-        <x:v>2010-2023 | BMW | X6 M | M50i, xDrive50i | S63</x:v>
+        <x:v>1997-2002 | BMW | Z3 | 2.3, 2.5i, 2.8, 3.0i | M52 2.8, M52TU 2.5/2.8, M54 2.5/3.0</x:v>
       </x:c>
       <x:c r="D249" s="9" t="str">
-        <x:v>S63 Rod Bearing Failure (X6 M)</x:v>
+        <x:v>Valve Cover Gasket Oil Leak (M52/M54 6-Cylinder)</x:v>
       </x:c>
       <x:c r="E249" s="9" t="str">
-        <x:v>PREVENTIVE: Replace rod bearings every 60,000-80,000 miles ($2,500-5,000 labor-intensive job). Use ACL Race 8B1578HX-STD ($150-250) or King CR8049SV ($120-200) upgraded bearings - these are stronger than OEM and provide better durability under high loads. Send oil samples for analysis (Blackstone Labs ~$30) every 5,000 miles to monitor bearing wear metals. If bearings have already failed: engine replacement required ($15,000-30,000). DO NOT buy used X6 M without documented bearing replacement history or fresh oil analysis.</x:v>
+        <x:v>Replace the valve cover gasket, the spark-plug-well/grommet seals, and the cover bolt seals. On M54 engines also clean oil from the plug wells and replace any oil-contaminated coil boots/coils. Use the correct torque sequence to avoid re-leaking. Inspect the cover for warping or cracks while it is off.</x:v>
       </x:c>
       <x:c r="F249" s="9" t="n">
         <x:v>0</x:v>
@@ -11850,21 +13178,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="250" ht="277.20001220703125" hidden="0" customHeight="1">
+    <x:row r="250" ht="1293.5999755859375" hidden="0" customHeight="1">
       <x:c r="A250" s="40" t="n">
         <x:v>249</x:v>
       </x:c>
       <x:c r="B250" s="9" t="str">
-        <x:v>bmw-x6m-vanos-solenoid-2015</x:v>
+        <x:v>bmw-z3-vanos-seals-1999</x:v>
       </x:c>
       <x:c r="C250" s="9" t="str">
-        <x:v>2015-2021 | BMW | X6 M | S63</x:v>
+        <x:v>1999-2002 | BMW | Z3 | M52, M54, S52</x:v>
       </x:c>
       <x:c r="D250" s="9" t="str">
-        <x:v>VANOS Solenoid Oil Sludge Buildup</x:v>
+        <x:v>VANOS Seal Failure (M52/M54/S52)</x:v>
       </x:c>
       <x:c r="E250" s="9" t="str">
-        <x:v>Remove and clean or replace the VANOS solenoids. Perform an engine oil flush. Strictly follow 7,500-mile oil change intervals with BMW LL-01 rated 0W-40 synthetic oil.</x:v>
+        <x:v>Confirm the fault by checking for cold-start VANOS rattle, rough idle, hesitation, and scanning for cam timing or mixture-related fault codes; on M52TU/M54/S52 engines, inspect VANOS operation and rule out vacuum leaks before disassembly. Repair typically involves removing the valve cover and VANOS unit, replacing the internal piston seals/O-rings with updated Viton/Teflon seals, renewing the valve cover gasket and VANOS oil line sealing washers, and then re-timing the cams to BMW specifications if required. If the unit still rattles after resealing, the VANOS bearing/anti-rattle components or the complete VANOS assembly may need replacement. Typical cost is about $60-$150 in seals/gaskets for DIY repair, $300-$700 for an independent shop reseal, or $800-$1,500+ if a rebuilt/replacement VANOS unit is installed.</x:v>
       </x:c>
       <x:c r="F250" s="9" t="n">
         <x:v>0</x:v>
@@ -11873,21 +13201,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="251" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="251" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A251" s="40" t="n">
         <x:v>250</x:v>
       </x:c>
       <x:c r="B251" s="9" t="str">
-        <x:v>bmw-x7-48v-battery-2020</x:v>
+        <x:v>bmw-z4-b58-coolant-tank-2019</x:v>
       </x:c>
       <x:c r="C251" s="9" t="str">
-        <x:v>2020-2023 | BMW | X7</x:v>
+        <x:v>2019-2026 | BMW | Z4 | B58</x:v>
       </x:c>
       <x:c r="D251" s="9" t="str">
-        <x:v>48V Mild Hybrid Battery Issues</x:v>
+        <x:v>B58 Coolant Expansion Tank Cracking</x:v>
       </x:c>
       <x:c r="E251" s="9" t="str">
-        <x:v>Replace the 48V mild hybrid battery ($1,000-2,000 at dealer). Requires dealer-level diagnostic tools and coding after installation - this is NOT a DIY repair. The 48V battery is separate from the main 12V battery. No aftermarket alternatives currently available. Check if vehicle is still under BMW warranty or extended warranty coverage. Some owners choose to live with the failed auto start-stop rather than pay for replacement.</x:v>
+        <x:v>Replace the coolant expansion tank with an updated BMW part or aftermarket aluminum tank. Inspect the tank and cap regularly for signs of cracking, discoloration, or seepage. When replacing, also replace the cap and check all coolant hoses for brittleness. Flush and refill with BMW-approved coolant.</x:v>
       </x:c>
       <x:c r="F251" s="9" t="n">
         <x:v>0</x:v>
@@ -11896,21 +13224,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="252" ht="726" hidden="0" customHeight="1">
+    <x:row r="252" ht="1306.800048828125" hidden="0" customHeight="1">
       <x:c r="A252" s="40" t="n">
         <x:v>251</x:v>
       </x:c>
       <x:c r="B252" s="9" t="str">
-        <x:v>bmw-x7-air-suspension-2019</x:v>
+        <x:v>bmw-z4-e85-convertible-top-hydraulic-2003</x:v>
       </x:c>
       <x:c r="C252" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>2003-2008 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D252" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Strut Failure (Standard Equipment)</x:v>
+        <x:v>Convertible Top Hydraulic Pump Motor Failure - E85 Z4</x:v>
       </x:c>
       <x:c r="E252" s="9" t="str">
-        <x:v>Replace failed air struts and/or compressor. Front strut left 37106869035 ($1,500-2,000), right 37106869036 ($1,500-2,000), rear 37106869039 ($1,000-1,500). Compressor 37206861882 ($800-1,200). RebuildMasterTech rebuilt struts ($600-900 each) are a more affordable alternative. Total repair can reach $2,180-5,000+ depending on which components have failed. Replace both struts on same axle simultaneously. Inspect at 50,000 miles for early signs of leaking.</x:v>
+        <x:v>Replace hydraulic pump motor assembly (BMW 54347193448 / supersedes 54347119633). OEM Genuine BMW pump: $800-$1,200. Aftermarket alternatives available on Amazon for $150-$300 but quality varies significantly. Dealer labor is $1,500-$2,500+ as BMW procedure requires full top removal. ZRoadster.org members have documented a motor relocation to the boot/trunk area which allows much easier future access. Hydraulic fluid: use Aral Vitamol ZHM or BMW 54340394395 hydraulic oil. PREVENTION: Clean drain holes annually, ensure rubber bungs are properly seated, and check for water intrusion in pump area at every service. Some owners have had success with pump motor rebuilds from roofmotors.co.uk ($300-$500) but quality of rebuilds varies.</x:v>
       </x:c>
       <x:c r="F252" s="9" t="n">
         <x:v>0</x:v>
@@ -11919,21 +13247,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="253" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="253" ht="1135.199951171875" hidden="0" customHeight="1">
       <x:c r="A253" s="40" t="n">
         <x:v>252</x:v>
       </x:c>
       <x:c r="B253" s="9" t="str">
-        <x:v>bmw-x7-air-suspension-compressor-2019</x:v>
+        <x:v>bmw-z4-e85-window-regulator-2003</x:v>
       </x:c>
       <x:c r="C253" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7</x:v>
+        <x:v>2003-2008 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D253" s="9" t="str">
-        <x:v>Air Suspension Compressor Failure</x:v>
+        <x:v>Power Window Regulator Failure - E85 Z4</x:v>
       </x:c>
       <x:c r="E253" s="9" t="str">
-        <x:v>Replace the air suspension compressor. Inspect all four air springs for leaks using soapy water solution. Replace any leaking air springs to prevent repeated compressor failure. Check the valve block for proper operation. The compressor is located under the rear of the vehicle.</x:v>
+        <x:v>Option 1 (Budget): Window regulator repair kit - replacement cables and rollers for ~$18-$25 from eBay/Amazon (BWR974 for left/driver side). Requires removing door panel and threading new cables through existing regulator frame. DIY-friendly with Z4-forum.com guides. Option 2 (Recommended): Full window regulator replacement. Driver side: BMW 51337198909 ($180-$280 OEM, $80-$150 aftermarket). Passenger side: BMW 51337198910 ($180-$280 OEM, $80-$150 aftermarket). Labor: $200-$400 at independent shop, $500-$700+ at dealer. DIY: 2-3 hours with door panel removal guide from Pelican Parts. ZRoadster.org recommends full replacement over repair kit for long-term reliability.</x:v>
       </x:c>
       <x:c r="F253" s="9" t="n">
         <x:v>0</x:v>
@@ -11942,21 +13270,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="254" ht="871.2000122070312" hidden="0" customHeight="1">
+    <x:row r="254" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A254" s="40" t="n">
         <x:v>253</x:v>
       </x:c>
       <x:c r="B254" s="9" t="str">
-        <x:v>bmw-x7-b58-coolant-2019</x:v>
+        <x:v>bmw-z4-electric-steering-rack-2003</x:v>
       </x:c>
       <x:c r="C254" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7 | xDrive40i | B58</x:v>
+        <x:v>2012-2012 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D254" s="9" t="str">
-        <x:v>B58 Coolant System Failures (xDrive40i)</x:v>
+        <x:v>2012 Z4 Electric Power-Steering Recall 12V-302</x:v>
       </x:c>
       <x:c r="E254" s="9" t="str">
-        <x:v>Replace failed coolant system components. Water pump 11518482250 ($300-400). Thermostat 11537644811 ($150-250). Replace expansion tank and all plastic coolant connections when performing repair to prevent cascading failures. For 2023+ models, check VIN for recall 24V-608 coverage for coolant pump connector. Total repair $500-2,500 depending on extent of damage. PREVENTIVE: Replace thermostat and water pump at 60,000-70,000 miles before failure. Inspect coolant hoses and connections at every oil change after 50k miles.</x:v>
+        <x:v>Check the VIN for an open 12V-302 campaign. If open, an authorized BMW dealer replaces the steering-assistance module free of charge. If the steering warning and audible alert occur, maintain control, reduce speed, stop safely and arrange dealer or roadside assistance; do not replace a steering rack from this card.</x:v>
       </x:c>
       <x:c r="F254" s="9" t="n">
         <x:v>0</x:v>
@@ -11965,21 +13293,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="255" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="255" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A255" s="40" t="n">
         <x:v>254</x:v>
       </x:c>
       <x:c r="B255" s="9" t="str">
-        <x:v>bmw-x7-b58-coolant-expansion-tank-2019</x:v>
+        <x:v>bmw-z4-electric-water-pump-2006</x:v>
       </x:c>
       <x:c r="C255" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7 | B58</x:v>
+        <x:v>2012-2016 | BMW | Z4 | N20</x:v>
       </x:c>
       <x:c r="D255" s="9" t="str">
-        <x:v>B58 Coolant Expansion Tank Crack</x:v>
+        <x:v>2012-2016 Z4 sDrive28i Water-Pump Connector Recall 24V-608</x:v>
       </x:c>
       <x:c r="E255" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with an updated BMW part that uses improved plastic composition. Also replace the cap and inspect all coolant hoses. Flush and refill the cooling system with BMW-approved coolant. Check for coolant contamination from the old tank.</x:v>
+        <x:v>Check the VIN for an open 24V-608 campaign. If open, an authorized BMW dealer inspects the water pump and connector, replaces them if necessary, and installs the protective shield free of charge. If smoke appears from the engine compartment, stop safely, switch off the vehicle, have occupants exit, move away from traffic and call emergency or roadside assistance; do not order a pump from this card.</x:v>
       </x:c>
       <x:c r="F255" s="9" t="n">
         <x:v>0</x:v>
@@ -11988,44 +13316,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="256" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="256" ht="1359.5999755859375" hidden="0" customHeight="1">
       <x:c r="A256" s="40" t="n">
         <x:v>255</x:v>
       </x:c>
       <x:c r="B256" s="9" t="str">
-        <x:v>bmw-x7-ibs-brake-recall-2023</x:v>
+        <x:v>bmw-z4-g29-b58-water-pump-2019</x:v>
       </x:c>
       <x:c r="C256" s="9" t="str">
-        <x:v>2023-2025 | BMW | X7</x:v>
+        <x:v>2019-2025 | BMW | Z4 | M40i, sDrive35i, sDrive35is | B48, B58</x:v>
       </x:c>
       <x:c r="D256" s="9" t="str">
-        <x:v>2023-2025 X7 Integrated Brake System Recall 26V-422</x:v>
+        <x:v>B48/B58 Electric Water Pump &amp; Thermostat Failure - G29 Z4</x:v>
       </x:c>
       <x:c r="E256" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; do not order brake electronics from this card.</x:v>
+        <x:v>Preventative replacement recommended at 60,000 miles. Always replace water pump and thermostat together - they share labor overlap and frequently fail concurrently. B48 sDrive30i: Water pump BMW 11518632586 ($300-$450), Thermostat BMW 11538685978 ($100-$150). B58 M40i: Water pump BMW 11518650986 ($350-$500), Thermostat BMW 11538685978 ($100-$150). Mishimoto offers performance water pump alternatives for B58 with improved impeller design. Replace 3 O-rings between thermostat and pump housing, plus 2 O-rings on coolant tube to head. Must replace water pump mounting bolts (torque-to-yield). Labor: 3-4 hours. FCP Euro lifetime warranty kits available. Also inspect plastic cylinder head coolant outlet adapter - known to shear off causing massive coolant leak.</x:v>
       </x:c>
       <x:c r="F256" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G256" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="257" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="257" ht="1122" hidden="0" customHeight="1">
       <x:c r="A257" s="40" t="n">
         <x:v>256</x:v>
       </x:c>
       <x:c r="B257" s="9" t="str">
-        <x:v>bmw-x7-n63-oil-consumption-2019</x:v>
+        <x:v>bmw-z4-n54-hpfp-2009</x:v>
       </x:c>
       <x:c r="C257" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7 | M50i, M60i, xDrive50i | N63TU3</x:v>
+        <x:v>2009-2011 | BMW | Z4 | M40i, sDrive35i, sDrive35is | N54</x:v>
       </x:c>
       <x:c r="D257" s="9" t="str">
-        <x:v>N63TU3 Oil Consumption &amp; Valve Stem Seal Degradation (xDrive50i/M50i/M60i)</x:v>
+        <x:v>N54 High Pressure Fuel Pump (HPFP) Failure - E89 Z4 sDrive35i/35is</x:v>
       </x:c>
       <x:c r="E257" s="9" t="str">
-        <x:v>Replace valve stem seals - extremely labor-intensive job requiring cylinder head work ($4,900-12,000 total). Elring seals 11340039494 for OEM spec. 5150 AutoSport Viton upgraded seals ($150-200) recommended for better heat resistance. AGA Tools kit includes specialized tools required. Reference TSB MC-10149960-9999 when visiting dealer. Check eligibility for class action settlement coverage. Some owners monitor oil levels and top off rather than repair. Use quality synthetic 0W-40 BMW LL-01 spec oil and check level every 500-1,000 miles.</x:v>
+        <x:v>Replace HPFP with latest revision Genuine BMW unit. The pump went through multiple revisions - ONLY install the latest version. Part number evolution: Original -&gt; 13517592881 (Index 10, TSB fix) -&gt; 13517616170 (latest revision, most reliable). Genuine BMW 13517616170 is the definitive fix ($350-$550 for pump). Replacement is straightforward DIY (1-2 hours) with basic tools. Also available as complete kit from FCP Euro with lifetime warranty. BMW extended warranty coverage to 10 years/120,000 miles under customer care package for original owners - check VIN eligibility. Replace low-pressure fuel sensor at same time (13537537319) as it may have been damaged by pressure fluctuations ($35-$55).</x:v>
       </x:c>
       <x:c r="F257" s="9" t="n">
         <x:v>0</x:v>
@@ -12034,21 +13362,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="258" ht="396" hidden="0" customHeight="1">
+    <x:row r="258" ht="580.7999877929688" hidden="0" customHeight="1">
       <x:c r="A258" s="40" t="n">
         <x:v>257</x:v>
       </x:c>
       <x:c r="B258" s="9" t="str">
-        <x:v>bmw-x7-panoramic-roof-rattle-2019</x:v>
+        <x:v>bmw-z4-n54-wastegate-rattle-2009</x:v>
       </x:c>
       <x:c r="C258" s="9" t="str">
-        <x:v>2019-2026 | BMW | X7</x:v>
+        <x:v>2009-2010 | BMW | Z4 | N54</x:v>
       </x:c>
       <x:c r="D258" s="9" t="str">
-        <x:v>Panoramic Sunroof Rattle and Creak</x:v>
+        <x:v>2009-2010 Z4 sDrive35i N54 Wastegate Diagnosis</x:v>
       </x:c>
       <x:c r="E258" s="9" t="str">
-        <x:v>Apply BMW-approved felt tape or lubricant to sunroof guide rails. Replace worn guide rail bushings. In severe cases, the sunroof cassette or seal may need replacement under warranty. BMW has issued updated guide rail components for early production vehicles.</x:v>
+        <x:v>Confirm the VIN, engine, production date, DME faults, boost-control data and noise source using current BMW diagnostic information. Check VIN-specific coverage history with BMW, recognizing that the bulletin's time/mileage window may have expired. Do not replace a turbocharger, actuator or wastegate from this card without the required diagnosis.</x:v>
       </x:c>
       <x:c r="F258" s="9" t="n">
         <x:v>0</x:v>
@@ -12057,21 +13385,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="259" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="259" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A259" s="40" t="n">
         <x:v>258</x:v>
       </x:c>
       <x:c r="B259" s="9" t="str">
-        <x:v>bmw-x7-sunroof-leak-2019</x:v>
+        <x:v>bmw-z4-soft-top-hydraulic-2003</x:v>
       </x:c>
       <x:c r="C259" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>2009-2016 | BMW | Z4</x:v>
       </x:c>
       <x:c r="D259" s="9" t="str">
-        <x:v>Panoramic Sunroof Water Leak</x:v>
+        <x:v>Retractable Hard Top Hydraulic Mechanism Failure</x:v>
       </x:c>
       <x:c r="E259" s="9" t="str">
-        <x:v>Clear clogged sunroof drain tubes ($100-300 at shop). Reference TSB SIB 54 11 19 when visiting dealer. For persistent leaks, drain tube connections or sunroof seal may need replacement ($500-1,500). If water has damaged interior electronics, repair costs can reach $3,000. PREVENTIVE: Clear sunroof drains annually, especially in areas with heavy tree debris. Run compressed air or flexible drain snake through drain tubes during oil changes. Keep sunroof track clean of debris.</x:v>
+        <x:v>Diagnose the leak location and replace the failed component. Common failure points are the main hydraulic cylinders (left and right), the hydraulic pump motor, and the flexible hoses. The hydraulic fluid should be flushed and replaced with BMW-approved CHF 11S fluid. A full system bleed is required after any repair.</x:v>
       </x:c>
       <x:c r="F259" s="9" t="n">
         <x:v>0</x:v>
@@ -12080,21 +13408,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="260" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="260" ht="1188" hidden="0" customHeight="1">
       <x:c r="A260" s="40" t="n">
         <x:v>259</x:v>
       </x:c>
       <x:c r="B260" s="9" t="str">
-        <x:v>bmw-x7-tire-wear-2019</x:v>
+        <x:v>bmw-z4-vanos-solenoid-2003</x:v>
       </x:c>
       <x:c r="C260" s="9" t="str">
-        <x:v>2019-2023 | BMW | X7</x:v>
+        <x:v>2003-2016 | BMW | Z4 | 2.5i, 3.0i, 3.0si, M40i, sDrive28i, sDrive30i, sDrive35i, sDrive35is | M54, N52, N54, N20</x:v>
       </x:c>
       <x:c r="D260" s="9" t="str">
-        <x:v>Premature Tire Wear (Especially 21"/22" Wheels)</x:v>
+        <x:v>VANOS Solenoid &amp; System Failure - E85/E89 Z4 (All Engines)</x:v>
       </x:c>
       <x:c r="E260" s="9" t="str">
-        <x:v>Have alignment adjusted to reduce aggressive camber settings ($200-400). Switch to quality tires designed for heavy SUVs: Michelin Pilot Sport 4S or Continental PremiumContact 6 are recommended. If possible, avoid 22" wheels and opt for 21" or smaller for better tire longevity and ride comfort. Alignment adjustment can extend tire life from 15,000 to 30,000+ miles. Total cost $200-2,000 depending on tire replacement needs. Check alignment every 10,000 miles.</x:v>
+        <x:v>Replace VANOS solenoids - inexpensive and straightforward repair. M54 (E85 2003-2005): 2 solenoids required, BMW 11361707323 ($35-$65 each). N52 (E85 2006-2008 / E89 2009-2011 28i): 2 solenoids, BMW 11367585425 ($40-$70 each). N54 (E89 35i/35is): 2 solenoids, BMW 11367585425 ($40-$70 each). N20 (E89 sDrive28i 2012-2016): 2 solenoids, BMW 11367585425 ($40-$70 each). Labor: under 1 hour for experienced mechanic, 2-3 hours DIY. Replace all solenoids at once even if only one has failed - the others are same age and will fail soon. Also replace VANOS solenoid O-rings and sealing plates during service. Clean VANOS system with Beisan Systems VANOS cleaning procedure for best results.</x:v>
       </x:c>
       <x:c r="F260" s="9" t="n">
         <x:v>0</x:v>
@@ -12103,597 +13431,26 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="261" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A261" s="40" t="n">
+    <x:row r="261" ht="554.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A261" s="42" t="n">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="B261" s="9" t="str">
-        <x:v>bmw-xm-airbag-passenger-knee-recall-2023</x:v>
-      </x:c>
-      <x:c r="C261" s="9" t="str">
-        <x:v>2023-2023 | BMW | XM</x:v>
-      </x:c>
-      <x:c r="D261" s="9" t="str">
-        <x:v>2023 XM Front-Passenger Knee-Airbag Recall 23V-622</x:v>
-      </x:c>
-      <x:c r="E261" s="9" t="str">
-        <x:v>Check the VIN for an open 23V-622 campaign. If open, an authorized BMW dealer replaces the front-passenger knee airbag free of charge. Do not attempt airbag diagnosis or order a clock spring or airbag module from this card; supplemental-restraint work requires trained personnel and VIN-selected parts.</x:v>
-      </x:c>
-      <x:c r="F261" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G261" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="262" ht="567.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A262" s="40" t="n">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="B262" s="9" t="str">
-        <x:v>bmw-xm-hybrid-drivetrain-hesitation-2023</x:v>
-      </x:c>
-      <x:c r="C262" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid, S68</x:v>
-      </x:c>
-      <x:c r="D262" s="9" t="str">
-        <x:v>Hybrid Drivetrain Hesitation and Power Delivery Lag</x:v>
-      </x:c>
-      <x:c r="E262" s="9" t="str">
-        <x:v>Visit the dealer for the latest transmission and hybrid system software calibration updates. Select Sport or Sport Plus mode for more consistent power delivery. The latest software revisions significantly improve the electric-to-V8 handoff smoothness. If hesitation persists after updates, the dealer can reset the transmission adaptation values to relearn driving patterns.</x:v>
-      </x:c>
-      <x:c r="F262" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G262" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="263" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A263" s="40" t="n">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="B263" s="9" t="str">
-        <x:v>bmw-xm-integrated-brake-system-recall-2023</x:v>
-      </x:c>
-      <x:c r="C263" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM</x:v>
-      </x:c>
-      <x:c r="D263" s="9" t="str">
-        <x:v>2023-2024 XM Integrated Brake System Recall 26V-422</x:v>
-      </x:c>
-      <x:c r="E263" s="9" t="str">
-        <x:v>Check the VIN at NHTSA and with an authorized BMW dealer when campaign 26V-422 VINs become searchable, and arrange the free dealer inspection and module replacement if required. If a brake warning appears or pedal effort increases, avoid abrupt braking, allow extra stopping distance, stop safely and contact BMW roadside assistance; wheel-speed sensors are not the recall remedy.</x:v>
-      </x:c>
-      <x:c r="F263" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G263" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="264" ht="646.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A264" s="40" t="n">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="B264" s="9" t="str">
-        <x:v>bmw-xm-suspension-ride-quality-2023</x:v>
-      </x:c>
-      <x:c r="C264" s="9" t="str">
-        <x:v>2023-2024 | BMW | XM | S68 4.4L Twin-Turbo V8 Hybrid</x:v>
-      </x:c>
-      <x:c r="D264" s="9" t="str">
-        <x:v>Harsh Ride Quality and Suspension Stiffness</x:v>
-      </x:c>
-      <x:c r="E264" s="9" t="str">
-        <x:v>Check tire pressures regularly - overinflated tires significantly worsen the harsh ride. Some owners report improved comfort by switching to a tire with a taller sidewall profile (if available for the XM's wheel size). Use Comfort mode for daily driving. Unfortunately, no aftermarket spring or damper solution currently exists to significantly improve the ride without compromising the handling needed for the XM's weight.</x:v>
-      </x:c>
-      <x:c r="F264" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G264" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="265" ht="528" hidden="0" customHeight="1">
-      <x:c r="A265" s="40" t="n">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="B265" s="9" t="str">
-        <x:v>bmw-z3-convertible-top-rear-window-cracking-clouding-bead-separatio</x:v>
-      </x:c>
-      <x:c r="C265" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D265" s="9" t="str">
-        <x:v>Convertible Top Rear Window Cracking, Clouding, and Bead Separation</x:v>
-      </x:c>
-      <x:c r="E265" s="9" t="str">
-        <x:v>Replace the rear window panel only — BMW used a zipper system so the clouded/cracked window unzips and a new window zips/tapes in without disturbing the fabric top. Re-gluing separated bead trim rarely holds, so window replacement is the durable fix. Job is a DIY-feasible 1-1.5 hours; replace the whole top only if the fabric is also degraded.</x:v>
-      </x:c>
-      <x:c r="F265" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G265" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="266" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A266" s="40" t="n">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="B266" s="9" t="str">
-        <x:v>bmw-z3-cooling-system-failure-1996</x:v>
-      </x:c>
-      <x:c r="C266" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D266" s="9" t="str">
-        <x:v>Cooling System Component Failures</x:v>
-      </x:c>
-      <x:c r="E266" s="9" t="str"/>
-      <x:c r="F266" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G266" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="267" ht="448.79998779296875" hidden="0" customHeight="1">
-      <x:c r="A267" s="40" t="n">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="B267" s="9" t="str">
-        <x:v>bmw-z3-cracked-exhaust-manifold-1-9l-4-cylinder</x:v>
-      </x:c>
-      <x:c r="C267" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3 | 1.9, 1.9i, Z3 1.9 | 1.9L M44 4-cylinder, 1.9L M43TU 4-cylinder</x:v>
-      </x:c>
-      <x:c r="D267" s="9" t="str">
-        <x:v>Cracked Exhaust Manifold on 1.9L 4-Cylinder (M44/M43)</x:v>
-      </x:c>
-      <x:c r="E267" s="9" t="str">
-        <x:v>Inspect the manifold for hairline cracks (a cold-engine listen or smoke test confirms the leak). Replace the cracked manifold with a used OE unit or an aftermarket stainless tubular header, and renew the manifold gasket and hardware. Allow roughly 3-4 hours labor.</x:v>
-      </x:c>
-      <x:c r="F267" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G267" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="268" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A268" s="40" t="n">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="B268" s="9" t="str">
-        <x:v>bmw-z3-differential-mount-ear-trunk-floor-pan-tearing</x:v>
-      </x:c>
-      <x:c r="C268" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D268" s="9" t="str">
-        <x:v>Differential Mount Ear and Trunk Floor Pan Tearing</x:v>
-      </x:c>
-      <x:c r="E268" s="9" t="str">
-        <x:v>Inspect the trunk floor around the differential mount and rear subframe pickup points for cracks, torn metal, and broken spot welds. Repair requires welding and a reinforcement/re-fabrication plate kit to tie the diff mount/subframe back into the floor. Switching the diff carrier bushings to polyurethane reduces carrier movement and the stress that causes the tearing. Catching it early greatly limits the repair scope.</x:v>
-      </x:c>
-      <x:c r="F268" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G268" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="269" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A269" s="40" t="n">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="B269" s="9" t="str">
-        <x:v>bmw-z3-door-window-regulator-clip-mounting-tab-failure</x:v>
-      </x:c>
-      <x:c r="C269" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D269" s="9" t="str">
-        <x:v>Door Window Regulator Clip / Mounting Tab Failure</x:v>
-      </x:c>
-      <x:c r="E269" s="9" t="str">
-        <x:v>Replace the broken plastic regulator clips, or replace the regulator assembly if the cable or mechanism is also worn. If the welded mounting tab/anchor has torn from the door frame, it must be re-welded or reinforced before fitting a new regulator. Lubricate the window channels to reduce drag on the new parts.</x:v>
-      </x:c>
-      <x:c r="F269" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G269" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="270" ht="686.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A270" s="40" t="n">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="B270" s="9" t="str">
-        <x:v>bmw-z3-fuel-level-sender-failure-causing-erratic-dead-fuel-gauge</x:v>
-      </x:c>
-      <x:c r="C270" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D270" s="9" t="str">
-        <x:v>Fuel Level Sender Failure Causing Erratic or Dead Fuel Gauge</x:v>
-      </x:c>
-      <x:c r="E270" s="9" t="str">
-        <x:v>Remove the access panel behind the seats and inspect the sender. A dirty or lightly worn ceramic/resistor plate can sometimes be cleaned, but a cracked plate or worn brushes requires replacing the sender unit (or the complete fuel-pump/sender carrier assembly). Also check the tank vent valve, as tank vacuum can deform the float arm. Confirm wiring/ground integrity before condemning the sender.</x:v>
-      </x:c>
-      <x:c r="F270" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G270" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="271" ht="488.3999938964844" hidden="0" customHeight="1">
-      <x:c r="A271" s="40" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="B271" s="9" t="str">
-        <x:v>bmw-z3-hvac-blower-final-stage-resistor-failure</x:v>
-      </x:c>
-      <x:c r="C271" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D271" s="9" t="str">
-        <x:v>HVAC Blower Final Stage Resistor Failure (Fan Only Works on Max)</x:v>
-      </x:c>
-      <x:c r="E271" s="9" t="str">
-        <x:v>Replace the blower final stage resistor (A/C cars: part under the scuttle/cowl; non-A/C cars: behind the passenger footwell panel). If a new resistor does not restore all speeds, test the blower motor itself, which may also be worn. Inspect for corrosion/water intrusion at the cowl on A/C cars.</x:v>
-      </x:c>
-      <x:c r="F271" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G271" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="272" ht="1584" hidden="0" customHeight="1">
-      <x:c r="A272" s="40" t="n">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="B272" s="9" t="str">
-        <x:v>bmw-z3-rear-subframe-crack-1996</x:v>
-      </x:c>
-      <x:c r="C272" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3</x:v>
-      </x:c>
-      <x:c r="D272" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracking</x:v>
-      </x:c>
-      <x:c r="E272" s="9" t="str">
-        <x:v>Inspect the trunk floor, differential mount area, and all rear subframe mounting points from above and below the car for spot-weld separation, torn sheet metal, and cracked seams; a dye penetrant test or removing trunk trim/seam sealer may be needed to reveal early damage. If cracking is present, the proper repair is to drop the rear axle carrier/subframe, weld and reinforce the damaged unibody mounting points and trunk floor with a reinforcement kit (commonly Randy Forbes-style dual-ear/differential mount reinforcement or equivalent), then reinstall with new subframe bushings, differential mount bushings, and perform a 4-wheel alignment. Minor early cracks may be repairable before major deformation, but advanced damage often requires fabrication and extensive welding by a chassis/body specialist; typical cost ranges from about $2,000-$3,500 for early reinforcement repairs and can exceed $4,000-$6,000 if the floor is torn or multiple mounting points are damaged.</x:v>
-      </x:c>
-      <x:c r="F272" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G272" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="273" ht="66" hidden="0" customHeight="1">
-      <x:c r="A273" s="40" t="n">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="B273" s="9" t="str">
-        <x:v>bmw-z3-rear-subframe-cracking-1996</x:v>
-      </x:c>
-      <x:c r="C273" s="9" t="str">
-        <x:v>1996-2002 | BMW | Z3 | M52, M54</x:v>
-      </x:c>
-      <x:c r="D273" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracks</x:v>
-      </x:c>
-      <x:c r="E273" s="9" t="str"/>
-      <x:c r="F273" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G273" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="274" ht="475.20001220703125" hidden="0" customHeight="1">
-      <x:c r="A274" s="40" t="n">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="B274" s="9" t="str">
-        <x:v>bmw-z3-valve-cover-gasket-oil-leak</x:v>
-      </x:c>
-      <x:c r="C274" s="9" t="str">
-        <x:v>1997-2002 | BMW | Z3 | 2.3, 2.5i, 2.8, 3.0i | M52 2.8, M52TU 2.5/2.8, M54 2.5/3.0</x:v>
-      </x:c>
-      <x:c r="D274" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak (M52/M54 6-Cylinder)</x:v>
-      </x:c>
-      <x:c r="E274" s="9" t="str">
-        <x:v>Replace the valve cover gasket, the spark-plug-well/grommet seals, and the cover bolt seals. On M54 engines also clean oil from the plug wells and replace any oil-contaminated coil boots/coils. Use the correct torque sequence to avoid re-leaking. Inspect the cover for warping or cracks while it is off.</x:v>
-      </x:c>
-      <x:c r="F274" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G274" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="275" ht="1293.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A275" s="40" t="n">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="B275" s="9" t="str">
-        <x:v>bmw-z3-vanos-seals-1999</x:v>
-      </x:c>
-      <x:c r="C275" s="9" t="str">
-        <x:v>1999-2002 | BMW | Z3 | M52, M54, S52</x:v>
-      </x:c>
-      <x:c r="D275" s="9" t="str">
-        <x:v>VANOS Seal Failure (M52/M54/S52)</x:v>
-      </x:c>
-      <x:c r="E275" s="9" t="str">
-        <x:v>Confirm the fault by checking for cold-start VANOS rattle, rough idle, hesitation, and scanning for cam timing or mixture-related fault codes; on M52TU/M54/S52 engines, inspect VANOS operation and rule out vacuum leaks before disassembly. Repair typically involves removing the valve cover and VANOS unit, replacing the internal piston seals/O-rings with updated Viton/Teflon seals, renewing the valve cover gasket and VANOS oil line sealing washers, and then re-timing the cams to BMW specifications if required. If the unit still rattles after resealing, the VANOS bearing/anti-rattle components or the complete VANOS assembly may need replacement. Typical cost is about $60-$150 in seals/gaskets for DIY repair, $300-$700 for an independent shop reseal, or $800-$1,500+ if a rebuilt/replacement VANOS unit is installed.</x:v>
-      </x:c>
-      <x:c r="F275" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G275" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="276" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A276" s="40" t="n">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="B276" s="9" t="str">
-        <x:v>bmw-z4-b58-coolant-tank-2019</x:v>
-      </x:c>
-      <x:c r="C276" s="9" t="str">
-        <x:v>2019-2026 | BMW | Z4 | B58</x:v>
-      </x:c>
-      <x:c r="D276" s="9" t="str">
-        <x:v>B58 Coolant Expansion Tank Cracking</x:v>
-      </x:c>
-      <x:c r="E276" s="9" t="str">
-        <x:v>Replace the coolant expansion tank with an updated BMW part or aftermarket aluminum tank. Inspect the tank and cap regularly for signs of cracking, discoloration, or seepage. When replacing, also replace the cap and check all coolant hoses for brittleness. Flush and refill with BMW-approved coolant.</x:v>
-      </x:c>
-      <x:c r="F276" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G276" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="277" ht="1306.800048828125" hidden="0" customHeight="1">
-      <x:c r="A277" s="40" t="n">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="B277" s="9" t="str">
-        <x:v>bmw-z4-e85-convertible-top-hydraulic-2003</x:v>
-      </x:c>
-      <x:c r="C277" s="9" t="str">
-        <x:v>2003-2008 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D277" s="9" t="str">
-        <x:v>Convertible Top Hydraulic Pump Motor Failure - E85 Z4</x:v>
-      </x:c>
-      <x:c r="E277" s="9" t="str">
-        <x:v>Replace hydraulic pump motor assembly (BMW 54347193448 / supersedes 54347119633). OEM Genuine BMW pump: $800-$1,200. Aftermarket alternatives available on Amazon for $150-$300 but quality varies significantly. Dealer labor is $1,500-$2,500+ as BMW procedure requires full top removal. ZRoadster.org members have documented a motor relocation to the boot/trunk area which allows much easier future access. Hydraulic fluid: use Aral Vitamol ZHM or BMW 54340394395 hydraulic oil. PREVENTION: Clean drain holes annually, ensure rubber bungs are properly seated, and check for water intrusion in pump area at every service. Some owners have had success with pump motor rebuilds from roofmotors.co.uk ($300-$500) but quality of rebuilds varies.</x:v>
-      </x:c>
-      <x:c r="F277" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G277" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="278" ht="1135.199951171875" hidden="0" customHeight="1">
-      <x:c r="A278" s="40" t="n">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="B278" s="9" t="str">
-        <x:v>bmw-z4-e85-window-regulator-2003</x:v>
-      </x:c>
-      <x:c r="C278" s="9" t="str">
-        <x:v>2003-2008 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D278" s="9" t="str">
-        <x:v>Power Window Regulator Failure - E85 Z4</x:v>
-      </x:c>
-      <x:c r="E278" s="9" t="str">
-        <x:v>Option 1 (Budget): Window regulator repair kit - replacement cables and rollers for ~$18-$25 from eBay/Amazon (BWR974 for left/driver side). Requires removing door panel and threading new cables through existing regulator frame. DIY-friendly with Z4-forum.com guides. Option 2 (Recommended): Full window regulator replacement. Driver side: BMW 51337198909 ($180-$280 OEM, $80-$150 aftermarket). Passenger side: BMW 51337198910 ($180-$280 OEM, $80-$150 aftermarket). Labor: $200-$400 at independent shop, $500-$700+ at dealer. DIY: 2-3 hours with door panel removal guide from Pelican Parts. ZRoadster.org recommends full replacement over repair kit for long-term reliability.</x:v>
-      </x:c>
-      <x:c r="F278" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G278" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="279" ht="514.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A279" s="40" t="n">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="B279" s="9" t="str">
-        <x:v>bmw-z4-electric-steering-rack-2003</x:v>
-      </x:c>
-      <x:c r="C279" s="9" t="str">
-        <x:v>2012-2012 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D279" s="9" t="str">
-        <x:v>2012 Z4 Electric Power-Steering Recall 12V-302</x:v>
-      </x:c>
-      <x:c r="E279" s="9" t="str">
-        <x:v>Check the VIN for an open 12V-302 campaign. If open, an authorized BMW dealer replaces the steering-assistance module free of charge. If the steering warning and audible alert occur, maintain control, reduce speed, stop safely and arrange dealer or roadside assistance; do not replace a steering rack from this card.</x:v>
-      </x:c>
-      <x:c r="F279" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G279" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="280" ht="633.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A280" s="40" t="n">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="B280" s="9" t="str">
-        <x:v>bmw-z4-electric-water-pump-2006</x:v>
-      </x:c>
-      <x:c r="C280" s="9" t="str">
-        <x:v>2012-2016 | BMW | Z4 | N20</x:v>
-      </x:c>
-      <x:c r="D280" s="9" t="str">
-        <x:v>2012-2016 Z4 sDrive28i Water-Pump Connector Recall 24V-608</x:v>
-      </x:c>
-      <x:c r="E280" s="9" t="str">
-        <x:v>Check the VIN for an open 24V-608 campaign. If open, an authorized BMW dealer inspects the water pump and connector, replaces them if necessary, and installs the protective shield free of charge. If smoke appears from the engine compartment, stop safely, switch off the vehicle, have occupants exit, move away from traffic and call emergency or roadside assistance; do not order a pump from this card.</x:v>
-      </x:c>
-      <x:c r="F280" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G280" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="281" ht="1359.5999755859375" hidden="0" customHeight="1">
-      <x:c r="A281" s="40" t="n">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="B281" s="9" t="str">
-        <x:v>bmw-z4-g29-b58-water-pump-2019</x:v>
-      </x:c>
-      <x:c r="C281" s="9" t="str">
-        <x:v>2019-2025 | BMW | Z4 | M40i, sDrive35i, sDrive35is | B48, B58</x:v>
-      </x:c>
-      <x:c r="D281" s="9" t="str">
-        <x:v>B48/B58 Electric Water Pump &amp; Thermostat Failure - G29 Z4</x:v>
-      </x:c>
-      <x:c r="E281" s="9" t="str">
-        <x:v>Preventative replacement recommended at 60,000 miles. Always replace water pump and thermostat together - they share labor overlap and frequently fail concurrently. B48 sDrive30i: Water pump BMW 11518632586 ($300-$450), Thermostat BMW 11538685978 ($100-$150). B58 M40i: Water pump BMW 11518650986 ($350-$500), Thermostat BMW 11538685978 ($100-$150). Mishimoto offers performance water pump alternatives for B58 with improved impeller design. Replace 3 O-rings between thermostat and pump housing, plus 2 O-rings on coolant tube to head. Must replace water pump mounting bolts (torque-to-yield). Labor: 3-4 hours. FCP Euro lifetime warranty kits available. Also inspect plastic cylinder head coolant outlet adapter - known to shear off causing massive coolant leak.</x:v>
-      </x:c>
-      <x:c r="F281" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G281" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="282" ht="1122" hidden="0" customHeight="1">
-      <x:c r="A282" s="40" t="n">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="B282" s="9" t="str">
-        <x:v>bmw-z4-n54-hpfp-2009</x:v>
-      </x:c>
-      <x:c r="C282" s="9" t="str">
-        <x:v>2009-2011 | BMW | Z4 | M40i, sDrive35i, sDrive35is | N54</x:v>
-      </x:c>
-      <x:c r="D282" s="9" t="str">
-        <x:v>N54 High Pressure Fuel Pump (HPFP) Failure - E89 Z4 sDrive35i/35is</x:v>
-      </x:c>
-      <x:c r="E282" s="9" t="str">
-        <x:v>Replace HPFP with latest revision Genuine BMW unit. The pump went through multiple revisions - ONLY install the latest version. Part number evolution: Original -&gt; 13517592881 (Index 10, TSB fix) -&gt; 13517616170 (latest revision, most reliable). Genuine BMW 13517616170 is the definitive fix ($350-$550 for pump). Replacement is straightforward DIY (1-2 hours) with basic tools. Also available as complete kit from FCP Euro with lifetime warranty. BMW extended warranty coverage to 10 years/120,000 miles under customer care package for original owners - check VIN eligibility. Replace low-pressure fuel sensor at same time (13537537319) as it may have been damaged by pressure fluctuations ($35-$55).</x:v>
-      </x:c>
-      <x:c r="F282" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G282" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="283" ht="580.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A283" s="40" t="n">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="B283" s="9" t="str">
-        <x:v>bmw-z4-n54-wastegate-rattle-2009</x:v>
-      </x:c>
-      <x:c r="C283" s="9" t="str">
-        <x:v>2009-2010 | BMW | Z4 | N54</x:v>
-      </x:c>
-      <x:c r="D283" s="9" t="str">
-        <x:v>2009-2010 Z4 sDrive35i N54 Wastegate Diagnosis</x:v>
-      </x:c>
-      <x:c r="E283" s="9" t="str">
-        <x:v>Confirm the VIN, engine, production date, DME faults, boost-control data and noise source using current BMW diagnostic information. Check VIN-specific coverage history with BMW, recognizing that the bulletin's time/mileage window may have expired. Do not replace a turbocharger, actuator or wastegate from this card without the required diagnosis.</x:v>
-      </x:c>
-      <x:c r="F283" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G283" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="284" ht="501.6000061035156" hidden="0" customHeight="1">
-      <x:c r="A284" s="40" t="n">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="B284" s="9" t="str">
-        <x:v>bmw-z4-soft-top-hydraulic-2003</x:v>
-      </x:c>
-      <x:c r="C284" s="9" t="str">
-        <x:v>2009-2016 | BMW | Z4</x:v>
-      </x:c>
-      <x:c r="D284" s="9" t="str">
-        <x:v>Retractable Hard Top Hydraulic Mechanism Failure</x:v>
-      </x:c>
-      <x:c r="E284" s="9" t="str">
-        <x:v>Diagnose the leak location and replace the failed component. Common failure points are the main hydraulic cylinders (left and right), the hydraulic pump motor, and the flexible hoses. The hydraulic fluid should be flushed and replaced with BMW-approved CHF 11S fluid. A full system bleed is required after any repair.</x:v>
-      </x:c>
-      <x:c r="F284" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G284" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="285" ht="1188" hidden="0" customHeight="1">
-      <x:c r="A285" s="40" t="n">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="B285" s="9" t="str">
-        <x:v>bmw-z4-vanos-solenoid-2003</x:v>
-      </x:c>
-      <x:c r="C285" s="9" t="str">
-        <x:v>2003-2016 | BMW | Z4 | 2.5i, 3.0i, 3.0si, M40i, sDrive28i, sDrive30i, sDrive35i, sDrive35is | M54, N52, N54, N20</x:v>
-      </x:c>
-      <x:c r="D285" s="9" t="str">
-        <x:v>VANOS Solenoid &amp; System Failure - E85/E89 Z4 (All Engines)</x:v>
-      </x:c>
-      <x:c r="E285" s="9" t="str">
-        <x:v>Replace VANOS solenoids - inexpensive and straightforward repair. M54 (E85 2003-2005): 2 solenoids required, BMW 11361707323 ($35-$65 each). N52 (E85 2006-2008 / E89 2009-2011 28i): 2 solenoids, BMW 11367585425 ($40-$70 each). N54 (E89 35i/35is): 2 solenoids, BMW 11367585425 ($40-$70 each). N20 (E89 sDrive28i 2012-2016): 2 solenoids, BMW 11367585425 ($40-$70 each). Labor: under 1 hour for experienced mechanic, 2-3 hours DIY. Replace all solenoids at once even if only one has failed - the others are same age and will fail soon. Also replace VANOS solenoid O-rings and sealing plates during service. Clean VANOS system with Beisan Systems VANOS cleaning procedure for best results.</x:v>
-      </x:c>
-      <x:c r="F285" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G285" s="41" t="str">
-        <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="286" ht="554.4000244140625" hidden="0" customHeight="1">
-      <x:c r="A286" s="42" t="n">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="B286" s="43" t="str">
+      <x:c r="B261" s="43" t="str">
         <x:v>bmw-z8-soft-top-mechanism-2000</x:v>
       </x:c>
-      <x:c r="C286" s="43" t="str">
+      <x:c r="C261" s="43" t="str">
         <x:v>2000-2003 | BMW | Z8</x:v>
       </x:c>
-      <x:c r="D286" s="43" t="str">
+      <x:c r="D261" s="43" t="str">
         <x:v>Power Soft Top Hydraulic System and Cable Failure</x:v>
       </x:c>
-      <x:c r="E286" s="43" t="str">
+      <x:c r="E261" s="43" t="str">
         <x:v>Rebuild the hydraulic cylinders with new seals rather than replacing ($200 vs $2,000+). Inspect and replace frayed cables. Adjust or replace the microswitch sensors at the windshield header latch. Lubricate the top mechanism pivot points with silicone grease annually. Store the car with the top up to reduce stress on the hydraulic system.</x:v>
       </x:c>
-      <x:c r="F286" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G286" s="44" t="str">
+      <x:c r="F261" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G261" s="44" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>

--- a/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
+++ b/outputs/bmw-repair-first-review/BMW-repair-first-fitment-review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2c17cda81a7d4bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="R0d753f5f65c04068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R36276f2dc1604ce6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R1ec443a6e9e64a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3195f58598d54c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMW Review" sheetId="2" r:id="R37e582cc9c904a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining Queue" sheetId="3" r:id="R6e18b9228123445b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" r:id="R99a4665312094945"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,7 +484,7 @@
         <x:v>Reviewed in this batch</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>125</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C5" s="11"/>
       <x:c r="D5" s="11"/>
@@ -498,7 +498,7 @@
         <x:v>Remaining queue</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>260</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C6" s="11"/>
       <x:c r="D6" s="11"/>
@@ -512,7 +512,7 @@
         <x:v>Issues with destinations</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>122</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C7" s="11"/>
       <x:c r="D7" s="11"/>
@@ -526,7 +526,7 @@
         <x:v>Destination entries</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>182</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C8" s="11"/>
       <x:c r="D8" s="11"/>
@@ -540,7 +540,7 @@
         <x:v>Distinct URLs</x:v>
       </x:c>
       <x:c r="B9" s="13" t="n">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C9" s="11"/>
       <x:c r="D9" s="11"/>
@@ -7396,45 +7396,1247 @@
       </x:c>
     </x:row>
     <x:row r="186" ht="778.7999877929688" hidden="0" customHeight="1">
-      <x:c r="A186" s="42" t="n">
+      <x:c r="A186" s="40" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B186" s="43" t="str">
+      <x:c r="B186" s="9" t="str">
         <x:v>bmw-i7-ota-update-failures-2025</x:v>
       </x:c>
-      <x:c r="C186" s="43" t="str">
+      <x:c r="C186" s="9" t="str">
         <x:v>2023-2024 | BMW | i7</x:v>
       </x:c>
-      <x:c r="D186" s="43" t="str">
+      <x:c r="D186" s="9" t="str">
         <x:v>G70 i7 Comfort-Access Faults after Remote Upgrade</x:v>
       </x:c>
-      <x:c r="E186" s="43" t="str">
+      <x:c r="E186" s="9" t="str">
         <x:v>Confirm that the complaint followed a BMW Remote Software Upgrade and read the exact BCP faults. Follow SIB 61 11 24 in ISTA to program and pair all FBD5/FBD5s remote-control receivers, clear faults and verify Comfort Access and Passive Go/Exit. Keep phones disconnected during receiver programming. BMW states that parts replacement will not solve this path. ShowMeTheParts resolves the exact 2023 i7 but has no software or receiver repair candidate, so all marketplace links are removed.</x:v>
       </x:c>
-      <x:c r="F186" s="43" t="str">
+      <x:c r="F186" s="9" t="str">
         <x:v>Confirm complaint followed Remote Software Upgrade; read BCP faults; ISTA programming/pairing of all FBD5/FBD5s receivers; verify Comfort Access and Passive Go/Exit</x:v>
       </x:c>
-      <x:c r="G186" s="43" t="str">
+      <x:c r="G186" s="9" t="str">
         <x:v>SOFTWARE/PAIRING SERVICE / NO RECEIVER PART</x:v>
       </x:c>
-      <x:c r="H186" s="43" t="str">
+      <x:c r="H186" s="9" t="str">
         <x:v>BMW dealer locator</x:v>
       </x:c>
-      <x:c r="I186" s="43" t="str">
+      <x:c r="I186" s="9" t="str">
         <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
       </x:c>
-      <x:c r="J186" s="43" t="str">
+      <x:c r="J186" s="9" t="str">
         <x:v>2023-2024 G70 i7 SIB 61 11 24 programming and receiver pairing</x:v>
       </x:c>
-      <x:c r="K186" s="43" t="str">
+      <x:c r="K186" s="9" t="str">
         <x:v>programming service</x:v>
       </x:c>
-      <x:c r="L186" s="43" t="str"/>
-      <x:c r="M186" s="43" t="str">
+      <x:c r="L186" s="9" t="str"/>
+      <x:c r="M186" s="9" t="str">
         <x:v>The source reports no software/receiver catalog candidate and states that parts replacement will not solve this path.</x:v>
       </x:c>
-      <x:c r="N186" s="44" t="str">
+      <x:c r="N186" s="41" t="str">
         <x:v>Rename this to Comfort Access faults after Remote Upgrade and do not link receivers or scanners.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="528" hidden="0" customHeight="1">
+      <x:c r="A187" s="40" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B187" s="9" t="str">
+        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
+      </x:c>
+      <x:c r="C187" s="9" t="str">
+        <x:v>2015-2020 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D187" s="9" t="str">
+        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
+      </x:c>
+      <x:c r="E187" s="9" t="str">
+        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
+      </x:c>
+      <x:c r="F187" s="9" t="str">
+        <x:v>ISTA Energy Diagnosis; verify CCM 415 and I-level; conditional whole-vehicle programming</x:v>
+      </x:c>
+      <x:c r="G187" s="9" t="str">
+        <x:v>BULLETIN DIAGNOSIS/PROGRAMMING SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H187" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I187" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J187" s="9" t="str">
+        <x:v>2015-2020 i8 CCM 415 energy diagnosis and conditional I-level programming</x:v>
+      </x:c>
+      <x:c r="K187" s="9" t="str">
+        <x:v>ISTA diagnosis/programming service</x:v>
+      </x:c>
+      <x:c r="L187" s="9" t="str"/>
+      <x:c r="M187" s="9" t="str">
+        <x:v>The source explicitly forbids a controller, generic maintainer, or scan-tool purchase; programming applies only when both bulletin conditions are met.</x:v>
+      </x:c>
+      <x:c r="N187" s="41" t="str">
+        <x:v>Keep the title and destination tied to CCM 415 sleep delay rather than generic battery drain.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="1042.800048828125" hidden="0" customHeight="1">
+      <x:c r="A188" s="40" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B188" s="9" t="str">
+        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
+      </x:c>
+      <x:c r="C188" s="9" t="str">
+        <x:v>2014-2020 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D188" s="9" t="str">
+        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
+      </x:c>
+      <x:c r="E188" s="9" t="str">
+        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
+      </x:c>
+      <x:c r="F188" s="9" t="str">
+        <x:v>VIN-specified AGM battery; reconnect safety wire; battery registration; HV restart/sleep-current/charging diagnosis</x:v>
+      </x:c>
+      <x:c r="G188" s="9" t="str">
+        <x:v>VIN/DIAGNOSIS SERVICE / BATTERY HELD</x:v>
+      </x:c>
+      <x:c r="H188" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I188" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J188" s="9" t="str">
+        <x:v>2014-2020 i8 battery registration, HV restart and charging-system diagnosis</x:v>
+      </x:c>
+      <x:c r="K188" s="9" t="str">
+        <x:v>hybrid-qualified service</x:v>
+      </x:c>
+      <x:c r="L188" s="9" t="str"/>
+      <x:c r="M188" s="9" t="str">
+        <x:v>The repair requires registration and may involve the high-voltage system; the source does not provide a verified battery capacity or current part number.</x:v>
+      </x:c>
+      <x:c r="N188" s="41" t="str">
+        <x:v>Add a battery product only after VIN/build-date capacity and terminal configuration are verified; do not infer one from AGM alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="950.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A189" s="40" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B189" s="9" t="str">
+        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
+      </x:c>
+      <x:c r="C189" s="9" t="str">
+        <x:v>2014-2020 | BMW | i8 | B38</x:v>
+      </x:c>
+      <x:c r="D189" s="9" t="str">
+        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
+      </x:c>
+      <x:c r="E189" s="9" t="str">
+        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
+      </x:c>
+      <x:c r="F189" s="9" t="str">
+        <x:v>Turbo oil-line/seal diagnosis; walnut blasting; conditional timing-chain kit; BMW-approved oil</x:v>
+      </x:c>
+      <x:c r="G189" s="9" t="str">
+        <x:v>MULTI-BRANCH SPECIALIST SERVICE / PARTS HELD</x:v>
+      </x:c>
+      <x:c r="H189" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I189" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J189" s="9" t="str">
+        <x:v>2014-2020 i8 B38 turbo, intake-valve and timing-chain diagnosis</x:v>
+      </x:c>
+      <x:c r="K189" s="9" t="str">
+        <x:v>BMW hybrid/engine service</x:v>
+      </x:c>
+      <x:c r="L189" s="9" t="str"/>
+      <x:c r="M189" s="9" t="str">
+        <x:v>Turbo, carbon and timing-chain paths are separate repairs and require diagnosis; the oil catalog is model-specific but viscosity/specification still varies by model year.</x:v>
+      </x:c>
+      <x:c r="N189" s="41" t="str">
+        <x:v>Split turbo, carbon buildup and timing-chain concerns before approving repair kits; do not call every rattle a timing-chain failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="132" hidden="0" customHeight="1">
+      <x:c r="A190" s="40" t="str"/>
+      <x:c r="B190" s="9" t="str"/>
+      <x:c r="C190" s="9" t="str"/>
+      <x:c r="D190" s="9" t="str"/>
+      <x:c r="E190" s="9" t="str"/>
+      <x:c r="F190" s="9" t="str"/>
+      <x:c r="G190" s="9" t="str"/>
+      <x:c r="H190" s="9" t="str">
+        <x:v>Genuine BMW i8 engine-oil catalog</x:v>
+      </x:c>
+      <x:c r="I190" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/accessories/bmw-i8-engine_oil.html</x:v>
+      </x:c>
+      <x:c r="J190" s="9" t="str">
+        <x:v>i8 oil catalog; confirm model year and owner-manual specification before ordering</x:v>
+      </x:c>
+      <x:c r="K190" s="9" t="str">
+        <x:v>preventive fluid</x:v>
+      </x:c>
+      <x:c r="L190" s="9" t="str"/>
+      <x:c r="M190" s="9" t="str"/>
+      <x:c r="N190" s="41" t="str"/>
+    </x:row>
+    <x:row r="191" ht="633.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A191" s="40" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B191" s="9" t="str">
+        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
+      </x:c>
+      <x:c r="C191" s="9" t="str">
+        <x:v>2014-2020 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D191" s="9" t="str">
+        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
+      </x:c>
+      <x:c r="E191" s="9" t="str">
+        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
+      </x:c>
+      <x:c r="F191" s="9" t="str">
+        <x:v>Door-release LED check; BDC fault scan; 12V Energy Diagnosis; key-fob batteries; conditional BMW latch reset</x:v>
+      </x:c>
+      <x:c r="G191" s="9" t="str">
+        <x:v>BULLETIN DIAGNOSIS/RESET SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H191" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I191" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J191" s="9" t="str">
+        <x:v>2014-2020 i8 BDC door-latch diagnosis and BMW reset procedure</x:v>
+      </x:c>
+      <x:c r="K191" s="9" t="str">
+        <x:v>ISTA/body-electronics service</x:v>
+      </x:c>
+      <x:c r="L191" s="9" t="str"/>
+      <x:c r="M191" s="9" t="str">
+        <x:v>The source explicitly says not to replace struts, hinges or actuators from this card.</x:v>
+      </x:c>
+      <x:c r="N191" s="41" t="str">
+        <x:v>Rename this to low-voltage door-latch failsafe diagnosis; the current actuator-style title is misleading.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="897.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A192" s="40" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B192" s="9" t="str">
+        <x:v>bmw-i8-charging-port-2014</x:v>
+      </x:c>
+      <x:c r="C192" s="9" t="str">
+        <x:v>2014-2020 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D192" s="9" t="str">
+        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
+      </x:c>
+      <x:c r="E192" s="9" t="str">
+        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
+      </x:c>
+      <x:c r="F192" s="9" t="str">
+        <x:v>Charge-flap/lock diagnosis; emergency release; white lithium grease; conditional actuator or complete wiring/port assembly</x:v>
+      </x:c>
+      <x:c r="G192" s="9" t="str">
+        <x:v>MAINTENANCE PRODUCT + DIAGNOSIS SERVICE / ACTUATOR HELD</x:v>
+      </x:c>
+      <x:c r="H192" s="9" t="str">
+        <x:v>CRC White Lithium Grease 05037</x:v>
+      </x:c>
+      <x:c r="I192" s="9" t="str">
+        <x:v>https://shop.advanceautoparts.com/p/crc-white-lithium-grease-10-wt-oz-05037/7070403-P</x:v>
+      </x:c>
+      <x:c r="J192" s="9" t="str">
+        <x:v>Metal charging-latch mechanism only; follow product and BMW cautions</x:v>
+      </x:c>
+      <x:c r="K192" s="9" t="str">
+        <x:v>named preventive lubricant</x:v>
+      </x:c>
+      <x:c r="L192" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/parts-list/2014-bmw-i8-coupe_i12/bodywork/charging_flap.html</x:v>
+      </x:c>
+      <x:c r="M192" s="9" t="str">
+        <x:v>The lubricant is a live named product suitable for automotive metal-to-metal use. The catalog page does not establish the source's claimed actuator or complete harness for every i8 year.</x:v>
+      </x:c>
+      <x:c r="N192" s="41" t="str">
+        <x:v>Do not link the flap ejector as an actuator or imply the catalog diagram is a complete charging-port assembly.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="132" hidden="0" customHeight="1">
+      <x:c r="A193" s="40" t="str"/>
+      <x:c r="B193" s="9" t="str"/>
+      <x:c r="C193" s="9" t="str"/>
+      <x:c r="D193" s="9" t="str"/>
+      <x:c r="E193" s="9" t="str"/>
+      <x:c r="F193" s="9" t="str"/>
+      <x:c r="G193" s="9" t="str"/>
+      <x:c r="H193" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I193" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J193" s="9" t="str">
+        <x:v>2014-2020 i8 recurring charge-flap, cable-lock or integrated port/harness fault</x:v>
+      </x:c>
+      <x:c r="K193" s="9" t="str">
+        <x:v>charging-system diagnosis/service</x:v>
+      </x:c>
+      <x:c r="L193" s="9" t="str"/>
+      <x:c r="M193" s="9" t="str"/>
+      <x:c r="N193" s="41" t="str"/>
+    </x:row>
+    <x:row r="194" ht="778.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A194" s="40" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B194" s="9" t="str">
+        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
+      </x:c>
+      <x:c r="C194" s="9" t="str">
+        <x:v>2014-2015 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D194" s="9" t="str">
+        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
+      </x:c>
+      <x:c r="E194" s="9" t="str">
+        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
+      </x:c>
+      <x:c r="F194" s="9" t="str">
+        <x:v>ISTA/D activation test for turbocharger coolant pump; conditional auxiliary-pump diagnosis</x:v>
+      </x:c>
+      <x:c r="G194" s="9" t="str">
+        <x:v>TEST-PLAN SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H194" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I194" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J194" s="9" t="str">
+        <x:v>2014-2015 i8 fault 20A503 ISTA pump-activation test</x:v>
+      </x:c>
+      <x:c r="K194" s="9" t="str">
+        <x:v>ISTA cooling-system diagnosis</x:v>
+      </x:c>
+      <x:c r="L194" s="9" t="str"/>
+      <x:c r="M194" s="9" t="str">
+        <x:v>No repair is required when activation succeeds and the fault does not return; exact turbo-pump fitment was not established.</x:v>
+      </x:c>
+      <x:c r="N194" s="41" t="str">
+        <x:v>Do not use a generic i8 water-pump listing for this auxiliary turbo-coolant circuit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="924" hidden="0" customHeight="1">
+      <x:c r="A195" s="40" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B195" s="9" t="str">
+        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
+      </x:c>
+      <x:c r="C195" s="9" t="str">
+        <x:v>2014-2020 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D195" s="9" t="str">
+        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
+      </x:c>
+      <x:c r="E195" s="9" t="str">
+        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
+      </x:c>
+      <x:c r="F195" s="9" t="str">
+        <x:v>Two door support struts; hinge/pin/bushing inspection; conditional latch diagnosis and alignment</x:v>
+      </x:c>
+      <x:c r="G195" s="9" t="str">
+        <x:v>EXACT PARTIAL PART APPROVAL + SERVICE</x:v>
+      </x:c>
+      <x:c r="H195" s="9" t="str">
+        <x:v>Genuine BMW door support strut 51227465481</x:v>
+      </x:c>
+      <x:c r="I195" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/parts/bmw-gas_pressurized_spring-51227465481.html</x:v>
+      </x:c>
+      <x:c r="J195" s="9" t="str">
+        <x:v>2014-2020 BMW i8 I12/I15; sold individually; required quantity two</x:v>
+      </x:c>
+      <x:c r="K195" s="9" t="str">
+        <x:v>door support strut</x:v>
+      </x:c>
+      <x:c r="L195" s="9" t="str">
+        <x:v>https://www.bmwpartsdeal.com/oem-bmw-i8-body_door_lift_support.html</x:v>
+      </x:c>
+      <x:c r="M195" s="9" t="str">
+        <x:v>The live OEM listing identifies i8 fitment, supersessions, stock status and required quantity two.</x:v>
+      </x:c>
+      <x:c r="N195" s="41" t="str">
+        <x:v>The source's latch part 51217229458 is not an i8 fitment and is rejected; diagnose the latch by VIN instead.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A196" s="40" t="str"/>
+      <x:c r="B196" s="9" t="str"/>
+      <x:c r="C196" s="9" t="str"/>
+      <x:c r="D196" s="9" t="str"/>
+      <x:c r="E196" s="9" t="str"/>
+      <x:c r="F196" s="9" t="str"/>
+      <x:c r="G196" s="9" t="str"/>
+      <x:c r="H196" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I196" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J196" s="9" t="str">
+        <x:v>i8 hinge, alignment or electronic latch diagnosis</x:v>
+      </x:c>
+      <x:c r="K196" s="9" t="str">
+        <x:v>body/door service</x:v>
+      </x:c>
+      <x:c r="L196" s="9" t="str"/>
+      <x:c r="M196" s="9" t="str"/>
+      <x:c r="N196" s="41" t="str"/>
+    </x:row>
+    <x:row r="197" ht="963.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A197" s="40" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B197" s="9" t="str">
+        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
+      </x:c>
+      <x:c r="C197" s="9" t="str">
+        <x:v>2014-2020 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D197" s="9" t="str">
+        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
+      </x:c>
+      <x:c r="E197" s="9" t="str">
+        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
+      </x:c>
+      <x:c r="F197" s="9" t="str">
+        <x:v>ISTA diagnosis; software update; grounds/connectors; 12V health; conditional VIN-specific harness</x:v>
+      </x:c>
+      <x:c r="G197" s="9" t="str">
+        <x:v>DIAGNOSIS/SOFTWARE SERVICE / NO GENERIC HARNESS</x:v>
+      </x:c>
+      <x:c r="H197" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I197" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J197" s="9" t="str">
+        <x:v>2014-2020 i8 electrical, software and sleep-current diagnosis</x:v>
+      </x:c>
+      <x:c r="K197" s="9" t="str">
+        <x:v>ISTA/electrical service</x:v>
+      </x:c>
+      <x:c r="L197" s="9" t="str"/>
+      <x:c r="M197" s="9" t="str">
+        <x:v>This is a symptom family, not one part failure; harness replacement is the last conditional branch and must be VIN-specific.</x:v>
+      </x:c>
+      <x:c r="N197" s="41" t="str">
+        <x:v>Do not monetize a generic battery, module or wiring harness before fault-led diagnosis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="646.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A198" s="40" t="n">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B198" s="9" t="str">
+        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
+      </x:c>
+      <x:c r="C198" s="9" t="str">
+        <x:v>2014-2014 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D198" s="9" t="str">
+        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
+      </x:c>
+      <x:c r="E198" s="9" t="str">
+        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
+      </x:c>
+      <x:c r="F198" s="9" t="str">
+        <x:v>VIN recall check; dealer inspection of ground-stud weld; conditional no-charge fuel-tank replacement</x:v>
+      </x:c>
+      <x:c r="G198" s="9" t="str">
+        <x:v>RECALL ROUTE / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H198" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I198" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J198" s="9" t="str">
+        <x:v>2014 i8; VIN required for campaign 14V-674</x:v>
+      </x:c>
+      <x:c r="K198" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L198" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="M198" s="9" t="str">
+        <x:v>The inspection and any tank replacement are recall work at no charge and are adjacent to high-voltage components.</x:v>
+      </x:c>
+      <x:c r="N198" s="41" t="str">
+        <x:v>No tank hardware or DIY inspection link belongs on this card.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="66" hidden="0" customHeight="1">
+      <x:c r="A199" s="40" t="str"/>
+      <x:c r="B199" s="9" t="str"/>
+      <x:c r="C199" s="9" t="str"/>
+      <x:c r="D199" s="9" t="str"/>
+      <x:c r="E199" s="9" t="str"/>
+      <x:c r="F199" s="9" t="str"/>
+      <x:c r="G199" s="9" t="str"/>
+      <x:c r="H199" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I199" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J199" s="9" t="str">
+        <x:v>2014 i8; VIN confirmation for 14V-674</x:v>
+      </x:c>
+      <x:c r="K199" s="9" t="str">
+        <x:v>independent recall lookup</x:v>
+      </x:c>
+      <x:c r="L199" s="9" t="str"/>
+      <x:c r="M199" s="9" t="str"/>
+      <x:c r="N199" s="41" t="str"/>
+    </x:row>
+    <x:row r="200" ht="726" hidden="0" customHeight="1">
+      <x:c r="A200" s="40" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B200" s="9" t="str">
+        <x:v>bmw-i8-hv-system-faults-2014</x:v>
+      </x:c>
+      <x:c r="C200" s="9" t="str">
+        <x:v>2014-2017 | BMW | i8</x:v>
+      </x:c>
+      <x:c r="D200" s="9" t="str">
+        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
+      </x:c>
+      <x:c r="E200" s="9" t="str">
+        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
+      </x:c>
+      <x:c r="F200" s="9" t="str">
+        <x:v>VIN coverage inquiry; ISTA diagnosis; conditional internal NTC repair kit by HV-certified technician</x:v>
+      </x:c>
+      <x:c r="G200" s="9" t="str">
+        <x:v>COVERAGE/HIGH-VOLTAGE SERVICE / NO RETAIL PART</x:v>
+      </x:c>
+      <x:c r="H200" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I200" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J200" s="9" t="str">
+        <x:v>2014-2017 i8 SIB 01 09 24 coverage and HV battery temperature-sensor diagnosis</x:v>
+      </x:c>
+      <x:c r="K200" s="9" t="str">
+        <x:v>HV-certified diagnosis/coverage service</x:v>
+      </x:c>
+      <x:c r="L200" s="9" t="str"/>
+      <x:c r="M200" s="9" t="str">
+        <x:v>The repair is internal to the high-voltage battery and only follows a confirmed cell-module temperature-sensor fault.</x:v>
+      </x:c>
+      <x:c r="N200" s="41" t="str">
+        <x:v>Do not link generic battery modules, temperature sensors or scan tools.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="963.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A201" s="40" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B201" s="9" t="str">
+        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
+      </x:c>
+      <x:c r="C201" s="9" t="str">
+        <x:v>2022-2025 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D201" s="9" t="str">
+        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
+      </x:c>
+      <x:c r="E201" s="9" t="str">
+        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
+      </x:c>
+      <x:c r="F201" s="9" t="str">
+        <x:v>Software update; sleep-current diagnosis; conditional 12V battery/CCU; battery registration</x:v>
+      </x:c>
+      <x:c r="G201" s="9" t="str">
+        <x:v>SOFTWARE/DIAGNOSIS SERVICE / BATTERY PART HELD</x:v>
+      </x:c>
+      <x:c r="H201" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I201" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J201" s="9" t="str">
+        <x:v>2022-2025 iX software, sleep-current, CCU and 12V battery-registration diagnosis</x:v>
+      </x:c>
+      <x:c r="K201" s="9" t="str">
+        <x:v>EV electrical service</x:v>
+      </x:c>
+      <x:c r="L201" s="9" t="str"/>
+      <x:c r="M201" s="9" t="str">
+        <x:v>The cited 01405A38CB9 number was not verified on a live fitment page and battery/CCU replacement is conditional.</x:v>
+      </x:c>
+      <x:c r="N201" s="41" t="str">
+        <x:v>Confirm VIN, battery capacity, terminal layout and current supersession before linking a battery or maintainer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="976.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A202" s="40" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B202" s="9" t="str">
+        <x:v>bmw-ix-air-suspension-2022</x:v>
+      </x:c>
+      <x:c r="C202" s="9" t="str">
+        <x:v>2022-2025 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D202" s="9" t="str">
+        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
+      </x:c>
+      <x:c r="E202" s="9" t="str">
+        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
+      </x:c>
+      <x:c r="F202" s="9" t="str">
+        <x:v>Leak/component diagnosis; conditional compressor, air spring or line; post-repair reset; warranty/goodwill check</x:v>
+      </x:c>
+      <x:c r="G202" s="9" t="str">
+        <x:v>DIAGNOSIS/WARRANTY SERVICE / PARTS HELD</x:v>
+      </x:c>
+      <x:c r="H202" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I202" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J202" s="9" t="str">
+        <x:v>2022-2025 iX xDrive50/M60 air-suspension diagnosis, warranty and calibration</x:v>
+      </x:c>
+      <x:c r="K202" s="9" t="str">
+        <x:v>suspension service</x:v>
+      </x:c>
+      <x:c r="L202" s="9" t="str"/>
+      <x:c r="M202" s="9" t="str">
+        <x:v>Compressor, corner spring and line are mutually conditional branches; no axle/corner or VIN-specific part is established.</x:v>
+      </x:c>
+      <x:c r="N202" s="41" t="str">
+        <x:v>Split by confirmed leaking component and corner before adding product links.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="422.3999938964844" hidden="0" customHeight="1">
+      <x:c r="A203" s="40" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B203" s="9" t="str">
+        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
+      </x:c>
+      <x:c r="C203" s="9" t="str">
+        <x:v>2022-2026 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D203" s="9" t="str">
+        <x:v>Air Suspension Calibration Errors</x:v>
+      </x:c>
+      <x:c r="E203" s="9" t="str">
+        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
+      </x:c>
+      <x:c r="F203" s="9" t="str">
+        <x:v>ISTA calibration routine; conditional ride-height sensor; post-wheel/tire calibration check</x:v>
+      </x:c>
+      <x:c r="G203" s="9" t="str">
+        <x:v>CALIBRATION SERVICE / SENSOR HELD</x:v>
+      </x:c>
+      <x:c r="H203" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I203" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J203" s="9" t="str">
+        <x:v>2022-2026 iX ISTA ride-height calibration and sensor diagnosis</x:v>
+      </x:c>
+      <x:c r="K203" s="9" t="str">
+        <x:v>suspension calibration service</x:v>
+      </x:c>
+      <x:c r="L203" s="9" t="str"/>
+      <x:c r="M203" s="9" t="str">
+        <x:v>Calibration is the first repair; sensor replacement requires a confirmed sensor fault and exact position.</x:v>
+      </x:c>
+      <x:c r="N203" s="41" t="str">
+        <x:v>Do not link a ride-height sensor without axle/side and VIN fitment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="897.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A204" s="40" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B204" s="9" t="str">
+        <x:v>bmw-ix-build-quality-2022</x:v>
+      </x:c>
+      <x:c r="C204" s="9" t="str">
+        <x:v>2022-2025 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D204" s="9" t="str">
+        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
+      </x:c>
+      <x:c r="E204" s="9" t="str">
+        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
+      </x:c>
+      <x:c r="F204" s="9" t="str">
+        <x:v>Warranty documentation; trim/rattle repair; panel adjustment; conditional goodwill or lemon-law review</x:v>
+      </x:c>
+      <x:c r="G204" s="9" t="str">
+        <x:v>WARRANTY/BODY SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H204" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I204" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J204" s="9" t="str">
+        <x:v>2022-2025 iX warranty inspection and body/trim adjustment</x:v>
+      </x:c>
+      <x:c r="K204" s="9" t="str">
+        <x:v>warranty service</x:v>
+      </x:c>
+      <x:c r="L204" s="9" t="str"/>
+      <x:c r="M204" s="9" t="str">
+        <x:v>The repair is inspection and warranty adjustment; generic clips or insulation cannot be approved without the affected location.</x:v>
+      </x:c>
+      <x:c r="N204" s="41" t="str">
+        <x:v>Do not link lemon-law services or trim parts from a broad build-quality complaint.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="844.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A205" s="40" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B205" s="9" t="str">
+        <x:v>bmw-ix-charging-failures-2022</x:v>
+      </x:c>
+      <x:c r="C205" s="9" t="str">
+        <x:v>2022-2024 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D205" s="9" t="str">
+        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
+      </x:c>
+      <x:c r="E205" s="9" t="str">
+        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
+      </x:c>
+      <x:c r="F205" s="9" t="str">
+        <x:v>Document failure; test another charger/outlet/adapter/station; inspect connection; ISTA charging test</x:v>
+      </x:c>
+      <x:c r="G205" s="9" t="str">
+        <x:v>INFRASTRUCTURE-FIRST DIAGNOSIS / NO PRODUCT</x:v>
+      </x:c>
+      <x:c r="H205" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I205" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J205" s="9" t="str">
+        <x:v>2022-2024 iX vehicle-side charging diagnosis after alternate-infrastructure test</x:v>
+      </x:c>
+      <x:c r="K205" s="9" t="str">
+        <x:v>EV charging diagnosis</x:v>
+      </x:c>
+      <x:c r="L205" s="9" t="str"/>
+      <x:c r="M205" s="9" t="str">
+        <x:v>The source explicitly says to test infrastructure before condemning the vehicle and reports no exact charging candidate.</x:v>
+      </x:c>
+      <x:c r="N205" s="41" t="str">
+        <x:v>Do not infer a cable, adapter, wallbox or onboard charger from a generic charging failure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="567.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A206" s="40" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B206" s="9" t="str">
+        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
+      </x:c>
+      <x:c r="C206" s="9" t="str">
+        <x:v>2022-2026 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D206" s="9" t="str">
+        <x:v>DC Fast Charging Speed Inconsistency</x:v>
+      </x:c>
+      <x:c r="E206" s="9" t="str">
+        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
+      </x:c>
+      <x:c r="F206" s="9" t="str">
+        <x:v>Navigation-triggered battery preconditioning; software update; alternate charging network; conditional onboard-charger diagnosis</x:v>
+      </x:c>
+      <x:c r="G206" s="9" t="str">
+        <x:v>USAGE/SOFTWARE/DIAGNOSIS SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H206" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I206" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J206" s="9" t="str">
+        <x:v>2022-2026 iX software and charging-hardware diagnosis after preconditioning/network comparison</x:v>
+      </x:c>
+      <x:c r="K206" s="9" t="str">
+        <x:v>EV charging service</x:v>
+      </x:c>
+      <x:c r="L206" s="9" t="str"/>
+      <x:c r="M206" s="9" t="str">
+        <x:v>Charge speed depends on temperature, battery state and infrastructure; hardware is only a conditional diagnosis branch.</x:v>
+      </x:c>
+      <x:c r="N206" s="41" t="str">
+        <x:v>Do not link an onboard charger or DC adapter from charging-speed inconsistency alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="607.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A207" s="40" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B207" s="9" t="str">
+        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
+      </x:c>
+      <x:c r="C207" s="9" t="str">
+        <x:v>2022-2024 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D207" s="9" t="str">
+        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
+      </x:c>
+      <x:c r="E207" s="9" t="str">
+        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+      </x:c>
+      <x:c r="F207" s="9" t="str">
+        <x:v>VIN recall check; free electric-drive-motor software update; post-remedy diagnosis if fault remains</x:v>
+      </x:c>
+      <x:c r="G207" s="9" t="str">
+        <x:v>RECALL/SOFTWARE ROUTE / NO PART</x:v>
+      </x:c>
+      <x:c r="H207" s="9" t="str">
+        <x:v>BMW recall lookup</x:v>
+      </x:c>
+      <x:c r="I207" s="9" t="str">
+        <x:v>https://www.bmwusa.com/safety-and-emission-recalls.html</x:v>
+      </x:c>
+      <x:c r="J207" s="9" t="str">
+        <x:v>2022-2024 iX; VIN required for campaign 25V-395</x:v>
+      </x:c>
+      <x:c r="K207" s="9" t="str">
+        <x:v>manufacturer recall lookup</x:v>
+      </x:c>
+      <x:c r="L207" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="M207" s="9" t="str">
+        <x:v>The stated remedy is a free software update, not a battery ECU, motor or battery purchase.</x:v>
+      </x:c>
+      <x:c r="N207" s="41" t="str">
+        <x:v>Keep all hardware links off this recall card.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="66" hidden="0" customHeight="1">
+      <x:c r="A208" s="40" t="str"/>
+      <x:c r="B208" s="9" t="str"/>
+      <x:c r="C208" s="9" t="str"/>
+      <x:c r="D208" s="9" t="str"/>
+      <x:c r="E208" s="9" t="str"/>
+      <x:c r="F208" s="9" t="str"/>
+      <x:c r="G208" s="9" t="str"/>
+      <x:c r="H208" s="9" t="str">
+        <x:v>NHTSA recall lookup</x:v>
+      </x:c>
+      <x:c r="I208" s="9" t="str">
+        <x:v>https://www.nhtsa.gov/recalls</x:v>
+      </x:c>
+      <x:c r="J208" s="9" t="str">
+        <x:v>2022-2024 iX; VIN confirmation for 25V-395</x:v>
+      </x:c>
+      <x:c r="K208" s="9" t="str">
+        <x:v>independent recall lookup</x:v>
+      </x:c>
+      <x:c r="L208" s="9" t="str"/>
+      <x:c r="M208" s="9" t="str"/>
+      <x:c r="N208" s="41" t="str"/>
+    </x:row>
+    <x:row r="209" ht="937.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A209" s="40" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B209" s="9" t="str">
+        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
+      </x:c>
+      <x:c r="C209" s="9" t="str">
+        <x:v>2022-2025 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D209" s="9" t="str">
+        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
+      </x:c>
+      <x:c r="E209" s="9" t="str">
+        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
+      </x:c>
+      <x:c r="F209" s="9" t="str">
+        <x:v>OTA update; soft reset; conditional dealer flash/factory reset; conditional MGU inspection</x:v>
+      </x:c>
+      <x:c r="G209" s="9" t="str">
+        <x:v>SOFTWARE/DIAGNOSIS SERVICE / MGU HELD</x:v>
+      </x:c>
+      <x:c r="H209" s="9" t="str">
+        <x:v>BMW Remote Software Upgrade</x:v>
+      </x:c>
+      <x:c r="I209" s="9" t="str">
+        <x:v>https://www.bmwusa.com/explore/connecteddrive/remote-software-upgrade.html</x:v>
+      </x:c>
+      <x:c r="J209" s="9" t="str">
+        <x:v>Eligible 2022-2025 iX; confirm offered update in vehicle/My BMW app</x:v>
+      </x:c>
+      <x:c r="K209" s="9" t="str">
+        <x:v>official software route</x:v>
+      </x:c>
+      <x:c r="L209" s="9" t="str"/>
+      <x:c r="M209" s="9" t="str">
+        <x:v>Reset and software are first-line; MGU replacement only follows persistent failure and dealer inspection.</x:v>
+      </x:c>
+      <x:c r="N209" s="41" t="str">
+        <x:v>Do not link a head unit before generation, VIN and diagnosis are known; remove unsupported version promises.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A210" s="40" t="str"/>
+      <x:c r="B210" s="9" t="str"/>
+      <x:c r="C210" s="9" t="str"/>
+      <x:c r="D210" s="9" t="str"/>
+      <x:c r="E210" s="9" t="str"/>
+      <x:c r="F210" s="9" t="str"/>
+      <x:c r="G210" s="9" t="str"/>
+      <x:c r="H210" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I210" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J210" s="9" t="str">
+        <x:v>Persistent iX reboot loop or head-unit hardware diagnosis</x:v>
+      </x:c>
+      <x:c r="K210" s="9" t="str">
+        <x:v>infotainment service</x:v>
+      </x:c>
+      <x:c r="L210" s="9" t="str"/>
+      <x:c r="M210" s="9" t="str"/>
+      <x:c r="N210" s="41" t="str"/>
+    </x:row>
+    <x:row r="211" ht="673.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A211" s="40" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B211" s="9" t="str">
+        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
+      </x:c>
+      <x:c r="C211" s="9" t="str">
+        <x:v>2022-2026 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D211" s="9" t="str">
+        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
+      </x:c>
+      <x:c r="E211" s="9" t="str">
+        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
+      </x:c>
+      <x:c r="F211" s="9" t="str">
+        <x:v>Sleep cycle; 70-second head-unit reset; directed 12V reset; ISTA display test; conditional whole-vehicle programming</x:v>
+      </x:c>
+      <x:c r="G211" s="9" t="str">
+        <x:v>BULLETIN TEST/PROGRAMMING SERVICE / NO DISPLAY</x:v>
+      </x:c>
+      <x:c r="H211" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I211" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J211" s="9" t="str">
+        <x:v>2022-2026 iX HU-H4/H5/H6 blackout test plan and programming</x:v>
+      </x:c>
+      <x:c r="K211" s="9" t="str">
+        <x:v>ISTA infotainment service</x:v>
+      </x:c>
+      <x:c r="L211" s="9" t="str"/>
+      <x:c r="M211" s="9" t="str">
+        <x:v>The source explicitly requires testing before display replacement and head-unit generation/I-level confirmation.</x:v>
+      </x:c>
+      <x:c r="N211" s="41" t="str">
+        <x:v>Do not link a display, head unit, battery or scanner from a black-screen symptom.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="818.4000244140625" hidden="0" customHeight="1">
+      <x:c r="A212" s="40" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B212" s="9" t="str">
+        <x:v>bmw-ix-phantom-braking-2022</x:v>
+      </x:c>
+      <x:c r="C212" s="9" t="str">
+        <x:v>2022-2024 | BMW | iX</x:v>
+      </x:c>
+      <x:c r="D212" s="9" t="str">
+        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
+      </x:c>
+      <x:c r="E212" s="9" t="str">
+        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
+      </x:c>
+      <x:c r="F212" s="9" t="str">
+        <x:v>ADCAM fault read; clean/inspect camera area and wipers; verify holder/windshield; conditional ISTA calibration</x:v>
+      </x:c>
+      <x:c r="G212" s="9" t="str">
+        <x:v>ADAS DIAGNOSIS/CALIBRATION SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H212" s="9" t="str">
+        <x:v>BMW dealer locator</x:v>
+      </x:c>
+      <x:c r="I212" s="9" t="str">
+        <x:v>https://www.bmwusa.com/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J212" s="9" t="str">
+        <x:v>2022-2024 iX ADCAM diagnosis and windshield-camera calibration</x:v>
+      </x:c>
+      <x:c r="K212" s="9" t="str">
+        <x:v>ADAS calibration service</x:v>
+      </x:c>
+      <x:c r="L212" s="9" t="str"/>
+      <x:c r="M212" s="9" t="str">
+        <x:v>BMW's path distinguishes installation/calibration faults from environmental operating limits; parts do not correct the latter.</x:v>
+      </x:c>
+      <x:c r="N212" s="41" t="str">
+        <x:v>Do not monetize camera, radar, wiper or scanner parts without a confirmed fault and position.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="541.2000122070312" hidden="0" customHeight="1">
+      <x:c r="A213" s="40" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B213" s="9" t="str">
+        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
+      </x:c>
+      <x:c r="C213" s="9" t="str">
+        <x:v>2022-2024 | BMW | iX3</x:v>
+      </x:c>
+      <x:c r="D213" s="9" t="str">
+        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
+      </x:c>
+      <x:c r="E213" s="9" t="str">
+        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
+      </x:c>
+      <x:c r="F213" s="9" t="str">
+        <x:v>OEM-spec AGM battery; battery tender; software/sleep-mode diagnosis</x:v>
+      </x:c>
+      <x:c r="G213" s="9" t="str">
+        <x:v>MARKET/VIN-SPECIFIC SERVICE / BATTERY HELD</x:v>
+      </x:c>
+      <x:c r="H213" s="9" t="str">
+        <x:v>BMW international dealer locator</x:v>
+      </x:c>
+      <x:c r="I213" s="9" t="str">
+        <x:v>https://www.bmw.com/en/footer/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J213" s="9" t="str">
+        <x:v>2022-2024 iX3 market/VIN-specific battery, software and sleep-current service</x:v>
+      </x:c>
+      <x:c r="K213" s="9" t="str">
+        <x:v>official service route</x:v>
+      </x:c>
+      <x:c r="L213" s="9" t="str"/>
+      <x:c r="M213" s="9" t="str">
+        <x:v>The iX3 was not a US retail model and the source gives no battery capacity, current part number or market specification.</x:v>
+      </x:c>
+      <x:c r="N213" s="41" t="str">
+        <x:v>A US product link would violate the requested market/fitment method; verify destination market and VIN first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="580.7999877929688" hidden="0" customHeight="1">
+      <x:c r="A214" s="40" t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B214" s="9" t="str">
+        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
+      </x:c>
+      <x:c r="C214" s="9" t="str">
+        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
+      </x:c>
+      <x:c r="D214" s="9" t="str">
+        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
+      </x:c>
+      <x:c r="E214" s="9" t="str">
+        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
+      </x:c>
+      <x:c r="F214" s="9" t="str">
+        <x:v>Key-fob/manual release; LIM scan; firmware updates; conditional charging-socket lock actuator or socket assembly</x:v>
+      </x:c>
+      <x:c r="G214" s="9" t="str">
+        <x:v>MARKET/VIN DIAGNOSIS SERVICE / PART HELD</x:v>
+      </x:c>
+      <x:c r="H214" s="9" t="str">
+        <x:v>BMW international dealer locator</x:v>
+      </x:c>
+      <x:c r="I214" s="9" t="str">
+        <x:v>https://www.bmw.com/en/footer/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J214" s="9" t="str">
+        <x:v>2021-2024 iX3 LIM diagnosis, firmware and charging-lock repair</x:v>
+      </x:c>
+      <x:c r="K214" s="9" t="str">
+        <x:v>official EV service route</x:v>
+      </x:c>
+      <x:c r="L214" s="9" t="str"/>
+      <x:c r="M214" s="9" t="str">
+        <x:v>Actuator versus socket assembly is conditional and market/VIN-specific; no exact US fitment product is supportable.</x:v>
+      </x:c>
+      <x:c r="N214" s="41" t="str">
+        <x:v>Do not reuse i3/i8 charge-flap or cable-lock parts for the iX3.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="660" hidden="0" customHeight="1">
+      <x:c r="A215" s="40" t="n">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B215" s="9" t="str">
+        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
+      </x:c>
+      <x:c r="C215" s="9" t="str">
+        <x:v>2021-2021 | BMW | iX3</x:v>
+      </x:c>
+      <x:c r="D215" s="9" t="str">
+        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
+      </x:c>
+      <x:c r="E215" s="9" t="str">
+        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
+      </x:c>
+      <x:c r="F215" s="9" t="str">
+        <x:v>VIN recall check; HV-qualified replacement of internal cell-supervision circuit</x:v>
+      </x:c>
+      <x:c r="G215" s="9" t="str">
+        <x:v>MARKET RECALL/HIGH-VOLTAGE SERVICE / NO PART</x:v>
+      </x:c>
+      <x:c r="H215" s="9" t="str">
+        <x:v>BMW international dealer locator</x:v>
+      </x:c>
+      <x:c r="I215" s="9" t="str">
+        <x:v>https://www.bmw.com/en/footer/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J215" s="9" t="str">
+        <x:v>2021 iX3 R/2023/133 or market-equivalent campaign; VIN required</x:v>
+      </x:c>
+      <x:c r="K215" s="9" t="str">
+        <x:v>official recall service route</x:v>
+      </x:c>
+      <x:c r="L215" s="9" t="str"/>
+      <x:c r="M215" s="9" t="str">
+        <x:v>This is a non-US campaign and an internal high-voltage-battery repair at no charge when covered.</x:v>
+      </x:c>
+      <x:c r="N215" s="41" t="str">
+        <x:v>Rename away from generic drivetrain harness and do not link a wiring harness.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="528" hidden="0" customHeight="1">
+      <x:c r="A216" s="40" t="n">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B216" s="9" t="str">
+        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
+      </x:c>
+      <x:c r="C216" s="9" t="str">
+        <x:v>2021-2021 | BMW | iX3</x:v>
+      </x:c>
+      <x:c r="D216" s="9" t="str">
+        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
+      </x:c>
+      <x:c r="E216" s="9" t="str">
+        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
+      </x:c>
+      <x:c r="F216" s="9" t="str">
+        <x:v>VIN recall check; free BMU reprogramming; fault-led diagnosis outside campaign</x:v>
+      </x:c>
+      <x:c r="G216" s="9" t="str">
+        <x:v>MARKET RECALL/SOFTWARE SERVICE / NO CHARGER</x:v>
+      </x:c>
+      <x:c r="H216" s="9" t="str">
+        <x:v>BMW international dealer locator</x:v>
+      </x:c>
+      <x:c r="I216" s="9" t="str">
+        <x:v>https://www.bmw.com/en/footer/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J216" s="9" t="str">
+        <x:v>2021 iX3 R/2021/361 or market-equivalent campaign; VIN required</x:v>
+      </x:c>
+      <x:c r="K216" s="9" t="str">
+        <x:v>official recall service route</x:v>
+      </x:c>
+      <x:c r="L216" s="9" t="str"/>
+      <x:c r="M216" s="9" t="str">
+        <x:v>The remedy is BMU reprogramming, not onboard-charger replacement, and the campaign is market-specific.</x:v>
+      </x:c>
+      <x:c r="N216" s="41" t="str">
+        <x:v>Correct the title to intermediate-circuit discharge recall and keep charger parts off the card.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="633.5999755859375" hidden="0" customHeight="1">
+      <x:c r="A217" s="42" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B217" s="43" t="str">
+        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
+      </x:c>
+      <x:c r="C217" s="43" t="str">
+        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
+      </x:c>
+      <x:c r="D217" s="43" t="str">
+        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
+      </x:c>
+      <x:c r="E217" s="43" t="str">
+        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
+      </x:c>
+      <x:c r="F217" s="43" t="str">
+        <x:v>Deliberate friction-brake use; annual caliper service; conditional rear discs/pads per axle; conditional side-specific caliper</x:v>
+      </x:c>
+      <x:c r="G217" s="43" t="str">
+        <x:v>MARKET/AXLE-SPECIFIC SERVICE / PARTS HELD</x:v>
+      </x:c>
+      <x:c r="H217" s="43" t="str">
+        <x:v>BMW international dealer locator</x:v>
+      </x:c>
+      <x:c r="I217" s="43" t="str">
+        <x:v>https://www.bmw.com/en/footer/dealer-locator.html</x:v>
+      </x:c>
+      <x:c r="J217" s="43" t="str">
+        <x:v>2021-2025 iX3 rear-brake inspection, caliper service and VIN-specific parts</x:v>
+      </x:c>
+      <x:c r="K217" s="43" t="str">
+        <x:v>official brake service route</x:v>
+      </x:c>
+      <x:c r="L217" s="43" t="str"/>
+      <x:c r="M217" s="43" t="str">
+        <x:v>The iX3 is market-specific and rear disc/pad/caliper numbers vary; the failed caliper side is not known.</x:v>
+      </x:c>
+      <x:c r="N217" s="44" t="str">
+        <x:v>Approve discs, pads and a left/right caliper only after destination market, VIN, axle dimensions and side are verified.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7478,21 +8680,21 @@
         <x:v>Queue status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="528" hidden="0" customHeight="1">
+    <x:row r="2" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-drain-2014</x:v>
+        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>2015-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D2" s="9" t="str">
-        <x:v>i8 CCM 415 Controller Sleep-Delay Diagnosis</x:v>
+        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
       </x:c>
       <x:c r="E2" s="9" t="str">
-        <x:v>Confirm CCM 415 and run BMW ISTA Energy Diagnosis. Only when the Controller is identified and the I-level is below I001-19-11-530 does the bulletin direct programming to that level or higher. If either condition is absent, continue standard diagnosis. Do not replace the Controller or buy a generic battery maintainer or scan tool as the repair.</x:v>
+        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
         <x:v>0</x:v>
@@ -7501,21 +8703,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="1042.800048828125" hidden="0" customHeight="1">
+    <x:row r="3" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A3" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>bmw-i8-12v-battery-hv-system-2014</x:v>
+        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2022-2024 | BMW | iX3</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>12V Battery &amp; High-Voltage System Interaction Issues</x:v>
+        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>For 12V battery replacement: Use BMW-spec AGM battery and ENSURE the small black safety wire under the red terminal cover is reconnected - this is the #1 cause of post-replacement "Drivetrain No Restart" errors. Register new battery via dealer ISTA tool. For HV battery discharge: If the HV battery fully depletes and 12V dies, the car may need dealer-level tools to restart the HV system. Preventive: Use a quality battery tender when vehicle will sit for more than 1 week. Check that all modules are sleeping properly (dealer can run a sleep current test). For alternator/charging system faults: Full electrical diagnosis required at BMW dealer or specialist.</x:v>
+        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
         <x:v>0</x:v>
@@ -7524,21 +8726,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="4" ht="712.7999877929688" hidden="0" customHeight="1">
       <x:c r="A4" s="40" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>bmw-i8-b38-turbo-timing-2014</x:v>
+        <x:v>bmw-m2-charge-pipe-2016</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8 | B38</x:v>
+        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D4" s="9" t="str">
-        <x:v>B38 Turbocharger &amp; Timing Chain Issues - High Mileage</x:v>
+        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
       </x:c>
       <x:c r="E4" s="9" t="str">
-        <x:v>Turbocharger: Inspect oil feed and return lines for leaks. Replace turbo seals and lines ($800-1,500) or complete turbo replacement ($2,000-4,000 for i8 due to mid-engine labor). Carbon buildup: Walnut blast intake valves every 40,000-60,000 miles ($400-800). Timing chain: If rattle is present, timing chain kit replacement needed ($2,000-4,000 including labor). Preventive: Use 5,000-7,000 mile oil change intervals with high-quality BMW LL-01 approved synthetic. Run the engine to full operating temperature on every drive (15+ minutes minimum) to burn off moisture. Check oil level monthly.</x:v>
+        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
         <x:v>0</x:v>
@@ -7547,21 +8749,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="5" ht="686.4000244140625" hidden="0" customHeight="1">
       <x:c r="A5" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>bmw-i8-butterfly-door-actuator-2014</x:v>
+        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2019-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
-        <x:v>i8 Low-Voltage Door-Latch Failsafe Diagnosis</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
       </x:c>
       <x:c r="E5" s="9" t="str">
-        <x:v>Check the door-release-switch LED and read Body Domain Controller faults. Run Energy Diagnosis for the 12-volt system and test the key-fob batteries. Repair the voltage cause first, then follow the BMW latch-reset procedure when the bulletin criteria are met. If BDC door-lock faults are present or the LED pattern does not match, continue ISTA diagnosis. Do not replace struts, hinges or actuators from this card.</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>0</x:v>
@@ -7570,21 +8772,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="6" ht="726" hidden="0" customHeight="1">
       <x:c r="A6" s="40" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>bmw-i8-charging-port-2014</x:v>
+        <x:v>bmw-m2-cooling-system-2016</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2020 | BMW | M2 | S55</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>Charging Port &amp; Charge Flap Actuator Failure</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>Charge flap actuator replacement is the most common fix. The actuator is accessed by removing interior trim panels. For stuck charging cable: Use the emergency manual release (located in trunk/frunk area - consult owner's manual for exact location). For sticky latch pin: Apply lithium grease aerosol every 3-4 months to the locking mechanism. For charge port failures: The charging port wiring harness is integrated and costs approximately $700+ for the complete assembly - it cannot be repaired as individual components. Dealer service typically required.</x:v>
+        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
         <x:v>0</x:v>
@@ -7593,21 +8795,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="7" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A7" s="40" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>bmw-i8-cooling-system-failure-2014</x:v>
+        <x:v>bmw-m2-dct-clutch-2016</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>2014-2015 | BMW | i8</x:v>
+        <x:v>2016-2020 | BMW | M2</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>Early i8 Turbo-Coolant-Pump Fault 20A503</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>Clear the fault and activate the turbocharger coolant pump with the specified ISTA/D test plan. If activation succeeds and 20A503 does not return, BMW says no repair is required at that time. If it returns during activation, continue ISTA diagnosis; the auxiliary coolant pump may then require replacement. ShowMeTheParts resolves exact 2015 i8 water-pump fitment and the 1.5-liter engine but returned no matching turbo-pump candidate, so no part link is approved.</x:v>
+        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:v>0</x:v>
@@ -7616,21 +8818,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="924" hidden="0" customHeight="1">
+    <x:row r="8" ht="462" hidden="0" customHeight="1">
       <x:c r="A8" s="40" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>bmw-i8-door-strut-hinge-2014</x:v>
+        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2021 | BMW | M2</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>Dihedral (Butterfly) Door Strut &amp; Hinge Wear</x:v>
+        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Gas strut replacement is the most common fix - both sides should be replaced together. BMW OEM struts are the only option (no aftermarket). Door hinge pin and bushing inspection should accompany strut replacement. Door latch actuator replacement for electronic lock failures. Hinge adjustment possible for minor alignment issues. DIY is possible with basic tools for strut replacement - YouTube videos from patsgarageonline provide step-by-step guidance. For door lock actuator: BMW part 51217229458 (2014-2020 models). Labor at dealer is 2-4 hours per side due to interior panel removal.</x:v>
+        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>0</x:v>
@@ -7639,21 +8841,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="9" ht="778.7999877929688" hidden="0" customHeight="1">
       <x:c r="A9" s="40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>bmw-i8-electrical-gremlins-2014</x:v>
+        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>2014-2020 | BMW | i8</x:v>
+        <x:v>2016-2018 | BMW | M2 | N55</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>Electrical System Gremlins - Wiring Harness &amp; Module Failures</x:v>
+        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
-        <x:v>Dealer diagnosis with ISTA is required for most electrical issues. Software updates often resolve phantom fault codes and infotainment glitches. For persistent issues, check all ground connections and connector integrity - heat cycling in the engine bay causes connector corrosion and pin-fit degradation. Complete wiring harness replacement ($3,000-8,000+) is the nuclear option for severe cases. Ensure 12V battery is in good health as many electrical gremlins are actually low-voltage symptoms. Maintain BMW extended warranty or purchase third-party warranty for electrical coverage.</x:v>
+        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>0</x:v>
@@ -7662,21 +8864,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="10" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A10" s="40" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>bmw-i8-fuel-tank-recall-2014</x:v>
+        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>2014-2014 | BMW | i8</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>2014 i8 Fuel-Tank Weld Recall 14V-674</x:v>
+        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>Check the VIN for an open 14V-674 campaign. If included, have an authorized BMW dealer inspect the fuel-tank ground-stud weld and replace the fuel tank if the BMW inspection fails or is questionable, at no charge. Do not attempt the high-voltage-adjacent inspection or order tank hardware from this card. If fuel odor or leakage appears, stop using the vehicle and contact BMW assistance.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
         <x:v>0</x:v>
@@ -7685,21 +8887,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="726" hidden="0" customHeight="1">
+    <x:row r="11" ht="858" hidden="0" customHeight="1">
       <x:c r="A11" s="40" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>bmw-i8-hv-system-faults-2014</x:v>
+        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>2014-2017 | BMW | i8</x:v>
+        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>2014-2017 i8 HV Battery Temperature-Sensor Path</x:v>
+        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>Check the VIN-specific Warranty Vehicle Inquiry for the SIB 01 09 24 coverage notice and perform BMW's corresponding ISTA diagnosis. If a cell-module temperature sensor is confirmed failed, a properly high-voltage-certified BMW technician follows the test plan to install the applicable internal NTC repair kit. No immediate repair is required without the documented problem, and independent battery disassembly or generic module replacement is unsafe.</x:v>
+        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
         <x:v>0</x:v>
@@ -7708,21 +8910,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="963.5999755859375" hidden="0" customHeight="1">
+    <x:row r="12" ht="462" hidden="0" customHeight="1">
       <x:c r="A12" s="40" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>bmw-ix-12v-battery-drain-2022</x:v>
+        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain - Sleep Mode &amp; Module Wake Issues</x:v>
+        <x:v>Valve Cover Gasket Oil Leak</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>First ensure latest software is installed - BMW has released OTA updates addressing sleep mode bugs. If 12V battery has been deeply discharged, it may be permanently damaged and need replacement. Use a BMW-approved battery tender for vehicles parked for extended periods. Dealer can perform a sleep current test to identify which module is preventing proper shutdown. If CCU (Central Charging Unit) is malfunctioning, it may need replacement under warranty. For battery replacement, part number for 60Ah AGM may include 01405A38CB9. Must be registered to IBS via BimmerLink or dealer ISTA.</x:v>
+        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
         <x:v>0</x:v>
@@ -7731,21 +8933,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="976.7999877929688" hidden="0" customHeight="1">
+    <x:row r="13" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A13" s="40" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-2022</x:v>
+        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>Air Suspension Compressor &amp; Air Spring Failures - xDrive50/M60</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
-        <x:v>Diagnosis required to identify failing component. Common repairs: Air compressor replacement ($600-1,200 parts + labor). Individual air spring replacement ($800-1,500 per corner). Air line repair/replacement ($100-500). Full system reset after any component replacement. Air springs typically last 50,000-70,000 miles; compressors can last 100,000+ miles if no leaks cause overwork. Check for air leaks using soapy water on air lines and spring connections. Dealer warranty covers air suspension for 4 years/50,000 miles. Some owners have had claims approved under BMW goodwill beyond warranty.</x:v>
+        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
         <x:v>0</x:v>
@@ -7754,21 +8956,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="422.3999938964844" hidden="0" customHeight="1">
+    <x:row r="14" ht="752.4000244140625" hidden="0" customHeight="1">
       <x:c r="A14" s="40" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>bmw-ix-air-suspension-calibration-2022</x:v>
+        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>Air Suspension Calibration Errors</x:v>
+        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>A suspension calibration reset via ISTA at the dealer resolves most cases. This involves driving the car through a specific calibration routine. If ride height sensors are faulty, they must be replaced. After any wheel or tire service, a calibration check is recommended.</x:v>
+        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
         <x:v>0</x:v>
@@ -7777,21 +8979,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="897.5999755859375" hidden="0" customHeight="1">
+    <x:row r="15" ht="528" hidden="0" customHeight="1">
       <x:c r="A15" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="9" t="str">
-        <x:v>bmw-ix-build-quality-2022</x:v>
+        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
-        <x:v>Panel Gaps &amp; Build Quality Issues</x:v>
+        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
       </x:c>
       <x:c r="E15" s="9" t="str">
-        <x:v>Most panel gap and trim issues can be addressed under BMW's 4 year/50,000 mile warranty at no cost. Document all issues with photos and bring to dealer service. For rattles, dealer can install additional insulation or tighten trim clips. For panel gap issues, body panel adjustment at dealer (covered under warranty). For persistent quality issues affecting enjoyment, document everything for potential BMW goodwill claim or lemon law consideration if the number of dealer visits is excessive. Some owners have negotiated buybacks on severely affected vehicles.</x:v>
+        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
         <x:v>0</x:v>
@@ -7800,21 +9002,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="844.7999877929688" hidden="0" customHeight="1">
+    <x:row r="16" ht="673.2000122070312" hidden="0" customHeight="1">
       <x:c r="A16" s="40" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>bmw-ix-charging-failures-2022</x:v>
+        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>iX Charger/Infrastructure-First Charging Diagnosis</x:v>
+        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>Document where and how the failure occurred, displayed messages, charger type, authentication method and vehicle charge settings. Test another charger, outlet, adapter or public station, inspect the plug/socket, and run BMW ISTA charging tests before condemning the vehicle. Only after the vehicle works at the dealer and fails at the customer location should infrastructure be treated as likely. Exact 2022 iX ShowMeTheParts data contains no charging category or candidate, so no retail link is approved.</x:v>
+        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
         <x:v>0</x:v>
@@ -7823,21 +9025,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="17" ht="831.5999755859375" hidden="0" customHeight="1">
       <x:c r="A17" s="40" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
-        <x:v>bmw-ix-dc-fast-charging-issues-2022</x:v>
+        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
-        <x:v>DC Fast Charging Speed Inconsistency</x:v>
+        <x:v>Rear Subframe Mounting Point Cracking</x:v>
       </x:c>
       <x:c r="E17" s="9" t="str">
-        <x:v>Pre-condition the battery using navigation to a DC fast charger (the car will warm the battery en route). Ensure the latest software is installed — BMW has released multiple charging optimization updates. Try different charging networks if one consistently underperforms. Some hardware issues require dealer diagnosis of the onboard charger.</x:v>
+        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
         <x:v>0</x:v>
@@ -7846,21 +9048,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="18" ht="594" hidden="0" customHeight="1">
       <x:c r="A18" s="40" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="9" t="str">
-        <x:v>bmw-ix-hv-battery-ecu-software-2022</x:v>
+        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>2022-2024 iX Propulsion-Loss Recall 25V-395</x:v>
+        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>Check the VIN for an open 25V-395 campaign. If included, install BMW's free electric-drive-motor software update through the authorized dealer or approved recall over-the-air process. Do not order a battery ECU, motor or battery part from this card. Capture any red warning and arrange diagnosis if the VIN is not included or the fault remains after the recall remedy.</x:v>
+        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
         <x:v>0</x:v>
@@ -7869,21 +9071,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="937.2000122070312" hidden="0" customHeight="1">
+    <x:row r="19" ht="950.4000244140625" hidden="0" customHeight="1">
       <x:c r="A19" s="40" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="9" t="str">
-        <x:v>bmw-ix-idrive8-crashes-2022</x:v>
+        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>2022-2025 | BMW | iX</x:v>
+        <x:v>2001-2006 | BMW | M3 | S54</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
-        <x:v>iDrive 8 System Crashes, Reboots &amp; Screen Blank</x:v>
+        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
       </x:c>
       <x:c r="E19" s="9" t="str">
-        <x:v>Install latest iDrive software via OTA update (Settings &gt; Software Update). Version .63+ resolved many stability issues. For immediate fix: Soft reset by holding volume/power button for 10+ seconds. For persistent crashes: Dealer can force-flash the head unit using ISTA. Some owners report improved stability by using wired CarPlay/Android Auto instead of wireless. Factory reset (Settings &gt; General &gt; Reset) can resolve persistent software corruption. If screen enters continuous reboot loop, dealer must perform head unit hardware inspection - may need MGU (main head unit) replacement.</x:v>
+        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
         <x:v>0</x:v>
@@ -7892,21 +9094,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="20" ht="396" hidden="0" customHeight="1">
       <x:c r="A20" s="40" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="9" t="str">
-        <x:v>bmw-ix-infotainment-screen-blackout-2022</x:v>
+        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>2022-2026 | BMW | iX</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>iX HU-H4/H5/H6 Multifunction Black-Screen Path</x:v>
+        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>Confirm the installed head-unit generation and current I-level. With the vehicle stationary, follow the bulletin sequence: full sleep cycle, a volume-control head-unit reset longer than 70 seconds, the BMW-directed 12-volt reset when necessary, then ISTA display test plan ABL-DIT-AT6581_CID3. Program the complete vehicle only through the BMW path and do not replace the display before the required tests.</x:v>
+        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
         <x:v>0</x:v>
@@ -7915,21 +9117,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="21" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A21" s="40" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="9" t="str">
-        <x:v>bmw-ix-phantom-braking-2022</x:v>
+        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX</x:v>
+        <x:v>2008-2013 | BMW | M3</x:v>
       </x:c>
       <x:c r="D21" s="9" t="str">
-        <x:v>iX ADCAM False-Warning and Sensor-Limit Diagnosis</x:v>
+        <x:v>EDC Electronic Damper Control System Failure</x:v>
       </x:c>
       <x:c r="E21" s="9" t="str">
-        <x:v>Read ADCAM fault memory with ISTA before replacing anything. Inspect and clean the windshield camera area, verify wiper performance and camera-holder installation, and document weather, light, traffic and road conditions. If fault 7E00A0 follows windshield replacement, start the required camera calibration in ISTA. If no fault or installation problem exists, explain the owner-manual operating limits; BMW states parts replacement does not correct environmental system limitations.</x:v>
+        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
       </x:c>
       <x:c r="F21" s="9" t="n">
         <x:v>0</x:v>
@@ -7938,21 +9140,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="541.2000122070312" hidden="0" customHeight="1">
+    <x:row r="22" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A22" s="40" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>bmw-ix3-12v-battery-drain-2022</x:v>
+        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>12V Auxiliary Battery Drain and Failure</x:v>
+        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>Replace the 12V AGM battery with an OEM-specification unit. If the vehicle will sit unused for more than 5-7 days, connect a BMW-approved battery tender. Disable unnecessary connected services in the iDrive settings to reduce parasitic drain. Have the dealer check for software updates that optimize sleep mode power management.</x:v>
+        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
       </x:c>
       <x:c r="F22" s="9" t="n">
         <x:v>0</x:v>
@@ -7961,21 +9163,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="580.7999877929688" hidden="0" customHeight="1">
+    <x:row r="23" ht="884.4000244140625" hidden="0" customHeight="1">
       <x:c r="A23" s="40" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>bmw-ix3-charging-socket-lock-fault-cable-will-not-unlock-charging-wo</x:v>
+        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
-        <x:v>2021-2024 | BMW | iX3 | eDrive40 | Gen5 eDrive40</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D23" s="9" t="str">
-        <x:v>Charging Socket Lock Fault — Cable Will Not Unlock / Charging Won't Initiate</x:v>
+        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
       </x:c>
       <x:c r="E23" s="9" t="str">
-        <x:v>Try locking then unlocking the car with the key fob to release the cable; if that fails, use the manual emergency-release strap in the boot to free the cable. For a recurring fault, the dealer scans the LIM, applies firmware updates to the charging electronics/BCM, and replaces the charging-socket lock actuator (or the socket assembly) if the actuator drive is defective.</x:v>
+        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
         <x:v>0</x:v>
@@ -7984,21 +9186,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="660" hidden="0" customHeight="1">
+    <x:row r="24" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A24" s="40" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>bmw-ix3-drivetrain-wire-harness-2022</x:v>
+        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>2021 iX3 Cell-Supervision Cable-Bridge Recall</x:v>
+        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2023/133 campaign or its market-equivalent code. If included, an authorized high-voltage-qualified BMW facility replaces the cell supervision circuit inside the high-voltage battery at no charge. Do not reseat battery connectors or order a generic wiring harness from this card. Exact ShowMeTheParts iX3 coverage contains no high-voltage component candidate.</x:v>
+        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
       </x:c>
       <x:c r="F24" s="9" t="n">
         <x:v>0</x:v>
@@ -8007,21 +9209,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="528" hidden="0" customHeight="1">
+    <x:row r="25" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A25" s="40" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="9" t="str">
-        <x:v>bmw-ix3-onboard-charger-manufacturing-fault-electric-shock-risk</x:v>
+        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
-        <x:v>2021-2021 | BMW | iX3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D25" s="9" t="str">
-        <x:v>2021 iX3 Intermediate-Circuit Discharge Recall</x:v>
+        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
       </x:c>
       <x:c r="E25" s="9" t="str">
-        <x:v>Check the VIN with BMW for an open R/2021/361 campaign or its market-equivalent code. If included, have an authorized BMW facility reprogram the Battery Management Unit at no charge. Do not replace an onboard charger or perform high-voltage measurements from this card; vehicles outside the recall require BMW fault-led diagnosis.</x:v>
+        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
       </x:c>
       <x:c r="F25" s="9" t="n">
         <x:v>0</x:v>
@@ -8030,21 +9232,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="26" ht="660" hidden="0" customHeight="1">
       <x:c r="A26" s="40" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>bmw-ix3-rear-brake-disc-corrosion-caliper-seizure-from-regen-under-u</x:v>
+        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>2021-2025 | BMW | iX3 | eDrive40, M Sport | Gen5 eDrive rear motor (RWD)</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>Rear Brake Disc Corrosion and Caliper Seizure from Regen Under-Use</x:v>
+        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>Periodically perform deliberate hard stops (BMW recommends this) or select a lower/adaptive regen mode so the friction brakes engage and clean themselves; in salty/humid regions service the rear calipers (clean and re-lube slide pins, free the pistons) at least annually. Once discs are pitted/scored or a caliper has seized, replace rear discs and pads per axle and rebuild or replace the affected caliper.</x:v>
+        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
         <x:v>0</x:v>
@@ -8053,21 +9255,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="27" ht="646.7999877929688" hidden="0" customHeight="1">
       <x:c r="A27" s="40" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="9" t="str">
-        <x:v>bmw-ix3-regen-braking-inconsistency-2022</x:v>
+        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D27" s="9" t="str">
-        <x:v>Regenerative Braking Lag and Inconsistency</x:v>
+        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
       </x:c>
       <x:c r="E27" s="9" t="str">
-        <x:v>Familiarize yourself with how regen braking changes based on battery state of charge and temperature. Use the paddle shifters to manually adjust regen levels. Check for BMW software updates that improve regen calibration. In cold weather or with a fully charged battery, rely more on the friction brakes and do not assume regen will provide full deceleration.</x:v>
+        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
         <x:v>0</x:v>
@@ -8076,21 +9278,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="554.4000244140625" hidden="0" customHeight="1">
+    <x:row r="28" ht="726" hidden="0" customHeight="1">
       <x:c r="A28" s="40" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="9" t="str">
-        <x:v>bmw-ix3-software-infotainment-glitches-2022</x:v>
+        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>2022-2024 | BMW | iX3</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>iDrive Infotainment Software Freezes and Reboots</x:v>
+        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>Perform a soft reset of the iDrive system by holding the volume/power knob for 30 seconds. Check for and install the latest BMW software update via OTA or at a dealer. If issues persist, the dealer may need to reflash the head unit firmware or replace the head unit hardware. Ensure the 12V battery is in good health, as low voltage can cause software instability.</x:v>
+        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
         <x:v>0</x:v>
@@ -8099,44 +9301,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="712.7999877929688" hidden="0" customHeight="1">
+    <x:row r="29" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A29" s="40" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="9" t="str">
-        <x:v>bmw-m2-charge-pipe-2016</x:v>
+        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
-        <x:v>2016-2016 | BMW | M2 | N55 3.0L turbo I6</x:v>
+        <x:v>2015-2018 | BMW | M3</x:v>
       </x:c>
       <x:c r="D29" s="9" t="str">
-        <x:v>Early F87 M2 Boost-Control Software Faults</x:v>
+        <x:v>Direct Fuel Injector Failure (S55)</x:v>
       </x:c>
       <x:c r="E29" s="9" t="str">
-        <x:v>Read the DME faults with the current BMW ISTA version and confirm the production date. If the vehicle meets SIB 12 17 16, program the vehicle to integration level F020-16-07-504 or higher. Do not replace a charge pipe from this card. ShowMeTheParts resolves exact 2016 M2 turbocharger and 3.0-liter fitment but returned no charge-pipe candidate; even a catalog match would not prove the BMW software fault or repair role.</x:v>
+        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="686.4000244140625" hidden="0" customHeight="1">
+    <x:row r="30" ht="633.5999755859375" hidden="0" customHeight="1">
       <x:c r="A30" s="40" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="9" t="str">
-        <x:v>bmw-m2-comp-s55-crank-hub-2019</x:v>
+        <x:v>bmw-m3-f80-water-pump-2015</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>2019-2020 | BMW | M2</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - M2 Competition</x:v>
+        <x:v>Electric Water Pump Failure (S55)</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway). Installation requires crankshaft pulley removal and careful torque specs. This is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Many M2 Competition owners perform this upgrade immediately after purchase.</x:v>
+        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
         <x:v>0</x:v>
@@ -8145,21 +9347,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="726" hidden="0" customHeight="1">
+    <x:row r="31" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A31" s="40" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="9" t="str">
-        <x:v>bmw-m2-cooling-system-2016</x:v>
+        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2 | S55</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D31" s="9" t="str">
-        <x:v>Cooling System Inadequacy Under Track Use - F87 M2/M2C</x:v>
+        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
       </x:c>
       <x:c r="E31" s="9" t="str">
-        <x:v>Install aftermarket cooling upgrades for track use: CSF radiator (higher core density), aftermarket oil cooler (Mishimoto, CSF), upgraded intercooler (Wagner, CSF), and coolant reroute kit. Remove kidney grille blockage for better airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Many serious track M2 owners install full cooling system upgrades ($2,500-4,000 total). For street use, stock cooling is adequate.</x:v>
+        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
         <x:v>0</x:v>
@@ -8168,21 +9370,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="32" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A32" s="40" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="9" t="str">
-        <x:v>bmw-m2-dct-clutch-2016</x:v>
+        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>2016-2020 | BMW | M2</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F87 M2/M2C</x:v>
+        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>Replace DCT clutch pack ($4,000-6,000 parts + labor). Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use. Transmission adaptation reset via BMW software often improves shift quality temporarily. Some performance shops offer upgraded clutch packs for track use. Extended warranty coverage highly recommended for DCT-equipped M2s.</x:v>
+        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
       </x:c>
       <x:c r="F32" s="9" t="n">
         <x:v>0</x:v>
@@ -8191,21 +9393,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="462" hidden="0" customHeight="1">
+    <x:row r="33" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A33" s="40" t="n">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>bmw-m2-dct-mechatronics-2016</x:v>
+        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
-        <x:v>2016-2021 | BMW | M2</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D33" s="9" t="str">
-        <x:v>DCT (M-DCT) Mechatronics Unit Failure</x:v>
+        <x:v>Coolant System Issues (S58)</x:v>
       </x:c>
       <x:c r="E33" s="9" t="str">
-        <x:v>Replace or rebuild the mechatronics unit. In some cases, a transmission adaptation reset via ISTA can resolve early-stage symptoms. Severe cases require full mechatronics replacement, which involves dropping the transmission. Fluid change every 30k miles helps extend life.</x:v>
+        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
         <x:v>0</x:v>
@@ -8214,21 +9416,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="778.7999877929688" hidden="0" customHeight="1">
+    <x:row r="34" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A34" s="40" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>bmw-m2-n55-rod-bearing-2016</x:v>
+        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>2016-2018 | BMW | M2 | N55</x:v>
+        <x:v>2021-2023 | BMW | M3</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>N55 Rod Bearing Premature Wear - F87 M2</x:v>
+        <x:v>iDrive 8 Software/Electronics Issues</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>Preventive rod bearing replacement recommended at 60,000 miles or before track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability. Oil analysis every 5,000 miles to monitor bearing wear (check for copper/lead particles). Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max for track cars. Some track-focused owners replace bearings every 50,000 miles preventively.</x:v>
+        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
         <x:v>0</x:v>
@@ -8237,21 +9439,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="35" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A35" s="40" t="n">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="9" t="str">
-        <x:v>bmw-m240i-b58-charge-pipe-2017</x:v>
+        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>2021-2021 | BMW | M3</x:v>
       </x:c>
       <x:c r="D35" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure Under Boost</x:v>
+        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
       </x:c>
       <x:c r="E35" s="9" t="str">
-        <x:v>Replace the factory plastic charge pipe with an upgraded aluminum aftermarket unit from manufacturers like Burger Motorsports, VRSF, or FTP Motorsport. If the failure occurs on a stock car, BMW may cover repair under warranty. After replacement, inspect the intercooler boots and all charge air connections for damage.</x:v>
+        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
         <x:v>0</x:v>
@@ -8260,21 +9462,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="858" hidden="0" customHeight="1">
+    <x:row r="36" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A36" s="40" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>bmw-m240i-b58-coolant-loss-2017</x:v>
+        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>2017-2020 | BMW | M240i | B58 3.0L turbo I6</x:v>
+        <x:v>2021-2023 | BMW | M3 | S58</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>F2x Cylinder-Head Coolant Vent-Line Service Action</x:v>
+        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>Check BMW AIR, DCSnet or the key-reader service menu for an open SIB 17 01 21 Service Action on the exact VIN. For an affected vehicle, replace the cylinder-head-to-expansion-tank coolant vent line following BMW Repair Instruction 17 12 012 and bleed/check the cooling system as required. Do not replace the expansion tank or electric water pump solely from this card. ShowMeTheParts resolves exact 2017 M240i fitment and lists hoses/pipes and water-pump categories, but catalog fitment does not establish this defect or repair.</x:v>
+        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
         <x:v>0</x:v>
@@ -8283,21 +9485,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="462" hidden="0" customHeight="1">
+    <x:row r="37" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A37" s="40" t="n">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="9" t="str">
-        <x:v>bmw-m240i-b58-valve-cover-gasket-2017</x:v>
+        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D37" s="9" t="str">
-        <x:v>Valve Cover Gasket Oil Leak</x:v>
+        <x:v>Power window regulator failure and interior trim rattles</x:v>
       </x:c>
       <x:c r="E37" s="9" t="str">
-        <x:v>Replace the valve cover gasket with an updated BMW part. If oil has entered spark plug tubes, replace spark plugs and inspect ignition coils. Clean all oil residue from the engine block. Some owners replace the entire valve cover assembly as the integrated PCV valve can also fail.</x:v>
+        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
         <x:v>0</x:v>
@@ -8306,21 +9508,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="38" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A38" s="40" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>bmw-m240i-b58-vanos-solenoid-2017</x:v>
+        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>2017-2024 | BMW | M240i | B58 3.0L Turbo I6</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>VANOS Solenoid O-Ring Failure</x:v>
+        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>Replace the VANOS solenoid o-rings with updated silicone o-rings. Clean the solenoid screens of any debris. If solenoids are contaminated, replace the entire solenoid unit. Use BMW-approved 0W-30 oil and maintain proper oil change intervals to reduce o-ring degradation.</x:v>
+        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
         <x:v>0</x:v>
@@ -8329,21 +9531,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="752.4000244140625" hidden="0" customHeight="1">
+    <x:row r="39" ht="343.20001220703125" hidden="0" customHeight="1">
       <x:c r="A39" s="40" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>bmw-m3-brittle-plastic-cooling-system-components-fail-catastrophica</x:v>
+        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>1995-1995 | BMW | M3 | S50 3.0L inline-six</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D39" s="9" t="str">
-        <x:v>1995 M3 Radiator-Cap Safety Recall 98V-178</x:v>
+        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
       </x:c>
       <x:c r="E39" s="9" t="str">
-        <x:v>Check the VIN for an open 98V-178 campaign. An authorized BMW dealer installs the redesigned radiator cap, which controls pressure and provides greater coolant overflow during overheating. Stop safely if an overheating warning appears and do not open a hot cooling system. ShowMeTheParts resolves exact 1995 M3 3.0-liter fitment and a radiator-cap candidate, but catalog fitment does not establish recall applicability or replace the free recall remedy.</x:v>
+        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
         <x:v>0</x:v>
@@ -8352,21 +9554,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="528" hidden="0" customHeight="1">
+    <x:row r="40" ht="488.3999938964844" hidden="0" customHeight="1">
       <x:c r="A40" s="40" t="n">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>bmw-m3-cs-s58-charge-pipe-2024</x:v>
+        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>2024-2024 | BMW | M3 CS | S58</x:v>
+        <x:v>2015-2018 | BMW | M3 | S55</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>Charge Pipe Cracking Under High Boost (S58 Engine)</x:v>
+        <x:v>S55 Crank Hub Slip/Failure</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>Replace the OEM plastic charge pipe with an aluminum or reinforced charge pipe from VRSF, Eventuri, or BMS. The aluminum pipe eliminates the cracking risk entirely and is a 30-minute DIY job. If the OEM pipe has cracked, also inspect the intercooler boots and couplers for damage from over-pressurization.</x:v>
+        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
         <x:v>0</x:v>
@@ -8375,21 +9577,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="673.2000122070312" hidden="0" customHeight="1">
+    <x:row r="41" ht="303.6000061035156" hidden="0" customHeight="1">
       <x:c r="A41" s="40" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>bmw-m3-e46-rod-bearing-2001</x:v>
+        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
       </x:c>
       <x:c r="D41" s="9" t="str">
-        <x:v>Rod Bearing Wear (S54 Engine)</x:v>
+        <x:v>S55/S58 Electric Water Pump Failure</x:v>
       </x:c>
       <x:c r="E41" s="9" t="str">
-        <x:v>Rod bearing replacement requires oil pan drop and is a 5-hour DIY or $1,500-$2,500 at a shop. King Racing CR6877XPC-STD (~$430-$450) with ceramic nano-composite coating are the top forum pick. ACL 6B2500H-STD (~$150-$200) is the budget option. BE-Clevite tri-metal bearings (~$350) are the premium choice. Send oil samples to Blackstone Labs every 5,000 miles to monitor bearing wear before symptoms appear.</x:v>
+        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
         <x:v>0</x:v>
@@ -8398,21 +9600,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="831.5999755859375" hidden="0" customHeight="1">
+    <x:row r="42" ht="462" hidden="0" customHeight="1">
       <x:c r="A42" s="40" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="9" t="str">
-        <x:v>bmw-m3-e46-subframe-crack-2001</x:v>
+        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>Rear Subframe Mounting Point Cracking</x:v>
+        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>Drop the rear subframe, inspect floor pan for cracks, repair any existing cracks, and weld in reinforcement plates. Turner Motorsport TDR4675412 (~$120-$150) or BimmerWorld expanded kit (~$125-$140) are the most popular kits. Through-bolting the front mounts and adding a rear X-brace provides the most comprehensive protection. This is a 15-20 hour job requiring welding equipment. Budget $1,500-$4,000 total at an experienced shop. Inspection is free - any shop can check for cracks with the car on a lift.</x:v>
+        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
         <x:v>0</x:v>
@@ -8421,21 +9623,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="594" hidden="0" customHeight="1">
+    <x:row r="43" ht="356.3999938964844" hidden="0" customHeight="1">
       <x:c r="A43" s="40" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="9" t="str">
-        <x:v>bmw-m3-e46-throttle-actuator-2001</x:v>
+        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D43" s="9" t="str">
-        <x:v>Electronic Throttle Actuator (EDR) Failure</x:v>
+        <x:v>S65 Throttle Body Actuator Failure</x:v>
       </x:c>
       <x:c r="E43" s="9" t="str">
-        <x:v>Since BMW discontinued the OEM part (13627840537), rebuilt units are the primary option. EBM Engineering (via Rogue Engineering) offers send-in rebuilds for $500-$700+core. ECU Testing (UK) offers motor rewinding + TPS repair for $300-$500. Installation is 2-3 hours ($300-$600 labor). Source a good used unit as a spare - availability is increasingly scarce.</x:v>
+        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
         <x:v>0</x:v>
@@ -8444,21 +9646,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="950.4000244140625" hidden="0" customHeight="1">
+    <x:row r="44" ht="250.8000030517578" hidden="0" customHeight="1">
       <x:c r="A44" s="40" t="n">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="9" t="str">
-        <x:v>bmw-m3-e46-vanos-failure-2001</x:v>
+        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>2001-2006 | BMW | M3 | S54</x:v>
+        <x:v>2008-2013 | BMW | M3 | S65</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>VANOS Unit Failure (S54 Double-VANOS)</x:v>
+        <x:v>VANOS Solenoid Wear and Failure</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>VANOS rebuild using Beisan Systems kits is the most cost-effective approach. For budget repair, start with seal kit (BS021, $60) and rattle elimination kit (BS022, $80). For comprehensive repair, add oil pump disk (BS025, $150+core) which saves ~$1,250 vs full replacement. Full rebuilt VANOS from Beisan (BS100, $1,990+core) or Mr Vanos (~$1,500 send-in service) for heavily worn units. Always replace VANOS gasket (BMW 11-36-7-831-938) during service. DIY is feasible with Beisan's detailed procedure guide (4-8 hours). Professional installation $500-$1,200.</x:v>
+        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
         <x:v>0</x:v>
@@ -8467,21 +9669,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="396" hidden="0" customHeight="1">
+    <x:row r="45" ht="607.2000122070312" hidden="0" customHeight="1">
       <x:c r="A45" s="40" t="n">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="9" t="str">
-        <x:v>bmw-m3-e92-differential-mount-subframe-stress</x:v>
+        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D45" s="9" t="str">
-        <x:v>E92 Rear Differential Mount and Subframe Stress</x:v>
+        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
       </x:c>
       <x:c r="E45" s="9" t="str">
-        <x:v>Upgrade to solid or polyurethane differential mounts. VAC Motorsports aluminum differential mount kit. Reinforce subframe with welded reinforcement plates if cracking has occurred. Regular inspection of differential mounting points.</x:v>
+        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals, often combined with an anti-rattle kit that addresses the cam-gear/shaft play. DIY on the seal kit is common; specialists also offer fully rebuilt exchange units.</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
         <x:v>0</x:v>
@@ -8490,21 +9692,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="46" ht="501.6000061035156" hidden="0" customHeight="1">
       <x:c r="A46" s="40" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="9" t="str">
-        <x:v>bmw-m3-e92-edc-damper-failure</x:v>
+        <x:v>bmw-m3-worn-rear-trailing-arm-bushings-suspension-mounts</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3</x:v>
+        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>EDC Electronic Damper Control System Failure</x:v>
+        <x:v>Worn rear trailing arm bushings (RTAB) and suspension mounts</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>Replace failed EDC dampers with OEM units (approximately $2,400 for all four). Bilstein B6 DampTronic replacement dampers (approximately $1,700 for all four). EDC delete kit with conventional performance coilovers. Replace EDC control module if module is the issue.</x:v>
+        <x:v>Replace the RTABs with genuine BMW rubber bushings or upgraded poly/spherical bushings; many owners add RTAB limiter kits to reduce deflection. Inspect and renew rear shock mounts and engine/transmission mounts at the same time. The RTAB job is a common DIY that can be done with the trailing arms on the car.</x:v>
       </x:c>
       <x:c r="F46" s="9" t="n">
         <x:v>0</x:v>
@@ -8513,21 +9715,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="765.5999755859375" hidden="0" customHeight="1">
+    <x:row r="47" ht="435.6000061035156" hidden="0" customHeight="1">
       <x:c r="A47" s="40" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="9" t="str">
-        <x:v>bmw-m3-e9x-idle-control-2008</x:v>
+        <x:v>bmw-m340i-12v-battery-drain-failure-battery-registration-issues</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
-        <x:v>2013-2013 | BMW | M3 | S65 4.0L V8</x:v>
+        <x:v>2019-2024 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D47" s="9" t="str">
-        <x:v>2013 S65 Idle-Control-Device Warranty Extension</x:v>
+        <x:v>12V Battery Drain and Failure / Battery Registration Issues</x:v>
       </x:c>
       <x:c r="E47" s="9" t="str">
-        <x:v>Confirm the exact model, production date and VIN-specific warranty comment and repair history before diagnosis. For a confirmed eligible failure, an authorized BMW center performs the BMW test module and replaces the idle control device when required. Do not infer coverage from rough idle alone. ShowMeTheParts resolves exact 2013 M3 4.0-liter fuel-injection fitment but returned no idle-control-valve candidate; catalog output would not establish failure or coverage.</x:v>
+        <x:v>Test and replace the AGM battery with the correct OEM-spec unit, then register the new battery with BimmerLink/ISTA so the charging strategy adapts. Diagnose parasitic drain and a faulty IBS cable/sensor if discharge persists. Drive long enough to fully recharge between trips.</x:v>
       </x:c>
       <x:c r="F47" s="9" t="n">
         <x:v>0</x:v>
@@ -8536,21 +9738,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="884.4000244140625" hidden="0" customHeight="1">
+    <x:row r="48" ht="528" hidden="0" customHeight="1">
       <x:c r="A48" s="40" t="n">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="9" t="str">
-        <x:v>bmw-m3-e9x-rod-bearing-2008</x:v>
+        <x:v>bmw-m340i-b58-carbon-buildup-2020</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>Rod Bearing Failure (S65 V8) - CRITICAL</x:v>
+        <x:v>Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>MANDATORY preventative replacement before 60,000-70,000 miles. Lang Racing Development custom ACL set (~$300-$350) achieves ideal 0.0023-0.0025" clearance using mixed shells (STD rod side + .001" oversize cap side). BE Bearings SP1527HK-STD-S65 ($590) is the premium option with tri-metal coating. Always replace with ARP 201-6001 connecting rod bolts ($250-$300) - factory stretch bolts cannot be reused. Professional installation $2,500-$3,500 total (8-15 hours labor). Dealer quotes $5,000-$9,500.</x:v>
+        <x:v>Walnut blast the intake valves every 50,000-60,000 miles. This involves removing the intake manifold and blasting walnut shell media at the valve backs to remove carbon deposits. Some owners use catch cans to reduce oil vapor entering the intake. BMW's official position is that carbon buildup is normal for direct-injection engines.</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
         <x:v>0</x:v>
@@ -8559,21 +9761,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="699.5999755859375" hidden="0" customHeight="1">
+    <x:row r="49" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A49" s="40" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="9" t="str">
-        <x:v>bmw-m3-e9x-throttle-actuator-2008</x:v>
+        <x:v>bmw-m340i-b58-coolant-loss-2020</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D49" s="9" t="str">
-        <x:v>Throttle Actuator Gear Failure (S65 V8)</x:v>
+        <x:v>Coolant Loss from Expansion Tank and Water Pump</x:v>
       </x:c>
       <x:c r="E49" s="9" t="str">
-        <x:v>Beisan Systems BS101 gear set ($250 per actuator, need 2) is the most cost-effective solution. BS102 ($300) includes send-in rebuild with new gears. Electronics rebuild from bimmerthrottlerepair.com (~$70 each) is essential alongside gear replacement - the voltage regulator IC degrades chronically. Total DIY rebuild cost: $570-$650 for both actuators. Evolve Automotive uprated actuators ($1,200-$1,500/pair) are the premium fix-it-once solution.</x:v>
+        <x:v>Replace the coolant expansion tank at first sign of cracking. Proactively replace the electric water pump before 60,000 miles. Replace the coolant vent line per BMW TSB. Use only BMW-approved blue coolant. Monitor coolant level monthly and pressure test the cooling system at every major service.</x:v>
       </x:c>
       <x:c r="F49" s="9" t="n">
         <x:v>0</x:v>
@@ -8582,21 +9784,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="50" ht="475.20001220703125" hidden="0" customHeight="1">
       <x:c r="A50" s="40" t="n">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="9" t="str">
-        <x:v>bmw-m3-e9x-vanos-solenoid-2008</x:v>
+        <x:v>bmw-m340i-b58-hpfp-failure-2020</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>VANOS Solenoid Failure (S65 V8)</x:v>
+        <x:v>High-Pressure Fuel Pump (HPFP) Failure</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>Replace VANOS solenoids with OEM parts. Intake solenoid: BMW 11367843118 (~$80-$150). Exhaust solenoid: BMW 11367843117 (~$80-$150). Always replace both solenoids on a bank simultaneously. Very DIY-friendly - solenoids are mounted on the front of the cylinder head (1-2 hours labor). Try cleaning first and swapping side-to-side to isolate the faulty solenoid before buying parts.</x:v>
+        <x:v>Replace the high-pressure fuel pump with the latest revised BMW part number. Verify the low-pressure fuel pump is providing adequate feed pressure. Use top-tier fuel and avoid running the tank below 1/4 to reduce strain on the fuel system. If under warranty, BMW will cover HPFP replacement.</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
         <x:v>0</x:v>
@@ -8605,21 +9807,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="660" hidden="0" customHeight="1">
+    <x:row r="51" ht="554.4000244140625" hidden="0" customHeight="1">
       <x:c r="A51" s="40" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="9" t="str">
-        <x:v>bmw-m3-elevated-oil-consumption-via-crankcase-ventilation-rings</x:v>
+        <x:v>bmw-m340i-b58-oil-filter-disintegration-2020</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6, B58</x:v>
       </x:c>
       <x:c r="D51" s="9" t="str">
-        <x:v>Elevated oil consumption via crankcase ventilation (CCV) and rings</x:v>
+        <x:v>Oil Filter Disintegration in Housing</x:v>
       </x:c>
       <x:c r="E51" s="9" t="str">
-        <x:v>Replace the CCV/oil-separator valve and its hoses first, as it is a frequent and relatively inexpensive culprit (get the cold-weather CCV variant in cold climates). Use a BMW-approved thicker synthetic (5W-40 such as Mobil 1 European, Liqui-Moly, or Pentosin). Persistent high consumption after CCV service points to worn rings/valve seals requiring more involved engine work. Regular level checks are essential.</x:v>
+        <x:v>Use only genuine BMW or Mann-branded oil filters (Mann is the OEM supplier). Change oil and filter every 5,000-7,000 miles rather than BMW's recommended 10,000-mile interval. When removing the old filter, inspect it carefully for signs of deterioration. If filter fragments are found in the housing, flush the housing thoroughly before installing the new filter.</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
         <x:v>0</x:v>
@@ -8628,21 +9830,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="646.7999877929688" hidden="0" customHeight="1">
+    <x:row r="52" ht="514.7999877929688" hidden="0" customHeight="1">
       <x:c r="A52" s="40" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="9" t="str">
-        <x:v>bmw-m3-f80-charge-pipe-2015</x:v>
+        <x:v>bmw-m340i-b58-wastegate-rattle-2020</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2020-2024 | BMW | M340i | B58 3.0L Turbo I6</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>Plastic Charge Pipe Failure (S55)</x:v>
+        <x:v>Turbo Wastegate Rattle at Idle</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>Replace with aluminum charge pipes. VRSF 10801050 (~$200-$250) is the most popular option with CNC billet aluminum flanges and pre-tapped 1/8" NPT bungs. BMS/Burger Motorsports (~$200-$300) is the other top choice. FTP Motorsport (~$180-$250) is the budget option. All are direct bolt-on replacements. Very DIY-friendly (1 hour). This is considered essential maintenance for any tuned car.</x:v>
+        <x:v>Have the wastegate actuator inspected for excessive play. Minor rattle without fault codes can be monitored. If boost control faults develop, replace the turbocharger wastegate actuator. In severe cases, the entire turbocharger assembly may need replacement. BMW may cover under warranty if fault codes are present.</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
         <x:v>0</x:v>
@@ -8651,21 +9853,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="726" hidden="0" customHeight="1">
+    <x:row r="53" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A53" s="40" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="9" t="str">
-        <x:v>bmw-m3-f80-crank-hub-2015</x:v>
+        <x:v>bmw-m340i-loss-brake-assist-from-brake-vacuum-pump-damage</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2020-2020 | BMW | M340i | B58 3.0L turbo inline-six</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>Crank Hub Slip/Failure (S55) - CRITICAL</x:v>
+        <x:v>2020 M340i Brake-Assist Recall 21V-598</x:v>
       </x:c>
       <x:c r="E53" s="9" t="str">
-        <x:v>SSR Performance double-keyed 4-pin crank hub kit (SSR-CHB-S55, ~$949) is the industry standard fix. Requires drilling the crankshaft - MUST be performed by a qualified technician with BMW specialty tools. Installation $800-$1,200 at an independent shop. Studio RSR offers complete installed service starting at $1,750 (includes oil change + coolant flush). Total parts + labor: $1,750-$2,200. The F80 Bimmerpost 'Crank Hub Issue Master Thread' is essential reading.</x:v>
+        <x:v>Check the VIN for an open 21V-598 campaign. An authorized BMW dealer updates the engine-management software free of charge and replaces the combined oil/vacuum pump if diagnosis shows it was already damaged. Do not order generic brake-vacuum parts from this card.</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
         <x:v>0</x:v>
@@ -8674,44 +9876,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="620.4000244140625" hidden="0" customHeight="1">
+    <x:row r="54" ht="462" hidden="0" customHeight="1">
       <x:c r="A54" s="40" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B54" s="9" t="str">
-        <x:v>bmw-m3-f80-injector-failure-2015</x:v>
+        <x:v>bmw-m340i-seat-belt-warning-audio-failure</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3</x:v>
+        <x:v>2019-2022 | BMW | M340i</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>Direct Fuel Injector Failure (S55)</x:v>
+        <x:v>2019-2022 M340i Seat-Belt Warning Recall 23V-584</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>Replace failed injectors with OEM updated version (BMW 13538616079, ~$80-$120/each). For tuned cars making higher boost, 1200cc S63TU-spec Bosch injectors (13647599876 / BOS-0261500136, ~$150-$200/each) provide 33% more fuel flow. Injector coding/adaptation via BMW diagnostic software is required after replacement. Professional installation $400-$800 for complete set.</x:v>
+        <x:v>Check the VIN for an open 23V-584 campaign. An authorized BMW dealer installs updated Receiver Audio Module software free of charge; eligible vehicles may also receive the remedy by BMW Remote Software Upgrade. Always use the seat belt regardless of warning-chime behavior.</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G54" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="633.5999755859375" hidden="0" customHeight="1">
+    <x:row r="55" ht="448.79998779296875" hidden="0" customHeight="1">
       <x:c r="A55" s="40" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B55" s="9" t="str">
-        <x:v>bmw-m3-f80-water-pump-2015</x:v>
+        <x:v>bmw-m340i-valve-cover-oil-filter-housing-gasket-oil-leaks</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D55" s="9" t="str">
-        <x:v>Electric Water Pump Failure (S55)</x:v>
+        <x:v>Valve Cover and Oil Filter Housing Gasket Oil Leaks (B58)</x:v>
       </x:c>
       <x:c r="E55" s="9" t="str">
-        <x:v>Replace with OEM/Continental water pump (BMW 11517846361, ~$260-$280). Always replace the water pump belt (BMW 11287848606, ~$20-$30) and thermostat during service. Flush the cooling system. OEM/Continental strongly recommended over aftermarket. Preemptive replacement recommended around 60,000 miles. Professional installation $400-$800 labor.</x:v>
+        <x:v>Replace the valve cover gasket and/or oil filter housing gasket. Many shops also replace the valve cover itself if it has warped. Clean any oil from spark-plug wells and inspect coils. Typical independent-shop cost is roughly $400-$900 depending on which gasket(s) and labor access.</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
         <x:v>0</x:v>
@@ -8720,21 +9922,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="56" ht="409.20001220703125" hidden="0" customHeight="1">
       <x:c r="A56" s="40" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="9" t="str">
-        <x:v>bmw-m3-g80-adaptive-suspension-2021</x:v>
+        <x:v>bmw-m340i-vanos-solenoid-o-ring-failure</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>Adaptive M Suspension Electronic Damper Failure</x:v>
+        <x:v>VANOS Solenoid O-Ring Failure</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>Software update at dealer ($0 under warranty, $150-$200 out of warranty) resolves many cases. Hardware failures require individual damper replacement ($500-$800/corner) or full set ($2,000-$3,500). Most G80 M3s should still be under warranty. Check for BMW software campaigns addressing adaptive suspension calibration.</x:v>
+        <x:v>Diagnose with a scan tool (VANOS/camshaft position fault codes), then replace the affected intake/exhaust VANOS solenoid(s) and O-rings. Solenoids are relatively inexpensive parts; cost is mostly diagnosis and labor, typically a few hundred dollars.</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
         <x:v>0</x:v>
@@ -8748,16 +9950,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B57" s="9" t="str">
-        <x:v>bmw-m3-g80-charge-pipe-2021</x:v>
+        <x:v>bmw-m340i-zf-8hp-harsh-jerky-low-speed-shifting-mechatronic-faults</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2019-2025 | BMW | M340i | M340i, M340i xDrive | B58</x:v>
       </x:c>
       <x:c r="D57" s="9" t="str">
-        <x:v>Plastic Y-Shaped Charge Pipe Failure (S58)</x:v>
+        <x:v>ZF 8HP Harsh / Jerky Low-Speed Shifting and Mechatronic Faults</x:v>
       </x:c>
       <x:c r="E57" s="9" t="str">
-        <x:v>Replace with aluminum charge pipe. FTP Motorsport (~$200-$300) is the most popular value option with CNC flanges and 1/8" NPT bungs. do88 Performance (~$300-$400) is the premium choice with measured 960 CFM vs OEM 835 CFM. Bolt-on replacement, very DIY-friendly. Essential for Stage 2+ tuned cars.</x:v>
+        <x:v>Perform the ZF 8-speed fluid-and-filter (pan) service rather than treating it as lifetime-fill; this resolves many shift-quality complaints. Let the drivetrain warm before hard driving. For persistent erratic shifting or warning lights, scan the transmission and repair/replace the mechatronic unit (valve body) as needed.</x:v>
       </x:c>
       <x:c r="F57" s="9" t="n">
         <x:v>0</x:v>
@@ -8766,21 +9968,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="567.5999755859375" hidden="0" customHeight="1">
+    <x:row r="58" ht="594" hidden="0" customHeight="1">
       <x:c r="A58" s="40" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="9" t="str">
-        <x:v>bmw-m3-g80-cooling-system-2021</x:v>
+        <x:v>bmw-m3cs-idrive-software-2024</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>Coolant System Issues (S58)</x:v>
+        <x:v>iDrive 8 Software Glitches and Screen Blackouts</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
-        <x:v>Monitor coolant level monthly. Most coolant loss on new G80s is normal system settling. Inspect all hose connections and clamps at regular intervals. Electric water pump replacement recommended around 60,000 km (~37,000 miles) preventatively. Always use BMW-approved coolant. Professional water pump replacement ~$1,100-$1,600.</x:v>
+        <x:v>Check for and install the latest BMW iDrive 8 software updates, which can be delivered over-the-air or at a dealer. Perform a soft reset by holding the iDrive controller button for 30 seconds. If screen blackouts persist, the dealer may need to replace the head unit or update the gateway module firmware. Ensure the 12V battery is in good condition, as low voltage can trigger software instability.</x:v>
       </x:c>
       <x:c r="F58" s="9" t="n">
         <x:v>0</x:v>
@@ -8789,21 +9991,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="514.7999877929688" hidden="0" customHeight="1">
+    <x:row r="59" ht="567.5999755859375" hidden="0" customHeight="1">
       <x:c r="A59" s="40" t="n">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="9" t="str">
-        <x:v>bmw-m3-g80-idrive-electronics-2021</x:v>
+        <x:v>bmw-m3cs-s58-carbon-buildup-2024</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D59" s="9" t="str">
-        <x:v>iDrive 8 Software/Electronics Issues</x:v>
+        <x:v>S58 Intake Valve Carbon Buildup</x:v>
       </x:c>
       <x:c r="E59" s="9" t="str">
-        <x:v>Hard reboot by holding start/stop button 30 seconds with car off. Most issues resolved by BMW over-the-air updates. Dealer software reflash for persistent problems ($0 under warranty). Head unit replacement ($2,000-$4,000) only for confirmed hardware failures. Keep phone firmware updated - many connectivity issues are phone-side.</x:v>
+        <x:v>Schedule walnut blast cleaning of the intake valves at 40,000-50,000 mile intervals. Install an oil catch can to reduce oil vapor entering the intake system. Use high-quality synthetic oil meeting BMW LL-01 specification and change at 5,000-7,000 mile intervals. Allow the engine to fully warm up before high-boost driving to ensure proper oil vapor management.</x:v>
       </x:c>
       <x:c r="F59" s="9" t="n">
         <x:v>0</x:v>
@@ -8812,21 +10014,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="818.4000244140625" hidden="0" customHeight="1">
+    <x:row r="60" ht="620.4000244140625" hidden="0" customHeight="1">
       <x:c r="A60" s="40" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="9" t="str">
-        <x:v>bmw-m3-g80-integrated-brake-system-recall</x:v>
+        <x:v>bmw-m3cs-s58-charge-pipe-crack-2024</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>2021-2021 | BMW | M3</x:v>
+        <x:v>2024-2024 | BMW | M3 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>2021 G80 Integrated Brake System Recall 21V-062</x:v>
+        <x:v>S58 Plastic Charge Pipe Cracking Under Boost</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>Check the VIN for an open 21V-062 campaign. If open, an authorized BMW dealer replaces the integrated brake system free of charge and performs the required programming. A stiff pedal or brake warning during hard braking requires safely stopping and arranging assistance. Do not replace wheel-speed sensors from this card. ShowMeTheParts resolves exact 2021 M3 brake-hydraulics fitment but returned no brake-booster candidate; catalog output cannot establish recall applicability.</x:v>
+        <x:v>Replace the factory plastic charge pipe with an aluminum aftermarket unit from do88, FTP Motorsport, or VRSF. These direct-fit replacements handle higher temperatures and pressures without risk of cracking. If the car is under warranty and the failure occurs on stock tune, BMW should cover the repair. Inspect the charge pipe during every service and before track days.</x:v>
       </x:c>
       <x:c r="F60" s="9" t="n">
         <x:v>0</x:v>
@@ -8835,21 +10037,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="435.6000061035156" hidden="0" customHeight="1">
+    <x:row r="61" ht="396" hidden="0" customHeight="1">
       <x:c r="A61" s="40" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B61" s="9" t="str">
-        <x:v>bmw-m3-g80-s58-carbon-buildup</x:v>
+        <x:v>bmw-m4-charge-pipe-blowoff-2015</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
-        <x:v>2021-2023 | BMW | M3 | S58</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D61" s="9" t="str">
-        <x:v>G80 S58 Engine Carbon Buildup on Intake Valves</x:v>
+        <x:v>Plastic Charge Pipe Blow-Off Under Boost</x:v>
       </x:c>
       <x:c r="E61" s="9" t="str">
-        <x:v>Walnut shell blasting to clean intake valves (every 50,000-70,000 miles). Catch can installation to reduce oil vapor entering intake. Regular Italian tune-ups (sustained high RPM driving) may slow buildup. Chemical cleaning treatments (less effective than walnut blasting).</x:v>
+        <x:v>Replace with an aluminum or silicone charge pipe. This is considered a must-do upgrade for any F82 M4. Many aftermarket options are direct bolt-on replacements. The job takes about 1-2 hours and requires removing the intake duct to access the charge pipe.</x:v>
       </x:c>
       <x:c r="F61" s="9" t="n">
         <x:v>0</x:v>
@@ -8858,21 +10060,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="448.79998779296875" hidden="0" customHeight="1">
+    <x:row r="62" ht="699.5999755859375" hidden="0" customHeight="1">
       <x:c r="A62" s="40" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="9" t="str">
-        <x:v>bmw-m3-power-window-regulator-failure-interior-trim-rattles</x:v>
+        <x:v>bmw-m4-convertible-top-2015</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>Power window regulator failure and interior trim rattles</x:v>
+        <x:v>Convertible Top Hydraulic Pump Failure - F83 M4 Convertible</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>Replace the failed regulator (and motor if worn). Genuine BMW regulators are strongly preferred, as aftermarket units are widely reported to have excessive joint play and short life. Reseat or replace cracked door-panel clips and glovebox hardware to address the associated trim rattles.</x:v>
+        <x:v>Diagnose specific failure: hydraulic pump motor, lines, microswitches, or latch mechanisms. Pump motor replacement is most common ($1,500-2,500). Check hydraulic fluid level and refill if low. Regular top cycling (minimum once per month) prevents seal degradation. Store with top UP to reduce strain on hydraulic system. Rebuilt hydraulic pumps available at lower cost than new OEM. Complex repair requiring specialized BMW knowledge.</x:v>
       </x:c>
       <x:c r="F62" s="9" t="n">
         <x:v>0</x:v>
@@ -8881,21 +10083,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="739.2000122070312" hidden="0" customHeight="1">
+    <x:row r="63" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A63" s="40" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="9" t="str">
-        <x:v>bmw-m3-rear-subframe-mounting-points-rear-axle-carrier-panel-cracki</x:v>
+        <x:v>bmw-m4-cooling-track-2015</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
-        <x:v>1995-1999 | BMW | M3 | Coupe, Sedan, Convertible | S50B30US 3.0L inline-6, S52B32US 3.2L inline-6</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D63" s="9" t="str">
-        <x:v>Rear subframe mounting points / rear axle carrier panel (RACP) cracking</x:v>
+        <x:v>Cooling System Inadequacy Under Track Use - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E63" s="9" t="str">
-        <x:v>Inspect the subframe mounts and surrounding trunk floor for cracks (best done from above in the trunk after scraping away seam sealer over the welds). The accepted repair is to weld up existing cracks and install reinforcement plates at the subframe mounting points; BMW itself produced reinforcement stampings used in factory/dealer repairs, and multiple aftermarket RACP reinforcement kits exist. This is a body/welding job, not a bolt-on.</x:v>
+        <x:v>Install comprehensive cooling upgrades for track use: CSF or Mishimoto high-capacity radiator, aftermarket oil cooler, upgraded intercoolers (Wagner, CSF), and transmission cooler. Remove kidney grille blockage for improved airflow. Install oil temperature and pressure gauges to monitor. Limit track sessions to 15-20 minutes with cool-down laps. Total cooling system upgrade costs $3,000-5,000 but essential for serious track use. For street-only M4s, stock cooling is adequate.</x:v>
       </x:c>
       <x:c r="F63" s="9" t="n">
         <x:v>0</x:v>
@@ -8904,21 +10106,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="343.20001220703125" hidden="0" customHeight="1">
+    <x:row r="64" ht="462" hidden="0" customHeight="1">
       <x:c r="A64" s="40" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="9" t="str">
-        <x:v>bmw-m3-s55-charge-pipe-failure</x:v>
+        <x:v>bmw-m4-crank-hub-bolt-2015</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>S55 Plastic Charge Pipe Cracking</x:v>
+        <x:v>S55 Crank Hub Bolt Loosening</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
-        <x:v>Replace with aluminum aftermarket charge pipes (ARM Motorsports, FTP, AMS Performance, BMS). Silicone couplers at connection points for improved sealing. Regular visual inspection of charge pipes for cracks.</x:v>
+        <x:v>Replace with an upgraded aftermarket crank hub bolt (ARP or IND). The job requires removing the radiator fan, accessory belt, and harmonic balancer to access the bolt. Use proper torque specs for the upgraded bolt. This is a preventative maintenance item for any M4 owner.</x:v>
       </x:c>
       <x:c r="F64" s="9" t="n">
         <x:v>0</x:v>
@@ -8927,21 +10129,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="488.3999938964844" hidden="0" customHeight="1">
+    <x:row r="65" ht="739.2000122070312" hidden="0" customHeight="1">
       <x:c r="A65" s="40" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B65" s="9" t="str">
-        <x:v>bmw-m3-s55-crank-hub-slip</x:v>
+        <x:v>bmw-m4-dct-clutch-2015</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
-        <x:v>2015-2018 | BMW | M3 | S55</x:v>
+        <x:v>2015-2020 | BMW | M4</x:v>
       </x:c>
       <x:c r="D65" s="9" t="str">
-        <x:v>S55 Crank Hub Slip/Failure</x:v>
+        <x:v>DCT Dual-Clutch Transmission Shudder &amp; Clutch Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E65" s="9" t="str">
-        <x:v>Install crank bolt capture plate over existing crank bolt (4-5 hours labor) as preventative measure. Upgrade to keyed/pinned crank hub assembly (Studio RSR, BimmerWorld). Spline-lock crank hub kits provide mechanical lock rather than friction. Essential for any tuned S55 or vehicles used on track.</x:v>
+        <x:v>Replace DCT clutch pack when symptoms appear. BMW recommends replacing all clutches together. Change DCT fluid every 30,000 miles with BMW-approved fluid to extend clutch life. Avoid excessive launch control use (limit to special occasions). Transmission adaptation reset via BMW software may temporarily improve shift quality. Extended warranty highly recommended for DCT-equipped M4s. Labor-intensive repair requires transmission removal.</x:v>
       </x:c>
       <x:c r="F65" s="9" t="n">
         <x:v>0</x:v>
@@ -8950,21 +10152,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="303.6000061035156" hidden="0" customHeight="1">
+    <x:row r="66" ht="462" hidden="0" customHeight="1">
       <x:c r="A66" s="40" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B66" s="9" t="str">
-        <x:v>bmw-m3-s55-water-pump-electric-failure</x:v>
+        <x:v>bmw-m4-rear-subframe-crack-2015</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>2015-2023 | BMW | M3 | S55, S58</x:v>
+        <x:v>2015-2026 | BMW | M4</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>S55/S58 Electric Water Pump Failure</x:v>
+        <x:v>Rear Subframe Cracking From Track Use</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>Replace electric water pump. Replace thermostat at same time (recommended). Flush cooling system when replacing pump. Consider OEM replacement - aftermarket quality varies.</x:v>
+        <x:v>Inspect subframe mounting points and welds regularly if the car sees track use. Reinforce with aftermarket subframe reinforcement plates or weld-in gussets. Severely cracked subframes must be replaced entirely. Upgraded subframe bushings (solid or reinforced) help distribute loads more evenly.</x:v>
       </x:c>
       <x:c r="F66" s="9" t="n">
         <x:v>0</x:v>
@@ -8973,21 +10175,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="462" hidden="0" customHeight="1">
+    <x:row r="67" ht="805.2000122070312" hidden="0" customHeight="1">
       <x:c r="A67" s="40" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="9" t="str">
-        <x:v>bmw-m3-s65-rod-bearing-failure</x:v>
+        <x:v>bmw-m4-s55-crank-hub-2015</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D67" s="9" t="str">
-        <x:v>S65 V8 Rod Bearing Premature Failure</x:v>
+        <x:v>S55 Crank Hub Failure (CATASTROPHIC) - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E67" s="9" t="str">
-        <x:v>Preventative rod bearing replacement before 70,000 miles. Upgrade to BE Bearings, ACL Race, or Mahle performance bearings with increased clearances. Regular oil analysis to detect early bearing wear. Use BMW-approved 10W-60 oil with frequent oil changes (5,000-7,500 mile intervals).</x:v>
+        <x:v>MANDATORY preventive replacement with upgraded pinned or keyed crank hub. Pure Turbos, VTT, and S55 Crank Hub Fix all sell upgraded solutions with mechanical retention (pin or keyway) that eliminates the slipping issue permanently. Installation requires crankshaft pulley removal and precise torque specs. This upgrade is considered essential maintenance for any S55-powered car, especially if tuned or tracked. Cost is $1,200-2,500 installed vs. $20,000+ for engine replacement after failure.</x:v>
       </x:c>
       <x:c r="F67" s="9" t="n">
         <x:v>0</x:v>
@@ -8996,44 +10198,44 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="356.3999938964844" hidden="0" customHeight="1">
+    <x:row r="68" ht="765.5999755859375" hidden="0" customHeight="1">
       <x:c r="A68" s="40" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="9" t="str">
-        <x:v>bmw-m3-s65-throttle-actuator-failure</x:v>
+        <x:v>bmw-m4-s55-injector-2015</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>S65 Throttle Body Actuator Failure</x:v>
+        <x:v>S55 High-Pressure Fuel Injector Failure - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>Replace failed throttle actuator(s) with OEM or upgraded units. Upgrade to Evolve Automotive uprated throttle actuators for improved durability. ECU Testing offers actuator rebuilds as a cost-effective alternative.</x:v>
+        <x:v>Replace all 6 injectors together to prevent repeat repairs. Perform walnut blast carbon cleaning on intake valves while injectors are removed (labor overlap saves $400-600). Use Top Tier gasoline to minimize carbon buildup. Add fuel system cleaner (Liqui Moly Valve Clean) every 5,000 miles to reduce carbon deposits. BMW parts are expensive; some shops use OEM Bosch injectors at lower cost. Labor is 4-6 hours for injector replacement.</x:v>
       </x:c>
       <x:c r="F68" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G68" s="41" t="str">
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="250.8000030517578" hidden="0" customHeight="1">
+    <x:row r="69" ht="818.4000244140625" hidden="0" customHeight="1">
       <x:c r="A69" s="40" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="9" t="str">
-        <x:v>bmw-m3-s65-vanos-solenoid-failure</x:v>
+        <x:v>bmw-m4-s55-rod-bearing-2015</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
-        <x:v>2008-2013 | BMW | M3 | S65</x:v>
+        <x:v>2015-2020 | BMW | M4 | S55</x:v>
       </x:c>
       <x:c r="D69" s="9" t="str">
-        <x:v>VANOS Solenoid Wear and Failure</x:v>
+        <x:v>S55 Rod Bearing Premature Wear - F82/F83 M4</x:v>
       </x:c>
       <x:c r="E69" s="9" t="str">
-        <x:v>Replace VANOS solenoids (typically done as a set). Use high-quality BMW-approved oil to prevent contamination. Maintain regular oil change intervals (5,000-7,500 miles).</x:v>
+        <x:v>Preventive rod bearing replacement at 60,000-80,000 miles or before extensive track use. Upgraded aftermarket bearings (ACL Race, King Racing) provide larger clearances and better durability than OEM. Regular oil analysis (Blackstone Labs) every 5,000 miles to monitor bearing wear. Use high-quality 5W-40 oil (Liqui Moly, Motul) and change every 5,000 miles max. Track-focused M4s should replace bearings every 50,000 miles. Labor is 8-12 hours, so many owners do this during clutch replacement.</x:v>
       </x:c>
       <x:c r="F69" s="9" t="n">
         <x:v>0</x:v>
@@ -9042,21 +10244,21 @@
         <x:v>PENDING REPAIR-FIRST REVIEW</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="607.2000122070312" hidden="0" customHeight="1">
+    <x:row r="70" ht="660" hidden="0" customHeight="1">
       <x:c r="A70" s="40" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B70" s="9" t="str">
-        <x:v>bmw-m3-single-vanos-variable-timing-unit-rattle-seal-failure</x:v>
+        <x:v>bmw-m4cs-brake-wear-track-2024</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>1996-1999 | BMW | M3 | Coupe, Sedan, Convertible | S52B32US 3.2L inline-6</x:v>
+        <x:v>2024-2024 | BMW | M4 CS | S58 3.0L Twin-Turbo I6</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>Single-VANOS variable-timing unit rattle and seal failure (S52)</x:v>
+        <x:v>Rapid Brake Pad and Rotor Wear from Track Use</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>First step is fresh BMW-approved synthetic oil, which can quiet borderline cases. The accepted permanent fix is a VANOS seal rebuild using proven kits (Beisan Systems, Dr. VANOS) that replace the degraded piston seals,